--- a/filetiendo.xlsx
+++ b/filetiendo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\viettel 2026\thang 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A046EBC-6D3F-4051-909A-A6209A3F9D01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20E19459-72BE-4896-8094-D18A401BB59C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="808" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4556,41 +4556,17 @@
     <xf numFmtId="0" fontId="66" fillId="0" borderId="109" xfId="11" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="109" xfId="11" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="177" xfId="11" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="50" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="135" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="134" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="133" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="50" fillId="5" borderId="127" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="5" borderId="130" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="128" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="140" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="139" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="138" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="5" borderId="127" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="24" borderId="132" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4604,10 +4580,34 @@
     <xf numFmtId="0" fontId="17" fillId="5" borderId="129" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="135" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="134" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="133" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="16" borderId="136" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="2" borderId="137" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="140" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="139" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="138" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="67" fillId="18" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4679,16 +4679,16 @@
     <xf numFmtId="0" fontId="63" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="47" fillId="5" borderId="152" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="5" borderId="151" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="148" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="147" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="5" borderId="152" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="5" borderId="151" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="51" fillId="5" borderId="150" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4708,6 +4708,12 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="155" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="158" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="157" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="159" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4733,10 +4739,10 @@
     <xf numFmtId="0" fontId="55" fillId="0" borderId="164" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="158" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="69" fillId="29" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="157" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="69" fillId="29" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="45" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4761,12 +4767,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="168" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="69" fillId="29" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="29" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="12">
     <cellStyle name="Comma" xfId="8" builtinId="3"/>
@@ -5656,166 +5656,166 @@
       </c>
     </row>
     <row r="2" spans="1:675" ht="23.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="210" t="s">
+      <c r="A2" s="200" t="s">
         <v>34</v>
       </c>
       <c r="B2" s="86"/>
       <c r="C2" s="15"/>
-      <c r="D2" s="216" t="s">
+      <c r="D2" s="211" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="216"/>
-      <c r="F2" s="216"/>
-      <c r="G2" s="216"/>
-      <c r="H2" s="216"/>
-      <c r="I2" s="216"/>
-      <c r="J2" s="216"/>
-      <c r="K2" s="216"/>
-      <c r="L2" s="216"/>
-      <c r="M2" s="216"/>
-      <c r="N2" s="216"/>
-      <c r="O2" s="216"/>
-      <c r="P2" s="216"/>
-      <c r="Q2" s="216"/>
-      <c r="R2" s="216"/>
-      <c r="S2" s="216"/>
-      <c r="T2" s="214" t="s">
+      <c r="E2" s="211"/>
+      <c r="F2" s="211"/>
+      <c r="G2" s="211"/>
+      <c r="H2" s="211"/>
+      <c r="I2" s="211"/>
+      <c r="J2" s="211"/>
+      <c r="K2" s="211"/>
+      <c r="L2" s="211"/>
+      <c r="M2" s="211"/>
+      <c r="N2" s="211"/>
+      <c r="O2" s="211"/>
+      <c r="P2" s="211"/>
+      <c r="Q2" s="211"/>
+      <c r="R2" s="211"/>
+      <c r="S2" s="211"/>
+      <c r="T2" s="206" t="s">
         <v>36</v>
       </c>
-      <c r="U2" s="214"/>
-      <c r="V2" s="214"/>
-      <c r="W2" s="214"/>
-      <c r="X2" s="214"/>
-      <c r="Y2" s="214"/>
-      <c r="Z2" s="214"/>
-      <c r="AA2" s="214"/>
-      <c r="AB2" s="214"/>
-      <c r="AC2" s="214"/>
-      <c r="AD2" s="214"/>
-      <c r="AE2" s="214"/>
-      <c r="AF2" s="214"/>
-      <c r="AG2" s="214"/>
-      <c r="AH2" s="214"/>
-      <c r="AI2" s="214"/>
-      <c r="AJ2" s="213" t="s">
+      <c r="U2" s="206"/>
+      <c r="V2" s="206"/>
+      <c r="W2" s="206"/>
+      <c r="X2" s="206"/>
+      <c r="Y2" s="206"/>
+      <c r="Z2" s="206"/>
+      <c r="AA2" s="206"/>
+      <c r="AB2" s="206"/>
+      <c r="AC2" s="206"/>
+      <c r="AD2" s="206"/>
+      <c r="AE2" s="206"/>
+      <c r="AF2" s="206"/>
+      <c r="AG2" s="206"/>
+      <c r="AH2" s="206"/>
+      <c r="AI2" s="206"/>
+      <c r="AJ2" s="205" t="s">
         <v>37</v>
       </c>
-      <c r="AK2" s="213"/>
-      <c r="AL2" s="213"/>
-      <c r="AM2" s="213"/>
-      <c r="AN2" s="213"/>
-      <c r="AO2" s="213"/>
-      <c r="AP2" s="213"/>
-      <c r="AQ2" s="213"/>
-      <c r="AR2" s="213"/>
-      <c r="AS2" s="213"/>
-      <c r="AT2" s="213"/>
-      <c r="AU2" s="213"/>
-      <c r="AV2" s="212" t="s">
+      <c r="AK2" s="205"/>
+      <c r="AL2" s="205"/>
+      <c r="AM2" s="205"/>
+      <c r="AN2" s="205"/>
+      <c r="AO2" s="205"/>
+      <c r="AP2" s="205"/>
+      <c r="AQ2" s="205"/>
+      <c r="AR2" s="205"/>
+      <c r="AS2" s="205"/>
+      <c r="AT2" s="205"/>
+      <c r="AU2" s="205"/>
+      <c r="AV2" s="204" t="s">
         <v>38</v>
       </c>
-      <c r="AW2" s="212"/>
-      <c r="AX2" s="212"/>
-      <c r="AY2" s="212"/>
-      <c r="AZ2" s="212"/>
-      <c r="BA2" s="212"/>
-      <c r="BB2" s="212"/>
-      <c r="BC2" s="212"/>
-      <c r="BD2" s="212"/>
-      <c r="BE2" s="212"/>
-      <c r="BF2" s="212"/>
-      <c r="BG2" s="212"/>
+      <c r="AW2" s="204"/>
+      <c r="AX2" s="204"/>
+      <c r="AY2" s="204"/>
+      <c r="AZ2" s="204"/>
+      <c r="BA2" s="204"/>
+      <c r="BB2" s="204"/>
+      <c r="BC2" s="204"/>
+      <c r="BD2" s="204"/>
+      <c r="BE2" s="204"/>
+      <c r="BF2" s="204"/>
+      <c r="BG2" s="204"/>
     </row>
     <row r="3" spans="1:675" s="3" customFormat="1" ht="28.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="210"/>
-      <c r="B3" s="217" t="s">
+      <c r="A3" s="200"/>
+      <c r="B3" s="212" t="s">
         <v>39</v>
       </c>
       <c r="C3" s="87"/>
-      <c r="D3" s="204" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="205"/>
-      <c r="F3" s="205"/>
-      <c r="G3" s="205"/>
-      <c r="H3" s="204" t="s">
+      <c r="D3" s="202" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="203"/>
+      <c r="F3" s="203"/>
+      <c r="G3" s="203"/>
+      <c r="H3" s="202" t="s">
         <v>40</v>
       </c>
-      <c r="I3" s="205"/>
-      <c r="J3" s="205"/>
-      <c r="K3" s="205"/>
-      <c r="L3" s="204" t="s">
+      <c r="I3" s="203"/>
+      <c r="J3" s="203"/>
+      <c r="K3" s="203"/>
+      <c r="L3" s="202" t="s">
         <v>41</v>
       </c>
-      <c r="M3" s="205"/>
-      <c r="N3" s="205"/>
-      <c r="O3" s="205"/>
-      <c r="P3" s="207" t="s">
+      <c r="M3" s="203"/>
+      <c r="N3" s="203"/>
+      <c r="O3" s="203"/>
+      <c r="P3" s="215" t="s">
         <v>42</v>
       </c>
-      <c r="Q3" s="208"/>
-      <c r="R3" s="208"/>
-      <c r="S3" s="209"/>
-      <c r="T3" s="204" t="s">
+      <c r="Q3" s="216"/>
+      <c r="R3" s="216"/>
+      <c r="S3" s="217"/>
+      <c r="T3" s="202" t="s">
         <v>43</v>
       </c>
-      <c r="U3" s="205"/>
-      <c r="V3" s="205"/>
-      <c r="W3" s="205"/>
-      <c r="X3" s="204" t="s">
+      <c r="U3" s="203"/>
+      <c r="V3" s="203"/>
+      <c r="W3" s="203"/>
+      <c r="X3" s="202" t="s">
         <v>45</v>
       </c>
-      <c r="Y3" s="205"/>
-      <c r="Z3" s="205"/>
-      <c r="AA3" s="205"/>
-      <c r="AB3" s="204" t="s">
+      <c r="Y3" s="203"/>
+      <c r="Z3" s="203"/>
+      <c r="AA3" s="203"/>
+      <c r="AB3" s="202" t="s">
         <v>47</v>
       </c>
-      <c r="AC3" s="205"/>
-      <c r="AD3" s="205"/>
-      <c r="AE3" s="205"/>
-      <c r="AF3" s="204" t="s">
+      <c r="AC3" s="203"/>
+      <c r="AD3" s="203"/>
+      <c r="AE3" s="203"/>
+      <c r="AF3" s="202" t="s">
         <v>48</v>
       </c>
-      <c r="AG3" s="205"/>
-      <c r="AH3" s="205"/>
-      <c r="AI3" s="205"/>
-      <c r="AJ3" s="201" t="s">
+      <c r="AG3" s="203"/>
+      <c r="AH3" s="203"/>
+      <c r="AI3" s="203"/>
+      <c r="AJ3" s="208" t="s">
         <v>51</v>
       </c>
-      <c r="AK3" s="202"/>
-      <c r="AL3" s="202"/>
-      <c r="AM3" s="203"/>
-      <c r="AN3" s="201" t="s">
+      <c r="AK3" s="209"/>
+      <c r="AL3" s="209"/>
+      <c r="AM3" s="210"/>
+      <c r="AN3" s="208" t="s">
         <v>14</v>
       </c>
-      <c r="AO3" s="202"/>
-      <c r="AP3" s="202"/>
-      <c r="AQ3" s="203"/>
-      <c r="AR3" s="201" t="s">
+      <c r="AO3" s="209"/>
+      <c r="AP3" s="209"/>
+      <c r="AQ3" s="210"/>
+      <c r="AR3" s="208" t="s">
         <v>52</v>
       </c>
-      <c r="AS3" s="202"/>
-      <c r="AT3" s="202"/>
-      <c r="AU3" s="203"/>
-      <c r="AV3" s="205" t="s">
+      <c r="AS3" s="209"/>
+      <c r="AT3" s="209"/>
+      <c r="AU3" s="210"/>
+      <c r="AV3" s="203" t="s">
         <v>16</v>
       </c>
-      <c r="AW3" s="205"/>
-      <c r="AX3" s="205"/>
-      <c r="AY3" s="205"/>
-      <c r="AZ3" s="205" t="s">
+      <c r="AW3" s="203"/>
+      <c r="AX3" s="203"/>
+      <c r="AY3" s="203"/>
+      <c r="AZ3" s="203" t="s">
         <v>54</v>
       </c>
-      <c r="BA3" s="205"/>
-      <c r="BB3" s="205"/>
-      <c r="BC3" s="205"/>
-      <c r="BD3" s="204" t="s">
+      <c r="BA3" s="203"/>
+      <c r="BB3" s="203"/>
+      <c r="BC3" s="203"/>
+      <c r="BD3" s="202" t="s">
         <v>55</v>
       </c>
-      <c r="BE3" s="205"/>
-      <c r="BF3" s="215"/>
-      <c r="BG3" s="205"/>
+      <c r="BE3" s="203"/>
+      <c r="BF3" s="207"/>
+      <c r="BG3" s="203"/>
       <c r="BH3" s="2"/>
       <c r="BI3" s="2"/>
       <c r="BJ3" s="2"/>
@@ -6434,8 +6434,8 @@
       <c r="YY3" s="2"/>
     </row>
     <row r="4" spans="1:675" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="211"/>
-      <c r="B4" s="217"/>
+      <c r="A4" s="201"/>
+      <c r="B4" s="212"/>
       <c r="C4" s="88"/>
       <c r="D4" s="8" t="s">
         <v>2</v>
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AS5" s="129">
         <f>(VLOOKUP(B5,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.77680000000000005</v>
+        <v>0.78980000000000006</v>
       </c>
       <c r="AT5" s="14">
         <f t="shared" ref="AT5:AT18" si="20">IF(AS5&lt;94.5%,0,IF(AS5&lt;95.54%,50%,IF(AS5&lt;AR5,80%,100%+(30%*(AS5-AR5)/3.39%))))</f>
@@ -6788,7 +6788,7 @@
       </c>
       <c r="AU5" s="54">
         <f t="shared" ref="AU5:AU18" si="21">AR5-AS5</f>
-        <v>0.19319999999999993</v>
+        <v>0.18019999999999992</v>
       </c>
       <c r="AV5" s="57">
         <f>VLOOKUP(C5,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7013,7 +7013,7 @@
       </c>
       <c r="AS6" s="129">
         <f>(VLOOKUP(B6,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.65590000000000004</v>
+        <v>0.68900000000000006</v>
       </c>
       <c r="AT6" s="14">
         <f t="shared" si="20"/>
@@ -7021,7 +7021,7 @@
       </c>
       <c r="AU6" s="54">
         <f t="shared" si="21"/>
-        <v>0.31409999999999993</v>
+        <v>0.28099999999999992</v>
       </c>
       <c r="AV6" s="57">
         <f>VLOOKUP(C6,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7246,7 +7246,7 @@
       </c>
       <c r="AS7" s="129">
         <f>(VLOOKUP(B7,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.73170000000000002</v>
+        <v>0.75019999999999998</v>
       </c>
       <c r="AT7" s="14">
         <f t="shared" si="20"/>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="AU7" s="54">
         <f t="shared" si="21"/>
-        <v>0.23829999999999996</v>
+        <v>0.2198</v>
       </c>
       <c r="AV7" s="57">
         <f>VLOOKUP(C7,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7479,7 +7479,7 @@
       </c>
       <c r="AS8" s="129">
         <f>(VLOOKUP(B8,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.30780000000000002</v>
+        <v>0.31659999999999999</v>
       </c>
       <c r="AT8" s="14">
         <f t="shared" si="20"/>
@@ -7487,7 +7487,7 @@
       </c>
       <c r="AU8" s="54">
         <f t="shared" si="21"/>
-        <v>0.6621999999999999</v>
+        <v>0.65339999999999998</v>
       </c>
       <c r="AV8" s="57">
         <f>VLOOKUP(C8,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="AS9" s="129">
         <f>(VLOOKUP(B9,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.54569999999999996</v>
+        <v>0.56869999999999998</v>
       </c>
       <c r="AT9" s="14">
         <f t="shared" si="20"/>
@@ -7720,7 +7720,7 @@
       </c>
       <c r="AU9" s="54">
         <f t="shared" si="21"/>
-        <v>0.42430000000000001</v>
+        <v>0.40129999999999999</v>
       </c>
       <c r="AV9" s="57">
         <f>VLOOKUP(C9,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7945,7 +7945,7 @@
       </c>
       <c r="AS10" s="129">
         <f>(VLOOKUP(B10,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.51470000000000005</v>
+        <v>0.55700000000000005</v>
       </c>
       <c r="AT10" s="14">
         <f t="shared" si="20"/>
@@ -7953,7 +7953,7 @@
       </c>
       <c r="AU10" s="54">
         <f t="shared" si="21"/>
-        <v>0.45529999999999993</v>
+        <v>0.41299999999999992</v>
       </c>
       <c r="AV10" s="57">
         <f>VLOOKUP(C10,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="AS11" s="129">
         <f>(VLOOKUP(B11,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.623</v>
+        <v>0.6412000000000001</v>
       </c>
       <c r="AT11" s="14">
         <f t="shared" si="20"/>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="AU11" s="54">
         <f t="shared" si="21"/>
-        <v>0.34699999999999998</v>
+        <v>0.32879999999999987</v>
       </c>
       <c r="AV11" s="57">
         <f>VLOOKUP(C11,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8411,7 +8411,7 @@
       </c>
       <c r="AS12" s="129">
         <f>(VLOOKUP(B12,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.58150000000000002</v>
+        <v>0.58609999999999995</v>
       </c>
       <c r="AT12" s="14">
         <f t="shared" si="20"/>
@@ -8419,7 +8419,7 @@
       </c>
       <c r="AU12" s="54">
         <f t="shared" si="21"/>
-        <v>0.38849999999999996</v>
+        <v>0.38390000000000002</v>
       </c>
       <c r="AV12" s="57">
         <f>VLOOKUP(C12,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8644,7 +8644,7 @@
       </c>
       <c r="AS13" s="129">
         <f>(VLOOKUP(B13,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.74010000000000009</v>
+        <v>0.77280000000000004</v>
       </c>
       <c r="AT13" s="14">
         <f t="shared" si="20"/>
@@ -8652,7 +8652,7 @@
       </c>
       <c r="AU13" s="54">
         <f t="shared" si="21"/>
-        <v>0.22989999999999988</v>
+        <v>0.19719999999999993</v>
       </c>
       <c r="AV13" s="57">
         <f>VLOOKUP(C13,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8877,7 +8877,7 @@
       </c>
       <c r="AS14" s="129">
         <f>(VLOOKUP(B14,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.56110000000000004</v>
+        <v>0.5756</v>
       </c>
       <c r="AT14" s="14">
         <f t="shared" si="20"/>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="AU14" s="54">
         <f t="shared" si="21"/>
-        <v>0.40889999999999993</v>
+        <v>0.39439999999999997</v>
       </c>
       <c r="AV14" s="57">
         <f>VLOOKUP(C14,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="AS15" s="129">
         <f>(VLOOKUP(B15,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.62829999999999997</v>
+        <v>0.64300000000000002</v>
       </c>
       <c r="AT15" s="14">
         <f t="shared" si="20"/>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="AU15" s="54">
         <f t="shared" si="21"/>
-        <v>0.3417</v>
+        <v>0.32699999999999996</v>
       </c>
       <c r="AV15" s="57">
         <f>VLOOKUP(C15,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="AS16" s="129">
         <f>(VLOOKUP(B16,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.69769999999999999</v>
+        <v>0.71420000000000006</v>
       </c>
       <c r="AT16" s="14">
         <f t="shared" si="20"/>
@@ -9351,7 +9351,7 @@
       </c>
       <c r="AU16" s="54">
         <f t="shared" si="21"/>
-        <v>0.27229999999999999</v>
+        <v>0.25579999999999992</v>
       </c>
       <c r="AV16" s="57">
         <f>VLOOKUP(C16,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="AS17" s="129">
         <f>(VLOOKUP(B17,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.7409</v>
+        <v>0.75930000000000009</v>
       </c>
       <c r="AT17" s="14">
         <f t="shared" si="20"/>
@@ -9584,7 +9584,7 @@
       </c>
       <c r="AU17" s="54">
         <f t="shared" si="21"/>
-        <v>0.22909999999999997</v>
+        <v>0.21069999999999989</v>
       </c>
       <c r="AV17" s="57">
         <f>VLOOKUP(C17,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -9809,7 +9809,7 @@
       </c>
       <c r="AS18" s="129">
         <f>(VLOOKUP(B18,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.72129999999999994</v>
+        <v>0.73239999999999994</v>
       </c>
       <c r="AT18" s="14">
         <f t="shared" si="20"/>
@@ -9817,7 +9817,7 @@
       </c>
       <c r="AU18" s="54">
         <f t="shared" si="21"/>
-        <v>0.24870000000000003</v>
+        <v>0.23760000000000003</v>
       </c>
       <c r="AV18" s="57">
         <f>VLOOKUP(C18,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -9874,11 +9874,11 @@
       <c r="C19" s="15"/>
       <c r="D19" s="15"/>
       <c r="E19" s="16"/>
-      <c r="F19" s="200">
+      <c r="F19" s="213">
         <f ca="1">TODAY()</f>
         <v>46076</v>
       </c>
-      <c r="G19" s="200"/>
+      <c r="G19" s="213"/>
       <c r="H19" s="90"/>
       <c r="I19" s="91">
         <f ca="1">DAY(F19)</f>
@@ -9891,33 +9891,33 @@
         <f ca="1">I19/J19</f>
         <v>0.74193548387096775</v>
       </c>
-      <c r="L19" s="206" t="s">
+      <c r="L19" s="214" t="s">
         <v>124</v>
       </c>
-      <c r="M19" s="206"/>
-      <c r="N19" s="206"/>
-      <c r="O19" s="206"/>
-      <c r="P19" s="206"/>
-      <c r="Q19" s="206"/>
-      <c r="R19" s="206"/>
-      <c r="S19" s="206"/>
-      <c r="T19" s="206"/>
-      <c r="U19" s="206"/>
-      <c r="V19" s="206"/>
-      <c r="W19" s="206"/>
-      <c r="X19" s="206"/>
-      <c r="Y19" s="206"/>
-      <c r="Z19" s="206"/>
-      <c r="AA19" s="206"/>
-      <c r="AB19" s="206"/>
-      <c r="AC19" s="206"/>
-      <c r="AD19" s="206"/>
-      <c r="AE19" s="206"/>
-      <c r="AF19" s="206"/>
-      <c r="AG19" s="206"/>
-      <c r="AH19" s="206"/>
-      <c r="AI19" s="206"/>
-      <c r="AJ19" s="206"/>
+      <c r="M19" s="214"/>
+      <c r="N19" s="214"/>
+      <c r="O19" s="214"/>
+      <c r="P19" s="214"/>
+      <c r="Q19" s="214"/>
+      <c r="R19" s="214"/>
+      <c r="S19" s="214"/>
+      <c r="T19" s="214"/>
+      <c r="U19" s="214"/>
+      <c r="V19" s="214"/>
+      <c r="W19" s="214"/>
+      <c r="X19" s="214"/>
+      <c r="Y19" s="214"/>
+      <c r="Z19" s="214"/>
+      <c r="AA19" s="214"/>
+      <c r="AB19" s="214"/>
+      <c r="AC19" s="214"/>
+      <c r="AD19" s="214"/>
+      <c r="AE19" s="214"/>
+      <c r="AF19" s="214"/>
+      <c r="AG19" s="214"/>
+      <c r="AH19" s="214"/>
+      <c r="AI19" s="214"/>
+      <c r="AJ19" s="214"/>
       <c r="AK19" s="16"/>
       <c r="AL19" s="32"/>
       <c r="AM19" s="16"/>
@@ -10110,6 +10110,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="AN3:AQ3"/>
+    <mergeCell ref="AF3:AI3"/>
+    <mergeCell ref="L19:AJ19"/>
+    <mergeCell ref="P3:S3"/>
+    <mergeCell ref="T3:W3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="X3:AA3"/>
     <mergeCell ref="AV2:BG2"/>
@@ -10126,12 +10132,6 @@
     <mergeCell ref="D3:G3"/>
     <mergeCell ref="H3:K3"/>
     <mergeCell ref="L3:O3"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="AN3:AQ3"/>
-    <mergeCell ref="AF3:AI3"/>
-    <mergeCell ref="L19:AJ19"/>
-    <mergeCell ref="P3:S3"/>
-    <mergeCell ref="T3:W3"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="C3:C4">
@@ -11147,7 +11147,7 @@
       </c>
       <c r="D14" s="74">
         <f>VLOOKUP($B$2,'TH NV'!$A$5:$BG$18,N14,0)</f>
-        <v>0.77680000000000005</v>
+        <v>0.78980000000000006</v>
       </c>
       <c r="E14" s="49" t="e">
         <f>VLOOKUP($B$2,'TH NV'!$A$1:$BG$18,70,0)</f>
@@ -11170,7 +11170,7 @@
       </c>
       <c r="J14" s="65">
         <f t="shared" si="2"/>
-        <v>0.19319999999999993</v>
+        <v>0.18019999999999992</v>
       </c>
       <c r="K14" s="222"/>
       <c r="L14" s="114" t="s">
@@ -11351,42 +11351,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:59" s="1" customFormat="1" ht="24.75" x14ac:dyDescent="0.45">
-      <c r="D1" s="216" t="s">
+      <c r="D1" s="211" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="216"/>
-      <c r="F1" s="216"/>
-      <c r="G1" s="216"/>
-      <c r="H1" s="216"/>
-      <c r="I1" s="216"/>
-      <c r="J1" s="216"/>
-      <c r="K1" s="216"/>
-      <c r="L1" s="216"/>
-      <c r="M1" s="216"/>
-      <c r="N1" s="216"/>
-      <c r="O1" s="216"/>
-      <c r="P1" s="216"/>
-      <c r="Q1" s="216"/>
-      <c r="R1" s="216"/>
-      <c r="S1" s="216"/>
-      <c r="T1" s="214" t="s">
+      <c r="E1" s="211"/>
+      <c r="F1" s="211"/>
+      <c r="G1" s="211"/>
+      <c r="H1" s="211"/>
+      <c r="I1" s="211"/>
+      <c r="J1" s="211"/>
+      <c r="K1" s="211"/>
+      <c r="L1" s="211"/>
+      <c r="M1" s="211"/>
+      <c r="N1" s="211"/>
+      <c r="O1" s="211"/>
+      <c r="P1" s="211"/>
+      <c r="Q1" s="211"/>
+      <c r="R1" s="211"/>
+      <c r="S1" s="211"/>
+      <c r="T1" s="206" t="s">
         <v>36</v>
       </c>
-      <c r="U1" s="214"/>
-      <c r="V1" s="214"/>
-      <c r="W1" s="214"/>
-      <c r="X1" s="214"/>
-      <c r="Y1" s="214"/>
-      <c r="Z1" s="214"/>
-      <c r="AA1" s="214"/>
-      <c r="AB1" s="214"/>
-      <c r="AC1" s="214"/>
-      <c r="AD1" s="214"/>
-      <c r="AE1" s="214"/>
-      <c r="AF1" s="214"/>
-      <c r="AG1" s="214"/>
-      <c r="AH1" s="214"/>
-      <c r="AI1" s="214"/>
+      <c r="U1" s="206"/>
+      <c r="V1" s="206"/>
+      <c r="W1" s="206"/>
+      <c r="X1" s="206"/>
+      <c r="Y1" s="206"/>
+      <c r="Z1" s="206"/>
+      <c r="AA1" s="206"/>
+      <c r="AB1" s="206"/>
+      <c r="AC1" s="206"/>
+      <c r="AD1" s="206"/>
+      <c r="AE1" s="206"/>
+      <c r="AF1" s="206"/>
+      <c r="AG1" s="206"/>
+      <c r="AH1" s="206"/>
+      <c r="AI1" s="206"/>
       <c r="AJ1" s="234" t="s">
         <v>37</v>
       </c>
@@ -11419,90 +11419,90 @@
     <row r="2" spans="1:59" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="204" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="205"/>
-      <c r="F2" s="205"/>
-      <c r="G2" s="205"/>
-      <c r="H2" s="204" t="s">
+      <c r="D2" s="202" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="203"/>
+      <c r="F2" s="203"/>
+      <c r="G2" s="203"/>
+      <c r="H2" s="202" t="s">
         <v>40</v>
       </c>
-      <c r="I2" s="205"/>
-      <c r="J2" s="205"/>
-      <c r="K2" s="205"/>
-      <c r="L2" s="204" t="s">
+      <c r="I2" s="203"/>
+      <c r="J2" s="203"/>
+      <c r="K2" s="203"/>
+      <c r="L2" s="202" t="s">
         <v>41</v>
       </c>
-      <c r="M2" s="205"/>
-      <c r="N2" s="205"/>
-      <c r="O2" s="205"/>
-      <c r="P2" s="207" t="s">
+      <c r="M2" s="203"/>
+      <c r="N2" s="203"/>
+      <c r="O2" s="203"/>
+      <c r="P2" s="215" t="s">
         <v>42</v>
       </c>
-      <c r="Q2" s="208"/>
-      <c r="R2" s="208"/>
-      <c r="S2" s="209"/>
-      <c r="T2" s="204" t="s">
+      <c r="Q2" s="216"/>
+      <c r="R2" s="216"/>
+      <c r="S2" s="217"/>
+      <c r="T2" s="202" t="s">
         <v>43</v>
       </c>
-      <c r="U2" s="205"/>
-      <c r="V2" s="205"/>
-      <c r="W2" s="205"/>
-      <c r="X2" s="204" t="s">
+      <c r="U2" s="203"/>
+      <c r="V2" s="203"/>
+      <c r="W2" s="203"/>
+      <c r="X2" s="202" t="s">
         <v>45</v>
       </c>
-      <c r="Y2" s="205"/>
-      <c r="Z2" s="205"/>
-      <c r="AA2" s="205"/>
-      <c r="AB2" s="204" t="s">
+      <c r="Y2" s="203"/>
+      <c r="Z2" s="203"/>
+      <c r="AA2" s="203"/>
+      <c r="AB2" s="202" t="s">
         <v>47</v>
       </c>
-      <c r="AC2" s="205"/>
-      <c r="AD2" s="205"/>
-      <c r="AE2" s="205"/>
-      <c r="AF2" s="204" t="s">
+      <c r="AC2" s="203"/>
+      <c r="AD2" s="203"/>
+      <c r="AE2" s="203"/>
+      <c r="AF2" s="202" t="s">
         <v>48</v>
       </c>
-      <c r="AG2" s="205"/>
-      <c r="AH2" s="205"/>
-      <c r="AI2" s="205"/>
-      <c r="AJ2" s="201" t="s">
+      <c r="AG2" s="203"/>
+      <c r="AH2" s="203"/>
+      <c r="AI2" s="203"/>
+      <c r="AJ2" s="208" t="s">
         <v>51</v>
       </c>
-      <c r="AK2" s="202"/>
-      <c r="AL2" s="202"/>
-      <c r="AM2" s="203"/>
-      <c r="AN2" s="201" t="s">
+      <c r="AK2" s="209"/>
+      <c r="AL2" s="209"/>
+      <c r="AM2" s="210"/>
+      <c r="AN2" s="208" t="s">
         <v>14</v>
       </c>
-      <c r="AO2" s="202"/>
-      <c r="AP2" s="202"/>
-      <c r="AQ2" s="203"/>
-      <c r="AR2" s="201" t="s">
+      <c r="AO2" s="209"/>
+      <c r="AP2" s="209"/>
+      <c r="AQ2" s="210"/>
+      <c r="AR2" s="208" t="s">
         <v>52</v>
       </c>
-      <c r="AS2" s="202"/>
-      <c r="AT2" s="202"/>
-      <c r="AU2" s="203"/>
-      <c r="AV2" s="205" t="s">
+      <c r="AS2" s="209"/>
+      <c r="AT2" s="209"/>
+      <c r="AU2" s="210"/>
+      <c r="AV2" s="203" t="s">
         <v>16</v>
       </c>
-      <c r="AW2" s="205"/>
-      <c r="AX2" s="205"/>
-      <c r="AY2" s="205"/>
-      <c r="AZ2" s="205" t="s">
+      <c r="AW2" s="203"/>
+      <c r="AX2" s="203"/>
+      <c r="AY2" s="203"/>
+      <c r="AZ2" s="203" t="s">
         <v>54</v>
       </c>
-      <c r="BA2" s="205"/>
-      <c r="BB2" s="205"/>
-      <c r="BC2" s="205"/>
-      <c r="BD2" s="204" t="s">
+      <c r="BA2" s="203"/>
+      <c r="BB2" s="203"/>
+      <c r="BC2" s="203"/>
+      <c r="BD2" s="202" t="s">
         <v>55</v>
       </c>
-      <c r="BE2" s="205"/>
-      <c r="BF2" s="215"/>
-      <c r="BG2" s="205"/>
+      <c r="BE2" s="203"/>
+      <c r="BF2" s="207"/>
+      <c r="BG2" s="203"/>
     </row>
     <row r="3" spans="1:59" ht="15" x14ac:dyDescent="0.45">
       <c r="B3" s="8" t="s">
@@ -11855,7 +11855,7 @@
       </c>
       <c r="AS4" s="129">
         <f>(VLOOKUP(B4,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.77680000000000005</v>
+        <v>0.78980000000000006</v>
       </c>
       <c r="AT4" s="14">
         <f t="shared" ref="AT4" si="20">IF(AS4&lt;94.5%,0,IF(AS4&lt;95.54%,50%,IF(AS4&lt;AR4,80%,100%+(30%*(AS4-AR4)/3.39%))))</f>
@@ -11863,7 +11863,7 @@
       </c>
       <c r="AU4" s="54">
         <f t="shared" ref="AU4" si="21">AR4-AS4</f>
-        <v>0.19319999999999993</v>
+        <v>0.18019999999999992</v>
       </c>
       <c r="AV4" s="57">
         <f>VLOOKUP(A4,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -12089,7 +12089,7 @@
       </c>
       <c r="AS5" s="129">
         <f>(VLOOKUP(B5,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.623</v>
+        <v>0.6412000000000001</v>
       </c>
       <c r="AT5" s="14">
         <f t="shared" ref="AT5:AT16" si="48">IF(AS5&lt;94.5%,0,IF(AS5&lt;95.54%,50%,IF(AS5&lt;AR5,80%,100%+(30%*(AS5-AR5)/3.39%))))</f>
@@ -12097,7 +12097,7 @@
       </c>
       <c r="AU5" s="54">
         <f t="shared" ref="AU5:AU16" si="49">AR5-AS5</f>
-        <v>0.34699999999999998</v>
+        <v>0.32879999999999987</v>
       </c>
       <c r="AV5" s="57">
         <f>VLOOKUP(A5,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -12323,7 +12323,7 @@
       </c>
       <c r="AS6" s="129">
         <f>(VLOOKUP(B6,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.58150000000000002</v>
+        <v>0.58609999999999995</v>
       </c>
       <c r="AT6" s="14">
         <f t="shared" si="48"/>
@@ -12331,7 +12331,7 @@
       </c>
       <c r="AU6" s="54">
         <f t="shared" si="49"/>
-        <v>0.38849999999999996</v>
+        <v>0.38390000000000002</v>
       </c>
       <c r="AV6" s="57">
         <f>VLOOKUP(A6,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -12557,7 +12557,7 @@
       </c>
       <c r="AS7" s="129">
         <f>(VLOOKUP(B7,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.56110000000000004</v>
+        <v>0.5756</v>
       </c>
       <c r="AT7" s="14">
         <f t="shared" si="48"/>
@@ -12565,7 +12565,7 @@
       </c>
       <c r="AU7" s="54">
         <f t="shared" si="49"/>
-        <v>0.40889999999999993</v>
+        <v>0.39439999999999997</v>
       </c>
       <c r="AV7" s="57">
         <f>VLOOKUP(A7,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -12791,7 +12791,7 @@
       </c>
       <c r="AS8" s="129">
         <f>(VLOOKUP(B8,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.69769999999999999</v>
+        <v>0.71420000000000006</v>
       </c>
       <c r="AT8" s="14">
         <f t="shared" si="48"/>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="AU8" s="54">
         <f t="shared" si="49"/>
-        <v>0.27229999999999999</v>
+        <v>0.25579999999999992</v>
       </c>
       <c r="AV8" s="57">
         <f>VLOOKUP(A8,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -13086,7 +13086,7 @@
       </c>
       <c r="AS10" s="129">
         <f>(VLOOKUP(B10,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.65590000000000004</v>
+        <v>0.68900000000000006</v>
       </c>
       <c r="AT10" s="14">
         <f t="shared" si="48"/>
@@ -13094,7 +13094,7 @@
       </c>
       <c r="AU10" s="54">
         <f t="shared" si="49"/>
-        <v>0.31409999999999993</v>
+        <v>0.28099999999999992</v>
       </c>
       <c r="AV10" s="57">
         <f>VLOOKUP(A10,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -13320,7 +13320,7 @@
       </c>
       <c r="AS11" s="129">
         <f>(VLOOKUP(B11,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.73170000000000002</v>
+        <v>0.75019999999999998</v>
       </c>
       <c r="AT11" s="14">
         <f t="shared" si="48"/>
@@ -13328,7 +13328,7 @@
       </c>
       <c r="AU11" s="54">
         <f t="shared" si="49"/>
-        <v>0.23829999999999996</v>
+        <v>0.2198</v>
       </c>
       <c r="AV11" s="57">
         <f>VLOOKUP(A11,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -13554,7 +13554,7 @@
       </c>
       <c r="AS12" s="129">
         <f>(VLOOKUP(B12,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.30780000000000002</v>
+        <v>0.31659999999999999</v>
       </c>
       <c r="AT12" s="14">
         <f t="shared" si="48"/>
@@ -13562,7 +13562,7 @@
       </c>
       <c r="AU12" s="54">
         <f t="shared" si="49"/>
-        <v>0.6621999999999999</v>
+        <v>0.65339999999999998</v>
       </c>
       <c r="AV12" s="57">
         <f>VLOOKUP(A12,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -13788,7 +13788,7 @@
       </c>
       <c r="AS13" s="129">
         <f>(VLOOKUP(B13,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.51470000000000005</v>
+        <v>0.55700000000000005</v>
       </c>
       <c r="AT13" s="14">
         <f t="shared" si="48"/>
@@ -13796,7 +13796,7 @@
       </c>
       <c r="AU13" s="54">
         <f t="shared" si="49"/>
-        <v>0.45529999999999993</v>
+        <v>0.41299999999999992</v>
       </c>
       <c r="AV13" s="57">
         <f>VLOOKUP(A13,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -14022,7 +14022,7 @@
       </c>
       <c r="AS14" s="129">
         <f>(VLOOKUP(B14,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.74010000000000009</v>
+        <v>0.77280000000000004</v>
       </c>
       <c r="AT14" s="14">
         <f t="shared" si="48"/>
@@ -14030,7 +14030,7 @@
       </c>
       <c r="AU14" s="54">
         <f t="shared" si="49"/>
-        <v>0.22989999999999988</v>
+        <v>0.19719999999999993</v>
       </c>
       <c r="AV14" s="57">
         <f>VLOOKUP(A14,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -14256,7 +14256,7 @@
       </c>
       <c r="AS15" s="129">
         <f>(VLOOKUP(B15,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.62829999999999997</v>
+        <v>0.64300000000000002</v>
       </c>
       <c r="AT15" s="14">
         <f t="shared" si="48"/>
@@ -14264,7 +14264,7 @@
       </c>
       <c r="AU15" s="54">
         <f t="shared" si="49"/>
-        <v>0.3417</v>
+        <v>0.32699999999999996</v>
       </c>
       <c r="AV15" s="57">
         <f>VLOOKUP(A15,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -14490,7 +14490,7 @@
       </c>
       <c r="AS16" s="129">
         <f>(VLOOKUP(B16,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.7409</v>
+        <v>0.75930000000000009</v>
       </c>
       <c r="AT16" s="14">
         <f t="shared" si="48"/>
@@ -14498,7 +14498,7 @@
       </c>
       <c r="AU16" s="54">
         <f t="shared" si="49"/>
-        <v>0.22909999999999997</v>
+        <v>0.21069999999999989</v>
       </c>
       <c r="AV16" s="57">
         <f>VLOOKUP(A16,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -14582,11 +14582,11 @@
       </c>
       <c r="C19" s="142">
         <f ca="1">SUMIF(cuoc!A7:P27,'tiến độ'!A19,cuoc!M7:M27)</f>
-        <v>417352699</v>
+        <v>426159900</v>
       </c>
       <c r="D19" s="142">
         <f ca="1">B19*0.968-C19</f>
-        <v>205821372.25599992</v>
+        <v>197014171.25599992</v>
       </c>
       <c r="E19" s="137"/>
       <c r="H19" s="137"/>
@@ -14603,11 +14603,11 @@
       </c>
       <c r="C20" s="143">
         <f ca="1">SUMIF(cuoc!A8:P27,'tiến độ'!A20,cuoc!M8:M27)</f>
-        <v>663687252</v>
+        <v>688184642</v>
       </c>
       <c r="D20" s="142">
         <f ca="1">B20*0.968-C20</f>
-        <v>280296674.77600002</v>
+        <v>255799284.77600002</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.45">
@@ -14793,6 +14793,11 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="D1:S1"/>
+    <mergeCell ref="D2:G2"/>
+    <mergeCell ref="H2:K2"/>
+    <mergeCell ref="L2:O2"/>
+    <mergeCell ref="P2:S2"/>
     <mergeCell ref="X2:AA2"/>
     <mergeCell ref="AB2:AE2"/>
     <mergeCell ref="AF2:AI2"/>
@@ -14806,11 +14811,6 @@
     <mergeCell ref="AJ2:AM2"/>
     <mergeCell ref="AN2:AQ2"/>
     <mergeCell ref="T2:W2"/>
-    <mergeCell ref="D1:S1"/>
-    <mergeCell ref="D2:G2"/>
-    <mergeCell ref="H2:K2"/>
-    <mergeCell ref="L2:O2"/>
-    <mergeCell ref="P2:S2"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="F4:F16">
@@ -23286,6 +23286,12 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="X5:AE5"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="H5:O5"/>
+    <mergeCell ref="P5:W5"/>
     <mergeCell ref="CB5:CI5"/>
     <mergeCell ref="CJ5:CQ5"/>
     <mergeCell ref="CR5:CY5"/>
@@ -23296,12 +23302,6 @@
     <mergeCell ref="BD5:BK5"/>
     <mergeCell ref="BL5:BS5"/>
     <mergeCell ref="BT5:CA5"/>
-    <mergeCell ref="X5:AE5"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="H5:O5"/>
-    <mergeCell ref="P5:W5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -23399,7 +23399,7 @@
       <c r="A3" s="100" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="245" t="s">
+      <c r="B3" s="243" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="101" t="s">
@@ -23411,70 +23411,70 @@
       <c r="E3" s="247" t="s">
         <v>202</v>
       </c>
-      <c r="F3" s="243" t="s">
+      <c r="F3" s="245" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="243" t="s">
+      <c r="G3" s="245" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="243" t="s">
+      <c r="H3" s="245" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="243" t="s">
+      <c r="I3" s="245" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="243" t="s">
+      <c r="J3" s="245" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="243" t="s">
+      <c r="K3" s="245" t="s">
         <v>11</v>
       </c>
-      <c r="L3" s="243" t="s">
+      <c r="L3" s="245" t="s">
         <v>12</v>
       </c>
-      <c r="M3" s="243" t="s">
+      <c r="M3" s="245" t="s">
         <v>203</v>
       </c>
-      <c r="N3" s="243" t="s">
+      <c r="N3" s="245" t="s">
         <v>286</v>
       </c>
-      <c r="O3" s="243" t="s">
+      <c r="O3" s="245" t="s">
         <v>14</v>
       </c>
-      <c r="P3" s="243" t="s">
+      <c r="P3" s="245" t="s">
         <v>15</v>
       </c>
-      <c r="Q3" s="243" t="s">
+      <c r="Q3" s="245" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="243" t="s">
+      <c r="R3" s="245" t="s">
         <v>17</v>
       </c>
-      <c r="S3" s="243" t="s">
+      <c r="S3" s="245" t="s">
         <v>18</v>
       </c>
       <c r="T3" s="99"/>
     </row>
     <row r="4" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="100"/>
-      <c r="B4" s="246"/>
+      <c r="B4" s="244"/>
       <c r="C4" s="101"/>
       <c r="D4" s="101"/>
       <c r="E4" s="248"/>
-      <c r="F4" s="244"/>
-      <c r="G4" s="244"/>
-      <c r="H4" s="244"/>
-      <c r="I4" s="244"/>
-      <c r="J4" s="244"/>
-      <c r="K4" s="244"/>
-      <c r="L4" s="244"/>
-      <c r="M4" s="244"/>
-      <c r="N4" s="244"/>
-      <c r="O4" s="244"/>
-      <c r="P4" s="244"/>
-      <c r="Q4" s="244"/>
-      <c r="R4" s="244"/>
-      <c r="S4" s="244"/>
+      <c r="F4" s="246"/>
+      <c r="G4" s="246"/>
+      <c r="H4" s="246"/>
+      <c r="I4" s="246"/>
+      <c r="J4" s="246"/>
+      <c r="K4" s="246"/>
+      <c r="L4" s="246"/>
+      <c r="M4" s="246"/>
+      <c r="N4" s="246"/>
+      <c r="O4" s="246"/>
+      <c r="P4" s="246"/>
+      <c r="Q4" s="246"/>
+      <c r="R4" s="246"/>
+      <c r="S4" s="246"/>
       <c r="T4" s="99"/>
     </row>
     <row r="5" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.45">
@@ -24792,6 +24792,12 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="S3:S4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="R3:R4"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="H3:H4"/>
@@ -24802,12 +24808,6 @@
     <mergeCell ref="K3:K4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="E3:E4"/>
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="S3:S4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="R3:R4"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.69991251615088756" right="0.69991251615088756" top="0.74990626395218019" bottom="0.74990626395218019" header="0.29996251027415122" footer="0.29996251027415122"/>
@@ -26083,68 +26083,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:48" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="256" t="s">
+      <c r="A1" s="258" t="s">
         <v>240</v>
       </c>
-      <c r="B1" s="256"/>
-      <c r="C1" s="256"/>
-      <c r="D1" s="256"/>
-      <c r="E1" s="256"/>
-      <c r="F1" s="256"/>
-      <c r="G1" s="256"/>
-      <c r="H1" s="256"/>
-      <c r="I1" s="256"/>
-      <c r="J1" s="256"/>
-      <c r="K1" s="256"/>
-      <c r="M1" s="259" t="s">
+      <c r="B1" s="258"/>
+      <c r="C1" s="258"/>
+      <c r="D1" s="258"/>
+      <c r="E1" s="258"/>
+      <c r="F1" s="258"/>
+      <c r="G1" s="258"/>
+      <c r="H1" s="258"/>
+      <c r="I1" s="258"/>
+      <c r="J1" s="258"/>
+      <c r="K1" s="258"/>
+      <c r="M1" s="261" t="s">
         <v>241</v>
       </c>
-      <c r="N1" s="259"/>
-      <c r="O1" s="259"/>
-      <c r="P1" s="259"/>
-      <c r="Q1" s="259"/>
-      <c r="R1" s="259"/>
-      <c r="S1" s="259"/>
-      <c r="T1" s="259"/>
-      <c r="U1" s="259"/>
-      <c r="V1" s="259"/>
-      <c r="W1" s="259"/>
-      <c r="X1" s="259"/>
-      <c r="Y1" s="259"/>
-      <c r="Z1" s="259"/>
+      <c r="N1" s="261"/>
+      <c r="O1" s="261"/>
+      <c r="P1" s="261"/>
+      <c r="Q1" s="261"/>
+      <c r="R1" s="261"/>
+      <c r="S1" s="261"/>
+      <c r="T1" s="261"/>
+      <c r="U1" s="261"/>
+      <c r="V1" s="261"/>
+      <c r="W1" s="261"/>
+      <c r="X1" s="261"/>
+      <c r="Y1" s="261"/>
+      <c r="Z1" s="261"/>
     </row>
     <row r="2" spans="1:48" ht="24.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="257"/>
-      <c r="B2" s="257"/>
-      <c r="C2" s="257"/>
-      <c r="D2" s="257"/>
-      <c r="E2" s="257"/>
-      <c r="F2" s="257"/>
-      <c r="G2" s="257"/>
-      <c r="H2" s="257"/>
-      <c r="I2" s="257"/>
-      <c r="J2" s="257"/>
-      <c r="K2" s="257"/>
-      <c r="M2" s="260"/>
-      <c r="N2" s="260"/>
-      <c r="O2" s="260"/>
-      <c r="P2" s="260"/>
-      <c r="Q2" s="260"/>
-      <c r="R2" s="260"/>
-      <c r="S2" s="260"/>
-      <c r="T2" s="260"/>
-      <c r="U2" s="260"/>
-      <c r="V2" s="260"/>
-      <c r="W2" s="260"/>
-      <c r="X2" s="260"/>
-      <c r="Y2" s="260"/>
-      <c r="Z2" s="260"/>
+      <c r="A2" s="259"/>
+      <c r="B2" s="259"/>
+      <c r="C2" s="259"/>
+      <c r="D2" s="259"/>
+      <c r="E2" s="259"/>
+      <c r="F2" s="259"/>
+      <c r="G2" s="259"/>
+      <c r="H2" s="259"/>
+      <c r="I2" s="259"/>
+      <c r="J2" s="259"/>
+      <c r="K2" s="259"/>
+      <c r="M2" s="262"/>
+      <c r="N2" s="262"/>
+      <c r="O2" s="262"/>
+      <c r="P2" s="262"/>
+      <c r="Q2" s="262"/>
+      <c r="R2" s="262"/>
+      <c r="S2" s="262"/>
+      <c r="T2" s="262"/>
+      <c r="U2" s="262"/>
+      <c r="V2" s="262"/>
+      <c r="W2" s="262"/>
+      <c r="X2" s="262"/>
+      <c r="Y2" s="262"/>
+      <c r="Z2" s="262"/>
     </row>
     <row r="3" spans="1:48" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="253" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="254" t="s">
+      <c r="A3" s="255" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="256" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="28" t="s">
@@ -26174,70 +26174,70 @@
       <c r="K3" s="28" t="s">
         <v>249</v>
       </c>
-      <c r="M3" s="258" t="s">
+      <c r="M3" s="260" t="s">
         <v>34</v>
       </c>
-      <c r="N3" s="204" t="s">
+      <c r="N3" s="202" t="s">
         <v>250</v>
       </c>
-      <c r="O3" s="205"/>
-      <c r="P3" s="205"/>
-      <c r="Q3" s="205"/>
-      <c r="R3" s="261" t="s">
+      <c r="O3" s="203"/>
+      <c r="P3" s="203"/>
+      <c r="Q3" s="203"/>
+      <c r="R3" s="253" t="s">
         <v>251</v>
       </c>
-      <c r="S3" s="204" t="s">
+      <c r="S3" s="202" t="s">
         <v>252</v>
       </c>
-      <c r="T3" s="205"/>
-      <c r="U3" s="205"/>
-      <c r="V3" s="205"/>
-      <c r="W3" s="261" t="s">
+      <c r="T3" s="203"/>
+      <c r="U3" s="203"/>
+      <c r="V3" s="203"/>
+      <c r="W3" s="253" t="s">
         <v>251</v>
       </c>
-      <c r="X3" s="207" t="s">
+      <c r="X3" s="215" t="s">
         <v>41</v>
       </c>
-      <c r="Y3" s="208"/>
-      <c r="Z3" s="208"/>
-      <c r="AA3" s="261" t="s">
+      <c r="Y3" s="216"/>
+      <c r="Z3" s="216"/>
+      <c r="AA3" s="253" t="s">
         <v>251</v>
       </c>
       <c r="AB3" s="71"/>
-      <c r="AC3" s="204" t="s">
+      <c r="AC3" s="202" t="s">
         <v>42</v>
       </c>
-      <c r="AD3" s="205"/>
-      <c r="AE3" s="205"/>
-      <c r="AF3" s="205"/>
-      <c r="AG3" s="204" t="s">
+      <c r="AD3" s="203"/>
+      <c r="AE3" s="203"/>
+      <c r="AF3" s="203"/>
+      <c r="AG3" s="202" t="s">
         <v>43</v>
       </c>
-      <c r="AH3" s="205"/>
-      <c r="AI3" s="205"/>
-      <c r="AJ3" s="205"/>
-      <c r="AK3" s="204" t="s">
+      <c r="AH3" s="203"/>
+      <c r="AI3" s="203"/>
+      <c r="AJ3" s="203"/>
+      <c r="AK3" s="202" t="s">
         <v>44</v>
       </c>
-      <c r="AL3" s="205"/>
-      <c r="AM3" s="205"/>
-      <c r="AN3" s="205"/>
-      <c r="AO3" s="204" t="s">
+      <c r="AL3" s="203"/>
+      <c r="AM3" s="203"/>
+      <c r="AN3" s="203"/>
+      <c r="AO3" s="202" t="s">
         <v>46</v>
       </c>
-      <c r="AP3" s="205"/>
-      <c r="AQ3" s="205"/>
-      <c r="AR3" s="205"/>
-      <c r="AS3" s="204" t="s">
+      <c r="AP3" s="203"/>
+      <c r="AQ3" s="203"/>
+      <c r="AR3" s="203"/>
+      <c r="AS3" s="202" t="s">
         <v>47</v>
       </c>
-      <c r="AT3" s="205"/>
-      <c r="AU3" s="205"/>
-      <c r="AV3" s="205"/>
+      <c r="AT3" s="203"/>
+      <c r="AU3" s="203"/>
+      <c r="AV3" s="203"/>
     </row>
     <row r="4" spans="1:48" ht="22.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="253"/>
-      <c r="B4" s="255"/>
+      <c r="A4" s="255"/>
+      <c r="B4" s="257"/>
       <c r="C4" s="24">
         <f t="shared" ref="C4:K4" si="0">SUM(C5:C19)</f>
         <v>15</v>
@@ -26274,7 +26274,7 @@
         <f t="shared" si="0"/>
         <v>134</v>
       </c>
-      <c r="M4" s="258"/>
+      <c r="M4" s="260"/>
       <c r="N4" s="8" t="s">
         <v>2</v>
       </c>
@@ -26287,7 +26287,7 @@
       <c r="Q4" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="R4" s="262"/>
+      <c r="R4" s="254"/>
       <c r="S4" s="8" t="s">
         <v>2</v>
       </c>
@@ -26300,7 +26300,7 @@
       <c r="V4" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="W4" s="262"/>
+      <c r="W4" s="254"/>
       <c r="X4" s="8" t="s">
         <v>2</v>
       </c>
@@ -26310,7 +26310,7 @@
       <c r="Z4" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="AA4" s="262"/>
+      <c r="AA4" s="254"/>
       <c r="AB4" s="51" t="s">
         <v>59</v>
       </c>
@@ -28699,6 +28699,12 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="A1:K2"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="N3:Q3"/>
+    <mergeCell ref="M1:Z2"/>
     <mergeCell ref="AS3:AV3"/>
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="W3:W4"/>
@@ -28709,12 +28715,6 @@
     <mergeCell ref="AK3:AN3"/>
     <mergeCell ref="AO3:AR3"/>
     <mergeCell ref="S3:V3"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="A1:K2"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="N3:Q3"/>
-    <mergeCell ref="M1:Z2"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="P5:P20">
@@ -28854,44 +28854,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="263"/>
-      <c r="B1" s="263"/>
-      <c r="C1" s="263"/>
-      <c r="D1" s="263"/>
-      <c r="E1" s="263"/>
-      <c r="F1" s="263"/>
-      <c r="G1" s="263"/>
-      <c r="H1" s="263"/>
-      <c r="I1" s="263"/>
-      <c r="J1" s="263"/>
-      <c r="K1" s="263"/>
-      <c r="L1" s="263"/>
-      <c r="M1" s="263"/>
-      <c r="N1" s="263"/>
-      <c r="O1" s="263"/>
-      <c r="P1" s="263"/>
+      <c r="A1" s="265"/>
+      <c r="B1" s="265"/>
+      <c r="C1" s="265"/>
+      <c r="D1" s="265"/>
+      <c r="E1" s="265"/>
+      <c r="F1" s="265"/>
+      <c r="G1" s="265"/>
+      <c r="H1" s="265"/>
+      <c r="I1" s="265"/>
+      <c r="J1" s="265"/>
+      <c r="K1" s="265"/>
+      <c r="L1" s="265"/>
+      <c r="M1" s="265"/>
+      <c r="N1" s="265"/>
+      <c r="O1" s="265"/>
+      <c r="P1" s="265"/>
     </row>
     <row r="2" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="264"/>
-      <c r="B2" s="264"/>
-      <c r="C2" s="264"/>
-      <c r="D2" s="264"/>
-      <c r="E2" s="264"/>
-      <c r="F2" s="264"/>
-      <c r="G2" s="264"/>
-      <c r="H2" s="264"/>
-      <c r="I2" s="264"/>
-      <c r="J2" s="264"/>
-      <c r="K2" s="264"/>
-      <c r="L2" s="264"/>
-      <c r="M2" s="264"/>
-      <c r="N2" s="264"/>
-      <c r="O2" s="264"/>
-      <c r="P2" s="264"/>
+      <c r="A2" s="266"/>
+      <c r="B2" s="266"/>
+      <c r="C2" s="266"/>
+      <c r="D2" s="266"/>
+      <c r="E2" s="266"/>
+      <c r="F2" s="266"/>
+      <c r="G2" s="266"/>
+      <c r="H2" s="266"/>
+      <c r="I2" s="266"/>
+      <c r="J2" s="266"/>
+      <c r="K2" s="266"/>
+      <c r="L2" s="266"/>
+      <c r="M2" s="266"/>
+      <c r="N2" s="266"/>
+      <c r="O2" s="266"/>
+      <c r="P2" s="266"/>
     </row>
     <row r="3" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="265"/>
-      <c r="B3" s="265"/>
+      <c r="A3" s="267"/>
+      <c r="B3" s="267"/>
       <c r="C3" s="133"/>
       <c r="D3" s="133"/>
       <c r="E3" s="133"/>
@@ -28908,10 +28908,10 @@
       <c r="P3" s="133"/>
     </row>
     <row r="4" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="267" t="s">
+      <c r="A4" s="269" t="s">
         <v>255</v>
       </c>
-      <c r="B4" s="267" t="s">
+      <c r="B4" s="269" t="s">
         <v>39</v>
       </c>
       <c r="C4" s="141"/>
@@ -28919,70 +28919,70 @@
       <c r="E4" s="141"/>
       <c r="F4" s="141"/>
       <c r="G4" s="141"/>
-      <c r="H4" s="266"/>
-      <c r="I4" s="266"/>
-      <c r="J4" s="266"/>
-      <c r="K4" s="266"/>
-      <c r="L4" s="266"/>
-      <c r="M4" s="266"/>
-      <c r="N4" s="266"/>
-      <c r="O4" s="266"/>
-      <c r="P4" s="266"/>
+      <c r="H4" s="268"/>
+      <c r="I4" s="268"/>
+      <c r="J4" s="268"/>
+      <c r="K4" s="268"/>
+      <c r="L4" s="268"/>
+      <c r="M4" s="268"/>
+      <c r="N4" s="268"/>
+      <c r="O4" s="268"/>
+      <c r="P4" s="268"/>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A5" s="270"/>
-      <c r="B5" s="270"/>
-      <c r="C5" s="267" t="s">
+      <c r="A5" s="272"/>
+      <c r="B5" s="272"/>
+      <c r="C5" s="269" t="s">
         <v>256</v>
       </c>
-      <c r="D5" s="267" t="s">
+      <c r="D5" s="269" t="s">
         <v>257</v>
       </c>
-      <c r="E5" s="268"/>
-      <c r="F5" s="267" t="s">
+      <c r="E5" s="270"/>
+      <c r="F5" s="269" t="s">
         <v>258</v>
       </c>
-      <c r="G5" s="268"/>
-      <c r="H5" s="267" t="s">
+      <c r="G5" s="270"/>
+      <c r="H5" s="269" t="s">
         <v>259</v>
       </c>
-      <c r="I5" s="268"/>
-      <c r="J5" s="267" t="s">
+      <c r="I5" s="270"/>
+      <c r="J5" s="269" t="s">
         <v>260</v>
       </c>
-      <c r="K5" s="268"/>
-      <c r="L5" s="271" t="s">
+      <c r="K5" s="270"/>
+      <c r="L5" s="273" t="s">
         <v>261</v>
       </c>
-      <c r="M5" s="268"/>
-      <c r="N5" s="266" t="s">
+      <c r="M5" s="270"/>
+      <c r="N5" s="268" t="s">
         <v>262</v>
       </c>
-      <c r="O5" s="272"/>
-      <c r="P5" s="267" t="s">
+      <c r="O5" s="274"/>
+      <c r="P5" s="269" t="s">
         <v>266</v>
       </c>
-      <c r="R5" s="273" t="s">
+      <c r="R5" s="263" t="s">
         <v>34</v>
       </c>
-      <c r="S5" s="273" t="s">
+      <c r="S5" s="263" t="s">
         <v>290</v>
       </c>
-      <c r="T5" s="273" t="s">
+      <c r="T5" s="263" t="s">
         <v>291</v>
       </c>
-      <c r="U5" s="273" t="s">
+      <c r="U5" s="263" t="s">
         <v>293</v>
       </c>
-      <c r="V5" s="274" t="s">
+      <c r="V5" s="264" t="s">
         <v>292</v>
       </c>
       <c r="W5" s="172"/>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A6" s="269"/>
-      <c r="B6" s="269"/>
-      <c r="C6" s="270"/>
+      <c r="A6" s="271"/>
+      <c r="B6" s="271"/>
+      <c r="C6" s="272"/>
       <c r="D6" s="134" t="s">
         <v>2</v>
       </c>
@@ -29019,12 +29019,12 @@
       <c r="O6" s="134" t="s">
         <v>263</v>
       </c>
-      <c r="P6" s="269"/>
-      <c r="R6" s="273"/>
-      <c r="S6" s="273"/>
-      <c r="T6" s="273"/>
-      <c r="U6" s="273"/>
-      <c r="V6" s="273"/>
+      <c r="P6" s="271"/>
+      <c r="R6" s="263"/>
+      <c r="S6" s="263"/>
+      <c r="T6" s="263"/>
+      <c r="U6" s="263"/>
+      <c r="V6" s="263"/>
       <c r="W6" s="172"/>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.45">
@@ -29056,26 +29056,26 @@
         <v>72573808</v>
       </c>
       <c r="J7" s="191">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K7" s="191">
-        <v>509000</v>
+        <v>1270896</v>
       </c>
       <c r="L7" s="191">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="M7" s="191">
-        <v>59028396</v>
+        <v>59790292</v>
       </c>
       <c r="N7" s="192">
-        <v>83.18</v>
+        <v>84.1</v>
       </c>
       <c r="O7" s="192">
-        <v>81.34</v>
+        <v>82.39</v>
       </c>
       <c r="P7" s="135">
         <f>I7*0.97-M7</f>
-        <v>11368197.760000005</v>
+        <v>10606301.760000005</v>
       </c>
       <c r="R7" s="173" t="s">
         <v>117</v>
@@ -29089,11 +29089,11 @@
       </c>
       <c r="U7" s="189">
         <f>VLOOKUP(R7,$C$7:$P$27,14,0)</f>
-        <v>27733838.799999997</v>
+        <v>26057253.799999997</v>
       </c>
       <c r="V7" s="175">
         <f>VLOOKUP(R7,$C$7:$P$27,14,0)-T7</f>
-        <v>0</v>
+        <v>-1676585</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.45">
@@ -29125,26 +29125,26 @@
         <v>70243418</v>
       </c>
       <c r="J8" s="194">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K8" s="194">
-        <v>0</v>
+        <v>1586389</v>
       </c>
       <c r="L8" s="194">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="M8" s="194">
-        <v>55273476</v>
+        <v>56859865</v>
       </c>
       <c r="N8" s="195">
-        <v>76.430000000000007</v>
+        <v>78.849999999999994</v>
       </c>
       <c r="O8" s="195">
-        <v>78.69</v>
+        <v>80.95</v>
       </c>
       <c r="P8" s="135">
         <f t="shared" ref="P8:P27" si="0">I8*0.97-M8</f>
-        <v>12862639.459999993</v>
+        <v>11276250.459999993</v>
       </c>
       <c r="R8" s="173" t="s">
         <v>67</v>
@@ -29158,11 +29158,11 @@
       </c>
       <c r="U8" s="189">
         <f t="shared" ref="U8:U17" si="2">VLOOKUP(R8,$C$7:$P$27,14,0)</f>
-        <v>28033862.310000002</v>
+        <v>26149040.310000002</v>
       </c>
       <c r="V8" s="175">
         <f t="shared" ref="V8:V17" si="3">VLOOKUP(R8,$C$7:$P$27,14,0)-T8</f>
-        <v>0</v>
+        <v>-1884822</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.45">
@@ -29194,26 +29194,26 @@
         <v>145101823</v>
       </c>
       <c r="J9" s="191">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="K9" s="191">
-        <v>160000</v>
+        <v>2044822</v>
       </c>
       <c r="L9" s="191">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="M9" s="191">
-        <v>112714906</v>
+        <v>114599728</v>
       </c>
       <c r="N9" s="192">
-        <v>75.34</v>
+        <v>76.709999999999994</v>
       </c>
       <c r="O9" s="192">
-        <v>77.680000000000007</v>
+        <v>78.98</v>
       </c>
       <c r="P9" s="135">
         <f t="shared" si="0"/>
-        <v>28033862.310000002</v>
+        <v>26149040.310000002</v>
       </c>
       <c r="R9" s="174" t="s">
         <v>87</v>
@@ -29227,11 +29227,11 @@
       </c>
       <c r="U9" s="189">
         <f t="shared" si="2"/>
-        <v>49090015.270000011</v>
+        <v>46511764.270000011</v>
       </c>
       <c r="V9" s="175">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-2578251</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.45">
@@ -29263,26 +29263,26 @@
         <v>51982396</v>
       </c>
       <c r="J10" s="194">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K10" s="194">
-        <v>100000</v>
+        <v>1258419</v>
       </c>
       <c r="L10" s="194">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="M10" s="194">
-        <v>39236420</v>
+        <v>40394839</v>
       </c>
       <c r="N10" s="195">
-        <v>75</v>
+        <v>77.27</v>
       </c>
       <c r="O10" s="195">
-        <v>75.48</v>
+        <v>77.709999999999994</v>
       </c>
       <c r="P10" s="135">
         <f t="shared" si="0"/>
-        <v>11186504.119999997</v>
+        <v>10028085.119999997</v>
       </c>
       <c r="R10" s="174" t="s">
         <v>110</v>
@@ -29296,28 +29296,28 @@
       </c>
       <c r="U10" s="189">
         <f t="shared" si="2"/>
-        <v>61083318.859999985</v>
+        <v>58912775.859999985</v>
       </c>
       <c r="V10" s="175">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-2170543</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A11" s="190" t="s">
-        <v>288</v>
+        <v>129</v>
       </c>
       <c r="B11" s="190" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C11" s="190" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="D11" s="191">
-        <v>559</v>
+        <v>1048</v>
       </c>
       <c r="E11" s="191">
-        <v>93597302</v>
+        <v>180440547</v>
       </c>
       <c r="F11" s="191">
         <v>0</v>
@@ -29326,32 +29326,32 @@
         <v>0</v>
       </c>
       <c r="H11" s="191">
-        <v>559</v>
+        <v>1048</v>
       </c>
       <c r="I11" s="191">
-        <v>93597302</v>
+        <v>180440547</v>
       </c>
       <c r="J11" s="191">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="K11" s="191">
-        <v>558651</v>
+        <v>6929191</v>
       </c>
       <c r="L11" s="191">
-        <v>408</v>
+        <v>787</v>
       </c>
       <c r="M11" s="191">
-        <v>70116733</v>
+        <v>139450047</v>
       </c>
       <c r="N11" s="192">
-        <v>72.989999999999995</v>
+        <v>75.099999999999994</v>
       </c>
       <c r="O11" s="192">
-        <v>74.91</v>
+        <v>77.28</v>
       </c>
       <c r="P11" s="135">
         <f t="shared" si="0"/>
-        <v>20672649.939999998</v>
+        <v>35577283.590000004</v>
       </c>
       <c r="R11" s="173" t="s">
         <v>99</v>
@@ -29365,11 +29365,11 @@
       </c>
       <c r="U11" s="189">
         <f t="shared" si="2"/>
-        <v>41167886.75</v>
+        <v>40670886.75</v>
       </c>
       <c r="V11" s="175">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-497000</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.45">
@@ -29377,16 +29377,16 @@
         <v>288</v>
       </c>
       <c r="B12" s="193" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="C12" s="193" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="D12" s="194">
-        <v>716</v>
+        <v>559</v>
       </c>
       <c r="E12" s="194">
-        <v>116427734</v>
+        <v>93597302</v>
       </c>
       <c r="F12" s="194">
         <v>0</v>
@@ -29395,32 +29395,32 @@
         <v>0</v>
       </c>
       <c r="H12" s="194">
-        <v>716</v>
+        <v>559</v>
       </c>
       <c r="I12" s="194">
-        <v>116427734</v>
+        <v>93597302</v>
       </c>
       <c r="J12" s="194">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="K12" s="194">
-        <v>270000</v>
+        <v>2342270</v>
       </c>
       <c r="L12" s="194">
-        <v>516</v>
+        <v>420</v>
       </c>
       <c r="M12" s="194">
-        <v>87160486</v>
+        <v>71900352</v>
       </c>
       <c r="N12" s="195">
-        <v>72.069999999999993</v>
+        <v>75.13</v>
       </c>
       <c r="O12" s="195">
-        <v>74.86</v>
+        <v>76.819999999999993</v>
       </c>
       <c r="P12" s="135">
         <f t="shared" si="0"/>
-        <v>25774415.980000004</v>
+        <v>18889030.939999998</v>
       </c>
       <c r="R12" s="173" t="s">
         <v>75</v>
@@ -29434,28 +29434,28 @@
       </c>
       <c r="U12" s="189">
         <f t="shared" si="2"/>
-        <v>36430325.520000011</v>
+        <v>33601046.520000011</v>
       </c>
       <c r="V12" s="175">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-2829279</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A13" s="190" t="s">
-        <v>129</v>
+        <v>288</v>
       </c>
       <c r="B13" s="190" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="C13" s="190" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="D13" s="191">
-        <v>1181</v>
+        <v>716</v>
       </c>
       <c r="E13" s="191">
-        <v>189656153</v>
+        <v>116427734</v>
       </c>
       <c r="F13" s="191">
         <v>0</v>
@@ -29464,32 +29464,32 @@
         <v>0</v>
       </c>
       <c r="H13" s="191">
-        <v>1181</v>
+        <v>716</v>
       </c>
       <c r="I13" s="191">
-        <v>189656153</v>
+        <v>116427734</v>
       </c>
       <c r="J13" s="191">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="K13" s="191">
-        <v>757317</v>
+        <v>2087490</v>
       </c>
       <c r="L13" s="191">
-        <v>858</v>
+        <v>531</v>
       </c>
       <c r="M13" s="191">
-        <v>140517492</v>
+        <v>88977976</v>
       </c>
       <c r="N13" s="192">
-        <v>72.650000000000006</v>
+        <v>74.16</v>
       </c>
       <c r="O13" s="192">
-        <v>74.09</v>
+        <v>76.42</v>
       </c>
       <c r="P13" s="135">
         <f t="shared" si="0"/>
-        <v>43448976.409999996</v>
+        <v>23956925.980000004</v>
       </c>
       <c r="R13" s="173" t="s">
         <v>107</v>
@@ -29503,11 +29503,11 @@
       </c>
       <c r="U13" s="189">
         <f t="shared" si="2"/>
-        <v>41487079.590000004</v>
+        <v>35577283.590000004</v>
       </c>
       <c r="V13" s="175">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-5909796</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.45">
@@ -29515,16 +29515,16 @@
         <v>129</v>
       </c>
       <c r="B14" s="193" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="C14" s="193" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="D14" s="194">
-        <v>1048</v>
+        <v>1181</v>
       </c>
       <c r="E14" s="194">
-        <v>180440547</v>
+        <v>189656153</v>
       </c>
       <c r="F14" s="194">
         <v>0</v>
@@ -29533,32 +29533,32 @@
         <v>0</v>
       </c>
       <c r="H14" s="194">
-        <v>1048</v>
+        <v>1181</v>
       </c>
       <c r="I14" s="194">
-        <v>180440547</v>
+        <v>189656153</v>
       </c>
       <c r="J14" s="194">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="K14" s="194">
-        <v>1019395</v>
+        <v>4245520</v>
       </c>
       <c r="L14" s="194">
-        <v>752</v>
+        <v>875</v>
       </c>
       <c r="M14" s="194">
-        <v>133540251</v>
+        <v>144005695</v>
       </c>
       <c r="N14" s="195">
-        <v>71.760000000000005</v>
+        <v>74.09</v>
       </c>
       <c r="O14" s="195">
-        <v>74.010000000000005</v>
+        <v>75.930000000000007</v>
       </c>
       <c r="P14" s="135">
         <f t="shared" si="0"/>
-        <v>41487079.590000004</v>
+        <v>39960773.409999996</v>
       </c>
       <c r="R14" s="174" t="s">
         <v>72</v>
@@ -29572,11 +29572,11 @@
       </c>
       <c r="U14" s="189">
         <f t="shared" si="2"/>
-        <v>50987798.199999988</v>
+        <v>45616717.199999988</v>
       </c>
       <c r="V14" s="175">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-5371081</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.45">
@@ -29608,26 +29608,26 @@
         <v>152862316</v>
       </c>
       <c r="J15" s="191">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="K15" s="191">
-        <v>165123</v>
+        <v>2994402</v>
       </c>
       <c r="L15" s="191">
-        <v>649</v>
+        <v>670</v>
       </c>
       <c r="M15" s="191">
-        <v>111846121</v>
+        <v>114675400</v>
       </c>
       <c r="N15" s="192">
-        <v>68.97</v>
+        <v>71.2</v>
       </c>
       <c r="O15" s="192">
-        <v>73.17</v>
+        <v>75.02</v>
       </c>
       <c r="P15" s="135">
         <f t="shared" si="0"/>
-        <v>36430325.520000011</v>
+        <v>33601046.520000011</v>
       </c>
       <c r="R15" s="174" t="s">
         <v>113</v>
@@ -29641,11 +29641,11 @@
       </c>
       <c r="U15" s="189">
         <f t="shared" si="2"/>
-        <v>66475047.400000006</v>
+        <v>63603201.400000006</v>
       </c>
       <c r="V15" s="175">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-2871846</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.45">
@@ -29677,26 +29677,26 @@
         <v>66800107</v>
       </c>
       <c r="J16" s="194">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K16" s="194">
-        <v>451977</v>
+        <v>1193140</v>
       </c>
       <c r="L16" s="194">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="M16" s="194">
-        <v>48185464</v>
+        <v>48926627</v>
       </c>
       <c r="N16" s="195">
-        <v>68.67</v>
+        <v>70.12</v>
       </c>
       <c r="O16" s="195">
-        <v>72.13</v>
+        <v>73.239999999999995</v>
       </c>
       <c r="P16" s="135">
         <f t="shared" si="0"/>
-        <v>16610639.789999999</v>
+        <v>15869476.789999999</v>
       </c>
       <c r="R16" s="174" t="s">
         <v>119</v>
@@ -29710,11 +29710,11 @@
       </c>
       <c r="U16" s="189">
         <f t="shared" si="2"/>
-        <v>43448976.409999996</v>
+        <v>39960773.409999996</v>
       </c>
       <c r="V16" s="175">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-3488203</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.45">
@@ -29746,26 +29746,26 @@
         <v>53605661</v>
       </c>
       <c r="J17" s="191">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K17" s="191">
-        <v>355000</v>
+        <v>1499682</v>
       </c>
       <c r="L17" s="191">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="M17" s="191">
-        <v>37920198</v>
+        <v>39064880</v>
       </c>
       <c r="N17" s="192">
-        <v>66.290000000000006</v>
+        <v>68.260000000000005</v>
       </c>
       <c r="O17" s="192">
-        <v>70.739999999999995</v>
+        <v>72.87</v>
       </c>
       <c r="P17" s="135">
         <f t="shared" si="0"/>
-        <v>14077293.170000002</v>
+        <v>12932611.170000002</v>
       </c>
       <c r="R17" s="173" t="s">
         <v>84</v>
@@ -29779,11 +29779,11 @@
       </c>
       <c r="U17" s="189">
         <f t="shared" si="2"/>
-        <v>43417827.670000002</v>
+        <v>39390642.670000002</v>
       </c>
       <c r="V17" s="175">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-4027185</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.45">
@@ -29815,26 +29815,26 @@
         <v>101866340</v>
       </c>
       <c r="J18" s="194">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K18" s="194">
-        <v>0</v>
+        <v>1676585</v>
       </c>
       <c r="L18" s="194">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="M18" s="194">
-        <v>71076511</v>
+        <v>72753096</v>
       </c>
       <c r="N18" s="195">
-        <v>66.67</v>
+        <v>68.38</v>
       </c>
       <c r="O18" s="195">
-        <v>69.77</v>
+        <v>71.42</v>
       </c>
       <c r="P18" s="135">
         <f t="shared" si="0"/>
-        <v>27733838.799999997</v>
+        <v>26057253.799999997</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.45">
@@ -29866,26 +29866,26 @@
         <v>50351985</v>
       </c>
       <c r="J19" s="191">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K19" s="191">
-        <v>0</v>
+        <v>830903</v>
       </c>
       <c r="L19" s="191">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="M19" s="191">
-        <v>34697236</v>
+        <v>35528139</v>
       </c>
       <c r="N19" s="192">
-        <v>65.72</v>
+        <v>67.3</v>
       </c>
       <c r="O19" s="192">
-        <v>68.91</v>
+        <v>70.56</v>
       </c>
       <c r="P19" s="135">
         <f t="shared" si="0"/>
-        <v>14144189.449999996</v>
+        <v>13313286.449999996</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.45">
@@ -29917,26 +29917,26 @@
         <v>162344260</v>
       </c>
       <c r="J20" s="194">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="K20" s="194">
-        <v>786437</v>
+        <v>6157518</v>
       </c>
       <c r="L20" s="194">
-        <v>631</v>
+        <v>655</v>
       </c>
       <c r="M20" s="194">
-        <v>106486134</v>
+        <v>111857215</v>
       </c>
       <c r="N20" s="195">
-        <v>65.19</v>
+        <v>67.67</v>
       </c>
       <c r="O20" s="195">
-        <v>65.59</v>
+        <v>68.900000000000006</v>
       </c>
       <c r="P20" s="135">
         <f t="shared" si="0"/>
-        <v>50987798.199999988</v>
+        <v>45616717.199999988</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.45">
@@ -29968,26 +29968,26 @@
         <v>194517020</v>
       </c>
       <c r="J21" s="191">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="K21" s="191">
-        <v>570329</v>
+        <v>3442175</v>
       </c>
       <c r="L21" s="191">
-        <v>735</v>
+        <v>753</v>
       </c>
       <c r="M21" s="191">
-        <v>122206462</v>
+        <v>125078308</v>
       </c>
       <c r="N21" s="192">
-        <v>61.35</v>
+        <v>62.85</v>
       </c>
       <c r="O21" s="192">
-        <v>62.83</v>
+        <v>64.3</v>
       </c>
       <c r="P21" s="135">
         <f t="shared" si="0"/>
-        <v>66475047.400000006</v>
+        <v>63603201.400000006</v>
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.45">
@@ -30019,26 +30019,26 @@
         <v>141474291</v>
       </c>
       <c r="J22" s="194">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="K22" s="194">
-        <v>233432</v>
+        <v>2811683</v>
       </c>
       <c r="L22" s="194">
-        <v>523</v>
+        <v>536</v>
       </c>
       <c r="M22" s="194">
-        <v>88140047</v>
+        <v>90718298</v>
       </c>
       <c r="N22" s="195">
-        <v>61.31</v>
+        <v>62.84</v>
       </c>
       <c r="O22" s="195">
-        <v>62.3</v>
+        <v>64.12</v>
       </c>
       <c r="P22" s="135">
         <f t="shared" si="0"/>
-        <v>49090015.270000011</v>
+        <v>46511764.270000011</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.45">
@@ -30070,26 +30070,26 @@
         <v>105953075</v>
       </c>
       <c r="J23" s="191">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K23" s="191">
-        <v>0</v>
+        <v>497000</v>
       </c>
       <c r="L23" s="191">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="M23" s="191">
-        <v>61606596</v>
+        <v>62103596</v>
       </c>
       <c r="N23" s="192">
-        <v>56.91</v>
+        <v>57.64</v>
       </c>
       <c r="O23" s="192">
-        <v>58.15</v>
+        <v>58.61</v>
       </c>
       <c r="P23" s="135">
         <f t="shared" si="0"/>
-        <v>41167886.75</v>
+        <v>40670886.75</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.45">
@@ -30121,26 +30121,26 @@
         <v>149379338</v>
       </c>
       <c r="J24" s="194">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="K24" s="194">
-        <v>106494</v>
+        <v>2277037</v>
       </c>
       <c r="L24" s="194">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="M24" s="194">
-        <v>83814639</v>
+        <v>85985182</v>
       </c>
       <c r="N24" s="195">
-        <v>56.73</v>
+        <v>58.07</v>
       </c>
       <c r="O24" s="195">
-        <v>56.11</v>
+        <v>57.56</v>
       </c>
       <c r="P24" s="135">
         <f t="shared" si="0"/>
-        <v>61083318.859999985</v>
+        <v>58912775.859999985</v>
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.45">
@@ -30172,26 +30172,26 @@
         <v>89879995</v>
       </c>
       <c r="J25" s="191">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="K25" s="191">
-        <v>185000</v>
+        <v>2253084</v>
       </c>
       <c r="L25" s="191">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="M25" s="191">
-        <v>49044586</v>
+        <v>51112670</v>
       </c>
       <c r="N25" s="192">
-        <v>52.56</v>
+        <v>54.76</v>
       </c>
       <c r="O25" s="192">
-        <v>54.57</v>
+        <v>56.87</v>
       </c>
       <c r="P25" s="135">
         <f t="shared" si="0"/>
-        <v>38139009.149999991</v>
+        <v>36070925.149999991</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.45">
@@ -30223,26 +30223,26 @@
         <v>95369711</v>
       </c>
       <c r="J26" s="194">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K26" s="194">
-        <v>100000</v>
+        <v>4127185</v>
       </c>
       <c r="L26" s="194">
-        <v>292</v>
+        <v>317</v>
       </c>
       <c r="M26" s="194">
-        <v>49090792</v>
+        <v>53117977</v>
       </c>
       <c r="N26" s="195">
-        <v>49.66</v>
+        <v>53.91</v>
       </c>
       <c r="O26" s="195">
-        <v>51.47</v>
+        <v>55.7</v>
       </c>
       <c r="P26" s="135">
         <f t="shared" si="0"/>
-        <v>43417827.670000002</v>
+        <v>39390642.670000002</v>
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.45">
@@ -30274,35 +30274,30 @@
         <v>105983346</v>
       </c>
       <c r="J27" s="191">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K27" s="191">
-        <v>0</v>
+        <v>932012</v>
       </c>
       <c r="L27" s="191">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="M27" s="191">
-        <v>32622142</v>
+        <v>33554154</v>
       </c>
       <c r="N27" s="192">
-        <v>30.89</v>
+        <v>31.77</v>
       </c>
       <c r="O27" s="192">
-        <v>30.78</v>
+        <v>31.66</v>
       </c>
       <c r="P27" s="135">
         <f t="shared" si="0"/>
-        <v>70181703.61999999</v>
+        <v>69249691.61999999</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="U5:U6"/>
-    <mergeCell ref="V5:V6"/>
-    <mergeCell ref="R5:R6"/>
-    <mergeCell ref="S5:S6"/>
-    <mergeCell ref="T5:T6"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
     <mergeCell ref="A3:B3"/>
@@ -30317,6 +30312,11 @@
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="L5:M5"/>
     <mergeCell ref="N5:O5"/>
+    <mergeCell ref="U5:U6"/>
+    <mergeCell ref="V5:V6"/>
+    <mergeCell ref="R5:R6"/>
+    <mergeCell ref="S5:S6"/>
+    <mergeCell ref="T5:T6"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="P7:P27">

--- a/filetiendo.xlsx
+++ b/filetiendo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\viettel 2026\thang 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20E19459-72BE-4896-8094-D18A401BB59C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{744DBD91-03DD-4D93-AEBF-AF9AB4EB2C3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="808" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4556,17 +4556,41 @@
     <xf numFmtId="0" fontId="66" fillId="0" borderId="109" xfId="11" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="109" xfId="11" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="177" xfId="11" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="50" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="5" borderId="127" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="135" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="134" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="133" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="5" borderId="130" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="128" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="140" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="139" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="138" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="5" borderId="127" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="24" borderId="132" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4580,34 +4604,10 @@
     <xf numFmtId="0" fontId="17" fillId="5" borderId="129" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="135" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="134" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="133" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="16" borderId="136" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="2" borderId="137" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="140" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="139" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="138" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="67" fillId="18" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4679,16 +4679,16 @@
     <xf numFmtId="0" fontId="63" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="148" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="147" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="47" fillId="5" borderId="152" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="5" borderId="151" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="148" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="147" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="51" fillId="5" borderId="150" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4708,12 +4708,6 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="155" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="158" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="157" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="159" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4739,10 +4733,10 @@
     <xf numFmtId="0" fontId="55" fillId="0" borderId="164" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="69" fillId="29" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="158" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="69" fillId="29" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="157" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="45" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4767,6 +4761,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="168" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="69" fillId="29" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="29" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="12">
     <cellStyle name="Comma" xfId="8" builtinId="3"/>
@@ -5656,166 +5656,166 @@
       </c>
     </row>
     <row r="2" spans="1:675" ht="23.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="200" t="s">
+      <c r="A2" s="210" t="s">
         <v>34</v>
       </c>
       <c r="B2" s="86"/>
       <c r="C2" s="15"/>
-      <c r="D2" s="211" t="s">
+      <c r="D2" s="216" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="211"/>
-      <c r="F2" s="211"/>
-      <c r="G2" s="211"/>
-      <c r="H2" s="211"/>
-      <c r="I2" s="211"/>
-      <c r="J2" s="211"/>
-      <c r="K2" s="211"/>
-      <c r="L2" s="211"/>
-      <c r="M2" s="211"/>
-      <c r="N2" s="211"/>
-      <c r="O2" s="211"/>
-      <c r="P2" s="211"/>
-      <c r="Q2" s="211"/>
-      <c r="R2" s="211"/>
-      <c r="S2" s="211"/>
-      <c r="T2" s="206" t="s">
+      <c r="E2" s="216"/>
+      <c r="F2" s="216"/>
+      <c r="G2" s="216"/>
+      <c r="H2" s="216"/>
+      <c r="I2" s="216"/>
+      <c r="J2" s="216"/>
+      <c r="K2" s="216"/>
+      <c r="L2" s="216"/>
+      <c r="M2" s="216"/>
+      <c r="N2" s="216"/>
+      <c r="O2" s="216"/>
+      <c r="P2" s="216"/>
+      <c r="Q2" s="216"/>
+      <c r="R2" s="216"/>
+      <c r="S2" s="216"/>
+      <c r="T2" s="214" t="s">
         <v>36</v>
       </c>
-      <c r="U2" s="206"/>
-      <c r="V2" s="206"/>
-      <c r="W2" s="206"/>
-      <c r="X2" s="206"/>
-      <c r="Y2" s="206"/>
-      <c r="Z2" s="206"/>
-      <c r="AA2" s="206"/>
-      <c r="AB2" s="206"/>
-      <c r="AC2" s="206"/>
-      <c r="AD2" s="206"/>
-      <c r="AE2" s="206"/>
-      <c r="AF2" s="206"/>
-      <c r="AG2" s="206"/>
-      <c r="AH2" s="206"/>
-      <c r="AI2" s="206"/>
-      <c r="AJ2" s="205" t="s">
+      <c r="U2" s="214"/>
+      <c r="V2" s="214"/>
+      <c r="W2" s="214"/>
+      <c r="X2" s="214"/>
+      <c r="Y2" s="214"/>
+      <c r="Z2" s="214"/>
+      <c r="AA2" s="214"/>
+      <c r="AB2" s="214"/>
+      <c r="AC2" s="214"/>
+      <c r="AD2" s="214"/>
+      <c r="AE2" s="214"/>
+      <c r="AF2" s="214"/>
+      <c r="AG2" s="214"/>
+      <c r="AH2" s="214"/>
+      <c r="AI2" s="214"/>
+      <c r="AJ2" s="213" t="s">
         <v>37</v>
       </c>
-      <c r="AK2" s="205"/>
-      <c r="AL2" s="205"/>
-      <c r="AM2" s="205"/>
-      <c r="AN2" s="205"/>
-      <c r="AO2" s="205"/>
-      <c r="AP2" s="205"/>
-      <c r="AQ2" s="205"/>
-      <c r="AR2" s="205"/>
-      <c r="AS2" s="205"/>
-      <c r="AT2" s="205"/>
-      <c r="AU2" s="205"/>
-      <c r="AV2" s="204" t="s">
+      <c r="AK2" s="213"/>
+      <c r="AL2" s="213"/>
+      <c r="AM2" s="213"/>
+      <c r="AN2" s="213"/>
+      <c r="AO2" s="213"/>
+      <c r="AP2" s="213"/>
+      <c r="AQ2" s="213"/>
+      <c r="AR2" s="213"/>
+      <c r="AS2" s="213"/>
+      <c r="AT2" s="213"/>
+      <c r="AU2" s="213"/>
+      <c r="AV2" s="212" t="s">
         <v>38</v>
       </c>
-      <c r="AW2" s="204"/>
-      <c r="AX2" s="204"/>
-      <c r="AY2" s="204"/>
-      <c r="AZ2" s="204"/>
-      <c r="BA2" s="204"/>
-      <c r="BB2" s="204"/>
-      <c r="BC2" s="204"/>
-      <c r="BD2" s="204"/>
-      <c r="BE2" s="204"/>
-      <c r="BF2" s="204"/>
-      <c r="BG2" s="204"/>
+      <c r="AW2" s="212"/>
+      <c r="AX2" s="212"/>
+      <c r="AY2" s="212"/>
+      <c r="AZ2" s="212"/>
+      <c r="BA2" s="212"/>
+      <c r="BB2" s="212"/>
+      <c r="BC2" s="212"/>
+      <c r="BD2" s="212"/>
+      <c r="BE2" s="212"/>
+      <c r="BF2" s="212"/>
+      <c r="BG2" s="212"/>
     </row>
     <row r="3" spans="1:675" s="3" customFormat="1" ht="28.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="200"/>
-      <c r="B3" s="212" t="s">
+      <c r="A3" s="210"/>
+      <c r="B3" s="217" t="s">
         <v>39</v>
       </c>
       <c r="C3" s="87"/>
-      <c r="D3" s="202" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="203"/>
-      <c r="F3" s="203"/>
-      <c r="G3" s="203"/>
-      <c r="H3" s="202" t="s">
+      <c r="D3" s="204" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="205"/>
+      <c r="F3" s="205"/>
+      <c r="G3" s="205"/>
+      <c r="H3" s="204" t="s">
         <v>40</v>
       </c>
-      <c r="I3" s="203"/>
-      <c r="J3" s="203"/>
-      <c r="K3" s="203"/>
-      <c r="L3" s="202" t="s">
+      <c r="I3" s="205"/>
+      <c r="J3" s="205"/>
+      <c r="K3" s="205"/>
+      <c r="L3" s="204" t="s">
         <v>41</v>
       </c>
-      <c r="M3" s="203"/>
-      <c r="N3" s="203"/>
-      <c r="O3" s="203"/>
-      <c r="P3" s="215" t="s">
+      <c r="M3" s="205"/>
+      <c r="N3" s="205"/>
+      <c r="O3" s="205"/>
+      <c r="P3" s="207" t="s">
         <v>42</v>
       </c>
-      <c r="Q3" s="216"/>
-      <c r="R3" s="216"/>
-      <c r="S3" s="217"/>
-      <c r="T3" s="202" t="s">
+      <c r="Q3" s="208"/>
+      <c r="R3" s="208"/>
+      <c r="S3" s="209"/>
+      <c r="T3" s="204" t="s">
         <v>43</v>
       </c>
-      <c r="U3" s="203"/>
-      <c r="V3" s="203"/>
-      <c r="W3" s="203"/>
-      <c r="X3" s="202" t="s">
+      <c r="U3" s="205"/>
+      <c r="V3" s="205"/>
+      <c r="W3" s="205"/>
+      <c r="X3" s="204" t="s">
         <v>45</v>
       </c>
-      <c r="Y3" s="203"/>
-      <c r="Z3" s="203"/>
-      <c r="AA3" s="203"/>
-      <c r="AB3" s="202" t="s">
+      <c r="Y3" s="205"/>
+      <c r="Z3" s="205"/>
+      <c r="AA3" s="205"/>
+      <c r="AB3" s="204" t="s">
         <v>47</v>
       </c>
-      <c r="AC3" s="203"/>
-      <c r="AD3" s="203"/>
-      <c r="AE3" s="203"/>
-      <c r="AF3" s="202" t="s">
+      <c r="AC3" s="205"/>
+      <c r="AD3" s="205"/>
+      <c r="AE3" s="205"/>
+      <c r="AF3" s="204" t="s">
         <v>48</v>
       </c>
-      <c r="AG3" s="203"/>
-      <c r="AH3" s="203"/>
-      <c r="AI3" s="203"/>
-      <c r="AJ3" s="208" t="s">
+      <c r="AG3" s="205"/>
+      <c r="AH3" s="205"/>
+      <c r="AI3" s="205"/>
+      <c r="AJ3" s="201" t="s">
         <v>51</v>
       </c>
-      <c r="AK3" s="209"/>
-      <c r="AL3" s="209"/>
-      <c r="AM3" s="210"/>
-      <c r="AN3" s="208" t="s">
+      <c r="AK3" s="202"/>
+      <c r="AL3" s="202"/>
+      <c r="AM3" s="203"/>
+      <c r="AN3" s="201" t="s">
         <v>14</v>
       </c>
-      <c r="AO3" s="209"/>
-      <c r="AP3" s="209"/>
-      <c r="AQ3" s="210"/>
-      <c r="AR3" s="208" t="s">
+      <c r="AO3" s="202"/>
+      <c r="AP3" s="202"/>
+      <c r="AQ3" s="203"/>
+      <c r="AR3" s="201" t="s">
         <v>52</v>
       </c>
-      <c r="AS3" s="209"/>
-      <c r="AT3" s="209"/>
-      <c r="AU3" s="210"/>
-      <c r="AV3" s="203" t="s">
+      <c r="AS3" s="202"/>
+      <c r="AT3" s="202"/>
+      <c r="AU3" s="203"/>
+      <c r="AV3" s="205" t="s">
         <v>16</v>
       </c>
-      <c r="AW3" s="203"/>
-      <c r="AX3" s="203"/>
-      <c r="AY3" s="203"/>
-      <c r="AZ3" s="203" t="s">
+      <c r="AW3" s="205"/>
+      <c r="AX3" s="205"/>
+      <c r="AY3" s="205"/>
+      <c r="AZ3" s="205" t="s">
         <v>54</v>
       </c>
-      <c r="BA3" s="203"/>
-      <c r="BB3" s="203"/>
-      <c r="BC3" s="203"/>
-      <c r="BD3" s="202" t="s">
+      <c r="BA3" s="205"/>
+      <c r="BB3" s="205"/>
+      <c r="BC3" s="205"/>
+      <c r="BD3" s="204" t="s">
         <v>55</v>
       </c>
-      <c r="BE3" s="203"/>
-      <c r="BF3" s="207"/>
-      <c r="BG3" s="203"/>
+      <c r="BE3" s="205"/>
+      <c r="BF3" s="215"/>
+      <c r="BG3" s="205"/>
       <c r="BH3" s="2"/>
       <c r="BI3" s="2"/>
       <c r="BJ3" s="2"/>
@@ -6434,8 +6434,8 @@
       <c r="YY3" s="2"/>
     </row>
     <row r="4" spans="1:675" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="201"/>
-      <c r="B4" s="212"/>
+      <c r="A4" s="211"/>
+      <c r="B4" s="217"/>
       <c r="C4" s="88"/>
       <c r="D4" s="8" t="s">
         <v>2</v>
@@ -7013,7 +7013,7 @@
       </c>
       <c r="AS6" s="129">
         <f>(VLOOKUP(B6,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.68900000000000006</v>
+        <v>0.69010000000000005</v>
       </c>
       <c r="AT6" s="14">
         <f t="shared" si="20"/>
@@ -7021,7 +7021,7 @@
       </c>
       <c r="AU6" s="54">
         <f t="shared" si="21"/>
-        <v>0.28099999999999992</v>
+        <v>0.27989999999999993</v>
       </c>
       <c r="AV6" s="57">
         <f>VLOOKUP(C6,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7246,7 +7246,7 @@
       </c>
       <c r="AS7" s="129">
         <f>(VLOOKUP(B7,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.75019999999999998</v>
+        <v>0.75159999999999993</v>
       </c>
       <c r="AT7" s="14">
         <f t="shared" si="20"/>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="AU7" s="54">
         <f t="shared" si="21"/>
-        <v>0.2198</v>
+        <v>0.21840000000000004</v>
       </c>
       <c r="AV7" s="57">
         <f>VLOOKUP(C7,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="AS9" s="129">
         <f>(VLOOKUP(B9,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.56869999999999998</v>
+        <v>0.57730000000000004</v>
       </c>
       <c r="AT9" s="14">
         <f t="shared" si="20"/>
@@ -7720,7 +7720,7 @@
       </c>
       <c r="AU9" s="54">
         <f t="shared" si="21"/>
-        <v>0.40129999999999999</v>
+        <v>0.39269999999999994</v>
       </c>
       <c r="AV9" s="57">
         <f>VLOOKUP(C9,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7945,7 +7945,7 @@
       </c>
       <c r="AS10" s="129">
         <f>(VLOOKUP(B10,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.55700000000000005</v>
+        <v>0.55869999999999997</v>
       </c>
       <c r="AT10" s="14">
         <f t="shared" si="20"/>
@@ -7953,7 +7953,7 @@
       </c>
       <c r="AU10" s="54">
         <f t="shared" si="21"/>
-        <v>0.41299999999999992</v>
+        <v>0.4113</v>
       </c>
       <c r="AV10" s="57">
         <f>VLOOKUP(C10,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="AS11" s="129">
         <f>(VLOOKUP(B11,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.6412000000000001</v>
+        <v>0.6604000000000001</v>
       </c>
       <c r="AT11" s="14">
         <f t="shared" si="20"/>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="AU11" s="54">
         <f t="shared" si="21"/>
-        <v>0.32879999999999987</v>
+        <v>0.30959999999999988</v>
       </c>
       <c r="AV11" s="57">
         <f>VLOOKUP(C11,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8411,7 +8411,7 @@
       </c>
       <c r="AS12" s="129">
         <f>(VLOOKUP(B12,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.58609999999999995</v>
+        <v>0.59140000000000004</v>
       </c>
       <c r="AT12" s="14">
         <f t="shared" si="20"/>
@@ -8419,7 +8419,7 @@
       </c>
       <c r="AU12" s="54">
         <f t="shared" si="21"/>
-        <v>0.38390000000000002</v>
+        <v>0.37859999999999994</v>
       </c>
       <c r="AV12" s="57">
         <f>VLOOKUP(C12,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8644,7 +8644,7 @@
       </c>
       <c r="AS13" s="129">
         <f>(VLOOKUP(B13,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.77280000000000004</v>
+        <v>0.77370000000000005</v>
       </c>
       <c r="AT13" s="14">
         <f t="shared" si="20"/>
@@ -8652,7 +8652,7 @@
       </c>
       <c r="AU13" s="54">
         <f t="shared" si="21"/>
-        <v>0.19719999999999993</v>
+        <v>0.19629999999999992</v>
       </c>
       <c r="AV13" s="57">
         <f>VLOOKUP(C13,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8877,7 +8877,7 @@
       </c>
       <c r="AS14" s="129">
         <f>(VLOOKUP(B14,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.5756</v>
+        <v>0.57600000000000007</v>
       </c>
       <c r="AT14" s="14">
         <f t="shared" si="20"/>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="AU14" s="54">
         <f t="shared" si="21"/>
-        <v>0.39439999999999997</v>
+        <v>0.39399999999999991</v>
       </c>
       <c r="AV14" s="57">
         <f>VLOOKUP(C14,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="AS16" s="129">
         <f>(VLOOKUP(B16,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.71420000000000006</v>
+        <v>0.72019999999999995</v>
       </c>
       <c r="AT16" s="14">
         <f t="shared" si="20"/>
@@ -9351,7 +9351,7 @@
       </c>
       <c r="AU16" s="54">
         <f t="shared" si="21"/>
-        <v>0.25579999999999992</v>
+        <v>0.24980000000000002</v>
       </c>
       <c r="AV16" s="57">
         <f>VLOOKUP(C16,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="AS17" s="129">
         <f>(VLOOKUP(B17,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.75930000000000009</v>
+        <v>0.76049999999999995</v>
       </c>
       <c r="AT17" s="14">
         <f t="shared" si="20"/>
@@ -9584,7 +9584,7 @@
       </c>
       <c r="AU17" s="54">
         <f t="shared" si="21"/>
-        <v>0.21069999999999989</v>
+        <v>0.20950000000000002</v>
       </c>
       <c r="AV17" s="57">
         <f>VLOOKUP(C17,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -9874,11 +9874,11 @@
       <c r="C19" s="15"/>
       <c r="D19" s="15"/>
       <c r="E19" s="16"/>
-      <c r="F19" s="213">
+      <c r="F19" s="200">
         <f ca="1">TODAY()</f>
         <v>46076</v>
       </c>
-      <c r="G19" s="213"/>
+      <c r="G19" s="200"/>
       <c r="H19" s="90"/>
       <c r="I19" s="91">
         <f ca="1">DAY(F19)</f>
@@ -9891,33 +9891,33 @@
         <f ca="1">I19/J19</f>
         <v>0.74193548387096775</v>
       </c>
-      <c r="L19" s="214" t="s">
+      <c r="L19" s="206" t="s">
         <v>124</v>
       </c>
-      <c r="M19" s="214"/>
-      <c r="N19" s="214"/>
-      <c r="O19" s="214"/>
-      <c r="P19" s="214"/>
-      <c r="Q19" s="214"/>
-      <c r="R19" s="214"/>
-      <c r="S19" s="214"/>
-      <c r="T19" s="214"/>
-      <c r="U19" s="214"/>
-      <c r="V19" s="214"/>
-      <c r="W19" s="214"/>
-      <c r="X19" s="214"/>
-      <c r="Y19" s="214"/>
-      <c r="Z19" s="214"/>
-      <c r="AA19" s="214"/>
-      <c r="AB19" s="214"/>
-      <c r="AC19" s="214"/>
-      <c r="AD19" s="214"/>
-      <c r="AE19" s="214"/>
-      <c r="AF19" s="214"/>
-      <c r="AG19" s="214"/>
-      <c r="AH19" s="214"/>
-      <c r="AI19" s="214"/>
-      <c r="AJ19" s="214"/>
+      <c r="M19" s="206"/>
+      <c r="N19" s="206"/>
+      <c r="O19" s="206"/>
+      <c r="P19" s="206"/>
+      <c r="Q19" s="206"/>
+      <c r="R19" s="206"/>
+      <c r="S19" s="206"/>
+      <c r="T19" s="206"/>
+      <c r="U19" s="206"/>
+      <c r="V19" s="206"/>
+      <c r="W19" s="206"/>
+      <c r="X19" s="206"/>
+      <c r="Y19" s="206"/>
+      <c r="Z19" s="206"/>
+      <c r="AA19" s="206"/>
+      <c r="AB19" s="206"/>
+      <c r="AC19" s="206"/>
+      <c r="AD19" s="206"/>
+      <c r="AE19" s="206"/>
+      <c r="AF19" s="206"/>
+      <c r="AG19" s="206"/>
+      <c r="AH19" s="206"/>
+      <c r="AI19" s="206"/>
+      <c r="AJ19" s="206"/>
       <c r="AK19" s="16"/>
       <c r="AL19" s="32"/>
       <c r="AM19" s="16"/>
@@ -10110,12 +10110,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="AN3:AQ3"/>
-    <mergeCell ref="AF3:AI3"/>
-    <mergeCell ref="L19:AJ19"/>
-    <mergeCell ref="P3:S3"/>
-    <mergeCell ref="T3:W3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="X3:AA3"/>
     <mergeCell ref="AV2:BG2"/>
@@ -10132,6 +10126,12 @@
     <mergeCell ref="D3:G3"/>
     <mergeCell ref="H3:K3"/>
     <mergeCell ref="L3:O3"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="AN3:AQ3"/>
+    <mergeCell ref="AF3:AI3"/>
+    <mergeCell ref="L19:AJ19"/>
+    <mergeCell ref="P3:S3"/>
+    <mergeCell ref="T3:W3"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="C3:C4">
@@ -11351,42 +11351,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:59" s="1" customFormat="1" ht="24.75" x14ac:dyDescent="0.45">
-      <c r="D1" s="211" t="s">
+      <c r="D1" s="216" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="211"/>
-      <c r="F1" s="211"/>
-      <c r="G1" s="211"/>
-      <c r="H1" s="211"/>
-      <c r="I1" s="211"/>
-      <c r="J1" s="211"/>
-      <c r="K1" s="211"/>
-      <c r="L1" s="211"/>
-      <c r="M1" s="211"/>
-      <c r="N1" s="211"/>
-      <c r="O1" s="211"/>
-      <c r="P1" s="211"/>
-      <c r="Q1" s="211"/>
-      <c r="R1" s="211"/>
-      <c r="S1" s="211"/>
-      <c r="T1" s="206" t="s">
+      <c r="E1" s="216"/>
+      <c r="F1" s="216"/>
+      <c r="G1" s="216"/>
+      <c r="H1" s="216"/>
+      <c r="I1" s="216"/>
+      <c r="J1" s="216"/>
+      <c r="K1" s="216"/>
+      <c r="L1" s="216"/>
+      <c r="M1" s="216"/>
+      <c r="N1" s="216"/>
+      <c r="O1" s="216"/>
+      <c r="P1" s="216"/>
+      <c r="Q1" s="216"/>
+      <c r="R1" s="216"/>
+      <c r="S1" s="216"/>
+      <c r="T1" s="214" t="s">
         <v>36</v>
       </c>
-      <c r="U1" s="206"/>
-      <c r="V1" s="206"/>
-      <c r="W1" s="206"/>
-      <c r="X1" s="206"/>
-      <c r="Y1" s="206"/>
-      <c r="Z1" s="206"/>
-      <c r="AA1" s="206"/>
-      <c r="AB1" s="206"/>
-      <c r="AC1" s="206"/>
-      <c r="AD1" s="206"/>
-      <c r="AE1" s="206"/>
-      <c r="AF1" s="206"/>
-      <c r="AG1" s="206"/>
-      <c r="AH1" s="206"/>
-      <c r="AI1" s="206"/>
+      <c r="U1" s="214"/>
+      <c r="V1" s="214"/>
+      <c r="W1" s="214"/>
+      <c r="X1" s="214"/>
+      <c r="Y1" s="214"/>
+      <c r="Z1" s="214"/>
+      <c r="AA1" s="214"/>
+      <c r="AB1" s="214"/>
+      <c r="AC1" s="214"/>
+      <c r="AD1" s="214"/>
+      <c r="AE1" s="214"/>
+      <c r="AF1" s="214"/>
+      <c r="AG1" s="214"/>
+      <c r="AH1" s="214"/>
+      <c r="AI1" s="214"/>
       <c r="AJ1" s="234" t="s">
         <v>37</v>
       </c>
@@ -11419,90 +11419,90 @@
     <row r="2" spans="1:59" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="202" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="203"/>
-      <c r="F2" s="203"/>
-      <c r="G2" s="203"/>
-      <c r="H2" s="202" t="s">
+      <c r="D2" s="204" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="205"/>
+      <c r="F2" s="205"/>
+      <c r="G2" s="205"/>
+      <c r="H2" s="204" t="s">
         <v>40</v>
       </c>
-      <c r="I2" s="203"/>
-      <c r="J2" s="203"/>
-      <c r="K2" s="203"/>
-      <c r="L2" s="202" t="s">
+      <c r="I2" s="205"/>
+      <c r="J2" s="205"/>
+      <c r="K2" s="205"/>
+      <c r="L2" s="204" t="s">
         <v>41</v>
       </c>
-      <c r="M2" s="203"/>
-      <c r="N2" s="203"/>
-      <c r="O2" s="203"/>
-      <c r="P2" s="215" t="s">
+      <c r="M2" s="205"/>
+      <c r="N2" s="205"/>
+      <c r="O2" s="205"/>
+      <c r="P2" s="207" t="s">
         <v>42</v>
       </c>
-      <c r="Q2" s="216"/>
-      <c r="R2" s="216"/>
-      <c r="S2" s="217"/>
-      <c r="T2" s="202" t="s">
+      <c r="Q2" s="208"/>
+      <c r="R2" s="208"/>
+      <c r="S2" s="209"/>
+      <c r="T2" s="204" t="s">
         <v>43</v>
       </c>
-      <c r="U2" s="203"/>
-      <c r="V2" s="203"/>
-      <c r="W2" s="203"/>
-      <c r="X2" s="202" t="s">
+      <c r="U2" s="205"/>
+      <c r="V2" s="205"/>
+      <c r="W2" s="205"/>
+      <c r="X2" s="204" t="s">
         <v>45</v>
       </c>
-      <c r="Y2" s="203"/>
-      <c r="Z2" s="203"/>
-      <c r="AA2" s="203"/>
-      <c r="AB2" s="202" t="s">
+      <c r="Y2" s="205"/>
+      <c r="Z2" s="205"/>
+      <c r="AA2" s="205"/>
+      <c r="AB2" s="204" t="s">
         <v>47</v>
       </c>
-      <c r="AC2" s="203"/>
-      <c r="AD2" s="203"/>
-      <c r="AE2" s="203"/>
-      <c r="AF2" s="202" t="s">
+      <c r="AC2" s="205"/>
+      <c r="AD2" s="205"/>
+      <c r="AE2" s="205"/>
+      <c r="AF2" s="204" t="s">
         <v>48</v>
       </c>
-      <c r="AG2" s="203"/>
-      <c r="AH2" s="203"/>
-      <c r="AI2" s="203"/>
-      <c r="AJ2" s="208" t="s">
+      <c r="AG2" s="205"/>
+      <c r="AH2" s="205"/>
+      <c r="AI2" s="205"/>
+      <c r="AJ2" s="201" t="s">
         <v>51</v>
       </c>
-      <c r="AK2" s="209"/>
-      <c r="AL2" s="209"/>
-      <c r="AM2" s="210"/>
-      <c r="AN2" s="208" t="s">
+      <c r="AK2" s="202"/>
+      <c r="AL2" s="202"/>
+      <c r="AM2" s="203"/>
+      <c r="AN2" s="201" t="s">
         <v>14</v>
       </c>
-      <c r="AO2" s="209"/>
-      <c r="AP2" s="209"/>
-      <c r="AQ2" s="210"/>
-      <c r="AR2" s="208" t="s">
+      <c r="AO2" s="202"/>
+      <c r="AP2" s="202"/>
+      <c r="AQ2" s="203"/>
+      <c r="AR2" s="201" t="s">
         <v>52</v>
       </c>
-      <c r="AS2" s="209"/>
-      <c r="AT2" s="209"/>
-      <c r="AU2" s="210"/>
-      <c r="AV2" s="203" t="s">
+      <c r="AS2" s="202"/>
+      <c r="AT2" s="202"/>
+      <c r="AU2" s="203"/>
+      <c r="AV2" s="205" t="s">
         <v>16</v>
       </c>
-      <c r="AW2" s="203"/>
-      <c r="AX2" s="203"/>
-      <c r="AY2" s="203"/>
-      <c r="AZ2" s="203" t="s">
+      <c r="AW2" s="205"/>
+      <c r="AX2" s="205"/>
+      <c r="AY2" s="205"/>
+      <c r="AZ2" s="205" t="s">
         <v>54</v>
       </c>
-      <c r="BA2" s="203"/>
-      <c r="BB2" s="203"/>
-      <c r="BC2" s="203"/>
-      <c r="BD2" s="202" t="s">
+      <c r="BA2" s="205"/>
+      <c r="BB2" s="205"/>
+      <c r="BC2" s="205"/>
+      <c r="BD2" s="204" t="s">
         <v>55</v>
       </c>
-      <c r="BE2" s="203"/>
-      <c r="BF2" s="207"/>
-      <c r="BG2" s="203"/>
+      <c r="BE2" s="205"/>
+      <c r="BF2" s="215"/>
+      <c r="BG2" s="205"/>
     </row>
     <row r="3" spans="1:59" ht="15" x14ac:dyDescent="0.45">
       <c r="B3" s="8" t="s">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="AS5" s="129">
         <f>(VLOOKUP(B5,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.6412000000000001</v>
+        <v>0.6604000000000001</v>
       </c>
       <c r="AT5" s="14">
         <f t="shared" ref="AT5:AT16" si="48">IF(AS5&lt;94.5%,0,IF(AS5&lt;95.54%,50%,IF(AS5&lt;AR5,80%,100%+(30%*(AS5-AR5)/3.39%))))</f>
@@ -12097,7 +12097,7 @@
       </c>
       <c r="AU5" s="54">
         <f t="shared" ref="AU5:AU16" si="49">AR5-AS5</f>
-        <v>0.32879999999999987</v>
+        <v>0.30959999999999988</v>
       </c>
       <c r="AV5" s="57">
         <f>VLOOKUP(A5,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -12323,7 +12323,7 @@
       </c>
       <c r="AS6" s="129">
         <f>(VLOOKUP(B6,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.58609999999999995</v>
+        <v>0.59140000000000004</v>
       </c>
       <c r="AT6" s="14">
         <f t="shared" si="48"/>
@@ -12331,7 +12331,7 @@
       </c>
       <c r="AU6" s="54">
         <f t="shared" si="49"/>
-        <v>0.38390000000000002</v>
+        <v>0.37859999999999994</v>
       </c>
       <c r="AV6" s="57">
         <f>VLOOKUP(A6,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -12557,7 +12557,7 @@
       </c>
       <c r="AS7" s="129">
         <f>(VLOOKUP(B7,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.5756</v>
+        <v>0.57600000000000007</v>
       </c>
       <c r="AT7" s="14">
         <f t="shared" si="48"/>
@@ -12565,7 +12565,7 @@
       </c>
       <c r="AU7" s="54">
         <f t="shared" si="49"/>
-        <v>0.39439999999999997</v>
+        <v>0.39399999999999991</v>
       </c>
       <c r="AV7" s="57">
         <f>VLOOKUP(A7,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -12791,7 +12791,7 @@
       </c>
       <c r="AS8" s="129">
         <f>(VLOOKUP(B8,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.71420000000000006</v>
+        <v>0.72019999999999995</v>
       </c>
       <c r="AT8" s="14">
         <f t="shared" si="48"/>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="AU8" s="54">
         <f t="shared" si="49"/>
-        <v>0.25579999999999992</v>
+        <v>0.24980000000000002</v>
       </c>
       <c r="AV8" s="57">
         <f>VLOOKUP(A8,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -13086,7 +13086,7 @@
       </c>
       <c r="AS10" s="129">
         <f>(VLOOKUP(B10,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.68900000000000006</v>
+        <v>0.69010000000000005</v>
       </c>
       <c r="AT10" s="14">
         <f t="shared" si="48"/>
@@ -13094,7 +13094,7 @@
       </c>
       <c r="AU10" s="54">
         <f t="shared" si="49"/>
-        <v>0.28099999999999992</v>
+        <v>0.27989999999999993</v>
       </c>
       <c r="AV10" s="57">
         <f>VLOOKUP(A10,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -13320,7 +13320,7 @@
       </c>
       <c r="AS11" s="129">
         <f>(VLOOKUP(B11,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.75019999999999998</v>
+        <v>0.75159999999999993</v>
       </c>
       <c r="AT11" s="14">
         <f t="shared" si="48"/>
@@ -13328,7 +13328,7 @@
       </c>
       <c r="AU11" s="54">
         <f t="shared" si="49"/>
-        <v>0.2198</v>
+        <v>0.21840000000000004</v>
       </c>
       <c r="AV11" s="57">
         <f>VLOOKUP(A11,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -13788,7 +13788,7 @@
       </c>
       <c r="AS13" s="129">
         <f>(VLOOKUP(B13,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.55700000000000005</v>
+        <v>0.55869999999999997</v>
       </c>
       <c r="AT13" s="14">
         <f t="shared" si="48"/>
@@ -13796,7 +13796,7 @@
       </c>
       <c r="AU13" s="54">
         <f t="shared" si="49"/>
-        <v>0.41299999999999992</v>
+        <v>0.4113</v>
       </c>
       <c r="AV13" s="57">
         <f>VLOOKUP(A13,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -14022,7 +14022,7 @@
       </c>
       <c r="AS14" s="129">
         <f>(VLOOKUP(B14,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.77280000000000004</v>
+        <v>0.77370000000000005</v>
       </c>
       <c r="AT14" s="14">
         <f t="shared" si="48"/>
@@ -14030,7 +14030,7 @@
       </c>
       <c r="AU14" s="54">
         <f t="shared" si="49"/>
-        <v>0.19719999999999993</v>
+        <v>0.19629999999999992</v>
       </c>
       <c r="AV14" s="57">
         <f>VLOOKUP(A14,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -14490,7 +14490,7 @@
       </c>
       <c r="AS16" s="129">
         <f>(VLOOKUP(B16,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.75930000000000009</v>
+        <v>0.76049999999999995</v>
       </c>
       <c r="AT16" s="14">
         <f t="shared" si="48"/>
@@ -14498,7 +14498,7 @@
       </c>
       <c r="AU16" s="54">
         <f t="shared" si="49"/>
-        <v>0.21069999999999989</v>
+        <v>0.20950000000000002</v>
       </c>
       <c r="AV16" s="57">
         <f>VLOOKUP(A16,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -14582,11 +14582,11 @@
       </c>
       <c r="C19" s="142">
         <f ca="1">SUMIF(cuoc!A7:P27,'tiến độ'!A19,cuoc!M7:M27)</f>
-        <v>426159900</v>
+        <v>430079987</v>
       </c>
       <c r="D19" s="142">
         <f ca="1">B19*0.968-C19</f>
-        <v>197014171.25599992</v>
+        <v>193094084.25599992</v>
       </c>
       <c r="E19" s="137"/>
       <c r="H19" s="137"/>
@@ -14603,11 +14603,11 @@
       </c>
       <c r="C20" s="143">
         <f ca="1">SUMIF(cuoc!A8:P27,'tiến độ'!A20,cuoc!M8:M27)</f>
-        <v>688184642</v>
+        <v>689131159</v>
       </c>
       <c r="D20" s="142">
         <f ca="1">B20*0.968-C20</f>
-        <v>255799284.77600002</v>
+        <v>254852767.77600002</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.45">
@@ -14793,11 +14793,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="D1:S1"/>
-    <mergeCell ref="D2:G2"/>
-    <mergeCell ref="H2:K2"/>
-    <mergeCell ref="L2:O2"/>
-    <mergeCell ref="P2:S2"/>
     <mergeCell ref="X2:AA2"/>
     <mergeCell ref="AB2:AE2"/>
     <mergeCell ref="AF2:AI2"/>
@@ -14811,6 +14806,11 @@
     <mergeCell ref="AJ2:AM2"/>
     <mergeCell ref="AN2:AQ2"/>
     <mergeCell ref="T2:W2"/>
+    <mergeCell ref="D1:S1"/>
+    <mergeCell ref="D2:G2"/>
+    <mergeCell ref="H2:K2"/>
+    <mergeCell ref="L2:O2"/>
+    <mergeCell ref="P2:S2"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="F4:F16">
@@ -23286,12 +23286,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="X5:AE5"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="H5:O5"/>
-    <mergeCell ref="P5:W5"/>
     <mergeCell ref="CB5:CI5"/>
     <mergeCell ref="CJ5:CQ5"/>
     <mergeCell ref="CR5:CY5"/>
@@ -23302,6 +23296,12 @@
     <mergeCell ref="BD5:BK5"/>
     <mergeCell ref="BL5:BS5"/>
     <mergeCell ref="BT5:CA5"/>
+    <mergeCell ref="X5:AE5"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="H5:O5"/>
+    <mergeCell ref="P5:W5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -23399,7 +23399,7 @@
       <c r="A3" s="100" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="243" t="s">
+      <c r="B3" s="245" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="101" t="s">
@@ -23411,70 +23411,70 @@
       <c r="E3" s="247" t="s">
         <v>202</v>
       </c>
-      <c r="F3" s="245" t="s">
+      <c r="F3" s="243" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="245" t="s">
+      <c r="G3" s="243" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="245" t="s">
+      <c r="H3" s="243" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="245" t="s">
+      <c r="I3" s="243" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="245" t="s">
+      <c r="J3" s="243" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="245" t="s">
+      <c r="K3" s="243" t="s">
         <v>11</v>
       </c>
-      <c r="L3" s="245" t="s">
+      <c r="L3" s="243" t="s">
         <v>12</v>
       </c>
-      <c r="M3" s="245" t="s">
+      <c r="M3" s="243" t="s">
         <v>203</v>
       </c>
-      <c r="N3" s="245" t="s">
+      <c r="N3" s="243" t="s">
         <v>286</v>
       </c>
-      <c r="O3" s="245" t="s">
+      <c r="O3" s="243" t="s">
         <v>14</v>
       </c>
-      <c r="P3" s="245" t="s">
+      <c r="P3" s="243" t="s">
         <v>15</v>
       </c>
-      <c r="Q3" s="245" t="s">
+      <c r="Q3" s="243" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="245" t="s">
+      <c r="R3" s="243" t="s">
         <v>17</v>
       </c>
-      <c r="S3" s="245" t="s">
+      <c r="S3" s="243" t="s">
         <v>18</v>
       </c>
       <c r="T3" s="99"/>
     </row>
     <row r="4" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="100"/>
-      <c r="B4" s="244"/>
+      <c r="B4" s="246"/>
       <c r="C4" s="101"/>
       <c r="D4" s="101"/>
       <c r="E4" s="248"/>
-      <c r="F4" s="246"/>
-      <c r="G4" s="246"/>
-      <c r="H4" s="246"/>
-      <c r="I4" s="246"/>
-      <c r="J4" s="246"/>
-      <c r="K4" s="246"/>
-      <c r="L4" s="246"/>
-      <c r="M4" s="246"/>
-      <c r="N4" s="246"/>
-      <c r="O4" s="246"/>
-      <c r="P4" s="246"/>
-      <c r="Q4" s="246"/>
-      <c r="R4" s="246"/>
-      <c r="S4" s="246"/>
+      <c r="F4" s="244"/>
+      <c r="G4" s="244"/>
+      <c r="H4" s="244"/>
+      <c r="I4" s="244"/>
+      <c r="J4" s="244"/>
+      <c r="K4" s="244"/>
+      <c r="L4" s="244"/>
+      <c r="M4" s="244"/>
+      <c r="N4" s="244"/>
+      <c r="O4" s="244"/>
+      <c r="P4" s="244"/>
+      <c r="Q4" s="244"/>
+      <c r="R4" s="244"/>
+      <c r="S4" s="244"/>
       <c r="T4" s="99"/>
     </row>
     <row r="5" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.45">
@@ -24792,12 +24792,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="S3:S4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="R3:R4"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="H3:H4"/>
@@ -24808,6 +24802,12 @@
     <mergeCell ref="K3:K4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="E3:E4"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="S3:S4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="R3:R4"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.69991251615088756" right="0.69991251615088756" top="0.74990626395218019" bottom="0.74990626395218019" header="0.29996251027415122" footer="0.29996251027415122"/>
@@ -26083,68 +26083,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:48" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="258" t="s">
+      <c r="A1" s="256" t="s">
         <v>240</v>
       </c>
-      <c r="B1" s="258"/>
-      <c r="C1" s="258"/>
-      <c r="D1" s="258"/>
-      <c r="E1" s="258"/>
-      <c r="F1" s="258"/>
-      <c r="G1" s="258"/>
-      <c r="H1" s="258"/>
-      <c r="I1" s="258"/>
-      <c r="J1" s="258"/>
-      <c r="K1" s="258"/>
-      <c r="M1" s="261" t="s">
+      <c r="B1" s="256"/>
+      <c r="C1" s="256"/>
+      <c r="D1" s="256"/>
+      <c r="E1" s="256"/>
+      <c r="F1" s="256"/>
+      <c r="G1" s="256"/>
+      <c r="H1" s="256"/>
+      <c r="I1" s="256"/>
+      <c r="J1" s="256"/>
+      <c r="K1" s="256"/>
+      <c r="M1" s="259" t="s">
         <v>241</v>
       </c>
-      <c r="N1" s="261"/>
-      <c r="O1" s="261"/>
-      <c r="P1" s="261"/>
-      <c r="Q1" s="261"/>
-      <c r="R1" s="261"/>
-      <c r="S1" s="261"/>
-      <c r="T1" s="261"/>
-      <c r="U1" s="261"/>
-      <c r="V1" s="261"/>
-      <c r="W1" s="261"/>
-      <c r="X1" s="261"/>
-      <c r="Y1" s="261"/>
-      <c r="Z1" s="261"/>
+      <c r="N1" s="259"/>
+      <c r="O1" s="259"/>
+      <c r="P1" s="259"/>
+      <c r="Q1" s="259"/>
+      <c r="R1" s="259"/>
+      <c r="S1" s="259"/>
+      <c r="T1" s="259"/>
+      <c r="U1" s="259"/>
+      <c r="V1" s="259"/>
+      <c r="W1" s="259"/>
+      <c r="X1" s="259"/>
+      <c r="Y1" s="259"/>
+      <c r="Z1" s="259"/>
     </row>
     <row r="2" spans="1:48" ht="24.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="259"/>
-      <c r="B2" s="259"/>
-      <c r="C2" s="259"/>
-      <c r="D2" s="259"/>
-      <c r="E2" s="259"/>
-      <c r="F2" s="259"/>
-      <c r="G2" s="259"/>
-      <c r="H2" s="259"/>
-      <c r="I2" s="259"/>
-      <c r="J2" s="259"/>
-      <c r="K2" s="259"/>
-      <c r="M2" s="262"/>
-      <c r="N2" s="262"/>
-      <c r="O2" s="262"/>
-      <c r="P2" s="262"/>
-      <c r="Q2" s="262"/>
-      <c r="R2" s="262"/>
-      <c r="S2" s="262"/>
-      <c r="T2" s="262"/>
-      <c r="U2" s="262"/>
-      <c r="V2" s="262"/>
-      <c r="W2" s="262"/>
-      <c r="X2" s="262"/>
-      <c r="Y2" s="262"/>
-      <c r="Z2" s="262"/>
+      <c r="A2" s="257"/>
+      <c r="B2" s="257"/>
+      <c r="C2" s="257"/>
+      <c r="D2" s="257"/>
+      <c r="E2" s="257"/>
+      <c r="F2" s="257"/>
+      <c r="G2" s="257"/>
+      <c r="H2" s="257"/>
+      <c r="I2" s="257"/>
+      <c r="J2" s="257"/>
+      <c r="K2" s="257"/>
+      <c r="M2" s="260"/>
+      <c r="N2" s="260"/>
+      <c r="O2" s="260"/>
+      <c r="P2" s="260"/>
+      <c r="Q2" s="260"/>
+      <c r="R2" s="260"/>
+      <c r="S2" s="260"/>
+      <c r="T2" s="260"/>
+      <c r="U2" s="260"/>
+      <c r="V2" s="260"/>
+      <c r="W2" s="260"/>
+      <c r="X2" s="260"/>
+      <c r="Y2" s="260"/>
+      <c r="Z2" s="260"/>
     </row>
     <row r="3" spans="1:48" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="255" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="256" t="s">
+      <c r="A3" s="253" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="254" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="28" t="s">
@@ -26174,70 +26174,70 @@
       <c r="K3" s="28" t="s">
         <v>249</v>
       </c>
-      <c r="M3" s="260" t="s">
+      <c r="M3" s="258" t="s">
         <v>34</v>
       </c>
-      <c r="N3" s="202" t="s">
+      <c r="N3" s="204" t="s">
         <v>250</v>
       </c>
-      <c r="O3" s="203"/>
-      <c r="P3" s="203"/>
-      <c r="Q3" s="203"/>
-      <c r="R3" s="253" t="s">
+      <c r="O3" s="205"/>
+      <c r="P3" s="205"/>
+      <c r="Q3" s="205"/>
+      <c r="R3" s="261" t="s">
         <v>251</v>
       </c>
-      <c r="S3" s="202" t="s">
+      <c r="S3" s="204" t="s">
         <v>252</v>
       </c>
-      <c r="T3" s="203"/>
-      <c r="U3" s="203"/>
-      <c r="V3" s="203"/>
-      <c r="W3" s="253" t="s">
+      <c r="T3" s="205"/>
+      <c r="U3" s="205"/>
+      <c r="V3" s="205"/>
+      <c r="W3" s="261" t="s">
         <v>251</v>
       </c>
-      <c r="X3" s="215" t="s">
+      <c r="X3" s="207" t="s">
         <v>41</v>
       </c>
-      <c r="Y3" s="216"/>
-      <c r="Z3" s="216"/>
-      <c r="AA3" s="253" t="s">
+      <c r="Y3" s="208"/>
+      <c r="Z3" s="208"/>
+      <c r="AA3" s="261" t="s">
         <v>251</v>
       </c>
       <c r="AB3" s="71"/>
-      <c r="AC3" s="202" t="s">
+      <c r="AC3" s="204" t="s">
         <v>42</v>
       </c>
-      <c r="AD3" s="203"/>
-      <c r="AE3" s="203"/>
-      <c r="AF3" s="203"/>
-      <c r="AG3" s="202" t="s">
+      <c r="AD3" s="205"/>
+      <c r="AE3" s="205"/>
+      <c r="AF3" s="205"/>
+      <c r="AG3" s="204" t="s">
         <v>43</v>
       </c>
-      <c r="AH3" s="203"/>
-      <c r="AI3" s="203"/>
-      <c r="AJ3" s="203"/>
-      <c r="AK3" s="202" t="s">
+      <c r="AH3" s="205"/>
+      <c r="AI3" s="205"/>
+      <c r="AJ3" s="205"/>
+      <c r="AK3" s="204" t="s">
         <v>44</v>
       </c>
-      <c r="AL3" s="203"/>
-      <c r="AM3" s="203"/>
-      <c r="AN3" s="203"/>
-      <c r="AO3" s="202" t="s">
+      <c r="AL3" s="205"/>
+      <c r="AM3" s="205"/>
+      <c r="AN3" s="205"/>
+      <c r="AO3" s="204" t="s">
         <v>46</v>
       </c>
-      <c r="AP3" s="203"/>
-      <c r="AQ3" s="203"/>
-      <c r="AR3" s="203"/>
-      <c r="AS3" s="202" t="s">
+      <c r="AP3" s="205"/>
+      <c r="AQ3" s="205"/>
+      <c r="AR3" s="205"/>
+      <c r="AS3" s="204" t="s">
         <v>47</v>
       </c>
-      <c r="AT3" s="203"/>
-      <c r="AU3" s="203"/>
-      <c r="AV3" s="203"/>
+      <c r="AT3" s="205"/>
+      <c r="AU3" s="205"/>
+      <c r="AV3" s="205"/>
     </row>
     <row r="4" spans="1:48" ht="22.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="255"/>
-      <c r="B4" s="257"/>
+      <c r="A4" s="253"/>
+      <c r="B4" s="255"/>
       <c r="C4" s="24">
         <f t="shared" ref="C4:K4" si="0">SUM(C5:C19)</f>
         <v>15</v>
@@ -26274,7 +26274,7 @@
         <f t="shared" si="0"/>
         <v>134</v>
       </c>
-      <c r="M4" s="260"/>
+      <c r="M4" s="258"/>
       <c r="N4" s="8" t="s">
         <v>2</v>
       </c>
@@ -26287,7 +26287,7 @@
       <c r="Q4" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="R4" s="254"/>
+      <c r="R4" s="262"/>
       <c r="S4" s="8" t="s">
         <v>2</v>
       </c>
@@ -26300,7 +26300,7 @@
       <c r="V4" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="W4" s="254"/>
+      <c r="W4" s="262"/>
       <c r="X4" s="8" t="s">
         <v>2</v>
       </c>
@@ -26310,7 +26310,7 @@
       <c r="Z4" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="AA4" s="254"/>
+      <c r="AA4" s="262"/>
       <c r="AB4" s="51" t="s">
         <v>59</v>
       </c>
@@ -28699,12 +28699,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="A1:K2"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="N3:Q3"/>
-    <mergeCell ref="M1:Z2"/>
     <mergeCell ref="AS3:AV3"/>
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="W3:W4"/>
@@ -28715,6 +28709,12 @@
     <mergeCell ref="AK3:AN3"/>
     <mergeCell ref="AO3:AR3"/>
     <mergeCell ref="S3:V3"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="A1:K2"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="N3:Q3"/>
+    <mergeCell ref="M1:Z2"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="P5:P20">
@@ -28854,44 +28854,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="265"/>
-      <c r="B1" s="265"/>
-      <c r="C1" s="265"/>
-      <c r="D1" s="265"/>
-      <c r="E1" s="265"/>
-      <c r="F1" s="265"/>
-      <c r="G1" s="265"/>
-      <c r="H1" s="265"/>
-      <c r="I1" s="265"/>
-      <c r="J1" s="265"/>
-      <c r="K1" s="265"/>
-      <c r="L1" s="265"/>
-      <c r="M1" s="265"/>
-      <c r="N1" s="265"/>
-      <c r="O1" s="265"/>
-      <c r="P1" s="265"/>
+      <c r="A1" s="263"/>
+      <c r="B1" s="263"/>
+      <c r="C1" s="263"/>
+      <c r="D1" s="263"/>
+      <c r="E1" s="263"/>
+      <c r="F1" s="263"/>
+      <c r="G1" s="263"/>
+      <c r="H1" s="263"/>
+      <c r="I1" s="263"/>
+      <c r="J1" s="263"/>
+      <c r="K1" s="263"/>
+      <c r="L1" s="263"/>
+      <c r="M1" s="263"/>
+      <c r="N1" s="263"/>
+      <c r="O1" s="263"/>
+      <c r="P1" s="263"/>
     </row>
     <row r="2" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="266"/>
-      <c r="B2" s="266"/>
-      <c r="C2" s="266"/>
-      <c r="D2" s="266"/>
-      <c r="E2" s="266"/>
-      <c r="F2" s="266"/>
-      <c r="G2" s="266"/>
-      <c r="H2" s="266"/>
-      <c r="I2" s="266"/>
-      <c r="J2" s="266"/>
-      <c r="K2" s="266"/>
-      <c r="L2" s="266"/>
-      <c r="M2" s="266"/>
-      <c r="N2" s="266"/>
-      <c r="O2" s="266"/>
-      <c r="P2" s="266"/>
+      <c r="A2" s="264"/>
+      <c r="B2" s="264"/>
+      <c r="C2" s="264"/>
+      <c r="D2" s="264"/>
+      <c r="E2" s="264"/>
+      <c r="F2" s="264"/>
+      <c r="G2" s="264"/>
+      <c r="H2" s="264"/>
+      <c r="I2" s="264"/>
+      <c r="J2" s="264"/>
+      <c r="K2" s="264"/>
+      <c r="L2" s="264"/>
+      <c r="M2" s="264"/>
+      <c r="N2" s="264"/>
+      <c r="O2" s="264"/>
+      <c r="P2" s="264"/>
     </row>
     <row r="3" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="267"/>
-      <c r="B3" s="267"/>
+      <c r="A3" s="265"/>
+      <c r="B3" s="265"/>
       <c r="C3" s="133"/>
       <c r="D3" s="133"/>
       <c r="E3" s="133"/>
@@ -28908,10 +28908,10 @@
       <c r="P3" s="133"/>
     </row>
     <row r="4" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="269" t="s">
+      <c r="A4" s="267" t="s">
         <v>255</v>
       </c>
-      <c r="B4" s="269" t="s">
+      <c r="B4" s="267" t="s">
         <v>39</v>
       </c>
       <c r="C4" s="141"/>
@@ -28919,70 +28919,70 @@
       <c r="E4" s="141"/>
       <c r="F4" s="141"/>
       <c r="G4" s="141"/>
-      <c r="H4" s="268"/>
-      <c r="I4" s="268"/>
-      <c r="J4" s="268"/>
-      <c r="K4" s="268"/>
-      <c r="L4" s="268"/>
-      <c r="M4" s="268"/>
-      <c r="N4" s="268"/>
-      <c r="O4" s="268"/>
-      <c r="P4" s="268"/>
+      <c r="H4" s="266"/>
+      <c r="I4" s="266"/>
+      <c r="J4" s="266"/>
+      <c r="K4" s="266"/>
+      <c r="L4" s="266"/>
+      <c r="M4" s="266"/>
+      <c r="N4" s="266"/>
+      <c r="O4" s="266"/>
+      <c r="P4" s="266"/>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A5" s="272"/>
-      <c r="B5" s="272"/>
-      <c r="C5" s="269" t="s">
+      <c r="A5" s="270"/>
+      <c r="B5" s="270"/>
+      <c r="C5" s="267" t="s">
         <v>256</v>
       </c>
-      <c r="D5" s="269" t="s">
+      <c r="D5" s="267" t="s">
         <v>257</v>
       </c>
-      <c r="E5" s="270"/>
-      <c r="F5" s="269" t="s">
+      <c r="E5" s="268"/>
+      <c r="F5" s="267" t="s">
         <v>258</v>
       </c>
-      <c r="G5" s="270"/>
-      <c r="H5" s="269" t="s">
+      <c r="G5" s="268"/>
+      <c r="H5" s="267" t="s">
         <v>259</v>
       </c>
-      <c r="I5" s="270"/>
-      <c r="J5" s="269" t="s">
+      <c r="I5" s="268"/>
+      <c r="J5" s="267" t="s">
         <v>260</v>
       </c>
-      <c r="K5" s="270"/>
-      <c r="L5" s="273" t="s">
+      <c r="K5" s="268"/>
+      <c r="L5" s="271" t="s">
         <v>261</v>
       </c>
-      <c r="M5" s="270"/>
-      <c r="N5" s="268" t="s">
+      <c r="M5" s="268"/>
+      <c r="N5" s="266" t="s">
         <v>262</v>
       </c>
-      <c r="O5" s="274"/>
-      <c r="P5" s="269" t="s">
+      <c r="O5" s="272"/>
+      <c r="P5" s="267" t="s">
         <v>266</v>
       </c>
-      <c r="R5" s="263" t="s">
+      <c r="R5" s="273" t="s">
         <v>34</v>
       </c>
-      <c r="S5" s="263" t="s">
+      <c r="S5" s="273" t="s">
         <v>290</v>
       </c>
-      <c r="T5" s="263" t="s">
+      <c r="T5" s="273" t="s">
         <v>291</v>
       </c>
-      <c r="U5" s="263" t="s">
+      <c r="U5" s="273" t="s">
         <v>293</v>
       </c>
-      <c r="V5" s="264" t="s">
+      <c r="V5" s="274" t="s">
         <v>292</v>
       </c>
       <c r="W5" s="172"/>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A6" s="271"/>
-      <c r="B6" s="271"/>
-      <c r="C6" s="272"/>
+      <c r="A6" s="269"/>
+      <c r="B6" s="269"/>
+      <c r="C6" s="270"/>
       <c r="D6" s="134" t="s">
         <v>2</v>
       </c>
@@ -29019,12 +29019,12 @@
       <c r="O6" s="134" t="s">
         <v>263</v>
       </c>
-      <c r="P6" s="271"/>
-      <c r="R6" s="263"/>
-      <c r="S6" s="263"/>
-      <c r="T6" s="263"/>
-      <c r="U6" s="263"/>
-      <c r="V6" s="263"/>
+      <c r="P6" s="269"/>
+      <c r="R6" s="273"/>
+      <c r="S6" s="273"/>
+      <c r="T6" s="273"/>
+      <c r="U6" s="273"/>
+      <c r="V6" s="273"/>
       <c r="W6" s="172"/>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.45">
@@ -29056,26 +29056,26 @@
         <v>72573808</v>
       </c>
       <c r="J7" s="191">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K7" s="191">
-        <v>1270896</v>
+        <v>1748413</v>
       </c>
       <c r="L7" s="191">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="M7" s="191">
-        <v>59790292</v>
+        <v>60267809</v>
       </c>
       <c r="N7" s="192">
-        <v>84.1</v>
+        <v>84.79</v>
       </c>
       <c r="O7" s="192">
-        <v>82.39</v>
+        <v>83.04</v>
       </c>
       <c r="P7" s="135">
         <f>I7*0.97-M7</f>
-        <v>10606301.760000005</v>
+        <v>10128784.760000005</v>
       </c>
       <c r="R7" s="173" t="s">
         <v>117</v>
@@ -29089,11 +29089,11 @@
       </c>
       <c r="U7" s="189">
         <f>VLOOKUP(R7,$C$7:$P$27,14,0)</f>
-        <v>26057253.799999997</v>
+        <v>25447380.799999997</v>
       </c>
       <c r="V7" s="175">
         <f>VLOOKUP(R7,$C$7:$P$27,14,0)-T7</f>
-        <v>-1676585</v>
+        <v>-2286458</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.45">
@@ -29125,26 +29125,26 @@
         <v>70243418</v>
       </c>
       <c r="J8" s="194">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K8" s="194">
-        <v>1586389</v>
+        <v>2075389</v>
       </c>
       <c r="L8" s="194">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="M8" s="194">
-        <v>56859865</v>
+        <v>57348865</v>
       </c>
       <c r="N8" s="195">
-        <v>78.849999999999994</v>
+        <v>79.3</v>
       </c>
       <c r="O8" s="195">
-        <v>80.95</v>
+        <v>81.64</v>
       </c>
       <c r="P8" s="135">
         <f t="shared" ref="P8:P27" si="0">I8*0.97-M8</f>
-        <v>11276250.459999993</v>
+        <v>10787250.459999993</v>
       </c>
       <c r="R8" s="173" t="s">
         <v>67</v>
@@ -29227,11 +29227,11 @@
       </c>
       <c r="U9" s="189">
         <f t="shared" si="2"/>
-        <v>46511764.270000011</v>
+        <v>43804298.270000011</v>
       </c>
       <c r="V9" s="175">
         <f t="shared" si="3"/>
-        <v>-2578251</v>
+        <v>-5285717</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.45">
@@ -29296,11 +29296,11 @@
       </c>
       <c r="U10" s="189">
         <f t="shared" si="2"/>
-        <v>58912775.859999985</v>
+        <v>58862085.859999985</v>
       </c>
       <c r="V10" s="175">
         <f t="shared" si="3"/>
-        <v>-2170543</v>
+        <v>-2221233</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.45">
@@ -29332,26 +29332,26 @@
         <v>180440547</v>
       </c>
       <c r="J11" s="191">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K11" s="191">
-        <v>6929191</v>
+        <v>7089191</v>
       </c>
       <c r="L11" s="191">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="M11" s="191">
-        <v>139450047</v>
+        <v>139610047</v>
       </c>
       <c r="N11" s="192">
-        <v>75.099999999999994</v>
+        <v>75.19</v>
       </c>
       <c r="O11" s="192">
-        <v>77.28</v>
+        <v>77.37</v>
       </c>
       <c r="P11" s="135">
         <f t="shared" si="0"/>
-        <v>35577283.590000004</v>
+        <v>35417283.590000004</v>
       </c>
       <c r="R11" s="173" t="s">
         <v>99</v>
@@ -29365,11 +29365,11 @@
       </c>
       <c r="U11" s="189">
         <f t="shared" si="2"/>
-        <v>40670886.75</v>
+        <v>40118828.75</v>
       </c>
       <c r="V11" s="175">
         <f t="shared" si="3"/>
-        <v>-497000</v>
+        <v>-1049058</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.45">
@@ -29401,26 +29401,26 @@
         <v>93597302</v>
       </c>
       <c r="J12" s="194">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K12" s="194">
-        <v>2342270</v>
+        <v>2492570</v>
       </c>
       <c r="L12" s="194">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M12" s="194">
-        <v>71900352</v>
+        <v>72050652</v>
       </c>
       <c r="N12" s="195">
-        <v>75.13</v>
+        <v>75.31</v>
       </c>
       <c r="O12" s="195">
-        <v>76.819999999999993</v>
+        <v>76.98</v>
       </c>
       <c r="P12" s="135">
         <f t="shared" si="0"/>
-        <v>18889030.939999998</v>
+        <v>18738730.939999998</v>
       </c>
       <c r="R12" s="173" t="s">
         <v>75</v>
@@ -29434,11 +29434,11 @@
       </c>
       <c r="U12" s="189">
         <f t="shared" si="2"/>
-        <v>33601046.520000011</v>
+        <v>33386091.520000011</v>
       </c>
       <c r="V12" s="175">
         <f t="shared" si="3"/>
-        <v>-2829279</v>
+        <v>-3044234</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.45">
@@ -29470,26 +29470,26 @@
         <v>116427734</v>
       </c>
       <c r="J13" s="191">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K13" s="191">
-        <v>2087490</v>
+        <v>2287490</v>
       </c>
       <c r="L13" s="191">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M13" s="191">
-        <v>88977976</v>
+        <v>89177976</v>
       </c>
       <c r="N13" s="192">
-        <v>74.16</v>
+        <v>74.3</v>
       </c>
       <c r="O13" s="192">
-        <v>76.42</v>
+        <v>76.599999999999994</v>
       </c>
       <c r="P13" s="135">
         <f t="shared" si="0"/>
-        <v>23956925.980000004</v>
+        <v>23756925.980000004</v>
       </c>
       <c r="R13" s="173" t="s">
         <v>107</v>
@@ -29503,11 +29503,11 @@
       </c>
       <c r="U13" s="189">
         <f t="shared" si="2"/>
-        <v>35577283.590000004</v>
+        <v>35417283.590000004</v>
       </c>
       <c r="V13" s="175">
         <f t="shared" si="3"/>
-        <v>-5909796</v>
+        <v>-6069796</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.45">
@@ -29539,26 +29539,26 @@
         <v>189656153</v>
       </c>
       <c r="J14" s="194">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K14" s="194">
-        <v>4245520</v>
+        <v>4472082</v>
       </c>
       <c r="L14" s="194">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="M14" s="194">
-        <v>144005695</v>
+        <v>144232257</v>
       </c>
       <c r="N14" s="195">
-        <v>74.09</v>
+        <v>74.260000000000005</v>
       </c>
       <c r="O14" s="195">
-        <v>75.930000000000007</v>
+        <v>76.05</v>
       </c>
       <c r="P14" s="135">
         <f t="shared" si="0"/>
-        <v>39960773.409999996</v>
+        <v>39734211.409999996</v>
       </c>
       <c r="R14" s="174" t="s">
         <v>72</v>
@@ -29572,11 +29572,11 @@
       </c>
       <c r="U14" s="189">
         <f t="shared" si="2"/>
-        <v>45616717.199999988</v>
+        <v>45436717.199999988</v>
       </c>
       <c r="V14" s="175">
         <f t="shared" si="3"/>
-        <v>-5371081</v>
+        <v>-5551081</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.45">
@@ -29608,26 +29608,26 @@
         <v>152862316</v>
       </c>
       <c r="J15" s="191">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K15" s="191">
-        <v>2994402</v>
+        <v>3209357</v>
       </c>
       <c r="L15" s="191">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="M15" s="191">
-        <v>114675400</v>
+        <v>114890355</v>
       </c>
       <c r="N15" s="192">
-        <v>71.2</v>
+        <v>71.31</v>
       </c>
       <c r="O15" s="192">
-        <v>75.02</v>
+        <v>75.16</v>
       </c>
       <c r="P15" s="135">
         <f t="shared" si="0"/>
-        <v>33601046.520000011</v>
+        <v>33386091.520000011</v>
       </c>
       <c r="R15" s="174" t="s">
         <v>113</v>
@@ -29710,11 +29710,11 @@
       </c>
       <c r="U16" s="189">
         <f t="shared" si="2"/>
-        <v>39960773.409999996</v>
+        <v>39734211.409999996</v>
       </c>
       <c r="V16" s="175">
         <f t="shared" si="3"/>
-        <v>-3488203</v>
+        <v>-3714765</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.45">
@@ -29746,26 +29746,26 @@
         <v>53605661</v>
       </c>
       <c r="J17" s="191">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K17" s="191">
-        <v>1499682</v>
+        <v>1679682</v>
       </c>
       <c r="L17" s="191">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M17" s="191">
-        <v>39064880</v>
+        <v>39244880</v>
       </c>
       <c r="N17" s="192">
-        <v>68.260000000000005</v>
+        <v>68.540000000000006</v>
       </c>
       <c r="O17" s="192">
-        <v>72.87</v>
+        <v>73.209999999999994</v>
       </c>
       <c r="P17" s="135">
         <f t="shared" si="0"/>
-        <v>12932611.170000002</v>
+        <v>12752611.170000002</v>
       </c>
       <c r="R17" s="173" t="s">
         <v>84</v>
@@ -29779,11 +29779,11 @@
       </c>
       <c r="U17" s="189">
         <f t="shared" si="2"/>
-        <v>39390642.670000002</v>
+        <v>39225642.670000002</v>
       </c>
       <c r="V17" s="175">
         <f t="shared" si="3"/>
-        <v>-4027185</v>
+        <v>-4192185</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.45">
@@ -29815,26 +29815,26 @@
         <v>101866340</v>
       </c>
       <c r="J18" s="194">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K18" s="194">
-        <v>1676585</v>
+        <v>2286458</v>
       </c>
       <c r="L18" s="194">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="M18" s="194">
-        <v>72753096</v>
+        <v>73362969</v>
       </c>
       <c r="N18" s="195">
-        <v>68.38</v>
+        <v>68.849999999999994</v>
       </c>
       <c r="O18" s="195">
-        <v>71.42</v>
+        <v>72.02</v>
       </c>
       <c r="P18" s="135">
         <f t="shared" si="0"/>
-        <v>26057253.799999997</v>
+        <v>25447380.799999997</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.45">
@@ -29866,26 +29866,26 @@
         <v>50351985</v>
       </c>
       <c r="J19" s="191">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K19" s="191">
-        <v>830903</v>
+        <v>995412</v>
       </c>
       <c r="L19" s="191">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M19" s="191">
-        <v>35528139</v>
+        <v>35692648</v>
       </c>
       <c r="N19" s="192">
-        <v>67.3</v>
+        <v>67.61</v>
       </c>
       <c r="O19" s="192">
-        <v>70.56</v>
+        <v>70.89</v>
       </c>
       <c r="P19" s="135">
         <f t="shared" si="0"/>
-        <v>13313286.449999996</v>
+        <v>13148777.449999996</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.45">
@@ -29917,43 +29917,43 @@
         <v>162344260</v>
       </c>
       <c r="J20" s="194">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K20" s="194">
-        <v>6157518</v>
+        <v>6337518</v>
       </c>
       <c r="L20" s="194">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="M20" s="194">
-        <v>111857215</v>
+        <v>112037215</v>
       </c>
       <c r="N20" s="195">
-        <v>67.67</v>
+        <v>67.77</v>
       </c>
       <c r="O20" s="195">
-        <v>68.900000000000006</v>
+        <v>69.010000000000005</v>
       </c>
       <c r="P20" s="135">
         <f t="shared" si="0"/>
-        <v>45616717.199999988</v>
+        <v>45436717.199999988</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A21" s="190" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B21" s="190" t="s">
-        <v>112</v>
+        <v>86</v>
       </c>
       <c r="C21" s="190" t="s">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="D21" s="191">
-        <v>1198</v>
+        <v>853</v>
       </c>
       <c r="E21" s="191">
-        <v>194517020</v>
+        <v>141474291</v>
       </c>
       <c r="F21" s="191">
         <v>0</v>
@@ -29962,49 +29962,49 @@
         <v>0</v>
       </c>
       <c r="H21" s="191">
-        <v>1198</v>
+        <v>853</v>
       </c>
       <c r="I21" s="191">
-        <v>194517020</v>
+        <v>141474291</v>
       </c>
       <c r="J21" s="191">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="K21" s="191">
-        <v>3442175</v>
+        <v>5519149</v>
       </c>
       <c r="L21" s="191">
-        <v>753</v>
+        <v>552</v>
       </c>
       <c r="M21" s="191">
-        <v>125078308</v>
+        <v>93425764</v>
       </c>
       <c r="N21" s="192">
-        <v>62.85</v>
+        <v>64.709999999999994</v>
       </c>
       <c r="O21" s="192">
-        <v>64.3</v>
+        <v>66.040000000000006</v>
       </c>
       <c r="P21" s="135">
         <f t="shared" si="0"/>
-        <v>63603201.400000006</v>
+        <v>43804298.270000011</v>
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A22" s="193" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B22" s="193" t="s">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="C22" s="193" t="s">
-        <v>87</v>
+        <v>113</v>
       </c>
       <c r="D22" s="194">
-        <v>853</v>
+        <v>1198</v>
       </c>
       <c r="E22" s="194">
-        <v>141474291</v>
+        <v>194517020</v>
       </c>
       <c r="F22" s="194">
         <v>0</v>
@@ -30013,32 +30013,32 @@
         <v>0</v>
       </c>
       <c r="H22" s="194">
-        <v>853</v>
+        <v>1198</v>
       </c>
       <c r="I22" s="194">
-        <v>141474291</v>
+        <v>194517020</v>
       </c>
       <c r="J22" s="194">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="K22" s="194">
-        <v>2811683</v>
+        <v>3442175</v>
       </c>
       <c r="L22" s="194">
-        <v>536</v>
+        <v>753</v>
       </c>
       <c r="M22" s="194">
-        <v>90718298</v>
+        <v>125078308</v>
       </c>
       <c r="N22" s="195">
-        <v>62.84</v>
+        <v>62.85</v>
       </c>
       <c r="O22" s="195">
-        <v>64.12</v>
+        <v>64.3</v>
       </c>
       <c r="P22" s="135">
         <f t="shared" si="0"/>
-        <v>46511764.270000011</v>
+        <v>63603201.400000006</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.45">
@@ -30070,43 +30070,43 @@
         <v>105953075</v>
       </c>
       <c r="J23" s="191">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K23" s="191">
-        <v>497000</v>
+        <v>1049058</v>
       </c>
       <c r="L23" s="191">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="M23" s="191">
-        <v>62103596</v>
+        <v>62655654</v>
       </c>
       <c r="N23" s="192">
-        <v>57.64</v>
+        <v>58.08</v>
       </c>
       <c r="O23" s="192">
-        <v>58.61</v>
+        <v>59.14</v>
       </c>
       <c r="P23" s="135">
         <f t="shared" si="0"/>
-        <v>40670886.75</v>
+        <v>40118828.75</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A24" s="193" t="s">
-        <v>128</v>
+        <v>288</v>
       </c>
       <c r="B24" s="193" t="s">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="C24" s="193" t="s">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="D24" s="194">
-        <v>892</v>
+        <v>546</v>
       </c>
       <c r="E24" s="194">
-        <v>149379338</v>
+        <v>89879995</v>
       </c>
       <c r="F24" s="194">
         <v>0</v>
@@ -30115,49 +30115,49 @@
         <v>0</v>
       </c>
       <c r="H24" s="194">
-        <v>892</v>
+        <v>546</v>
       </c>
       <c r="I24" s="194">
-        <v>149379338</v>
+        <v>89879995</v>
       </c>
       <c r="J24" s="194">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K24" s="194">
-        <v>2277037</v>
+        <v>3026875</v>
       </c>
       <c r="L24" s="194">
-        <v>518</v>
+        <v>304</v>
       </c>
       <c r="M24" s="194">
-        <v>85985182</v>
+        <v>51886461</v>
       </c>
       <c r="N24" s="195">
-        <v>58.07</v>
+        <v>55.68</v>
       </c>
       <c r="O24" s="195">
-        <v>57.56</v>
+        <v>57.73</v>
       </c>
       <c r="P24" s="135">
         <f t="shared" si="0"/>
-        <v>58912775.859999985</v>
+        <v>35297134.149999991</v>
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A25" s="190" t="s">
-        <v>288</v>
+        <v>128</v>
       </c>
       <c r="B25" s="190" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="C25" s="190" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="D25" s="191">
-        <v>546</v>
+        <v>892</v>
       </c>
       <c r="E25" s="191">
-        <v>89879995</v>
+        <v>149379338</v>
       </c>
       <c r="F25" s="191">
         <v>0</v>
@@ -30166,32 +30166,32 @@
         <v>0</v>
       </c>
       <c r="H25" s="191">
-        <v>546</v>
+        <v>892</v>
       </c>
       <c r="I25" s="191">
-        <v>89879995</v>
+        <v>149379338</v>
       </c>
       <c r="J25" s="191">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K25" s="191">
-        <v>2253084</v>
+        <v>2327727</v>
       </c>
       <c r="L25" s="191">
-        <v>299</v>
+        <v>519</v>
       </c>
       <c r="M25" s="191">
-        <v>51112670</v>
+        <v>86035872</v>
       </c>
       <c r="N25" s="192">
-        <v>54.76</v>
+        <v>58.18</v>
       </c>
       <c r="O25" s="192">
-        <v>56.87</v>
+        <v>57.6</v>
       </c>
       <c r="P25" s="135">
         <f t="shared" si="0"/>
-        <v>36070925.149999991</v>
+        <v>58862085.859999985</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.45">
@@ -30223,26 +30223,26 @@
         <v>95369711</v>
       </c>
       <c r="J26" s="194">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K26" s="194">
-        <v>4127185</v>
+        <v>4292185</v>
       </c>
       <c r="L26" s="194">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M26" s="194">
-        <v>53117977</v>
+        <v>53282977</v>
       </c>
       <c r="N26" s="195">
-        <v>53.91</v>
+        <v>54.08</v>
       </c>
       <c r="O26" s="195">
-        <v>55.7</v>
+        <v>55.87</v>
       </c>
       <c r="P26" s="135">
         <f t="shared" si="0"/>
-        <v>39390642.670000002</v>
+        <v>39225642.670000002</v>
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.45">
@@ -30298,6 +30298,11 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="U5:U6"/>
+    <mergeCell ref="V5:V6"/>
+    <mergeCell ref="R5:R6"/>
+    <mergeCell ref="S5:S6"/>
+    <mergeCell ref="T5:T6"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
     <mergeCell ref="A3:B3"/>
@@ -30312,11 +30317,6 @@
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="L5:M5"/>
     <mergeCell ref="N5:O5"/>
-    <mergeCell ref="U5:U6"/>
-    <mergeCell ref="V5:V6"/>
-    <mergeCell ref="R5:R6"/>
-    <mergeCell ref="S5:S6"/>
-    <mergeCell ref="T5:T6"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="P7:P27">

--- a/filetiendo.xlsx
+++ b/filetiendo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\viettel 2026\thang 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{744DBD91-03DD-4D93-AEBF-AF9AB4EB2C3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D30356FE-07CC-475B-9035-AE788864ECBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="808" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4556,41 +4556,17 @@
     <xf numFmtId="0" fontId="66" fillId="0" borderId="109" xfId="11" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="109" xfId="11" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="177" xfId="11" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="50" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="135" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="134" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="133" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="50" fillId="5" borderId="127" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="5" borderId="130" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="128" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="140" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="139" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="138" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="5" borderId="127" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="24" borderId="132" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4604,10 +4580,34 @@
     <xf numFmtId="0" fontId="17" fillId="5" borderId="129" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="135" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="134" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="133" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="16" borderId="136" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="2" borderId="137" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="140" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="139" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="138" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="67" fillId="18" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4679,16 +4679,16 @@
     <xf numFmtId="0" fontId="63" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="47" fillId="5" borderId="152" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="5" borderId="151" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="148" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="147" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="5" borderId="152" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="5" borderId="151" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="51" fillId="5" borderId="150" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4708,6 +4708,12 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="155" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="158" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="157" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="159" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4733,10 +4739,10 @@
     <xf numFmtId="0" fontId="55" fillId="0" borderId="164" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="158" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="69" fillId="29" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="157" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="69" fillId="29" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="45" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4761,12 +4767,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="168" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="69" fillId="29" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="29" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="12">
     <cellStyle name="Comma" xfId="8" builtinId="3"/>
@@ -5656,166 +5656,166 @@
       </c>
     </row>
     <row r="2" spans="1:675" ht="23.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="210" t="s">
+      <c r="A2" s="200" t="s">
         <v>34</v>
       </c>
       <c r="B2" s="86"/>
       <c r="C2" s="15"/>
-      <c r="D2" s="216" t="s">
+      <c r="D2" s="211" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="216"/>
-      <c r="F2" s="216"/>
-      <c r="G2" s="216"/>
-      <c r="H2" s="216"/>
-      <c r="I2" s="216"/>
-      <c r="J2" s="216"/>
-      <c r="K2" s="216"/>
-      <c r="L2" s="216"/>
-      <c r="M2" s="216"/>
-      <c r="N2" s="216"/>
-      <c r="O2" s="216"/>
-      <c r="P2" s="216"/>
-      <c r="Q2" s="216"/>
-      <c r="R2" s="216"/>
-      <c r="S2" s="216"/>
-      <c r="T2" s="214" t="s">
+      <c r="E2" s="211"/>
+      <c r="F2" s="211"/>
+      <c r="G2" s="211"/>
+      <c r="H2" s="211"/>
+      <c r="I2" s="211"/>
+      <c r="J2" s="211"/>
+      <c r="K2" s="211"/>
+      <c r="L2" s="211"/>
+      <c r="M2" s="211"/>
+      <c r="N2" s="211"/>
+      <c r="O2" s="211"/>
+      <c r="P2" s="211"/>
+      <c r="Q2" s="211"/>
+      <c r="R2" s="211"/>
+      <c r="S2" s="211"/>
+      <c r="T2" s="206" t="s">
         <v>36</v>
       </c>
-      <c r="U2" s="214"/>
-      <c r="V2" s="214"/>
-      <c r="W2" s="214"/>
-      <c r="X2" s="214"/>
-      <c r="Y2" s="214"/>
-      <c r="Z2" s="214"/>
-      <c r="AA2" s="214"/>
-      <c r="AB2" s="214"/>
-      <c r="AC2" s="214"/>
-      <c r="AD2" s="214"/>
-      <c r="AE2" s="214"/>
-      <c r="AF2" s="214"/>
-      <c r="AG2" s="214"/>
-      <c r="AH2" s="214"/>
-      <c r="AI2" s="214"/>
-      <c r="AJ2" s="213" t="s">
+      <c r="U2" s="206"/>
+      <c r="V2" s="206"/>
+      <c r="W2" s="206"/>
+      <c r="X2" s="206"/>
+      <c r="Y2" s="206"/>
+      <c r="Z2" s="206"/>
+      <c r="AA2" s="206"/>
+      <c r="AB2" s="206"/>
+      <c r="AC2" s="206"/>
+      <c r="AD2" s="206"/>
+      <c r="AE2" s="206"/>
+      <c r="AF2" s="206"/>
+      <c r="AG2" s="206"/>
+      <c r="AH2" s="206"/>
+      <c r="AI2" s="206"/>
+      <c r="AJ2" s="205" t="s">
         <v>37</v>
       </c>
-      <c r="AK2" s="213"/>
-      <c r="AL2" s="213"/>
-      <c r="AM2" s="213"/>
-      <c r="AN2" s="213"/>
-      <c r="AO2" s="213"/>
-      <c r="AP2" s="213"/>
-      <c r="AQ2" s="213"/>
-      <c r="AR2" s="213"/>
-      <c r="AS2" s="213"/>
-      <c r="AT2" s="213"/>
-      <c r="AU2" s="213"/>
-      <c r="AV2" s="212" t="s">
+      <c r="AK2" s="205"/>
+      <c r="AL2" s="205"/>
+      <c r="AM2" s="205"/>
+      <c r="AN2" s="205"/>
+      <c r="AO2" s="205"/>
+      <c r="AP2" s="205"/>
+      <c r="AQ2" s="205"/>
+      <c r="AR2" s="205"/>
+      <c r="AS2" s="205"/>
+      <c r="AT2" s="205"/>
+      <c r="AU2" s="205"/>
+      <c r="AV2" s="204" t="s">
         <v>38</v>
       </c>
-      <c r="AW2" s="212"/>
-      <c r="AX2" s="212"/>
-      <c r="AY2" s="212"/>
-      <c r="AZ2" s="212"/>
-      <c r="BA2" s="212"/>
-      <c r="BB2" s="212"/>
-      <c r="BC2" s="212"/>
-      <c r="BD2" s="212"/>
-      <c r="BE2" s="212"/>
-      <c r="BF2" s="212"/>
-      <c r="BG2" s="212"/>
+      <c r="AW2" s="204"/>
+      <c r="AX2" s="204"/>
+      <c r="AY2" s="204"/>
+      <c r="AZ2" s="204"/>
+      <c r="BA2" s="204"/>
+      <c r="BB2" s="204"/>
+      <c r="BC2" s="204"/>
+      <c r="BD2" s="204"/>
+      <c r="BE2" s="204"/>
+      <c r="BF2" s="204"/>
+      <c r="BG2" s="204"/>
     </row>
     <row r="3" spans="1:675" s="3" customFormat="1" ht="28.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="210"/>
-      <c r="B3" s="217" t="s">
+      <c r="A3" s="200"/>
+      <c r="B3" s="212" t="s">
         <v>39</v>
       </c>
       <c r="C3" s="87"/>
-      <c r="D3" s="204" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="205"/>
-      <c r="F3" s="205"/>
-      <c r="G3" s="205"/>
-      <c r="H3" s="204" t="s">
+      <c r="D3" s="202" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="203"/>
+      <c r="F3" s="203"/>
+      <c r="G3" s="203"/>
+      <c r="H3" s="202" t="s">
         <v>40</v>
       </c>
-      <c r="I3" s="205"/>
-      <c r="J3" s="205"/>
-      <c r="K3" s="205"/>
-      <c r="L3" s="204" t="s">
+      <c r="I3" s="203"/>
+      <c r="J3" s="203"/>
+      <c r="K3" s="203"/>
+      <c r="L3" s="202" t="s">
         <v>41</v>
       </c>
-      <c r="M3" s="205"/>
-      <c r="N3" s="205"/>
-      <c r="O3" s="205"/>
-      <c r="P3" s="207" t="s">
+      <c r="M3" s="203"/>
+      <c r="N3" s="203"/>
+      <c r="O3" s="203"/>
+      <c r="P3" s="215" t="s">
         <v>42</v>
       </c>
-      <c r="Q3" s="208"/>
-      <c r="R3" s="208"/>
-      <c r="S3" s="209"/>
-      <c r="T3" s="204" t="s">
+      <c r="Q3" s="216"/>
+      <c r="R3" s="216"/>
+      <c r="S3" s="217"/>
+      <c r="T3" s="202" t="s">
         <v>43</v>
       </c>
-      <c r="U3" s="205"/>
-      <c r="V3" s="205"/>
-      <c r="W3" s="205"/>
-      <c r="X3" s="204" t="s">
+      <c r="U3" s="203"/>
+      <c r="V3" s="203"/>
+      <c r="W3" s="203"/>
+      <c r="X3" s="202" t="s">
         <v>45</v>
       </c>
-      <c r="Y3" s="205"/>
-      <c r="Z3" s="205"/>
-      <c r="AA3" s="205"/>
-      <c r="AB3" s="204" t="s">
+      <c r="Y3" s="203"/>
+      <c r="Z3" s="203"/>
+      <c r="AA3" s="203"/>
+      <c r="AB3" s="202" t="s">
         <v>47</v>
       </c>
-      <c r="AC3" s="205"/>
-      <c r="AD3" s="205"/>
-      <c r="AE3" s="205"/>
-      <c r="AF3" s="204" t="s">
+      <c r="AC3" s="203"/>
+      <c r="AD3" s="203"/>
+      <c r="AE3" s="203"/>
+      <c r="AF3" s="202" t="s">
         <v>48</v>
       </c>
-      <c r="AG3" s="205"/>
-      <c r="AH3" s="205"/>
-      <c r="AI3" s="205"/>
-      <c r="AJ3" s="201" t="s">
+      <c r="AG3" s="203"/>
+      <c r="AH3" s="203"/>
+      <c r="AI3" s="203"/>
+      <c r="AJ3" s="208" t="s">
         <v>51</v>
       </c>
-      <c r="AK3" s="202"/>
-      <c r="AL3" s="202"/>
-      <c r="AM3" s="203"/>
-      <c r="AN3" s="201" t="s">
+      <c r="AK3" s="209"/>
+      <c r="AL3" s="209"/>
+      <c r="AM3" s="210"/>
+      <c r="AN3" s="208" t="s">
         <v>14</v>
       </c>
-      <c r="AO3" s="202"/>
-      <c r="AP3" s="202"/>
-      <c r="AQ3" s="203"/>
-      <c r="AR3" s="201" t="s">
+      <c r="AO3" s="209"/>
+      <c r="AP3" s="209"/>
+      <c r="AQ3" s="210"/>
+      <c r="AR3" s="208" t="s">
         <v>52</v>
       </c>
-      <c r="AS3" s="202"/>
-      <c r="AT3" s="202"/>
-      <c r="AU3" s="203"/>
-      <c r="AV3" s="205" t="s">
+      <c r="AS3" s="209"/>
+      <c r="AT3" s="209"/>
+      <c r="AU3" s="210"/>
+      <c r="AV3" s="203" t="s">
         <v>16</v>
       </c>
-      <c r="AW3" s="205"/>
-      <c r="AX3" s="205"/>
-      <c r="AY3" s="205"/>
-      <c r="AZ3" s="205" t="s">
+      <c r="AW3" s="203"/>
+      <c r="AX3" s="203"/>
+      <c r="AY3" s="203"/>
+      <c r="AZ3" s="203" t="s">
         <v>54</v>
       </c>
-      <c r="BA3" s="205"/>
-      <c r="BB3" s="205"/>
-      <c r="BC3" s="205"/>
-      <c r="BD3" s="204" t="s">
+      <c r="BA3" s="203"/>
+      <c r="BB3" s="203"/>
+      <c r="BC3" s="203"/>
+      <c r="BD3" s="202" t="s">
         <v>55</v>
       </c>
-      <c r="BE3" s="205"/>
-      <c r="BF3" s="215"/>
-      <c r="BG3" s="205"/>
+      <c r="BE3" s="203"/>
+      <c r="BF3" s="207"/>
+      <c r="BG3" s="203"/>
       <c r="BH3" s="2"/>
       <c r="BI3" s="2"/>
       <c r="BJ3" s="2"/>
@@ -6434,8 +6434,8 @@
       <c r="YY3" s="2"/>
     </row>
     <row r="4" spans="1:675" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="211"/>
-      <c r="B4" s="217"/>
+      <c r="A4" s="201"/>
+      <c r="B4" s="212"/>
       <c r="C4" s="88"/>
       <c r="D4" s="8" t="s">
         <v>2</v>
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AS5" s="129">
         <f>(VLOOKUP(B5,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.78980000000000006</v>
+        <v>0.79400000000000004</v>
       </c>
       <c r="AT5" s="14">
         <f t="shared" ref="AT5:AT18" si="20">IF(AS5&lt;94.5%,0,IF(AS5&lt;95.54%,50%,IF(AS5&lt;AR5,80%,100%+(30%*(AS5-AR5)/3.39%))))</f>
@@ -6788,7 +6788,7 @@
       </c>
       <c r="AU5" s="54">
         <f t="shared" ref="AU5:AU18" si="21">AR5-AS5</f>
-        <v>0.18019999999999992</v>
+        <v>0.17599999999999993</v>
       </c>
       <c r="AV5" s="57">
         <f>VLOOKUP(C5,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7013,7 +7013,7 @@
       </c>
       <c r="AS6" s="129">
         <f>(VLOOKUP(B6,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.69010000000000005</v>
+        <v>0.70279999999999998</v>
       </c>
       <c r="AT6" s="14">
         <f t="shared" si="20"/>
@@ -7021,7 +7021,7 @@
       </c>
       <c r="AU6" s="54">
         <f t="shared" si="21"/>
-        <v>0.27989999999999993</v>
+        <v>0.26719999999999999</v>
       </c>
       <c r="AV6" s="57">
         <f>VLOOKUP(C6,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7246,7 +7246,7 @@
       </c>
       <c r="AS7" s="129">
         <f>(VLOOKUP(B7,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.75159999999999993</v>
+        <v>0.75800000000000001</v>
       </c>
       <c r="AT7" s="14">
         <f t="shared" si="20"/>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="AU7" s="54">
         <f t="shared" si="21"/>
-        <v>0.21840000000000004</v>
+        <v>0.21199999999999997</v>
       </c>
       <c r="AV7" s="57">
         <f>VLOOKUP(C7,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7479,7 +7479,7 @@
       </c>
       <c r="AS8" s="129">
         <f>(VLOOKUP(B8,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.31659999999999999</v>
+        <v>0.48759999999999998</v>
       </c>
       <c r="AT8" s="14">
         <f t="shared" si="20"/>
@@ -7487,7 +7487,7 @@
       </c>
       <c r="AU8" s="54">
         <f t="shared" si="21"/>
-        <v>0.65339999999999998</v>
+        <v>0.4824</v>
       </c>
       <c r="AV8" s="57">
         <f>VLOOKUP(C8,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="AS9" s="129">
         <f>(VLOOKUP(B9,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.57730000000000004</v>
+        <v>0.62570000000000003</v>
       </c>
       <c r="AT9" s="14">
         <f t="shared" si="20"/>
@@ -7720,7 +7720,7 @@
       </c>
       <c r="AU9" s="54">
         <f t="shared" si="21"/>
-        <v>0.39269999999999994</v>
+        <v>0.34429999999999994</v>
       </c>
       <c r="AV9" s="57">
         <f>VLOOKUP(C9,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7945,7 +7945,7 @@
       </c>
       <c r="AS10" s="129">
         <f>(VLOOKUP(B10,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.55869999999999997</v>
+        <v>0.72040000000000004</v>
       </c>
       <c r="AT10" s="14">
         <f t="shared" si="20"/>
@@ -7953,7 +7953,7 @@
       </c>
       <c r="AU10" s="54">
         <f t="shared" si="21"/>
-        <v>0.4113</v>
+        <v>0.24959999999999993</v>
       </c>
       <c r="AV10" s="57">
         <f>VLOOKUP(C10,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="AS11" s="129">
         <f>(VLOOKUP(B11,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.6604000000000001</v>
+        <v>0.7037000000000001</v>
       </c>
       <c r="AT11" s="14">
         <f t="shared" si="20"/>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="AU11" s="54">
         <f t="shared" si="21"/>
-        <v>0.30959999999999988</v>
+        <v>0.26629999999999987</v>
       </c>
       <c r="AV11" s="57">
         <f>VLOOKUP(C11,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8411,7 +8411,7 @@
       </c>
       <c r="AS12" s="129">
         <f>(VLOOKUP(B12,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.59140000000000004</v>
+        <v>0.67500000000000004</v>
       </c>
       <c r="AT12" s="14">
         <f t="shared" si="20"/>
@@ -8419,7 +8419,7 @@
       </c>
       <c r="AU12" s="54">
         <f t="shared" si="21"/>
-        <v>0.37859999999999994</v>
+        <v>0.29499999999999993</v>
       </c>
       <c r="AV12" s="57">
         <f>VLOOKUP(C12,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8644,7 +8644,7 @@
       </c>
       <c r="AS13" s="129">
         <f>(VLOOKUP(B13,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.77370000000000005</v>
+        <v>0.78879999999999995</v>
       </c>
       <c r="AT13" s="14">
         <f t="shared" si="20"/>
@@ -8652,7 +8652,7 @@
       </c>
       <c r="AU13" s="54">
         <f t="shared" si="21"/>
-        <v>0.19629999999999992</v>
+        <v>0.18120000000000003</v>
       </c>
       <c r="AV13" s="57">
         <f>VLOOKUP(C13,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8877,7 +8877,7 @@
       </c>
       <c r="AS14" s="129">
         <f>(VLOOKUP(B14,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.57600000000000007</v>
+        <v>0.6409999999999999</v>
       </c>
       <c r="AT14" s="14">
         <f t="shared" si="20"/>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="AU14" s="54">
         <f t="shared" si="21"/>
-        <v>0.39399999999999991</v>
+        <v>0.32900000000000007</v>
       </c>
       <c r="AV14" s="57">
         <f>VLOOKUP(C14,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="AS15" s="129">
         <f>(VLOOKUP(B15,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.64300000000000002</v>
+        <v>0.64950000000000008</v>
       </c>
       <c r="AT15" s="14">
         <f t="shared" si="20"/>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="AU15" s="54">
         <f t="shared" si="21"/>
-        <v>0.32699999999999996</v>
+        <v>0.3204999999999999</v>
       </c>
       <c r="AV15" s="57">
         <f>VLOOKUP(C15,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="AS16" s="129">
         <f>(VLOOKUP(B16,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.72019999999999995</v>
+        <v>0.7288</v>
       </c>
       <c r="AT16" s="14">
         <f t="shared" si="20"/>
@@ -9351,7 +9351,7 @@
       </c>
       <c r="AU16" s="54">
         <f t="shared" si="21"/>
-        <v>0.24980000000000002</v>
+        <v>0.24119999999999997</v>
       </c>
       <c r="AV16" s="57">
         <f>VLOOKUP(C16,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="AS17" s="129">
         <f>(VLOOKUP(B17,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.76049999999999995</v>
+        <v>0.76200000000000001</v>
       </c>
       <c r="AT17" s="14">
         <f t="shared" si="20"/>
@@ -9584,7 +9584,7 @@
       </c>
       <c r="AU17" s="54">
         <f t="shared" si="21"/>
-        <v>0.20950000000000002</v>
+        <v>0.20799999999999996</v>
       </c>
       <c r="AV17" s="57">
         <f>VLOOKUP(C17,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -9809,7 +9809,7 @@
       </c>
       <c r="AS18" s="129">
         <f>(VLOOKUP(B18,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.73239999999999994</v>
+        <v>0.73819999999999997</v>
       </c>
       <c r="AT18" s="14">
         <f t="shared" si="20"/>
@@ -9817,7 +9817,7 @@
       </c>
       <c r="AU18" s="54">
         <f t="shared" si="21"/>
-        <v>0.23760000000000003</v>
+        <v>0.23180000000000001</v>
       </c>
       <c r="AV18" s="57">
         <f>VLOOKUP(C18,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -9874,50 +9874,50 @@
       <c r="C19" s="15"/>
       <c r="D19" s="15"/>
       <c r="E19" s="16"/>
-      <c r="F19" s="200">
+      <c r="F19" s="213">
         <f ca="1">TODAY()</f>
-        <v>46076</v>
-      </c>
-      <c r="G19" s="200"/>
+        <v>46077</v>
+      </c>
+      <c r="G19" s="213"/>
       <c r="H19" s="90"/>
       <c r="I19" s="91">
         <f ca="1">DAY(F19)</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J19" s="92">
         <v>31</v>
       </c>
       <c r="K19" s="95">
         <f ca="1">I19/J19</f>
-        <v>0.74193548387096775</v>
-      </c>
-      <c r="L19" s="206" t="s">
+        <v>0.77419354838709675</v>
+      </c>
+      <c r="L19" s="214" t="s">
         <v>124</v>
       </c>
-      <c r="M19" s="206"/>
-      <c r="N19" s="206"/>
-      <c r="O19" s="206"/>
-      <c r="P19" s="206"/>
-      <c r="Q19" s="206"/>
-      <c r="R19" s="206"/>
-      <c r="S19" s="206"/>
-      <c r="T19" s="206"/>
-      <c r="U19" s="206"/>
-      <c r="V19" s="206"/>
-      <c r="W19" s="206"/>
-      <c r="X19" s="206"/>
-      <c r="Y19" s="206"/>
-      <c r="Z19" s="206"/>
-      <c r="AA19" s="206"/>
-      <c r="AB19" s="206"/>
-      <c r="AC19" s="206"/>
-      <c r="AD19" s="206"/>
-      <c r="AE19" s="206"/>
-      <c r="AF19" s="206"/>
-      <c r="AG19" s="206"/>
-      <c r="AH19" s="206"/>
-      <c r="AI19" s="206"/>
-      <c r="AJ19" s="206"/>
+      <c r="M19" s="214"/>
+      <c r="N19" s="214"/>
+      <c r="O19" s="214"/>
+      <c r="P19" s="214"/>
+      <c r="Q19" s="214"/>
+      <c r="R19" s="214"/>
+      <c r="S19" s="214"/>
+      <c r="T19" s="214"/>
+      <c r="U19" s="214"/>
+      <c r="V19" s="214"/>
+      <c r="W19" s="214"/>
+      <c r="X19" s="214"/>
+      <c r="Y19" s="214"/>
+      <c r="Z19" s="214"/>
+      <c r="AA19" s="214"/>
+      <c r="AB19" s="214"/>
+      <c r="AC19" s="214"/>
+      <c r="AD19" s="214"/>
+      <c r="AE19" s="214"/>
+      <c r="AF19" s="214"/>
+      <c r="AG19" s="214"/>
+      <c r="AH19" s="214"/>
+      <c r="AI19" s="214"/>
+      <c r="AJ19" s="214"/>
       <c r="AK19" s="16"/>
       <c r="AL19" s="32"/>
       <c r="AM19" s="16"/>
@@ -10110,6 +10110,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="AN3:AQ3"/>
+    <mergeCell ref="AF3:AI3"/>
+    <mergeCell ref="L19:AJ19"/>
+    <mergeCell ref="P3:S3"/>
+    <mergeCell ref="T3:W3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="X3:AA3"/>
     <mergeCell ref="AV2:BG2"/>
@@ -10126,12 +10132,6 @@
     <mergeCell ref="D3:G3"/>
     <mergeCell ref="H3:K3"/>
     <mergeCell ref="L3:O3"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="AN3:AQ3"/>
-    <mergeCell ref="AF3:AI3"/>
-    <mergeCell ref="L19:AJ19"/>
-    <mergeCell ref="P3:S3"/>
-    <mergeCell ref="T3:W3"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="C3:C4">
@@ -11147,7 +11147,7 @@
       </c>
       <c r="D14" s="74">
         <f>VLOOKUP($B$2,'TH NV'!$A$5:$BG$18,N14,0)</f>
-        <v>0.78980000000000006</v>
+        <v>0.79400000000000004</v>
       </c>
       <c r="E14" s="49" t="e">
         <f>VLOOKUP($B$2,'TH NV'!$A$1:$BG$18,70,0)</f>
@@ -11170,7 +11170,7 @@
       </c>
       <c r="J14" s="65">
         <f t="shared" si="2"/>
-        <v>0.18019999999999992</v>
+        <v>0.17599999999999993</v>
       </c>
       <c r="K14" s="222"/>
       <c r="L14" s="114" t="s">
@@ -11351,42 +11351,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:59" s="1" customFormat="1" ht="24.75" x14ac:dyDescent="0.45">
-      <c r="D1" s="216" t="s">
+      <c r="D1" s="211" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="216"/>
-      <c r="F1" s="216"/>
-      <c r="G1" s="216"/>
-      <c r="H1" s="216"/>
-      <c r="I1" s="216"/>
-      <c r="J1" s="216"/>
-      <c r="K1" s="216"/>
-      <c r="L1" s="216"/>
-      <c r="M1" s="216"/>
-      <c r="N1" s="216"/>
-      <c r="O1" s="216"/>
-      <c r="P1" s="216"/>
-      <c r="Q1" s="216"/>
-      <c r="R1" s="216"/>
-      <c r="S1" s="216"/>
-      <c r="T1" s="214" t="s">
+      <c r="E1" s="211"/>
+      <c r="F1" s="211"/>
+      <c r="G1" s="211"/>
+      <c r="H1" s="211"/>
+      <c r="I1" s="211"/>
+      <c r="J1" s="211"/>
+      <c r="K1" s="211"/>
+      <c r="L1" s="211"/>
+      <c r="M1" s="211"/>
+      <c r="N1" s="211"/>
+      <c r="O1" s="211"/>
+      <c r="P1" s="211"/>
+      <c r="Q1" s="211"/>
+      <c r="R1" s="211"/>
+      <c r="S1" s="211"/>
+      <c r="T1" s="206" t="s">
         <v>36</v>
       </c>
-      <c r="U1" s="214"/>
-      <c r="V1" s="214"/>
-      <c r="W1" s="214"/>
-      <c r="X1" s="214"/>
-      <c r="Y1" s="214"/>
-      <c r="Z1" s="214"/>
-      <c r="AA1" s="214"/>
-      <c r="AB1" s="214"/>
-      <c r="AC1" s="214"/>
-      <c r="AD1" s="214"/>
-      <c r="AE1" s="214"/>
-      <c r="AF1" s="214"/>
-      <c r="AG1" s="214"/>
-      <c r="AH1" s="214"/>
-      <c r="AI1" s="214"/>
+      <c r="U1" s="206"/>
+      <c r="V1" s="206"/>
+      <c r="W1" s="206"/>
+      <c r="X1" s="206"/>
+      <c r="Y1" s="206"/>
+      <c r="Z1" s="206"/>
+      <c r="AA1" s="206"/>
+      <c r="AB1" s="206"/>
+      <c r="AC1" s="206"/>
+      <c r="AD1" s="206"/>
+      <c r="AE1" s="206"/>
+      <c r="AF1" s="206"/>
+      <c r="AG1" s="206"/>
+      <c r="AH1" s="206"/>
+      <c r="AI1" s="206"/>
       <c r="AJ1" s="234" t="s">
         <v>37</v>
       </c>
@@ -11419,90 +11419,90 @@
     <row r="2" spans="1:59" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="204" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="205"/>
-      <c r="F2" s="205"/>
-      <c r="G2" s="205"/>
-      <c r="H2" s="204" t="s">
+      <c r="D2" s="202" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="203"/>
+      <c r="F2" s="203"/>
+      <c r="G2" s="203"/>
+      <c r="H2" s="202" t="s">
         <v>40</v>
       </c>
-      <c r="I2" s="205"/>
-      <c r="J2" s="205"/>
-      <c r="K2" s="205"/>
-      <c r="L2" s="204" t="s">
+      <c r="I2" s="203"/>
+      <c r="J2" s="203"/>
+      <c r="K2" s="203"/>
+      <c r="L2" s="202" t="s">
         <v>41</v>
       </c>
-      <c r="M2" s="205"/>
-      <c r="N2" s="205"/>
-      <c r="O2" s="205"/>
-      <c r="P2" s="207" t="s">
+      <c r="M2" s="203"/>
+      <c r="N2" s="203"/>
+      <c r="O2" s="203"/>
+      <c r="P2" s="215" t="s">
         <v>42</v>
       </c>
-      <c r="Q2" s="208"/>
-      <c r="R2" s="208"/>
-      <c r="S2" s="209"/>
-      <c r="T2" s="204" t="s">
+      <c r="Q2" s="216"/>
+      <c r="R2" s="216"/>
+      <c r="S2" s="217"/>
+      <c r="T2" s="202" t="s">
         <v>43</v>
       </c>
-      <c r="U2" s="205"/>
-      <c r="V2" s="205"/>
-      <c r="W2" s="205"/>
-      <c r="X2" s="204" t="s">
+      <c r="U2" s="203"/>
+      <c r="V2" s="203"/>
+      <c r="W2" s="203"/>
+      <c r="X2" s="202" t="s">
         <v>45</v>
       </c>
-      <c r="Y2" s="205"/>
-      <c r="Z2" s="205"/>
-      <c r="AA2" s="205"/>
-      <c r="AB2" s="204" t="s">
+      <c r="Y2" s="203"/>
+      <c r="Z2" s="203"/>
+      <c r="AA2" s="203"/>
+      <c r="AB2" s="202" t="s">
         <v>47</v>
       </c>
-      <c r="AC2" s="205"/>
-      <c r="AD2" s="205"/>
-      <c r="AE2" s="205"/>
-      <c r="AF2" s="204" t="s">
+      <c r="AC2" s="203"/>
+      <c r="AD2" s="203"/>
+      <c r="AE2" s="203"/>
+      <c r="AF2" s="202" t="s">
         <v>48</v>
       </c>
-      <c r="AG2" s="205"/>
-      <c r="AH2" s="205"/>
-      <c r="AI2" s="205"/>
-      <c r="AJ2" s="201" t="s">
+      <c r="AG2" s="203"/>
+      <c r="AH2" s="203"/>
+      <c r="AI2" s="203"/>
+      <c r="AJ2" s="208" t="s">
         <v>51</v>
       </c>
-      <c r="AK2" s="202"/>
-      <c r="AL2" s="202"/>
-      <c r="AM2" s="203"/>
-      <c r="AN2" s="201" t="s">
+      <c r="AK2" s="209"/>
+      <c r="AL2" s="209"/>
+      <c r="AM2" s="210"/>
+      <c r="AN2" s="208" t="s">
         <v>14</v>
       </c>
-      <c r="AO2" s="202"/>
-      <c r="AP2" s="202"/>
-      <c r="AQ2" s="203"/>
-      <c r="AR2" s="201" t="s">
+      <c r="AO2" s="209"/>
+      <c r="AP2" s="209"/>
+      <c r="AQ2" s="210"/>
+      <c r="AR2" s="208" t="s">
         <v>52</v>
       </c>
-      <c r="AS2" s="202"/>
-      <c r="AT2" s="202"/>
-      <c r="AU2" s="203"/>
-      <c r="AV2" s="205" t="s">
+      <c r="AS2" s="209"/>
+      <c r="AT2" s="209"/>
+      <c r="AU2" s="210"/>
+      <c r="AV2" s="203" t="s">
         <v>16</v>
       </c>
-      <c r="AW2" s="205"/>
-      <c r="AX2" s="205"/>
-      <c r="AY2" s="205"/>
-      <c r="AZ2" s="205" t="s">
+      <c r="AW2" s="203"/>
+      <c r="AX2" s="203"/>
+      <c r="AY2" s="203"/>
+      <c r="AZ2" s="203" t="s">
         <v>54</v>
       </c>
-      <c r="BA2" s="205"/>
-      <c r="BB2" s="205"/>
-      <c r="BC2" s="205"/>
-      <c r="BD2" s="204" t="s">
+      <c r="BA2" s="203"/>
+      <c r="BB2" s="203"/>
+      <c r="BC2" s="203"/>
+      <c r="BD2" s="202" t="s">
         <v>55</v>
       </c>
-      <c r="BE2" s="205"/>
-      <c r="BF2" s="215"/>
-      <c r="BG2" s="205"/>
+      <c r="BE2" s="203"/>
+      <c r="BF2" s="207"/>
+      <c r="BG2" s="203"/>
     </row>
     <row r="3" spans="1:59" ht="15" x14ac:dyDescent="0.45">
       <c r="B3" s="8" t="s">
@@ -11855,7 +11855,7 @@
       </c>
       <c r="AS4" s="129">
         <f>(VLOOKUP(B4,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.78980000000000006</v>
+        <v>0.79400000000000004</v>
       </c>
       <c r="AT4" s="14">
         <f t="shared" ref="AT4" si="20">IF(AS4&lt;94.5%,0,IF(AS4&lt;95.54%,50%,IF(AS4&lt;AR4,80%,100%+(30%*(AS4-AR4)/3.39%))))</f>
@@ -11863,7 +11863,7 @@
       </c>
       <c r="AU4" s="54">
         <f t="shared" ref="AU4" si="21">AR4-AS4</f>
-        <v>0.18019999999999992</v>
+        <v>0.17599999999999993</v>
       </c>
       <c r="AV4" s="57">
         <f>VLOOKUP(A4,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -12089,7 +12089,7 @@
       </c>
       <c r="AS5" s="129">
         <f>(VLOOKUP(B5,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.6604000000000001</v>
+        <v>0.7037000000000001</v>
       </c>
       <c r="AT5" s="14">
         <f t="shared" ref="AT5:AT16" si="48">IF(AS5&lt;94.5%,0,IF(AS5&lt;95.54%,50%,IF(AS5&lt;AR5,80%,100%+(30%*(AS5-AR5)/3.39%))))</f>
@@ -12097,7 +12097,7 @@
       </c>
       <c r="AU5" s="54">
         <f t="shared" ref="AU5:AU16" si="49">AR5-AS5</f>
-        <v>0.30959999999999988</v>
+        <v>0.26629999999999987</v>
       </c>
       <c r="AV5" s="57">
         <f>VLOOKUP(A5,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -12323,7 +12323,7 @@
       </c>
       <c r="AS6" s="129">
         <f>(VLOOKUP(B6,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.59140000000000004</v>
+        <v>0.67500000000000004</v>
       </c>
       <c r="AT6" s="14">
         <f t="shared" si="48"/>
@@ -12331,7 +12331,7 @@
       </c>
       <c r="AU6" s="54">
         <f t="shared" si="49"/>
-        <v>0.37859999999999994</v>
+        <v>0.29499999999999993</v>
       </c>
       <c r="AV6" s="57">
         <f>VLOOKUP(A6,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -12557,7 +12557,7 @@
       </c>
       <c r="AS7" s="129">
         <f>(VLOOKUP(B7,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.57600000000000007</v>
+        <v>0.6409999999999999</v>
       </c>
       <c r="AT7" s="14">
         <f t="shared" si="48"/>
@@ -12565,7 +12565,7 @@
       </c>
       <c r="AU7" s="54">
         <f t="shared" si="49"/>
-        <v>0.39399999999999991</v>
+        <v>0.32900000000000007</v>
       </c>
       <c r="AV7" s="57">
         <f>VLOOKUP(A7,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -12791,7 +12791,7 @@
       </c>
       <c r="AS8" s="129">
         <f>(VLOOKUP(B8,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.72019999999999995</v>
+        <v>0.7288</v>
       </c>
       <c r="AT8" s="14">
         <f t="shared" si="48"/>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="AU8" s="54">
         <f t="shared" si="49"/>
-        <v>0.24980000000000002</v>
+        <v>0.24119999999999997</v>
       </c>
       <c r="AV8" s="57">
         <f>VLOOKUP(A8,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -13086,7 +13086,7 @@
       </c>
       <c r="AS10" s="129">
         <f>(VLOOKUP(B10,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.69010000000000005</v>
+        <v>0.70279999999999998</v>
       </c>
       <c r="AT10" s="14">
         <f t="shared" si="48"/>
@@ -13094,7 +13094,7 @@
       </c>
       <c r="AU10" s="54">
         <f t="shared" si="49"/>
-        <v>0.27989999999999993</v>
+        <v>0.26719999999999999</v>
       </c>
       <c r="AV10" s="57">
         <f>VLOOKUP(A10,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -13320,7 +13320,7 @@
       </c>
       <c r="AS11" s="129">
         <f>(VLOOKUP(B11,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.75159999999999993</v>
+        <v>0.75800000000000001</v>
       </c>
       <c r="AT11" s="14">
         <f t="shared" si="48"/>
@@ -13328,7 +13328,7 @@
       </c>
       <c r="AU11" s="54">
         <f t="shared" si="49"/>
-        <v>0.21840000000000004</v>
+        <v>0.21199999999999997</v>
       </c>
       <c r="AV11" s="57">
         <f>VLOOKUP(A11,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -13554,7 +13554,7 @@
       </c>
       <c r="AS12" s="129">
         <f>(VLOOKUP(B12,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.31659999999999999</v>
+        <v>0.48759999999999998</v>
       </c>
       <c r="AT12" s="14">
         <f t="shared" si="48"/>
@@ -13562,7 +13562,7 @@
       </c>
       <c r="AU12" s="54">
         <f t="shared" si="49"/>
-        <v>0.65339999999999998</v>
+        <v>0.4824</v>
       </c>
       <c r="AV12" s="57">
         <f>VLOOKUP(A12,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -13788,7 +13788,7 @@
       </c>
       <c r="AS13" s="129">
         <f>(VLOOKUP(B13,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.55869999999999997</v>
+        <v>0.72040000000000004</v>
       </c>
       <c r="AT13" s="14">
         <f t="shared" si="48"/>
@@ -13796,7 +13796,7 @@
       </c>
       <c r="AU13" s="54">
         <f t="shared" si="49"/>
-        <v>0.4113</v>
+        <v>0.24959999999999993</v>
       </c>
       <c r="AV13" s="57">
         <f>VLOOKUP(A13,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -14022,7 +14022,7 @@
       </c>
       <c r="AS14" s="129">
         <f>(VLOOKUP(B14,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.77370000000000005</v>
+        <v>0.78879999999999995</v>
       </c>
       <c r="AT14" s="14">
         <f t="shared" si="48"/>
@@ -14030,7 +14030,7 @@
       </c>
       <c r="AU14" s="54">
         <f t="shared" si="49"/>
-        <v>0.19629999999999992</v>
+        <v>0.18120000000000003</v>
       </c>
       <c r="AV14" s="57">
         <f>VLOOKUP(A14,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -14256,7 +14256,7 @@
       </c>
       <c r="AS15" s="129">
         <f>(VLOOKUP(B15,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.64300000000000002</v>
+        <v>0.64950000000000008</v>
       </c>
       <c r="AT15" s="14">
         <f t="shared" si="48"/>
@@ -14264,7 +14264,7 @@
       </c>
       <c r="AU15" s="54">
         <f t="shared" si="49"/>
-        <v>0.32699999999999996</v>
+        <v>0.3204999999999999</v>
       </c>
       <c r="AV15" s="57">
         <f>VLOOKUP(A15,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -14490,7 +14490,7 @@
       </c>
       <c r="AS16" s="129">
         <f>(VLOOKUP(B16,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.76049999999999995</v>
+        <v>0.76200000000000001</v>
       </c>
       <c r="AT16" s="14">
         <f t="shared" si="48"/>
@@ -14498,7 +14498,7 @@
       </c>
       <c r="AU16" s="54">
         <f t="shared" si="49"/>
-        <v>0.20950000000000002</v>
+        <v>0.20799999999999996</v>
       </c>
       <c r="AV16" s="57">
         <f>VLOOKUP(A16,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -14582,11 +14582,11 @@
       </c>
       <c r="C19" s="142">
         <f ca="1">SUMIF(cuoc!A7:P27,'tiến độ'!A19,cuoc!M7:M27)</f>
-        <v>430079987</v>
+        <v>456273113</v>
       </c>
       <c r="D19" s="142">
         <f ca="1">B19*0.968-C19</f>
-        <v>193094084.25599992</v>
+        <v>166900958.25599992</v>
       </c>
       <c r="E19" s="137"/>
       <c r="H19" s="137"/>
@@ -14603,11 +14603,11 @@
       </c>
       <c r="C20" s="143">
         <f ca="1">SUMIF(cuoc!A8:P27,'tiến độ'!A20,cuoc!M8:M27)</f>
-        <v>689131159</v>
+        <v>711857872</v>
       </c>
       <c r="D20" s="142">
         <f ca="1">B20*0.968-C20</f>
-        <v>254852767.77600002</v>
+        <v>232126054.77600002</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.45">
@@ -14793,6 +14793,11 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="D1:S1"/>
+    <mergeCell ref="D2:G2"/>
+    <mergeCell ref="H2:K2"/>
+    <mergeCell ref="L2:O2"/>
+    <mergeCell ref="P2:S2"/>
     <mergeCell ref="X2:AA2"/>
     <mergeCell ref="AB2:AE2"/>
     <mergeCell ref="AF2:AI2"/>
@@ -14806,11 +14811,6 @@
     <mergeCell ref="AJ2:AM2"/>
     <mergeCell ref="AN2:AQ2"/>
     <mergeCell ref="T2:W2"/>
-    <mergeCell ref="D1:S1"/>
-    <mergeCell ref="D2:G2"/>
-    <mergeCell ref="H2:K2"/>
-    <mergeCell ref="L2:O2"/>
-    <mergeCell ref="P2:S2"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="F4:F16">
@@ -23286,6 +23286,12 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="X5:AE5"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="H5:O5"/>
+    <mergeCell ref="P5:W5"/>
     <mergeCell ref="CB5:CI5"/>
     <mergeCell ref="CJ5:CQ5"/>
     <mergeCell ref="CR5:CY5"/>
@@ -23296,12 +23302,6 @@
     <mergeCell ref="BD5:BK5"/>
     <mergeCell ref="BL5:BS5"/>
     <mergeCell ref="BT5:CA5"/>
-    <mergeCell ref="X5:AE5"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="H5:O5"/>
-    <mergeCell ref="P5:W5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -23399,7 +23399,7 @@
       <c r="A3" s="100" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="245" t="s">
+      <c r="B3" s="243" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="101" t="s">
@@ -23411,70 +23411,70 @@
       <c r="E3" s="247" t="s">
         <v>202</v>
       </c>
-      <c r="F3" s="243" t="s">
+      <c r="F3" s="245" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="243" t="s">
+      <c r="G3" s="245" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="243" t="s">
+      <c r="H3" s="245" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="243" t="s">
+      <c r="I3" s="245" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="243" t="s">
+      <c r="J3" s="245" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="243" t="s">
+      <c r="K3" s="245" t="s">
         <v>11</v>
       </c>
-      <c r="L3" s="243" t="s">
+      <c r="L3" s="245" t="s">
         <v>12</v>
       </c>
-      <c r="M3" s="243" t="s">
+      <c r="M3" s="245" t="s">
         <v>203</v>
       </c>
-      <c r="N3" s="243" t="s">
+      <c r="N3" s="245" t="s">
         <v>286</v>
       </c>
-      <c r="O3" s="243" t="s">
+      <c r="O3" s="245" t="s">
         <v>14</v>
       </c>
-      <c r="P3" s="243" t="s">
+      <c r="P3" s="245" t="s">
         <v>15</v>
       </c>
-      <c r="Q3" s="243" t="s">
+      <c r="Q3" s="245" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="243" t="s">
+      <c r="R3" s="245" t="s">
         <v>17</v>
       </c>
-      <c r="S3" s="243" t="s">
+      <c r="S3" s="245" t="s">
         <v>18</v>
       </c>
       <c r="T3" s="99"/>
     </row>
     <row r="4" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="100"/>
-      <c r="B4" s="246"/>
+      <c r="B4" s="244"/>
       <c r="C4" s="101"/>
       <c r="D4" s="101"/>
       <c r="E4" s="248"/>
-      <c r="F4" s="244"/>
-      <c r="G4" s="244"/>
-      <c r="H4" s="244"/>
-      <c r="I4" s="244"/>
-      <c r="J4" s="244"/>
-      <c r="K4" s="244"/>
-      <c r="L4" s="244"/>
-      <c r="M4" s="244"/>
-      <c r="N4" s="244"/>
-      <c r="O4" s="244"/>
-      <c r="P4" s="244"/>
-      <c r="Q4" s="244"/>
-      <c r="R4" s="244"/>
-      <c r="S4" s="244"/>
+      <c r="F4" s="246"/>
+      <c r="G4" s="246"/>
+      <c r="H4" s="246"/>
+      <c r="I4" s="246"/>
+      <c r="J4" s="246"/>
+      <c r="K4" s="246"/>
+      <c r="L4" s="246"/>
+      <c r="M4" s="246"/>
+      <c r="N4" s="246"/>
+      <c r="O4" s="246"/>
+      <c r="P4" s="246"/>
+      <c r="Q4" s="246"/>
+      <c r="R4" s="246"/>
+      <c r="S4" s="246"/>
       <c r="T4" s="99"/>
     </row>
     <row r="5" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.45">
@@ -24792,6 +24792,12 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="S3:S4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="R3:R4"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="H3:H4"/>
@@ -24802,12 +24808,6 @@
     <mergeCell ref="K3:K4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="E3:E4"/>
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="S3:S4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="R3:R4"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.69991251615088756" right="0.69991251615088756" top="0.74990626395218019" bottom="0.74990626395218019" header="0.29996251027415122" footer="0.29996251027415122"/>
@@ -26083,68 +26083,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:48" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="256" t="s">
+      <c r="A1" s="258" t="s">
         <v>240</v>
       </c>
-      <c r="B1" s="256"/>
-      <c r="C1" s="256"/>
-      <c r="D1" s="256"/>
-      <c r="E1" s="256"/>
-      <c r="F1" s="256"/>
-      <c r="G1" s="256"/>
-      <c r="H1" s="256"/>
-      <c r="I1" s="256"/>
-      <c r="J1" s="256"/>
-      <c r="K1" s="256"/>
-      <c r="M1" s="259" t="s">
+      <c r="B1" s="258"/>
+      <c r="C1" s="258"/>
+      <c r="D1" s="258"/>
+      <c r="E1" s="258"/>
+      <c r="F1" s="258"/>
+      <c r="G1" s="258"/>
+      <c r="H1" s="258"/>
+      <c r="I1" s="258"/>
+      <c r="J1" s="258"/>
+      <c r="K1" s="258"/>
+      <c r="M1" s="261" t="s">
         <v>241</v>
       </c>
-      <c r="N1" s="259"/>
-      <c r="O1" s="259"/>
-      <c r="P1" s="259"/>
-      <c r="Q1" s="259"/>
-      <c r="R1" s="259"/>
-      <c r="S1" s="259"/>
-      <c r="T1" s="259"/>
-      <c r="U1" s="259"/>
-      <c r="V1" s="259"/>
-      <c r="W1" s="259"/>
-      <c r="X1" s="259"/>
-      <c r="Y1" s="259"/>
-      <c r="Z1" s="259"/>
+      <c r="N1" s="261"/>
+      <c r="O1" s="261"/>
+      <c r="P1" s="261"/>
+      <c r="Q1" s="261"/>
+      <c r="R1" s="261"/>
+      <c r="S1" s="261"/>
+      <c r="T1" s="261"/>
+      <c r="U1" s="261"/>
+      <c r="V1" s="261"/>
+      <c r="W1" s="261"/>
+      <c r="X1" s="261"/>
+      <c r="Y1" s="261"/>
+      <c r="Z1" s="261"/>
     </row>
     <row r="2" spans="1:48" ht="24.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="257"/>
-      <c r="B2" s="257"/>
-      <c r="C2" s="257"/>
-      <c r="D2" s="257"/>
-      <c r="E2" s="257"/>
-      <c r="F2" s="257"/>
-      <c r="G2" s="257"/>
-      <c r="H2" s="257"/>
-      <c r="I2" s="257"/>
-      <c r="J2" s="257"/>
-      <c r="K2" s="257"/>
-      <c r="M2" s="260"/>
-      <c r="N2" s="260"/>
-      <c r="O2" s="260"/>
-      <c r="P2" s="260"/>
-      <c r="Q2" s="260"/>
-      <c r="R2" s="260"/>
-      <c r="S2" s="260"/>
-      <c r="T2" s="260"/>
-      <c r="U2" s="260"/>
-      <c r="V2" s="260"/>
-      <c r="W2" s="260"/>
-      <c r="X2" s="260"/>
-      <c r="Y2" s="260"/>
-      <c r="Z2" s="260"/>
+      <c r="A2" s="259"/>
+      <c r="B2" s="259"/>
+      <c r="C2" s="259"/>
+      <c r="D2" s="259"/>
+      <c r="E2" s="259"/>
+      <c r="F2" s="259"/>
+      <c r="G2" s="259"/>
+      <c r="H2" s="259"/>
+      <c r="I2" s="259"/>
+      <c r="J2" s="259"/>
+      <c r="K2" s="259"/>
+      <c r="M2" s="262"/>
+      <c r="N2" s="262"/>
+      <c r="O2" s="262"/>
+      <c r="P2" s="262"/>
+      <c r="Q2" s="262"/>
+      <c r="R2" s="262"/>
+      <c r="S2" s="262"/>
+      <c r="T2" s="262"/>
+      <c r="U2" s="262"/>
+      <c r="V2" s="262"/>
+      <c r="W2" s="262"/>
+      <c r="X2" s="262"/>
+      <c r="Y2" s="262"/>
+      <c r="Z2" s="262"/>
     </row>
     <row r="3" spans="1:48" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="253" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="254" t="s">
+      <c r="A3" s="255" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="256" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="28" t="s">
@@ -26174,70 +26174,70 @@
       <c r="K3" s="28" t="s">
         <v>249</v>
       </c>
-      <c r="M3" s="258" t="s">
+      <c r="M3" s="260" t="s">
         <v>34</v>
       </c>
-      <c r="N3" s="204" t="s">
+      <c r="N3" s="202" t="s">
         <v>250</v>
       </c>
-      <c r="O3" s="205"/>
-      <c r="P3" s="205"/>
-      <c r="Q3" s="205"/>
-      <c r="R3" s="261" t="s">
+      <c r="O3" s="203"/>
+      <c r="P3" s="203"/>
+      <c r="Q3" s="203"/>
+      <c r="R3" s="253" t="s">
         <v>251</v>
       </c>
-      <c r="S3" s="204" t="s">
+      <c r="S3" s="202" t="s">
         <v>252</v>
       </c>
-      <c r="T3" s="205"/>
-      <c r="U3" s="205"/>
-      <c r="V3" s="205"/>
-      <c r="W3" s="261" t="s">
+      <c r="T3" s="203"/>
+      <c r="U3" s="203"/>
+      <c r="V3" s="203"/>
+      <c r="W3" s="253" t="s">
         <v>251</v>
       </c>
-      <c r="X3" s="207" t="s">
+      <c r="X3" s="215" t="s">
         <v>41</v>
       </c>
-      <c r="Y3" s="208"/>
-      <c r="Z3" s="208"/>
-      <c r="AA3" s="261" t="s">
+      <c r="Y3" s="216"/>
+      <c r="Z3" s="216"/>
+      <c r="AA3" s="253" t="s">
         <v>251</v>
       </c>
       <c r="AB3" s="71"/>
-      <c r="AC3" s="204" t="s">
+      <c r="AC3" s="202" t="s">
         <v>42</v>
       </c>
-      <c r="AD3" s="205"/>
-      <c r="AE3" s="205"/>
-      <c r="AF3" s="205"/>
-      <c r="AG3" s="204" t="s">
+      <c r="AD3" s="203"/>
+      <c r="AE3" s="203"/>
+      <c r="AF3" s="203"/>
+      <c r="AG3" s="202" t="s">
         <v>43</v>
       </c>
-      <c r="AH3" s="205"/>
-      <c r="AI3" s="205"/>
-      <c r="AJ3" s="205"/>
-      <c r="AK3" s="204" t="s">
+      <c r="AH3" s="203"/>
+      <c r="AI3" s="203"/>
+      <c r="AJ3" s="203"/>
+      <c r="AK3" s="202" t="s">
         <v>44</v>
       </c>
-      <c r="AL3" s="205"/>
-      <c r="AM3" s="205"/>
-      <c r="AN3" s="205"/>
-      <c r="AO3" s="204" t="s">
+      <c r="AL3" s="203"/>
+      <c r="AM3" s="203"/>
+      <c r="AN3" s="203"/>
+      <c r="AO3" s="202" t="s">
         <v>46</v>
       </c>
-      <c r="AP3" s="205"/>
-      <c r="AQ3" s="205"/>
-      <c r="AR3" s="205"/>
-      <c r="AS3" s="204" t="s">
+      <c r="AP3" s="203"/>
+      <c r="AQ3" s="203"/>
+      <c r="AR3" s="203"/>
+      <c r="AS3" s="202" t="s">
         <v>47</v>
       </c>
-      <c r="AT3" s="205"/>
-      <c r="AU3" s="205"/>
-      <c r="AV3" s="205"/>
+      <c r="AT3" s="203"/>
+      <c r="AU3" s="203"/>
+      <c r="AV3" s="203"/>
     </row>
     <row r="4" spans="1:48" ht="22.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="253"/>
-      <c r="B4" s="255"/>
+      <c r="A4" s="255"/>
+      <c r="B4" s="257"/>
       <c r="C4" s="24">
         <f t="shared" ref="C4:K4" si="0">SUM(C5:C19)</f>
         <v>15</v>
@@ -26274,7 +26274,7 @@
         <f t="shared" si="0"/>
         <v>134</v>
       </c>
-      <c r="M4" s="258"/>
+      <c r="M4" s="260"/>
       <c r="N4" s="8" t="s">
         <v>2</v>
       </c>
@@ -26287,7 +26287,7 @@
       <c r="Q4" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="R4" s="262"/>
+      <c r="R4" s="254"/>
       <c r="S4" s="8" t="s">
         <v>2</v>
       </c>
@@ -26300,7 +26300,7 @@
       <c r="V4" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="W4" s="262"/>
+      <c r="W4" s="254"/>
       <c r="X4" s="8" t="s">
         <v>2</v>
       </c>
@@ -26310,7 +26310,7 @@
       <c r="Z4" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="AA4" s="262"/>
+      <c r="AA4" s="254"/>
       <c r="AB4" s="51" t="s">
         <v>59</v>
       </c>
@@ -28699,6 +28699,12 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="A1:K2"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="N3:Q3"/>
+    <mergeCell ref="M1:Z2"/>
     <mergeCell ref="AS3:AV3"/>
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="W3:W4"/>
@@ -28709,12 +28715,6 @@
     <mergeCell ref="AK3:AN3"/>
     <mergeCell ref="AO3:AR3"/>
     <mergeCell ref="S3:V3"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="A1:K2"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="N3:Q3"/>
-    <mergeCell ref="M1:Z2"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="P5:P20">
@@ -28854,44 +28854,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="263"/>
-      <c r="B1" s="263"/>
-      <c r="C1" s="263"/>
-      <c r="D1" s="263"/>
-      <c r="E1" s="263"/>
-      <c r="F1" s="263"/>
-      <c r="G1" s="263"/>
-      <c r="H1" s="263"/>
-      <c r="I1" s="263"/>
-      <c r="J1" s="263"/>
-      <c r="K1" s="263"/>
-      <c r="L1" s="263"/>
-      <c r="M1" s="263"/>
-      <c r="N1" s="263"/>
-      <c r="O1" s="263"/>
-      <c r="P1" s="263"/>
+      <c r="A1" s="265"/>
+      <c r="B1" s="265"/>
+      <c r="C1" s="265"/>
+      <c r="D1" s="265"/>
+      <c r="E1" s="265"/>
+      <c r="F1" s="265"/>
+      <c r="G1" s="265"/>
+      <c r="H1" s="265"/>
+      <c r="I1" s="265"/>
+      <c r="J1" s="265"/>
+      <c r="K1" s="265"/>
+      <c r="L1" s="265"/>
+      <c r="M1" s="265"/>
+      <c r="N1" s="265"/>
+      <c r="O1" s="265"/>
+      <c r="P1" s="265"/>
     </row>
     <row r="2" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="264"/>
-      <c r="B2" s="264"/>
-      <c r="C2" s="264"/>
-      <c r="D2" s="264"/>
-      <c r="E2" s="264"/>
-      <c r="F2" s="264"/>
-      <c r="G2" s="264"/>
-      <c r="H2" s="264"/>
-      <c r="I2" s="264"/>
-      <c r="J2" s="264"/>
-      <c r="K2" s="264"/>
-      <c r="L2" s="264"/>
-      <c r="M2" s="264"/>
-      <c r="N2" s="264"/>
-      <c r="O2" s="264"/>
-      <c r="P2" s="264"/>
+      <c r="A2" s="266"/>
+      <c r="B2" s="266"/>
+      <c r="C2" s="266"/>
+      <c r="D2" s="266"/>
+      <c r="E2" s="266"/>
+      <c r="F2" s="266"/>
+      <c r="G2" s="266"/>
+      <c r="H2" s="266"/>
+      <c r="I2" s="266"/>
+      <c r="J2" s="266"/>
+      <c r="K2" s="266"/>
+      <c r="L2" s="266"/>
+      <c r="M2" s="266"/>
+      <c r="N2" s="266"/>
+      <c r="O2" s="266"/>
+      <c r="P2" s="266"/>
     </row>
     <row r="3" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="265"/>
-      <c r="B3" s="265"/>
+      <c r="A3" s="267"/>
+      <c r="B3" s="267"/>
       <c r="C3" s="133"/>
       <c r="D3" s="133"/>
       <c r="E3" s="133"/>
@@ -28908,10 +28908,10 @@
       <c r="P3" s="133"/>
     </row>
     <row r="4" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="267" t="s">
+      <c r="A4" s="269" t="s">
         <v>255</v>
       </c>
-      <c r="B4" s="267" t="s">
+      <c r="B4" s="269" t="s">
         <v>39</v>
       </c>
       <c r="C4" s="141"/>
@@ -28919,70 +28919,70 @@
       <c r="E4" s="141"/>
       <c r="F4" s="141"/>
       <c r="G4" s="141"/>
-      <c r="H4" s="266"/>
-      <c r="I4" s="266"/>
-      <c r="J4" s="266"/>
-      <c r="K4" s="266"/>
-      <c r="L4" s="266"/>
-      <c r="M4" s="266"/>
-      <c r="N4" s="266"/>
-      <c r="O4" s="266"/>
-      <c r="P4" s="266"/>
+      <c r="H4" s="268"/>
+      <c r="I4" s="268"/>
+      <c r="J4" s="268"/>
+      <c r="K4" s="268"/>
+      <c r="L4" s="268"/>
+      <c r="M4" s="268"/>
+      <c r="N4" s="268"/>
+      <c r="O4" s="268"/>
+      <c r="P4" s="268"/>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A5" s="270"/>
-      <c r="B5" s="270"/>
-      <c r="C5" s="267" t="s">
+      <c r="A5" s="272"/>
+      <c r="B5" s="272"/>
+      <c r="C5" s="269" t="s">
         <v>256</v>
       </c>
-      <c r="D5" s="267" t="s">
+      <c r="D5" s="269" t="s">
         <v>257</v>
       </c>
-      <c r="E5" s="268"/>
-      <c r="F5" s="267" t="s">
+      <c r="E5" s="270"/>
+      <c r="F5" s="269" t="s">
         <v>258</v>
       </c>
-      <c r="G5" s="268"/>
-      <c r="H5" s="267" t="s">
+      <c r="G5" s="270"/>
+      <c r="H5" s="269" t="s">
         <v>259</v>
       </c>
-      <c r="I5" s="268"/>
-      <c r="J5" s="267" t="s">
+      <c r="I5" s="270"/>
+      <c r="J5" s="269" t="s">
         <v>260</v>
       </c>
-      <c r="K5" s="268"/>
-      <c r="L5" s="271" t="s">
+      <c r="K5" s="270"/>
+      <c r="L5" s="273" t="s">
         <v>261</v>
       </c>
-      <c r="M5" s="268"/>
-      <c r="N5" s="266" t="s">
+      <c r="M5" s="270"/>
+      <c r="N5" s="268" t="s">
         <v>262</v>
       </c>
-      <c r="O5" s="272"/>
-      <c r="P5" s="267" t="s">
+      <c r="O5" s="274"/>
+      <c r="P5" s="269" t="s">
         <v>266</v>
       </c>
-      <c r="R5" s="273" t="s">
+      <c r="R5" s="263" t="s">
         <v>34</v>
       </c>
-      <c r="S5" s="273" t="s">
+      <c r="S5" s="263" t="s">
         <v>290</v>
       </c>
-      <c r="T5" s="273" t="s">
+      <c r="T5" s="263" t="s">
         <v>291</v>
       </c>
-      <c r="U5" s="273" t="s">
+      <c r="U5" s="263" t="s">
         <v>293</v>
       </c>
-      <c r="V5" s="274" t="s">
+      <c r="V5" s="264" t="s">
         <v>292</v>
       </c>
       <c r="W5" s="172"/>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A6" s="269"/>
-      <c r="B6" s="269"/>
-      <c r="C6" s="270"/>
+      <c r="A6" s="271"/>
+      <c r="B6" s="271"/>
+      <c r="C6" s="272"/>
       <c r="D6" s="134" t="s">
         <v>2</v>
       </c>
@@ -29019,12 +29019,12 @@
       <c r="O6" s="134" t="s">
         <v>263</v>
       </c>
-      <c r="P6" s="269"/>
-      <c r="R6" s="273"/>
-      <c r="S6" s="273"/>
-      <c r="T6" s="273"/>
-      <c r="U6" s="273"/>
-      <c r="V6" s="273"/>
+      <c r="P6" s="271"/>
+      <c r="R6" s="263"/>
+      <c r="S6" s="263"/>
+      <c r="T6" s="263"/>
+      <c r="U6" s="263"/>
+      <c r="V6" s="263"/>
       <c r="W6" s="172"/>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.45">
@@ -29056,10 +29056,10 @@
         <v>72573808</v>
       </c>
       <c r="J7" s="191">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K7" s="191">
-        <v>1748413</v>
+        <v>0</v>
       </c>
       <c r="L7" s="191">
         <v>368</v>
@@ -29089,11 +29089,11 @@
       </c>
       <c r="U7" s="189">
         <f>VLOOKUP(R7,$C$7:$P$27,14,0)</f>
-        <v>25447380.799999997</v>
+        <v>24566377.799999997</v>
       </c>
       <c r="V7" s="175">
         <f>VLOOKUP(R7,$C$7:$P$27,14,0)-T7</f>
-        <v>-2286458</v>
+        <v>-3167461</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.45">
@@ -29125,26 +29125,26 @@
         <v>70243418</v>
       </c>
       <c r="J8" s="194">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="K8" s="194">
-        <v>2075389</v>
+        <v>83140</v>
       </c>
       <c r="L8" s="194">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="M8" s="194">
-        <v>57348865</v>
+        <v>57612005</v>
       </c>
       <c r="N8" s="195">
-        <v>79.3</v>
+        <v>79.739999999999995</v>
       </c>
       <c r="O8" s="195">
-        <v>81.64</v>
+        <v>82.02</v>
       </c>
       <c r="P8" s="135">
         <f t="shared" ref="P8:P27" si="0">I8*0.97-M8</f>
-        <v>10787250.459999993</v>
+        <v>10524110.459999993</v>
       </c>
       <c r="R8" s="173" t="s">
         <v>67</v>
@@ -29158,11 +29158,11 @@
       </c>
       <c r="U8" s="189">
         <f t="shared" ref="U8:U17" si="2">VLOOKUP(R8,$C$7:$P$27,14,0)</f>
-        <v>26149040.310000002</v>
+        <v>25544909.310000002</v>
       </c>
       <c r="V8" s="175">
         <f t="shared" ref="V8:V17" si="3">VLOOKUP(R8,$C$7:$P$27,14,0)-T8</f>
-        <v>-1884822</v>
+        <v>-2488953</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.45">
@@ -29194,26 +29194,26 @@
         <v>145101823</v>
       </c>
       <c r="J9" s="191">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="K9" s="191">
-        <v>2044822</v>
+        <v>323131</v>
       </c>
       <c r="L9" s="191">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="M9" s="191">
-        <v>114599728</v>
+        <v>115203859</v>
       </c>
       <c r="N9" s="192">
-        <v>76.709999999999994</v>
+        <v>77.17</v>
       </c>
       <c r="O9" s="192">
-        <v>78.98</v>
+        <v>79.400000000000006</v>
       </c>
       <c r="P9" s="135">
         <f t="shared" si="0"/>
-        <v>26149040.310000002</v>
+        <v>25544909.310000002</v>
       </c>
       <c r="R9" s="174" t="s">
         <v>87</v>
@@ -29227,28 +29227,28 @@
       </c>
       <c r="U9" s="189">
         <f t="shared" si="2"/>
-        <v>43804298.270000011</v>
+        <v>37677111.270000011</v>
       </c>
       <c r="V9" s="175">
         <f t="shared" si="3"/>
-        <v>-5285717</v>
+        <v>-11412904</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A10" s="193" t="s">
-        <v>288</v>
+        <v>129</v>
       </c>
       <c r="B10" s="193" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="C10" s="193" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="D10" s="194">
-        <v>308</v>
+        <v>1048</v>
       </c>
       <c r="E10" s="194">
-        <v>51982396</v>
+        <v>180440547</v>
       </c>
       <c r="F10" s="194">
         <v>0</v>
@@ -29257,32 +29257,32 @@
         <v>0</v>
       </c>
       <c r="H10" s="194">
-        <v>308</v>
+        <v>1048</v>
       </c>
       <c r="I10" s="194">
-        <v>51982396</v>
+        <v>180440547</v>
       </c>
       <c r="J10" s="194">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="K10" s="194">
-        <v>1258419</v>
+        <v>2234000</v>
       </c>
       <c r="L10" s="194">
-        <v>238</v>
+        <v>807</v>
       </c>
       <c r="M10" s="194">
-        <v>40394839</v>
+        <v>142334047</v>
       </c>
       <c r="N10" s="195">
-        <v>77.27</v>
+        <v>77</v>
       </c>
       <c r="O10" s="195">
-        <v>77.709999999999994</v>
+        <v>78.88</v>
       </c>
       <c r="P10" s="135">
         <f t="shared" si="0"/>
-        <v>10028085.119999997</v>
+        <v>32693283.590000004</v>
       </c>
       <c r="R10" s="174" t="s">
         <v>110</v>
@@ -29296,28 +29296,28 @@
       </c>
       <c r="U10" s="189">
         <f t="shared" si="2"/>
-        <v>58862085.859999985</v>
+        <v>49140087.859999985</v>
       </c>
       <c r="V10" s="175">
         <f t="shared" si="3"/>
-        <v>-2221233</v>
+        <v>-11943231</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A11" s="190" t="s">
-        <v>129</v>
+        <v>288</v>
       </c>
       <c r="B11" s="190" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="C11" s="190" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="D11" s="191">
-        <v>1048</v>
+        <v>308</v>
       </c>
       <c r="E11" s="191">
-        <v>180440547</v>
+        <v>51982396</v>
       </c>
       <c r="F11" s="191">
         <v>0</v>
@@ -29326,32 +29326,32 @@
         <v>0</v>
       </c>
       <c r="H11" s="191">
-        <v>1048</v>
+        <v>308</v>
       </c>
       <c r="I11" s="191">
-        <v>180440547</v>
+        <v>51982396</v>
       </c>
       <c r="J11" s="191">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K11" s="191">
-        <v>7089191</v>
+        <v>0</v>
       </c>
       <c r="L11" s="191">
-        <v>788</v>
+        <v>238</v>
       </c>
       <c r="M11" s="191">
-        <v>139610047</v>
+        <v>40394839</v>
       </c>
       <c r="N11" s="192">
-        <v>75.19</v>
+        <v>77.27</v>
       </c>
       <c r="O11" s="192">
-        <v>77.37</v>
+        <v>77.709999999999994</v>
       </c>
       <c r="P11" s="135">
         <f t="shared" si="0"/>
-        <v>35417283.590000004</v>
+        <v>10028085.119999997</v>
       </c>
       <c r="R11" s="173" t="s">
         <v>99</v>
@@ -29365,11 +29365,11 @@
       </c>
       <c r="U11" s="189">
         <f t="shared" si="2"/>
-        <v>40118828.75</v>
+        <v>31260021.75</v>
       </c>
       <c r="V11" s="175">
         <f t="shared" si="3"/>
-        <v>-1049058</v>
+        <v>-9907865</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.45">
@@ -29401,26 +29401,26 @@
         <v>93597302</v>
       </c>
       <c r="J12" s="194">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="K12" s="194">
-        <v>2492570</v>
+        <v>662979</v>
       </c>
       <c r="L12" s="194">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M12" s="194">
-        <v>72050652</v>
+        <v>72713631</v>
       </c>
       <c r="N12" s="195">
-        <v>75.31</v>
+        <v>75.67</v>
       </c>
       <c r="O12" s="195">
-        <v>76.98</v>
+        <v>77.69</v>
       </c>
       <c r="P12" s="135">
         <f t="shared" si="0"/>
-        <v>18738730.939999998</v>
+        <v>18075751.939999998</v>
       </c>
       <c r="R12" s="173" t="s">
         <v>75</v>
@@ -29434,11 +29434,11 @@
       </c>
       <c r="U12" s="189">
         <f t="shared" si="2"/>
-        <v>33386091.520000011</v>
+        <v>32413249.520000011</v>
       </c>
       <c r="V12" s="175">
         <f t="shared" si="3"/>
-        <v>-3044234</v>
+        <v>-4017076</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.45">
@@ -29470,26 +29470,26 @@
         <v>116427734</v>
       </c>
       <c r="J13" s="191">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="K13" s="191">
-        <v>2287490</v>
+        <v>332230</v>
       </c>
       <c r="L13" s="191">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="M13" s="191">
-        <v>89177976</v>
+        <v>89755206</v>
       </c>
       <c r="N13" s="192">
-        <v>74.3</v>
+        <v>74.86</v>
       </c>
       <c r="O13" s="192">
-        <v>76.599999999999994</v>
+        <v>77.09</v>
       </c>
       <c r="P13" s="135">
         <f t="shared" si="0"/>
-        <v>23756925.980000004</v>
+        <v>23179695.980000004</v>
       </c>
       <c r="R13" s="173" t="s">
         <v>107</v>
@@ -29503,11 +29503,11 @@
       </c>
       <c r="U13" s="189">
         <f t="shared" si="2"/>
-        <v>35417283.590000004</v>
+        <v>32693283.590000004</v>
       </c>
       <c r="V13" s="175">
         <f t="shared" si="3"/>
-        <v>-6069796</v>
+        <v>-8793796</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.45">
@@ -29539,26 +29539,26 @@
         <v>189656153</v>
       </c>
       <c r="J14" s="194">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="K14" s="194">
-        <v>4472082</v>
+        <v>100000</v>
       </c>
       <c r="L14" s="194">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="M14" s="194">
-        <v>144232257</v>
+        <v>144524669</v>
       </c>
       <c r="N14" s="195">
-        <v>74.260000000000005</v>
+        <v>74.510000000000005</v>
       </c>
       <c r="O14" s="195">
-        <v>76.05</v>
+        <v>76.2</v>
       </c>
       <c r="P14" s="135">
         <f t="shared" si="0"/>
-        <v>39734211.409999996</v>
+        <v>39441799.409999996</v>
       </c>
       <c r="R14" s="174" t="s">
         <v>72</v>
@@ -29572,11 +29572,11 @@
       </c>
       <c r="U14" s="189">
         <f t="shared" si="2"/>
-        <v>45436717.199999988</v>
+        <v>43381090.199999988</v>
       </c>
       <c r="V14" s="175">
         <f t="shared" si="3"/>
-        <v>-5551081</v>
+        <v>-7606708</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.45">
@@ -29608,26 +29608,26 @@
         <v>152862316</v>
       </c>
       <c r="J15" s="191">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="K15" s="191">
-        <v>3209357</v>
+        <v>124425</v>
       </c>
       <c r="L15" s="191">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="M15" s="191">
-        <v>114890355</v>
+        <v>115863197</v>
       </c>
       <c r="N15" s="192">
-        <v>71.31</v>
+        <v>72.05</v>
       </c>
       <c r="O15" s="192">
-        <v>75.16</v>
+        <v>75.8</v>
       </c>
       <c r="P15" s="135">
         <f t="shared" si="0"/>
-        <v>33386091.520000011</v>
+        <v>32413249.520000011</v>
       </c>
       <c r="R15" s="174" t="s">
         <v>113</v>
@@ -29641,11 +29641,11 @@
       </c>
       <c r="U15" s="189">
         <f t="shared" si="2"/>
-        <v>63603201.400000006</v>
+        <v>62342498.400000006</v>
       </c>
       <c r="V15" s="175">
         <f t="shared" si="3"/>
-        <v>-2871846</v>
+        <v>-4132549</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.45">
@@ -29653,16 +29653,16 @@
         <v>288</v>
       </c>
       <c r="B16" s="193" t="s">
-        <v>120</v>
+        <v>89</v>
       </c>
       <c r="C16" s="193" t="s">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="D16" s="194">
-        <v>415</v>
+        <v>356</v>
       </c>
       <c r="E16" s="194">
-        <v>66800107</v>
+        <v>53605661</v>
       </c>
       <c r="F16" s="194">
         <v>0</v>
@@ -29671,32 +29671,32 @@
         <v>0</v>
       </c>
       <c r="H16" s="194">
-        <v>415</v>
+        <v>356</v>
       </c>
       <c r="I16" s="194">
-        <v>66800107</v>
+        <v>53605661</v>
       </c>
       <c r="J16" s="194">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K16" s="194">
-        <v>1193140</v>
+        <v>120406</v>
       </c>
       <c r="L16" s="194">
-        <v>291</v>
+        <v>248</v>
       </c>
       <c r="M16" s="194">
-        <v>48926627</v>
+        <v>39700286</v>
       </c>
       <c r="N16" s="195">
-        <v>70.12</v>
+        <v>69.66</v>
       </c>
       <c r="O16" s="195">
-        <v>73.239999999999995</v>
+        <v>74.06</v>
       </c>
       <c r="P16" s="135">
         <f t="shared" si="0"/>
-        <v>15869476.789999999</v>
+        <v>12297205.170000002</v>
       </c>
       <c r="R16" s="174" t="s">
         <v>119</v>
@@ -29710,11 +29710,11 @@
       </c>
       <c r="U16" s="189">
         <f t="shared" si="2"/>
-        <v>39734211.409999996</v>
+        <v>39441799.409999996</v>
       </c>
       <c r="V16" s="175">
         <f t="shared" si="3"/>
-        <v>-3714765</v>
+        <v>-4007177</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.45">
@@ -29722,16 +29722,16 @@
         <v>288</v>
       </c>
       <c r="B17" s="190" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="C17" s="190" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
       <c r="D17" s="191">
-        <v>356</v>
+        <v>415</v>
       </c>
       <c r="E17" s="191">
-        <v>53605661</v>
+        <v>66800107</v>
       </c>
       <c r="F17" s="191">
         <v>0</v>
@@ -29740,32 +29740,32 @@
         <v>0</v>
       </c>
       <c r="H17" s="191">
-        <v>356</v>
+        <v>415</v>
       </c>
       <c r="I17" s="191">
-        <v>53605661</v>
+        <v>66800107</v>
       </c>
       <c r="J17" s="191">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K17" s="191">
-        <v>1679682</v>
+        <v>0</v>
       </c>
       <c r="L17" s="191">
-        <v>244</v>
+        <v>293</v>
       </c>
       <c r="M17" s="191">
-        <v>39244880</v>
+        <v>49312585</v>
       </c>
       <c r="N17" s="192">
-        <v>68.540000000000006</v>
+        <v>70.599999999999994</v>
       </c>
       <c r="O17" s="192">
-        <v>73.209999999999994</v>
+        <v>73.819999999999993</v>
       </c>
       <c r="P17" s="135">
         <f t="shared" si="0"/>
-        <v>12752611.170000002</v>
+        <v>15483518.789999999</v>
       </c>
       <c r="R17" s="173" t="s">
         <v>84</v>
@@ -29779,28 +29779,28 @@
       </c>
       <c r="U17" s="189">
         <f t="shared" si="2"/>
-        <v>39225642.670000002</v>
+        <v>23804513.670000002</v>
       </c>
       <c r="V17" s="175">
         <f t="shared" si="3"/>
-        <v>-4192185</v>
+        <v>-19613314</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A18" s="193" t="s">
-        <v>128</v>
+        <v>288</v>
       </c>
       <c r="B18" s="193" t="s">
-        <v>116</v>
+        <v>289</v>
       </c>
       <c r="C18" s="193" t="s">
-        <v>117</v>
+        <v>284</v>
       </c>
       <c r="D18" s="194">
-        <v>642</v>
+        <v>318</v>
       </c>
       <c r="E18" s="194">
-        <v>101866340</v>
+        <v>50351985</v>
       </c>
       <c r="F18" s="194">
         <v>0</v>
@@ -29809,49 +29809,49 @@
         <v>0</v>
       </c>
       <c r="H18" s="194">
-        <v>642</v>
+        <v>318</v>
       </c>
       <c r="I18" s="194">
-        <v>101866340</v>
+        <v>50351985</v>
       </c>
       <c r="J18" s="194">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K18" s="194">
-        <v>2286458</v>
+        <v>0</v>
       </c>
       <c r="L18" s="194">
-        <v>442</v>
+        <v>224</v>
       </c>
       <c r="M18" s="194">
-        <v>73362969</v>
+        <v>37022198</v>
       </c>
       <c r="N18" s="195">
-        <v>68.849999999999994</v>
+        <v>70.44</v>
       </c>
       <c r="O18" s="195">
-        <v>72.02</v>
+        <v>73.53</v>
       </c>
       <c r="P18" s="135">
         <f t="shared" si="0"/>
-        <v>25447380.799999997</v>
+        <v>11819227.449999996</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A19" s="190" t="s">
-        <v>288</v>
+        <v>128</v>
       </c>
       <c r="B19" s="190" t="s">
-        <v>289</v>
+        <v>116</v>
       </c>
       <c r="C19" s="190" t="s">
-        <v>284</v>
+        <v>117</v>
       </c>
       <c r="D19" s="191">
-        <v>318</v>
+        <v>642</v>
       </c>
       <c r="E19" s="191">
-        <v>50351985</v>
+        <v>101866340</v>
       </c>
       <c r="F19" s="191">
         <v>0</v>
@@ -29860,32 +29860,32 @@
         <v>0</v>
       </c>
       <c r="H19" s="191">
-        <v>318</v>
+        <v>642</v>
       </c>
       <c r="I19" s="191">
-        <v>50351985</v>
+        <v>101866340</v>
       </c>
       <c r="J19" s="191">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K19" s="191">
-        <v>995412</v>
+        <v>228099</v>
       </c>
       <c r="L19" s="191">
-        <v>215</v>
+        <v>448</v>
       </c>
       <c r="M19" s="191">
-        <v>35692648</v>
+        <v>74243972</v>
       </c>
       <c r="N19" s="192">
-        <v>67.61</v>
+        <v>69.78</v>
       </c>
       <c r="O19" s="192">
-        <v>70.89</v>
+        <v>72.88</v>
       </c>
       <c r="P19" s="135">
         <f t="shared" si="0"/>
-        <v>13148777.449999996</v>
+        <v>24566377.799999997</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.45">
@@ -29893,16 +29893,16 @@
         <v>129</v>
       </c>
       <c r="B20" s="193" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="C20" s="193" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="D20" s="194">
-        <v>968</v>
+        <v>588</v>
       </c>
       <c r="E20" s="194">
-        <v>162344260</v>
+        <v>95369711</v>
       </c>
       <c r="F20" s="194">
         <v>0</v>
@@ -29911,32 +29911,32 @@
         <v>0</v>
       </c>
       <c r="H20" s="194">
-        <v>968</v>
+        <v>588</v>
       </c>
       <c r="I20" s="194">
-        <v>162344260</v>
+        <v>95369711</v>
       </c>
       <c r="J20" s="194">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="K20" s="194">
-        <v>6337518</v>
+        <v>12863161</v>
       </c>
       <c r="L20" s="194">
-        <v>656</v>
+        <v>414</v>
       </c>
       <c r="M20" s="194">
-        <v>112037215</v>
+        <v>68704106</v>
       </c>
       <c r="N20" s="195">
-        <v>67.77</v>
+        <v>70.41</v>
       </c>
       <c r="O20" s="195">
-        <v>69.010000000000005</v>
+        <v>72.040000000000006</v>
       </c>
       <c r="P20" s="135">
         <f t="shared" si="0"/>
-        <v>45436717.199999988</v>
+        <v>23804513.670000002</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.45">
@@ -29968,26 +29968,26 @@
         <v>141474291</v>
       </c>
       <c r="J21" s="191">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="K21" s="191">
-        <v>5519149</v>
+        <v>358927</v>
       </c>
       <c r="L21" s="191">
-        <v>552</v>
+        <v>592</v>
       </c>
       <c r="M21" s="191">
-        <v>93425764</v>
+        <v>99552951</v>
       </c>
       <c r="N21" s="192">
-        <v>64.709999999999994</v>
+        <v>69.400000000000006</v>
       </c>
       <c r="O21" s="192">
-        <v>66.040000000000006</v>
+        <v>70.37</v>
       </c>
       <c r="P21" s="135">
         <f t="shared" si="0"/>
-        <v>43804298.270000011</v>
+        <v>37677111.270000011</v>
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.45">
@@ -29995,16 +29995,16 @@
         <v>129</v>
       </c>
       <c r="B22" s="193" t="s">
-        <v>112</v>
+        <v>71</v>
       </c>
       <c r="C22" s="193" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
       <c r="D22" s="194">
-        <v>1198</v>
+        <v>968</v>
       </c>
       <c r="E22" s="194">
-        <v>194517020</v>
+        <v>162344260</v>
       </c>
       <c r="F22" s="194">
         <v>0</v>
@@ -30013,32 +30013,32 @@
         <v>0</v>
       </c>
       <c r="H22" s="194">
-        <v>1198</v>
+        <v>968</v>
       </c>
       <c r="I22" s="194">
-        <v>194517020</v>
+        <v>162344260</v>
       </c>
       <c r="J22" s="194">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="K22" s="194">
-        <v>3442175</v>
+        <v>536613</v>
       </c>
       <c r="L22" s="194">
-        <v>753</v>
+        <v>670</v>
       </c>
       <c r="M22" s="194">
-        <v>125078308</v>
+        <v>114092842</v>
       </c>
       <c r="N22" s="195">
-        <v>62.85</v>
+        <v>69.209999999999994</v>
       </c>
       <c r="O22" s="195">
-        <v>64.3</v>
+        <v>70.28</v>
       </c>
       <c r="P22" s="135">
         <f t="shared" si="0"/>
-        <v>63603201.400000006</v>
+        <v>43381090.199999988</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.45">
@@ -30070,43 +30070,43 @@
         <v>105953075</v>
       </c>
       <c r="J23" s="191">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K23" s="191">
-        <v>1049058</v>
+        <v>168000</v>
       </c>
       <c r="L23" s="191">
-        <v>399</v>
+        <v>451</v>
       </c>
       <c r="M23" s="191">
-        <v>62655654</v>
+        <v>71514461</v>
       </c>
       <c r="N23" s="192">
-        <v>58.08</v>
+        <v>65.650000000000006</v>
       </c>
       <c r="O23" s="192">
-        <v>59.14</v>
+        <v>67.5</v>
       </c>
       <c r="P23" s="135">
         <f t="shared" si="0"/>
-        <v>40118828.75</v>
+        <v>31260021.75</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A24" s="193" t="s">
-        <v>288</v>
+        <v>129</v>
       </c>
       <c r="B24" s="193" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="C24" s="193" t="s">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="D24" s="194">
-        <v>546</v>
+        <v>1198</v>
       </c>
       <c r="E24" s="194">
-        <v>89879995</v>
+        <v>194517020</v>
       </c>
       <c r="F24" s="194">
         <v>0</v>
@@ -30115,32 +30115,32 @@
         <v>0</v>
       </c>
       <c r="H24" s="194">
-        <v>546</v>
+        <v>1198</v>
       </c>
       <c r="I24" s="194">
-        <v>89879995</v>
+        <v>194517020</v>
       </c>
       <c r="J24" s="194">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="K24" s="194">
-        <v>3026875</v>
+        <v>294983</v>
       </c>
       <c r="L24" s="194">
-        <v>304</v>
+        <v>759</v>
       </c>
       <c r="M24" s="194">
-        <v>51886461</v>
+        <v>126339011</v>
       </c>
       <c r="N24" s="195">
-        <v>55.68</v>
+        <v>63.36</v>
       </c>
       <c r="O24" s="195">
-        <v>57.73</v>
+        <v>64.95</v>
       </c>
       <c r="P24" s="135">
         <f t="shared" si="0"/>
-        <v>35297134.149999991</v>
+        <v>62342498.400000006</v>
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.45">
@@ -30172,43 +30172,43 @@
         <v>149379338</v>
       </c>
       <c r="J25" s="191">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="K25" s="191">
-        <v>2327727</v>
+        <v>5451000</v>
       </c>
       <c r="L25" s="191">
-        <v>519</v>
+        <v>577</v>
       </c>
       <c r="M25" s="191">
-        <v>86035872</v>
+        <v>95757870</v>
       </c>
       <c r="N25" s="192">
-        <v>58.18</v>
+        <v>64.69</v>
       </c>
       <c r="O25" s="192">
-        <v>57.6</v>
+        <v>64.099999999999994</v>
       </c>
       <c r="P25" s="135">
         <f t="shared" si="0"/>
-        <v>58862085.859999985</v>
+        <v>49140087.859999985</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A26" s="193" t="s">
-        <v>129</v>
+        <v>288</v>
       </c>
       <c r="B26" s="193" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C26" s="193" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D26" s="194">
-        <v>588</v>
+        <v>546</v>
       </c>
       <c r="E26" s="194">
-        <v>95369711</v>
+        <v>89879995</v>
       </c>
       <c r="F26" s="194">
         <v>0</v>
@@ -30217,32 +30217,32 @@
         <v>0</v>
       </c>
       <c r="H26" s="194">
-        <v>588</v>
+        <v>546</v>
       </c>
       <c r="I26" s="194">
-        <v>95369711</v>
+        <v>89879995</v>
       </c>
       <c r="J26" s="194">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="K26" s="194">
-        <v>4292185</v>
+        <v>118230</v>
       </c>
       <c r="L26" s="194">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="M26" s="194">
-        <v>53282977</v>
+        <v>56235390</v>
       </c>
       <c r="N26" s="195">
-        <v>54.08</v>
+        <v>60.62</v>
       </c>
       <c r="O26" s="195">
-        <v>55.87</v>
+        <v>62.57</v>
       </c>
       <c r="P26" s="135">
         <f t="shared" si="0"/>
-        <v>39225642.670000002</v>
+        <v>30948205.149999991</v>
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.45">
@@ -30274,35 +30274,30 @@
         <v>105983346</v>
       </c>
       <c r="J27" s="191">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="K27" s="191">
-        <v>932012</v>
+        <v>7838032</v>
       </c>
       <c r="L27" s="191">
-        <v>217</v>
+        <v>355</v>
       </c>
       <c r="M27" s="191">
-        <v>33554154</v>
+        <v>51681346</v>
       </c>
       <c r="N27" s="192">
-        <v>31.77</v>
+        <v>51.98</v>
       </c>
       <c r="O27" s="192">
-        <v>31.66</v>
+        <v>48.76</v>
       </c>
       <c r="P27" s="135">
         <f t="shared" si="0"/>
-        <v>69249691.61999999</v>
+        <v>51122499.61999999</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="U5:U6"/>
-    <mergeCell ref="V5:V6"/>
-    <mergeCell ref="R5:R6"/>
-    <mergeCell ref="S5:S6"/>
-    <mergeCell ref="T5:T6"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
     <mergeCell ref="A3:B3"/>
@@ -30317,6 +30312,11 @@
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="L5:M5"/>
     <mergeCell ref="N5:O5"/>
+    <mergeCell ref="U5:U6"/>
+    <mergeCell ref="V5:V6"/>
+    <mergeCell ref="R5:R6"/>
+    <mergeCell ref="S5:S6"/>
+    <mergeCell ref="T5:T6"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="P7:P27">

--- a/filetiendo.xlsx
+++ b/filetiendo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\viettel 2026\thang 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D30356FE-07CC-475B-9035-AE788864ECBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFCD2D9C-B6F2-43B4-A833-7C6814F3EE02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="808" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AS5" s="129">
         <f>(VLOOKUP(B5,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.79400000000000004</v>
+        <v>0.80079999999999996</v>
       </c>
       <c r="AT5" s="14">
         <f t="shared" ref="AT5:AT18" si="20">IF(AS5&lt;94.5%,0,IF(AS5&lt;95.54%,50%,IF(AS5&lt;AR5,80%,100%+(30%*(AS5-AR5)/3.39%))))</f>
@@ -6788,7 +6788,7 @@
       </c>
       <c r="AU5" s="54">
         <f t="shared" ref="AU5:AU18" si="21">AR5-AS5</f>
-        <v>0.17599999999999993</v>
+        <v>0.16920000000000002</v>
       </c>
       <c r="AV5" s="57">
         <f>VLOOKUP(C5,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7013,7 +7013,7 @@
       </c>
       <c r="AS6" s="129">
         <f>(VLOOKUP(B6,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.70279999999999998</v>
+        <v>0.71310000000000007</v>
       </c>
       <c r="AT6" s="14">
         <f t="shared" si="20"/>
@@ -7021,7 +7021,7 @@
       </c>
       <c r="AU6" s="54">
         <f t="shared" si="21"/>
-        <v>0.26719999999999999</v>
+        <v>0.25689999999999991</v>
       </c>
       <c r="AV6" s="57">
         <f>VLOOKUP(C6,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7200,15 +7200,15 @@
       </c>
       <c r="AG7" s="13">
         <f>VLOOKUP(C7,GBOC!$E$7:$DG$29,$B$27,0)</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AH7" s="14">
         <f t="shared" si="14"/>
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="AI7" s="52">
         <f t="shared" si="15"/>
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="AJ7" s="57">
         <f>VLOOKUP(C7,'Giao CT'!$D$6:$S$20,11,0)</f>
@@ -7246,7 +7246,7 @@
       </c>
       <c r="AS7" s="129">
         <f>(VLOOKUP(B7,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.75800000000000001</v>
+        <v>0.76590000000000003</v>
       </c>
       <c r="AT7" s="14">
         <f t="shared" si="20"/>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="AU7" s="54">
         <f t="shared" si="21"/>
-        <v>0.21199999999999997</v>
+        <v>0.20409999999999995</v>
       </c>
       <c r="AV7" s="57">
         <f>VLOOKUP(C7,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7479,7 +7479,7 @@
       </c>
       <c r="AS8" s="129">
         <f>(VLOOKUP(B8,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.48759999999999998</v>
+        <v>0.64260000000000006</v>
       </c>
       <c r="AT8" s="14">
         <f t="shared" si="20"/>
@@ -7487,7 +7487,7 @@
       </c>
       <c r="AU8" s="54">
         <f t="shared" si="21"/>
-        <v>0.4824</v>
+        <v>0.32739999999999991</v>
       </c>
       <c r="AV8" s="57">
         <f>VLOOKUP(C8,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7634,15 +7634,15 @@
       </c>
       <c r="Y9" s="13">
         <f>VLOOKUP(C9,GBOC!$E$7:$DG$29,$B$25,0)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z9" s="14">
         <f t="shared" si="10"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA9" s="52">
         <f t="shared" si="11"/>
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="AB9" s="57">
         <f>VLOOKUP(C9,'Giao CT'!$D$6:$S$20,9,0)</f>
@@ -7650,15 +7650,15 @@
       </c>
       <c r="AC9" s="13">
         <f>VLOOKUP(C9,GBOC!$E$7:$DG$29,$B$26,0)</f>
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD9" s="14">
         <f t="shared" si="12"/>
-        <v>2.1</v>
+        <v>2.125</v>
       </c>
       <c r="AE9" s="52">
         <f t="shared" si="13"/>
-        <v>-44</v>
+        <v>-45</v>
       </c>
       <c r="AF9" s="57">
         <f>VLOOKUP(C9,'Giao CT'!$D$6:$S$20,10,0)</f>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="AS9" s="129">
         <f>(VLOOKUP(B9,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.62570000000000003</v>
+        <v>0.63890000000000002</v>
       </c>
       <c r="AT9" s="14">
         <f t="shared" si="20"/>
@@ -7720,7 +7720,7 @@
       </c>
       <c r="AU9" s="54">
         <f t="shared" si="21"/>
-        <v>0.34429999999999994</v>
+        <v>0.33109999999999995</v>
       </c>
       <c r="AV9" s="57">
         <f>VLOOKUP(C9,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7945,7 +7945,7 @@
       </c>
       <c r="AS10" s="129">
         <f>(VLOOKUP(B10,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.72040000000000004</v>
+        <v>0.7340000000000001</v>
       </c>
       <c r="AT10" s="14">
         <f t="shared" si="20"/>
@@ -7953,7 +7953,7 @@
       </c>
       <c r="AU10" s="54">
         <f t="shared" si="21"/>
-        <v>0.24959999999999993</v>
+        <v>0.23599999999999988</v>
       </c>
       <c r="AV10" s="57">
         <f>VLOOKUP(C10,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="AS11" s="129">
         <f>(VLOOKUP(B11,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.7037000000000001</v>
+        <v>0.71579999999999999</v>
       </c>
       <c r="AT11" s="14">
         <f t="shared" si="20"/>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="AU11" s="54">
         <f t="shared" si="21"/>
-        <v>0.26629999999999987</v>
+        <v>0.25419999999999998</v>
       </c>
       <c r="AV11" s="57">
         <f>VLOOKUP(C11,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8253,15 +8253,15 @@
       </c>
       <c r="E12" s="64">
         <f>VLOOKUP(C12,GBOC!$E$7:$DG$29,$B$20,0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F12" s="14">
         <f t="shared" si="0"/>
-        <v>1.125</v>
+        <v>1.25</v>
       </c>
       <c r="G12" s="52">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H12" s="12">
         <f>VLOOKUP(C12,'Giao CT'!$D$6:$S$20,4,0)</f>
@@ -8269,15 +8269,15 @@
       </c>
       <c r="I12" s="13">
         <f>VLOOKUP(C12,GBOC!$E$7:$DG$29,$B$21,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J12" s="14">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="K12" s="52">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L12" s="12">
         <f>VLOOKUP(C12,'Giao CT'!$D$6:$S$20,5,0)</f>
@@ -8411,7 +8411,7 @@
       </c>
       <c r="AS12" s="129">
         <f>(VLOOKUP(B12,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.67500000000000004</v>
+        <v>0.69159999999999999</v>
       </c>
       <c r="AT12" s="14">
         <f t="shared" si="20"/>
@@ -8419,7 +8419,7 @@
       </c>
       <c r="AU12" s="54">
         <f t="shared" si="21"/>
-        <v>0.29499999999999993</v>
+        <v>0.27839999999999998</v>
       </c>
       <c r="AV12" s="57">
         <f>VLOOKUP(C12,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8582,15 +8582,15 @@
       </c>
       <c r="AC13" s="13">
         <f>VLOOKUP(C13,GBOC!$E$7:$DG$29,$B$26,0)</f>
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AD13" s="14">
         <f t="shared" si="12"/>
-        <v>2.2000000000000002</v>
+        <v>2.2333333333333334</v>
       </c>
       <c r="AE13" s="52">
         <f t="shared" si="13"/>
-        <v>-36</v>
+        <v>-37</v>
       </c>
       <c r="AF13" s="57">
         <f>VLOOKUP(C13,'Giao CT'!$D$6:$S$20,10,0)</f>
@@ -8644,7 +8644,7 @@
       </c>
       <c r="AS13" s="129">
         <f>(VLOOKUP(B13,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.78879999999999995</v>
+        <v>0.79359999999999997</v>
       </c>
       <c r="AT13" s="14">
         <f t="shared" si="20"/>
@@ -8652,7 +8652,7 @@
       </c>
       <c r="AU13" s="54">
         <f t="shared" si="21"/>
-        <v>0.18120000000000003</v>
+        <v>0.1764</v>
       </c>
       <c r="AV13" s="57">
         <f>VLOOKUP(C13,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8877,7 +8877,7 @@
       </c>
       <c r="AS14" s="129">
         <f>(VLOOKUP(B14,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.6409999999999999</v>
+        <v>0.66079999999999994</v>
       </c>
       <c r="AT14" s="14">
         <f t="shared" si="20"/>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="AU14" s="54">
         <f t="shared" si="21"/>
-        <v>0.32900000000000007</v>
+        <v>0.30920000000000003</v>
       </c>
       <c r="AV14" s="57">
         <f>VLOOKUP(C14,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8952,15 +8952,15 @@
       </c>
       <c r="E15" s="64">
         <f>VLOOKUP(C15,GBOC!$E$7:$DG$29,$B$20,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F15" s="14">
         <f t="shared" si="0"/>
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="G15" s="52">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" s="12">
         <f>VLOOKUP(C15,'Giao CT'!$D$6:$S$20,4,0)</f>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="AS15" s="129">
         <f>(VLOOKUP(B15,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.64950000000000008</v>
+        <v>0.6634000000000001</v>
       </c>
       <c r="AT15" s="14">
         <f t="shared" si="20"/>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="AU15" s="54">
         <f t="shared" si="21"/>
-        <v>0.3204999999999999</v>
+        <v>0.30659999999999987</v>
       </c>
       <c r="AV15" s="57">
         <f>VLOOKUP(C15,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="AS16" s="129">
         <f>(VLOOKUP(B16,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.7288</v>
+        <v>0.7419</v>
       </c>
       <c r="AT16" s="14">
         <f t="shared" si="20"/>
@@ -9351,7 +9351,7 @@
       </c>
       <c r="AU16" s="54">
         <f t="shared" si="21"/>
-        <v>0.24119999999999997</v>
+        <v>0.22809999999999997</v>
       </c>
       <c r="AV16" s="57">
         <f>VLOOKUP(C16,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="AS17" s="129">
         <f>(VLOOKUP(B17,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.76200000000000001</v>
+        <v>0.77190000000000003</v>
       </c>
       <c r="AT17" s="14">
         <f t="shared" si="20"/>
@@ -9584,7 +9584,7 @@
       </c>
       <c r="AU17" s="54">
         <f t="shared" si="21"/>
-        <v>0.20799999999999996</v>
+        <v>0.19809999999999994</v>
       </c>
       <c r="AV17" s="57">
         <f>VLOOKUP(C17,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -9809,7 +9809,7 @@
       </c>
       <c r="AS18" s="129">
         <f>(VLOOKUP(B18,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.73819999999999997</v>
+        <v>0.746</v>
       </c>
       <c r="AT18" s="14">
         <f t="shared" si="20"/>
@@ -9817,7 +9817,7 @@
       </c>
       <c r="AU18" s="54">
         <f t="shared" si="21"/>
-        <v>0.23180000000000001</v>
+        <v>0.22399999999999998</v>
       </c>
       <c r="AV18" s="57">
         <f>VLOOKUP(C18,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -11147,7 +11147,7 @@
       </c>
       <c r="D14" s="74">
         <f>VLOOKUP($B$2,'TH NV'!$A$5:$BG$18,N14,0)</f>
-        <v>0.79400000000000004</v>
+        <v>0.80079999999999996</v>
       </c>
       <c r="E14" s="49" t="e">
         <f>VLOOKUP($B$2,'TH NV'!$A$1:$BG$18,70,0)</f>
@@ -11170,7 +11170,7 @@
       </c>
       <c r="J14" s="65">
         <f t="shared" si="2"/>
-        <v>0.17599999999999993</v>
+        <v>0.16920000000000002</v>
       </c>
       <c r="K14" s="222"/>
       <c r="L14" s="114" t="s">
@@ -11855,7 +11855,7 @@
       </c>
       <c r="AS4" s="129">
         <f>(VLOOKUP(B4,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.79400000000000004</v>
+        <v>0.80079999999999996</v>
       </c>
       <c r="AT4" s="14">
         <f t="shared" ref="AT4" si="20">IF(AS4&lt;94.5%,0,IF(AS4&lt;95.54%,50%,IF(AS4&lt;AR4,80%,100%+(30%*(AS4-AR4)/3.39%))))</f>
@@ -11863,7 +11863,7 @@
       </c>
       <c r="AU4" s="54">
         <f t="shared" ref="AU4" si="21">AR4-AS4</f>
-        <v>0.17599999999999993</v>
+        <v>0.16920000000000002</v>
       </c>
       <c r="AV4" s="57">
         <f>VLOOKUP(A4,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -12089,7 +12089,7 @@
       </c>
       <c r="AS5" s="129">
         <f>(VLOOKUP(B5,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.7037000000000001</v>
+        <v>0.71579999999999999</v>
       </c>
       <c r="AT5" s="14">
         <f t="shared" ref="AT5:AT16" si="48">IF(AS5&lt;94.5%,0,IF(AS5&lt;95.54%,50%,IF(AS5&lt;AR5,80%,100%+(30%*(AS5-AR5)/3.39%))))</f>
@@ -12097,7 +12097,7 @@
       </c>
       <c r="AU5" s="54">
         <f t="shared" ref="AU5:AU16" si="49">AR5-AS5</f>
-        <v>0.26629999999999987</v>
+        <v>0.25419999999999998</v>
       </c>
       <c r="AV5" s="57">
         <f>VLOOKUP(A5,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -12164,15 +12164,15 @@
       </c>
       <c r="E6" s="64">
         <f>VLOOKUP(A6,GBOC!$E$7:$DG$29,$B$21,0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F6" s="14">
         <f t="shared" si="28"/>
-        <v>1.125</v>
+        <v>1.25</v>
       </c>
       <c r="G6" s="52">
         <f t="shared" si="29"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H6" s="140">
         <f>VLOOKUP(A6,'Giao CT'!$D$6:$S$20,4,0)</f>
@@ -12180,15 +12180,15 @@
       </c>
       <c r="I6" s="13">
         <f>VLOOKUP(A6,GBOC!$E$7:$DG$29,$B$22,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J6" s="14">
         <f t="shared" si="30"/>
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="K6" s="52">
         <f t="shared" si="31"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L6" s="140">
         <f>VLOOKUP(A6,'Giao CT'!$D$6:$S$20,5,0)</f>
@@ -12323,7 +12323,7 @@
       </c>
       <c r="AS6" s="129">
         <f>(VLOOKUP(B6,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.67500000000000004</v>
+        <v>0.69159999999999999</v>
       </c>
       <c r="AT6" s="14">
         <f t="shared" si="48"/>
@@ -12331,7 +12331,7 @@
       </c>
       <c r="AU6" s="54">
         <f t="shared" si="49"/>
-        <v>0.29499999999999993</v>
+        <v>0.27839999999999998</v>
       </c>
       <c r="AV6" s="57">
         <f>VLOOKUP(A6,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -12557,7 +12557,7 @@
       </c>
       <c r="AS7" s="129">
         <f>(VLOOKUP(B7,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.6409999999999999</v>
+        <v>0.66079999999999994</v>
       </c>
       <c r="AT7" s="14">
         <f t="shared" si="48"/>
@@ -12565,7 +12565,7 @@
       </c>
       <c r="AU7" s="54">
         <f t="shared" si="49"/>
-        <v>0.32900000000000007</v>
+        <v>0.30920000000000003</v>
       </c>
       <c r="AV7" s="57">
         <f>VLOOKUP(A7,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -12791,7 +12791,7 @@
       </c>
       <c r="AS8" s="129">
         <f>(VLOOKUP(B8,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.7288</v>
+        <v>0.7419</v>
       </c>
       <c r="AT8" s="14">
         <f t="shared" si="48"/>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="AU8" s="54">
         <f t="shared" si="49"/>
-        <v>0.24119999999999997</v>
+        <v>0.22809999999999997</v>
       </c>
       <c r="AV8" s="57">
         <f>VLOOKUP(A8,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -13086,7 +13086,7 @@
       </c>
       <c r="AS10" s="129">
         <f>(VLOOKUP(B10,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.70279999999999998</v>
+        <v>0.71310000000000007</v>
       </c>
       <c r="AT10" s="14">
         <f t="shared" si="48"/>
@@ -13094,7 +13094,7 @@
       </c>
       <c r="AU10" s="54">
         <f t="shared" si="49"/>
-        <v>0.26719999999999999</v>
+        <v>0.25689999999999991</v>
       </c>
       <c r="AV10" s="57">
         <f>VLOOKUP(A10,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -13273,15 +13273,15 @@
       </c>
       <c r="AG11" s="13">
         <f>VLOOKUP(A11,GBOC!$E$7:$DG$29,$B$28,0)</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AH11" s="14">
         <f t="shared" si="42"/>
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="AI11" s="52">
         <f t="shared" si="43"/>
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="AJ11" s="57">
         <f>VLOOKUP(A11,'Giao CT'!$D$6:$S$20,11,0)</f>
@@ -13320,7 +13320,7 @@
       </c>
       <c r="AS11" s="129">
         <f>(VLOOKUP(B11,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.75800000000000001</v>
+        <v>0.76590000000000003</v>
       </c>
       <c r="AT11" s="14">
         <f t="shared" si="48"/>
@@ -13328,7 +13328,7 @@
       </c>
       <c r="AU11" s="54">
         <f t="shared" si="49"/>
-        <v>0.21199999999999997</v>
+        <v>0.20409999999999995</v>
       </c>
       <c r="AV11" s="57">
         <f>VLOOKUP(A11,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -13554,7 +13554,7 @@
       </c>
       <c r="AS12" s="129">
         <f>(VLOOKUP(B12,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.48759999999999998</v>
+        <v>0.64260000000000006</v>
       </c>
       <c r="AT12" s="14">
         <f t="shared" si="48"/>
@@ -13562,7 +13562,7 @@
       </c>
       <c r="AU12" s="54">
         <f t="shared" si="49"/>
-        <v>0.4824</v>
+        <v>0.32739999999999991</v>
       </c>
       <c r="AV12" s="57">
         <f>VLOOKUP(A12,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -13788,7 +13788,7 @@
       </c>
       <c r="AS13" s="129">
         <f>(VLOOKUP(B13,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.72040000000000004</v>
+        <v>0.7340000000000001</v>
       </c>
       <c r="AT13" s="14">
         <f t="shared" si="48"/>
@@ -13796,7 +13796,7 @@
       </c>
       <c r="AU13" s="54">
         <f t="shared" si="49"/>
-        <v>0.24959999999999993</v>
+        <v>0.23599999999999988</v>
       </c>
       <c r="AV13" s="57">
         <f>VLOOKUP(A13,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -13959,15 +13959,15 @@
       </c>
       <c r="AC14" s="13">
         <f>VLOOKUP(A14,GBOC!$E$7:$DG$29,$B$27,0)</f>
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AD14" s="14">
         <f t="shared" si="40"/>
-        <v>2.2000000000000002</v>
+        <v>2.2333333333333334</v>
       </c>
       <c r="AE14" s="52">
         <f t="shared" si="41"/>
-        <v>-36</v>
+        <v>-37</v>
       </c>
       <c r="AF14" s="57">
         <f>VLOOKUP(A14,'Giao CT'!$D$6:$S$20,10,0)</f>
@@ -14022,7 +14022,7 @@
       </c>
       <c r="AS14" s="129">
         <f>(VLOOKUP(B14,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.78879999999999995</v>
+        <v>0.79359999999999997</v>
       </c>
       <c r="AT14" s="14">
         <f t="shared" si="48"/>
@@ -14030,7 +14030,7 @@
       </c>
       <c r="AU14" s="54">
         <f t="shared" si="49"/>
-        <v>0.18120000000000003</v>
+        <v>0.1764</v>
       </c>
       <c r="AV14" s="57">
         <f>VLOOKUP(A14,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -14097,15 +14097,15 @@
       </c>
       <c r="E15" s="64">
         <f>VLOOKUP(A15,GBOC!$E$7:$DG$29,$B$21,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F15" s="14">
         <f t="shared" si="28"/>
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="G15" s="52">
         <f t="shared" si="29"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" s="140">
         <f>VLOOKUP(A15,'Giao CT'!$D$6:$S$20,4,0)</f>
@@ -14256,7 +14256,7 @@
       </c>
       <c r="AS15" s="129">
         <f>(VLOOKUP(B15,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.64950000000000008</v>
+        <v>0.6634000000000001</v>
       </c>
       <c r="AT15" s="14">
         <f t="shared" si="48"/>
@@ -14264,7 +14264,7 @@
       </c>
       <c r="AU15" s="54">
         <f t="shared" si="49"/>
-        <v>0.3204999999999999</v>
+        <v>0.30659999999999987</v>
       </c>
       <c r="AV15" s="57">
         <f>VLOOKUP(A15,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -14490,7 +14490,7 @@
       </c>
       <c r="AS16" s="129">
         <f>(VLOOKUP(B16,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.76200000000000001</v>
+        <v>0.77190000000000003</v>
       </c>
       <c r="AT16" s="14">
         <f t="shared" si="48"/>
@@ -14498,7 +14498,7 @@
       </c>
       <c r="AU16" s="54">
         <f t="shared" si="49"/>
-        <v>0.20799999999999996</v>
+        <v>0.19809999999999994</v>
       </c>
       <c r="AV16" s="57">
         <f>VLOOKUP(A16,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -14582,11 +14582,11 @@
       </c>
       <c r="C19" s="142">
         <f ca="1">SUMIF(cuoc!A7:P27,'tiến độ'!A19,cuoc!M7:M27)</f>
-        <v>456273113</v>
+        <v>465017488</v>
       </c>
       <c r="D19" s="142">
         <f ca="1">B19*0.968-C19</f>
-        <v>166900958.25599992</v>
+        <v>158156583.25599992</v>
       </c>
       <c r="E19" s="137"/>
       <c r="H19" s="137"/>
@@ -14603,11 +14603,11 @@
       </c>
       <c r="C20" s="143">
         <f ca="1">SUMIF(cuoc!A8:P27,'tiến độ'!A20,cuoc!M8:M27)</f>
-        <v>711857872</v>
+        <v>721476778</v>
       </c>
       <c r="D20" s="142">
         <f ca="1">B20*0.968-C20</f>
-        <v>232126054.77600002</v>
+        <v>222507148.77600002</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.45">
@@ -15950,7 +15950,7 @@
         <v>12</v>
       </c>
       <c r="L7" s="197">
-        <v>218.18</v>
+        <v>208.7</v>
       </c>
       <c r="M7" s="197">
         <v>171.43</v>
@@ -15974,7 +15974,7 @@
         <v>6</v>
       </c>
       <c r="T7" s="197">
-        <v>190.91</v>
+        <v>182.61</v>
       </c>
       <c r="U7" s="197">
         <v>150</v>
@@ -16022,7 +16022,7 @@
         <v>1</v>
       </c>
       <c r="AJ7" s="197">
-        <v>168.18</v>
+        <v>169.57</v>
       </c>
       <c r="AK7" s="197">
         <v>175</v>
@@ -16058,7 +16058,7 @@
         <v>100</v>
       </c>
       <c r="AV7" s="197">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AW7" s="197">
         <v>35</v>
@@ -16070,7 +16070,7 @@
         <v>37</v>
       </c>
       <c r="AZ7" s="197">
-        <v>134.55000000000001</v>
+        <v>128.69999999999999</v>
       </c>
       <c r="BA7" s="197">
         <v>105.71</v>
@@ -16094,7 +16094,7 @@
         <v>4</v>
       </c>
       <c r="BH7" s="197">
-        <v>101.82</v>
+        <v>97.39</v>
       </c>
       <c r="BI7" s="197">
         <v>80</v>
@@ -16136,16 +16136,16 @@
         <v>1</v>
       </c>
       <c r="BV7" s="197">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW7" s="197">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX7" s="197">
-        <v>0</v>
+        <v>121.74</v>
       </c>
       <c r="BY7" s="197">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BZ7" s="197">
         <v>0</v>
@@ -16154,7 +16154,7 @@
         <v>100</v>
       </c>
       <c r="CB7" s="197">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CC7" s="197">
         <v>8</v>
@@ -16166,7 +16166,7 @@
         <v>5</v>
       </c>
       <c r="CF7" s="197">
-        <v>79.55</v>
+        <v>76.09</v>
       </c>
       <c r="CG7" s="197">
         <v>62.5</v>
@@ -16190,7 +16190,7 @@
         <v>9</v>
       </c>
       <c r="CN7" s="197">
-        <v>286.36</v>
+        <v>273.91000000000003</v>
       </c>
       <c r="CO7" s="197">
         <v>225</v>
@@ -16214,7 +16214,7 @@
         <v>5</v>
       </c>
       <c r="CV7" s="197">
-        <v>159.09</v>
+        <v>152.16999999999999</v>
       </c>
       <c r="CW7" s="197">
         <v>125</v>
@@ -16238,7 +16238,7 @@
         <v>6</v>
       </c>
       <c r="DD7" s="197">
-        <v>763.64</v>
+        <v>730.43</v>
       </c>
       <c r="DE7" s="197">
         <v>600</v>
@@ -16279,13 +16279,13 @@
         <v>7</v>
       </c>
       <c r="J8" s="197">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" s="197">
         <v>13</v>
       </c>
       <c r="L8" s="197">
-        <v>236.36</v>
+        <v>226.09</v>
       </c>
       <c r="M8" s="197">
         <v>185.71</v>
@@ -16309,7 +16309,7 @@
         <v>4</v>
       </c>
       <c r="T8" s="197">
-        <v>127.27</v>
+        <v>121.74</v>
       </c>
       <c r="U8" s="197">
         <v>100</v>
@@ -16357,7 +16357,7 @@
         <v>2</v>
       </c>
       <c r="AJ8" s="197">
-        <v>149.09</v>
+        <v>151.30000000000001</v>
       </c>
       <c r="AK8" s="197">
         <v>160</v>
@@ -16393,7 +16393,7 @@
         <v>100</v>
       </c>
       <c r="AV8" s="197">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW8" s="197">
         <v>30</v>
@@ -16405,7 +16405,7 @@
         <v>71</v>
       </c>
       <c r="AZ8" s="197">
-        <v>301.20999999999998</v>
+        <v>288.12</v>
       </c>
       <c r="BA8" s="197">
         <v>236.67</v>
@@ -16429,7 +16429,7 @@
         <v>5</v>
       </c>
       <c r="BH8" s="197">
-        <v>127.27</v>
+        <v>121.74</v>
       </c>
       <c r="BI8" s="197">
         <v>100</v>
@@ -16489,7 +16489,7 @@
         <v>100</v>
       </c>
       <c r="CB8" s="197">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CC8" s="197">
         <v>8</v>
@@ -16501,7 +16501,7 @@
         <v>10</v>
       </c>
       <c r="CF8" s="197">
-        <v>159.09</v>
+        <v>152.16999999999999</v>
       </c>
       <c r="CG8" s="197">
         <v>125</v>
@@ -16525,7 +16525,7 @@
         <v>7</v>
       </c>
       <c r="CN8" s="197">
-        <v>222.73</v>
+        <v>213.04</v>
       </c>
       <c r="CO8" s="197">
         <v>175</v>
@@ -16549,7 +16549,7 @@
         <v>4</v>
       </c>
       <c r="CV8" s="197">
-        <v>127.27</v>
+        <v>121.74</v>
       </c>
       <c r="CW8" s="197">
         <v>100</v>
@@ -16573,7 +16573,7 @@
         <v>6</v>
       </c>
       <c r="DD8" s="197">
-        <v>763.64</v>
+        <v>730.43</v>
       </c>
       <c r="DE8" s="197">
         <v>600</v>
@@ -16620,7 +16620,7 @@
         <v>12</v>
       </c>
       <c r="L9" s="197">
-        <v>218.18</v>
+        <v>208.7</v>
       </c>
       <c r="M9" s="197">
         <v>171.43</v>
@@ -16644,7 +16644,7 @@
         <v>4</v>
       </c>
       <c r="T9" s="197">
-        <v>127.27</v>
+        <v>121.74</v>
       </c>
       <c r="U9" s="197">
         <v>100</v>
@@ -16668,7 +16668,7 @@
         <v>1</v>
       </c>
       <c r="AB9" s="197">
-        <v>42.42</v>
+        <v>40.58</v>
       </c>
       <c r="AC9" s="197">
         <v>33.33</v>
@@ -16728,7 +16728,7 @@
         <v>100</v>
       </c>
       <c r="AV9" s="197">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW9" s="197">
         <v>30</v>
@@ -16740,7 +16740,7 @@
         <v>27</v>
       </c>
       <c r="AZ9" s="197">
-        <v>114.55</v>
+        <v>109.57</v>
       </c>
       <c r="BA9" s="197">
         <v>90</v>
@@ -16764,7 +16764,7 @@
         <v>5</v>
       </c>
       <c r="BH9" s="197">
-        <v>127.27</v>
+        <v>121.74</v>
       </c>
       <c r="BI9" s="197">
         <v>100</v>
@@ -16824,7 +16824,7 @@
         <v>100</v>
       </c>
       <c r="CB9" s="197">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CC9" s="197">
         <v>8</v>
@@ -16833,13 +16833,13 @@
         <v>0</v>
       </c>
       <c r="CE9" s="197">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="CF9" s="197">
-        <v>95.45</v>
+        <v>182.61</v>
       </c>
       <c r="CG9" s="197">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="CH9" s="197">
         <v>0</v>
@@ -16860,7 +16860,7 @@
         <v>3</v>
       </c>
       <c r="CN9" s="197">
-        <v>95.45</v>
+        <v>91.3</v>
       </c>
       <c r="CO9" s="197">
         <v>75</v>
@@ -16884,7 +16884,7 @@
         <v>5</v>
       </c>
       <c r="CV9" s="197">
-        <v>212.12</v>
+        <v>202.9</v>
       </c>
       <c r="CW9" s="197">
         <v>166.67</v>
@@ -16908,7 +16908,7 @@
         <v>2</v>
       </c>
       <c r="DD9" s="197">
-        <v>254.55</v>
+        <v>243.48</v>
       </c>
       <c r="DE9" s="197">
         <v>200</v>
@@ -16955,7 +16955,7 @@
         <v>5</v>
       </c>
       <c r="L10" s="197">
-        <v>90.91</v>
+        <v>86.96</v>
       </c>
       <c r="M10" s="197">
         <v>71.430000000000007</v>
@@ -16979,7 +16979,7 @@
         <v>4</v>
       </c>
       <c r="T10" s="197">
-        <v>169.7</v>
+        <v>162.32</v>
       </c>
       <c r="U10" s="197">
         <v>133.33000000000001</v>
@@ -17027,7 +17027,7 @@
         <v>1</v>
       </c>
       <c r="AJ10" s="197">
-        <v>157.58000000000001</v>
+        <v>159.41999999999999</v>
       </c>
       <c r="AK10" s="197">
         <v>166.67</v>
@@ -17063,7 +17063,7 @@
         <v>100</v>
       </c>
       <c r="AV10" s="197">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW10" s="197">
         <v>30</v>
@@ -17075,7 +17075,7 @@
         <v>9</v>
       </c>
       <c r="AZ10" s="197">
-        <v>38.18</v>
+        <v>36.520000000000003</v>
       </c>
       <c r="BA10" s="197">
         <v>30</v>
@@ -17099,7 +17099,7 @@
         <v>2</v>
       </c>
       <c r="BH10" s="197">
-        <v>63.64</v>
+        <v>60.87</v>
       </c>
       <c r="BI10" s="197">
         <v>50</v>
@@ -17159,7 +17159,7 @@
         <v>100</v>
       </c>
       <c r="CB10" s="197">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CC10" s="197">
         <v>8</v>
@@ -17195,7 +17195,7 @@
         <v>3</v>
       </c>
       <c r="CN10" s="197">
-        <v>95.45</v>
+        <v>91.3</v>
       </c>
       <c r="CO10" s="197">
         <v>75</v>
@@ -17290,7 +17290,7 @@
         <v>8</v>
       </c>
       <c r="L11" s="197">
-        <v>145.44999999999999</v>
+        <v>139.13</v>
       </c>
       <c r="M11" s="197">
         <v>114.29</v>
@@ -17314,7 +17314,7 @@
         <v>4</v>
       </c>
       <c r="T11" s="197">
-        <v>127.27</v>
+        <v>121.74</v>
       </c>
       <c r="U11" s="197">
         <v>100</v>
@@ -17362,7 +17362,7 @@
         <v>2</v>
       </c>
       <c r="AJ11" s="197">
-        <v>136.36000000000001</v>
+        <v>139.13</v>
       </c>
       <c r="AK11" s="197">
         <v>150</v>
@@ -17398,7 +17398,7 @@
         <v>100</v>
       </c>
       <c r="AV11" s="197">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="AW11" s="197">
         <v>40</v>
@@ -17407,19 +17407,19 @@
         <v>0</v>
       </c>
       <c r="AY11" s="197">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AZ11" s="197">
-        <v>267.27</v>
+        <v>258.7</v>
       </c>
       <c r="BA11" s="197">
-        <v>210</v>
+        <v>212.5</v>
       </c>
       <c r="BB11" s="197">
         <v>1</v>
       </c>
       <c r="BC11" s="197">
-        <v>8300</v>
+        <v>8400</v>
       </c>
       <c r="BD11" s="197">
         <v>4</v>
@@ -17434,7 +17434,7 @@
         <v>4</v>
       </c>
       <c r="BH11" s="197">
-        <v>101.82</v>
+        <v>97.39</v>
       </c>
       <c r="BI11" s="197">
         <v>80</v>
@@ -17482,7 +17482,7 @@
         <v>1</v>
       </c>
       <c r="BX11" s="197">
-        <v>127.27</v>
+        <v>121.74</v>
       </c>
       <c r="BY11" s="197">
         <v>100</v>
@@ -17494,7 +17494,7 @@
         <v>100</v>
       </c>
       <c r="CB11" s="197">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CC11" s="197">
         <v>8</v>
@@ -17506,7 +17506,7 @@
         <v>7</v>
       </c>
       <c r="CF11" s="197">
-        <v>111.36</v>
+        <v>106.52</v>
       </c>
       <c r="CG11" s="197">
         <v>87.5</v>
@@ -17530,7 +17530,7 @@
         <v>3</v>
       </c>
       <c r="CN11" s="197">
-        <v>95.45</v>
+        <v>91.3</v>
       </c>
       <c r="CO11" s="197">
         <v>75</v>
@@ -17554,7 +17554,7 @@
         <v>3</v>
       </c>
       <c r="CV11" s="197">
-        <v>95.45</v>
+        <v>91.3</v>
       </c>
       <c r="CW11" s="197">
         <v>75</v>
@@ -17575,19 +17575,19 @@
         <v>0</v>
       </c>
       <c r="DC11" s="197">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DD11" s="197">
-        <v>1018.18</v>
+        <v>1095.6500000000001</v>
       </c>
       <c r="DE11" s="197">
+        <v>900</v>
+      </c>
+      <c r="DF11" s="197">
+        <v>1</v>
+      </c>
+      <c r="DG11" s="197">
         <v>800</v>
-      </c>
-      <c r="DF11" s="197">
-        <v>1</v>
-      </c>
-      <c r="DG11" s="197">
-        <v>700</v>
       </c>
     </row>
     <row r="12" spans="1:111" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -17625,7 +17625,7 @@
         <v>5</v>
       </c>
       <c r="L12" s="197">
-        <v>90.91</v>
+        <v>86.96</v>
       </c>
       <c r="M12" s="197">
         <v>71.430000000000007</v>
@@ -17649,7 +17649,7 @@
         <v>2</v>
       </c>
       <c r="T12" s="197">
-        <v>84.85</v>
+        <v>81.16</v>
       </c>
       <c r="U12" s="197">
         <v>66.67</v>
@@ -17733,7 +17733,7 @@
         <v>100</v>
       </c>
       <c r="AV12" s="197">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW12" s="197">
         <v>30</v>
@@ -17745,7 +17745,7 @@
         <v>26</v>
       </c>
       <c r="AZ12" s="197">
-        <v>110.3</v>
+        <v>105.51</v>
       </c>
       <c r="BA12" s="197">
         <v>86.67</v>
@@ -17769,7 +17769,7 @@
         <v>1</v>
       </c>
       <c r="BH12" s="197">
-        <v>31.82</v>
+        <v>30.43</v>
       </c>
       <c r="BI12" s="197">
         <v>25</v>
@@ -17829,7 +17829,7 @@
         <v>100</v>
       </c>
       <c r="CB12" s="197">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CC12" s="197">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>3</v>
       </c>
       <c r="CF12" s="197">
-        <v>47.73</v>
+        <v>45.65</v>
       </c>
       <c r="CG12" s="197">
         <v>37.5</v>
@@ -17865,7 +17865,7 @@
         <v>2</v>
       </c>
       <c r="CN12" s="197">
-        <v>63.64</v>
+        <v>60.87</v>
       </c>
       <c r="CO12" s="197">
         <v>50</v>
@@ -17889,7 +17889,7 @@
         <v>3</v>
       </c>
       <c r="CV12" s="197">
-        <v>127.27</v>
+        <v>121.74</v>
       </c>
       <c r="CW12" s="197">
         <v>100</v>
@@ -17913,7 +17913,7 @@
         <v>3</v>
       </c>
       <c r="DD12" s="197">
-        <v>381.82</v>
+        <v>365.22</v>
       </c>
       <c r="DE12" s="197">
         <v>300</v>
@@ -17948,7 +17948,7 @@
         <v>128</v>
       </c>
       <c r="H13" s="197">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I13" s="197">
         <v>8</v>
@@ -17960,7 +17960,7 @@
         <v>8</v>
       </c>
       <c r="L13" s="197">
-        <v>127.27</v>
+        <v>121.74</v>
       </c>
       <c r="M13" s="197">
         <v>100</v>
@@ -17984,7 +17984,7 @@
         <v>3</v>
       </c>
       <c r="T13" s="197">
-        <v>95.45</v>
+        <v>91.3</v>
       </c>
       <c r="U13" s="197">
         <v>75</v>
@@ -18032,7 +18032,7 @@
         <v>2</v>
       </c>
       <c r="AJ13" s="197">
-        <v>149.09</v>
+        <v>151.30000000000001</v>
       </c>
       <c r="AK13" s="197">
         <v>160</v>
@@ -18068,7 +18068,7 @@
         <v>100</v>
       </c>
       <c r="AV13" s="197">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AW13" s="197">
         <v>50</v>
@@ -18080,7 +18080,7 @@
         <v>69</v>
       </c>
       <c r="AZ13" s="197">
-        <v>175.64</v>
+        <v>168</v>
       </c>
       <c r="BA13" s="197">
         <v>138</v>
@@ -18104,7 +18104,7 @@
         <v>4</v>
       </c>
       <c r="BH13" s="197">
-        <v>101.82</v>
+        <v>97.39</v>
       </c>
       <c r="BI13" s="197">
         <v>80</v>
@@ -18176,7 +18176,7 @@
         <v>11</v>
       </c>
       <c r="CF13" s="197">
-        <v>155.56</v>
+        <v>148.79</v>
       </c>
       <c r="CG13" s="197">
         <v>122.22</v>
@@ -18200,7 +18200,7 @@
         <v>1</v>
       </c>
       <c r="CN13" s="197">
-        <v>25.45</v>
+        <v>24.35</v>
       </c>
       <c r="CO13" s="197">
         <v>20</v>
@@ -18224,7 +18224,7 @@
         <v>3</v>
       </c>
       <c r="CV13" s="197">
-        <v>95.45</v>
+        <v>91.3</v>
       </c>
       <c r="CW13" s="197">
         <v>75</v>
@@ -18295,7 +18295,7 @@
         <v>8</v>
       </c>
       <c r="L14" s="197">
-        <v>145.44999999999999</v>
+        <v>139.13</v>
       </c>
       <c r="M14" s="197">
         <v>114.29</v>
@@ -18319,7 +18319,7 @@
         <v>5</v>
       </c>
       <c r="T14" s="197">
-        <v>159.09</v>
+        <v>152.16999999999999</v>
       </c>
       <c r="U14" s="197">
         <v>125</v>
@@ -18343,7 +18343,7 @@
         <v>1</v>
       </c>
       <c r="AB14" s="197">
-        <v>63.64</v>
+        <v>60.87</v>
       </c>
       <c r="AC14" s="197">
         <v>50</v>
@@ -18364,13 +18364,13 @@
         <v>0</v>
       </c>
       <c r="AI14" s="197">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ14" s="197">
-        <v>168.18</v>
+        <v>139.13</v>
       </c>
       <c r="AK14" s="197">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="AL14" s="197">
         <v>0</v>
@@ -18403,7 +18403,7 @@
         <v>100</v>
       </c>
       <c r="AV14" s="197">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AW14" s="197">
         <v>60</v>
@@ -18415,7 +18415,7 @@
         <v>199</v>
       </c>
       <c r="AZ14" s="197">
-        <v>422.12</v>
+        <v>403.77</v>
       </c>
       <c r="BA14" s="197">
         <v>331.67</v>
@@ -18439,7 +18439,7 @@
         <v>3</v>
       </c>
       <c r="BH14" s="197">
-        <v>76.36</v>
+        <v>73.040000000000006</v>
       </c>
       <c r="BI14" s="197">
         <v>60</v>
@@ -18463,7 +18463,7 @@
         <v>6</v>
       </c>
       <c r="BP14" s="197">
-        <v>763.64</v>
+        <v>730.43</v>
       </c>
       <c r="BQ14" s="197">
         <v>600</v>
@@ -18487,7 +18487,7 @@
         <v>1</v>
       </c>
       <c r="BX14" s="197">
-        <v>127.27</v>
+        <v>121.74</v>
       </c>
       <c r="BY14" s="197">
         <v>100</v>
@@ -18499,7 +18499,7 @@
         <v>100</v>
       </c>
       <c r="CB14" s="197">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CC14" s="197">
         <v>8</v>
@@ -18511,7 +18511,7 @@
         <v>17</v>
       </c>
       <c r="CF14" s="197">
-        <v>270.45</v>
+        <v>258.7</v>
       </c>
       <c r="CG14" s="197">
         <v>212.5</v>
@@ -18535,7 +18535,7 @@
         <v>7</v>
       </c>
       <c r="CN14" s="197">
-        <v>222.73</v>
+        <v>213.04</v>
       </c>
       <c r="CO14" s="197">
         <v>175</v>
@@ -18559,7 +18559,7 @@
         <v>9</v>
       </c>
       <c r="CV14" s="197">
-        <v>286.36</v>
+        <v>273.91000000000003</v>
       </c>
       <c r="CW14" s="197">
         <v>225</v>
@@ -18583,16 +18583,16 @@
         <v>15</v>
       </c>
       <c r="DD14" s="197">
-        <v>1909.09</v>
+        <v>1826.09</v>
       </c>
       <c r="DE14" s="197">
         <v>1500</v>
       </c>
       <c r="DF14" s="197">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DG14" s="197">
-        <v>1400</v>
+        <v>650</v>
       </c>
     </row>
     <row r="15" spans="1:111" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -18618,22 +18618,22 @@
         <v>128</v>
       </c>
       <c r="H15" s="197">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I15" s="197">
         <v>8</v>
       </c>
       <c r="J15" s="197">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" s="197">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L15" s="197">
-        <v>143.18</v>
+        <v>152.16999999999999</v>
       </c>
       <c r="M15" s="197">
-        <v>112.5</v>
+        <v>125</v>
       </c>
       <c r="N15" s="197">
         <v>0</v>
@@ -18648,16 +18648,16 @@
         <v>4</v>
       </c>
       <c r="R15" s="197">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" s="197">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T15" s="197">
-        <v>63.64</v>
+        <v>91.3</v>
       </c>
       <c r="U15" s="197">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="V15" s="197">
         <v>0</v>
@@ -18738,7 +18738,7 @@
         <v>100</v>
       </c>
       <c r="AV15" s="197">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW15" s="197">
         <v>30</v>
@@ -18750,7 +18750,7 @@
         <v>60</v>
       </c>
       <c r="AZ15" s="197">
-        <v>254.55</v>
+        <v>243.48</v>
       </c>
       <c r="BA15" s="197">
         <v>200</v>
@@ -18774,7 +18774,7 @@
         <v>3</v>
       </c>
       <c r="BH15" s="197">
-        <v>76.36</v>
+        <v>73.040000000000006</v>
       </c>
       <c r="BI15" s="197">
         <v>60</v>
@@ -18822,7 +18822,7 @@
         <v>1</v>
       </c>
       <c r="BX15" s="197">
-        <v>127.27</v>
+        <v>121.74</v>
       </c>
       <c r="BY15" s="197">
         <v>100</v>
@@ -18846,7 +18846,7 @@
         <v>11</v>
       </c>
       <c r="CF15" s="197">
-        <v>155.56</v>
+        <v>148.79</v>
       </c>
       <c r="CG15" s="197">
         <v>122.22</v>
@@ -18870,7 +18870,7 @@
         <v>6</v>
       </c>
       <c r="CN15" s="197">
-        <v>152.72999999999999</v>
+        <v>146.09</v>
       </c>
       <c r="CO15" s="197">
         <v>120</v>
@@ -18894,7 +18894,7 @@
         <v>2</v>
       </c>
       <c r="CV15" s="197">
-        <v>84.85</v>
+        <v>81.16</v>
       </c>
       <c r="CW15" s="197">
         <v>66.67</v>
@@ -18918,7 +18918,7 @@
         <v>1</v>
       </c>
       <c r="DD15" s="197">
-        <v>127.27</v>
+        <v>121.74</v>
       </c>
       <c r="DE15" s="197">
         <v>100</v>
@@ -18959,16 +18959,16 @@
         <v>7</v>
       </c>
       <c r="J16" s="197">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" s="197">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L16" s="197">
-        <v>90.91</v>
+        <v>104.35</v>
       </c>
       <c r="M16" s="197">
-        <v>71.430000000000007</v>
+        <v>85.71</v>
       </c>
       <c r="N16" s="197">
         <v>0</v>
@@ -18989,7 +18989,7 @@
         <v>2</v>
       </c>
       <c r="T16" s="197">
-        <v>63.64</v>
+        <v>60.87</v>
       </c>
       <c r="U16" s="197">
         <v>50</v>
@@ -19037,7 +19037,7 @@
         <v>5</v>
       </c>
       <c r="AJ16" s="197">
-        <v>40.909999999999997</v>
+        <v>47.83</v>
       </c>
       <c r="AK16" s="197">
         <v>75</v>
@@ -19073,7 +19073,7 @@
         <v>100</v>
       </c>
       <c r="AV16" s="197">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AW16" s="197">
         <v>35</v>
@@ -19082,13 +19082,13 @@
         <v>0</v>
       </c>
       <c r="AY16" s="197">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AZ16" s="197">
-        <v>334.55</v>
+        <v>323.48</v>
       </c>
       <c r="BA16" s="197">
-        <v>262.86</v>
+        <v>265.70999999999998</v>
       </c>
       <c r="BB16" s="197">
         <v>0</v>
@@ -19109,7 +19109,7 @@
         <v>2</v>
       </c>
       <c r="BH16" s="197">
-        <v>50.91</v>
+        <v>48.7</v>
       </c>
       <c r="BI16" s="197">
         <v>40</v>
@@ -19133,7 +19133,7 @@
         <v>2</v>
       </c>
       <c r="BP16" s="197">
-        <v>254.55</v>
+        <v>243.48</v>
       </c>
       <c r="BQ16" s="197">
         <v>200</v>
@@ -19157,7 +19157,7 @@
         <v>1</v>
       </c>
       <c r="BX16" s="197">
-        <v>127.27</v>
+        <v>121.74</v>
       </c>
       <c r="BY16" s="197">
         <v>100</v>
@@ -19169,7 +19169,7 @@
         <v>100</v>
       </c>
       <c r="CB16" s="197">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CC16" s="197">
         <v>8</v>
@@ -19181,7 +19181,7 @@
         <v>6</v>
       </c>
       <c r="CF16" s="197">
-        <v>95.45</v>
+        <v>91.3</v>
       </c>
       <c r="CG16" s="197">
         <v>75</v>
@@ -19205,7 +19205,7 @@
         <v>4</v>
       </c>
       <c r="CN16" s="197">
-        <v>127.27</v>
+        <v>121.74</v>
       </c>
       <c r="CO16" s="197">
         <v>100</v>
@@ -19223,16 +19223,16 @@
         <v>4</v>
       </c>
       <c r="CT16" s="197">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CU16" s="197">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CV16" s="197">
-        <v>222.73</v>
+        <v>243.48</v>
       </c>
       <c r="CW16" s="197">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="CX16" s="197">
         <v>0</v>
@@ -19250,19 +19250,19 @@
         <v>0</v>
       </c>
       <c r="DC16" s="197">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DD16" s="197">
-        <v>1145.45</v>
+        <v>1217.3900000000001</v>
       </c>
       <c r="DE16" s="197">
+        <v>1000</v>
+      </c>
+      <c r="DF16" s="197">
+        <v>1</v>
+      </c>
+      <c r="DG16" s="197">
         <v>900</v>
-      </c>
-      <c r="DF16" s="197">
-        <v>1</v>
-      </c>
-      <c r="DG16" s="197">
-        <v>800</v>
       </c>
     </row>
     <row r="17" spans="1:111" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -19300,7 +19300,7 @@
         <v>5</v>
       </c>
       <c r="L17" s="197">
-        <v>90.91</v>
+        <v>86.96</v>
       </c>
       <c r="M17" s="197">
         <v>71.430000000000007</v>
@@ -19324,7 +19324,7 @@
         <v>6</v>
       </c>
       <c r="T17" s="197">
-        <v>190.91</v>
+        <v>182.61</v>
       </c>
       <c r="U17" s="197">
         <v>150</v>
@@ -19348,7 +19348,7 @@
         <v>1</v>
       </c>
       <c r="AB17" s="197">
-        <v>42.42</v>
+        <v>40.58</v>
       </c>
       <c r="AC17" s="197">
         <v>33.33</v>
@@ -19369,19 +19369,19 @@
         <v>0</v>
       </c>
       <c r="AI17" s="197">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ17" s="197">
-        <v>168.18</v>
+        <v>139.13</v>
       </c>
       <c r="AK17" s="197">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="AL17" s="197">
         <v>1</v>
       </c>
       <c r="AM17" s="197">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN17" s="197">
         <v>3</v>
@@ -19408,7 +19408,7 @@
         <v>100</v>
       </c>
       <c r="AV17" s="197">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AW17" s="197">
         <v>35</v>
@@ -19420,7 +19420,7 @@
         <v>57</v>
       </c>
       <c r="AZ17" s="197">
-        <v>207.27</v>
+        <v>198.26</v>
       </c>
       <c r="BA17" s="197">
         <v>162.86000000000001</v>
@@ -19444,7 +19444,7 @@
         <v>6</v>
       </c>
       <c r="BH17" s="197">
-        <v>152.72999999999999</v>
+        <v>146.09</v>
       </c>
       <c r="BI17" s="197">
         <v>120</v>
@@ -19504,7 +19504,7 @@
         <v>100</v>
       </c>
       <c r="CB17" s="197">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CC17" s="197">
         <v>8</v>
@@ -19516,7 +19516,7 @@
         <v>11</v>
       </c>
       <c r="CF17" s="197">
-        <v>175</v>
+        <v>167.39</v>
       </c>
       <c r="CG17" s="197">
         <v>137.5</v>
@@ -19540,7 +19540,7 @@
         <v>6</v>
       </c>
       <c r="CN17" s="197">
-        <v>190.91</v>
+        <v>182.61</v>
       </c>
       <c r="CO17" s="197">
         <v>150</v>
@@ -19564,7 +19564,7 @@
         <v>5</v>
       </c>
       <c r="CV17" s="197">
-        <v>159.09</v>
+        <v>152.16999999999999</v>
       </c>
       <c r="CW17" s="197">
         <v>125</v>
@@ -19588,7 +19588,7 @@
         <v>10</v>
       </c>
       <c r="DD17" s="197">
-        <v>1272.73</v>
+        <v>1217.3900000000001</v>
       </c>
       <c r="DE17" s="197">
         <v>1000</v>
@@ -19635,7 +19635,7 @@
         <v>6</v>
       </c>
       <c r="L18" s="197">
-        <v>109.09</v>
+        <v>104.35</v>
       </c>
       <c r="M18" s="197">
         <v>85.71</v>
@@ -19659,7 +19659,7 @@
         <v>9</v>
       </c>
       <c r="T18" s="197">
-        <v>286.36</v>
+        <v>273.91000000000003</v>
       </c>
       <c r="U18" s="197">
         <v>225</v>
@@ -19683,7 +19683,7 @@
         <v>1</v>
       </c>
       <c r="AB18" s="197">
-        <v>42.42</v>
+        <v>40.58</v>
       </c>
       <c r="AC18" s="197">
         <v>33.33</v>
@@ -19707,7 +19707,7 @@
         <v>3</v>
       </c>
       <c r="AJ18" s="197">
-        <v>123.64</v>
+        <v>126.96</v>
       </c>
       <c r="AK18" s="197">
         <v>140</v>
@@ -19743,7 +19743,7 @@
         <v>100</v>
       </c>
       <c r="AV18" s="197">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW18" s="197">
         <v>30</v>
@@ -19752,13 +19752,13 @@
         <v>0</v>
       </c>
       <c r="AY18" s="197">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AZ18" s="197">
-        <v>280</v>
+        <v>271.88</v>
       </c>
       <c r="BA18" s="197">
-        <v>220</v>
+        <v>223.33</v>
       </c>
       <c r="BB18" s="197">
         <v>0</v>
@@ -19779,7 +19779,7 @@
         <v>3</v>
       </c>
       <c r="BH18" s="197">
-        <v>76.36</v>
+        <v>73.040000000000006</v>
       </c>
       <c r="BI18" s="197">
         <v>60</v>
@@ -19839,7 +19839,7 @@
         <v>100</v>
       </c>
       <c r="CB18" s="197">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CC18" s="197">
         <v>8</v>
@@ -19851,7 +19851,7 @@
         <v>8</v>
       </c>
       <c r="CF18" s="197">
-        <v>127.27</v>
+        <v>121.74</v>
       </c>
       <c r="CG18" s="197">
         <v>100</v>
@@ -19875,7 +19875,7 @@
         <v>6</v>
       </c>
       <c r="CN18" s="197">
-        <v>190.91</v>
+        <v>182.61</v>
       </c>
       <c r="CO18" s="197">
         <v>150</v>
@@ -19899,7 +19899,7 @@
         <v>5</v>
       </c>
       <c r="CV18" s="197">
-        <v>159.09</v>
+        <v>152.16999999999999</v>
       </c>
       <c r="CW18" s="197">
         <v>125</v>
@@ -19923,7 +19923,7 @@
         <v>9</v>
       </c>
       <c r="DD18" s="197">
-        <v>1145.45</v>
+        <v>1095.6500000000001</v>
       </c>
       <c r="DE18" s="197">
         <v>900</v>
@@ -19958,7 +19958,7 @@
         <v>128</v>
       </c>
       <c r="H19" s="197">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I19" s="197">
         <v>8</v>
@@ -19970,7 +19970,7 @@
         <v>8</v>
       </c>
       <c r="L19" s="197">
-        <v>127.27</v>
+        <v>121.74</v>
       </c>
       <c r="M19" s="197">
         <v>100</v>
@@ -19994,7 +19994,7 @@
         <v>2</v>
       </c>
       <c r="T19" s="197">
-        <v>63.64</v>
+        <v>60.87</v>
       </c>
       <c r="U19" s="197">
         <v>50</v>
@@ -20042,7 +20042,7 @@
         <v>2</v>
       </c>
       <c r="AJ19" s="197">
-        <v>149.09</v>
+        <v>151.30000000000001</v>
       </c>
       <c r="AK19" s="197">
         <v>160</v>
@@ -20078,7 +20078,7 @@
         <v>100</v>
       </c>
       <c r="AV19" s="197">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW19" s="197">
         <v>30</v>
@@ -20090,7 +20090,7 @@
         <v>13</v>
       </c>
       <c r="AZ19" s="197">
-        <v>55.15</v>
+        <v>52.75</v>
       </c>
       <c r="BA19" s="197">
         <v>43.33</v>
@@ -20114,7 +20114,7 @@
         <v>1</v>
       </c>
       <c r="BH19" s="197">
-        <v>25.45</v>
+        <v>24.35</v>
       </c>
       <c r="BI19" s="197">
         <v>20</v>
@@ -20210,7 +20210,7 @@
         <v>3</v>
       </c>
       <c r="CN19" s="197">
-        <v>76.36</v>
+        <v>73.040000000000006</v>
       </c>
       <c r="CO19" s="197">
         <v>60</v>
@@ -20234,7 +20234,7 @@
         <v>1</v>
       </c>
       <c r="CV19" s="197">
-        <v>42.42</v>
+        <v>40.58</v>
       </c>
       <c r="CW19" s="197">
         <v>33.33</v>
@@ -20258,7 +20258,7 @@
         <v>1</v>
       </c>
       <c r="DD19" s="197">
-        <v>127.27</v>
+        <v>121.74</v>
       </c>
       <c r="DE19" s="197">
         <v>100</v>
@@ -20299,16 +20299,16 @@
         <v>7</v>
       </c>
       <c r="J20" s="197">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" s="197">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L20" s="197">
-        <v>109.09</v>
+        <v>121.74</v>
       </c>
       <c r="M20" s="197">
-        <v>85.71</v>
+        <v>100</v>
       </c>
       <c r="N20" s="197">
         <v>0</v>
@@ -20329,7 +20329,7 @@
         <v>5</v>
       </c>
       <c r="T20" s="197">
-        <v>159.09</v>
+        <v>152.16999999999999</v>
       </c>
       <c r="U20" s="197">
         <v>125</v>
@@ -20413,7 +20413,7 @@
         <v>100</v>
       </c>
       <c r="AV20" s="197">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW20" s="197">
         <v>30</v>
@@ -20425,7 +20425,7 @@
         <v>51</v>
       </c>
       <c r="AZ20" s="197">
-        <v>216.36</v>
+        <v>206.96</v>
       </c>
       <c r="BA20" s="197">
         <v>170</v>
@@ -20449,7 +20449,7 @@
         <v>2</v>
       </c>
       <c r="BH20" s="197">
-        <v>50.91</v>
+        <v>48.7</v>
       </c>
       <c r="BI20" s="197">
         <v>40</v>
@@ -20509,7 +20509,7 @@
         <v>100</v>
       </c>
       <c r="CB20" s="197">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CC20" s="197">
         <v>8</v>
@@ -20521,7 +20521,7 @@
         <v>5</v>
       </c>
       <c r="CF20" s="197">
-        <v>79.55</v>
+        <v>76.09</v>
       </c>
       <c r="CG20" s="197">
         <v>62.5</v>
@@ -20545,7 +20545,7 @@
         <v>2</v>
       </c>
       <c r="CN20" s="197">
-        <v>63.64</v>
+        <v>60.87</v>
       </c>
       <c r="CO20" s="197">
         <v>50</v>
@@ -20569,7 +20569,7 @@
         <v>4</v>
       </c>
       <c r="CV20" s="197">
-        <v>127.27</v>
+        <v>121.74</v>
       </c>
       <c r="CW20" s="197">
         <v>100</v>
@@ -20593,7 +20593,7 @@
         <v>1</v>
       </c>
       <c r="DD20" s="197">
-        <v>127.27</v>
+        <v>121.74</v>
       </c>
       <c r="DE20" s="197">
         <v>100</v>
@@ -20640,7 +20640,7 @@
         <v>3</v>
       </c>
       <c r="L21" s="197">
-        <v>76.36</v>
+        <v>73.040000000000006</v>
       </c>
       <c r="M21" s="197">
         <v>60</v>
@@ -20664,7 +20664,7 @@
         <v>3</v>
       </c>
       <c r="T21" s="197">
-        <v>127.27</v>
+        <v>121.74</v>
       </c>
       <c r="U21" s="197">
         <v>100</v>
@@ -20712,7 +20712,7 @@
         <v>1</v>
       </c>
       <c r="AJ21" s="197">
-        <v>157.58000000000001</v>
+        <v>159.41999999999999</v>
       </c>
       <c r="AK21" s="197">
         <v>166.67</v>
@@ -20760,7 +20760,7 @@
         <v>15</v>
       </c>
       <c r="AZ21" s="197">
-        <v>95.45</v>
+        <v>91.3</v>
       </c>
       <c r="BA21" s="197">
         <v>75</v>
@@ -20784,7 +20784,7 @@
         <v>1</v>
       </c>
       <c r="BH21" s="197">
-        <v>25.45</v>
+        <v>24.35</v>
       </c>
       <c r="BI21" s="197">
         <v>20</v>
@@ -20844,7 +20844,7 @@
         <v>100</v>
       </c>
       <c r="CB21" s="197">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CC21" s="197">
         <v>8</v>
@@ -20856,7 +20856,7 @@
         <v>1</v>
       </c>
       <c r="CF21" s="197">
-        <v>15.91</v>
+        <v>15.22</v>
       </c>
       <c r="CG21" s="197">
         <v>12.5</v>
@@ -20880,7 +20880,7 @@
         <v>3</v>
       </c>
       <c r="CN21" s="197">
-        <v>95.45</v>
+        <v>91.3</v>
       </c>
       <c r="CO21" s="197">
         <v>75</v>
@@ -20904,7 +20904,7 @@
         <v>2</v>
       </c>
       <c r="CV21" s="197">
-        <v>84.85</v>
+        <v>81.16</v>
       </c>
       <c r="CW21" s="197">
         <v>66.67</v>
@@ -20928,7 +20928,7 @@
         <v>2</v>
       </c>
       <c r="DD21" s="197">
-        <v>254.55</v>
+        <v>243.48</v>
       </c>
       <c r="DE21" s="197">
         <v>200</v>
@@ -20963,7 +20963,7 @@
         <v>128</v>
       </c>
       <c r="H22" s="197">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I22" s="197">
         <v>8</v>
@@ -20975,7 +20975,7 @@
         <v>8</v>
       </c>
       <c r="L22" s="197">
-        <v>127.27</v>
+        <v>121.74</v>
       </c>
       <c r="M22" s="197">
         <v>100</v>
@@ -20999,7 +20999,7 @@
         <v>6</v>
       </c>
       <c r="T22" s="197">
-        <v>190.91</v>
+        <v>182.61</v>
       </c>
       <c r="U22" s="197">
         <v>150</v>
@@ -21083,7 +21083,7 @@
         <v>100</v>
       </c>
       <c r="AV22" s="197">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW22" s="197">
         <v>30</v>
@@ -21095,7 +21095,7 @@
         <v>61</v>
       </c>
       <c r="AZ22" s="197">
-        <v>258.79000000000002</v>
+        <v>247.54</v>
       </c>
       <c r="BA22" s="197">
         <v>203.33</v>
@@ -21119,7 +21119,7 @@
         <v>3</v>
       </c>
       <c r="BH22" s="197">
-        <v>76.36</v>
+        <v>73.040000000000006</v>
       </c>
       <c r="BI22" s="197">
         <v>60</v>
@@ -21167,7 +21167,7 @@
         <v>2</v>
       </c>
       <c r="BX22" s="197">
-        <v>254.55</v>
+        <v>243.48</v>
       </c>
       <c r="BY22" s="197">
         <v>200</v>
@@ -21191,7 +21191,7 @@
         <v>11</v>
       </c>
       <c r="CF22" s="197">
-        <v>155.56</v>
+        <v>148.79</v>
       </c>
       <c r="CG22" s="197">
         <v>122.22</v>
@@ -21215,7 +21215,7 @@
         <v>3</v>
       </c>
       <c r="CN22" s="197">
-        <v>76.36</v>
+        <v>73.040000000000006</v>
       </c>
       <c r="CO22" s="197">
         <v>60</v>
@@ -21239,7 +21239,7 @@
         <v>4</v>
       </c>
       <c r="CV22" s="197">
-        <v>127.27</v>
+        <v>121.74</v>
       </c>
       <c r="CW22" s="197">
         <v>100</v>
@@ -21263,7 +21263,7 @@
         <v>2</v>
       </c>
       <c r="DD22" s="197">
-        <v>254.55</v>
+        <v>243.48</v>
       </c>
       <c r="DE22" s="197">
         <v>200</v>
@@ -21310,7 +21310,7 @@
         <v>11</v>
       </c>
       <c r="L23" s="197">
-        <v>200</v>
+        <v>191.3</v>
       </c>
       <c r="M23" s="197">
         <v>157.13999999999999</v>
@@ -21334,7 +21334,7 @@
         <v>5</v>
       </c>
       <c r="T23" s="197">
-        <v>159.09</v>
+        <v>152.16999999999999</v>
       </c>
       <c r="U23" s="197">
         <v>125</v>
@@ -21418,7 +21418,7 @@
         <v>100</v>
       </c>
       <c r="AV23" s="197">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AW23" s="197">
         <v>60</v>
@@ -21430,7 +21430,7 @@
         <v>171</v>
       </c>
       <c r="AZ23" s="197">
-        <v>362.73</v>
+        <v>346.96</v>
       </c>
       <c r="BA23" s="197">
         <v>285</v>
@@ -21454,7 +21454,7 @@
         <v>4</v>
       </c>
       <c r="BH23" s="197">
-        <v>101.82</v>
+        <v>97.39</v>
       </c>
       <c r="BI23" s="197">
         <v>80</v>
@@ -21502,7 +21502,7 @@
         <v>1</v>
       </c>
       <c r="BX23" s="197">
-        <v>127.27</v>
+        <v>121.74</v>
       </c>
       <c r="BY23" s="197">
         <v>100</v>
@@ -21514,7 +21514,7 @@
         <v>100</v>
       </c>
       <c r="CB23" s="197">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CC23" s="197">
         <v>8</v>
@@ -21526,7 +21526,7 @@
         <v>21</v>
       </c>
       <c r="CF23" s="197">
-        <v>334.09</v>
+        <v>319.57</v>
       </c>
       <c r="CG23" s="197">
         <v>262.5</v>
@@ -21550,7 +21550,7 @@
         <v>5</v>
       </c>
       <c r="CN23" s="197">
-        <v>159.09</v>
+        <v>152.16999999999999</v>
       </c>
       <c r="CO23" s="197">
         <v>125</v>
@@ -21568,13 +21568,13 @@
         <v>4</v>
       </c>
       <c r="CT23" s="197">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CU23" s="197">
         <v>8</v>
       </c>
       <c r="CV23" s="197">
-        <v>254.55</v>
+        <v>243.48</v>
       </c>
       <c r="CW23" s="197">
         <v>200</v>
@@ -21598,7 +21598,7 @@
         <v>21</v>
       </c>
       <c r="DD23" s="197">
-        <v>2672.73</v>
+        <v>2556.52</v>
       </c>
       <c r="DE23" s="197">
         <v>2100</v>
@@ -21645,7 +21645,7 @@
         <v>4</v>
       </c>
       <c r="L24" s="197">
-        <v>169.7</v>
+        <v>162.32</v>
       </c>
       <c r="M24" s="197">
         <v>133.33000000000001</v>
@@ -21723,7 +21723,7 @@
         <v>200</v>
       </c>
       <c r="AL24" s="197">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM24" s="197">
         <v>-100</v>
@@ -21753,7 +21753,7 @@
         <v>100</v>
       </c>
       <c r="AV24" s="197">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW24" s="197">
         <v>14</v>
@@ -21765,7 +21765,7 @@
         <v>3</v>
       </c>
       <c r="AZ24" s="197">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BA24" s="197">
         <v>21.43</v>
@@ -21789,7 +21789,7 @@
         <v>2</v>
       </c>
       <c r="BH24" s="197">
-        <v>127.27</v>
+        <v>121.74</v>
       </c>
       <c r="BI24" s="197">
         <v>100</v>
@@ -21909,7 +21909,7 @@
         <v>2</v>
       </c>
       <c r="CV24" s="197">
-        <v>84.85</v>
+        <v>81.16</v>
       </c>
       <c r="CW24" s="197">
         <v>66.67</v>
@@ -21965,7 +21965,7 @@
         <v>277</v>
       </c>
       <c r="G25" s="196" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H25" s="198"/>
       <c r="I25" s="198"/>
@@ -22008,7 +22008,7 @@
       <c r="AT25" s="198"/>
       <c r="AU25" s="198"/>
       <c r="AV25" s="197">
-        <v>1069</v>
+        <v>1117</v>
       </c>
       <c r="AW25" s="197">
         <v>1360</v>
@@ -22072,7 +22072,7 @@
         <v>100</v>
       </c>
       <c r="CB25" s="197">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="CC25" s="197">
         <v>120</v>
@@ -22112,7 +22112,7 @@
       <c r="CX25" s="198"/>
       <c r="CY25" s="198"/>
       <c r="CZ25" s="197">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="DA25" s="197">
         <v>257</v>
@@ -22314,7 +22314,7 @@
         <v>3</v>
       </c>
       <c r="L27" s="197">
-        <v>95.45</v>
+        <v>91.3</v>
       </c>
       <c r="M27" s="197">
         <v>75</v>
@@ -22338,7 +22338,7 @@
         <v>4</v>
       </c>
       <c r="T27" s="197">
-        <v>254.55</v>
+        <v>243.48</v>
       </c>
       <c r="U27" s="197">
         <v>200</v>
@@ -22386,7 +22386,7 @@
         <v>1</v>
       </c>
       <c r="AJ27" s="197">
-        <v>136.36000000000001</v>
+        <v>139.13</v>
       </c>
       <c r="AK27" s="197">
         <v>150</v>
@@ -22434,7 +22434,7 @@
         <v>30</v>
       </c>
       <c r="AZ27" s="197">
-        <v>181.82</v>
+        <v>173.91</v>
       </c>
       <c r="BA27" s="197">
         <v>142.86000000000001</v>
@@ -22458,7 +22458,7 @@
         <v>1</v>
       </c>
       <c r="BH27" s="197">
-        <v>42.42</v>
+        <v>40.58</v>
       </c>
       <c r="BI27" s="197">
         <v>33.33</v>
@@ -22506,7 +22506,7 @@
         <v>1</v>
       </c>
       <c r="BX27" s="197">
-        <v>127.27</v>
+        <v>121.74</v>
       </c>
       <c r="BY27" s="197">
         <v>100</v>
@@ -22530,7 +22530,7 @@
         <v>6</v>
       </c>
       <c r="CF27" s="197">
-        <v>127.27</v>
+        <v>121.74</v>
       </c>
       <c r="CG27" s="197">
         <v>100</v>
@@ -22554,7 +22554,7 @@
         <v>2</v>
       </c>
       <c r="CN27" s="197">
-        <v>84.85</v>
+        <v>81.16</v>
       </c>
       <c r="CO27" s="197">
         <v>66.67</v>
@@ -22578,7 +22578,7 @@
         <v>1</v>
       </c>
       <c r="CV27" s="197">
-        <v>42.42</v>
+        <v>40.58</v>
       </c>
       <c r="CW27" s="197">
         <v>33.33</v>
@@ -22602,7 +22602,7 @@
         <v>3</v>
       </c>
       <c r="DD27" s="197">
-        <v>381.82</v>
+        <v>365.22</v>
       </c>
       <c r="DE27" s="197">
         <v>300</v>
@@ -22637,7 +22637,7 @@
         <v>128</v>
       </c>
       <c r="H28" s="197">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I28" s="197">
         <v>8</v>
@@ -22649,7 +22649,7 @@
         <v>7</v>
       </c>
       <c r="L28" s="197">
-        <v>111.36</v>
+        <v>106.52</v>
       </c>
       <c r="M28" s="197">
         <v>87.5</v>
@@ -22673,7 +22673,7 @@
         <v>6</v>
       </c>
       <c r="T28" s="197">
-        <v>190.91</v>
+        <v>182.61</v>
       </c>
       <c r="U28" s="197">
         <v>150</v>
@@ -22721,7 +22721,7 @@
         <v>3</v>
       </c>
       <c r="AJ28" s="197">
-        <v>123.64</v>
+        <v>126.96</v>
       </c>
       <c r="AK28" s="197">
         <v>140</v>
@@ -22745,7 +22745,7 @@
         <v>1</v>
       </c>
       <c r="AR28" s="197">
-        <v>31.82</v>
+        <v>30.43</v>
       </c>
       <c r="AS28" s="197">
         <v>25</v>
@@ -22757,7 +22757,7 @@
         <v>100</v>
       </c>
       <c r="AV28" s="197">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW28" s="197">
         <v>30</v>
@@ -22769,7 +22769,7 @@
         <v>33</v>
       </c>
       <c r="AZ28" s="197">
-        <v>140</v>
+        <v>133.91</v>
       </c>
       <c r="BA28" s="197">
         <v>110</v>
@@ -22793,7 +22793,7 @@
         <v>5</v>
       </c>
       <c r="BH28" s="197">
-        <v>127.27</v>
+        <v>121.74</v>
       </c>
       <c r="BI28" s="197">
         <v>100</v>
@@ -22841,7 +22841,7 @@
         <v>1</v>
       </c>
       <c r="BX28" s="197">
-        <v>127.27</v>
+        <v>121.74</v>
       </c>
       <c r="BY28" s="197">
         <v>100</v>
@@ -22865,7 +22865,7 @@
         <v>12</v>
       </c>
       <c r="CF28" s="197">
-        <v>169.7</v>
+        <v>162.32</v>
       </c>
       <c r="CG28" s="197">
         <v>133.33000000000001</v>
@@ -22889,7 +22889,7 @@
         <v>6</v>
       </c>
       <c r="CN28" s="197">
-        <v>152.72999999999999</v>
+        <v>146.09</v>
       </c>
       <c r="CO28" s="197">
         <v>120</v>
@@ -22913,7 +22913,7 @@
         <v>4</v>
       </c>
       <c r="CV28" s="197">
-        <v>127.27</v>
+        <v>121.74</v>
       </c>
       <c r="CW28" s="197">
         <v>100</v>
@@ -22937,7 +22937,7 @@
         <v>1</v>
       </c>
       <c r="DD28" s="197">
-        <v>127.27</v>
+        <v>121.74</v>
       </c>
       <c r="DE28" s="197">
         <v>100</v>
@@ -22984,7 +22984,7 @@
         <v>2</v>
       </c>
       <c r="L29" s="197">
-        <v>84.85</v>
+        <v>81.16</v>
       </c>
       <c r="M29" s="197">
         <v>66.67</v>
@@ -23008,7 +23008,7 @@
         <v>2</v>
       </c>
       <c r="T29" s="197">
-        <v>127.27</v>
+        <v>121.74</v>
       </c>
       <c r="U29" s="197">
         <v>100</v>
@@ -23092,7 +23092,7 @@
         <v>100</v>
       </c>
       <c r="AV29" s="197">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW29" s="197">
         <v>14</v>
@@ -23104,7 +23104,7 @@
         <v>13</v>
       </c>
       <c r="AZ29" s="197">
-        <v>118.18</v>
+        <v>113.04</v>
       </c>
       <c r="BA29" s="197">
         <v>92.86</v>
@@ -23200,7 +23200,7 @@
         <v>3</v>
       </c>
       <c r="CF29" s="197">
-        <v>76.36</v>
+        <v>73.040000000000006</v>
       </c>
       <c r="CG29" s="197">
         <v>60</v>
@@ -23224,7 +23224,7 @@
         <v>1</v>
       </c>
       <c r="CN29" s="197">
-        <v>42.42</v>
+        <v>40.58</v>
       </c>
       <c r="CO29" s="197">
         <v>33.33</v>
@@ -23248,7 +23248,7 @@
         <v>4</v>
       </c>
       <c r="CV29" s="197">
-        <v>169.7</v>
+        <v>162.32</v>
       </c>
       <c r="CW29" s="197">
         <v>133.33000000000001</v>
@@ -23272,7 +23272,7 @@
         <v>1</v>
       </c>
       <c r="DD29" s="197">
-        <v>127.27</v>
+        <v>121.74</v>
       </c>
       <c r="DE29" s="197">
         <v>100</v>
@@ -29056,26 +29056,26 @@
         <v>72573808</v>
       </c>
       <c r="J7" s="191">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K7" s="191">
-        <v>0</v>
+        <v>904499</v>
       </c>
       <c r="L7" s="191">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="M7" s="191">
-        <v>60267809</v>
+        <v>61172308</v>
       </c>
       <c r="N7" s="192">
-        <v>84.79</v>
+        <v>86.18</v>
       </c>
       <c r="O7" s="192">
-        <v>83.04</v>
+        <v>84.29</v>
       </c>
       <c r="P7" s="135">
         <f>I7*0.97-M7</f>
-        <v>10128784.760000005</v>
+        <v>9224285.7600000054</v>
       </c>
       <c r="R7" s="173" t="s">
         <v>117</v>
@@ -29085,15 +29085,15 @@
         <v>101866340</v>
       </c>
       <c r="T7" s="175">
-        <v>27733838.799999997</v>
+        <v>23239489.799999997</v>
       </c>
       <c r="U7" s="189">
         <f>VLOOKUP(R7,$C$7:$P$27,14,0)</f>
-        <v>24566377.799999997</v>
+        <v>23239489.799999997</v>
       </c>
       <c r="V7" s="175">
         <f>VLOOKUP(R7,$C$7:$P$27,14,0)-T7</f>
-        <v>-3167461</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.45">
@@ -29125,26 +29125,26 @@
         <v>70243418</v>
       </c>
       <c r="J8" s="194">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K8" s="194">
-        <v>83140</v>
+        <v>772900</v>
       </c>
       <c r="L8" s="194">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="M8" s="194">
-        <v>57612005</v>
+        <v>58301765</v>
       </c>
       <c r="N8" s="195">
-        <v>79.739999999999995</v>
+        <v>80.84</v>
       </c>
       <c r="O8" s="195">
-        <v>82.02</v>
+        <v>83</v>
       </c>
       <c r="P8" s="135">
         <f t="shared" ref="P8:P27" si="0">I8*0.97-M8</f>
-        <v>10524110.459999993</v>
+        <v>9834350.4599999934</v>
       </c>
       <c r="R8" s="173" t="s">
         <v>67</v>
@@ -29154,15 +29154,15 @@
         <v>145101823</v>
       </c>
       <c r="T8" s="175">
-        <v>28033862.310000002</v>
+        <v>24558081.310000002</v>
       </c>
       <c r="U8" s="189">
         <f t="shared" ref="U8:U17" si="2">VLOOKUP(R8,$C$7:$P$27,14,0)</f>
-        <v>25544909.310000002</v>
+        <v>24558081.310000002</v>
       </c>
       <c r="V8" s="175">
         <f t="shared" ref="V8:V17" si="3">VLOOKUP(R8,$C$7:$P$27,14,0)-T8</f>
-        <v>-2488953</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.45">
@@ -29194,26 +29194,26 @@
         <v>145101823</v>
       </c>
       <c r="J9" s="191">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K9" s="191">
-        <v>323131</v>
+        <v>1309959</v>
       </c>
       <c r="L9" s="191">
-        <v>676</v>
+        <v>683</v>
       </c>
       <c r="M9" s="191">
-        <v>115203859</v>
+        <v>116190687</v>
       </c>
       <c r="N9" s="192">
-        <v>77.17</v>
+        <v>77.97</v>
       </c>
       <c r="O9" s="192">
-        <v>79.400000000000006</v>
+        <v>80.08</v>
       </c>
       <c r="P9" s="135">
         <f t="shared" si="0"/>
-        <v>25544909.310000002</v>
+        <v>24558081.310000002</v>
       </c>
       <c r="R9" s="174" t="s">
         <v>87</v>
@@ -29223,32 +29223,32 @@
         <v>141474291</v>
       </c>
       <c r="T9" s="175">
-        <v>49090015.270000011</v>
+        <v>35959578.270000011</v>
       </c>
       <c r="U9" s="189">
         <f t="shared" si="2"/>
-        <v>37677111.270000011</v>
+        <v>35959578.270000011</v>
       </c>
       <c r="V9" s="175">
         <f t="shared" si="3"/>
-        <v>-11412904</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A10" s="193" t="s">
-        <v>129</v>
+        <v>288</v>
       </c>
       <c r="B10" s="193" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="C10" s="193" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="D10" s="194">
-        <v>1048</v>
+        <v>308</v>
       </c>
       <c r="E10" s="194">
-        <v>180440547</v>
+        <v>51982396</v>
       </c>
       <c r="F10" s="194">
         <v>0</v>
@@ -29257,32 +29257,32 @@
         <v>0</v>
       </c>
       <c r="H10" s="194">
-        <v>1048</v>
+        <v>308</v>
       </c>
       <c r="I10" s="194">
-        <v>180440547</v>
+        <v>51982396</v>
       </c>
       <c r="J10" s="194">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="K10" s="194">
-        <v>2234000</v>
+        <v>1193885</v>
       </c>
       <c r="L10" s="194">
-        <v>807</v>
+        <v>243</v>
       </c>
       <c r="M10" s="194">
-        <v>142334047</v>
+        <v>41588724</v>
       </c>
       <c r="N10" s="195">
-        <v>77</v>
+        <v>78.900000000000006</v>
       </c>
       <c r="O10" s="195">
-        <v>78.88</v>
+        <v>80.010000000000005</v>
       </c>
       <c r="P10" s="135">
         <f t="shared" si="0"/>
-        <v>32693283.590000004</v>
+        <v>8834200.1199999973</v>
       </c>
       <c r="R10" s="174" t="s">
         <v>110</v>
@@ -29292,32 +29292,32 @@
         <v>149379338</v>
       </c>
       <c r="T10" s="175">
-        <v>61083318.859999985</v>
+        <v>46186242.859999985</v>
       </c>
       <c r="U10" s="189">
         <f t="shared" si="2"/>
-        <v>49140087.859999985</v>
+        <v>46186242.859999985</v>
       </c>
       <c r="V10" s="175">
         <f t="shared" si="3"/>
-        <v>-11943231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A11" s="190" t="s">
-        <v>288</v>
+        <v>129</v>
       </c>
       <c r="B11" s="190" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="C11" s="190" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="D11" s="191">
-        <v>308</v>
+        <v>1048</v>
       </c>
       <c r="E11" s="191">
-        <v>51982396</v>
+        <v>180440547</v>
       </c>
       <c r="F11" s="191">
         <v>0</v>
@@ -29326,32 +29326,32 @@
         <v>0</v>
       </c>
       <c r="H11" s="191">
-        <v>308</v>
+        <v>1048</v>
       </c>
       <c r="I11" s="191">
-        <v>51982396</v>
+        <v>180440547</v>
       </c>
       <c r="J11" s="191">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K11" s="191">
-        <v>0</v>
+        <v>3091276</v>
       </c>
       <c r="L11" s="191">
-        <v>238</v>
+        <v>810</v>
       </c>
       <c r="M11" s="191">
-        <v>40394839</v>
+        <v>143191323</v>
       </c>
       <c r="N11" s="192">
-        <v>77.27</v>
+        <v>77.290000000000006</v>
       </c>
       <c r="O11" s="192">
-        <v>77.709999999999994</v>
+        <v>79.36</v>
       </c>
       <c r="P11" s="135">
         <f t="shared" si="0"/>
-        <v>10028085.119999997</v>
+        <v>31836007.590000004</v>
       </c>
       <c r="R11" s="173" t="s">
         <v>99</v>
@@ -29361,15 +29361,15 @@
         <v>105953075</v>
       </c>
       <c r="T11" s="175">
-        <v>41167886.75</v>
+        <v>29500740.75</v>
       </c>
       <c r="U11" s="189">
         <f t="shared" si="2"/>
-        <v>31260021.75</v>
+        <v>29500740.75</v>
       </c>
       <c r="V11" s="175">
         <f t="shared" si="3"/>
-        <v>-9907865</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.45">
@@ -29401,26 +29401,26 @@
         <v>93597302</v>
       </c>
       <c r="J12" s="194">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K12" s="194">
-        <v>662979</v>
+        <v>2122634</v>
       </c>
       <c r="L12" s="194">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="M12" s="194">
-        <v>72713631</v>
+        <v>74173286</v>
       </c>
       <c r="N12" s="195">
-        <v>75.67</v>
+        <v>77.459999999999994</v>
       </c>
       <c r="O12" s="195">
-        <v>77.69</v>
+        <v>79.25</v>
       </c>
       <c r="P12" s="135">
         <f t="shared" si="0"/>
-        <v>18075751.939999998</v>
+        <v>16616096.939999998</v>
       </c>
       <c r="R12" s="173" t="s">
         <v>75</v>
@@ -29430,15 +29430,15 @@
         <v>152862316</v>
       </c>
       <c r="T12" s="175">
-        <v>36430325.520000011</v>
+        <v>31197103.520000011</v>
       </c>
       <c r="U12" s="189">
         <f t="shared" si="2"/>
-        <v>32413249.520000011</v>
+        <v>31197103.520000011</v>
       </c>
       <c r="V12" s="175">
         <f t="shared" si="3"/>
-        <v>-4017076</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.45">
@@ -29470,26 +29470,26 @@
         <v>116427734</v>
       </c>
       <c r="J13" s="191">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K13" s="191">
-        <v>332230</v>
+        <v>1371257</v>
       </c>
       <c r="L13" s="191">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="M13" s="191">
-        <v>89755206</v>
+        <v>90794233</v>
       </c>
       <c r="N13" s="192">
-        <v>74.86</v>
+        <v>75.84</v>
       </c>
       <c r="O13" s="192">
-        <v>77.09</v>
+        <v>77.98</v>
       </c>
       <c r="P13" s="135">
         <f t="shared" si="0"/>
-        <v>23179695.980000004</v>
+        <v>22140668.980000004</v>
       </c>
       <c r="R13" s="173" t="s">
         <v>107</v>
@@ -29499,15 +29499,15 @@
         <v>180440547</v>
       </c>
       <c r="T13" s="175">
-        <v>41487079.590000004</v>
+        <v>31836007.590000004</v>
       </c>
       <c r="U13" s="189">
         <f t="shared" si="2"/>
-        <v>32693283.590000004</v>
+        <v>31836007.590000004</v>
       </c>
       <c r="V13" s="175">
         <f t="shared" si="3"/>
-        <v>-8793796</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.45">
@@ -29539,26 +29539,26 @@
         <v>189656153</v>
       </c>
       <c r="J14" s="194">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="K14" s="194">
-        <v>100000</v>
+        <v>1974868</v>
       </c>
       <c r="L14" s="194">
-        <v>880</v>
+        <v>894</v>
       </c>
       <c r="M14" s="194">
-        <v>144524669</v>
+        <v>146399537</v>
       </c>
       <c r="N14" s="195">
-        <v>74.510000000000005</v>
+        <v>75.7</v>
       </c>
       <c r="O14" s="195">
-        <v>76.2</v>
+        <v>77.19</v>
       </c>
       <c r="P14" s="135">
         <f t="shared" si="0"/>
-        <v>39441799.409999996</v>
+        <v>37566931.409999996</v>
       </c>
       <c r="R14" s="174" t="s">
         <v>72</v>
@@ -29568,15 +29568,15 @@
         <v>162344260</v>
       </c>
       <c r="T14" s="175">
-        <v>50987798.199999988</v>
+        <v>41712909.199999988</v>
       </c>
       <c r="U14" s="189">
         <f t="shared" si="2"/>
-        <v>43381090.199999988</v>
+        <v>41712909.199999988</v>
       </c>
       <c r="V14" s="175">
         <f t="shared" si="3"/>
-        <v>-7606708</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.45">
@@ -29608,26 +29608,26 @@
         <v>152862316</v>
       </c>
       <c r="J15" s="191">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="K15" s="191">
-        <v>124425</v>
+        <v>1340571</v>
       </c>
       <c r="L15" s="191">
-        <v>678</v>
+        <v>690</v>
       </c>
       <c r="M15" s="191">
-        <v>115863197</v>
+        <v>117079343</v>
       </c>
       <c r="N15" s="192">
-        <v>72.05</v>
+        <v>73.33</v>
       </c>
       <c r="O15" s="192">
-        <v>75.8</v>
+        <v>76.59</v>
       </c>
       <c r="P15" s="135">
         <f t="shared" si="0"/>
-        <v>32413249.520000011</v>
+        <v>31197103.520000011</v>
       </c>
       <c r="R15" s="174" t="s">
         <v>113</v>
@@ -29637,15 +29637,15 @@
         <v>194517020</v>
       </c>
       <c r="T15" s="175">
-        <v>66475047.400000006</v>
+        <v>59633806.400000006</v>
       </c>
       <c r="U15" s="189">
         <f t="shared" si="2"/>
-        <v>62342498.400000006</v>
+        <v>59633806.400000006</v>
       </c>
       <c r="V15" s="175">
         <f t="shared" si="3"/>
-        <v>-4132549</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.45">
@@ -29677,26 +29677,26 @@
         <v>53605661</v>
       </c>
       <c r="J16" s="194">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K16" s="194">
-        <v>120406</v>
+        <v>1297321</v>
       </c>
       <c r="L16" s="194">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="M16" s="194">
-        <v>39700286</v>
+        <v>40877201</v>
       </c>
       <c r="N16" s="195">
-        <v>69.66</v>
+        <v>72.47</v>
       </c>
       <c r="O16" s="195">
-        <v>74.06</v>
+        <v>76.260000000000005</v>
       </c>
       <c r="P16" s="135">
         <f t="shared" si="0"/>
-        <v>12297205.170000002</v>
+        <v>11120290.170000002</v>
       </c>
       <c r="R16" s="174" t="s">
         <v>119</v>
@@ -29706,15 +29706,15 @@
         <v>189656153</v>
       </c>
       <c r="T16" s="175">
-        <v>43448976.409999996</v>
+        <v>37566931.409999996</v>
       </c>
       <c r="U16" s="189">
         <f t="shared" si="2"/>
-        <v>39441799.409999996</v>
+        <v>37566931.409999996</v>
       </c>
       <c r="V16" s="175">
         <f t="shared" si="3"/>
-        <v>-4007177</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.45">
@@ -29746,26 +29746,26 @@
         <v>66800107</v>
       </c>
       <c r="J17" s="191">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K17" s="191">
-        <v>0</v>
+        <v>520496</v>
       </c>
       <c r="L17" s="191">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="M17" s="191">
-        <v>49312585</v>
+        <v>49833081</v>
       </c>
       <c r="N17" s="192">
-        <v>70.599999999999994</v>
+        <v>71.569999999999993</v>
       </c>
       <c r="O17" s="192">
-        <v>73.819999999999993</v>
+        <v>74.599999999999994</v>
       </c>
       <c r="P17" s="135">
         <f t="shared" si="0"/>
-        <v>15483518.789999999</v>
+        <v>14963022.789999999</v>
       </c>
       <c r="R17" s="173" t="s">
         <v>84</v>
@@ -29775,32 +29775,32 @@
         <v>95369711</v>
       </c>
       <c r="T17" s="175">
-        <v>43417827.670000002</v>
+        <v>22510770.670000002</v>
       </c>
       <c r="U17" s="189">
         <f t="shared" si="2"/>
-        <v>23804513.670000002</v>
+        <v>22510770.670000002</v>
       </c>
       <c r="V17" s="175">
         <f t="shared" si="3"/>
-        <v>-19613314</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A18" s="193" t="s">
-        <v>288</v>
+        <v>128</v>
       </c>
       <c r="B18" s="193" t="s">
-        <v>289</v>
+        <v>116</v>
       </c>
       <c r="C18" s="193" t="s">
-        <v>284</v>
+        <v>117</v>
       </c>
       <c r="D18" s="194">
-        <v>318</v>
+        <v>642</v>
       </c>
       <c r="E18" s="194">
-        <v>50351985</v>
+        <v>101866340</v>
       </c>
       <c r="F18" s="194">
         <v>0</v>
@@ -29809,49 +29809,49 @@
         <v>0</v>
       </c>
       <c r="H18" s="194">
-        <v>318</v>
+        <v>642</v>
       </c>
       <c r="I18" s="194">
-        <v>50351985</v>
+        <v>101866340</v>
       </c>
       <c r="J18" s="194">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K18" s="194">
-        <v>0</v>
+        <v>1554987</v>
       </c>
       <c r="L18" s="194">
-        <v>224</v>
+        <v>457</v>
       </c>
       <c r="M18" s="194">
-        <v>37022198</v>
+        <v>75570860</v>
       </c>
       <c r="N18" s="195">
-        <v>70.44</v>
+        <v>71.180000000000007</v>
       </c>
       <c r="O18" s="195">
-        <v>73.53</v>
+        <v>74.19</v>
       </c>
       <c r="P18" s="135">
         <f t="shared" si="0"/>
-        <v>11819227.449999996</v>
+        <v>23239489.799999997</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A19" s="190" t="s">
-        <v>128</v>
+        <v>288</v>
       </c>
       <c r="B19" s="190" t="s">
-        <v>116</v>
+        <v>289</v>
       </c>
       <c r="C19" s="190" t="s">
-        <v>117</v>
+        <v>284</v>
       </c>
       <c r="D19" s="191">
-        <v>642</v>
+        <v>318</v>
       </c>
       <c r="E19" s="191">
-        <v>101866340</v>
+        <v>50351985</v>
       </c>
       <c r="F19" s="191">
         <v>0</v>
@@ -29860,32 +29860,32 @@
         <v>0</v>
       </c>
       <c r="H19" s="191">
-        <v>642</v>
+        <v>318</v>
       </c>
       <c r="I19" s="191">
-        <v>101866340</v>
+        <v>50351985</v>
       </c>
       <c r="J19" s="191">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K19" s="191">
-        <v>228099</v>
+        <v>92893</v>
       </c>
       <c r="L19" s="191">
-        <v>448</v>
+        <v>226</v>
       </c>
       <c r="M19" s="191">
-        <v>74243972</v>
+        <v>37115091</v>
       </c>
       <c r="N19" s="192">
-        <v>69.78</v>
+        <v>71.069999999999993</v>
       </c>
       <c r="O19" s="192">
-        <v>72.88</v>
+        <v>73.709999999999994</v>
       </c>
       <c r="P19" s="135">
         <f t="shared" si="0"/>
-        <v>24566377.799999997</v>
+        <v>11726334.449999996</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.45">
@@ -29917,26 +29917,26 @@
         <v>95369711</v>
       </c>
       <c r="J20" s="194">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K20" s="194">
-        <v>12863161</v>
+        <v>14156904</v>
       </c>
       <c r="L20" s="194">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="M20" s="194">
-        <v>68704106</v>
+        <v>69997849</v>
       </c>
       <c r="N20" s="195">
-        <v>70.41</v>
+        <v>72.11</v>
       </c>
       <c r="O20" s="195">
-        <v>72.040000000000006</v>
+        <v>73.400000000000006</v>
       </c>
       <c r="P20" s="135">
         <f t="shared" si="0"/>
-        <v>23804513.670000002</v>
+        <v>22510770.670000002</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.45">
@@ -29968,26 +29968,26 @@
         <v>141474291</v>
       </c>
       <c r="J21" s="191">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="K21" s="191">
-        <v>358927</v>
+        <v>2076460</v>
       </c>
       <c r="L21" s="191">
-        <v>592</v>
+        <v>605</v>
       </c>
       <c r="M21" s="191">
-        <v>99552951</v>
+        <v>101270484</v>
       </c>
       <c r="N21" s="192">
-        <v>69.400000000000006</v>
+        <v>70.930000000000007</v>
       </c>
       <c r="O21" s="192">
-        <v>70.37</v>
+        <v>71.58</v>
       </c>
       <c r="P21" s="135">
         <f t="shared" si="0"/>
-        <v>37677111.270000011</v>
+        <v>35959578.270000011</v>
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.45">
@@ -30019,26 +30019,26 @@
         <v>162344260</v>
       </c>
       <c r="J22" s="194">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K22" s="194">
-        <v>536613</v>
+        <v>2204794</v>
       </c>
       <c r="L22" s="194">
-        <v>670</v>
+        <v>679</v>
       </c>
       <c r="M22" s="194">
-        <v>114092842</v>
+        <v>115761023</v>
       </c>
       <c r="N22" s="195">
-        <v>69.209999999999994</v>
+        <v>70.14</v>
       </c>
       <c r="O22" s="195">
-        <v>70.28</v>
+        <v>71.31</v>
       </c>
       <c r="P22" s="135">
         <f t="shared" si="0"/>
-        <v>43381090.199999988</v>
+        <v>41712909.199999988</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.45">
@@ -30070,26 +30070,26 @@
         <v>105953075</v>
       </c>
       <c r="J23" s="191">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="K23" s="191">
-        <v>168000</v>
+        <v>1927281</v>
       </c>
       <c r="L23" s="191">
-        <v>451</v>
+        <v>465</v>
       </c>
       <c r="M23" s="191">
-        <v>71514461</v>
+        <v>73273742</v>
       </c>
       <c r="N23" s="192">
-        <v>65.650000000000006</v>
+        <v>67.69</v>
       </c>
       <c r="O23" s="192">
-        <v>67.5</v>
+        <v>69.16</v>
       </c>
       <c r="P23" s="135">
         <f t="shared" si="0"/>
-        <v>31260021.75</v>
+        <v>29500740.75</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.45">
@@ -30121,26 +30121,26 @@
         <v>194517020</v>
       </c>
       <c r="J24" s="194">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="K24" s="194">
-        <v>294983</v>
+        <v>3003675</v>
       </c>
       <c r="L24" s="194">
-        <v>759</v>
+        <v>775</v>
       </c>
       <c r="M24" s="194">
-        <v>126339011</v>
+        <v>129047703</v>
       </c>
       <c r="N24" s="195">
-        <v>63.36</v>
+        <v>64.69</v>
       </c>
       <c r="O24" s="195">
-        <v>64.95</v>
+        <v>66.34</v>
       </c>
       <c r="P24" s="135">
         <f t="shared" si="0"/>
-        <v>62342498.400000006</v>
+        <v>59633806.400000006</v>
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.45">
@@ -30172,26 +30172,26 @@
         <v>149379338</v>
       </c>
       <c r="J25" s="191">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="K25" s="191">
-        <v>5451000</v>
+        <v>8404845</v>
       </c>
       <c r="L25" s="191">
-        <v>577</v>
+        <v>597</v>
       </c>
       <c r="M25" s="191">
-        <v>95757870</v>
+        <v>98711715</v>
       </c>
       <c r="N25" s="192">
-        <v>64.69</v>
+        <v>66.930000000000007</v>
       </c>
       <c r="O25" s="192">
-        <v>64.099999999999994</v>
+        <v>66.08</v>
       </c>
       <c r="P25" s="135">
         <f t="shared" si="0"/>
-        <v>49140087.859999985</v>
+        <v>46186242.859999985</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.45">
@@ -30199,16 +30199,16 @@
         <v>288</v>
       </c>
       <c r="B26" s="193" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C26" s="193" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D26" s="194">
-        <v>546</v>
+        <v>683</v>
       </c>
       <c r="E26" s="194">
-        <v>89879995</v>
+        <v>105983346</v>
       </c>
       <c r="F26" s="194">
         <v>0</v>
@@ -30217,32 +30217,32 @@
         <v>0</v>
       </c>
       <c r="H26" s="194">
-        <v>546</v>
+        <v>683</v>
       </c>
       <c r="I26" s="194">
-        <v>89879995</v>
+        <v>105983346</v>
       </c>
       <c r="J26" s="194">
-        <v>1</v>
+        <v>164</v>
       </c>
       <c r="K26" s="194">
-        <v>118230</v>
+        <v>24260428</v>
       </c>
       <c r="L26" s="194">
-        <v>331</v>
+        <v>442</v>
       </c>
       <c r="M26" s="194">
-        <v>56235390</v>
+        <v>68103742</v>
       </c>
       <c r="N26" s="195">
-        <v>60.62</v>
+        <v>64.709999999999994</v>
       </c>
       <c r="O26" s="195">
-        <v>62.57</v>
+        <v>64.260000000000005</v>
       </c>
       <c r="P26" s="135">
         <f t="shared" si="0"/>
-        <v>30948205.149999991</v>
+        <v>34700103.61999999</v>
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.45">
@@ -30250,16 +30250,16 @@
         <v>288</v>
       </c>
       <c r="B27" s="190" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C27" s="190" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D27" s="191">
-        <v>683</v>
+        <v>546</v>
       </c>
       <c r="E27" s="191">
-        <v>105983346</v>
+        <v>89879995</v>
       </c>
       <c r="F27" s="191">
         <v>0</v>
@@ -30268,32 +30268,32 @@
         <v>0</v>
       </c>
       <c r="H27" s="191">
-        <v>683</v>
+        <v>546</v>
       </c>
       <c r="I27" s="191">
-        <v>105983346</v>
+        <v>89879995</v>
       </c>
       <c r="J27" s="191">
-        <v>77</v>
+        <v>9</v>
       </c>
       <c r="K27" s="191">
-        <v>7838032</v>
+        <v>1305214</v>
       </c>
       <c r="L27" s="191">
-        <v>355</v>
+        <v>339</v>
       </c>
       <c r="M27" s="191">
-        <v>51681346</v>
+        <v>57422374</v>
       </c>
       <c r="N27" s="192">
-        <v>51.98</v>
+        <v>62.09</v>
       </c>
       <c r="O27" s="192">
-        <v>48.76</v>
+        <v>63.89</v>
       </c>
       <c r="P27" s="135">
         <f t="shared" si="0"/>
-        <v>51122499.61999999</v>
+        <v>29761221.149999991</v>
       </c>
     </row>
   </sheetData>

--- a/filetiendo.xlsx
+++ b/filetiendo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\viettel 2026\thang 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFCD2D9C-B6F2-43B4-A833-7C6814F3EE02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBCF3737-3657-4695-8DA6-265985A38845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="808" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1049" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1049" uniqueCount="293">
   <si>
     <t>STT</t>
   </si>
@@ -918,9 +918,6 @@
     <t>Mybox</t>
   </si>
   <si>
-    <t>TAIDT2_CTX_DVTM_LDG</t>
-  </si>
-  <si>
     <t>MAITTN_LDG_CNKD</t>
   </si>
   <si>
@@ -4556,17 +4553,41 @@
     <xf numFmtId="0" fontId="66" fillId="0" borderId="109" xfId="11" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="109" xfId="11" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="177" xfId="11" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="50" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="5" borderId="127" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="135" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="134" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="133" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="5" borderId="130" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="128" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="140" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="139" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="138" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="5" borderId="127" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="24" borderId="132" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4580,34 +4601,10 @@
     <xf numFmtId="0" fontId="17" fillId="5" borderId="129" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="135" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="134" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="133" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="16" borderId="136" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="2" borderId="137" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="140" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="139" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="138" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="67" fillId="18" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4679,16 +4676,16 @@
     <xf numFmtId="0" fontId="63" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="148" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="147" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="47" fillId="5" borderId="152" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="5" borderId="151" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="148" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="147" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="51" fillId="5" borderId="150" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4708,12 +4705,6 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="155" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="158" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="157" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="159" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4739,10 +4730,10 @@
     <xf numFmtId="0" fontId="55" fillId="0" borderId="164" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="69" fillId="29" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="158" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="69" fillId="29" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="157" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="45" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4767,6 +4758,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="168" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="69" fillId="29" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="29" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="12">
     <cellStyle name="Comma" xfId="8" builtinId="3"/>
@@ -5656,166 +5653,166 @@
       </c>
     </row>
     <row r="2" spans="1:675" ht="23.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="200" t="s">
+      <c r="A2" s="210" t="s">
         <v>34</v>
       </c>
       <c r="B2" s="86"/>
       <c r="C2" s="15"/>
-      <c r="D2" s="211" t="s">
+      <c r="D2" s="216" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="211"/>
-      <c r="F2" s="211"/>
-      <c r="G2" s="211"/>
-      <c r="H2" s="211"/>
-      <c r="I2" s="211"/>
-      <c r="J2" s="211"/>
-      <c r="K2" s="211"/>
-      <c r="L2" s="211"/>
-      <c r="M2" s="211"/>
-      <c r="N2" s="211"/>
-      <c r="O2" s="211"/>
-      <c r="P2" s="211"/>
-      <c r="Q2" s="211"/>
-      <c r="R2" s="211"/>
-      <c r="S2" s="211"/>
-      <c r="T2" s="206" t="s">
+      <c r="E2" s="216"/>
+      <c r="F2" s="216"/>
+      <c r="G2" s="216"/>
+      <c r="H2" s="216"/>
+      <c r="I2" s="216"/>
+      <c r="J2" s="216"/>
+      <c r="K2" s="216"/>
+      <c r="L2" s="216"/>
+      <c r="M2" s="216"/>
+      <c r="N2" s="216"/>
+      <c r="O2" s="216"/>
+      <c r="P2" s="216"/>
+      <c r="Q2" s="216"/>
+      <c r="R2" s="216"/>
+      <c r="S2" s="216"/>
+      <c r="T2" s="214" t="s">
         <v>36</v>
       </c>
-      <c r="U2" s="206"/>
-      <c r="V2" s="206"/>
-      <c r="W2" s="206"/>
-      <c r="X2" s="206"/>
-      <c r="Y2" s="206"/>
-      <c r="Z2" s="206"/>
-      <c r="AA2" s="206"/>
-      <c r="AB2" s="206"/>
-      <c r="AC2" s="206"/>
-      <c r="AD2" s="206"/>
-      <c r="AE2" s="206"/>
-      <c r="AF2" s="206"/>
-      <c r="AG2" s="206"/>
-      <c r="AH2" s="206"/>
-      <c r="AI2" s="206"/>
-      <c r="AJ2" s="205" t="s">
+      <c r="U2" s="214"/>
+      <c r="V2" s="214"/>
+      <c r="W2" s="214"/>
+      <c r="X2" s="214"/>
+      <c r="Y2" s="214"/>
+      <c r="Z2" s="214"/>
+      <c r="AA2" s="214"/>
+      <c r="AB2" s="214"/>
+      <c r="AC2" s="214"/>
+      <c r="AD2" s="214"/>
+      <c r="AE2" s="214"/>
+      <c r="AF2" s="214"/>
+      <c r="AG2" s="214"/>
+      <c r="AH2" s="214"/>
+      <c r="AI2" s="214"/>
+      <c r="AJ2" s="213" t="s">
         <v>37</v>
       </c>
-      <c r="AK2" s="205"/>
-      <c r="AL2" s="205"/>
-      <c r="AM2" s="205"/>
-      <c r="AN2" s="205"/>
-      <c r="AO2" s="205"/>
-      <c r="AP2" s="205"/>
-      <c r="AQ2" s="205"/>
-      <c r="AR2" s="205"/>
-      <c r="AS2" s="205"/>
-      <c r="AT2" s="205"/>
-      <c r="AU2" s="205"/>
-      <c r="AV2" s="204" t="s">
+      <c r="AK2" s="213"/>
+      <c r="AL2" s="213"/>
+      <c r="AM2" s="213"/>
+      <c r="AN2" s="213"/>
+      <c r="AO2" s="213"/>
+      <c r="AP2" s="213"/>
+      <c r="AQ2" s="213"/>
+      <c r="AR2" s="213"/>
+      <c r="AS2" s="213"/>
+      <c r="AT2" s="213"/>
+      <c r="AU2" s="213"/>
+      <c r="AV2" s="212" t="s">
         <v>38</v>
       </c>
-      <c r="AW2" s="204"/>
-      <c r="AX2" s="204"/>
-      <c r="AY2" s="204"/>
-      <c r="AZ2" s="204"/>
-      <c r="BA2" s="204"/>
-      <c r="BB2" s="204"/>
-      <c r="BC2" s="204"/>
-      <c r="BD2" s="204"/>
-      <c r="BE2" s="204"/>
-      <c r="BF2" s="204"/>
-      <c r="BG2" s="204"/>
+      <c r="AW2" s="212"/>
+      <c r="AX2" s="212"/>
+      <c r="AY2" s="212"/>
+      <c r="AZ2" s="212"/>
+      <c r="BA2" s="212"/>
+      <c r="BB2" s="212"/>
+      <c r="BC2" s="212"/>
+      <c r="BD2" s="212"/>
+      <c r="BE2" s="212"/>
+      <c r="BF2" s="212"/>
+      <c r="BG2" s="212"/>
     </row>
     <row r="3" spans="1:675" s="3" customFormat="1" ht="28.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="200"/>
-      <c r="B3" s="212" t="s">
+      <c r="A3" s="210"/>
+      <c r="B3" s="217" t="s">
         <v>39</v>
       </c>
       <c r="C3" s="87"/>
-      <c r="D3" s="202" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="203"/>
-      <c r="F3" s="203"/>
-      <c r="G3" s="203"/>
-      <c r="H3" s="202" t="s">
+      <c r="D3" s="204" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="205"/>
+      <c r="F3" s="205"/>
+      <c r="G3" s="205"/>
+      <c r="H3" s="204" t="s">
         <v>40</v>
       </c>
-      <c r="I3" s="203"/>
-      <c r="J3" s="203"/>
-      <c r="K3" s="203"/>
-      <c r="L3" s="202" t="s">
+      <c r="I3" s="205"/>
+      <c r="J3" s="205"/>
+      <c r="K3" s="205"/>
+      <c r="L3" s="204" t="s">
         <v>41</v>
       </c>
-      <c r="M3" s="203"/>
-      <c r="N3" s="203"/>
-      <c r="O3" s="203"/>
-      <c r="P3" s="215" t="s">
+      <c r="M3" s="205"/>
+      <c r="N3" s="205"/>
+      <c r="O3" s="205"/>
+      <c r="P3" s="207" t="s">
         <v>42</v>
       </c>
-      <c r="Q3" s="216"/>
-      <c r="R3" s="216"/>
-      <c r="S3" s="217"/>
-      <c r="T3" s="202" t="s">
+      <c r="Q3" s="208"/>
+      <c r="R3" s="208"/>
+      <c r="S3" s="209"/>
+      <c r="T3" s="204" t="s">
         <v>43</v>
       </c>
-      <c r="U3" s="203"/>
-      <c r="V3" s="203"/>
-      <c r="W3" s="203"/>
-      <c r="X3" s="202" t="s">
+      <c r="U3" s="205"/>
+      <c r="V3" s="205"/>
+      <c r="W3" s="205"/>
+      <c r="X3" s="204" t="s">
         <v>45</v>
       </c>
-      <c r="Y3" s="203"/>
-      <c r="Z3" s="203"/>
-      <c r="AA3" s="203"/>
-      <c r="AB3" s="202" t="s">
+      <c r="Y3" s="205"/>
+      <c r="Z3" s="205"/>
+      <c r="AA3" s="205"/>
+      <c r="AB3" s="204" t="s">
         <v>47</v>
       </c>
-      <c r="AC3" s="203"/>
-      <c r="AD3" s="203"/>
-      <c r="AE3" s="203"/>
-      <c r="AF3" s="202" t="s">
+      <c r="AC3" s="205"/>
+      <c r="AD3" s="205"/>
+      <c r="AE3" s="205"/>
+      <c r="AF3" s="204" t="s">
         <v>48</v>
       </c>
-      <c r="AG3" s="203"/>
-      <c r="AH3" s="203"/>
-      <c r="AI3" s="203"/>
-      <c r="AJ3" s="208" t="s">
+      <c r="AG3" s="205"/>
+      <c r="AH3" s="205"/>
+      <c r="AI3" s="205"/>
+      <c r="AJ3" s="201" t="s">
         <v>51</v>
       </c>
-      <c r="AK3" s="209"/>
-      <c r="AL3" s="209"/>
-      <c r="AM3" s="210"/>
-      <c r="AN3" s="208" t="s">
+      <c r="AK3" s="202"/>
+      <c r="AL3" s="202"/>
+      <c r="AM3" s="203"/>
+      <c r="AN3" s="201" t="s">
         <v>14</v>
       </c>
-      <c r="AO3" s="209"/>
-      <c r="AP3" s="209"/>
-      <c r="AQ3" s="210"/>
-      <c r="AR3" s="208" t="s">
+      <c r="AO3" s="202"/>
+      <c r="AP3" s="202"/>
+      <c r="AQ3" s="203"/>
+      <c r="AR3" s="201" t="s">
         <v>52</v>
       </c>
-      <c r="AS3" s="209"/>
-      <c r="AT3" s="209"/>
-      <c r="AU3" s="210"/>
-      <c r="AV3" s="203" t="s">
+      <c r="AS3" s="202"/>
+      <c r="AT3" s="202"/>
+      <c r="AU3" s="203"/>
+      <c r="AV3" s="205" t="s">
         <v>16</v>
       </c>
-      <c r="AW3" s="203"/>
-      <c r="AX3" s="203"/>
-      <c r="AY3" s="203"/>
-      <c r="AZ3" s="203" t="s">
+      <c r="AW3" s="205"/>
+      <c r="AX3" s="205"/>
+      <c r="AY3" s="205"/>
+      <c r="AZ3" s="205" t="s">
         <v>54</v>
       </c>
-      <c r="BA3" s="203"/>
-      <c r="BB3" s="203"/>
-      <c r="BC3" s="203"/>
-      <c r="BD3" s="202" t="s">
+      <c r="BA3" s="205"/>
+      <c r="BB3" s="205"/>
+      <c r="BC3" s="205"/>
+      <c r="BD3" s="204" t="s">
         <v>55</v>
       </c>
-      <c r="BE3" s="203"/>
-      <c r="BF3" s="207"/>
-      <c r="BG3" s="203"/>
+      <c r="BE3" s="205"/>
+      <c r="BF3" s="215"/>
+      <c r="BG3" s="205"/>
       <c r="BH3" s="2"/>
       <c r="BI3" s="2"/>
       <c r="BJ3" s="2"/>
@@ -6434,8 +6431,8 @@
       <c r="YY3" s="2"/>
     </row>
     <row r="4" spans="1:675" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="201"/>
-      <c r="B4" s="212"/>
+      <c r="A4" s="211"/>
+      <c r="B4" s="217"/>
       <c r="C4" s="88"/>
       <c r="D4" s="8" t="s">
         <v>2</v>
@@ -6780,7 +6777,7 @@
       </c>
       <c r="AS5" s="129">
         <f>(VLOOKUP(B5,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.80079999999999996</v>
+        <v>0.83250000000000002</v>
       </c>
       <c r="AT5" s="14">
         <f t="shared" ref="AT5:AT18" si="20">IF(AS5&lt;94.5%,0,IF(AS5&lt;95.54%,50%,IF(AS5&lt;AR5,80%,100%+(30%*(AS5-AR5)/3.39%))))</f>
@@ -6788,7 +6785,7 @@
       </c>
       <c r="AU5" s="54">
         <f t="shared" ref="AU5:AU18" si="21">AR5-AS5</f>
-        <v>0.16920000000000002</v>
+        <v>0.13749999999999996</v>
       </c>
       <c r="AV5" s="57">
         <f>VLOOKUP(C5,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7013,7 +7010,7 @@
       </c>
       <c r="AS6" s="129">
         <f>(VLOOKUP(B6,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.71310000000000007</v>
+        <v>0.75790000000000013</v>
       </c>
       <c r="AT6" s="14">
         <f t="shared" si="20"/>
@@ -7021,7 +7018,7 @@
       </c>
       <c r="AU6" s="54">
         <f t="shared" si="21"/>
-        <v>0.25689999999999991</v>
+        <v>0.21209999999999984</v>
       </c>
       <c r="AV6" s="57">
         <f>VLOOKUP(C6,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7246,7 +7243,7 @@
       </c>
       <c r="AS7" s="129">
         <f>(VLOOKUP(B7,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.76590000000000003</v>
+        <v>0.79480000000000006</v>
       </c>
       <c r="AT7" s="14">
         <f t="shared" si="20"/>
@@ -7254,7 +7251,7 @@
       </c>
       <c r="AU7" s="54">
         <f t="shared" si="21"/>
-        <v>0.20409999999999995</v>
+        <v>0.17519999999999991</v>
       </c>
       <c r="AV7" s="57">
         <f>VLOOKUP(C7,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7479,7 +7476,7 @@
       </c>
       <c r="AS8" s="129">
         <f>(VLOOKUP(B8,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.64260000000000006</v>
+        <v>0.8034</v>
       </c>
       <c r="AT8" s="14">
         <f t="shared" si="20"/>
@@ -7487,7 +7484,7 @@
       </c>
       <c r="AU8" s="54">
         <f t="shared" si="21"/>
-        <v>0.32739999999999991</v>
+        <v>0.16659999999999997</v>
       </c>
       <c r="AV8" s="57">
         <f>VLOOKUP(C8,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7712,7 +7709,7 @@
       </c>
       <c r="AS9" s="129">
         <f>(VLOOKUP(B9,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.63890000000000002</v>
+        <v>0.66239999999999999</v>
       </c>
       <c r="AT9" s="14">
         <f t="shared" si="20"/>
@@ -7720,7 +7717,7 @@
       </c>
       <c r="AU9" s="54">
         <f t="shared" si="21"/>
-        <v>0.33109999999999995</v>
+        <v>0.30759999999999998</v>
       </c>
       <c r="AV9" s="57">
         <f>VLOOKUP(C9,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7945,7 +7942,7 @@
       </c>
       <c r="AS10" s="129">
         <f>(VLOOKUP(B10,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.7340000000000001</v>
+        <v>0.76080000000000003</v>
       </c>
       <c r="AT10" s="14">
         <f t="shared" si="20"/>
@@ -7953,7 +7950,7 @@
       </c>
       <c r="AU10" s="54">
         <f t="shared" si="21"/>
-        <v>0.23599999999999988</v>
+        <v>0.20919999999999994</v>
       </c>
       <c r="AV10" s="57">
         <f>VLOOKUP(C10,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8178,7 +8175,7 @@
       </c>
       <c r="AS11" s="129">
         <f>(VLOOKUP(B11,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.71579999999999999</v>
+        <v>0.74230000000000007</v>
       </c>
       <c r="AT11" s="14">
         <f t="shared" si="20"/>
@@ -8186,7 +8183,7 @@
       </c>
       <c r="AU11" s="54">
         <f t="shared" si="21"/>
-        <v>0.25419999999999998</v>
+        <v>0.2276999999999999</v>
       </c>
       <c r="AV11" s="57">
         <f>VLOOKUP(C11,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8411,7 +8408,7 @@
       </c>
       <c r="AS12" s="129">
         <f>(VLOOKUP(B12,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.69159999999999999</v>
+        <v>0.71950000000000003</v>
       </c>
       <c r="AT12" s="14">
         <f t="shared" si="20"/>
@@ -8419,7 +8416,7 @@
       </c>
       <c r="AU12" s="54">
         <f t="shared" si="21"/>
-        <v>0.27839999999999998</v>
+        <v>0.25049999999999994</v>
       </c>
       <c r="AV12" s="57">
         <f>VLOOKUP(C12,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8644,7 +8641,7 @@
       </c>
       <c r="AS13" s="129">
         <f>(VLOOKUP(B13,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.79359999999999997</v>
+        <v>0.82000000000000006</v>
       </c>
       <c r="AT13" s="14">
         <f t="shared" si="20"/>
@@ -8652,7 +8649,7 @@
       </c>
       <c r="AU13" s="54">
         <f t="shared" si="21"/>
-        <v>0.1764</v>
+        <v>0.14999999999999991</v>
       </c>
       <c r="AV13" s="57">
         <f>VLOOKUP(C13,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8877,7 +8874,7 @@
       </c>
       <c r="AS14" s="129">
         <f>(VLOOKUP(B14,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.66079999999999994</v>
+        <v>0.67670000000000008</v>
       </c>
       <c r="AT14" s="14">
         <f t="shared" si="20"/>
@@ -8885,7 +8882,7 @@
       </c>
       <c r="AU14" s="54">
         <f t="shared" si="21"/>
-        <v>0.30920000000000003</v>
+        <v>0.29329999999999989</v>
       </c>
       <c r="AV14" s="57">
         <f>VLOOKUP(C14,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -9110,7 +9107,7 @@
       </c>
       <c r="AS15" s="129">
         <f>(VLOOKUP(B15,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.6634000000000001</v>
+        <v>0.69000000000000006</v>
       </c>
       <c r="AT15" s="14">
         <f t="shared" si="20"/>
@@ -9118,7 +9115,7 @@
       </c>
       <c r="AU15" s="54">
         <f t="shared" si="21"/>
-        <v>0.30659999999999987</v>
+        <v>0.27999999999999992</v>
       </c>
       <c r="AV15" s="57">
         <f>VLOOKUP(C15,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -9343,7 +9340,7 @@
       </c>
       <c r="AS16" s="129">
         <f>(VLOOKUP(B16,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.7419</v>
+        <v>0.78260000000000007</v>
       </c>
       <c r="AT16" s="14">
         <f t="shared" si="20"/>
@@ -9351,7 +9348,7 @@
       </c>
       <c r="AU16" s="54">
         <f t="shared" si="21"/>
-        <v>0.22809999999999997</v>
+        <v>0.1873999999999999</v>
       </c>
       <c r="AV16" s="57">
         <f>VLOOKUP(C16,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -9576,7 +9573,7 @@
       </c>
       <c r="AS17" s="129">
         <f>(VLOOKUP(B17,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.77190000000000003</v>
+        <v>0.79709999999999992</v>
       </c>
       <c r="AT17" s="14">
         <f t="shared" si="20"/>
@@ -9584,7 +9581,7 @@
       </c>
       <c r="AU17" s="54">
         <f t="shared" si="21"/>
-        <v>0.19809999999999994</v>
+        <v>0.17290000000000005</v>
       </c>
       <c r="AV17" s="57">
         <f>VLOOKUP(C17,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -9809,7 +9806,7 @@
       </c>
       <c r="AS18" s="129">
         <f>(VLOOKUP(B18,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.746</v>
+        <v>0.76400000000000012</v>
       </c>
       <c r="AT18" s="14">
         <f t="shared" si="20"/>
@@ -9817,7 +9814,7 @@
       </c>
       <c r="AU18" s="54">
         <f t="shared" si="21"/>
-        <v>0.22399999999999998</v>
+        <v>0.20599999999999985</v>
       </c>
       <c r="AV18" s="57">
         <f>VLOOKUP(C18,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -9874,11 +9871,11 @@
       <c r="C19" s="15"/>
       <c r="D19" s="15"/>
       <c r="E19" s="16"/>
-      <c r="F19" s="213">
+      <c r="F19" s="200">
         <f ca="1">TODAY()</f>
         <v>46077</v>
       </c>
-      <c r="G19" s="213"/>
+      <c r="G19" s="200"/>
       <c r="H19" s="90"/>
       <c r="I19" s="91">
         <f ca="1">DAY(F19)</f>
@@ -9891,33 +9888,33 @@
         <f ca="1">I19/J19</f>
         <v>0.77419354838709675</v>
       </c>
-      <c r="L19" s="214" t="s">
+      <c r="L19" s="206" t="s">
         <v>124</v>
       </c>
-      <c r="M19" s="214"/>
-      <c r="N19" s="214"/>
-      <c r="O19" s="214"/>
-      <c r="P19" s="214"/>
-      <c r="Q19" s="214"/>
-      <c r="R19" s="214"/>
-      <c r="S19" s="214"/>
-      <c r="T19" s="214"/>
-      <c r="U19" s="214"/>
-      <c r="V19" s="214"/>
-      <c r="W19" s="214"/>
-      <c r="X19" s="214"/>
-      <c r="Y19" s="214"/>
-      <c r="Z19" s="214"/>
-      <c r="AA19" s="214"/>
-      <c r="AB19" s="214"/>
-      <c r="AC19" s="214"/>
-      <c r="AD19" s="214"/>
-      <c r="AE19" s="214"/>
-      <c r="AF19" s="214"/>
-      <c r="AG19" s="214"/>
-      <c r="AH19" s="214"/>
-      <c r="AI19" s="214"/>
-      <c r="AJ19" s="214"/>
+      <c r="M19" s="206"/>
+      <c r="N19" s="206"/>
+      <c r="O19" s="206"/>
+      <c r="P19" s="206"/>
+      <c r="Q19" s="206"/>
+      <c r="R19" s="206"/>
+      <c r="S19" s="206"/>
+      <c r="T19" s="206"/>
+      <c r="U19" s="206"/>
+      <c r="V19" s="206"/>
+      <c r="W19" s="206"/>
+      <c r="X19" s="206"/>
+      <c r="Y19" s="206"/>
+      <c r="Z19" s="206"/>
+      <c r="AA19" s="206"/>
+      <c r="AB19" s="206"/>
+      <c r="AC19" s="206"/>
+      <c r="AD19" s="206"/>
+      <c r="AE19" s="206"/>
+      <c r="AF19" s="206"/>
+      <c r="AG19" s="206"/>
+      <c r="AH19" s="206"/>
+      <c r="AI19" s="206"/>
+      <c r="AJ19" s="206"/>
       <c r="AK19" s="16"/>
       <c r="AL19" s="32"/>
       <c r="AM19" s="16"/>
@@ -10110,12 +10107,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="AN3:AQ3"/>
-    <mergeCell ref="AF3:AI3"/>
-    <mergeCell ref="L19:AJ19"/>
-    <mergeCell ref="P3:S3"/>
-    <mergeCell ref="T3:W3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="X3:AA3"/>
     <mergeCell ref="AV2:BG2"/>
@@ -10132,6 +10123,12 @@
     <mergeCell ref="D3:G3"/>
     <mergeCell ref="H3:K3"/>
     <mergeCell ref="L3:O3"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="AN3:AQ3"/>
+    <mergeCell ref="AF3:AI3"/>
+    <mergeCell ref="L19:AJ19"/>
+    <mergeCell ref="P3:S3"/>
+    <mergeCell ref="T3:W3"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="C3:C4">
@@ -11147,7 +11144,7 @@
       </c>
       <c r="D14" s="74">
         <f>VLOOKUP($B$2,'TH NV'!$A$5:$BG$18,N14,0)</f>
-        <v>0.80079999999999996</v>
+        <v>0.83250000000000002</v>
       </c>
       <c r="E14" s="49" t="e">
         <f>VLOOKUP($B$2,'TH NV'!$A$1:$BG$18,70,0)</f>
@@ -11170,7 +11167,7 @@
       </c>
       <c r="J14" s="65">
         <f t="shared" si="2"/>
-        <v>0.16920000000000002</v>
+        <v>0.13749999999999996</v>
       </c>
       <c r="K14" s="222"/>
       <c r="L14" s="114" t="s">
@@ -11351,42 +11348,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:59" s="1" customFormat="1" ht="24.75" x14ac:dyDescent="0.45">
-      <c r="D1" s="211" t="s">
+      <c r="D1" s="216" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="211"/>
-      <c r="F1" s="211"/>
-      <c r="G1" s="211"/>
-      <c r="H1" s="211"/>
-      <c r="I1" s="211"/>
-      <c r="J1" s="211"/>
-      <c r="K1" s="211"/>
-      <c r="L1" s="211"/>
-      <c r="M1" s="211"/>
-      <c r="N1" s="211"/>
-      <c r="O1" s="211"/>
-      <c r="P1" s="211"/>
-      <c r="Q1" s="211"/>
-      <c r="R1" s="211"/>
-      <c r="S1" s="211"/>
-      <c r="T1" s="206" t="s">
+      <c r="E1" s="216"/>
+      <c r="F1" s="216"/>
+      <c r="G1" s="216"/>
+      <c r="H1" s="216"/>
+      <c r="I1" s="216"/>
+      <c r="J1" s="216"/>
+      <c r="K1" s="216"/>
+      <c r="L1" s="216"/>
+      <c r="M1" s="216"/>
+      <c r="N1" s="216"/>
+      <c r="O1" s="216"/>
+      <c r="P1" s="216"/>
+      <c r="Q1" s="216"/>
+      <c r="R1" s="216"/>
+      <c r="S1" s="216"/>
+      <c r="T1" s="214" t="s">
         <v>36</v>
       </c>
-      <c r="U1" s="206"/>
-      <c r="V1" s="206"/>
-      <c r="W1" s="206"/>
-      <c r="X1" s="206"/>
-      <c r="Y1" s="206"/>
-      <c r="Z1" s="206"/>
-      <c r="AA1" s="206"/>
-      <c r="AB1" s="206"/>
-      <c r="AC1" s="206"/>
-      <c r="AD1" s="206"/>
-      <c r="AE1" s="206"/>
-      <c r="AF1" s="206"/>
-      <c r="AG1" s="206"/>
-      <c r="AH1" s="206"/>
-      <c r="AI1" s="206"/>
+      <c r="U1" s="214"/>
+      <c r="V1" s="214"/>
+      <c r="W1" s="214"/>
+      <c r="X1" s="214"/>
+      <c r="Y1" s="214"/>
+      <c r="Z1" s="214"/>
+      <c r="AA1" s="214"/>
+      <c r="AB1" s="214"/>
+      <c r="AC1" s="214"/>
+      <c r="AD1" s="214"/>
+      <c r="AE1" s="214"/>
+      <c r="AF1" s="214"/>
+      <c r="AG1" s="214"/>
+      <c r="AH1" s="214"/>
+      <c r="AI1" s="214"/>
       <c r="AJ1" s="234" t="s">
         <v>37</v>
       </c>
@@ -11419,90 +11416,90 @@
     <row r="2" spans="1:59" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="202" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="203"/>
-      <c r="F2" s="203"/>
-      <c r="G2" s="203"/>
-      <c r="H2" s="202" t="s">
+      <c r="D2" s="204" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="205"/>
+      <c r="F2" s="205"/>
+      <c r="G2" s="205"/>
+      <c r="H2" s="204" t="s">
         <v>40</v>
       </c>
-      <c r="I2" s="203"/>
-      <c r="J2" s="203"/>
-      <c r="K2" s="203"/>
-      <c r="L2" s="202" t="s">
+      <c r="I2" s="205"/>
+      <c r="J2" s="205"/>
+      <c r="K2" s="205"/>
+      <c r="L2" s="204" t="s">
         <v>41</v>
       </c>
-      <c r="M2" s="203"/>
-      <c r="N2" s="203"/>
-      <c r="O2" s="203"/>
-      <c r="P2" s="215" t="s">
+      <c r="M2" s="205"/>
+      <c r="N2" s="205"/>
+      <c r="O2" s="205"/>
+      <c r="P2" s="207" t="s">
         <v>42</v>
       </c>
-      <c r="Q2" s="216"/>
-      <c r="R2" s="216"/>
-      <c r="S2" s="217"/>
-      <c r="T2" s="202" t="s">
+      <c r="Q2" s="208"/>
+      <c r="R2" s="208"/>
+      <c r="S2" s="209"/>
+      <c r="T2" s="204" t="s">
         <v>43</v>
       </c>
-      <c r="U2" s="203"/>
-      <c r="V2" s="203"/>
-      <c r="W2" s="203"/>
-      <c r="X2" s="202" t="s">
+      <c r="U2" s="205"/>
+      <c r="V2" s="205"/>
+      <c r="W2" s="205"/>
+      <c r="X2" s="204" t="s">
         <v>45</v>
       </c>
-      <c r="Y2" s="203"/>
-      <c r="Z2" s="203"/>
-      <c r="AA2" s="203"/>
-      <c r="AB2" s="202" t="s">
+      <c r="Y2" s="205"/>
+      <c r="Z2" s="205"/>
+      <c r="AA2" s="205"/>
+      <c r="AB2" s="204" t="s">
         <v>47</v>
       </c>
-      <c r="AC2" s="203"/>
-      <c r="AD2" s="203"/>
-      <c r="AE2" s="203"/>
-      <c r="AF2" s="202" t="s">
+      <c r="AC2" s="205"/>
+      <c r="AD2" s="205"/>
+      <c r="AE2" s="205"/>
+      <c r="AF2" s="204" t="s">
         <v>48</v>
       </c>
-      <c r="AG2" s="203"/>
-      <c r="AH2" s="203"/>
-      <c r="AI2" s="203"/>
-      <c r="AJ2" s="208" t="s">
+      <c r="AG2" s="205"/>
+      <c r="AH2" s="205"/>
+      <c r="AI2" s="205"/>
+      <c r="AJ2" s="201" t="s">
         <v>51</v>
       </c>
-      <c r="AK2" s="209"/>
-      <c r="AL2" s="209"/>
-      <c r="AM2" s="210"/>
-      <c r="AN2" s="208" t="s">
+      <c r="AK2" s="202"/>
+      <c r="AL2" s="202"/>
+      <c r="AM2" s="203"/>
+      <c r="AN2" s="201" t="s">
         <v>14</v>
       </c>
-      <c r="AO2" s="209"/>
-      <c r="AP2" s="209"/>
-      <c r="AQ2" s="210"/>
-      <c r="AR2" s="208" t="s">
+      <c r="AO2" s="202"/>
+      <c r="AP2" s="202"/>
+      <c r="AQ2" s="203"/>
+      <c r="AR2" s="201" t="s">
         <v>52</v>
       </c>
-      <c r="AS2" s="209"/>
-      <c r="AT2" s="209"/>
-      <c r="AU2" s="210"/>
-      <c r="AV2" s="203" t="s">
+      <c r="AS2" s="202"/>
+      <c r="AT2" s="202"/>
+      <c r="AU2" s="203"/>
+      <c r="AV2" s="205" t="s">
         <v>16</v>
       </c>
-      <c r="AW2" s="203"/>
-      <c r="AX2" s="203"/>
-      <c r="AY2" s="203"/>
-      <c r="AZ2" s="203" t="s">
+      <c r="AW2" s="205"/>
+      <c r="AX2" s="205"/>
+      <c r="AY2" s="205"/>
+      <c r="AZ2" s="205" t="s">
         <v>54</v>
       </c>
-      <c r="BA2" s="203"/>
-      <c r="BB2" s="203"/>
-      <c r="BC2" s="203"/>
-      <c r="BD2" s="202" t="s">
+      <c r="BA2" s="205"/>
+      <c r="BB2" s="205"/>
+      <c r="BC2" s="205"/>
+      <c r="BD2" s="204" t="s">
         <v>55</v>
       </c>
-      <c r="BE2" s="203"/>
-      <c r="BF2" s="207"/>
-      <c r="BG2" s="203"/>
+      <c r="BE2" s="205"/>
+      <c r="BF2" s="215"/>
+      <c r="BG2" s="205"/>
     </row>
     <row r="3" spans="1:59" ht="15" x14ac:dyDescent="0.45">
       <c r="B3" s="8" t="s">
@@ -11855,7 +11852,7 @@
       </c>
       <c r="AS4" s="129">
         <f>(VLOOKUP(B4,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.80079999999999996</v>
+        <v>0.83250000000000002</v>
       </c>
       <c r="AT4" s="14">
         <f t="shared" ref="AT4" si="20">IF(AS4&lt;94.5%,0,IF(AS4&lt;95.54%,50%,IF(AS4&lt;AR4,80%,100%+(30%*(AS4-AR4)/3.39%))))</f>
@@ -11863,7 +11860,7 @@
       </c>
       <c r="AU4" s="54">
         <f t="shared" ref="AU4" si="21">AR4-AS4</f>
-        <v>0.16920000000000002</v>
+        <v>0.13749999999999996</v>
       </c>
       <c r="AV4" s="57">
         <f>VLOOKUP(A4,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -12089,7 +12086,7 @@
       </c>
       <c r="AS5" s="129">
         <f>(VLOOKUP(B5,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.71579999999999999</v>
+        <v>0.74230000000000007</v>
       </c>
       <c r="AT5" s="14">
         <f t="shared" ref="AT5:AT16" si="48">IF(AS5&lt;94.5%,0,IF(AS5&lt;95.54%,50%,IF(AS5&lt;AR5,80%,100%+(30%*(AS5-AR5)/3.39%))))</f>
@@ -12097,7 +12094,7 @@
       </c>
       <c r="AU5" s="54">
         <f t="shared" ref="AU5:AU16" si="49">AR5-AS5</f>
-        <v>0.25419999999999998</v>
+        <v>0.2276999999999999</v>
       </c>
       <c r="AV5" s="57">
         <f>VLOOKUP(A5,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -12323,7 +12320,7 @@
       </c>
       <c r="AS6" s="129">
         <f>(VLOOKUP(B6,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.69159999999999999</v>
+        <v>0.71950000000000003</v>
       </c>
       <c r="AT6" s="14">
         <f t="shared" si="48"/>
@@ -12331,7 +12328,7 @@
       </c>
       <c r="AU6" s="54">
         <f t="shared" si="49"/>
-        <v>0.27839999999999998</v>
+        <v>0.25049999999999994</v>
       </c>
       <c r="AV6" s="57">
         <f>VLOOKUP(A6,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -12557,7 +12554,7 @@
       </c>
       <c r="AS7" s="129">
         <f>(VLOOKUP(B7,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.66079999999999994</v>
+        <v>0.67670000000000008</v>
       </c>
       <c r="AT7" s="14">
         <f t="shared" si="48"/>
@@ -12565,7 +12562,7 @@
       </c>
       <c r="AU7" s="54">
         <f t="shared" si="49"/>
-        <v>0.30920000000000003</v>
+        <v>0.29329999999999989</v>
       </c>
       <c r="AV7" s="57">
         <f>VLOOKUP(A7,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -12791,7 +12788,7 @@
       </c>
       <c r="AS8" s="129">
         <f>(VLOOKUP(B8,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.7419</v>
+        <v>0.78260000000000007</v>
       </c>
       <c r="AT8" s="14">
         <f t="shared" si="48"/>
@@ -12799,7 +12796,7 @@
       </c>
       <c r="AU8" s="54">
         <f t="shared" si="49"/>
-        <v>0.22809999999999997</v>
+        <v>0.1873999999999999</v>
       </c>
       <c r="AV8" s="57">
         <f>VLOOKUP(A8,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -13086,7 +13083,7 @@
       </c>
       <c r="AS10" s="129">
         <f>(VLOOKUP(B10,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.71310000000000007</v>
+        <v>0.75790000000000013</v>
       </c>
       <c r="AT10" s="14">
         <f t="shared" si="48"/>
@@ -13094,7 +13091,7 @@
       </c>
       <c r="AU10" s="54">
         <f t="shared" si="49"/>
-        <v>0.25689999999999991</v>
+        <v>0.21209999999999984</v>
       </c>
       <c r="AV10" s="57">
         <f>VLOOKUP(A10,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -13320,7 +13317,7 @@
       </c>
       <c r="AS11" s="129">
         <f>(VLOOKUP(B11,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.76590000000000003</v>
+        <v>0.79480000000000006</v>
       </c>
       <c r="AT11" s="14">
         <f t="shared" si="48"/>
@@ -13328,7 +13325,7 @@
       </c>
       <c r="AU11" s="54">
         <f t="shared" si="49"/>
-        <v>0.20409999999999995</v>
+        <v>0.17519999999999991</v>
       </c>
       <c r="AV11" s="57">
         <f>VLOOKUP(A11,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -13554,7 +13551,7 @@
       </c>
       <c r="AS12" s="129">
         <f>(VLOOKUP(B12,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.64260000000000006</v>
+        <v>0.8034</v>
       </c>
       <c r="AT12" s="14">
         <f t="shared" si="48"/>
@@ -13562,7 +13559,7 @@
       </c>
       <c r="AU12" s="54">
         <f t="shared" si="49"/>
-        <v>0.32739999999999991</v>
+        <v>0.16659999999999997</v>
       </c>
       <c r="AV12" s="57">
         <f>VLOOKUP(A12,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -13788,7 +13785,7 @@
       </c>
       <c r="AS13" s="129">
         <f>(VLOOKUP(B13,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.7340000000000001</v>
+        <v>0.76080000000000003</v>
       </c>
       <c r="AT13" s="14">
         <f t="shared" si="48"/>
@@ -13796,7 +13793,7 @@
       </c>
       <c r="AU13" s="54">
         <f t="shared" si="49"/>
-        <v>0.23599999999999988</v>
+        <v>0.20919999999999994</v>
       </c>
       <c r="AV13" s="57">
         <f>VLOOKUP(A13,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -14022,7 +14019,7 @@
       </c>
       <c r="AS14" s="129">
         <f>(VLOOKUP(B14,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.79359999999999997</v>
+        <v>0.82000000000000006</v>
       </c>
       <c r="AT14" s="14">
         <f t="shared" si="48"/>
@@ -14030,7 +14027,7 @@
       </c>
       <c r="AU14" s="54">
         <f t="shared" si="49"/>
-        <v>0.1764</v>
+        <v>0.14999999999999991</v>
       </c>
       <c r="AV14" s="57">
         <f>VLOOKUP(A14,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -14256,7 +14253,7 @@
       </c>
       <c r="AS15" s="129">
         <f>(VLOOKUP(B15,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.6634000000000001</v>
+        <v>0.69000000000000006</v>
       </c>
       <c r="AT15" s="14">
         <f t="shared" si="48"/>
@@ -14264,7 +14261,7 @@
       </c>
       <c r="AU15" s="54">
         <f t="shared" si="49"/>
-        <v>0.30659999999999987</v>
+        <v>0.27999999999999992</v>
       </c>
       <c r="AV15" s="57">
         <f>VLOOKUP(A15,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -14490,7 +14487,7 @@
       </c>
       <c r="AS16" s="129">
         <f>(VLOOKUP(B16,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.77190000000000003</v>
+        <v>0.79709999999999992</v>
       </c>
       <c r="AT16" s="14">
         <f t="shared" si="48"/>
@@ -14498,7 +14495,7 @@
       </c>
       <c r="AU16" s="54">
         <f t="shared" si="49"/>
-        <v>0.19809999999999994</v>
+        <v>0.17290000000000005</v>
       </c>
       <c r="AV16" s="57">
         <f>VLOOKUP(A16,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -14582,11 +14579,11 @@
       </c>
       <c r="C19" s="142">
         <f ca="1">SUMIF(cuoc!A7:P27,'tiến độ'!A19,cuoc!M7:M27)</f>
-        <v>465017488</v>
+        <v>482839706</v>
       </c>
       <c r="D19" s="142">
         <f ca="1">B19*0.968-C19</f>
-        <v>158156583.25599992</v>
+        <v>140334365.25599992</v>
       </c>
       <c r="E19" s="137"/>
       <c r="H19" s="137"/>
@@ -14599,15 +14596,15 @@
       </c>
       <c r="B20" s="143">
         <f ca="1">SUMIF(cuoc!A8:P27,'tiến độ'!A20,cuoc!I8:I27)</f>
-        <v>975190007</v>
+        <v>1081173353</v>
       </c>
       <c r="C20" s="143">
         <f ca="1">SUMIF(cuoc!A8:P27,'tiến độ'!A20,cuoc!M8:M27)</f>
-        <v>721476778</v>
+        <v>835585327</v>
       </c>
       <c r="D20" s="142">
         <f ca="1">B20*0.968-C20</f>
-        <v>222507148.77600002</v>
+        <v>210990478.704</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.45">
@@ -14793,11 +14790,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="D1:S1"/>
-    <mergeCell ref="D2:G2"/>
-    <mergeCell ref="H2:K2"/>
-    <mergeCell ref="L2:O2"/>
-    <mergeCell ref="P2:S2"/>
     <mergeCell ref="X2:AA2"/>
     <mergeCell ref="AB2:AE2"/>
     <mergeCell ref="AF2:AI2"/>
@@ -14811,6 +14803,11 @@
     <mergeCell ref="AJ2:AM2"/>
     <mergeCell ref="AN2:AQ2"/>
     <mergeCell ref="T2:W2"/>
+    <mergeCell ref="D1:S1"/>
+    <mergeCell ref="D2:G2"/>
+    <mergeCell ref="H2:K2"/>
+    <mergeCell ref="L2:O2"/>
+    <mergeCell ref="P2:S2"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="F4:F16">
@@ -23286,12 +23283,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="X5:AE5"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="H5:O5"/>
-    <mergeCell ref="P5:W5"/>
     <mergeCell ref="CB5:CI5"/>
     <mergeCell ref="CJ5:CQ5"/>
     <mergeCell ref="CR5:CY5"/>
@@ -23302,6 +23293,12 @@
     <mergeCell ref="BD5:BK5"/>
     <mergeCell ref="BL5:BS5"/>
     <mergeCell ref="BT5:CA5"/>
+    <mergeCell ref="X5:AE5"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="H5:O5"/>
+    <mergeCell ref="P5:W5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -23399,7 +23396,7 @@
       <c r="A3" s="100" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="243" t="s">
+      <c r="B3" s="245" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="101" t="s">
@@ -23411,70 +23408,70 @@
       <c r="E3" s="247" t="s">
         <v>202</v>
       </c>
-      <c r="F3" s="245" t="s">
+      <c r="F3" s="243" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="245" t="s">
+      <c r="G3" s="243" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="245" t="s">
+      <c r="H3" s="243" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="245" t="s">
+      <c r="I3" s="243" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="245" t="s">
+      <c r="J3" s="243" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="245" t="s">
+      <c r="K3" s="243" t="s">
         <v>11</v>
       </c>
-      <c r="L3" s="245" t="s">
+      <c r="L3" s="243" t="s">
         <v>12</v>
       </c>
-      <c r="M3" s="245" t="s">
+      <c r="M3" s="243" t="s">
         <v>203</v>
       </c>
-      <c r="N3" s="245" t="s">
+      <c r="N3" s="243" t="s">
         <v>286</v>
       </c>
-      <c r="O3" s="245" t="s">
+      <c r="O3" s="243" t="s">
         <v>14</v>
       </c>
-      <c r="P3" s="245" t="s">
+      <c r="P3" s="243" t="s">
         <v>15</v>
       </c>
-      <c r="Q3" s="245" t="s">
+      <c r="Q3" s="243" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="245" t="s">
+      <c r="R3" s="243" t="s">
         <v>17</v>
       </c>
-      <c r="S3" s="245" t="s">
+      <c r="S3" s="243" t="s">
         <v>18</v>
       </c>
       <c r="T3" s="99"/>
     </row>
     <row r="4" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="100"/>
-      <c r="B4" s="244"/>
+      <c r="B4" s="246"/>
       <c r="C4" s="101"/>
       <c r="D4" s="101"/>
       <c r="E4" s="248"/>
-      <c r="F4" s="246"/>
-      <c r="G4" s="246"/>
-      <c r="H4" s="246"/>
-      <c r="I4" s="246"/>
-      <c r="J4" s="246"/>
-      <c r="K4" s="246"/>
-      <c r="L4" s="246"/>
-      <c r="M4" s="246"/>
-      <c r="N4" s="246"/>
-      <c r="O4" s="246"/>
-      <c r="P4" s="246"/>
-      <c r="Q4" s="246"/>
-      <c r="R4" s="246"/>
-      <c r="S4" s="246"/>
+      <c r="F4" s="244"/>
+      <c r="G4" s="244"/>
+      <c r="H4" s="244"/>
+      <c r="I4" s="244"/>
+      <c r="J4" s="244"/>
+      <c r="K4" s="244"/>
+      <c r="L4" s="244"/>
+      <c r="M4" s="244"/>
+      <c r="N4" s="244"/>
+      <c r="O4" s="244"/>
+      <c r="P4" s="244"/>
+      <c r="Q4" s="244"/>
+      <c r="R4" s="244"/>
+      <c r="S4" s="244"/>
       <c r="T4" s="99"/>
     </row>
     <row r="5" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.45">
@@ -24792,12 +24789,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="S3:S4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="R3:R4"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="H3:H4"/>
@@ -24808,6 +24799,12 @@
     <mergeCell ref="K3:K4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="E3:E4"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="S3:S4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="R3:R4"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.69991251615088756" right="0.69991251615088756" top="0.74990626395218019" bottom="0.74990626395218019" header="0.29996251027415122" footer="0.29996251027415122"/>
@@ -26083,68 +26080,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:48" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="258" t="s">
+      <c r="A1" s="256" t="s">
         <v>240</v>
       </c>
-      <c r="B1" s="258"/>
-      <c r="C1" s="258"/>
-      <c r="D1" s="258"/>
-      <c r="E1" s="258"/>
-      <c r="F1" s="258"/>
-      <c r="G1" s="258"/>
-      <c r="H1" s="258"/>
-      <c r="I1" s="258"/>
-      <c r="J1" s="258"/>
-      <c r="K1" s="258"/>
-      <c r="M1" s="261" t="s">
+      <c r="B1" s="256"/>
+      <c r="C1" s="256"/>
+      <c r="D1" s="256"/>
+      <c r="E1" s="256"/>
+      <c r="F1" s="256"/>
+      <c r="G1" s="256"/>
+      <c r="H1" s="256"/>
+      <c r="I1" s="256"/>
+      <c r="J1" s="256"/>
+      <c r="K1" s="256"/>
+      <c r="M1" s="259" t="s">
         <v>241</v>
       </c>
-      <c r="N1" s="261"/>
-      <c r="O1" s="261"/>
-      <c r="P1" s="261"/>
-      <c r="Q1" s="261"/>
-      <c r="R1" s="261"/>
-      <c r="S1" s="261"/>
-      <c r="T1" s="261"/>
-      <c r="U1" s="261"/>
-      <c r="V1" s="261"/>
-      <c r="W1" s="261"/>
-      <c r="X1" s="261"/>
-      <c r="Y1" s="261"/>
-      <c r="Z1" s="261"/>
+      <c r="N1" s="259"/>
+      <c r="O1" s="259"/>
+      <c r="P1" s="259"/>
+      <c r="Q1" s="259"/>
+      <c r="R1" s="259"/>
+      <c r="S1" s="259"/>
+      <c r="T1" s="259"/>
+      <c r="U1" s="259"/>
+      <c r="V1" s="259"/>
+      <c r="W1" s="259"/>
+      <c r="X1" s="259"/>
+      <c r="Y1" s="259"/>
+      <c r="Z1" s="259"/>
     </row>
     <row r="2" spans="1:48" ht="24.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="259"/>
-      <c r="B2" s="259"/>
-      <c r="C2" s="259"/>
-      <c r="D2" s="259"/>
-      <c r="E2" s="259"/>
-      <c r="F2" s="259"/>
-      <c r="G2" s="259"/>
-      <c r="H2" s="259"/>
-      <c r="I2" s="259"/>
-      <c r="J2" s="259"/>
-      <c r="K2" s="259"/>
-      <c r="M2" s="262"/>
-      <c r="N2" s="262"/>
-      <c r="O2" s="262"/>
-      <c r="P2" s="262"/>
-      <c r="Q2" s="262"/>
-      <c r="R2" s="262"/>
-      <c r="S2" s="262"/>
-      <c r="T2" s="262"/>
-      <c r="U2" s="262"/>
-      <c r="V2" s="262"/>
-      <c r="W2" s="262"/>
-      <c r="X2" s="262"/>
-      <c r="Y2" s="262"/>
-      <c r="Z2" s="262"/>
+      <c r="A2" s="257"/>
+      <c r="B2" s="257"/>
+      <c r="C2" s="257"/>
+      <c r="D2" s="257"/>
+      <c r="E2" s="257"/>
+      <c r="F2" s="257"/>
+      <c r="G2" s="257"/>
+      <c r="H2" s="257"/>
+      <c r="I2" s="257"/>
+      <c r="J2" s="257"/>
+      <c r="K2" s="257"/>
+      <c r="M2" s="260"/>
+      <c r="N2" s="260"/>
+      <c r="O2" s="260"/>
+      <c r="P2" s="260"/>
+      <c r="Q2" s="260"/>
+      <c r="R2" s="260"/>
+      <c r="S2" s="260"/>
+      <c r="T2" s="260"/>
+      <c r="U2" s="260"/>
+      <c r="V2" s="260"/>
+      <c r="W2" s="260"/>
+      <c r="X2" s="260"/>
+      <c r="Y2" s="260"/>
+      <c r="Z2" s="260"/>
     </row>
     <row r="3" spans="1:48" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="255" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="256" t="s">
+      <c r="A3" s="253" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="254" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="28" t="s">
@@ -26174,70 +26171,70 @@
       <c r="K3" s="28" t="s">
         <v>249</v>
       </c>
-      <c r="M3" s="260" t="s">
+      <c r="M3" s="258" t="s">
         <v>34</v>
       </c>
-      <c r="N3" s="202" t="s">
+      <c r="N3" s="204" t="s">
         <v>250</v>
       </c>
-      <c r="O3" s="203"/>
-      <c r="P3" s="203"/>
-      <c r="Q3" s="203"/>
-      <c r="R3" s="253" t="s">
+      <c r="O3" s="205"/>
+      <c r="P3" s="205"/>
+      <c r="Q3" s="205"/>
+      <c r="R3" s="261" t="s">
         <v>251</v>
       </c>
-      <c r="S3" s="202" t="s">
+      <c r="S3" s="204" t="s">
         <v>252</v>
       </c>
-      <c r="T3" s="203"/>
-      <c r="U3" s="203"/>
-      <c r="V3" s="203"/>
-      <c r="W3" s="253" t="s">
+      <c r="T3" s="205"/>
+      <c r="U3" s="205"/>
+      <c r="V3" s="205"/>
+      <c r="W3" s="261" t="s">
         <v>251</v>
       </c>
-      <c r="X3" s="215" t="s">
+      <c r="X3" s="207" t="s">
         <v>41</v>
       </c>
-      <c r="Y3" s="216"/>
-      <c r="Z3" s="216"/>
-      <c r="AA3" s="253" t="s">
+      <c r="Y3" s="208"/>
+      <c r="Z3" s="208"/>
+      <c r="AA3" s="261" t="s">
         <v>251</v>
       </c>
       <c r="AB3" s="71"/>
-      <c r="AC3" s="202" t="s">
+      <c r="AC3" s="204" t="s">
         <v>42</v>
       </c>
-      <c r="AD3" s="203"/>
-      <c r="AE3" s="203"/>
-      <c r="AF3" s="203"/>
-      <c r="AG3" s="202" t="s">
+      <c r="AD3" s="205"/>
+      <c r="AE3" s="205"/>
+      <c r="AF3" s="205"/>
+      <c r="AG3" s="204" t="s">
         <v>43</v>
       </c>
-      <c r="AH3" s="203"/>
-      <c r="AI3" s="203"/>
-      <c r="AJ3" s="203"/>
-      <c r="AK3" s="202" t="s">
+      <c r="AH3" s="205"/>
+      <c r="AI3" s="205"/>
+      <c r="AJ3" s="205"/>
+      <c r="AK3" s="204" t="s">
         <v>44</v>
       </c>
-      <c r="AL3" s="203"/>
-      <c r="AM3" s="203"/>
-      <c r="AN3" s="203"/>
-      <c r="AO3" s="202" t="s">
+      <c r="AL3" s="205"/>
+      <c r="AM3" s="205"/>
+      <c r="AN3" s="205"/>
+      <c r="AO3" s="204" t="s">
         <v>46</v>
       </c>
-      <c r="AP3" s="203"/>
-      <c r="AQ3" s="203"/>
-      <c r="AR3" s="203"/>
-      <c r="AS3" s="202" t="s">
+      <c r="AP3" s="205"/>
+      <c r="AQ3" s="205"/>
+      <c r="AR3" s="205"/>
+      <c r="AS3" s="204" t="s">
         <v>47</v>
       </c>
-      <c r="AT3" s="203"/>
-      <c r="AU3" s="203"/>
-      <c r="AV3" s="203"/>
+      <c r="AT3" s="205"/>
+      <c r="AU3" s="205"/>
+      <c r="AV3" s="205"/>
     </row>
     <row r="4" spans="1:48" ht="22.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="255"/>
-      <c r="B4" s="257"/>
+      <c r="A4" s="253"/>
+      <c r="B4" s="255"/>
       <c r="C4" s="24">
         <f t="shared" ref="C4:K4" si="0">SUM(C5:C19)</f>
         <v>15</v>
@@ -26274,7 +26271,7 @@
         <f t="shared" si="0"/>
         <v>134</v>
       </c>
-      <c r="M4" s="260"/>
+      <c r="M4" s="258"/>
       <c r="N4" s="8" t="s">
         <v>2</v>
       </c>
@@ -26287,7 +26284,7 @@
       <c r="Q4" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="R4" s="254"/>
+      <c r="R4" s="262"/>
       <c r="S4" s="8" t="s">
         <v>2</v>
       </c>
@@ -26300,7 +26297,7 @@
       <c r="V4" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="W4" s="254"/>
+      <c r="W4" s="262"/>
       <c r="X4" s="8" t="s">
         <v>2</v>
       </c>
@@ -26310,7 +26307,7 @@
       <c r="Z4" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="AA4" s="254"/>
+      <c r="AA4" s="262"/>
       <c r="AB4" s="51" t="s">
         <v>59</v>
       </c>
@@ -28699,12 +28696,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="A1:K2"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="N3:Q3"/>
-    <mergeCell ref="M1:Z2"/>
     <mergeCell ref="AS3:AV3"/>
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="W3:W4"/>
@@ -28715,6 +28706,12 @@
     <mergeCell ref="AK3:AN3"/>
     <mergeCell ref="AO3:AR3"/>
     <mergeCell ref="S3:V3"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="A1:K2"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="N3:Q3"/>
+    <mergeCell ref="M1:Z2"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="P5:P20">
@@ -28854,44 +28851,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="265"/>
-      <c r="B1" s="265"/>
-      <c r="C1" s="265"/>
-      <c r="D1" s="265"/>
-      <c r="E1" s="265"/>
-      <c r="F1" s="265"/>
-      <c r="G1" s="265"/>
-      <c r="H1" s="265"/>
-      <c r="I1" s="265"/>
-      <c r="J1" s="265"/>
-      <c r="K1" s="265"/>
-      <c r="L1" s="265"/>
-      <c r="M1" s="265"/>
-      <c r="N1" s="265"/>
-      <c r="O1" s="265"/>
-      <c r="P1" s="265"/>
+      <c r="A1" s="263"/>
+      <c r="B1" s="263"/>
+      <c r="C1" s="263"/>
+      <c r="D1" s="263"/>
+      <c r="E1" s="263"/>
+      <c r="F1" s="263"/>
+      <c r="G1" s="263"/>
+      <c r="H1" s="263"/>
+      <c r="I1" s="263"/>
+      <c r="J1" s="263"/>
+      <c r="K1" s="263"/>
+      <c r="L1" s="263"/>
+      <c r="M1" s="263"/>
+      <c r="N1" s="263"/>
+      <c r="O1" s="263"/>
+      <c r="P1" s="263"/>
     </row>
     <row r="2" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="266"/>
-      <c r="B2" s="266"/>
-      <c r="C2" s="266"/>
-      <c r="D2" s="266"/>
-      <c r="E2" s="266"/>
-      <c r="F2" s="266"/>
-      <c r="G2" s="266"/>
-      <c r="H2" s="266"/>
-      <c r="I2" s="266"/>
-      <c r="J2" s="266"/>
-      <c r="K2" s="266"/>
-      <c r="L2" s="266"/>
-      <c r="M2" s="266"/>
-      <c r="N2" s="266"/>
-      <c r="O2" s="266"/>
-      <c r="P2" s="266"/>
+      <c r="A2" s="264"/>
+      <c r="B2" s="264"/>
+      <c r="C2" s="264"/>
+      <c r="D2" s="264"/>
+      <c r="E2" s="264"/>
+      <c r="F2" s="264"/>
+      <c r="G2" s="264"/>
+      <c r="H2" s="264"/>
+      <c r="I2" s="264"/>
+      <c r="J2" s="264"/>
+      <c r="K2" s="264"/>
+      <c r="L2" s="264"/>
+      <c r="M2" s="264"/>
+      <c r="N2" s="264"/>
+      <c r="O2" s="264"/>
+      <c r="P2" s="264"/>
     </row>
     <row r="3" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="267"/>
-      <c r="B3" s="267"/>
+      <c r="A3" s="265"/>
+      <c r="B3" s="265"/>
       <c r="C3" s="133"/>
       <c r="D3" s="133"/>
       <c r="E3" s="133"/>
@@ -28908,10 +28905,10 @@
       <c r="P3" s="133"/>
     </row>
     <row r="4" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="269" t="s">
+      <c r="A4" s="267" t="s">
         <v>255</v>
       </c>
-      <c r="B4" s="269" t="s">
+      <c r="B4" s="267" t="s">
         <v>39</v>
       </c>
       <c r="C4" s="141"/>
@@ -28919,70 +28916,70 @@
       <c r="E4" s="141"/>
       <c r="F4" s="141"/>
       <c r="G4" s="141"/>
-      <c r="H4" s="268"/>
-      <c r="I4" s="268"/>
-      <c r="J4" s="268"/>
-      <c r="K4" s="268"/>
-      <c r="L4" s="268"/>
-      <c r="M4" s="268"/>
-      <c r="N4" s="268"/>
-      <c r="O4" s="268"/>
-      <c r="P4" s="268"/>
+      <c r="H4" s="266"/>
+      <c r="I4" s="266"/>
+      <c r="J4" s="266"/>
+      <c r="K4" s="266"/>
+      <c r="L4" s="266"/>
+      <c r="M4" s="266"/>
+      <c r="N4" s="266"/>
+      <c r="O4" s="266"/>
+      <c r="P4" s="266"/>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A5" s="272"/>
-      <c r="B5" s="272"/>
-      <c r="C5" s="269" t="s">
+      <c r="A5" s="270"/>
+      <c r="B5" s="270"/>
+      <c r="C5" s="267" t="s">
         <v>256</v>
       </c>
-      <c r="D5" s="269" t="s">
+      <c r="D5" s="267" t="s">
         <v>257</v>
       </c>
-      <c r="E5" s="270"/>
-      <c r="F5" s="269" t="s">
+      <c r="E5" s="268"/>
+      <c r="F5" s="267" t="s">
         <v>258</v>
       </c>
-      <c r="G5" s="270"/>
-      <c r="H5" s="269" t="s">
+      <c r="G5" s="268"/>
+      <c r="H5" s="267" t="s">
         <v>259</v>
       </c>
-      <c r="I5" s="270"/>
-      <c r="J5" s="269" t="s">
+      <c r="I5" s="268"/>
+      <c r="J5" s="267" t="s">
         <v>260</v>
       </c>
-      <c r="K5" s="270"/>
-      <c r="L5" s="273" t="s">
+      <c r="K5" s="268"/>
+      <c r="L5" s="271" t="s">
         <v>261</v>
       </c>
-      <c r="M5" s="270"/>
-      <c r="N5" s="268" t="s">
+      <c r="M5" s="268"/>
+      <c r="N5" s="266" t="s">
         <v>262</v>
       </c>
-      <c r="O5" s="274"/>
-      <c r="P5" s="269" t="s">
+      <c r="O5" s="272"/>
+      <c r="P5" s="267" t="s">
         <v>266</v>
       </c>
-      <c r="R5" s="263" t="s">
+      <c r="R5" s="273" t="s">
         <v>34</v>
       </c>
-      <c r="S5" s="263" t="s">
+      <c r="S5" s="273" t="s">
+        <v>289</v>
+      </c>
+      <c r="T5" s="273" t="s">
         <v>290</v>
       </c>
-      <c r="T5" s="263" t="s">
+      <c r="U5" s="273" t="s">
+        <v>292</v>
+      </c>
+      <c r="V5" s="274" t="s">
         <v>291</v>
-      </c>
-      <c r="U5" s="263" t="s">
-        <v>293</v>
-      </c>
-      <c r="V5" s="264" t="s">
-        <v>292</v>
       </c>
       <c r="W5" s="172"/>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A6" s="271"/>
-      <c r="B6" s="271"/>
-      <c r="C6" s="272"/>
+      <c r="A6" s="269"/>
+      <c r="B6" s="269"/>
+      <c r="C6" s="270"/>
       <c r="D6" s="134" t="s">
         <v>2</v>
       </c>
@@ -29019,29 +29016,29 @@
       <c r="O6" s="134" t="s">
         <v>263</v>
       </c>
-      <c r="P6" s="271"/>
-      <c r="R6" s="263"/>
-      <c r="S6" s="263"/>
-      <c r="T6" s="263"/>
-      <c r="U6" s="263"/>
-      <c r="V6" s="263"/>
+      <c r="P6" s="269"/>
+      <c r="R6" s="273"/>
+      <c r="S6" s="273"/>
+      <c r="T6" s="273"/>
+      <c r="U6" s="273"/>
+      <c r="V6" s="273"/>
       <c r="W6" s="172"/>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A7" s="190" t="s">
-        <v>288</v>
+        <v>179</v>
       </c>
       <c r="B7" s="190" t="s">
-        <v>68</v>
+        <v>101</v>
       </c>
       <c r="C7" s="190" t="s">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="D7" s="191">
-        <v>434</v>
+        <v>454</v>
       </c>
       <c r="E7" s="191">
-        <v>72573808</v>
+        <v>70243418</v>
       </c>
       <c r="F7" s="191">
         <v>0</v>
@@ -29050,32 +29047,32 @@
         <v>0</v>
       </c>
       <c r="H7" s="191">
-        <v>434</v>
+        <v>454</v>
       </c>
       <c r="I7" s="191">
-        <v>72573808</v>
+        <v>70243418</v>
       </c>
       <c r="J7" s="191">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="K7" s="191">
-        <v>904499</v>
+        <v>2938520</v>
       </c>
       <c r="L7" s="191">
-        <v>374</v>
+        <v>391</v>
       </c>
       <c r="M7" s="191">
-        <v>61172308</v>
+        <v>60467385</v>
       </c>
       <c r="N7" s="192">
-        <v>86.18</v>
+        <v>86.12</v>
       </c>
       <c r="O7" s="192">
-        <v>84.29</v>
+        <v>86.08</v>
       </c>
       <c r="P7" s="135">
         <f>I7*0.97-M7</f>
-        <v>9224285.7600000054</v>
+        <v>7668730.4599999934</v>
       </c>
       <c r="R7" s="173" t="s">
         <v>117</v>
@@ -29089,28 +29086,28 @@
       </c>
       <c r="U7" s="189">
         <f>VLOOKUP(R7,$C$7:$P$27,14,0)</f>
-        <v>23239489.799999997</v>
+        <v>19090002.799999997</v>
       </c>
       <c r="V7" s="175">
         <f>VLOOKUP(R7,$C$7:$P$27,14,0)-T7</f>
-        <v>0</v>
+        <v>-4149487</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A8" s="193" t="s">
-        <v>288</v>
+        <v>179</v>
       </c>
       <c r="B8" s="193" t="s">
-        <v>101</v>
+        <v>68</v>
       </c>
       <c r="C8" s="193" t="s">
-        <v>102</v>
+        <v>69</v>
       </c>
       <c r="D8" s="194">
-        <v>454</v>
+        <v>434</v>
       </c>
       <c r="E8" s="194">
-        <v>70243418</v>
+        <v>72573808</v>
       </c>
       <c r="F8" s="194">
         <v>0</v>
@@ -29119,32 +29116,32 @@
         <v>0</v>
       </c>
       <c r="H8" s="194">
-        <v>454</v>
+        <v>434</v>
       </c>
       <c r="I8" s="194">
-        <v>70243418</v>
+        <v>72573808</v>
       </c>
       <c r="J8" s="194">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="K8" s="194">
-        <v>772900</v>
+        <v>2181875</v>
       </c>
       <c r="L8" s="194">
-        <v>367</v>
+        <v>383</v>
       </c>
       <c r="M8" s="194">
-        <v>58301765</v>
+        <v>62449684</v>
       </c>
       <c r="N8" s="195">
-        <v>80.84</v>
+        <v>88.25</v>
       </c>
       <c r="O8" s="195">
-        <v>83</v>
+        <v>86.05</v>
       </c>
       <c r="P8" s="135">
         <f t="shared" ref="P8:P27" si="0">I8*0.97-M8</f>
-        <v>9834350.4599999934</v>
+        <v>7946909.7600000054</v>
       </c>
       <c r="R8" s="173" t="s">
         <v>67</v>
@@ -29158,11 +29155,11 @@
       </c>
       <c r="U8" s="189">
         <f t="shared" ref="U8:U17" si="2">VLOOKUP(R8,$C$7:$P$27,14,0)</f>
-        <v>24558081.310000002</v>
+        <v>19955680.310000002</v>
       </c>
       <c r="V8" s="175">
         <f t="shared" ref="V8:V17" si="3">VLOOKUP(R8,$C$7:$P$27,14,0)-T8</f>
-        <v>0</v>
+        <v>-4602401</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.45">
@@ -29194,26 +29191,26 @@
         <v>145101823</v>
       </c>
       <c r="J9" s="191">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="K9" s="191">
-        <v>1309959</v>
+        <v>5912360</v>
       </c>
       <c r="L9" s="191">
-        <v>683</v>
+        <v>718</v>
       </c>
       <c r="M9" s="191">
-        <v>116190687</v>
+        <v>120793088</v>
       </c>
       <c r="N9" s="192">
-        <v>77.97</v>
+        <v>81.96</v>
       </c>
       <c r="O9" s="192">
-        <v>80.08</v>
+        <v>83.25</v>
       </c>
       <c r="P9" s="135">
         <f t="shared" si="0"/>
-        <v>24558081.310000002</v>
+        <v>19955680.310000002</v>
       </c>
       <c r="R9" s="174" t="s">
         <v>87</v>
@@ -29227,28 +29224,28 @@
       </c>
       <c r="U9" s="189">
         <f t="shared" si="2"/>
-        <v>35959578.270000011</v>
+        <v>32219020.270000011</v>
       </c>
       <c r="V9" s="175">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-3740558</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A10" s="193" t="s">
-        <v>288</v>
+        <v>179</v>
       </c>
       <c r="B10" s="193" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="C10" s="193" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="D10" s="194">
-        <v>308</v>
+        <v>716</v>
       </c>
       <c r="E10" s="194">
-        <v>51982396</v>
+        <v>116427734</v>
       </c>
       <c r="F10" s="194">
         <v>0</v>
@@ -29257,32 +29254,32 @@
         <v>0</v>
       </c>
       <c r="H10" s="194">
-        <v>308</v>
+        <v>716</v>
       </c>
       <c r="I10" s="194">
-        <v>51982396</v>
+        <v>116427734</v>
       </c>
       <c r="J10" s="194">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="K10" s="194">
-        <v>1193885</v>
+        <v>6819495</v>
       </c>
       <c r="L10" s="194">
-        <v>243</v>
+        <v>576</v>
       </c>
       <c r="M10" s="194">
-        <v>41588724</v>
+        <v>96242471</v>
       </c>
       <c r="N10" s="195">
-        <v>78.900000000000006</v>
+        <v>80.45</v>
       </c>
       <c r="O10" s="195">
-        <v>80.010000000000005</v>
+        <v>82.66</v>
       </c>
       <c r="P10" s="135">
         <f t="shared" si="0"/>
-        <v>8834200.1199999973</v>
+        <v>16692430.980000004</v>
       </c>
       <c r="R10" s="174" t="s">
         <v>110</v>
@@ -29296,28 +29293,28 @@
       </c>
       <c r="U10" s="189">
         <f t="shared" si="2"/>
-        <v>46186242.859999985</v>
+        <v>43813145.859999985</v>
       </c>
       <c r="V10" s="175">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-2373097</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A11" s="190" t="s">
-        <v>129</v>
+        <v>179</v>
       </c>
       <c r="B11" s="190" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="C11" s="190" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="D11" s="191">
-        <v>1048</v>
+        <v>356</v>
       </c>
       <c r="E11" s="191">
-        <v>180440547</v>
+        <v>53605661</v>
       </c>
       <c r="F11" s="191">
         <v>0</v>
@@ -29326,32 +29323,32 @@
         <v>0</v>
       </c>
       <c r="H11" s="191">
-        <v>1048</v>
+        <v>356</v>
       </c>
       <c r="I11" s="191">
-        <v>180440547</v>
+        <v>53605661</v>
       </c>
       <c r="J11" s="191">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="K11" s="191">
-        <v>3091276</v>
+        <v>4547499</v>
       </c>
       <c r="L11" s="191">
-        <v>810</v>
+        <v>281</v>
       </c>
       <c r="M11" s="191">
-        <v>143191323</v>
+        <v>44127379</v>
       </c>
       <c r="N11" s="192">
-        <v>77.290000000000006</v>
+        <v>78.930000000000007</v>
       </c>
       <c r="O11" s="192">
-        <v>79.36</v>
+        <v>82.32</v>
       </c>
       <c r="P11" s="135">
         <f t="shared" si="0"/>
-        <v>31836007.590000004</v>
+        <v>7870112.1700000018</v>
       </c>
       <c r="R11" s="173" t="s">
         <v>99</v>
@@ -29365,16 +29362,16 @@
       </c>
       <c r="U11" s="189">
         <f t="shared" si="2"/>
-        <v>29500740.75</v>
+        <v>26544065.75</v>
       </c>
       <c r="V11" s="175">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-2956675</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A12" s="193" t="s">
-        <v>288</v>
+        <v>179</v>
       </c>
       <c r="B12" s="193" t="s">
         <v>114</v>
@@ -29401,26 +29398,26 @@
         <v>93597302</v>
       </c>
       <c r="J12" s="194">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K12" s="194">
-        <v>2122634</v>
+        <v>4817593</v>
       </c>
       <c r="L12" s="194">
-        <v>433</v>
+        <v>450</v>
       </c>
       <c r="M12" s="194">
-        <v>74173286</v>
+        <v>76868245</v>
       </c>
       <c r="N12" s="195">
-        <v>77.459999999999994</v>
+        <v>80.5</v>
       </c>
       <c r="O12" s="195">
-        <v>79.25</v>
+        <v>82.13</v>
       </c>
       <c r="P12" s="135">
         <f t="shared" si="0"/>
-        <v>16616096.939999998</v>
+        <v>13921137.939999998</v>
       </c>
       <c r="R12" s="173" t="s">
         <v>75</v>
@@ -29434,28 +29431,28 @@
       </c>
       <c r="U12" s="189">
         <f t="shared" si="2"/>
-        <v>31197103.520000011</v>
+        <v>26783206.520000011</v>
       </c>
       <c r="V12" s="175">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-4413897</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A13" s="190" t="s">
-        <v>288</v>
+        <v>129</v>
       </c>
       <c r="B13" s="190" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C13" s="190" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D13" s="191">
-        <v>716</v>
+        <v>1048</v>
       </c>
       <c r="E13" s="191">
-        <v>116427734</v>
+        <v>180440547</v>
       </c>
       <c r="F13" s="191">
         <v>0</v>
@@ -29464,32 +29461,32 @@
         <v>0</v>
       </c>
       <c r="H13" s="191">
-        <v>716</v>
+        <v>1048</v>
       </c>
       <c r="I13" s="191">
-        <v>116427734</v>
+        <v>180440547</v>
       </c>
       <c r="J13" s="191">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="K13" s="191">
-        <v>1371257</v>
+        <v>7863074</v>
       </c>
       <c r="L13" s="191">
-        <v>543</v>
+        <v>841</v>
       </c>
       <c r="M13" s="191">
-        <v>90794233</v>
+        <v>147963121</v>
       </c>
       <c r="N13" s="192">
-        <v>75.84</v>
+        <v>80.25</v>
       </c>
       <c r="O13" s="192">
-        <v>77.98</v>
+        <v>82</v>
       </c>
       <c r="P13" s="135">
         <f t="shared" si="0"/>
-        <v>22140668.980000004</v>
+        <v>27064209.590000004</v>
       </c>
       <c r="R13" s="173" t="s">
         <v>107</v>
@@ -29503,28 +29500,28 @@
       </c>
       <c r="U13" s="189">
         <f t="shared" si="2"/>
-        <v>31836007.590000004</v>
+        <v>27064209.590000004</v>
       </c>
       <c r="V13" s="175">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-4771798</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A14" s="193" t="s">
-        <v>129</v>
+        <v>179</v>
       </c>
       <c r="B14" s="193" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C14" s="193" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D14" s="194">
-        <v>1181</v>
+        <v>308</v>
       </c>
       <c r="E14" s="194">
-        <v>189656153</v>
+        <v>51982396</v>
       </c>
       <c r="F14" s="194">
         <v>0</v>
@@ -29533,32 +29530,32 @@
         <v>0</v>
       </c>
       <c r="H14" s="194">
-        <v>1181</v>
+        <v>308</v>
       </c>
       <c r="I14" s="194">
-        <v>189656153</v>
+        <v>51982396</v>
       </c>
       <c r="J14" s="194">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K14" s="194">
-        <v>1974868</v>
+        <v>2151835</v>
       </c>
       <c r="L14" s="194">
-        <v>894</v>
+        <v>249</v>
       </c>
       <c r="M14" s="194">
-        <v>146399537</v>
+        <v>42546674</v>
       </c>
       <c r="N14" s="195">
-        <v>75.7</v>
+        <v>80.84</v>
       </c>
       <c r="O14" s="195">
-        <v>77.19</v>
+        <v>81.849999999999994</v>
       </c>
       <c r="P14" s="135">
         <f t="shared" si="0"/>
-        <v>37566931.409999996</v>
+        <v>7876250.1199999973</v>
       </c>
       <c r="R14" s="174" t="s">
         <v>72</v>
@@ -29572,11 +29569,11 @@
       </c>
       <c r="U14" s="189">
         <f t="shared" si="2"/>
-        <v>41712909.199999988</v>
+        <v>34439517.199999988</v>
       </c>
       <c r="V14" s="175">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-7273392</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.45">
@@ -29584,16 +29581,16 @@
         <v>129</v>
       </c>
       <c r="B15" s="190" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C15" s="190" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D15" s="191">
-        <v>941</v>
+        <v>683</v>
       </c>
       <c r="E15" s="191">
-        <v>152862316</v>
+        <v>105983346</v>
       </c>
       <c r="F15" s="191">
         <v>0</v>
@@ -29602,32 +29599,32 @@
         <v>0</v>
       </c>
       <c r="H15" s="191">
-        <v>941</v>
+        <v>683</v>
       </c>
       <c r="I15" s="191">
-        <v>152862316</v>
+        <v>105983346</v>
       </c>
       <c r="J15" s="191">
-        <v>13</v>
+        <v>262</v>
       </c>
       <c r="K15" s="191">
-        <v>1340571</v>
+        <v>41299032</v>
       </c>
       <c r="L15" s="191">
-        <v>690</v>
+        <v>540</v>
       </c>
       <c r="M15" s="191">
-        <v>117079343</v>
+        <v>85142346</v>
       </c>
       <c r="N15" s="192">
-        <v>73.33</v>
+        <v>79.06</v>
       </c>
       <c r="O15" s="192">
-        <v>76.59</v>
+        <v>80.34</v>
       </c>
       <c r="P15" s="135">
         <f t="shared" si="0"/>
-        <v>31197103.520000011</v>
+        <v>17661499.61999999</v>
       </c>
       <c r="R15" s="174" t="s">
         <v>113</v>
@@ -29641,28 +29638,28 @@
       </c>
       <c r="U15" s="189">
         <f t="shared" si="2"/>
-        <v>59633806.400000006</v>
+        <v>54473782.400000006</v>
       </c>
       <c r="V15" s="175">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-5160024</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A16" s="193" t="s">
-        <v>288</v>
+        <v>129</v>
       </c>
       <c r="B16" s="193" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="C16" s="193" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="D16" s="194">
-        <v>356</v>
+        <v>1181</v>
       </c>
       <c r="E16" s="194">
-        <v>53605661</v>
+        <v>189656153</v>
       </c>
       <c r="F16" s="194">
         <v>0</v>
@@ -29671,32 +29668,32 @@
         <v>0</v>
       </c>
       <c r="H16" s="194">
-        <v>356</v>
+        <v>1181</v>
       </c>
       <c r="I16" s="194">
-        <v>53605661</v>
+        <v>189656153</v>
       </c>
       <c r="J16" s="194">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="K16" s="194">
-        <v>1297321</v>
+        <v>6757771</v>
       </c>
       <c r="L16" s="194">
-        <v>258</v>
+        <v>927</v>
       </c>
       <c r="M16" s="194">
-        <v>40877201</v>
+        <v>151182440</v>
       </c>
       <c r="N16" s="195">
-        <v>72.47</v>
+        <v>78.489999999999995</v>
       </c>
       <c r="O16" s="195">
-        <v>76.260000000000005</v>
+        <v>79.709999999999994</v>
       </c>
       <c r="P16" s="135">
         <f t="shared" si="0"/>
-        <v>11120290.170000002</v>
+        <v>32784028.409999996</v>
       </c>
       <c r="R16" s="174" t="s">
         <v>119</v>
@@ -29710,28 +29707,28 @@
       </c>
       <c r="U16" s="189">
         <f t="shared" si="2"/>
-        <v>37566931.409999996</v>
+        <v>32784028.409999996</v>
       </c>
       <c r="V16" s="175">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-4782903</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A17" s="190" t="s">
-        <v>288</v>
+        <v>129</v>
       </c>
       <c r="B17" s="190" t="s">
-        <v>120</v>
+        <v>74</v>
       </c>
       <c r="C17" s="190" t="s">
-        <v>121</v>
+        <v>75</v>
       </c>
       <c r="D17" s="191">
-        <v>415</v>
+        <v>941</v>
       </c>
       <c r="E17" s="191">
-        <v>66800107</v>
+        <v>152862316</v>
       </c>
       <c r="F17" s="191">
         <v>0</v>
@@ -29740,32 +29737,32 @@
         <v>0</v>
       </c>
       <c r="H17" s="191">
-        <v>415</v>
+        <v>941</v>
       </c>
       <c r="I17" s="191">
-        <v>66800107</v>
+        <v>152862316</v>
       </c>
       <c r="J17" s="191">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="K17" s="191">
-        <v>520496</v>
+        <v>5754468</v>
       </c>
       <c r="L17" s="191">
-        <v>297</v>
+        <v>717</v>
       </c>
       <c r="M17" s="191">
-        <v>49833081</v>
+        <v>121493240</v>
       </c>
       <c r="N17" s="192">
-        <v>71.569999999999993</v>
+        <v>76.2</v>
       </c>
       <c r="O17" s="192">
-        <v>74.599999999999994</v>
+        <v>79.48</v>
       </c>
       <c r="P17" s="135">
         <f t="shared" si="0"/>
-        <v>14963022.789999999</v>
+        <v>26783206.520000011</v>
       </c>
       <c r="R17" s="173" t="s">
         <v>84</v>
@@ -29779,11 +29776,11 @@
       </c>
       <c r="U17" s="189">
         <f t="shared" si="2"/>
-        <v>22510770.670000002</v>
+        <v>19946581.670000002</v>
       </c>
       <c r="V17" s="175">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-2564189</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.45">
@@ -29815,34 +29812,34 @@
         <v>101866340</v>
       </c>
       <c r="J18" s="194">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="K18" s="194">
-        <v>1554987</v>
+        <v>5704474</v>
       </c>
       <c r="L18" s="194">
-        <v>457</v>
+        <v>483</v>
       </c>
       <c r="M18" s="194">
-        <v>75570860</v>
+        <v>79720347</v>
       </c>
       <c r="N18" s="195">
-        <v>71.180000000000007</v>
+        <v>75.23</v>
       </c>
       <c r="O18" s="195">
-        <v>74.19</v>
+        <v>78.260000000000005</v>
       </c>
       <c r="P18" s="135">
         <f t="shared" si="0"/>
-        <v>23239489.799999997</v>
+        <v>19090002.799999997</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A19" s="190" t="s">
+        <v>179</v>
+      </c>
+      <c r="B19" s="190" t="s">
         <v>288</v>
-      </c>
-      <c r="B19" s="190" t="s">
-        <v>289</v>
       </c>
       <c r="C19" s="190" t="s">
         <v>284</v>
@@ -29866,43 +29863,43 @@
         <v>50351985</v>
       </c>
       <c r="J19" s="191">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="K19" s="191">
-        <v>92893</v>
+        <v>1966983</v>
       </c>
       <c r="L19" s="191">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="M19" s="191">
-        <v>37115091</v>
+        <v>38989181</v>
       </c>
       <c r="N19" s="192">
-        <v>71.069999999999993</v>
+        <v>75.16</v>
       </c>
       <c r="O19" s="192">
-        <v>73.709999999999994</v>
+        <v>77.430000000000007</v>
       </c>
       <c r="P19" s="135">
         <f t="shared" si="0"/>
-        <v>11726334.449999996</v>
+        <v>9852244.4499999955</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A20" s="193" t="s">
-        <v>129</v>
+        <v>179</v>
       </c>
       <c r="B20" s="193" t="s">
-        <v>83</v>
+        <v>120</v>
       </c>
       <c r="C20" s="193" t="s">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="D20" s="194">
-        <v>588</v>
+        <v>415</v>
       </c>
       <c r="E20" s="194">
-        <v>95369711</v>
+        <v>66800107</v>
       </c>
       <c r="F20" s="194">
         <v>0</v>
@@ -29911,49 +29908,49 @@
         <v>0</v>
       </c>
       <c r="H20" s="194">
-        <v>588</v>
+        <v>415</v>
       </c>
       <c r="I20" s="194">
-        <v>95369711</v>
+        <v>66800107</v>
       </c>
       <c r="J20" s="194">
-        <v>90</v>
+        <v>11</v>
       </c>
       <c r="K20" s="194">
-        <v>14156904</v>
+        <v>1720613</v>
       </c>
       <c r="L20" s="194">
-        <v>424</v>
+        <v>304</v>
       </c>
       <c r="M20" s="194">
-        <v>69997849</v>
+        <v>51033198</v>
       </c>
       <c r="N20" s="195">
-        <v>72.11</v>
+        <v>73.25</v>
       </c>
       <c r="O20" s="195">
-        <v>73.400000000000006</v>
+        <v>76.400000000000006</v>
       </c>
       <c r="P20" s="135">
         <f t="shared" si="0"/>
-        <v>22510770.670000002</v>
+        <v>13762905.789999999</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A21" s="190" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B21" s="190" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C21" s="190" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D21" s="191">
-        <v>853</v>
+        <v>588</v>
       </c>
       <c r="E21" s="191">
-        <v>141474291</v>
+        <v>95369711</v>
       </c>
       <c r="F21" s="191">
         <v>0</v>
@@ -29962,32 +29959,32 @@
         <v>0</v>
       </c>
       <c r="H21" s="191">
-        <v>853</v>
+        <v>588</v>
       </c>
       <c r="I21" s="191">
-        <v>141474291</v>
+        <v>95369711</v>
       </c>
       <c r="J21" s="191">
-        <v>14</v>
+        <v>107</v>
       </c>
       <c r="K21" s="191">
-        <v>2076460</v>
+        <v>16721093</v>
       </c>
       <c r="L21" s="191">
-        <v>605</v>
+        <v>441</v>
       </c>
       <c r="M21" s="191">
-        <v>101270484</v>
+        <v>72562038</v>
       </c>
       <c r="N21" s="192">
-        <v>70.930000000000007</v>
+        <v>75</v>
       </c>
       <c r="O21" s="192">
-        <v>71.58</v>
+        <v>76.08</v>
       </c>
       <c r="P21" s="135">
         <f t="shared" si="0"/>
-        <v>35959578.270000011</v>
+        <v>19946581.670000002</v>
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.45">
@@ -30019,26 +30016,26 @@
         <v>162344260</v>
       </c>
       <c r="J22" s="194">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="K22" s="194">
-        <v>2204794</v>
+        <v>9478186</v>
       </c>
       <c r="L22" s="194">
-        <v>679</v>
+        <v>726</v>
       </c>
       <c r="M22" s="194">
-        <v>115761023</v>
+        <v>123034415</v>
       </c>
       <c r="N22" s="195">
-        <v>70.14</v>
+        <v>75</v>
       </c>
       <c r="O22" s="195">
-        <v>71.31</v>
+        <v>75.790000000000006</v>
       </c>
       <c r="P22" s="135">
         <f t="shared" si="0"/>
-        <v>41712909.199999988</v>
+        <v>34439517.199999988</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.45">
@@ -30046,16 +30043,16 @@
         <v>128</v>
       </c>
       <c r="B23" s="190" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="C23" s="190" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="D23" s="191">
-        <v>687</v>
+        <v>853</v>
       </c>
       <c r="E23" s="191">
-        <v>105953075</v>
+        <v>141474291</v>
       </c>
       <c r="F23" s="191">
         <v>0</v>
@@ -30064,49 +30061,49 @@
         <v>0</v>
       </c>
       <c r="H23" s="191">
-        <v>687</v>
+        <v>853</v>
       </c>
       <c r="I23" s="191">
-        <v>105953075</v>
+        <v>141474291</v>
       </c>
       <c r="J23" s="191">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="K23" s="191">
-        <v>1927281</v>
+        <v>5817018</v>
       </c>
       <c r="L23" s="191">
-        <v>465</v>
+        <v>632</v>
       </c>
       <c r="M23" s="191">
-        <v>73273742</v>
+        <v>105011042</v>
       </c>
       <c r="N23" s="192">
-        <v>67.69</v>
+        <v>74.09</v>
       </c>
       <c r="O23" s="192">
-        <v>69.16</v>
+        <v>74.23</v>
       </c>
       <c r="P23" s="135">
         <f t="shared" si="0"/>
-        <v>29500740.75</v>
+        <v>32219020.270000011</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A24" s="193" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B24" s="193" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="C24" s="193" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="D24" s="194">
-        <v>1198</v>
+        <v>687</v>
       </c>
       <c r="E24" s="194">
-        <v>194517020</v>
+        <v>105953075</v>
       </c>
       <c r="F24" s="194">
         <v>0</v>
@@ -30115,49 +30112,49 @@
         <v>0</v>
       </c>
       <c r="H24" s="194">
-        <v>1198</v>
+        <v>687</v>
       </c>
       <c r="I24" s="194">
-        <v>194517020</v>
+        <v>105953075</v>
       </c>
       <c r="J24" s="194">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="K24" s="194">
-        <v>3003675</v>
+        <v>4883956</v>
       </c>
       <c r="L24" s="194">
-        <v>775</v>
+        <v>483</v>
       </c>
       <c r="M24" s="194">
-        <v>129047703</v>
+        <v>76230417</v>
       </c>
       <c r="N24" s="195">
-        <v>64.69</v>
+        <v>70.31</v>
       </c>
       <c r="O24" s="195">
-        <v>66.34</v>
+        <v>71.95</v>
       </c>
       <c r="P24" s="135">
         <f t="shared" si="0"/>
-        <v>59633806.400000006</v>
+        <v>26544065.75</v>
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A25" s="190" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B25" s="190" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C25" s="190" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D25" s="191">
-        <v>892</v>
+        <v>1198</v>
       </c>
       <c r="E25" s="191">
-        <v>149379338</v>
+        <v>194517020</v>
       </c>
       <c r="F25" s="191">
         <v>0</v>
@@ -30166,49 +30163,49 @@
         <v>0</v>
       </c>
       <c r="H25" s="191">
-        <v>892</v>
+        <v>1198</v>
       </c>
       <c r="I25" s="191">
-        <v>149379338</v>
+        <v>194517020</v>
       </c>
       <c r="J25" s="191">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="K25" s="191">
-        <v>8404845</v>
+        <v>8163699</v>
       </c>
       <c r="L25" s="191">
-        <v>597</v>
+        <v>815</v>
       </c>
       <c r="M25" s="191">
-        <v>98711715</v>
+        <v>134207727</v>
       </c>
       <c r="N25" s="192">
-        <v>66.930000000000007</v>
+        <v>68.03</v>
       </c>
       <c r="O25" s="192">
-        <v>66.08</v>
+        <v>69</v>
       </c>
       <c r="P25" s="135">
         <f t="shared" si="0"/>
-        <v>46186242.859999985</v>
+        <v>54473782.400000006</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A26" s="193" t="s">
-        <v>288</v>
+        <v>128</v>
       </c>
       <c r="B26" s="193" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="C26" s="193" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="D26" s="194">
-        <v>683</v>
+        <v>892</v>
       </c>
       <c r="E26" s="194">
-        <v>105983346</v>
+        <v>149379338</v>
       </c>
       <c r="F26" s="194">
         <v>0</v>
@@ -30217,37 +30214,37 @@
         <v>0</v>
       </c>
       <c r="H26" s="194">
-        <v>683</v>
+        <v>892</v>
       </c>
       <c r="I26" s="194">
-        <v>105983346</v>
+        <v>149379338</v>
       </c>
       <c r="J26" s="194">
-        <v>164</v>
+        <v>65</v>
       </c>
       <c r="K26" s="194">
-        <v>24260428</v>
+        <v>10777942</v>
       </c>
       <c r="L26" s="194">
-        <v>442</v>
+        <v>612</v>
       </c>
       <c r="M26" s="194">
-        <v>68103742</v>
+        <v>101084812</v>
       </c>
       <c r="N26" s="195">
-        <v>64.709999999999994</v>
+        <v>68.61</v>
       </c>
       <c r="O26" s="195">
-        <v>64.260000000000005</v>
+        <v>67.67</v>
       </c>
       <c r="P26" s="135">
         <f t="shared" si="0"/>
-        <v>34700103.61999999</v>
+        <v>43813145.859999985</v>
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A27" s="190" t="s">
-        <v>288</v>
+        <v>179</v>
       </c>
       <c r="B27" s="190" t="s">
         <v>80</v>
@@ -30274,30 +30271,35 @@
         <v>89879995</v>
       </c>
       <c r="J27" s="191">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="K27" s="191">
-        <v>1305214</v>
+        <v>3418858</v>
       </c>
       <c r="L27" s="191">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="M27" s="191">
-        <v>57422374</v>
+        <v>59536018</v>
       </c>
       <c r="N27" s="192">
-        <v>62.09</v>
+        <v>64.650000000000006</v>
       </c>
       <c r="O27" s="192">
-        <v>63.89</v>
+        <v>66.239999999999995</v>
       </c>
       <c r="P27" s="135">
         <f t="shared" si="0"/>
-        <v>29761221.149999991</v>
+        <v>27647577.149999991</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="U5:U6"/>
+    <mergeCell ref="V5:V6"/>
+    <mergeCell ref="R5:R6"/>
+    <mergeCell ref="S5:S6"/>
+    <mergeCell ref="T5:T6"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
     <mergeCell ref="A3:B3"/>
@@ -30312,11 +30314,6 @@
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="L5:M5"/>
     <mergeCell ref="N5:O5"/>
-    <mergeCell ref="U5:U6"/>
-    <mergeCell ref="V5:V6"/>
-    <mergeCell ref="R5:R6"/>
-    <mergeCell ref="S5:S6"/>
-    <mergeCell ref="T5:T6"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="P7:P27">

--- a/filetiendo.xlsx
+++ b/filetiendo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\viettel 2026\thang 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBCF3737-3657-4695-8DA6-265985A38845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C12DA01-4A61-4BDC-BA41-CCBB98C93814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="808" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="808" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TH NV" sheetId="2" r:id="rId1"/>
@@ -4553,41 +4553,17 @@
     <xf numFmtId="0" fontId="66" fillId="0" borderId="109" xfId="11" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="109" xfId="11" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="177" xfId="11" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="50" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="135" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="134" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="133" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="50" fillId="5" borderId="127" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="5" borderId="130" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="128" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="140" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="139" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="138" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="5" borderId="127" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="24" borderId="132" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4601,10 +4577,34 @@
     <xf numFmtId="0" fontId="17" fillId="5" borderId="129" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="135" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="134" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="133" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="16" borderId="136" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="2" borderId="137" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="140" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="139" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="138" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="67" fillId="18" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4676,16 +4676,16 @@
     <xf numFmtId="0" fontId="63" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="47" fillId="5" borderId="152" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="5" borderId="151" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="148" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="147" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="5" borderId="152" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="5" borderId="151" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="51" fillId="5" borderId="150" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4705,6 +4705,12 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="155" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="158" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="157" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="159" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4730,10 +4736,10 @@
     <xf numFmtId="0" fontId="55" fillId="0" borderId="164" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="158" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="69" fillId="29" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="157" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="69" fillId="29" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="45" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4758,12 +4764,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="168" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="69" fillId="29" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="29" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="12">
     <cellStyle name="Comma" xfId="8" builtinId="3"/>
@@ -5653,166 +5653,166 @@
       </c>
     </row>
     <row r="2" spans="1:675" ht="23.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="210" t="s">
+      <c r="A2" s="200" t="s">
         <v>34</v>
       </c>
       <c r="B2" s="86"/>
       <c r="C2" s="15"/>
-      <c r="D2" s="216" t="s">
+      <c r="D2" s="211" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="216"/>
-      <c r="F2" s="216"/>
-      <c r="G2" s="216"/>
-      <c r="H2" s="216"/>
-      <c r="I2" s="216"/>
-      <c r="J2" s="216"/>
-      <c r="K2" s="216"/>
-      <c r="L2" s="216"/>
-      <c r="M2" s="216"/>
-      <c r="N2" s="216"/>
-      <c r="O2" s="216"/>
-      <c r="P2" s="216"/>
-      <c r="Q2" s="216"/>
-      <c r="R2" s="216"/>
-      <c r="S2" s="216"/>
-      <c r="T2" s="214" t="s">
+      <c r="E2" s="211"/>
+      <c r="F2" s="211"/>
+      <c r="G2" s="211"/>
+      <c r="H2" s="211"/>
+      <c r="I2" s="211"/>
+      <c r="J2" s="211"/>
+      <c r="K2" s="211"/>
+      <c r="L2" s="211"/>
+      <c r="M2" s="211"/>
+      <c r="N2" s="211"/>
+      <c r="O2" s="211"/>
+      <c r="P2" s="211"/>
+      <c r="Q2" s="211"/>
+      <c r="R2" s="211"/>
+      <c r="S2" s="211"/>
+      <c r="T2" s="206" t="s">
         <v>36</v>
       </c>
-      <c r="U2" s="214"/>
-      <c r="V2" s="214"/>
-      <c r="W2" s="214"/>
-      <c r="X2" s="214"/>
-      <c r="Y2" s="214"/>
-      <c r="Z2" s="214"/>
-      <c r="AA2" s="214"/>
-      <c r="AB2" s="214"/>
-      <c r="AC2" s="214"/>
-      <c r="AD2" s="214"/>
-      <c r="AE2" s="214"/>
-      <c r="AF2" s="214"/>
-      <c r="AG2" s="214"/>
-      <c r="AH2" s="214"/>
-      <c r="AI2" s="214"/>
-      <c r="AJ2" s="213" t="s">
+      <c r="U2" s="206"/>
+      <c r="V2" s="206"/>
+      <c r="W2" s="206"/>
+      <c r="X2" s="206"/>
+      <c r="Y2" s="206"/>
+      <c r="Z2" s="206"/>
+      <c r="AA2" s="206"/>
+      <c r="AB2" s="206"/>
+      <c r="AC2" s="206"/>
+      <c r="AD2" s="206"/>
+      <c r="AE2" s="206"/>
+      <c r="AF2" s="206"/>
+      <c r="AG2" s="206"/>
+      <c r="AH2" s="206"/>
+      <c r="AI2" s="206"/>
+      <c r="AJ2" s="205" t="s">
         <v>37</v>
       </c>
-      <c r="AK2" s="213"/>
-      <c r="AL2" s="213"/>
-      <c r="AM2" s="213"/>
-      <c r="AN2" s="213"/>
-      <c r="AO2" s="213"/>
-      <c r="AP2" s="213"/>
-      <c r="AQ2" s="213"/>
-      <c r="AR2" s="213"/>
-      <c r="AS2" s="213"/>
-      <c r="AT2" s="213"/>
-      <c r="AU2" s="213"/>
-      <c r="AV2" s="212" t="s">
+      <c r="AK2" s="205"/>
+      <c r="AL2" s="205"/>
+      <c r="AM2" s="205"/>
+      <c r="AN2" s="205"/>
+      <c r="AO2" s="205"/>
+      <c r="AP2" s="205"/>
+      <c r="AQ2" s="205"/>
+      <c r="AR2" s="205"/>
+      <c r="AS2" s="205"/>
+      <c r="AT2" s="205"/>
+      <c r="AU2" s="205"/>
+      <c r="AV2" s="204" t="s">
         <v>38</v>
       </c>
-      <c r="AW2" s="212"/>
-      <c r="AX2" s="212"/>
-      <c r="AY2" s="212"/>
-      <c r="AZ2" s="212"/>
-      <c r="BA2" s="212"/>
-      <c r="BB2" s="212"/>
-      <c r="BC2" s="212"/>
-      <c r="BD2" s="212"/>
-      <c r="BE2" s="212"/>
-      <c r="BF2" s="212"/>
-      <c r="BG2" s="212"/>
+      <c r="AW2" s="204"/>
+      <c r="AX2" s="204"/>
+      <c r="AY2" s="204"/>
+      <c r="AZ2" s="204"/>
+      <c r="BA2" s="204"/>
+      <c r="BB2" s="204"/>
+      <c r="BC2" s="204"/>
+      <c r="BD2" s="204"/>
+      <c r="BE2" s="204"/>
+      <c r="BF2" s="204"/>
+      <c r="BG2" s="204"/>
     </row>
     <row r="3" spans="1:675" s="3" customFormat="1" ht="28.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="210"/>
-      <c r="B3" s="217" t="s">
+      <c r="A3" s="200"/>
+      <c r="B3" s="212" t="s">
         <v>39</v>
       </c>
       <c r="C3" s="87"/>
-      <c r="D3" s="204" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="205"/>
-      <c r="F3" s="205"/>
-      <c r="G3" s="205"/>
-      <c r="H3" s="204" t="s">
+      <c r="D3" s="202" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="203"/>
+      <c r="F3" s="203"/>
+      <c r="G3" s="203"/>
+      <c r="H3" s="202" t="s">
         <v>40</v>
       </c>
-      <c r="I3" s="205"/>
-      <c r="J3" s="205"/>
-      <c r="K3" s="205"/>
-      <c r="L3" s="204" t="s">
+      <c r="I3" s="203"/>
+      <c r="J3" s="203"/>
+      <c r="K3" s="203"/>
+      <c r="L3" s="202" t="s">
         <v>41</v>
       </c>
-      <c r="M3" s="205"/>
-      <c r="N3" s="205"/>
-      <c r="O3" s="205"/>
-      <c r="P3" s="207" t="s">
+      <c r="M3" s="203"/>
+      <c r="N3" s="203"/>
+      <c r="O3" s="203"/>
+      <c r="P3" s="215" t="s">
         <v>42</v>
       </c>
-      <c r="Q3" s="208"/>
-      <c r="R3" s="208"/>
-      <c r="S3" s="209"/>
-      <c r="T3" s="204" t="s">
+      <c r="Q3" s="216"/>
+      <c r="R3" s="216"/>
+      <c r="S3" s="217"/>
+      <c r="T3" s="202" t="s">
         <v>43</v>
       </c>
-      <c r="U3" s="205"/>
-      <c r="V3" s="205"/>
-      <c r="W3" s="205"/>
-      <c r="X3" s="204" t="s">
+      <c r="U3" s="203"/>
+      <c r="V3" s="203"/>
+      <c r="W3" s="203"/>
+      <c r="X3" s="202" t="s">
         <v>45</v>
       </c>
-      <c r="Y3" s="205"/>
-      <c r="Z3" s="205"/>
-      <c r="AA3" s="205"/>
-      <c r="AB3" s="204" t="s">
+      <c r="Y3" s="203"/>
+      <c r="Z3" s="203"/>
+      <c r="AA3" s="203"/>
+      <c r="AB3" s="202" t="s">
         <v>47</v>
       </c>
-      <c r="AC3" s="205"/>
-      <c r="AD3" s="205"/>
-      <c r="AE3" s="205"/>
-      <c r="AF3" s="204" t="s">
+      <c r="AC3" s="203"/>
+      <c r="AD3" s="203"/>
+      <c r="AE3" s="203"/>
+      <c r="AF3" s="202" t="s">
         <v>48</v>
       </c>
-      <c r="AG3" s="205"/>
-      <c r="AH3" s="205"/>
-      <c r="AI3" s="205"/>
-      <c r="AJ3" s="201" t="s">
+      <c r="AG3" s="203"/>
+      <c r="AH3" s="203"/>
+      <c r="AI3" s="203"/>
+      <c r="AJ3" s="208" t="s">
         <v>51</v>
       </c>
-      <c r="AK3" s="202"/>
-      <c r="AL3" s="202"/>
-      <c r="AM3" s="203"/>
-      <c r="AN3" s="201" t="s">
+      <c r="AK3" s="209"/>
+      <c r="AL3" s="209"/>
+      <c r="AM3" s="210"/>
+      <c r="AN3" s="208" t="s">
         <v>14</v>
       </c>
-      <c r="AO3" s="202"/>
-      <c r="AP3" s="202"/>
-      <c r="AQ3" s="203"/>
-      <c r="AR3" s="201" t="s">
+      <c r="AO3" s="209"/>
+      <c r="AP3" s="209"/>
+      <c r="AQ3" s="210"/>
+      <c r="AR3" s="208" t="s">
         <v>52</v>
       </c>
-      <c r="AS3" s="202"/>
-      <c r="AT3" s="202"/>
-      <c r="AU3" s="203"/>
-      <c r="AV3" s="205" t="s">
+      <c r="AS3" s="209"/>
+      <c r="AT3" s="209"/>
+      <c r="AU3" s="210"/>
+      <c r="AV3" s="203" t="s">
         <v>16</v>
       </c>
-      <c r="AW3" s="205"/>
-      <c r="AX3" s="205"/>
-      <c r="AY3" s="205"/>
-      <c r="AZ3" s="205" t="s">
+      <c r="AW3" s="203"/>
+      <c r="AX3" s="203"/>
+      <c r="AY3" s="203"/>
+      <c r="AZ3" s="203" t="s">
         <v>54</v>
       </c>
-      <c r="BA3" s="205"/>
-      <c r="BB3" s="205"/>
-      <c r="BC3" s="205"/>
-      <c r="BD3" s="204" t="s">
+      <c r="BA3" s="203"/>
+      <c r="BB3" s="203"/>
+      <c r="BC3" s="203"/>
+      <c r="BD3" s="202" t="s">
         <v>55</v>
       </c>
-      <c r="BE3" s="205"/>
-      <c r="BF3" s="215"/>
-      <c r="BG3" s="205"/>
+      <c r="BE3" s="203"/>
+      <c r="BF3" s="207"/>
+      <c r="BG3" s="203"/>
       <c r="BH3" s="2"/>
       <c r="BI3" s="2"/>
       <c r="BJ3" s="2"/>
@@ -6431,8 +6431,8 @@
       <c r="YY3" s="2"/>
     </row>
     <row r="4" spans="1:675" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="211"/>
-      <c r="B4" s="217"/>
+      <c r="A4" s="201"/>
+      <c r="B4" s="212"/>
       <c r="C4" s="88"/>
       <c r="D4" s="8" t="s">
         <v>2</v>
@@ -9309,15 +9309,15 @@
         <v>4</v>
       </c>
       <c r="AK16" s="13">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AL16" s="14">
         <f t="shared" si="16"/>
-        <v>-0.5</v>
+        <v>1</v>
       </c>
       <c r="AM16" s="67">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN16" s="57">
         <f>VLOOKUP(C16,'Giao CT'!$D$6:$S$20,12,0)</f>
@@ -9871,11 +9871,11 @@
       <c r="C19" s="15"/>
       <c r="D19" s="15"/>
       <c r="E19" s="16"/>
-      <c r="F19" s="200">
+      <c r="F19" s="213">
         <f ca="1">TODAY()</f>
         <v>46077</v>
       </c>
-      <c r="G19" s="200"/>
+      <c r="G19" s="213"/>
       <c r="H19" s="90"/>
       <c r="I19" s="91">
         <f ca="1">DAY(F19)</f>
@@ -9888,33 +9888,33 @@
         <f ca="1">I19/J19</f>
         <v>0.77419354838709675</v>
       </c>
-      <c r="L19" s="206" t="s">
+      <c r="L19" s="214" t="s">
         <v>124</v>
       </c>
-      <c r="M19" s="206"/>
-      <c r="N19" s="206"/>
-      <c r="O19" s="206"/>
-      <c r="P19" s="206"/>
-      <c r="Q19" s="206"/>
-      <c r="R19" s="206"/>
-      <c r="S19" s="206"/>
-      <c r="T19" s="206"/>
-      <c r="U19" s="206"/>
-      <c r="V19" s="206"/>
-      <c r="W19" s="206"/>
-      <c r="X19" s="206"/>
-      <c r="Y19" s="206"/>
-      <c r="Z19" s="206"/>
-      <c r="AA19" s="206"/>
-      <c r="AB19" s="206"/>
-      <c r="AC19" s="206"/>
-      <c r="AD19" s="206"/>
-      <c r="AE19" s="206"/>
-      <c r="AF19" s="206"/>
-      <c r="AG19" s="206"/>
-      <c r="AH19" s="206"/>
-      <c r="AI19" s="206"/>
-      <c r="AJ19" s="206"/>
+      <c r="M19" s="214"/>
+      <c r="N19" s="214"/>
+      <c r="O19" s="214"/>
+      <c r="P19" s="214"/>
+      <c r="Q19" s="214"/>
+      <c r="R19" s="214"/>
+      <c r="S19" s="214"/>
+      <c r="T19" s="214"/>
+      <c r="U19" s="214"/>
+      <c r="V19" s="214"/>
+      <c r="W19" s="214"/>
+      <c r="X19" s="214"/>
+      <c r="Y19" s="214"/>
+      <c r="Z19" s="214"/>
+      <c r="AA19" s="214"/>
+      <c r="AB19" s="214"/>
+      <c r="AC19" s="214"/>
+      <c r="AD19" s="214"/>
+      <c r="AE19" s="214"/>
+      <c r="AF19" s="214"/>
+      <c r="AG19" s="214"/>
+      <c r="AH19" s="214"/>
+      <c r="AI19" s="214"/>
+      <c r="AJ19" s="214"/>
       <c r="AK19" s="16"/>
       <c r="AL19" s="32"/>
       <c r="AM19" s="16"/>
@@ -10107,6 +10107,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="AN3:AQ3"/>
+    <mergeCell ref="AF3:AI3"/>
+    <mergeCell ref="L19:AJ19"/>
+    <mergeCell ref="P3:S3"/>
+    <mergeCell ref="T3:W3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="X3:AA3"/>
     <mergeCell ref="AV2:BG2"/>
@@ -10123,12 +10129,6 @@
     <mergeCell ref="D3:G3"/>
     <mergeCell ref="H3:K3"/>
     <mergeCell ref="L3:O3"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="AN3:AQ3"/>
-    <mergeCell ref="AF3:AI3"/>
-    <mergeCell ref="L19:AJ19"/>
-    <mergeCell ref="P3:S3"/>
-    <mergeCell ref="T3:W3"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="C3:C4">
@@ -11348,42 +11348,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:59" s="1" customFormat="1" ht="24.75" x14ac:dyDescent="0.45">
-      <c r="D1" s="216" t="s">
+      <c r="D1" s="211" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="216"/>
-      <c r="F1" s="216"/>
-      <c r="G1" s="216"/>
-      <c r="H1" s="216"/>
-      <c r="I1" s="216"/>
-      <c r="J1" s="216"/>
-      <c r="K1" s="216"/>
-      <c r="L1" s="216"/>
-      <c r="M1" s="216"/>
-      <c r="N1" s="216"/>
-      <c r="O1" s="216"/>
-      <c r="P1" s="216"/>
-      <c r="Q1" s="216"/>
-      <c r="R1" s="216"/>
-      <c r="S1" s="216"/>
-      <c r="T1" s="214" t="s">
+      <c r="E1" s="211"/>
+      <c r="F1" s="211"/>
+      <c r="G1" s="211"/>
+      <c r="H1" s="211"/>
+      <c r="I1" s="211"/>
+      <c r="J1" s="211"/>
+      <c r="K1" s="211"/>
+      <c r="L1" s="211"/>
+      <c r="M1" s="211"/>
+      <c r="N1" s="211"/>
+      <c r="O1" s="211"/>
+      <c r="P1" s="211"/>
+      <c r="Q1" s="211"/>
+      <c r="R1" s="211"/>
+      <c r="S1" s="211"/>
+      <c r="T1" s="206" t="s">
         <v>36</v>
       </c>
-      <c r="U1" s="214"/>
-      <c r="V1" s="214"/>
-      <c r="W1" s="214"/>
-      <c r="X1" s="214"/>
-      <c r="Y1" s="214"/>
-      <c r="Z1" s="214"/>
-      <c r="AA1" s="214"/>
-      <c r="AB1" s="214"/>
-      <c r="AC1" s="214"/>
-      <c r="AD1" s="214"/>
-      <c r="AE1" s="214"/>
-      <c r="AF1" s="214"/>
-      <c r="AG1" s="214"/>
-      <c r="AH1" s="214"/>
-      <c r="AI1" s="214"/>
+      <c r="U1" s="206"/>
+      <c r="V1" s="206"/>
+      <c r="W1" s="206"/>
+      <c r="X1" s="206"/>
+      <c r="Y1" s="206"/>
+      <c r="Z1" s="206"/>
+      <c r="AA1" s="206"/>
+      <c r="AB1" s="206"/>
+      <c r="AC1" s="206"/>
+      <c r="AD1" s="206"/>
+      <c r="AE1" s="206"/>
+      <c r="AF1" s="206"/>
+      <c r="AG1" s="206"/>
+      <c r="AH1" s="206"/>
+      <c r="AI1" s="206"/>
       <c r="AJ1" s="234" t="s">
         <v>37</v>
       </c>
@@ -11416,90 +11416,90 @@
     <row r="2" spans="1:59" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="204" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="205"/>
-      <c r="F2" s="205"/>
-      <c r="G2" s="205"/>
-      <c r="H2" s="204" t="s">
+      <c r="D2" s="202" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="203"/>
+      <c r="F2" s="203"/>
+      <c r="G2" s="203"/>
+      <c r="H2" s="202" t="s">
         <v>40</v>
       </c>
-      <c r="I2" s="205"/>
-      <c r="J2" s="205"/>
-      <c r="K2" s="205"/>
-      <c r="L2" s="204" t="s">
+      <c r="I2" s="203"/>
+      <c r="J2" s="203"/>
+      <c r="K2" s="203"/>
+      <c r="L2" s="202" t="s">
         <v>41</v>
       </c>
-      <c r="M2" s="205"/>
-      <c r="N2" s="205"/>
-      <c r="O2" s="205"/>
-      <c r="P2" s="207" t="s">
+      <c r="M2" s="203"/>
+      <c r="N2" s="203"/>
+      <c r="O2" s="203"/>
+      <c r="P2" s="215" t="s">
         <v>42</v>
       </c>
-      <c r="Q2" s="208"/>
-      <c r="R2" s="208"/>
-      <c r="S2" s="209"/>
-      <c r="T2" s="204" t="s">
+      <c r="Q2" s="216"/>
+      <c r="R2" s="216"/>
+      <c r="S2" s="217"/>
+      <c r="T2" s="202" t="s">
         <v>43</v>
       </c>
-      <c r="U2" s="205"/>
-      <c r="V2" s="205"/>
-      <c r="W2" s="205"/>
-      <c r="X2" s="204" t="s">
+      <c r="U2" s="203"/>
+      <c r="V2" s="203"/>
+      <c r="W2" s="203"/>
+      <c r="X2" s="202" t="s">
         <v>45</v>
       </c>
-      <c r="Y2" s="205"/>
-      <c r="Z2" s="205"/>
-      <c r="AA2" s="205"/>
-      <c r="AB2" s="204" t="s">
+      <c r="Y2" s="203"/>
+      <c r="Z2" s="203"/>
+      <c r="AA2" s="203"/>
+      <c r="AB2" s="202" t="s">
         <v>47</v>
       </c>
-      <c r="AC2" s="205"/>
-      <c r="AD2" s="205"/>
-      <c r="AE2" s="205"/>
-      <c r="AF2" s="204" t="s">
+      <c r="AC2" s="203"/>
+      <c r="AD2" s="203"/>
+      <c r="AE2" s="203"/>
+      <c r="AF2" s="202" t="s">
         <v>48</v>
       </c>
-      <c r="AG2" s="205"/>
-      <c r="AH2" s="205"/>
-      <c r="AI2" s="205"/>
-      <c r="AJ2" s="201" t="s">
+      <c r="AG2" s="203"/>
+      <c r="AH2" s="203"/>
+      <c r="AI2" s="203"/>
+      <c r="AJ2" s="208" t="s">
         <v>51</v>
       </c>
-      <c r="AK2" s="202"/>
-      <c r="AL2" s="202"/>
-      <c r="AM2" s="203"/>
-      <c r="AN2" s="201" t="s">
+      <c r="AK2" s="209"/>
+      <c r="AL2" s="209"/>
+      <c r="AM2" s="210"/>
+      <c r="AN2" s="208" t="s">
         <v>14</v>
       </c>
-      <c r="AO2" s="202"/>
-      <c r="AP2" s="202"/>
-      <c r="AQ2" s="203"/>
-      <c r="AR2" s="201" t="s">
+      <c r="AO2" s="209"/>
+      <c r="AP2" s="209"/>
+      <c r="AQ2" s="210"/>
+      <c r="AR2" s="208" t="s">
         <v>52</v>
       </c>
-      <c r="AS2" s="202"/>
-      <c r="AT2" s="202"/>
-      <c r="AU2" s="203"/>
-      <c r="AV2" s="205" t="s">
+      <c r="AS2" s="209"/>
+      <c r="AT2" s="209"/>
+      <c r="AU2" s="210"/>
+      <c r="AV2" s="203" t="s">
         <v>16</v>
       </c>
-      <c r="AW2" s="205"/>
-      <c r="AX2" s="205"/>
-      <c r="AY2" s="205"/>
-      <c r="AZ2" s="205" t="s">
+      <c r="AW2" s="203"/>
+      <c r="AX2" s="203"/>
+      <c r="AY2" s="203"/>
+      <c r="AZ2" s="203" t="s">
         <v>54</v>
       </c>
-      <c r="BA2" s="205"/>
-      <c r="BB2" s="205"/>
-      <c r="BC2" s="205"/>
-      <c r="BD2" s="204" t="s">
+      <c r="BA2" s="203"/>
+      <c r="BB2" s="203"/>
+      <c r="BC2" s="203"/>
+      <c r="BD2" s="202" t="s">
         <v>55</v>
       </c>
-      <c r="BE2" s="205"/>
-      <c r="BF2" s="215"/>
-      <c r="BG2" s="205"/>
+      <c r="BE2" s="203"/>
+      <c r="BF2" s="207"/>
+      <c r="BG2" s="203"/>
     </row>
     <row r="3" spans="1:59" ht="15" x14ac:dyDescent="0.45">
       <c r="B3" s="8" t="s">
@@ -12757,15 +12757,15 @@
       </c>
       <c r="AK8" s="13">
         <f>VLOOKUP(B8,'TH NV'!$B$5:$BG$18,36,0)</f>
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AL8" s="14">
         <f t="shared" si="44"/>
-        <v>-0.5</v>
+        <v>1</v>
       </c>
       <c r="AM8" s="67">
         <f t="shared" si="45"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN8" s="57">
         <f>VLOOKUP(A8,'Giao CT'!$D$6:$S$20,12,0)</f>
@@ -14790,6 +14790,11 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="D1:S1"/>
+    <mergeCell ref="D2:G2"/>
+    <mergeCell ref="H2:K2"/>
+    <mergeCell ref="L2:O2"/>
+    <mergeCell ref="P2:S2"/>
     <mergeCell ref="X2:AA2"/>
     <mergeCell ref="AB2:AE2"/>
     <mergeCell ref="AF2:AI2"/>
@@ -14803,11 +14808,6 @@
     <mergeCell ref="AJ2:AM2"/>
     <mergeCell ref="AN2:AQ2"/>
     <mergeCell ref="T2:W2"/>
-    <mergeCell ref="D1:S1"/>
-    <mergeCell ref="D2:G2"/>
-    <mergeCell ref="H2:K2"/>
-    <mergeCell ref="L2:O2"/>
-    <mergeCell ref="P2:S2"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="F4:F16">
@@ -23283,6 +23283,12 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="X5:AE5"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="H5:O5"/>
+    <mergeCell ref="P5:W5"/>
     <mergeCell ref="CB5:CI5"/>
     <mergeCell ref="CJ5:CQ5"/>
     <mergeCell ref="CR5:CY5"/>
@@ -23293,12 +23299,6 @@
     <mergeCell ref="BD5:BK5"/>
     <mergeCell ref="BL5:BS5"/>
     <mergeCell ref="BT5:CA5"/>
-    <mergeCell ref="X5:AE5"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="H5:O5"/>
-    <mergeCell ref="P5:W5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -23396,7 +23396,7 @@
       <c r="A3" s="100" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="245" t="s">
+      <c r="B3" s="243" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="101" t="s">
@@ -23408,70 +23408,70 @@
       <c r="E3" s="247" t="s">
         <v>202</v>
       </c>
-      <c r="F3" s="243" t="s">
+      <c r="F3" s="245" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="243" t="s">
+      <c r="G3" s="245" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="243" t="s">
+      <c r="H3" s="245" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="243" t="s">
+      <c r="I3" s="245" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="243" t="s">
+      <c r="J3" s="245" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="243" t="s">
+      <c r="K3" s="245" t="s">
         <v>11</v>
       </c>
-      <c r="L3" s="243" t="s">
+      <c r="L3" s="245" t="s">
         <v>12</v>
       </c>
-      <c r="M3" s="243" t="s">
+      <c r="M3" s="245" t="s">
         <v>203</v>
       </c>
-      <c r="N3" s="243" t="s">
+      <c r="N3" s="245" t="s">
         <v>286</v>
       </c>
-      <c r="O3" s="243" t="s">
+      <c r="O3" s="245" t="s">
         <v>14</v>
       </c>
-      <c r="P3" s="243" t="s">
+      <c r="P3" s="245" t="s">
         <v>15</v>
       </c>
-      <c r="Q3" s="243" t="s">
+      <c r="Q3" s="245" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="243" t="s">
+      <c r="R3" s="245" t="s">
         <v>17</v>
       </c>
-      <c r="S3" s="243" t="s">
+      <c r="S3" s="245" t="s">
         <v>18</v>
       </c>
       <c r="T3" s="99"/>
     </row>
     <row r="4" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="100"/>
-      <c r="B4" s="246"/>
+      <c r="B4" s="244"/>
       <c r="C4" s="101"/>
       <c r="D4" s="101"/>
       <c r="E4" s="248"/>
-      <c r="F4" s="244"/>
-      <c r="G4" s="244"/>
-      <c r="H4" s="244"/>
-      <c r="I4" s="244"/>
-      <c r="J4" s="244"/>
-      <c r="K4" s="244"/>
-      <c r="L4" s="244"/>
-      <c r="M4" s="244"/>
-      <c r="N4" s="244"/>
-      <c r="O4" s="244"/>
-      <c r="P4" s="244"/>
-      <c r="Q4" s="244"/>
-      <c r="R4" s="244"/>
-      <c r="S4" s="244"/>
+      <c r="F4" s="246"/>
+      <c r="G4" s="246"/>
+      <c r="H4" s="246"/>
+      <c r="I4" s="246"/>
+      <c r="J4" s="246"/>
+      <c r="K4" s="246"/>
+      <c r="L4" s="246"/>
+      <c r="M4" s="246"/>
+      <c r="N4" s="246"/>
+      <c r="O4" s="246"/>
+      <c r="P4" s="246"/>
+      <c r="Q4" s="246"/>
+      <c r="R4" s="246"/>
+      <c r="S4" s="246"/>
       <c r="T4" s="99"/>
     </row>
     <row r="5" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.45">
@@ -24789,6 +24789,12 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="S3:S4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="R3:R4"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="H3:H4"/>
@@ -24799,12 +24805,6 @@
     <mergeCell ref="K3:K4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="E3:E4"/>
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="S3:S4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="R3:R4"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.69991251615088756" right="0.69991251615088756" top="0.74990626395218019" bottom="0.74990626395218019" header="0.29996251027415122" footer="0.29996251027415122"/>
@@ -26080,68 +26080,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:48" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="256" t="s">
+      <c r="A1" s="258" t="s">
         <v>240</v>
       </c>
-      <c r="B1" s="256"/>
-      <c r="C1" s="256"/>
-      <c r="D1" s="256"/>
-      <c r="E1" s="256"/>
-      <c r="F1" s="256"/>
-      <c r="G1" s="256"/>
-      <c r="H1" s="256"/>
-      <c r="I1" s="256"/>
-      <c r="J1" s="256"/>
-      <c r="K1" s="256"/>
-      <c r="M1" s="259" t="s">
+      <c r="B1" s="258"/>
+      <c r="C1" s="258"/>
+      <c r="D1" s="258"/>
+      <c r="E1" s="258"/>
+      <c r="F1" s="258"/>
+      <c r="G1" s="258"/>
+      <c r="H1" s="258"/>
+      <c r="I1" s="258"/>
+      <c r="J1" s="258"/>
+      <c r="K1" s="258"/>
+      <c r="M1" s="261" t="s">
         <v>241</v>
       </c>
-      <c r="N1" s="259"/>
-      <c r="O1" s="259"/>
-      <c r="P1" s="259"/>
-      <c r="Q1" s="259"/>
-      <c r="R1" s="259"/>
-      <c r="S1" s="259"/>
-      <c r="T1" s="259"/>
-      <c r="U1" s="259"/>
-      <c r="V1" s="259"/>
-      <c r="W1" s="259"/>
-      <c r="X1" s="259"/>
-      <c r="Y1" s="259"/>
-      <c r="Z1" s="259"/>
+      <c r="N1" s="261"/>
+      <c r="O1" s="261"/>
+      <c r="P1" s="261"/>
+      <c r="Q1" s="261"/>
+      <c r="R1" s="261"/>
+      <c r="S1" s="261"/>
+      <c r="T1" s="261"/>
+      <c r="U1" s="261"/>
+      <c r="V1" s="261"/>
+      <c r="W1" s="261"/>
+      <c r="X1" s="261"/>
+      <c r="Y1" s="261"/>
+      <c r="Z1" s="261"/>
     </row>
     <row r="2" spans="1:48" ht="24.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="257"/>
-      <c r="B2" s="257"/>
-      <c r="C2" s="257"/>
-      <c r="D2" s="257"/>
-      <c r="E2" s="257"/>
-      <c r="F2" s="257"/>
-      <c r="G2" s="257"/>
-      <c r="H2" s="257"/>
-      <c r="I2" s="257"/>
-      <c r="J2" s="257"/>
-      <c r="K2" s="257"/>
-      <c r="M2" s="260"/>
-      <c r="N2" s="260"/>
-      <c r="O2" s="260"/>
-      <c r="P2" s="260"/>
-      <c r="Q2" s="260"/>
-      <c r="R2" s="260"/>
-      <c r="S2" s="260"/>
-      <c r="T2" s="260"/>
-      <c r="U2" s="260"/>
-      <c r="V2" s="260"/>
-      <c r="W2" s="260"/>
-      <c r="X2" s="260"/>
-      <c r="Y2" s="260"/>
-      <c r="Z2" s="260"/>
+      <c r="A2" s="259"/>
+      <c r="B2" s="259"/>
+      <c r="C2" s="259"/>
+      <c r="D2" s="259"/>
+      <c r="E2" s="259"/>
+      <c r="F2" s="259"/>
+      <c r="G2" s="259"/>
+      <c r="H2" s="259"/>
+      <c r="I2" s="259"/>
+      <c r="J2" s="259"/>
+      <c r="K2" s="259"/>
+      <c r="M2" s="262"/>
+      <c r="N2" s="262"/>
+      <c r="O2" s="262"/>
+      <c r="P2" s="262"/>
+      <c r="Q2" s="262"/>
+      <c r="R2" s="262"/>
+      <c r="S2" s="262"/>
+      <c r="T2" s="262"/>
+      <c r="U2" s="262"/>
+      <c r="V2" s="262"/>
+      <c r="W2" s="262"/>
+      <c r="X2" s="262"/>
+      <c r="Y2" s="262"/>
+      <c r="Z2" s="262"/>
     </row>
     <row r="3" spans="1:48" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="253" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="254" t="s">
+      <c r="A3" s="255" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="256" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="28" t="s">
@@ -26171,70 +26171,70 @@
       <c r="K3" s="28" t="s">
         <v>249</v>
       </c>
-      <c r="M3" s="258" t="s">
+      <c r="M3" s="260" t="s">
         <v>34</v>
       </c>
-      <c r="N3" s="204" t="s">
+      <c r="N3" s="202" t="s">
         <v>250</v>
       </c>
-      <c r="O3" s="205"/>
-      <c r="P3" s="205"/>
-      <c r="Q3" s="205"/>
-      <c r="R3" s="261" t="s">
+      <c r="O3" s="203"/>
+      <c r="P3" s="203"/>
+      <c r="Q3" s="203"/>
+      <c r="R3" s="253" t="s">
         <v>251</v>
       </c>
-      <c r="S3" s="204" t="s">
+      <c r="S3" s="202" t="s">
         <v>252</v>
       </c>
-      <c r="T3" s="205"/>
-      <c r="U3" s="205"/>
-      <c r="V3" s="205"/>
-      <c r="W3" s="261" t="s">
+      <c r="T3" s="203"/>
+      <c r="U3" s="203"/>
+      <c r="V3" s="203"/>
+      <c r="W3" s="253" t="s">
         <v>251</v>
       </c>
-      <c r="X3" s="207" t="s">
+      <c r="X3" s="215" t="s">
         <v>41</v>
       </c>
-      <c r="Y3" s="208"/>
-      <c r="Z3" s="208"/>
-      <c r="AA3" s="261" t="s">
+      <c r="Y3" s="216"/>
+      <c r="Z3" s="216"/>
+      <c r="AA3" s="253" t="s">
         <v>251</v>
       </c>
       <c r="AB3" s="71"/>
-      <c r="AC3" s="204" t="s">
+      <c r="AC3" s="202" t="s">
         <v>42</v>
       </c>
-      <c r="AD3" s="205"/>
-      <c r="AE3" s="205"/>
-      <c r="AF3" s="205"/>
-      <c r="AG3" s="204" t="s">
+      <c r="AD3" s="203"/>
+      <c r="AE3" s="203"/>
+      <c r="AF3" s="203"/>
+      <c r="AG3" s="202" t="s">
         <v>43</v>
       </c>
-      <c r="AH3" s="205"/>
-      <c r="AI3" s="205"/>
-      <c r="AJ3" s="205"/>
-      <c r="AK3" s="204" t="s">
+      <c r="AH3" s="203"/>
+      <c r="AI3" s="203"/>
+      <c r="AJ3" s="203"/>
+      <c r="AK3" s="202" t="s">
         <v>44</v>
       </c>
-      <c r="AL3" s="205"/>
-      <c r="AM3" s="205"/>
-      <c r="AN3" s="205"/>
-      <c r="AO3" s="204" t="s">
+      <c r="AL3" s="203"/>
+      <c r="AM3" s="203"/>
+      <c r="AN3" s="203"/>
+      <c r="AO3" s="202" t="s">
         <v>46</v>
       </c>
-      <c r="AP3" s="205"/>
-      <c r="AQ3" s="205"/>
-      <c r="AR3" s="205"/>
-      <c r="AS3" s="204" t="s">
+      <c r="AP3" s="203"/>
+      <c r="AQ3" s="203"/>
+      <c r="AR3" s="203"/>
+      <c r="AS3" s="202" t="s">
         <v>47</v>
       </c>
-      <c r="AT3" s="205"/>
-      <c r="AU3" s="205"/>
-      <c r="AV3" s="205"/>
+      <c r="AT3" s="203"/>
+      <c r="AU3" s="203"/>
+      <c r="AV3" s="203"/>
     </row>
     <row r="4" spans="1:48" ht="22.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="253"/>
-      <c r="B4" s="255"/>
+      <c r="A4" s="255"/>
+      <c r="B4" s="257"/>
       <c r="C4" s="24">
         <f t="shared" ref="C4:K4" si="0">SUM(C5:C19)</f>
         <v>15</v>
@@ -26271,7 +26271,7 @@
         <f t="shared" si="0"/>
         <v>134</v>
       </c>
-      <c r="M4" s="258"/>
+      <c r="M4" s="260"/>
       <c r="N4" s="8" t="s">
         <v>2</v>
       </c>
@@ -26284,7 +26284,7 @@
       <c r="Q4" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="R4" s="262"/>
+      <c r="R4" s="254"/>
       <c r="S4" s="8" t="s">
         <v>2</v>
       </c>
@@ -26297,7 +26297,7 @@
       <c r="V4" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="W4" s="262"/>
+      <c r="W4" s="254"/>
       <c r="X4" s="8" t="s">
         <v>2</v>
       </c>
@@ -26307,7 +26307,7 @@
       <c r="Z4" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="AA4" s="262"/>
+      <c r="AA4" s="254"/>
       <c r="AB4" s="51" t="s">
         <v>59</v>
       </c>
@@ -28696,6 +28696,12 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="A1:K2"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="N3:Q3"/>
+    <mergeCell ref="M1:Z2"/>
     <mergeCell ref="AS3:AV3"/>
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="W3:W4"/>
@@ -28706,12 +28712,6 @@
     <mergeCell ref="AK3:AN3"/>
     <mergeCell ref="AO3:AR3"/>
     <mergeCell ref="S3:V3"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="A1:K2"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="N3:Q3"/>
-    <mergeCell ref="M1:Z2"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="P5:P20">
@@ -28851,44 +28851,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="263"/>
-      <c r="B1" s="263"/>
-      <c r="C1" s="263"/>
-      <c r="D1" s="263"/>
-      <c r="E1" s="263"/>
-      <c r="F1" s="263"/>
-      <c r="G1" s="263"/>
-      <c r="H1" s="263"/>
-      <c r="I1" s="263"/>
-      <c r="J1" s="263"/>
-      <c r="K1" s="263"/>
-      <c r="L1" s="263"/>
-      <c r="M1" s="263"/>
-      <c r="N1" s="263"/>
-      <c r="O1" s="263"/>
-      <c r="P1" s="263"/>
+      <c r="A1" s="265"/>
+      <c r="B1" s="265"/>
+      <c r="C1" s="265"/>
+      <c r="D1" s="265"/>
+      <c r="E1" s="265"/>
+      <c r="F1" s="265"/>
+      <c r="G1" s="265"/>
+      <c r="H1" s="265"/>
+      <c r="I1" s="265"/>
+      <c r="J1" s="265"/>
+      <c r="K1" s="265"/>
+      <c r="L1" s="265"/>
+      <c r="M1" s="265"/>
+      <c r="N1" s="265"/>
+      <c r="O1" s="265"/>
+      <c r="P1" s="265"/>
     </row>
     <row r="2" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="264"/>
-      <c r="B2" s="264"/>
-      <c r="C2" s="264"/>
-      <c r="D2" s="264"/>
-      <c r="E2" s="264"/>
-      <c r="F2" s="264"/>
-      <c r="G2" s="264"/>
-      <c r="H2" s="264"/>
-      <c r="I2" s="264"/>
-      <c r="J2" s="264"/>
-      <c r="K2" s="264"/>
-      <c r="L2" s="264"/>
-      <c r="M2" s="264"/>
-      <c r="N2" s="264"/>
-      <c r="O2" s="264"/>
-      <c r="P2" s="264"/>
+      <c r="A2" s="266"/>
+      <c r="B2" s="266"/>
+      <c r="C2" s="266"/>
+      <c r="D2" s="266"/>
+      <c r="E2" s="266"/>
+      <c r="F2" s="266"/>
+      <c r="G2" s="266"/>
+      <c r="H2" s="266"/>
+      <c r="I2" s="266"/>
+      <c r="J2" s="266"/>
+      <c r="K2" s="266"/>
+      <c r="L2" s="266"/>
+      <c r="M2" s="266"/>
+      <c r="N2" s="266"/>
+      <c r="O2" s="266"/>
+      <c r="P2" s="266"/>
     </row>
     <row r="3" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="265"/>
-      <c r="B3" s="265"/>
+      <c r="A3" s="267"/>
+      <c r="B3" s="267"/>
       <c r="C3" s="133"/>
       <c r="D3" s="133"/>
       <c r="E3" s="133"/>
@@ -28905,10 +28905,10 @@
       <c r="P3" s="133"/>
     </row>
     <row r="4" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="267" t="s">
+      <c r="A4" s="269" t="s">
         <v>255</v>
       </c>
-      <c r="B4" s="267" t="s">
+      <c r="B4" s="269" t="s">
         <v>39</v>
       </c>
       <c r="C4" s="141"/>
@@ -28916,70 +28916,70 @@
       <c r="E4" s="141"/>
       <c r="F4" s="141"/>
       <c r="G4" s="141"/>
-      <c r="H4" s="266"/>
-      <c r="I4" s="266"/>
-      <c r="J4" s="266"/>
-      <c r="K4" s="266"/>
-      <c r="L4" s="266"/>
-      <c r="M4" s="266"/>
-      <c r="N4" s="266"/>
-      <c r="O4" s="266"/>
-      <c r="P4" s="266"/>
+      <c r="H4" s="268"/>
+      <c r="I4" s="268"/>
+      <c r="J4" s="268"/>
+      <c r="K4" s="268"/>
+      <c r="L4" s="268"/>
+      <c r="M4" s="268"/>
+      <c r="N4" s="268"/>
+      <c r="O4" s="268"/>
+      <c r="P4" s="268"/>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A5" s="270"/>
-      <c r="B5" s="270"/>
-      <c r="C5" s="267" t="s">
+      <c r="A5" s="272"/>
+      <c r="B5" s="272"/>
+      <c r="C5" s="269" t="s">
         <v>256</v>
       </c>
-      <c r="D5" s="267" t="s">
+      <c r="D5" s="269" t="s">
         <v>257</v>
       </c>
-      <c r="E5" s="268"/>
-      <c r="F5" s="267" t="s">
+      <c r="E5" s="270"/>
+      <c r="F5" s="269" t="s">
         <v>258</v>
       </c>
-      <c r="G5" s="268"/>
-      <c r="H5" s="267" t="s">
+      <c r="G5" s="270"/>
+      <c r="H5" s="269" t="s">
         <v>259</v>
       </c>
-      <c r="I5" s="268"/>
-      <c r="J5" s="267" t="s">
+      <c r="I5" s="270"/>
+      <c r="J5" s="269" t="s">
         <v>260</v>
       </c>
-      <c r="K5" s="268"/>
-      <c r="L5" s="271" t="s">
+      <c r="K5" s="270"/>
+      <c r="L5" s="273" t="s">
         <v>261</v>
       </c>
-      <c r="M5" s="268"/>
-      <c r="N5" s="266" t="s">
+      <c r="M5" s="270"/>
+      <c r="N5" s="268" t="s">
         <v>262</v>
       </c>
-      <c r="O5" s="272"/>
-      <c r="P5" s="267" t="s">
+      <c r="O5" s="274"/>
+      <c r="P5" s="269" t="s">
         <v>266</v>
       </c>
-      <c r="R5" s="273" t="s">
+      <c r="R5" s="263" t="s">
         <v>34</v>
       </c>
-      <c r="S5" s="273" t="s">
+      <c r="S5" s="263" t="s">
         <v>289</v>
       </c>
-      <c r="T5" s="273" t="s">
+      <c r="T5" s="263" t="s">
         <v>290</v>
       </c>
-      <c r="U5" s="273" t="s">
+      <c r="U5" s="263" t="s">
         <v>292</v>
       </c>
-      <c r="V5" s="274" t="s">
+      <c r="V5" s="264" t="s">
         <v>291</v>
       </c>
       <c r="W5" s="172"/>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A6" s="269"/>
-      <c r="B6" s="269"/>
-      <c r="C6" s="270"/>
+      <c r="A6" s="271"/>
+      <c r="B6" s="271"/>
+      <c r="C6" s="272"/>
       <c r="D6" s="134" t="s">
         <v>2</v>
       </c>
@@ -29016,12 +29016,12 @@
       <c r="O6" s="134" t="s">
         <v>263</v>
       </c>
-      <c r="P6" s="269"/>
-      <c r="R6" s="273"/>
-      <c r="S6" s="273"/>
-      <c r="T6" s="273"/>
-      <c r="U6" s="273"/>
-      <c r="V6" s="273"/>
+      <c r="P6" s="271"/>
+      <c r="R6" s="263"/>
+      <c r="S6" s="263"/>
+      <c r="T6" s="263"/>
+      <c r="U6" s="263"/>
+      <c r="V6" s="263"/>
       <c r="W6" s="172"/>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.45">
@@ -30295,11 +30295,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="U5:U6"/>
-    <mergeCell ref="V5:V6"/>
-    <mergeCell ref="R5:R6"/>
-    <mergeCell ref="S5:S6"/>
-    <mergeCell ref="T5:T6"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
     <mergeCell ref="A3:B3"/>
@@ -30314,6 +30309,11 @@
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="L5:M5"/>
     <mergeCell ref="N5:O5"/>
+    <mergeCell ref="U5:U6"/>
+    <mergeCell ref="V5:V6"/>
+    <mergeCell ref="R5:R6"/>
+    <mergeCell ref="S5:S6"/>
+    <mergeCell ref="T5:T6"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="P7:P27">

--- a/filetiendo.xlsx
+++ b/filetiendo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\viettel 2026\thang 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C12DA01-4A61-4BDC-BA41-CCBB98C93814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB8E068C-CB38-444B-86AB-D10A1F4240DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="808" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="808" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TH NV" sheetId="2" r:id="rId1"/>
@@ -4553,17 +4553,41 @@
     <xf numFmtId="0" fontId="66" fillId="0" borderId="109" xfId="11" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="109" xfId="11" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="177" xfId="11" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="50" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="5" borderId="127" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="135" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="134" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="133" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="5" borderId="130" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="128" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="140" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="139" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="138" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="5" borderId="127" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="24" borderId="132" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4577,34 +4601,10 @@
     <xf numFmtId="0" fontId="17" fillId="5" borderId="129" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="135" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="134" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="133" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="16" borderId="136" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="2" borderId="137" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="140" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="139" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="138" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="67" fillId="18" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4676,16 +4676,16 @@
     <xf numFmtId="0" fontId="63" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="148" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="147" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="47" fillId="5" borderId="152" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="5" borderId="151" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="148" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="147" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="51" fillId="5" borderId="150" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4705,12 +4705,6 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="155" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="158" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="157" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="159" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4736,10 +4730,10 @@
     <xf numFmtId="0" fontId="55" fillId="0" borderId="164" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="69" fillId="29" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="158" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="69" fillId="29" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="157" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="45" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4764,6 +4758,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="168" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="69" fillId="29" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="29" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="12">
     <cellStyle name="Comma" xfId="8" builtinId="3"/>
@@ -5653,166 +5653,166 @@
       </c>
     </row>
     <row r="2" spans="1:675" ht="23.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="200" t="s">
+      <c r="A2" s="210" t="s">
         <v>34</v>
       </c>
       <c r="B2" s="86"/>
       <c r="C2" s="15"/>
-      <c r="D2" s="211" t="s">
+      <c r="D2" s="216" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="211"/>
-      <c r="F2" s="211"/>
-      <c r="G2" s="211"/>
-      <c r="H2" s="211"/>
-      <c r="I2" s="211"/>
-      <c r="J2" s="211"/>
-      <c r="K2" s="211"/>
-      <c r="L2" s="211"/>
-      <c r="M2" s="211"/>
-      <c r="N2" s="211"/>
-      <c r="O2" s="211"/>
-      <c r="P2" s="211"/>
-      <c r="Q2" s="211"/>
-      <c r="R2" s="211"/>
-      <c r="S2" s="211"/>
-      <c r="T2" s="206" t="s">
+      <c r="E2" s="216"/>
+      <c r="F2" s="216"/>
+      <c r="G2" s="216"/>
+      <c r="H2" s="216"/>
+      <c r="I2" s="216"/>
+      <c r="J2" s="216"/>
+      <c r="K2" s="216"/>
+      <c r="L2" s="216"/>
+      <c r="M2" s="216"/>
+      <c r="N2" s="216"/>
+      <c r="O2" s="216"/>
+      <c r="P2" s="216"/>
+      <c r="Q2" s="216"/>
+      <c r="R2" s="216"/>
+      <c r="S2" s="216"/>
+      <c r="T2" s="214" t="s">
         <v>36</v>
       </c>
-      <c r="U2" s="206"/>
-      <c r="V2" s="206"/>
-      <c r="W2" s="206"/>
-      <c r="X2" s="206"/>
-      <c r="Y2" s="206"/>
-      <c r="Z2" s="206"/>
-      <c r="AA2" s="206"/>
-      <c r="AB2" s="206"/>
-      <c r="AC2" s="206"/>
-      <c r="AD2" s="206"/>
-      <c r="AE2" s="206"/>
-      <c r="AF2" s="206"/>
-      <c r="AG2" s="206"/>
-      <c r="AH2" s="206"/>
-      <c r="AI2" s="206"/>
-      <c r="AJ2" s="205" t="s">
+      <c r="U2" s="214"/>
+      <c r="V2" s="214"/>
+      <c r="W2" s="214"/>
+      <c r="X2" s="214"/>
+      <c r="Y2" s="214"/>
+      <c r="Z2" s="214"/>
+      <c r="AA2" s="214"/>
+      <c r="AB2" s="214"/>
+      <c r="AC2" s="214"/>
+      <c r="AD2" s="214"/>
+      <c r="AE2" s="214"/>
+      <c r="AF2" s="214"/>
+      <c r="AG2" s="214"/>
+      <c r="AH2" s="214"/>
+      <c r="AI2" s="214"/>
+      <c r="AJ2" s="213" t="s">
         <v>37</v>
       </c>
-      <c r="AK2" s="205"/>
-      <c r="AL2" s="205"/>
-      <c r="AM2" s="205"/>
-      <c r="AN2" s="205"/>
-      <c r="AO2" s="205"/>
-      <c r="AP2" s="205"/>
-      <c r="AQ2" s="205"/>
-      <c r="AR2" s="205"/>
-      <c r="AS2" s="205"/>
-      <c r="AT2" s="205"/>
-      <c r="AU2" s="205"/>
-      <c r="AV2" s="204" t="s">
+      <c r="AK2" s="213"/>
+      <c r="AL2" s="213"/>
+      <c r="AM2" s="213"/>
+      <c r="AN2" s="213"/>
+      <c r="AO2" s="213"/>
+      <c r="AP2" s="213"/>
+      <c r="AQ2" s="213"/>
+      <c r="AR2" s="213"/>
+      <c r="AS2" s="213"/>
+      <c r="AT2" s="213"/>
+      <c r="AU2" s="213"/>
+      <c r="AV2" s="212" t="s">
         <v>38</v>
       </c>
-      <c r="AW2" s="204"/>
-      <c r="AX2" s="204"/>
-      <c r="AY2" s="204"/>
-      <c r="AZ2" s="204"/>
-      <c r="BA2" s="204"/>
-      <c r="BB2" s="204"/>
-      <c r="BC2" s="204"/>
-      <c r="BD2" s="204"/>
-      <c r="BE2" s="204"/>
-      <c r="BF2" s="204"/>
-      <c r="BG2" s="204"/>
+      <c r="AW2" s="212"/>
+      <c r="AX2" s="212"/>
+      <c r="AY2" s="212"/>
+      <c r="AZ2" s="212"/>
+      <c r="BA2" s="212"/>
+      <c r="BB2" s="212"/>
+      <c r="BC2" s="212"/>
+      <c r="BD2" s="212"/>
+      <c r="BE2" s="212"/>
+      <c r="BF2" s="212"/>
+      <c r="BG2" s="212"/>
     </row>
     <row r="3" spans="1:675" s="3" customFormat="1" ht="28.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="200"/>
-      <c r="B3" s="212" t="s">
+      <c r="A3" s="210"/>
+      <c r="B3" s="217" t="s">
         <v>39</v>
       </c>
       <c r="C3" s="87"/>
-      <c r="D3" s="202" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="203"/>
-      <c r="F3" s="203"/>
-      <c r="G3" s="203"/>
-      <c r="H3" s="202" t="s">
+      <c r="D3" s="204" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="205"/>
+      <c r="F3" s="205"/>
+      <c r="G3" s="205"/>
+      <c r="H3" s="204" t="s">
         <v>40</v>
       </c>
-      <c r="I3" s="203"/>
-      <c r="J3" s="203"/>
-      <c r="K3" s="203"/>
-      <c r="L3" s="202" t="s">
+      <c r="I3" s="205"/>
+      <c r="J3" s="205"/>
+      <c r="K3" s="205"/>
+      <c r="L3" s="204" t="s">
         <v>41</v>
       </c>
-      <c r="M3" s="203"/>
-      <c r="N3" s="203"/>
-      <c r="O3" s="203"/>
-      <c r="P3" s="215" t="s">
+      <c r="M3" s="205"/>
+      <c r="N3" s="205"/>
+      <c r="O3" s="205"/>
+      <c r="P3" s="207" t="s">
         <v>42</v>
       </c>
-      <c r="Q3" s="216"/>
-      <c r="R3" s="216"/>
-      <c r="S3" s="217"/>
-      <c r="T3" s="202" t="s">
+      <c r="Q3" s="208"/>
+      <c r="R3" s="208"/>
+      <c r="S3" s="209"/>
+      <c r="T3" s="204" t="s">
         <v>43</v>
       </c>
-      <c r="U3" s="203"/>
-      <c r="V3" s="203"/>
-      <c r="W3" s="203"/>
-      <c r="X3" s="202" t="s">
+      <c r="U3" s="205"/>
+      <c r="V3" s="205"/>
+      <c r="W3" s="205"/>
+      <c r="X3" s="204" t="s">
         <v>45</v>
       </c>
-      <c r="Y3" s="203"/>
-      <c r="Z3" s="203"/>
-      <c r="AA3" s="203"/>
-      <c r="AB3" s="202" t="s">
+      <c r="Y3" s="205"/>
+      <c r="Z3" s="205"/>
+      <c r="AA3" s="205"/>
+      <c r="AB3" s="204" t="s">
         <v>47</v>
       </c>
-      <c r="AC3" s="203"/>
-      <c r="AD3" s="203"/>
-      <c r="AE3" s="203"/>
-      <c r="AF3" s="202" t="s">
+      <c r="AC3" s="205"/>
+      <c r="AD3" s="205"/>
+      <c r="AE3" s="205"/>
+      <c r="AF3" s="204" t="s">
         <v>48</v>
       </c>
-      <c r="AG3" s="203"/>
-      <c r="AH3" s="203"/>
-      <c r="AI3" s="203"/>
-      <c r="AJ3" s="208" t="s">
+      <c r="AG3" s="205"/>
+      <c r="AH3" s="205"/>
+      <c r="AI3" s="205"/>
+      <c r="AJ3" s="201" t="s">
         <v>51</v>
       </c>
-      <c r="AK3" s="209"/>
-      <c r="AL3" s="209"/>
-      <c r="AM3" s="210"/>
-      <c r="AN3" s="208" t="s">
+      <c r="AK3" s="202"/>
+      <c r="AL3" s="202"/>
+      <c r="AM3" s="203"/>
+      <c r="AN3" s="201" t="s">
         <v>14</v>
       </c>
-      <c r="AO3" s="209"/>
-      <c r="AP3" s="209"/>
-      <c r="AQ3" s="210"/>
-      <c r="AR3" s="208" t="s">
+      <c r="AO3" s="202"/>
+      <c r="AP3" s="202"/>
+      <c r="AQ3" s="203"/>
+      <c r="AR3" s="201" t="s">
         <v>52</v>
       </c>
-      <c r="AS3" s="209"/>
-      <c r="AT3" s="209"/>
-      <c r="AU3" s="210"/>
-      <c r="AV3" s="203" t="s">
+      <c r="AS3" s="202"/>
+      <c r="AT3" s="202"/>
+      <c r="AU3" s="203"/>
+      <c r="AV3" s="205" t="s">
         <v>16</v>
       </c>
-      <c r="AW3" s="203"/>
-      <c r="AX3" s="203"/>
-      <c r="AY3" s="203"/>
-      <c r="AZ3" s="203" t="s">
+      <c r="AW3" s="205"/>
+      <c r="AX3" s="205"/>
+      <c r="AY3" s="205"/>
+      <c r="AZ3" s="205" t="s">
         <v>54</v>
       </c>
-      <c r="BA3" s="203"/>
-      <c r="BB3" s="203"/>
-      <c r="BC3" s="203"/>
-      <c r="BD3" s="202" t="s">
+      <c r="BA3" s="205"/>
+      <c r="BB3" s="205"/>
+      <c r="BC3" s="205"/>
+      <c r="BD3" s="204" t="s">
         <v>55</v>
       </c>
-      <c r="BE3" s="203"/>
-      <c r="BF3" s="207"/>
-      <c r="BG3" s="203"/>
+      <c r="BE3" s="205"/>
+      <c r="BF3" s="215"/>
+      <c r="BG3" s="205"/>
       <c r="BH3" s="2"/>
       <c r="BI3" s="2"/>
       <c r="BJ3" s="2"/>
@@ -6431,8 +6431,8 @@
       <c r="YY3" s="2"/>
     </row>
     <row r="4" spans="1:675" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="201"/>
-      <c r="B4" s="212"/>
+      <c r="A4" s="211"/>
+      <c r="B4" s="217"/>
       <c r="C4" s="88"/>
       <c r="D4" s="8" t="s">
         <v>2</v>
@@ -6777,7 +6777,7 @@
       </c>
       <c r="AS5" s="129">
         <f>(VLOOKUP(B5,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.83250000000000002</v>
+        <v>0.84370000000000012</v>
       </c>
       <c r="AT5" s="14">
         <f t="shared" ref="AT5:AT18" si="20">IF(AS5&lt;94.5%,0,IF(AS5&lt;95.54%,50%,IF(AS5&lt;AR5,80%,100%+(30%*(AS5-AR5)/3.39%))))</f>
@@ -6785,7 +6785,7 @@
       </c>
       <c r="AU5" s="54">
         <f t="shared" ref="AU5:AU18" si="21">AR5-AS5</f>
-        <v>0.13749999999999996</v>
+        <v>0.12629999999999986</v>
       </c>
       <c r="AV5" s="57">
         <f>VLOOKUP(C5,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="AS6" s="129">
         <f>(VLOOKUP(B6,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.75790000000000013</v>
+        <v>0.77450000000000008</v>
       </c>
       <c r="AT6" s="14">
         <f t="shared" si="20"/>
@@ -7018,7 +7018,7 @@
       </c>
       <c r="AU6" s="54">
         <f t="shared" si="21"/>
-        <v>0.21209999999999984</v>
+        <v>0.1954999999999999</v>
       </c>
       <c r="AV6" s="57">
         <f>VLOOKUP(C6,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7243,7 +7243,7 @@
       </c>
       <c r="AS7" s="129">
         <f>(VLOOKUP(B7,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.79480000000000006</v>
+        <v>0.81630000000000003</v>
       </c>
       <c r="AT7" s="14">
         <f t="shared" si="20"/>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="AU7" s="54">
         <f t="shared" si="21"/>
-        <v>0.17519999999999991</v>
+        <v>0.15369999999999995</v>
       </c>
       <c r="AV7" s="57">
         <f>VLOOKUP(C7,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7476,7 +7476,7 @@
       </c>
       <c r="AS8" s="129">
         <f>(VLOOKUP(B8,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.8034</v>
+        <v>0.81730000000000003</v>
       </c>
       <c r="AT8" s="14">
         <f t="shared" si="20"/>
@@ -7484,7 +7484,7 @@
       </c>
       <c r="AU8" s="54">
         <f t="shared" si="21"/>
-        <v>0.16659999999999997</v>
+        <v>0.15269999999999995</v>
       </c>
       <c r="AV8" s="57">
         <f>VLOOKUP(C8,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7709,7 +7709,7 @@
       </c>
       <c r="AS9" s="129">
         <f>(VLOOKUP(B9,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.66239999999999999</v>
+        <v>0.67390000000000005</v>
       </c>
       <c r="AT9" s="14">
         <f t="shared" si="20"/>
@@ -7717,7 +7717,7 @@
       </c>
       <c r="AU9" s="54">
         <f t="shared" si="21"/>
-        <v>0.30759999999999998</v>
+        <v>0.29609999999999992</v>
       </c>
       <c r="AV9" s="57">
         <f>VLOOKUP(C9,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7942,7 +7942,7 @@
       </c>
       <c r="AS10" s="129">
         <f>(VLOOKUP(B10,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.76080000000000003</v>
+        <v>0.7853</v>
       </c>
       <c r="AT10" s="14">
         <f t="shared" si="20"/>
@@ -7950,7 +7950,7 @@
       </c>
       <c r="AU10" s="54">
         <f t="shared" si="21"/>
-        <v>0.20919999999999994</v>
+        <v>0.18469999999999998</v>
       </c>
       <c r="AV10" s="57">
         <f>VLOOKUP(C10,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="AS11" s="129">
         <f>(VLOOKUP(B11,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.74230000000000007</v>
+        <v>0.75290000000000012</v>
       </c>
       <c r="AT11" s="14">
         <f t="shared" si="20"/>
@@ -8183,7 +8183,7 @@
       </c>
       <c r="AU11" s="54">
         <f t="shared" si="21"/>
-        <v>0.2276999999999999</v>
+        <v>0.21709999999999985</v>
       </c>
       <c r="AV11" s="57">
         <f>VLOOKUP(C11,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="AS12" s="129">
         <f>(VLOOKUP(B12,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.71950000000000003</v>
+        <v>0.72239999999999993</v>
       </c>
       <c r="AT12" s="14">
         <f t="shared" si="20"/>
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AU12" s="54">
         <f t="shared" si="21"/>
-        <v>0.25049999999999994</v>
+        <v>0.24760000000000004</v>
       </c>
       <c r="AV12" s="57">
         <f>VLOOKUP(C12,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="AS13" s="129">
         <f>(VLOOKUP(B13,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.82000000000000006</v>
+        <v>0.83689999999999998</v>
       </c>
       <c r="AT13" s="14">
         <f t="shared" si="20"/>
@@ -8649,7 +8649,7 @@
       </c>
       <c r="AU13" s="54">
         <f t="shared" si="21"/>
-        <v>0.14999999999999991</v>
+        <v>0.1331</v>
       </c>
       <c r="AV13" s="57">
         <f>VLOOKUP(C13,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="AS14" s="129">
         <f>(VLOOKUP(B14,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.67670000000000008</v>
+        <v>0.68610000000000004</v>
       </c>
       <c r="AT14" s="14">
         <f t="shared" si="20"/>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="AU14" s="54">
         <f t="shared" si="21"/>
-        <v>0.29329999999999989</v>
+        <v>0.28389999999999993</v>
       </c>
       <c r="AV14" s="57">
         <f>VLOOKUP(C14,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -9107,7 +9107,7 @@
       </c>
       <c r="AS15" s="129">
         <f>(VLOOKUP(B15,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.69000000000000006</v>
+        <v>0.72840000000000005</v>
       </c>
       <c r="AT15" s="14">
         <f t="shared" si="20"/>
@@ -9115,7 +9115,7 @@
       </c>
       <c r="AU15" s="54">
         <f t="shared" si="21"/>
-        <v>0.27999999999999992</v>
+        <v>0.24159999999999993</v>
       </c>
       <c r="AV15" s="57">
         <f>VLOOKUP(C15,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -9340,7 +9340,7 @@
       </c>
       <c r="AS16" s="129">
         <f>(VLOOKUP(B16,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.78260000000000007</v>
+        <v>0.80200000000000005</v>
       </c>
       <c r="AT16" s="14">
         <f t="shared" si="20"/>
@@ -9348,7 +9348,7 @@
       </c>
       <c r="AU16" s="54">
         <f t="shared" si="21"/>
-        <v>0.1873999999999999</v>
+        <v>0.16799999999999993</v>
       </c>
       <c r="AV16" s="57">
         <f>VLOOKUP(C16,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -9573,7 +9573,7 @@
       </c>
       <c r="AS17" s="129">
         <f>(VLOOKUP(B17,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.79709999999999992</v>
+        <v>0.80740000000000001</v>
       </c>
       <c r="AT17" s="14">
         <f t="shared" si="20"/>
@@ -9581,7 +9581,7 @@
       </c>
       <c r="AU17" s="54">
         <f t="shared" si="21"/>
-        <v>0.17290000000000005</v>
+        <v>0.16259999999999997</v>
       </c>
       <c r="AV17" s="57">
         <f>VLOOKUP(C17,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -9806,7 +9806,7 @@
       </c>
       <c r="AS18" s="129">
         <f>(VLOOKUP(B18,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.76400000000000012</v>
+        <v>0.76989999999999992</v>
       </c>
       <c r="AT18" s="14">
         <f t="shared" si="20"/>
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AU18" s="54">
         <f t="shared" si="21"/>
-        <v>0.20599999999999985</v>
+        <v>0.20010000000000006</v>
       </c>
       <c r="AV18" s="57">
         <f>VLOOKUP(C18,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -9871,11 +9871,11 @@
       <c r="C19" s="15"/>
       <c r="D19" s="15"/>
       <c r="E19" s="16"/>
-      <c r="F19" s="213">
+      <c r="F19" s="200">
         <f ca="1">TODAY()</f>
         <v>46077</v>
       </c>
-      <c r="G19" s="213"/>
+      <c r="G19" s="200"/>
       <c r="H19" s="90"/>
       <c r="I19" s="91">
         <f ca="1">DAY(F19)</f>
@@ -9888,33 +9888,33 @@
         <f ca="1">I19/J19</f>
         <v>0.77419354838709675</v>
       </c>
-      <c r="L19" s="214" t="s">
+      <c r="L19" s="206" t="s">
         <v>124</v>
       </c>
-      <c r="M19" s="214"/>
-      <c r="N19" s="214"/>
-      <c r="O19" s="214"/>
-      <c r="P19" s="214"/>
-      <c r="Q19" s="214"/>
-      <c r="R19" s="214"/>
-      <c r="S19" s="214"/>
-      <c r="T19" s="214"/>
-      <c r="U19" s="214"/>
-      <c r="V19" s="214"/>
-      <c r="W19" s="214"/>
-      <c r="X19" s="214"/>
-      <c r="Y19" s="214"/>
-      <c r="Z19" s="214"/>
-      <c r="AA19" s="214"/>
-      <c r="AB19" s="214"/>
-      <c r="AC19" s="214"/>
-      <c r="AD19" s="214"/>
-      <c r="AE19" s="214"/>
-      <c r="AF19" s="214"/>
-      <c r="AG19" s="214"/>
-      <c r="AH19" s="214"/>
-      <c r="AI19" s="214"/>
-      <c r="AJ19" s="214"/>
+      <c r="M19" s="206"/>
+      <c r="N19" s="206"/>
+      <c r="O19" s="206"/>
+      <c r="P19" s="206"/>
+      <c r="Q19" s="206"/>
+      <c r="R19" s="206"/>
+      <c r="S19" s="206"/>
+      <c r="T19" s="206"/>
+      <c r="U19" s="206"/>
+      <c r="V19" s="206"/>
+      <c r="W19" s="206"/>
+      <c r="X19" s="206"/>
+      <c r="Y19" s="206"/>
+      <c r="Z19" s="206"/>
+      <c r="AA19" s="206"/>
+      <c r="AB19" s="206"/>
+      <c r="AC19" s="206"/>
+      <c r="AD19" s="206"/>
+      <c r="AE19" s="206"/>
+      <c r="AF19" s="206"/>
+      <c r="AG19" s="206"/>
+      <c r="AH19" s="206"/>
+      <c r="AI19" s="206"/>
+      <c r="AJ19" s="206"/>
       <c r="AK19" s="16"/>
       <c r="AL19" s="32"/>
       <c r="AM19" s="16"/>
@@ -10107,12 +10107,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="AN3:AQ3"/>
-    <mergeCell ref="AF3:AI3"/>
-    <mergeCell ref="L19:AJ19"/>
-    <mergeCell ref="P3:S3"/>
-    <mergeCell ref="T3:W3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="X3:AA3"/>
     <mergeCell ref="AV2:BG2"/>
@@ -10129,6 +10123,12 @@
     <mergeCell ref="D3:G3"/>
     <mergeCell ref="H3:K3"/>
     <mergeCell ref="L3:O3"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="AN3:AQ3"/>
+    <mergeCell ref="AF3:AI3"/>
+    <mergeCell ref="L19:AJ19"/>
+    <mergeCell ref="P3:S3"/>
+    <mergeCell ref="T3:W3"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="C3:C4">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="D14" s="74">
         <f>VLOOKUP($B$2,'TH NV'!$A$5:$BG$18,N14,0)</f>
-        <v>0.83250000000000002</v>
+        <v>0.84370000000000012</v>
       </c>
       <c r="E14" s="49" t="e">
         <f>VLOOKUP($B$2,'TH NV'!$A$1:$BG$18,70,0)</f>
@@ -11167,7 +11167,7 @@
       </c>
       <c r="J14" s="65">
         <f t="shared" si="2"/>
-        <v>0.13749999999999996</v>
+        <v>0.12629999999999986</v>
       </c>
       <c r="K14" s="222"/>
       <c r="L14" s="114" t="s">
@@ -11348,42 +11348,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:59" s="1" customFormat="1" ht="24.75" x14ac:dyDescent="0.45">
-      <c r="D1" s="211" t="s">
+      <c r="D1" s="216" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="211"/>
-      <c r="F1" s="211"/>
-      <c r="G1" s="211"/>
-      <c r="H1" s="211"/>
-      <c r="I1" s="211"/>
-      <c r="J1" s="211"/>
-      <c r="K1" s="211"/>
-      <c r="L1" s="211"/>
-      <c r="M1" s="211"/>
-      <c r="N1" s="211"/>
-      <c r="O1" s="211"/>
-      <c r="P1" s="211"/>
-      <c r="Q1" s="211"/>
-      <c r="R1" s="211"/>
-      <c r="S1" s="211"/>
-      <c r="T1" s="206" t="s">
+      <c r="E1" s="216"/>
+      <c r="F1" s="216"/>
+      <c r="G1" s="216"/>
+      <c r="H1" s="216"/>
+      <c r="I1" s="216"/>
+      <c r="J1" s="216"/>
+      <c r="K1" s="216"/>
+      <c r="L1" s="216"/>
+      <c r="M1" s="216"/>
+      <c r="N1" s="216"/>
+      <c r="O1" s="216"/>
+      <c r="P1" s="216"/>
+      <c r="Q1" s="216"/>
+      <c r="R1" s="216"/>
+      <c r="S1" s="216"/>
+      <c r="T1" s="214" t="s">
         <v>36</v>
       </c>
-      <c r="U1" s="206"/>
-      <c r="V1" s="206"/>
-      <c r="W1" s="206"/>
-      <c r="X1" s="206"/>
-      <c r="Y1" s="206"/>
-      <c r="Z1" s="206"/>
-      <c r="AA1" s="206"/>
-      <c r="AB1" s="206"/>
-      <c r="AC1" s="206"/>
-      <c r="AD1" s="206"/>
-      <c r="AE1" s="206"/>
-      <c r="AF1" s="206"/>
-      <c r="AG1" s="206"/>
-      <c r="AH1" s="206"/>
-      <c r="AI1" s="206"/>
+      <c r="U1" s="214"/>
+      <c r="V1" s="214"/>
+      <c r="W1" s="214"/>
+      <c r="X1" s="214"/>
+      <c r="Y1" s="214"/>
+      <c r="Z1" s="214"/>
+      <c r="AA1" s="214"/>
+      <c r="AB1" s="214"/>
+      <c r="AC1" s="214"/>
+      <c r="AD1" s="214"/>
+      <c r="AE1" s="214"/>
+      <c r="AF1" s="214"/>
+      <c r="AG1" s="214"/>
+      <c r="AH1" s="214"/>
+      <c r="AI1" s="214"/>
       <c r="AJ1" s="234" t="s">
         <v>37</v>
       </c>
@@ -11416,90 +11416,90 @@
     <row r="2" spans="1:59" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="202" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="203"/>
-      <c r="F2" s="203"/>
-      <c r="G2" s="203"/>
-      <c r="H2" s="202" t="s">
+      <c r="D2" s="204" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="205"/>
+      <c r="F2" s="205"/>
+      <c r="G2" s="205"/>
+      <c r="H2" s="204" t="s">
         <v>40</v>
       </c>
-      <c r="I2" s="203"/>
-      <c r="J2" s="203"/>
-      <c r="K2" s="203"/>
-      <c r="L2" s="202" t="s">
+      <c r="I2" s="205"/>
+      <c r="J2" s="205"/>
+      <c r="K2" s="205"/>
+      <c r="L2" s="204" t="s">
         <v>41</v>
       </c>
-      <c r="M2" s="203"/>
-      <c r="N2" s="203"/>
-      <c r="O2" s="203"/>
-      <c r="P2" s="215" t="s">
+      <c r="M2" s="205"/>
+      <c r="N2" s="205"/>
+      <c r="O2" s="205"/>
+      <c r="P2" s="207" t="s">
         <v>42</v>
       </c>
-      <c r="Q2" s="216"/>
-      <c r="R2" s="216"/>
-      <c r="S2" s="217"/>
-      <c r="T2" s="202" t="s">
+      <c r="Q2" s="208"/>
+      <c r="R2" s="208"/>
+      <c r="S2" s="209"/>
+      <c r="T2" s="204" t="s">
         <v>43</v>
       </c>
-      <c r="U2" s="203"/>
-      <c r="V2" s="203"/>
-      <c r="W2" s="203"/>
-      <c r="X2" s="202" t="s">
+      <c r="U2" s="205"/>
+      <c r="V2" s="205"/>
+      <c r="W2" s="205"/>
+      <c r="X2" s="204" t="s">
         <v>45</v>
       </c>
-      <c r="Y2" s="203"/>
-      <c r="Z2" s="203"/>
-      <c r="AA2" s="203"/>
-      <c r="AB2" s="202" t="s">
+      <c r="Y2" s="205"/>
+      <c r="Z2" s="205"/>
+      <c r="AA2" s="205"/>
+      <c r="AB2" s="204" t="s">
         <v>47</v>
       </c>
-      <c r="AC2" s="203"/>
-      <c r="AD2" s="203"/>
-      <c r="AE2" s="203"/>
-      <c r="AF2" s="202" t="s">
+      <c r="AC2" s="205"/>
+      <c r="AD2" s="205"/>
+      <c r="AE2" s="205"/>
+      <c r="AF2" s="204" t="s">
         <v>48</v>
       </c>
-      <c r="AG2" s="203"/>
-      <c r="AH2" s="203"/>
-      <c r="AI2" s="203"/>
-      <c r="AJ2" s="208" t="s">
+      <c r="AG2" s="205"/>
+      <c r="AH2" s="205"/>
+      <c r="AI2" s="205"/>
+      <c r="AJ2" s="201" t="s">
         <v>51</v>
       </c>
-      <c r="AK2" s="209"/>
-      <c r="AL2" s="209"/>
-      <c r="AM2" s="210"/>
-      <c r="AN2" s="208" t="s">
+      <c r="AK2" s="202"/>
+      <c r="AL2" s="202"/>
+      <c r="AM2" s="203"/>
+      <c r="AN2" s="201" t="s">
         <v>14</v>
       </c>
-      <c r="AO2" s="209"/>
-      <c r="AP2" s="209"/>
-      <c r="AQ2" s="210"/>
-      <c r="AR2" s="208" t="s">
+      <c r="AO2" s="202"/>
+      <c r="AP2" s="202"/>
+      <c r="AQ2" s="203"/>
+      <c r="AR2" s="201" t="s">
         <v>52</v>
       </c>
-      <c r="AS2" s="209"/>
-      <c r="AT2" s="209"/>
-      <c r="AU2" s="210"/>
-      <c r="AV2" s="203" t="s">
+      <c r="AS2" s="202"/>
+      <c r="AT2" s="202"/>
+      <c r="AU2" s="203"/>
+      <c r="AV2" s="205" t="s">
         <v>16</v>
       </c>
-      <c r="AW2" s="203"/>
-      <c r="AX2" s="203"/>
-      <c r="AY2" s="203"/>
-      <c r="AZ2" s="203" t="s">
+      <c r="AW2" s="205"/>
+      <c r="AX2" s="205"/>
+      <c r="AY2" s="205"/>
+      <c r="AZ2" s="205" t="s">
         <v>54</v>
       </c>
-      <c r="BA2" s="203"/>
-      <c r="BB2" s="203"/>
-      <c r="BC2" s="203"/>
-      <c r="BD2" s="202" t="s">
+      <c r="BA2" s="205"/>
+      <c r="BB2" s="205"/>
+      <c r="BC2" s="205"/>
+      <c r="BD2" s="204" t="s">
         <v>55</v>
       </c>
-      <c r="BE2" s="203"/>
-      <c r="BF2" s="207"/>
-      <c r="BG2" s="203"/>
+      <c r="BE2" s="205"/>
+      <c r="BF2" s="215"/>
+      <c r="BG2" s="205"/>
     </row>
     <row r="3" spans="1:59" ht="15" x14ac:dyDescent="0.45">
       <c r="B3" s="8" t="s">
@@ -11852,7 +11852,7 @@
       </c>
       <c r="AS4" s="129">
         <f>(VLOOKUP(B4,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.83250000000000002</v>
+        <v>0.84370000000000012</v>
       </c>
       <c r="AT4" s="14">
         <f t="shared" ref="AT4" si="20">IF(AS4&lt;94.5%,0,IF(AS4&lt;95.54%,50%,IF(AS4&lt;AR4,80%,100%+(30%*(AS4-AR4)/3.39%))))</f>
@@ -11860,7 +11860,7 @@
       </c>
       <c r="AU4" s="54">
         <f t="shared" ref="AU4" si="21">AR4-AS4</f>
-        <v>0.13749999999999996</v>
+        <v>0.12629999999999986</v>
       </c>
       <c r="AV4" s="57">
         <f>VLOOKUP(A4,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -12086,7 +12086,7 @@
       </c>
       <c r="AS5" s="129">
         <f>(VLOOKUP(B5,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.74230000000000007</v>
+        <v>0.75290000000000012</v>
       </c>
       <c r="AT5" s="14">
         <f t="shared" ref="AT5:AT16" si="48">IF(AS5&lt;94.5%,0,IF(AS5&lt;95.54%,50%,IF(AS5&lt;AR5,80%,100%+(30%*(AS5-AR5)/3.39%))))</f>
@@ -12094,7 +12094,7 @@
       </c>
       <c r="AU5" s="54">
         <f t="shared" ref="AU5:AU16" si="49">AR5-AS5</f>
-        <v>0.2276999999999999</v>
+        <v>0.21709999999999985</v>
       </c>
       <c r="AV5" s="57">
         <f>VLOOKUP(A5,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -12320,7 +12320,7 @@
       </c>
       <c r="AS6" s="129">
         <f>(VLOOKUP(B6,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.71950000000000003</v>
+        <v>0.72239999999999993</v>
       </c>
       <c r="AT6" s="14">
         <f t="shared" si="48"/>
@@ -12328,7 +12328,7 @@
       </c>
       <c r="AU6" s="54">
         <f t="shared" si="49"/>
-        <v>0.25049999999999994</v>
+        <v>0.24760000000000004</v>
       </c>
       <c r="AV6" s="57">
         <f>VLOOKUP(A6,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -12554,7 +12554,7 @@
       </c>
       <c r="AS7" s="129">
         <f>(VLOOKUP(B7,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.67670000000000008</v>
+        <v>0.68610000000000004</v>
       </c>
       <c r="AT7" s="14">
         <f t="shared" si="48"/>
@@ -12562,7 +12562,7 @@
       </c>
       <c r="AU7" s="54">
         <f t="shared" si="49"/>
-        <v>0.29329999999999989</v>
+        <v>0.28389999999999993</v>
       </c>
       <c r="AV7" s="57">
         <f>VLOOKUP(A7,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -12788,7 +12788,7 @@
       </c>
       <c r="AS8" s="129">
         <f>(VLOOKUP(B8,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.78260000000000007</v>
+        <v>0.80200000000000005</v>
       </c>
       <c r="AT8" s="14">
         <f t="shared" si="48"/>
@@ -12796,7 +12796,7 @@
       </c>
       <c r="AU8" s="54">
         <f t="shared" si="49"/>
-        <v>0.1873999999999999</v>
+        <v>0.16799999999999993</v>
       </c>
       <c r="AV8" s="57">
         <f>VLOOKUP(A8,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -13083,7 +13083,7 @@
       </c>
       <c r="AS10" s="129">
         <f>(VLOOKUP(B10,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.75790000000000013</v>
+        <v>0.77450000000000008</v>
       </c>
       <c r="AT10" s="14">
         <f t="shared" si="48"/>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="AU10" s="54">
         <f t="shared" si="49"/>
-        <v>0.21209999999999984</v>
+        <v>0.1954999999999999</v>
       </c>
       <c r="AV10" s="57">
         <f>VLOOKUP(A10,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -13317,7 +13317,7 @@
       </c>
       <c r="AS11" s="129">
         <f>(VLOOKUP(B11,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.79480000000000006</v>
+        <v>0.81630000000000003</v>
       </c>
       <c r="AT11" s="14">
         <f t="shared" si="48"/>
@@ -13325,7 +13325,7 @@
       </c>
       <c r="AU11" s="54">
         <f t="shared" si="49"/>
-        <v>0.17519999999999991</v>
+        <v>0.15369999999999995</v>
       </c>
       <c r="AV11" s="57">
         <f>VLOOKUP(A11,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -13551,7 +13551,7 @@
       </c>
       <c r="AS12" s="129">
         <f>(VLOOKUP(B12,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.8034</v>
+        <v>0.81730000000000003</v>
       </c>
       <c r="AT12" s="14">
         <f t="shared" si="48"/>
@@ -13559,7 +13559,7 @@
       </c>
       <c r="AU12" s="54">
         <f t="shared" si="49"/>
-        <v>0.16659999999999997</v>
+        <v>0.15269999999999995</v>
       </c>
       <c r="AV12" s="57">
         <f>VLOOKUP(A12,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -13785,7 +13785,7 @@
       </c>
       <c r="AS13" s="129">
         <f>(VLOOKUP(B13,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.76080000000000003</v>
+        <v>0.7853</v>
       </c>
       <c r="AT13" s="14">
         <f t="shared" si="48"/>
@@ -13793,7 +13793,7 @@
       </c>
       <c r="AU13" s="54">
         <f t="shared" si="49"/>
-        <v>0.20919999999999994</v>
+        <v>0.18469999999999998</v>
       </c>
       <c r="AV13" s="57">
         <f>VLOOKUP(A13,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -14019,7 +14019,7 @@
       </c>
       <c r="AS14" s="129">
         <f>(VLOOKUP(B14,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.82000000000000006</v>
+        <v>0.83689999999999998</v>
       </c>
       <c r="AT14" s="14">
         <f t="shared" si="48"/>
@@ -14027,7 +14027,7 @@
       </c>
       <c r="AU14" s="54">
         <f t="shared" si="49"/>
-        <v>0.14999999999999991</v>
+        <v>0.1331</v>
       </c>
       <c r="AV14" s="57">
         <f>VLOOKUP(A14,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -14253,7 +14253,7 @@
       </c>
       <c r="AS15" s="129">
         <f>(VLOOKUP(B15,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.69000000000000006</v>
+        <v>0.72840000000000005</v>
       </c>
       <c r="AT15" s="14">
         <f t="shared" si="48"/>
@@ -14261,7 +14261,7 @@
       </c>
       <c r="AU15" s="54">
         <f t="shared" si="49"/>
-        <v>0.27999999999999992</v>
+        <v>0.24159999999999993</v>
       </c>
       <c r="AV15" s="57">
         <f>VLOOKUP(A15,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -14487,7 +14487,7 @@
       </c>
       <c r="AS16" s="129">
         <f>(VLOOKUP(B16,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.79709999999999992</v>
+        <v>0.80740000000000001</v>
       </c>
       <c r="AT16" s="14">
         <f t="shared" si="48"/>
@@ -14495,7 +14495,7 @@
       </c>
       <c r="AU16" s="54">
         <f t="shared" si="49"/>
-        <v>0.17290000000000005</v>
+        <v>0.16259999999999997</v>
       </c>
       <c r="AV16" s="57">
         <f>VLOOKUP(A16,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -14579,11 +14579,11 @@
       </c>
       <c r="C19" s="142">
         <f ca="1">SUMIF(cuoc!A7:P27,'tiến độ'!A19,cuoc!M7:M27)</f>
-        <v>482839706</v>
+        <v>489669973</v>
       </c>
       <c r="D19" s="142">
         <f ca="1">B19*0.968-C19</f>
-        <v>140334365.25599992</v>
+        <v>133504098.25599992</v>
       </c>
       <c r="E19" s="137"/>
       <c r="H19" s="137"/>
@@ -14600,11 +14600,11 @@
       </c>
       <c r="C20" s="143">
         <f ca="1">SUMIF(cuoc!A8:P27,'tiến độ'!A20,cuoc!M8:M27)</f>
-        <v>835585327</v>
+        <v>857855141</v>
       </c>
       <c r="D20" s="142">
         <f ca="1">B20*0.968-C20</f>
-        <v>210990478.704</v>
+        <v>188720664.704</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.45">
@@ -14790,11 +14790,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="D1:S1"/>
-    <mergeCell ref="D2:G2"/>
-    <mergeCell ref="H2:K2"/>
-    <mergeCell ref="L2:O2"/>
-    <mergeCell ref="P2:S2"/>
     <mergeCell ref="X2:AA2"/>
     <mergeCell ref="AB2:AE2"/>
     <mergeCell ref="AF2:AI2"/>
@@ -14808,6 +14803,11 @@
     <mergeCell ref="AJ2:AM2"/>
     <mergeCell ref="AN2:AQ2"/>
     <mergeCell ref="T2:W2"/>
+    <mergeCell ref="D1:S1"/>
+    <mergeCell ref="D2:G2"/>
+    <mergeCell ref="H2:K2"/>
+    <mergeCell ref="L2:O2"/>
+    <mergeCell ref="P2:S2"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="F4:F16">
@@ -23283,12 +23283,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="X5:AE5"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="H5:O5"/>
-    <mergeCell ref="P5:W5"/>
     <mergeCell ref="CB5:CI5"/>
     <mergeCell ref="CJ5:CQ5"/>
     <mergeCell ref="CR5:CY5"/>
@@ -23299,6 +23293,12 @@
     <mergeCell ref="BD5:BK5"/>
     <mergeCell ref="BL5:BS5"/>
     <mergeCell ref="BT5:CA5"/>
+    <mergeCell ref="X5:AE5"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="H5:O5"/>
+    <mergeCell ref="P5:W5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -23396,7 +23396,7 @@
       <c r="A3" s="100" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="243" t="s">
+      <c r="B3" s="245" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="101" t="s">
@@ -23408,70 +23408,70 @@
       <c r="E3" s="247" t="s">
         <v>202</v>
       </c>
-      <c r="F3" s="245" t="s">
+      <c r="F3" s="243" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="245" t="s">
+      <c r="G3" s="243" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="245" t="s">
+      <c r="H3" s="243" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="245" t="s">
+      <c r="I3" s="243" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="245" t="s">
+      <c r="J3" s="243" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="245" t="s">
+      <c r="K3" s="243" t="s">
         <v>11</v>
       </c>
-      <c r="L3" s="245" t="s">
+      <c r="L3" s="243" t="s">
         <v>12</v>
       </c>
-      <c r="M3" s="245" t="s">
+      <c r="M3" s="243" t="s">
         <v>203</v>
       </c>
-      <c r="N3" s="245" t="s">
+      <c r="N3" s="243" t="s">
         <v>286</v>
       </c>
-      <c r="O3" s="245" t="s">
+      <c r="O3" s="243" t="s">
         <v>14</v>
       </c>
-      <c r="P3" s="245" t="s">
+      <c r="P3" s="243" t="s">
         <v>15</v>
       </c>
-      <c r="Q3" s="245" t="s">
+      <c r="Q3" s="243" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="245" t="s">
+      <c r="R3" s="243" t="s">
         <v>17</v>
       </c>
-      <c r="S3" s="245" t="s">
+      <c r="S3" s="243" t="s">
         <v>18</v>
       </c>
       <c r="T3" s="99"/>
     </row>
     <row r="4" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="100"/>
-      <c r="B4" s="244"/>
+      <c r="B4" s="246"/>
       <c r="C4" s="101"/>
       <c r="D4" s="101"/>
       <c r="E4" s="248"/>
-      <c r="F4" s="246"/>
-      <c r="G4" s="246"/>
-      <c r="H4" s="246"/>
-      <c r="I4" s="246"/>
-      <c r="J4" s="246"/>
-      <c r="K4" s="246"/>
-      <c r="L4" s="246"/>
-      <c r="M4" s="246"/>
-      <c r="N4" s="246"/>
-      <c r="O4" s="246"/>
-      <c r="P4" s="246"/>
-      <c r="Q4" s="246"/>
-      <c r="R4" s="246"/>
-      <c r="S4" s="246"/>
+      <c r="F4" s="244"/>
+      <c r="G4" s="244"/>
+      <c r="H4" s="244"/>
+      <c r="I4" s="244"/>
+      <c r="J4" s="244"/>
+      <c r="K4" s="244"/>
+      <c r="L4" s="244"/>
+      <c r="M4" s="244"/>
+      <c r="N4" s="244"/>
+      <c r="O4" s="244"/>
+      <c r="P4" s="244"/>
+      <c r="Q4" s="244"/>
+      <c r="R4" s="244"/>
+      <c r="S4" s="244"/>
       <c r="T4" s="99"/>
     </row>
     <row r="5" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.45">
@@ -24789,12 +24789,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="S3:S4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="R3:R4"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="H3:H4"/>
@@ -24805,6 +24799,12 @@
     <mergeCell ref="K3:K4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="E3:E4"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="S3:S4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="R3:R4"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.69991251615088756" right="0.69991251615088756" top="0.74990626395218019" bottom="0.74990626395218019" header="0.29996251027415122" footer="0.29996251027415122"/>
@@ -26080,68 +26080,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:48" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="258" t="s">
+      <c r="A1" s="256" t="s">
         <v>240</v>
       </c>
-      <c r="B1" s="258"/>
-      <c r="C1" s="258"/>
-      <c r="D1" s="258"/>
-      <c r="E1" s="258"/>
-      <c r="F1" s="258"/>
-      <c r="G1" s="258"/>
-      <c r="H1" s="258"/>
-      <c r="I1" s="258"/>
-      <c r="J1" s="258"/>
-      <c r="K1" s="258"/>
-      <c r="M1" s="261" t="s">
+      <c r="B1" s="256"/>
+      <c r="C1" s="256"/>
+      <c r="D1" s="256"/>
+      <c r="E1" s="256"/>
+      <c r="F1" s="256"/>
+      <c r="G1" s="256"/>
+      <c r="H1" s="256"/>
+      <c r="I1" s="256"/>
+      <c r="J1" s="256"/>
+      <c r="K1" s="256"/>
+      <c r="M1" s="259" t="s">
         <v>241</v>
       </c>
-      <c r="N1" s="261"/>
-      <c r="O1" s="261"/>
-      <c r="P1" s="261"/>
-      <c r="Q1" s="261"/>
-      <c r="R1" s="261"/>
-      <c r="S1" s="261"/>
-      <c r="T1" s="261"/>
-      <c r="U1" s="261"/>
-      <c r="V1" s="261"/>
-      <c r="W1" s="261"/>
-      <c r="X1" s="261"/>
-      <c r="Y1" s="261"/>
-      <c r="Z1" s="261"/>
+      <c r="N1" s="259"/>
+      <c r="O1" s="259"/>
+      <c r="P1" s="259"/>
+      <c r="Q1" s="259"/>
+      <c r="R1" s="259"/>
+      <c r="S1" s="259"/>
+      <c r="T1" s="259"/>
+      <c r="U1" s="259"/>
+      <c r="V1" s="259"/>
+      <c r="W1" s="259"/>
+      <c r="X1" s="259"/>
+      <c r="Y1" s="259"/>
+      <c r="Z1" s="259"/>
     </row>
     <row r="2" spans="1:48" ht="24.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="259"/>
-      <c r="B2" s="259"/>
-      <c r="C2" s="259"/>
-      <c r="D2" s="259"/>
-      <c r="E2" s="259"/>
-      <c r="F2" s="259"/>
-      <c r="G2" s="259"/>
-      <c r="H2" s="259"/>
-      <c r="I2" s="259"/>
-      <c r="J2" s="259"/>
-      <c r="K2" s="259"/>
-      <c r="M2" s="262"/>
-      <c r="N2" s="262"/>
-      <c r="O2" s="262"/>
-      <c r="P2" s="262"/>
-      <c r="Q2" s="262"/>
-      <c r="R2" s="262"/>
-      <c r="S2" s="262"/>
-      <c r="T2" s="262"/>
-      <c r="U2" s="262"/>
-      <c r="V2" s="262"/>
-      <c r="W2" s="262"/>
-      <c r="X2" s="262"/>
-      <c r="Y2" s="262"/>
-      <c r="Z2" s="262"/>
+      <c r="A2" s="257"/>
+      <c r="B2" s="257"/>
+      <c r="C2" s="257"/>
+      <c r="D2" s="257"/>
+      <c r="E2" s="257"/>
+      <c r="F2" s="257"/>
+      <c r="G2" s="257"/>
+      <c r="H2" s="257"/>
+      <c r="I2" s="257"/>
+      <c r="J2" s="257"/>
+      <c r="K2" s="257"/>
+      <c r="M2" s="260"/>
+      <c r="N2" s="260"/>
+      <c r="O2" s="260"/>
+      <c r="P2" s="260"/>
+      <c r="Q2" s="260"/>
+      <c r="R2" s="260"/>
+      <c r="S2" s="260"/>
+      <c r="T2" s="260"/>
+      <c r="U2" s="260"/>
+      <c r="V2" s="260"/>
+      <c r="W2" s="260"/>
+      <c r="X2" s="260"/>
+      <c r="Y2" s="260"/>
+      <c r="Z2" s="260"/>
     </row>
     <row r="3" spans="1:48" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="255" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="256" t="s">
+      <c r="A3" s="253" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="254" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="28" t="s">
@@ -26171,70 +26171,70 @@
       <c r="K3" s="28" t="s">
         <v>249</v>
       </c>
-      <c r="M3" s="260" t="s">
+      <c r="M3" s="258" t="s">
         <v>34</v>
       </c>
-      <c r="N3" s="202" t="s">
+      <c r="N3" s="204" t="s">
         <v>250</v>
       </c>
-      <c r="O3" s="203"/>
-      <c r="P3" s="203"/>
-      <c r="Q3" s="203"/>
-      <c r="R3" s="253" t="s">
+      <c r="O3" s="205"/>
+      <c r="P3" s="205"/>
+      <c r="Q3" s="205"/>
+      <c r="R3" s="261" t="s">
         <v>251</v>
       </c>
-      <c r="S3" s="202" t="s">
+      <c r="S3" s="204" t="s">
         <v>252</v>
       </c>
-      <c r="T3" s="203"/>
-      <c r="U3" s="203"/>
-      <c r="V3" s="203"/>
-      <c r="W3" s="253" t="s">
+      <c r="T3" s="205"/>
+      <c r="U3" s="205"/>
+      <c r="V3" s="205"/>
+      <c r="W3" s="261" t="s">
         <v>251</v>
       </c>
-      <c r="X3" s="215" t="s">
+      <c r="X3" s="207" t="s">
         <v>41</v>
       </c>
-      <c r="Y3" s="216"/>
-      <c r="Z3" s="216"/>
-      <c r="AA3" s="253" t="s">
+      <c r="Y3" s="208"/>
+      <c r="Z3" s="208"/>
+      <c r="AA3" s="261" t="s">
         <v>251</v>
       </c>
       <c r="AB3" s="71"/>
-      <c r="AC3" s="202" t="s">
+      <c r="AC3" s="204" t="s">
         <v>42</v>
       </c>
-      <c r="AD3" s="203"/>
-      <c r="AE3" s="203"/>
-      <c r="AF3" s="203"/>
-      <c r="AG3" s="202" t="s">
+      <c r="AD3" s="205"/>
+      <c r="AE3" s="205"/>
+      <c r="AF3" s="205"/>
+      <c r="AG3" s="204" t="s">
         <v>43</v>
       </c>
-      <c r="AH3" s="203"/>
-      <c r="AI3" s="203"/>
-      <c r="AJ3" s="203"/>
-      <c r="AK3" s="202" t="s">
+      <c r="AH3" s="205"/>
+      <c r="AI3" s="205"/>
+      <c r="AJ3" s="205"/>
+      <c r="AK3" s="204" t="s">
         <v>44</v>
       </c>
-      <c r="AL3" s="203"/>
-      <c r="AM3" s="203"/>
-      <c r="AN3" s="203"/>
-      <c r="AO3" s="202" t="s">
+      <c r="AL3" s="205"/>
+      <c r="AM3" s="205"/>
+      <c r="AN3" s="205"/>
+      <c r="AO3" s="204" t="s">
         <v>46</v>
       </c>
-      <c r="AP3" s="203"/>
-      <c r="AQ3" s="203"/>
-      <c r="AR3" s="203"/>
-      <c r="AS3" s="202" t="s">
+      <c r="AP3" s="205"/>
+      <c r="AQ3" s="205"/>
+      <c r="AR3" s="205"/>
+      <c r="AS3" s="204" t="s">
         <v>47</v>
       </c>
-      <c r="AT3" s="203"/>
-      <c r="AU3" s="203"/>
-      <c r="AV3" s="203"/>
+      <c r="AT3" s="205"/>
+      <c r="AU3" s="205"/>
+      <c r="AV3" s="205"/>
     </row>
     <row r="4" spans="1:48" ht="22.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="255"/>
-      <c r="B4" s="257"/>
+      <c r="A4" s="253"/>
+      <c r="B4" s="255"/>
       <c r="C4" s="24">
         <f t="shared" ref="C4:K4" si="0">SUM(C5:C19)</f>
         <v>15</v>
@@ -26271,7 +26271,7 @@
         <f t="shared" si="0"/>
         <v>134</v>
       </c>
-      <c r="M4" s="260"/>
+      <c r="M4" s="258"/>
       <c r="N4" s="8" t="s">
         <v>2</v>
       </c>
@@ -26284,7 +26284,7 @@
       <c r="Q4" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="R4" s="254"/>
+      <c r="R4" s="262"/>
       <c r="S4" s="8" t="s">
         <v>2</v>
       </c>
@@ -26297,7 +26297,7 @@
       <c r="V4" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="W4" s="254"/>
+      <c r="W4" s="262"/>
       <c r="X4" s="8" t="s">
         <v>2</v>
       </c>
@@ -26307,7 +26307,7 @@
       <c r="Z4" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="AA4" s="254"/>
+      <c r="AA4" s="262"/>
       <c r="AB4" s="51" t="s">
         <v>59</v>
       </c>
@@ -28696,12 +28696,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="A1:K2"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="N3:Q3"/>
-    <mergeCell ref="M1:Z2"/>
     <mergeCell ref="AS3:AV3"/>
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="W3:W4"/>
@@ -28712,6 +28706,12 @@
     <mergeCell ref="AK3:AN3"/>
     <mergeCell ref="AO3:AR3"/>
     <mergeCell ref="S3:V3"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="A1:K2"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="N3:Q3"/>
+    <mergeCell ref="M1:Z2"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="P5:P20">
@@ -28851,44 +28851,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="265"/>
-      <c r="B1" s="265"/>
-      <c r="C1" s="265"/>
-      <c r="D1" s="265"/>
-      <c r="E1" s="265"/>
-      <c r="F1" s="265"/>
-      <c r="G1" s="265"/>
-      <c r="H1" s="265"/>
-      <c r="I1" s="265"/>
-      <c r="J1" s="265"/>
-      <c r="K1" s="265"/>
-      <c r="L1" s="265"/>
-      <c r="M1" s="265"/>
-      <c r="N1" s="265"/>
-      <c r="O1" s="265"/>
-      <c r="P1" s="265"/>
+      <c r="A1" s="263"/>
+      <c r="B1" s="263"/>
+      <c r="C1" s="263"/>
+      <c r="D1" s="263"/>
+      <c r="E1" s="263"/>
+      <c r="F1" s="263"/>
+      <c r="G1" s="263"/>
+      <c r="H1" s="263"/>
+      <c r="I1" s="263"/>
+      <c r="J1" s="263"/>
+      <c r="K1" s="263"/>
+      <c r="L1" s="263"/>
+      <c r="M1" s="263"/>
+      <c r="N1" s="263"/>
+      <c r="O1" s="263"/>
+      <c r="P1" s="263"/>
     </row>
     <row r="2" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="266"/>
-      <c r="B2" s="266"/>
-      <c r="C2" s="266"/>
-      <c r="D2" s="266"/>
-      <c r="E2" s="266"/>
-      <c r="F2" s="266"/>
-      <c r="G2" s="266"/>
-      <c r="H2" s="266"/>
-      <c r="I2" s="266"/>
-      <c r="J2" s="266"/>
-      <c r="K2" s="266"/>
-      <c r="L2" s="266"/>
-      <c r="M2" s="266"/>
-      <c r="N2" s="266"/>
-      <c r="O2" s="266"/>
-      <c r="P2" s="266"/>
+      <c r="A2" s="264"/>
+      <c r="B2" s="264"/>
+      <c r="C2" s="264"/>
+      <c r="D2" s="264"/>
+      <c r="E2" s="264"/>
+      <c r="F2" s="264"/>
+      <c r="G2" s="264"/>
+      <c r="H2" s="264"/>
+      <c r="I2" s="264"/>
+      <c r="J2" s="264"/>
+      <c r="K2" s="264"/>
+      <c r="L2" s="264"/>
+      <c r="M2" s="264"/>
+      <c r="N2" s="264"/>
+      <c r="O2" s="264"/>
+      <c r="P2" s="264"/>
     </row>
     <row r="3" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="267"/>
-      <c r="B3" s="267"/>
+      <c r="A3" s="265"/>
+      <c r="B3" s="265"/>
       <c r="C3" s="133"/>
       <c r="D3" s="133"/>
       <c r="E3" s="133"/>
@@ -28905,10 +28905,10 @@
       <c r="P3" s="133"/>
     </row>
     <row r="4" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="269" t="s">
+      <c r="A4" s="267" t="s">
         <v>255</v>
       </c>
-      <c r="B4" s="269" t="s">
+      <c r="B4" s="267" t="s">
         <v>39</v>
       </c>
       <c r="C4" s="141"/>
@@ -28916,70 +28916,70 @@
       <c r="E4" s="141"/>
       <c r="F4" s="141"/>
       <c r="G4" s="141"/>
-      <c r="H4" s="268"/>
-      <c r="I4" s="268"/>
-      <c r="J4" s="268"/>
-      <c r="K4" s="268"/>
-      <c r="L4" s="268"/>
-      <c r="M4" s="268"/>
-      <c r="N4" s="268"/>
-      <c r="O4" s="268"/>
-      <c r="P4" s="268"/>
+      <c r="H4" s="266"/>
+      <c r="I4" s="266"/>
+      <c r="J4" s="266"/>
+      <c r="K4" s="266"/>
+      <c r="L4" s="266"/>
+      <c r="M4" s="266"/>
+      <c r="N4" s="266"/>
+      <c r="O4" s="266"/>
+      <c r="P4" s="266"/>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A5" s="272"/>
-      <c r="B5" s="272"/>
-      <c r="C5" s="269" t="s">
+      <c r="A5" s="270"/>
+      <c r="B5" s="270"/>
+      <c r="C5" s="267" t="s">
         <v>256</v>
       </c>
-      <c r="D5" s="269" t="s">
+      <c r="D5" s="267" t="s">
         <v>257</v>
       </c>
-      <c r="E5" s="270"/>
-      <c r="F5" s="269" t="s">
+      <c r="E5" s="268"/>
+      <c r="F5" s="267" t="s">
         <v>258</v>
       </c>
-      <c r="G5" s="270"/>
-      <c r="H5" s="269" t="s">
+      <c r="G5" s="268"/>
+      <c r="H5" s="267" t="s">
         <v>259</v>
       </c>
-      <c r="I5" s="270"/>
-      <c r="J5" s="269" t="s">
+      <c r="I5" s="268"/>
+      <c r="J5" s="267" t="s">
         <v>260</v>
       </c>
-      <c r="K5" s="270"/>
-      <c r="L5" s="273" t="s">
+      <c r="K5" s="268"/>
+      <c r="L5" s="271" t="s">
         <v>261</v>
       </c>
-      <c r="M5" s="270"/>
-      <c r="N5" s="268" t="s">
+      <c r="M5" s="268"/>
+      <c r="N5" s="266" t="s">
         <v>262</v>
       </c>
-      <c r="O5" s="274"/>
-      <c r="P5" s="269" t="s">
+      <c r="O5" s="272"/>
+      <c r="P5" s="267" t="s">
         <v>266</v>
       </c>
-      <c r="R5" s="263" t="s">
+      <c r="R5" s="273" t="s">
         <v>34</v>
       </c>
-      <c r="S5" s="263" t="s">
+      <c r="S5" s="273" t="s">
         <v>289</v>
       </c>
-      <c r="T5" s="263" t="s">
+      <c r="T5" s="273" t="s">
         <v>290</v>
       </c>
-      <c r="U5" s="263" t="s">
+      <c r="U5" s="273" t="s">
         <v>292</v>
       </c>
-      <c r="V5" s="264" t="s">
+      <c r="V5" s="274" t="s">
         <v>291</v>
       </c>
       <c r="W5" s="172"/>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A6" s="271"/>
-      <c r="B6" s="271"/>
-      <c r="C6" s="272"/>
+      <c r="A6" s="269"/>
+      <c r="B6" s="269"/>
+      <c r="C6" s="270"/>
       <c r="D6" s="134" t="s">
         <v>2</v>
       </c>
@@ -29016,12 +29016,12 @@
       <c r="O6" s="134" t="s">
         <v>263</v>
       </c>
-      <c r="P6" s="271"/>
-      <c r="R6" s="263"/>
-      <c r="S6" s="263"/>
-      <c r="T6" s="263"/>
-      <c r="U6" s="263"/>
-      <c r="V6" s="263"/>
+      <c r="P6" s="269"/>
+      <c r="R6" s="273"/>
+      <c r="S6" s="273"/>
+      <c r="T6" s="273"/>
+      <c r="U6" s="273"/>
+      <c r="V6" s="273"/>
       <c r="W6" s="172"/>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.45">
@@ -29053,26 +29053,26 @@
         <v>70243418</v>
       </c>
       <c r="J7" s="191">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="K7" s="191">
-        <v>2938520</v>
+        <v>4265641</v>
       </c>
       <c r="L7" s="191">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="M7" s="191">
-        <v>60467385</v>
+        <v>61794506</v>
       </c>
       <c r="N7" s="192">
-        <v>86.12</v>
+        <v>88.55</v>
       </c>
       <c r="O7" s="192">
-        <v>86.08</v>
+        <v>87.97</v>
       </c>
       <c r="P7" s="135">
         <f>I7*0.97-M7</f>
-        <v>7668730.4599999934</v>
+        <v>6341609.4599999934</v>
       </c>
       <c r="R7" s="173" t="s">
         <v>117</v>
@@ -29086,11 +29086,11 @@
       </c>
       <c r="U7" s="189">
         <f>VLOOKUP(R7,$C$7:$P$27,14,0)</f>
-        <v>19090002.799999997</v>
+        <v>17116720.799999997</v>
       </c>
       <c r="V7" s="175">
         <f>VLOOKUP(R7,$C$7:$P$27,14,0)-T7</f>
-        <v>-4149487</v>
+        <v>-6122769</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.45">
@@ -29122,26 +29122,26 @@
         <v>72573808</v>
       </c>
       <c r="J8" s="194">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K8" s="194">
-        <v>2181875</v>
+        <v>2760329</v>
       </c>
       <c r="L8" s="194">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="M8" s="194">
-        <v>62449684</v>
+        <v>63028138</v>
       </c>
       <c r="N8" s="195">
-        <v>88.25</v>
+        <v>89.4</v>
       </c>
       <c r="O8" s="195">
-        <v>86.05</v>
+        <v>86.85</v>
       </c>
       <c r="P8" s="135">
         <f t="shared" ref="P8:P27" si="0">I8*0.97-M8</f>
-        <v>7946909.7600000054</v>
+        <v>7368455.7600000054</v>
       </c>
       <c r="R8" s="173" t="s">
         <v>67</v>
@@ -29155,28 +29155,28 @@
       </c>
       <c r="U8" s="189">
         <f t="shared" ref="U8:U17" si="2">VLOOKUP(R8,$C$7:$P$27,14,0)</f>
-        <v>19955680.310000002</v>
+        <v>18332228.310000002</v>
       </c>
       <c r="V8" s="175">
         <f t="shared" ref="V8:V17" si="3">VLOOKUP(R8,$C$7:$P$27,14,0)-T8</f>
-        <v>-4602401</v>
+        <v>-6225853</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A9" s="190" t="s">
-        <v>128</v>
+        <v>179</v>
       </c>
       <c r="B9" s="190" t="s">
-        <v>66</v>
+        <v>288</v>
       </c>
       <c r="C9" s="190" t="s">
-        <v>67</v>
+        <v>284</v>
       </c>
       <c r="D9" s="191">
-        <v>876</v>
+        <v>318</v>
       </c>
       <c r="E9" s="191">
-        <v>145101823</v>
+        <v>50351985</v>
       </c>
       <c r="F9" s="191">
         <v>0</v>
@@ -29185,32 +29185,32 @@
         <v>0</v>
       </c>
       <c r="H9" s="191">
-        <v>876</v>
+        <v>318</v>
       </c>
       <c r="I9" s="191">
-        <v>145101823</v>
+        <v>50351985</v>
       </c>
       <c r="J9" s="191">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="K9" s="191">
-        <v>5912360</v>
+        <v>5920895</v>
       </c>
       <c r="L9" s="191">
-        <v>718</v>
+        <v>261</v>
       </c>
       <c r="M9" s="191">
-        <v>120793088</v>
+        <v>42943093</v>
       </c>
       <c r="N9" s="192">
-        <v>81.96</v>
+        <v>82.08</v>
       </c>
       <c r="O9" s="192">
-        <v>83.25</v>
+        <v>85.29</v>
       </c>
       <c r="P9" s="135">
         <f t="shared" si="0"/>
-        <v>19955680.310000002</v>
+        <v>5898332.4499999955</v>
       </c>
       <c r="R9" s="174" t="s">
         <v>87</v>
@@ -29224,28 +29224,28 @@
       </c>
       <c r="U9" s="189">
         <f t="shared" si="2"/>
-        <v>32219020.270000011</v>
+        <v>30707826.270000011</v>
       </c>
       <c r="V9" s="175">
         <f t="shared" si="3"/>
-        <v>-3740558</v>
+        <v>-5251752</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A10" s="193" t="s">
-        <v>179</v>
+        <v>128</v>
       </c>
       <c r="B10" s="193" t="s">
-        <v>104</v>
+        <v>66</v>
       </c>
       <c r="C10" s="193" t="s">
-        <v>105</v>
+        <v>67</v>
       </c>
       <c r="D10" s="194">
-        <v>716</v>
+        <v>876</v>
       </c>
       <c r="E10" s="194">
-        <v>116427734</v>
+        <v>145101823</v>
       </c>
       <c r="F10" s="194">
         <v>0</v>
@@ -29254,32 +29254,32 @@
         <v>0</v>
       </c>
       <c r="H10" s="194">
-        <v>716</v>
+        <v>876</v>
       </c>
       <c r="I10" s="194">
-        <v>116427734</v>
+        <v>145101823</v>
       </c>
       <c r="J10" s="194">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="K10" s="194">
-        <v>6819495</v>
+        <v>7535812</v>
       </c>
       <c r="L10" s="194">
-        <v>576</v>
+        <v>728</v>
       </c>
       <c r="M10" s="194">
-        <v>96242471</v>
+        <v>122416540</v>
       </c>
       <c r="N10" s="195">
-        <v>80.45</v>
+        <v>83.11</v>
       </c>
       <c r="O10" s="195">
-        <v>82.66</v>
+        <v>84.37</v>
       </c>
       <c r="P10" s="135">
         <f t="shared" si="0"/>
-        <v>16692430.980000004</v>
+        <v>18332228.310000002</v>
       </c>
       <c r="R10" s="174" t="s">
         <v>110</v>
@@ -29293,11 +29293,11 @@
       </c>
       <c r="U10" s="189">
         <f t="shared" si="2"/>
-        <v>43813145.859999985</v>
+        <v>42404016.859999985</v>
       </c>
       <c r="V10" s="175">
         <f t="shared" si="3"/>
-        <v>-2373097</v>
+        <v>-3782226</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.45">
@@ -29305,16 +29305,16 @@
         <v>179</v>
       </c>
       <c r="B11" s="190" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="C11" s="190" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="D11" s="191">
-        <v>356</v>
+        <v>716</v>
       </c>
       <c r="E11" s="191">
-        <v>53605661</v>
+        <v>116427734</v>
       </c>
       <c r="F11" s="191">
         <v>0</v>
@@ -29323,32 +29323,32 @@
         <v>0</v>
       </c>
       <c r="H11" s="191">
-        <v>356</v>
+        <v>716</v>
       </c>
       <c r="I11" s="191">
-        <v>53605661</v>
+        <v>116427734</v>
       </c>
       <c r="J11" s="191">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="K11" s="191">
-        <v>4547499</v>
+        <v>8397670</v>
       </c>
       <c r="L11" s="191">
-        <v>281</v>
+        <v>587</v>
       </c>
       <c r="M11" s="191">
-        <v>44127379</v>
+        <v>97820646</v>
       </c>
       <c r="N11" s="192">
-        <v>78.930000000000007</v>
+        <v>81.98</v>
       </c>
       <c r="O11" s="192">
-        <v>82.32</v>
+        <v>84.02</v>
       </c>
       <c r="P11" s="135">
         <f t="shared" si="0"/>
-        <v>7870112.1700000018</v>
+        <v>15114255.980000004</v>
       </c>
       <c r="R11" s="173" t="s">
         <v>99</v>
@@ -29362,28 +29362,28 @@
       </c>
       <c r="U11" s="189">
         <f t="shared" si="2"/>
-        <v>26544065.75</v>
+        <v>26230855.75</v>
       </c>
       <c r="V11" s="175">
         <f t="shared" si="3"/>
-        <v>-2956675</v>
+        <v>-3269885</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A12" s="193" t="s">
-        <v>179</v>
+        <v>129</v>
       </c>
       <c r="B12" s="193" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C12" s="193" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="D12" s="194">
-        <v>559</v>
+        <v>1048</v>
       </c>
       <c r="E12" s="194">
-        <v>93597302</v>
+        <v>180440547</v>
       </c>
       <c r="F12" s="194">
         <v>0</v>
@@ -29392,32 +29392,32 @@
         <v>0</v>
       </c>
       <c r="H12" s="194">
-        <v>559</v>
+        <v>1048</v>
       </c>
       <c r="I12" s="194">
-        <v>93597302</v>
+        <v>180440547</v>
       </c>
       <c r="J12" s="194">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="K12" s="194">
-        <v>4817593</v>
+        <v>10913215</v>
       </c>
       <c r="L12" s="194">
-        <v>450</v>
+        <v>859</v>
       </c>
       <c r="M12" s="194">
-        <v>76868245</v>
+        <v>151013262</v>
       </c>
       <c r="N12" s="195">
-        <v>80.5</v>
+        <v>81.97</v>
       </c>
       <c r="O12" s="195">
-        <v>82.13</v>
+        <v>83.69</v>
       </c>
       <c r="P12" s="135">
         <f t="shared" si="0"/>
-        <v>13921137.939999998</v>
+        <v>24014068.590000004</v>
       </c>
       <c r="R12" s="173" t="s">
         <v>75</v>
@@ -29431,28 +29431,28 @@
       </c>
       <c r="U12" s="189">
         <f t="shared" si="2"/>
-        <v>26783206.520000011</v>
+        <v>23492697.520000011</v>
       </c>
       <c r="V12" s="175">
         <f t="shared" si="3"/>
-        <v>-4413897</v>
+        <v>-7704406</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A13" s="190" t="s">
-        <v>129</v>
+        <v>179</v>
       </c>
       <c r="B13" s="190" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="C13" s="190" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="D13" s="191">
-        <v>1048</v>
+        <v>308</v>
       </c>
       <c r="E13" s="191">
-        <v>180440547</v>
+        <v>51982396</v>
       </c>
       <c r="F13" s="191">
         <v>0</v>
@@ -29461,32 +29461,32 @@
         <v>0</v>
       </c>
       <c r="H13" s="191">
-        <v>1048</v>
+        <v>308</v>
       </c>
       <c r="I13" s="191">
-        <v>180440547</v>
+        <v>51982396</v>
       </c>
       <c r="J13" s="191">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="K13" s="191">
-        <v>7863074</v>
+        <v>3001015</v>
       </c>
       <c r="L13" s="191">
-        <v>841</v>
+        <v>254</v>
       </c>
       <c r="M13" s="191">
-        <v>147963121</v>
+        <v>43395854</v>
       </c>
       <c r="N13" s="192">
-        <v>80.25</v>
+        <v>82.47</v>
       </c>
       <c r="O13" s="192">
-        <v>82</v>
+        <v>83.48</v>
       </c>
       <c r="P13" s="135">
         <f t="shared" si="0"/>
-        <v>27064209.590000004</v>
+        <v>7027070.1199999973</v>
       </c>
       <c r="R13" s="173" t="s">
         <v>107</v>
@@ -29500,11 +29500,11 @@
       </c>
       <c r="U13" s="189">
         <f t="shared" si="2"/>
-        <v>27064209.590000004</v>
+        <v>24014068.590000004</v>
       </c>
       <c r="V13" s="175">
         <f t="shared" si="3"/>
-        <v>-4771798</v>
+        <v>-7821939</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.45">
@@ -29512,16 +29512,16 @@
         <v>179</v>
       </c>
       <c r="B14" s="193" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C14" s="193" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="D14" s="194">
-        <v>308</v>
+        <v>559</v>
       </c>
       <c r="E14" s="194">
-        <v>51982396</v>
+        <v>93597302</v>
       </c>
       <c r="F14" s="194">
         <v>0</v>
@@ -29530,32 +29530,32 @@
         <v>0</v>
       </c>
       <c r="H14" s="194">
-        <v>308</v>
+        <v>559</v>
       </c>
       <c r="I14" s="194">
-        <v>51982396</v>
+        <v>93597302</v>
       </c>
       <c r="J14" s="194">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="K14" s="194">
-        <v>2151835</v>
+        <v>5828410</v>
       </c>
       <c r="L14" s="194">
-        <v>249</v>
+        <v>456</v>
       </c>
       <c r="M14" s="194">
-        <v>42546674</v>
+        <v>77879062</v>
       </c>
       <c r="N14" s="195">
-        <v>80.84</v>
+        <v>81.569999999999993</v>
       </c>
       <c r="O14" s="195">
-        <v>81.849999999999994</v>
+        <v>83.21</v>
       </c>
       <c r="P14" s="135">
         <f t="shared" si="0"/>
-        <v>7876250.1199999973</v>
+        <v>12910320.939999998</v>
       </c>
       <c r="R14" s="174" t="s">
         <v>72</v>
@@ -29569,28 +29569,28 @@
       </c>
       <c r="U14" s="189">
         <f t="shared" si="2"/>
-        <v>34439517.199999988</v>
+        <v>31740385.199999988</v>
       </c>
       <c r="V14" s="175">
         <f t="shared" si="3"/>
-        <v>-7273392</v>
+        <v>-9972524</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A15" s="190" t="s">
-        <v>129</v>
+        <v>179</v>
       </c>
       <c r="B15" s="190" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="C15" s="190" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="D15" s="191">
-        <v>683</v>
+        <v>356</v>
       </c>
       <c r="E15" s="191">
-        <v>105983346</v>
+        <v>53605661</v>
       </c>
       <c r="F15" s="191">
         <v>0</v>
@@ -29599,32 +29599,32 @@
         <v>0</v>
       </c>
       <c r="H15" s="191">
-        <v>683</v>
+        <v>356</v>
       </c>
       <c r="I15" s="191">
-        <v>105983346</v>
+        <v>53605661</v>
       </c>
       <c r="J15" s="191">
-        <v>262</v>
+        <v>40</v>
       </c>
       <c r="K15" s="191">
-        <v>41299032</v>
+        <v>4972415</v>
       </c>
       <c r="L15" s="191">
-        <v>540</v>
+        <v>286</v>
       </c>
       <c r="M15" s="191">
-        <v>85142346</v>
+        <v>44552295</v>
       </c>
       <c r="N15" s="192">
-        <v>79.06</v>
+        <v>80.34</v>
       </c>
       <c r="O15" s="192">
-        <v>80.34</v>
+        <v>83.11</v>
       </c>
       <c r="P15" s="135">
         <f t="shared" si="0"/>
-        <v>17661499.61999999</v>
+        <v>7445196.1700000018</v>
       </c>
       <c r="R15" s="174" t="s">
         <v>113</v>
@@ -29638,11 +29638,11 @@
       </c>
       <c r="U15" s="189">
         <f t="shared" si="2"/>
-        <v>54473782.400000006</v>
+        <v>47005029.400000006</v>
       </c>
       <c r="V15" s="175">
         <f t="shared" si="3"/>
-        <v>-5160024</v>
+        <v>-12628777</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.45">
@@ -29650,16 +29650,16 @@
         <v>129</v>
       </c>
       <c r="B16" s="193" t="s">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="C16" s="193" t="s">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="D16" s="194">
-        <v>1181</v>
+        <v>683</v>
       </c>
       <c r="E16" s="194">
-        <v>189656153</v>
+        <v>105983346</v>
       </c>
       <c r="F16" s="194">
         <v>0</v>
@@ -29668,32 +29668,32 @@
         <v>0</v>
       </c>
       <c r="H16" s="194">
-        <v>1181</v>
+        <v>683</v>
       </c>
       <c r="I16" s="194">
-        <v>189656153</v>
+        <v>105983346</v>
       </c>
       <c r="J16" s="194">
-        <v>48</v>
+        <v>273</v>
       </c>
       <c r="K16" s="194">
-        <v>6757771</v>
+        <v>42777833</v>
       </c>
       <c r="L16" s="194">
-        <v>927</v>
+        <v>551</v>
       </c>
       <c r="M16" s="194">
-        <v>151182440</v>
+        <v>86621147</v>
       </c>
       <c r="N16" s="195">
-        <v>78.489999999999995</v>
+        <v>80.67</v>
       </c>
       <c r="O16" s="195">
-        <v>79.709999999999994</v>
+        <v>81.73</v>
       </c>
       <c r="P16" s="135">
         <f t="shared" si="0"/>
-        <v>32784028.409999996</v>
+        <v>16182698.61999999</v>
       </c>
       <c r="R16" s="174" t="s">
         <v>119</v>
@@ -29707,11 +29707,11 @@
       </c>
       <c r="U16" s="189">
         <f t="shared" si="2"/>
-        <v>32784028.409999996</v>
+        <v>30837114.409999996</v>
       </c>
       <c r="V16" s="175">
         <f t="shared" si="3"/>
-        <v>-4782903</v>
+        <v>-6729817</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.45">
@@ -29743,26 +29743,26 @@
         <v>152862316</v>
       </c>
       <c r="J17" s="191">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="K17" s="191">
-        <v>5754468</v>
+        <v>9044977</v>
       </c>
       <c r="L17" s="191">
-        <v>717</v>
+        <v>740</v>
       </c>
       <c r="M17" s="191">
-        <v>121493240</v>
+        <v>124783749</v>
       </c>
       <c r="N17" s="192">
-        <v>76.2</v>
+        <v>78.64</v>
       </c>
       <c r="O17" s="192">
-        <v>79.48</v>
+        <v>81.63</v>
       </c>
       <c r="P17" s="135">
         <f t="shared" si="0"/>
-        <v>26783206.520000011</v>
+        <v>23492697.520000011</v>
       </c>
       <c r="R17" s="173" t="s">
         <v>84</v>
@@ -29776,28 +29776,28 @@
       </c>
       <c r="U17" s="189">
         <f t="shared" si="2"/>
-        <v>19946581.670000002</v>
+        <v>17611017.670000002</v>
       </c>
       <c r="V17" s="175">
         <f t="shared" si="3"/>
-        <v>-2564189</v>
+        <v>-4899753</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A18" s="193" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B18" s="193" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C18" s="193" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D18" s="194">
-        <v>642</v>
+        <v>1181</v>
       </c>
       <c r="E18" s="194">
-        <v>101866340</v>
+        <v>189656153</v>
       </c>
       <c r="F18" s="194">
         <v>0</v>
@@ -29806,49 +29806,49 @@
         <v>0</v>
       </c>
       <c r="H18" s="194">
-        <v>642</v>
+        <v>1181</v>
       </c>
       <c r="I18" s="194">
-        <v>101866340</v>
+        <v>189656153</v>
       </c>
       <c r="J18" s="194">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="K18" s="194">
-        <v>5704474</v>
+        <v>8704685</v>
       </c>
       <c r="L18" s="194">
-        <v>483</v>
+        <v>941</v>
       </c>
       <c r="M18" s="194">
-        <v>79720347</v>
+        <v>153129354</v>
       </c>
       <c r="N18" s="195">
-        <v>75.23</v>
+        <v>79.680000000000007</v>
       </c>
       <c r="O18" s="195">
-        <v>78.260000000000005</v>
+        <v>80.739999999999995</v>
       </c>
       <c r="P18" s="135">
         <f t="shared" si="0"/>
-        <v>19090002.799999997</v>
+        <v>30837114.409999996</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A19" s="190" t="s">
-        <v>179</v>
+        <v>128</v>
       </c>
       <c r="B19" s="190" t="s">
-        <v>288</v>
+        <v>116</v>
       </c>
       <c r="C19" s="190" t="s">
-        <v>284</v>
+        <v>117</v>
       </c>
       <c r="D19" s="191">
-        <v>318</v>
+        <v>642</v>
       </c>
       <c r="E19" s="191">
-        <v>50351985</v>
+        <v>101866340</v>
       </c>
       <c r="F19" s="191">
         <v>0</v>
@@ -29857,49 +29857,49 @@
         <v>0</v>
       </c>
       <c r="H19" s="191">
-        <v>318</v>
+        <v>642</v>
       </c>
       <c r="I19" s="191">
-        <v>50351985</v>
+        <v>101866340</v>
       </c>
       <c r="J19" s="191">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="K19" s="191">
-        <v>1966983</v>
+        <v>7677756</v>
       </c>
       <c r="L19" s="191">
-        <v>239</v>
+        <v>497</v>
       </c>
       <c r="M19" s="191">
-        <v>38989181</v>
+        <v>81693629</v>
       </c>
       <c r="N19" s="192">
-        <v>75.16</v>
+        <v>77.41</v>
       </c>
       <c r="O19" s="192">
-        <v>77.430000000000007</v>
+        <v>80.2</v>
       </c>
       <c r="P19" s="135">
         <f t="shared" si="0"/>
-        <v>9852244.4499999955</v>
+        <v>17116720.799999997</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A20" s="193" t="s">
-        <v>179</v>
+        <v>129</v>
       </c>
       <c r="B20" s="193" t="s">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="C20" s="193" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="D20" s="194">
-        <v>415</v>
+        <v>588</v>
       </c>
       <c r="E20" s="194">
-        <v>66800107</v>
+        <v>95369711</v>
       </c>
       <c r="F20" s="194">
         <v>0</v>
@@ -29908,32 +29908,32 @@
         <v>0</v>
       </c>
       <c r="H20" s="194">
-        <v>415</v>
+        <v>588</v>
       </c>
       <c r="I20" s="194">
-        <v>66800107</v>
+        <v>95369711</v>
       </c>
       <c r="J20" s="194">
-        <v>11</v>
+        <v>124</v>
       </c>
       <c r="K20" s="194">
-        <v>1720613</v>
+        <v>19056657</v>
       </c>
       <c r="L20" s="194">
-        <v>304</v>
+        <v>458</v>
       </c>
       <c r="M20" s="194">
-        <v>51033198</v>
+        <v>74897602</v>
       </c>
       <c r="N20" s="195">
-        <v>73.25</v>
+        <v>77.89</v>
       </c>
       <c r="O20" s="195">
-        <v>76.400000000000006</v>
+        <v>78.53</v>
       </c>
       <c r="P20" s="135">
         <f t="shared" si="0"/>
-        <v>13762905.789999999</v>
+        <v>17611017.670000002</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.45">
@@ -29941,16 +29941,16 @@
         <v>129</v>
       </c>
       <c r="B21" s="190" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C21" s="190" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="D21" s="191">
-        <v>588</v>
+        <v>968</v>
       </c>
       <c r="E21" s="191">
-        <v>95369711</v>
+        <v>162344260</v>
       </c>
       <c r="F21" s="191">
         <v>0</v>
@@ -29959,49 +29959,49 @@
         <v>0</v>
       </c>
       <c r="H21" s="191">
-        <v>588</v>
+        <v>968</v>
       </c>
       <c r="I21" s="191">
-        <v>95369711</v>
+        <v>162344260</v>
       </c>
       <c r="J21" s="191">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="K21" s="191">
-        <v>16721093</v>
+        <v>12177318</v>
       </c>
       <c r="L21" s="191">
-        <v>441</v>
+        <v>743</v>
       </c>
       <c r="M21" s="191">
-        <v>72562038</v>
+        <v>125733547</v>
       </c>
       <c r="N21" s="192">
-        <v>75</v>
+        <v>76.760000000000005</v>
       </c>
       <c r="O21" s="192">
-        <v>76.08</v>
+        <v>77.45</v>
       </c>
       <c r="P21" s="135">
         <f t="shared" si="0"/>
-        <v>19946581.670000002</v>
+        <v>31740385.199999988</v>
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A22" s="193" t="s">
-        <v>129</v>
+        <v>179</v>
       </c>
       <c r="B22" s="193" t="s">
-        <v>71</v>
+        <v>120</v>
       </c>
       <c r="C22" s="193" t="s">
-        <v>72</v>
+        <v>121</v>
       </c>
       <c r="D22" s="194">
-        <v>968</v>
+        <v>415</v>
       </c>
       <c r="E22" s="194">
-        <v>162344260</v>
+        <v>66800107</v>
       </c>
       <c r="F22" s="194">
         <v>0</v>
@@ -30010,32 +30010,32 @@
         <v>0</v>
       </c>
       <c r="H22" s="194">
-        <v>968</v>
+        <v>415</v>
       </c>
       <c r="I22" s="194">
-        <v>162344260</v>
+        <v>66800107</v>
       </c>
       <c r="J22" s="194">
-        <v>59</v>
+        <v>15</v>
       </c>
       <c r="K22" s="194">
-        <v>9478186</v>
+        <v>2117813</v>
       </c>
       <c r="L22" s="194">
-        <v>726</v>
+        <v>308</v>
       </c>
       <c r="M22" s="194">
-        <v>123034415</v>
+        <v>51430398</v>
       </c>
       <c r="N22" s="195">
-        <v>75</v>
+        <v>74.22</v>
       </c>
       <c r="O22" s="195">
-        <v>75.790000000000006</v>
+        <v>76.989999999999995</v>
       </c>
       <c r="P22" s="135">
         <f t="shared" si="0"/>
-        <v>34439517.199999988</v>
+        <v>13365705.789999999</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.45">
@@ -30067,43 +30067,43 @@
         <v>141474291</v>
       </c>
       <c r="J23" s="191">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="K23" s="191">
-        <v>5817018</v>
+        <v>7328212</v>
       </c>
       <c r="L23" s="191">
-        <v>632</v>
+        <v>642</v>
       </c>
       <c r="M23" s="191">
-        <v>105011042</v>
+        <v>106522236</v>
       </c>
       <c r="N23" s="192">
-        <v>74.09</v>
+        <v>75.260000000000005</v>
       </c>
       <c r="O23" s="192">
-        <v>74.23</v>
+        <v>75.290000000000006</v>
       </c>
       <c r="P23" s="135">
         <f t="shared" si="0"/>
-        <v>32219020.270000011</v>
+        <v>30707826.270000011</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A24" s="193" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B24" s="193" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="C24" s="193" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="D24" s="194">
-        <v>687</v>
+        <v>1198</v>
       </c>
       <c r="E24" s="194">
-        <v>105953075</v>
+        <v>194517020</v>
       </c>
       <c r="F24" s="194">
         <v>0</v>
@@ -30112,49 +30112,49 @@
         <v>0</v>
       </c>
       <c r="H24" s="194">
-        <v>687</v>
+        <v>1198</v>
       </c>
       <c r="I24" s="194">
-        <v>105953075</v>
+        <v>194517020</v>
       </c>
       <c r="J24" s="194">
-        <v>33</v>
+        <v>94</v>
       </c>
       <c r="K24" s="194">
-        <v>4883956</v>
+        <v>15632452</v>
       </c>
       <c r="L24" s="194">
-        <v>483</v>
+        <v>852</v>
       </c>
       <c r="M24" s="194">
-        <v>76230417</v>
+        <v>141676480</v>
       </c>
       <c r="N24" s="195">
-        <v>70.31</v>
+        <v>71.12</v>
       </c>
       <c r="O24" s="195">
-        <v>71.95</v>
+        <v>72.84</v>
       </c>
       <c r="P24" s="135">
         <f t="shared" si="0"/>
-        <v>26544065.75</v>
+        <v>47005029.400000006</v>
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A25" s="190" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B25" s="190" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="C25" s="190" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="D25" s="191">
-        <v>1198</v>
+        <v>687</v>
       </c>
       <c r="E25" s="191">
-        <v>194517020</v>
+        <v>105953075</v>
       </c>
       <c r="F25" s="191">
         <v>0</v>
@@ -30163,32 +30163,32 @@
         <v>0</v>
       </c>
       <c r="H25" s="191">
-        <v>1198</v>
+        <v>687</v>
       </c>
       <c r="I25" s="191">
-        <v>194517020</v>
+        <v>105953075</v>
       </c>
       <c r="J25" s="191">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="K25" s="191">
-        <v>8163699</v>
+        <v>5197166</v>
       </c>
       <c r="L25" s="191">
-        <v>815</v>
+        <v>486</v>
       </c>
       <c r="M25" s="191">
-        <v>134207727</v>
+        <v>76543627</v>
       </c>
       <c r="N25" s="192">
-        <v>68.03</v>
+        <v>70.739999999999995</v>
       </c>
       <c r="O25" s="192">
-        <v>69</v>
+        <v>72.239999999999995</v>
       </c>
       <c r="P25" s="135">
         <f t="shared" si="0"/>
-        <v>54473782.400000006</v>
+        <v>26230855.75</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.45">
@@ -30220,26 +30220,26 @@
         <v>149379338</v>
       </c>
       <c r="J26" s="194">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="K26" s="194">
-        <v>10777942</v>
+        <v>12187071</v>
       </c>
       <c r="L26" s="194">
-        <v>612</v>
+        <v>625</v>
       </c>
       <c r="M26" s="194">
-        <v>101084812</v>
+        <v>102493941</v>
       </c>
       <c r="N26" s="195">
+        <v>70.069999999999993</v>
+      </c>
+      <c r="O26" s="195">
         <v>68.61</v>
-      </c>
-      <c r="O26" s="195">
-        <v>67.67</v>
       </c>
       <c r="P26" s="135">
         <f t="shared" si="0"/>
-        <v>43813145.859999985</v>
+        <v>42404016.859999985</v>
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.45">
@@ -30271,30 +30271,35 @@
         <v>89879995</v>
       </c>
       <c r="J27" s="191">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="K27" s="191">
-        <v>3418858</v>
+        <v>4450889</v>
       </c>
       <c r="L27" s="191">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="M27" s="191">
-        <v>59536018</v>
+        <v>60568049</v>
       </c>
       <c r="N27" s="192">
-        <v>64.650000000000006</v>
+        <v>65.930000000000007</v>
       </c>
       <c r="O27" s="192">
-        <v>66.239999999999995</v>
+        <v>67.39</v>
       </c>
       <c r="P27" s="135">
         <f t="shared" si="0"/>
-        <v>27647577.149999991</v>
+        <v>26615546.149999991</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="U5:U6"/>
+    <mergeCell ref="V5:V6"/>
+    <mergeCell ref="R5:R6"/>
+    <mergeCell ref="S5:S6"/>
+    <mergeCell ref="T5:T6"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
     <mergeCell ref="A3:B3"/>
@@ -30309,11 +30314,6 @@
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="L5:M5"/>
     <mergeCell ref="N5:O5"/>
-    <mergeCell ref="U5:U6"/>
-    <mergeCell ref="V5:V6"/>
-    <mergeCell ref="R5:R6"/>
-    <mergeCell ref="S5:S6"/>
-    <mergeCell ref="T5:T6"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="P7:P27">

--- a/filetiendo.xlsx
+++ b/filetiendo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\viettel 2026\thang 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB8E068C-CB38-444B-86AB-D10A1F4240DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3964438-9F7C-4921-8219-C0F20FC97407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="808" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4553,41 +4553,17 @@
     <xf numFmtId="0" fontId="66" fillId="0" borderId="109" xfId="11" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="109" xfId="11" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="177" xfId="11" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="50" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="135" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="134" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="133" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="50" fillId="5" borderId="127" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="5" borderId="130" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="128" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="140" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="139" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="138" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="5" borderId="127" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="24" borderId="132" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4601,10 +4577,34 @@
     <xf numFmtId="0" fontId="17" fillId="5" borderId="129" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="135" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="134" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="133" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="16" borderId="136" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="2" borderId="137" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="140" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="139" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="138" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="67" fillId="18" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4676,16 +4676,16 @@
     <xf numFmtId="0" fontId="63" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="47" fillId="5" borderId="152" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="5" borderId="151" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="148" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="147" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="5" borderId="152" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="5" borderId="151" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="51" fillId="5" borderId="150" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4705,6 +4705,12 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="155" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="158" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="157" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="159" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4730,10 +4736,10 @@
     <xf numFmtId="0" fontId="55" fillId="0" borderId="164" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="158" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="69" fillId="29" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="157" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="69" fillId="29" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="45" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4758,12 +4764,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="168" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="69" fillId="29" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="29" borderId="165" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="12">
     <cellStyle name="Comma" xfId="8" builtinId="3"/>
@@ -5653,166 +5653,166 @@
       </c>
     </row>
     <row r="2" spans="1:675" ht="23.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="210" t="s">
+      <c r="A2" s="200" t="s">
         <v>34</v>
       </c>
       <c r="B2" s="86"/>
       <c r="C2" s="15"/>
-      <c r="D2" s="216" t="s">
+      <c r="D2" s="211" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="216"/>
-      <c r="F2" s="216"/>
-      <c r="G2" s="216"/>
-      <c r="H2" s="216"/>
-      <c r="I2" s="216"/>
-      <c r="J2" s="216"/>
-      <c r="K2" s="216"/>
-      <c r="L2" s="216"/>
-      <c r="M2" s="216"/>
-      <c r="N2" s="216"/>
-      <c r="O2" s="216"/>
-      <c r="P2" s="216"/>
-      <c r="Q2" s="216"/>
-      <c r="R2" s="216"/>
-      <c r="S2" s="216"/>
-      <c r="T2" s="214" t="s">
+      <c r="E2" s="211"/>
+      <c r="F2" s="211"/>
+      <c r="G2" s="211"/>
+      <c r="H2" s="211"/>
+      <c r="I2" s="211"/>
+      <c r="J2" s="211"/>
+      <c r="K2" s="211"/>
+      <c r="L2" s="211"/>
+      <c r="M2" s="211"/>
+      <c r="N2" s="211"/>
+      <c r="O2" s="211"/>
+      <c r="P2" s="211"/>
+      <c r="Q2" s="211"/>
+      <c r="R2" s="211"/>
+      <c r="S2" s="211"/>
+      <c r="T2" s="206" t="s">
         <v>36</v>
       </c>
-      <c r="U2" s="214"/>
-      <c r="V2" s="214"/>
-      <c r="W2" s="214"/>
-      <c r="X2" s="214"/>
-      <c r="Y2" s="214"/>
-      <c r="Z2" s="214"/>
-      <c r="AA2" s="214"/>
-      <c r="AB2" s="214"/>
-      <c r="AC2" s="214"/>
-      <c r="AD2" s="214"/>
-      <c r="AE2" s="214"/>
-      <c r="AF2" s="214"/>
-      <c r="AG2" s="214"/>
-      <c r="AH2" s="214"/>
-      <c r="AI2" s="214"/>
-      <c r="AJ2" s="213" t="s">
+      <c r="U2" s="206"/>
+      <c r="V2" s="206"/>
+      <c r="W2" s="206"/>
+      <c r="X2" s="206"/>
+      <c r="Y2" s="206"/>
+      <c r="Z2" s="206"/>
+      <c r="AA2" s="206"/>
+      <c r="AB2" s="206"/>
+      <c r="AC2" s="206"/>
+      <c r="AD2" s="206"/>
+      <c r="AE2" s="206"/>
+      <c r="AF2" s="206"/>
+      <c r="AG2" s="206"/>
+      <c r="AH2" s="206"/>
+      <c r="AI2" s="206"/>
+      <c r="AJ2" s="205" t="s">
         <v>37</v>
       </c>
-      <c r="AK2" s="213"/>
-      <c r="AL2" s="213"/>
-      <c r="AM2" s="213"/>
-      <c r="AN2" s="213"/>
-      <c r="AO2" s="213"/>
-      <c r="AP2" s="213"/>
-      <c r="AQ2" s="213"/>
-      <c r="AR2" s="213"/>
-      <c r="AS2" s="213"/>
-      <c r="AT2" s="213"/>
-      <c r="AU2" s="213"/>
-      <c r="AV2" s="212" t="s">
+      <c r="AK2" s="205"/>
+      <c r="AL2" s="205"/>
+      <c r="AM2" s="205"/>
+      <c r="AN2" s="205"/>
+      <c r="AO2" s="205"/>
+      <c r="AP2" s="205"/>
+      <c r="AQ2" s="205"/>
+      <c r="AR2" s="205"/>
+      <c r="AS2" s="205"/>
+      <c r="AT2" s="205"/>
+      <c r="AU2" s="205"/>
+      <c r="AV2" s="204" t="s">
         <v>38</v>
       </c>
-      <c r="AW2" s="212"/>
-      <c r="AX2" s="212"/>
-      <c r="AY2" s="212"/>
-      <c r="AZ2" s="212"/>
-      <c r="BA2" s="212"/>
-      <c r="BB2" s="212"/>
-      <c r="BC2" s="212"/>
-      <c r="BD2" s="212"/>
-      <c r="BE2" s="212"/>
-      <c r="BF2" s="212"/>
-      <c r="BG2" s="212"/>
+      <c r="AW2" s="204"/>
+      <c r="AX2" s="204"/>
+      <c r="AY2" s="204"/>
+      <c r="AZ2" s="204"/>
+      <c r="BA2" s="204"/>
+      <c r="BB2" s="204"/>
+      <c r="BC2" s="204"/>
+      <c r="BD2" s="204"/>
+      <c r="BE2" s="204"/>
+      <c r="BF2" s="204"/>
+      <c r="BG2" s="204"/>
     </row>
     <row r="3" spans="1:675" s="3" customFormat="1" ht="28.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="210"/>
-      <c r="B3" s="217" t="s">
+      <c r="A3" s="200"/>
+      <c r="B3" s="212" t="s">
         <v>39</v>
       </c>
       <c r="C3" s="87"/>
-      <c r="D3" s="204" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="205"/>
-      <c r="F3" s="205"/>
-      <c r="G3" s="205"/>
-      <c r="H3" s="204" t="s">
+      <c r="D3" s="202" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="203"/>
+      <c r="F3" s="203"/>
+      <c r="G3" s="203"/>
+      <c r="H3" s="202" t="s">
         <v>40</v>
       </c>
-      <c r="I3" s="205"/>
-      <c r="J3" s="205"/>
-      <c r="K3" s="205"/>
-      <c r="L3" s="204" t="s">
+      <c r="I3" s="203"/>
+      <c r="J3" s="203"/>
+      <c r="K3" s="203"/>
+      <c r="L3" s="202" t="s">
         <v>41</v>
       </c>
-      <c r="M3" s="205"/>
-      <c r="N3" s="205"/>
-      <c r="O3" s="205"/>
-      <c r="P3" s="207" t="s">
+      <c r="M3" s="203"/>
+      <c r="N3" s="203"/>
+      <c r="O3" s="203"/>
+      <c r="P3" s="215" t="s">
         <v>42</v>
       </c>
-      <c r="Q3" s="208"/>
-      <c r="R3" s="208"/>
-      <c r="S3" s="209"/>
-      <c r="T3" s="204" t="s">
+      <c r="Q3" s="216"/>
+      <c r="R3" s="216"/>
+      <c r="S3" s="217"/>
+      <c r="T3" s="202" t="s">
         <v>43</v>
       </c>
-      <c r="U3" s="205"/>
-      <c r="V3" s="205"/>
-      <c r="W3" s="205"/>
-      <c r="X3" s="204" t="s">
+      <c r="U3" s="203"/>
+      <c r="V3" s="203"/>
+      <c r="W3" s="203"/>
+      <c r="X3" s="202" t="s">
         <v>45</v>
       </c>
-      <c r="Y3" s="205"/>
-      <c r="Z3" s="205"/>
-      <c r="AA3" s="205"/>
-      <c r="AB3" s="204" t="s">
+      <c r="Y3" s="203"/>
+      <c r="Z3" s="203"/>
+      <c r="AA3" s="203"/>
+      <c r="AB3" s="202" t="s">
         <v>47</v>
       </c>
-      <c r="AC3" s="205"/>
-      <c r="AD3" s="205"/>
-      <c r="AE3" s="205"/>
-      <c r="AF3" s="204" t="s">
+      <c r="AC3" s="203"/>
+      <c r="AD3" s="203"/>
+      <c r="AE3" s="203"/>
+      <c r="AF3" s="202" t="s">
         <v>48</v>
       </c>
-      <c r="AG3" s="205"/>
-      <c r="AH3" s="205"/>
-      <c r="AI3" s="205"/>
-      <c r="AJ3" s="201" t="s">
+      <c r="AG3" s="203"/>
+      <c r="AH3" s="203"/>
+      <c r="AI3" s="203"/>
+      <c r="AJ3" s="208" t="s">
         <v>51</v>
       </c>
-      <c r="AK3" s="202"/>
-      <c r="AL3" s="202"/>
-      <c r="AM3" s="203"/>
-      <c r="AN3" s="201" t="s">
+      <c r="AK3" s="209"/>
+      <c r="AL3" s="209"/>
+      <c r="AM3" s="210"/>
+      <c r="AN3" s="208" t="s">
         <v>14</v>
       </c>
-      <c r="AO3" s="202"/>
-      <c r="AP3" s="202"/>
-      <c r="AQ3" s="203"/>
-      <c r="AR3" s="201" t="s">
+      <c r="AO3" s="209"/>
+      <c r="AP3" s="209"/>
+      <c r="AQ3" s="210"/>
+      <c r="AR3" s="208" t="s">
         <v>52</v>
       </c>
-      <c r="AS3" s="202"/>
-      <c r="AT3" s="202"/>
-      <c r="AU3" s="203"/>
-      <c r="AV3" s="205" t="s">
+      <c r="AS3" s="209"/>
+      <c r="AT3" s="209"/>
+      <c r="AU3" s="210"/>
+      <c r="AV3" s="203" t="s">
         <v>16</v>
       </c>
-      <c r="AW3" s="205"/>
-      <c r="AX3" s="205"/>
-      <c r="AY3" s="205"/>
-      <c r="AZ3" s="205" t="s">
+      <c r="AW3" s="203"/>
+      <c r="AX3" s="203"/>
+      <c r="AY3" s="203"/>
+      <c r="AZ3" s="203" t="s">
         <v>54</v>
       </c>
-      <c r="BA3" s="205"/>
-      <c r="BB3" s="205"/>
-      <c r="BC3" s="205"/>
-      <c r="BD3" s="204" t="s">
+      <c r="BA3" s="203"/>
+      <c r="BB3" s="203"/>
+      <c r="BC3" s="203"/>
+      <c r="BD3" s="202" t="s">
         <v>55</v>
       </c>
-      <c r="BE3" s="205"/>
-      <c r="BF3" s="215"/>
-      <c r="BG3" s="205"/>
+      <c r="BE3" s="203"/>
+      <c r="BF3" s="207"/>
+      <c r="BG3" s="203"/>
       <c r="BH3" s="2"/>
       <c r="BI3" s="2"/>
       <c r="BJ3" s="2"/>
@@ -6431,8 +6431,8 @@
       <c r="YY3" s="2"/>
     </row>
     <row r="4" spans="1:675" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="211"/>
-      <c r="B4" s="217"/>
+      <c r="A4" s="201"/>
+      <c r="B4" s="212"/>
       <c r="C4" s="88"/>
       <c r="D4" s="8" t="s">
         <v>2</v>
@@ -6777,7 +6777,7 @@
       </c>
       <c r="AS5" s="129">
         <f>(VLOOKUP(B5,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.84370000000000012</v>
+        <v>0.84599999999999997</v>
       </c>
       <c r="AT5" s="14">
         <f t="shared" ref="AT5:AT18" si="20">IF(AS5&lt;94.5%,0,IF(AS5&lt;95.54%,50%,IF(AS5&lt;AR5,80%,100%+(30%*(AS5-AR5)/3.39%))))</f>
@@ -6785,7 +6785,7 @@
       </c>
       <c r="AU5" s="54">
         <f t="shared" ref="AU5:AU18" si="21">AR5-AS5</f>
-        <v>0.12629999999999986</v>
+        <v>0.124</v>
       </c>
       <c r="AV5" s="57">
         <f>VLOOKUP(C5,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="AS6" s="129">
         <f>(VLOOKUP(B6,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.77450000000000008</v>
+        <v>0.78190000000000004</v>
       </c>
       <c r="AT6" s="14">
         <f t="shared" si="20"/>
@@ -7018,7 +7018,7 @@
       </c>
       <c r="AU6" s="54">
         <f t="shared" si="21"/>
-        <v>0.1954999999999999</v>
+        <v>0.18809999999999993</v>
       </c>
       <c r="AV6" s="57">
         <f>VLOOKUP(C6,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7243,7 +7243,7 @@
       </c>
       <c r="AS7" s="129">
         <f>(VLOOKUP(B7,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.81630000000000003</v>
+        <v>0.82590000000000008</v>
       </c>
       <c r="AT7" s="14">
         <f t="shared" si="20"/>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="AU7" s="54">
         <f t="shared" si="21"/>
-        <v>0.15369999999999995</v>
+        <v>0.14409999999999989</v>
       </c>
       <c r="AV7" s="57">
         <f>VLOOKUP(C7,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7476,7 +7476,7 @@
       </c>
       <c r="AS8" s="129">
         <f>(VLOOKUP(B8,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.81730000000000003</v>
+        <v>0.81810000000000005</v>
       </c>
       <c r="AT8" s="14">
         <f t="shared" si="20"/>
@@ -7484,7 +7484,7 @@
       </c>
       <c r="AU8" s="54">
         <f t="shared" si="21"/>
-        <v>0.15269999999999995</v>
+        <v>0.15189999999999992</v>
       </c>
       <c r="AV8" s="57">
         <f>VLOOKUP(C8,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7709,7 +7709,7 @@
       </c>
       <c r="AS9" s="129">
         <f>(VLOOKUP(B9,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.67390000000000005</v>
+        <v>0.8246</v>
       </c>
       <c r="AT9" s="14">
         <f t="shared" si="20"/>
@@ -7717,7 +7717,7 @@
       </c>
       <c r="AU9" s="54">
         <f t="shared" si="21"/>
-        <v>0.29609999999999992</v>
+        <v>0.14539999999999997</v>
       </c>
       <c r="AV9" s="57">
         <f>VLOOKUP(C9,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7942,7 +7942,7 @@
       </c>
       <c r="AS10" s="129">
         <f>(VLOOKUP(B10,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.7853</v>
+        <v>0.78849999999999998</v>
       </c>
       <c r="AT10" s="14">
         <f t="shared" si="20"/>
@@ -7950,7 +7950,7 @@
       </c>
       <c r="AU10" s="54">
         <f t="shared" si="21"/>
-        <v>0.18469999999999998</v>
+        <v>0.18149999999999999</v>
       </c>
       <c r="AV10" s="57">
         <f>VLOOKUP(C10,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="AS11" s="129">
         <f>(VLOOKUP(B11,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.75290000000000012</v>
+        <v>0.78110000000000002</v>
       </c>
       <c r="AT11" s="14">
         <f t="shared" si="20"/>
@@ -8183,7 +8183,7 @@
       </c>
       <c r="AU11" s="54">
         <f t="shared" si="21"/>
-        <v>0.21709999999999985</v>
+        <v>0.18889999999999996</v>
       </c>
       <c r="AV11" s="57">
         <f>VLOOKUP(C11,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="AS12" s="129">
         <f>(VLOOKUP(B12,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.72239999999999993</v>
+        <v>0.79359999999999997</v>
       </c>
       <c r="AT12" s="14">
         <f t="shared" si="20"/>
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AU12" s="54">
         <f t="shared" si="21"/>
-        <v>0.24760000000000004</v>
+        <v>0.1764</v>
       </c>
       <c r="AV12" s="57">
         <f>VLOOKUP(C12,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="AS13" s="129">
         <f>(VLOOKUP(B13,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.83689999999999998</v>
+        <v>0.84310000000000007</v>
       </c>
       <c r="AT13" s="14">
         <f t="shared" si="20"/>
@@ -8649,7 +8649,7 @@
       </c>
       <c r="AU13" s="54">
         <f t="shared" si="21"/>
-        <v>0.1331</v>
+        <v>0.1268999999999999</v>
       </c>
       <c r="AV13" s="57">
         <f>VLOOKUP(C13,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="AS14" s="129">
         <f>(VLOOKUP(B14,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.68610000000000004</v>
+        <v>0.69230000000000003</v>
       </c>
       <c r="AT14" s="14">
         <f t="shared" si="20"/>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="AU14" s="54">
         <f t="shared" si="21"/>
-        <v>0.28389999999999993</v>
+        <v>0.27769999999999995</v>
       </c>
       <c r="AV14" s="57">
         <f>VLOOKUP(C14,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -9107,7 +9107,7 @@
       </c>
       <c r="AS15" s="129">
         <f>(VLOOKUP(B15,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.72840000000000005</v>
+        <v>0.73290000000000011</v>
       </c>
       <c r="AT15" s="14">
         <f t="shared" si="20"/>
@@ -9115,7 +9115,7 @@
       </c>
       <c r="AU15" s="54">
         <f t="shared" si="21"/>
-        <v>0.24159999999999993</v>
+        <v>0.23709999999999987</v>
       </c>
       <c r="AV15" s="57">
         <f>VLOOKUP(C15,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -9340,7 +9340,7 @@
       </c>
       <c r="AS16" s="129">
         <f>(VLOOKUP(B16,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.80200000000000005</v>
+        <v>0.81240000000000001</v>
       </c>
       <c r="AT16" s="14">
         <f t="shared" si="20"/>
@@ -9348,7 +9348,7 @@
       </c>
       <c r="AU16" s="54">
         <f t="shared" si="21"/>
-        <v>0.16799999999999993</v>
+        <v>0.15759999999999996</v>
       </c>
       <c r="AV16" s="57">
         <f>VLOOKUP(C16,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -9573,7 +9573,7 @@
       </c>
       <c r="AS17" s="129">
         <f>(VLOOKUP(B17,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.80740000000000001</v>
+        <v>0.81189999999999996</v>
       </c>
       <c r="AT17" s="14">
         <f t="shared" si="20"/>
@@ -9581,7 +9581,7 @@
       </c>
       <c r="AU17" s="54">
         <f t="shared" si="21"/>
-        <v>0.16259999999999997</v>
+        <v>0.15810000000000002</v>
       </c>
       <c r="AV17" s="57">
         <f>VLOOKUP(C17,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -9806,7 +9806,7 @@
       </c>
       <c r="AS18" s="129">
         <f>(VLOOKUP(B18,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.76989999999999992</v>
+        <v>0.78280000000000005</v>
       </c>
       <c r="AT18" s="14">
         <f t="shared" si="20"/>
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AU18" s="54">
         <f t="shared" si="21"/>
-        <v>0.20010000000000006</v>
+        <v>0.18719999999999992</v>
       </c>
       <c r="AV18" s="57">
         <f>VLOOKUP(C18,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -9871,50 +9871,50 @@
       <c r="C19" s="15"/>
       <c r="D19" s="15"/>
       <c r="E19" s="16"/>
-      <c r="F19" s="200">
+      <c r="F19" s="213">
         <f ca="1">TODAY()</f>
-        <v>46077</v>
-      </c>
-      <c r="G19" s="200"/>
+        <v>46078</v>
+      </c>
+      <c r="G19" s="213"/>
       <c r="H19" s="90"/>
       <c r="I19" s="91">
         <f ca="1">DAY(F19)</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J19" s="92">
         <v>31</v>
       </c>
       <c r="K19" s="95">
         <f ca="1">I19/J19</f>
-        <v>0.77419354838709675</v>
-      </c>
-      <c r="L19" s="206" t="s">
+        <v>0.80645161290322576</v>
+      </c>
+      <c r="L19" s="214" t="s">
         <v>124</v>
       </c>
-      <c r="M19" s="206"/>
-      <c r="N19" s="206"/>
-      <c r="O19" s="206"/>
-      <c r="P19" s="206"/>
-      <c r="Q19" s="206"/>
-      <c r="R19" s="206"/>
-      <c r="S19" s="206"/>
-      <c r="T19" s="206"/>
-      <c r="U19" s="206"/>
-      <c r="V19" s="206"/>
-      <c r="W19" s="206"/>
-      <c r="X19" s="206"/>
-      <c r="Y19" s="206"/>
-      <c r="Z19" s="206"/>
-      <c r="AA19" s="206"/>
-      <c r="AB19" s="206"/>
-      <c r="AC19" s="206"/>
-      <c r="AD19" s="206"/>
-      <c r="AE19" s="206"/>
-      <c r="AF19" s="206"/>
-      <c r="AG19" s="206"/>
-      <c r="AH19" s="206"/>
-      <c r="AI19" s="206"/>
-      <c r="AJ19" s="206"/>
+      <c r="M19" s="214"/>
+      <c r="N19" s="214"/>
+      <c r="O19" s="214"/>
+      <c r="P19" s="214"/>
+      <c r="Q19" s="214"/>
+      <c r="R19" s="214"/>
+      <c r="S19" s="214"/>
+      <c r="T19" s="214"/>
+      <c r="U19" s="214"/>
+      <c r="V19" s="214"/>
+      <c r="W19" s="214"/>
+      <c r="X19" s="214"/>
+      <c r="Y19" s="214"/>
+      <c r="Z19" s="214"/>
+      <c r="AA19" s="214"/>
+      <c r="AB19" s="214"/>
+      <c r="AC19" s="214"/>
+      <c r="AD19" s="214"/>
+      <c r="AE19" s="214"/>
+      <c r="AF19" s="214"/>
+      <c r="AG19" s="214"/>
+      <c r="AH19" s="214"/>
+      <c r="AI19" s="214"/>
+      <c r="AJ19" s="214"/>
       <c r="AK19" s="16"/>
       <c r="AL19" s="32"/>
       <c r="AM19" s="16"/>
@@ -10107,6 +10107,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="AN3:AQ3"/>
+    <mergeCell ref="AF3:AI3"/>
+    <mergeCell ref="L19:AJ19"/>
+    <mergeCell ref="P3:S3"/>
+    <mergeCell ref="T3:W3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="X3:AA3"/>
     <mergeCell ref="AV2:BG2"/>
@@ -10123,12 +10129,6 @@
     <mergeCell ref="D3:G3"/>
     <mergeCell ref="H3:K3"/>
     <mergeCell ref="L3:O3"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="AN3:AQ3"/>
-    <mergeCell ref="AF3:AI3"/>
-    <mergeCell ref="L19:AJ19"/>
-    <mergeCell ref="P3:S3"/>
-    <mergeCell ref="T3:W3"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="C3:C4">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="D14" s="74">
         <f>VLOOKUP($B$2,'TH NV'!$A$5:$BG$18,N14,0)</f>
-        <v>0.84370000000000012</v>
+        <v>0.84599999999999997</v>
       </c>
       <c r="E14" s="49" t="e">
         <f>VLOOKUP($B$2,'TH NV'!$A$1:$BG$18,70,0)</f>
@@ -11167,7 +11167,7 @@
       </c>
       <c r="J14" s="65">
         <f t="shared" si="2"/>
-        <v>0.12629999999999986</v>
+        <v>0.124</v>
       </c>
       <c r="K14" s="222"/>
       <c r="L14" s="114" t="s">
@@ -11348,42 +11348,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:59" s="1" customFormat="1" ht="24.75" x14ac:dyDescent="0.45">
-      <c r="D1" s="216" t="s">
+      <c r="D1" s="211" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="216"/>
-      <c r="F1" s="216"/>
-      <c r="G1" s="216"/>
-      <c r="H1" s="216"/>
-      <c r="I1" s="216"/>
-      <c r="J1" s="216"/>
-      <c r="K1" s="216"/>
-      <c r="L1" s="216"/>
-      <c r="M1" s="216"/>
-      <c r="N1" s="216"/>
-      <c r="O1" s="216"/>
-      <c r="P1" s="216"/>
-      <c r="Q1" s="216"/>
-      <c r="R1" s="216"/>
-      <c r="S1" s="216"/>
-      <c r="T1" s="214" t="s">
+      <c r="E1" s="211"/>
+      <c r="F1" s="211"/>
+      <c r="G1" s="211"/>
+      <c r="H1" s="211"/>
+      <c r="I1" s="211"/>
+      <c r="J1" s="211"/>
+      <c r="K1" s="211"/>
+      <c r="L1" s="211"/>
+      <c r="M1" s="211"/>
+      <c r="N1" s="211"/>
+      <c r="O1" s="211"/>
+      <c r="P1" s="211"/>
+      <c r="Q1" s="211"/>
+      <c r="R1" s="211"/>
+      <c r="S1" s="211"/>
+      <c r="T1" s="206" t="s">
         <v>36</v>
       </c>
-      <c r="U1" s="214"/>
-      <c r="V1" s="214"/>
-      <c r="W1" s="214"/>
-      <c r="X1" s="214"/>
-      <c r="Y1" s="214"/>
-      <c r="Z1" s="214"/>
-      <c r="AA1" s="214"/>
-      <c r="AB1" s="214"/>
-      <c r="AC1" s="214"/>
-      <c r="AD1" s="214"/>
-      <c r="AE1" s="214"/>
-      <c r="AF1" s="214"/>
-      <c r="AG1" s="214"/>
-      <c r="AH1" s="214"/>
-      <c r="AI1" s="214"/>
+      <c r="U1" s="206"/>
+      <c r="V1" s="206"/>
+      <c r="W1" s="206"/>
+      <c r="X1" s="206"/>
+      <c r="Y1" s="206"/>
+      <c r="Z1" s="206"/>
+      <c r="AA1" s="206"/>
+      <c r="AB1" s="206"/>
+      <c r="AC1" s="206"/>
+      <c r="AD1" s="206"/>
+      <c r="AE1" s="206"/>
+      <c r="AF1" s="206"/>
+      <c r="AG1" s="206"/>
+      <c r="AH1" s="206"/>
+      <c r="AI1" s="206"/>
       <c r="AJ1" s="234" t="s">
         <v>37</v>
       </c>
@@ -11416,90 +11416,90 @@
     <row r="2" spans="1:59" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="204" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="205"/>
-      <c r="F2" s="205"/>
-      <c r="G2" s="205"/>
-      <c r="H2" s="204" t="s">
+      <c r="D2" s="202" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="203"/>
+      <c r="F2" s="203"/>
+      <c r="G2" s="203"/>
+      <c r="H2" s="202" t="s">
         <v>40</v>
       </c>
-      <c r="I2" s="205"/>
-      <c r="J2" s="205"/>
-      <c r="K2" s="205"/>
-      <c r="L2" s="204" t="s">
+      <c r="I2" s="203"/>
+      <c r="J2" s="203"/>
+      <c r="K2" s="203"/>
+      <c r="L2" s="202" t="s">
         <v>41</v>
       </c>
-      <c r="M2" s="205"/>
-      <c r="N2" s="205"/>
-      <c r="O2" s="205"/>
-      <c r="P2" s="207" t="s">
+      <c r="M2" s="203"/>
+      <c r="N2" s="203"/>
+      <c r="O2" s="203"/>
+      <c r="P2" s="215" t="s">
         <v>42</v>
       </c>
-      <c r="Q2" s="208"/>
-      <c r="R2" s="208"/>
-      <c r="S2" s="209"/>
-      <c r="T2" s="204" t="s">
+      <c r="Q2" s="216"/>
+      <c r="R2" s="216"/>
+      <c r="S2" s="217"/>
+      <c r="T2" s="202" t="s">
         <v>43</v>
       </c>
-      <c r="U2" s="205"/>
-      <c r="V2" s="205"/>
-      <c r="W2" s="205"/>
-      <c r="X2" s="204" t="s">
+      <c r="U2" s="203"/>
+      <c r="V2" s="203"/>
+      <c r="W2" s="203"/>
+      <c r="X2" s="202" t="s">
         <v>45</v>
       </c>
-      <c r="Y2" s="205"/>
-      <c r="Z2" s="205"/>
-      <c r="AA2" s="205"/>
-      <c r="AB2" s="204" t="s">
+      <c r="Y2" s="203"/>
+      <c r="Z2" s="203"/>
+      <c r="AA2" s="203"/>
+      <c r="AB2" s="202" t="s">
         <v>47</v>
       </c>
-      <c r="AC2" s="205"/>
-      <c r="AD2" s="205"/>
-      <c r="AE2" s="205"/>
-      <c r="AF2" s="204" t="s">
+      <c r="AC2" s="203"/>
+      <c r="AD2" s="203"/>
+      <c r="AE2" s="203"/>
+      <c r="AF2" s="202" t="s">
         <v>48</v>
       </c>
-      <c r="AG2" s="205"/>
-      <c r="AH2" s="205"/>
-      <c r="AI2" s="205"/>
-      <c r="AJ2" s="201" t="s">
+      <c r="AG2" s="203"/>
+      <c r="AH2" s="203"/>
+      <c r="AI2" s="203"/>
+      <c r="AJ2" s="208" t="s">
         <v>51</v>
       </c>
-      <c r="AK2" s="202"/>
-      <c r="AL2" s="202"/>
-      <c r="AM2" s="203"/>
-      <c r="AN2" s="201" t="s">
+      <c r="AK2" s="209"/>
+      <c r="AL2" s="209"/>
+      <c r="AM2" s="210"/>
+      <c r="AN2" s="208" t="s">
         <v>14</v>
       </c>
-      <c r="AO2" s="202"/>
-      <c r="AP2" s="202"/>
-      <c r="AQ2" s="203"/>
-      <c r="AR2" s="201" t="s">
+      <c r="AO2" s="209"/>
+      <c r="AP2" s="209"/>
+      <c r="AQ2" s="210"/>
+      <c r="AR2" s="208" t="s">
         <v>52</v>
       </c>
-      <c r="AS2" s="202"/>
-      <c r="AT2" s="202"/>
-      <c r="AU2" s="203"/>
-      <c r="AV2" s="205" t="s">
+      <c r="AS2" s="209"/>
+      <c r="AT2" s="209"/>
+      <c r="AU2" s="210"/>
+      <c r="AV2" s="203" t="s">
         <v>16</v>
       </c>
-      <c r="AW2" s="205"/>
-      <c r="AX2" s="205"/>
-      <c r="AY2" s="205"/>
-      <c r="AZ2" s="205" t="s">
+      <c r="AW2" s="203"/>
+      <c r="AX2" s="203"/>
+      <c r="AY2" s="203"/>
+      <c r="AZ2" s="203" t="s">
         <v>54</v>
       </c>
-      <c r="BA2" s="205"/>
-      <c r="BB2" s="205"/>
-      <c r="BC2" s="205"/>
-      <c r="BD2" s="204" t="s">
+      <c r="BA2" s="203"/>
+      <c r="BB2" s="203"/>
+      <c r="BC2" s="203"/>
+      <c r="BD2" s="202" t="s">
         <v>55</v>
       </c>
-      <c r="BE2" s="205"/>
-      <c r="BF2" s="215"/>
-      <c r="BG2" s="205"/>
+      <c r="BE2" s="203"/>
+      <c r="BF2" s="207"/>
+      <c r="BG2" s="203"/>
     </row>
     <row r="3" spans="1:59" ht="15" x14ac:dyDescent="0.45">
       <c r="B3" s="8" t="s">
@@ -11852,7 +11852,7 @@
       </c>
       <c r="AS4" s="129">
         <f>(VLOOKUP(B4,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.84370000000000012</v>
+        <v>0.84599999999999997</v>
       </c>
       <c r="AT4" s="14">
         <f t="shared" ref="AT4" si="20">IF(AS4&lt;94.5%,0,IF(AS4&lt;95.54%,50%,IF(AS4&lt;AR4,80%,100%+(30%*(AS4-AR4)/3.39%))))</f>
@@ -11860,7 +11860,7 @@
       </c>
       <c r="AU4" s="54">
         <f t="shared" ref="AU4" si="21">AR4-AS4</f>
-        <v>0.12629999999999986</v>
+        <v>0.124</v>
       </c>
       <c r="AV4" s="57">
         <f>VLOOKUP(A4,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -12086,7 +12086,7 @@
       </c>
       <c r="AS5" s="129">
         <f>(VLOOKUP(B5,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.75290000000000012</v>
+        <v>0.78110000000000002</v>
       </c>
       <c r="AT5" s="14">
         <f t="shared" ref="AT5:AT16" si="48">IF(AS5&lt;94.5%,0,IF(AS5&lt;95.54%,50%,IF(AS5&lt;AR5,80%,100%+(30%*(AS5-AR5)/3.39%))))</f>
@@ -12094,7 +12094,7 @@
       </c>
       <c r="AU5" s="54">
         <f t="shared" ref="AU5:AU16" si="49">AR5-AS5</f>
-        <v>0.21709999999999985</v>
+        <v>0.18889999999999996</v>
       </c>
       <c r="AV5" s="57">
         <f>VLOOKUP(A5,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -12320,7 +12320,7 @@
       </c>
       <c r="AS6" s="129">
         <f>(VLOOKUP(B6,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.72239999999999993</v>
+        <v>0.79359999999999997</v>
       </c>
       <c r="AT6" s="14">
         <f t="shared" si="48"/>
@@ -12328,7 +12328,7 @@
       </c>
       <c r="AU6" s="54">
         <f t="shared" si="49"/>
-        <v>0.24760000000000004</v>
+        <v>0.1764</v>
       </c>
       <c r="AV6" s="57">
         <f>VLOOKUP(A6,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -12554,7 +12554,7 @@
       </c>
       <c r="AS7" s="129">
         <f>(VLOOKUP(B7,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.68610000000000004</v>
+        <v>0.69230000000000003</v>
       </c>
       <c r="AT7" s="14">
         <f t="shared" si="48"/>
@@ -12562,7 +12562,7 @@
       </c>
       <c r="AU7" s="54">
         <f t="shared" si="49"/>
-        <v>0.28389999999999993</v>
+        <v>0.27769999999999995</v>
       </c>
       <c r="AV7" s="57">
         <f>VLOOKUP(A7,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -12788,7 +12788,7 @@
       </c>
       <c r="AS8" s="129">
         <f>(VLOOKUP(B8,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.80200000000000005</v>
+        <v>0.81240000000000001</v>
       </c>
       <c r="AT8" s="14">
         <f t="shared" si="48"/>
@@ -12796,7 +12796,7 @@
       </c>
       <c r="AU8" s="54">
         <f t="shared" si="49"/>
-        <v>0.16799999999999993</v>
+        <v>0.15759999999999996</v>
       </c>
       <c r="AV8" s="57">
         <f>VLOOKUP(A8,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -13083,7 +13083,7 @@
       </c>
       <c r="AS10" s="129">
         <f>(VLOOKUP(B10,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.77450000000000008</v>
+        <v>0.78190000000000004</v>
       </c>
       <c r="AT10" s="14">
         <f t="shared" si="48"/>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="AU10" s="54">
         <f t="shared" si="49"/>
-        <v>0.1954999999999999</v>
+        <v>0.18809999999999993</v>
       </c>
       <c r="AV10" s="57">
         <f>VLOOKUP(A10,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -13317,7 +13317,7 @@
       </c>
       <c r="AS11" s="129">
         <f>(VLOOKUP(B11,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.81630000000000003</v>
+        <v>0.82590000000000008</v>
       </c>
       <c r="AT11" s="14">
         <f t="shared" si="48"/>
@@ -13325,7 +13325,7 @@
       </c>
       <c r="AU11" s="54">
         <f t="shared" si="49"/>
-        <v>0.15369999999999995</v>
+        <v>0.14409999999999989</v>
       </c>
       <c r="AV11" s="57">
         <f>VLOOKUP(A11,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -13551,7 +13551,7 @@
       </c>
       <c r="AS12" s="129">
         <f>(VLOOKUP(B12,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.81730000000000003</v>
+        <v>0.81810000000000005</v>
       </c>
       <c r="AT12" s="14">
         <f t="shared" si="48"/>
@@ -13559,7 +13559,7 @@
       </c>
       <c r="AU12" s="54">
         <f t="shared" si="49"/>
-        <v>0.15269999999999995</v>
+        <v>0.15189999999999992</v>
       </c>
       <c r="AV12" s="57">
         <f>VLOOKUP(A12,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -13785,7 +13785,7 @@
       </c>
       <c r="AS13" s="129">
         <f>(VLOOKUP(B13,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.7853</v>
+        <v>0.78849999999999998</v>
       </c>
       <c r="AT13" s="14">
         <f t="shared" si="48"/>
@@ -13793,7 +13793,7 @@
       </c>
       <c r="AU13" s="54">
         <f t="shared" si="49"/>
-        <v>0.18469999999999998</v>
+        <v>0.18149999999999999</v>
       </c>
       <c r="AV13" s="57">
         <f>VLOOKUP(A13,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -14019,7 +14019,7 @@
       </c>
       <c r="AS14" s="129">
         <f>(VLOOKUP(B14,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.83689999999999998</v>
+        <v>0.84310000000000007</v>
       </c>
       <c r="AT14" s="14">
         <f t="shared" si="48"/>
@@ -14027,7 +14027,7 @@
       </c>
       <c r="AU14" s="54">
         <f t="shared" si="49"/>
-        <v>0.1331</v>
+        <v>0.1268999999999999</v>
       </c>
       <c r="AV14" s="57">
         <f>VLOOKUP(A14,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -14253,7 +14253,7 @@
       </c>
       <c r="AS15" s="129">
         <f>(VLOOKUP(B15,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.72840000000000005</v>
+        <v>0.73290000000000011</v>
       </c>
       <c r="AT15" s="14">
         <f t="shared" si="48"/>
@@ -14261,7 +14261,7 @@
       </c>
       <c r="AU15" s="54">
         <f t="shared" si="49"/>
-        <v>0.24159999999999993</v>
+        <v>0.23709999999999987</v>
       </c>
       <c r="AV15" s="57">
         <f>VLOOKUP(A15,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -14487,7 +14487,7 @@
       </c>
       <c r="AS16" s="129">
         <f>(VLOOKUP(B16,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.80740000000000001</v>
+        <v>0.81189999999999996</v>
       </c>
       <c r="AT16" s="14">
         <f t="shared" si="48"/>
@@ -14495,7 +14495,7 @@
       </c>
       <c r="AU16" s="54">
         <f t="shared" si="49"/>
-        <v>0.16259999999999997</v>
+        <v>0.15810000000000002</v>
       </c>
       <c r="AV16" s="57">
         <f>VLOOKUP(A16,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -14579,11 +14579,11 @@
       </c>
       <c r="C19" s="142">
         <f ca="1">SUMIF(cuoc!A7:P27,'tiến độ'!A19,cuoc!M7:M27)</f>
-        <v>489669973</v>
+        <v>503512937</v>
       </c>
       <c r="D19" s="142">
         <f ca="1">B19*0.968-C19</f>
-        <v>133504098.25599992</v>
+        <v>119661134.25599992</v>
       </c>
       <c r="E19" s="137"/>
       <c r="H19" s="137"/>
@@ -14600,11 +14600,11 @@
       </c>
       <c r="C20" s="143">
         <f ca="1">SUMIF(cuoc!A8:P27,'tiến độ'!A20,cuoc!M8:M27)</f>
-        <v>857855141</v>
+        <v>863741713</v>
       </c>
       <c r="D20" s="142">
         <f ca="1">B20*0.968-C20</f>
-        <v>188720664.704</v>
+        <v>182834092.704</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.45">
@@ -14790,6 +14790,11 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="D1:S1"/>
+    <mergeCell ref="D2:G2"/>
+    <mergeCell ref="H2:K2"/>
+    <mergeCell ref="L2:O2"/>
+    <mergeCell ref="P2:S2"/>
     <mergeCell ref="X2:AA2"/>
     <mergeCell ref="AB2:AE2"/>
     <mergeCell ref="AF2:AI2"/>
@@ -14803,11 +14808,6 @@
     <mergeCell ref="AJ2:AM2"/>
     <mergeCell ref="AN2:AQ2"/>
     <mergeCell ref="T2:W2"/>
-    <mergeCell ref="D1:S1"/>
-    <mergeCell ref="D2:G2"/>
-    <mergeCell ref="H2:K2"/>
-    <mergeCell ref="L2:O2"/>
-    <mergeCell ref="P2:S2"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="F4:F16">
@@ -23283,6 +23283,12 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="X5:AE5"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="H5:O5"/>
+    <mergeCell ref="P5:W5"/>
     <mergeCell ref="CB5:CI5"/>
     <mergeCell ref="CJ5:CQ5"/>
     <mergeCell ref="CR5:CY5"/>
@@ -23293,12 +23299,6 @@
     <mergeCell ref="BD5:BK5"/>
     <mergeCell ref="BL5:BS5"/>
     <mergeCell ref="BT5:CA5"/>
-    <mergeCell ref="X5:AE5"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="H5:O5"/>
-    <mergeCell ref="P5:W5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -23396,7 +23396,7 @@
       <c r="A3" s="100" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="245" t="s">
+      <c r="B3" s="243" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="101" t="s">
@@ -23408,70 +23408,70 @@
       <c r="E3" s="247" t="s">
         <v>202</v>
       </c>
-      <c r="F3" s="243" t="s">
+      <c r="F3" s="245" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="243" t="s">
+      <c r="G3" s="245" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="243" t="s">
+      <c r="H3" s="245" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="243" t="s">
+      <c r="I3" s="245" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="243" t="s">
+      <c r="J3" s="245" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="243" t="s">
+      <c r="K3" s="245" t="s">
         <v>11</v>
       </c>
-      <c r="L3" s="243" t="s">
+      <c r="L3" s="245" t="s">
         <v>12</v>
       </c>
-      <c r="M3" s="243" t="s">
+      <c r="M3" s="245" t="s">
         <v>203</v>
       </c>
-      <c r="N3" s="243" t="s">
+      <c r="N3" s="245" t="s">
         <v>286</v>
       </c>
-      <c r="O3" s="243" t="s">
+      <c r="O3" s="245" t="s">
         <v>14</v>
       </c>
-      <c r="P3" s="243" t="s">
+      <c r="P3" s="245" t="s">
         <v>15</v>
       </c>
-      <c r="Q3" s="243" t="s">
+      <c r="Q3" s="245" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="243" t="s">
+      <c r="R3" s="245" t="s">
         <v>17</v>
       </c>
-      <c r="S3" s="243" t="s">
+      <c r="S3" s="245" t="s">
         <v>18</v>
       </c>
       <c r="T3" s="99"/>
     </row>
     <row r="4" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="100"/>
-      <c r="B4" s="246"/>
+      <c r="B4" s="244"/>
       <c r="C4" s="101"/>
       <c r="D4" s="101"/>
       <c r="E4" s="248"/>
-      <c r="F4" s="244"/>
-      <c r="G4" s="244"/>
-      <c r="H4" s="244"/>
-      <c r="I4" s="244"/>
-      <c r="J4" s="244"/>
-      <c r="K4" s="244"/>
-      <c r="L4" s="244"/>
-      <c r="M4" s="244"/>
-      <c r="N4" s="244"/>
-      <c r="O4" s="244"/>
-      <c r="P4" s="244"/>
-      <c r="Q4" s="244"/>
-      <c r="R4" s="244"/>
-      <c r="S4" s="244"/>
+      <c r="F4" s="246"/>
+      <c r="G4" s="246"/>
+      <c r="H4" s="246"/>
+      <c r="I4" s="246"/>
+      <c r="J4" s="246"/>
+      <c r="K4" s="246"/>
+      <c r="L4" s="246"/>
+      <c r="M4" s="246"/>
+      <c r="N4" s="246"/>
+      <c r="O4" s="246"/>
+      <c r="P4" s="246"/>
+      <c r="Q4" s="246"/>
+      <c r="R4" s="246"/>
+      <c r="S4" s="246"/>
       <c r="T4" s="99"/>
     </row>
     <row r="5" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.45">
@@ -24789,6 +24789,12 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="S3:S4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="R3:R4"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="H3:H4"/>
@@ -24799,12 +24805,6 @@
     <mergeCell ref="K3:K4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="E3:E4"/>
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="S3:S4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="R3:R4"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.69991251615088756" right="0.69991251615088756" top="0.74990626395218019" bottom="0.74990626395218019" header="0.29996251027415122" footer="0.29996251027415122"/>
@@ -26080,68 +26080,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:48" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="256" t="s">
+      <c r="A1" s="258" t="s">
         <v>240</v>
       </c>
-      <c r="B1" s="256"/>
-      <c r="C1" s="256"/>
-      <c r="D1" s="256"/>
-      <c r="E1" s="256"/>
-      <c r="F1" s="256"/>
-      <c r="G1" s="256"/>
-      <c r="H1" s="256"/>
-      <c r="I1" s="256"/>
-      <c r="J1" s="256"/>
-      <c r="K1" s="256"/>
-      <c r="M1" s="259" t="s">
+      <c r="B1" s="258"/>
+      <c r="C1" s="258"/>
+      <c r="D1" s="258"/>
+      <c r="E1" s="258"/>
+      <c r="F1" s="258"/>
+      <c r="G1" s="258"/>
+      <c r="H1" s="258"/>
+      <c r="I1" s="258"/>
+      <c r="J1" s="258"/>
+      <c r="K1" s="258"/>
+      <c r="M1" s="261" t="s">
         <v>241</v>
       </c>
-      <c r="N1" s="259"/>
-      <c r="O1" s="259"/>
-      <c r="P1" s="259"/>
-      <c r="Q1" s="259"/>
-      <c r="R1" s="259"/>
-      <c r="S1" s="259"/>
-      <c r="T1" s="259"/>
-      <c r="U1" s="259"/>
-      <c r="V1" s="259"/>
-      <c r="W1" s="259"/>
-      <c r="X1" s="259"/>
-      <c r="Y1" s="259"/>
-      <c r="Z1" s="259"/>
+      <c r="N1" s="261"/>
+      <c r="O1" s="261"/>
+      <c r="P1" s="261"/>
+      <c r="Q1" s="261"/>
+      <c r="R1" s="261"/>
+      <c r="S1" s="261"/>
+      <c r="T1" s="261"/>
+      <c r="U1" s="261"/>
+      <c r="V1" s="261"/>
+      <c r="W1" s="261"/>
+      <c r="X1" s="261"/>
+      <c r="Y1" s="261"/>
+      <c r="Z1" s="261"/>
     </row>
     <row r="2" spans="1:48" ht="24.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="257"/>
-      <c r="B2" s="257"/>
-      <c r="C2" s="257"/>
-      <c r="D2" s="257"/>
-      <c r="E2" s="257"/>
-      <c r="F2" s="257"/>
-      <c r="G2" s="257"/>
-      <c r="H2" s="257"/>
-      <c r="I2" s="257"/>
-      <c r="J2" s="257"/>
-      <c r="K2" s="257"/>
-      <c r="M2" s="260"/>
-      <c r="N2" s="260"/>
-      <c r="O2" s="260"/>
-      <c r="P2" s="260"/>
-      <c r="Q2" s="260"/>
-      <c r="R2" s="260"/>
-      <c r="S2" s="260"/>
-      <c r="T2" s="260"/>
-      <c r="U2" s="260"/>
-      <c r="V2" s="260"/>
-      <c r="W2" s="260"/>
-      <c r="X2" s="260"/>
-      <c r="Y2" s="260"/>
-      <c r="Z2" s="260"/>
+      <c r="A2" s="259"/>
+      <c r="B2" s="259"/>
+      <c r="C2" s="259"/>
+      <c r="D2" s="259"/>
+      <c r="E2" s="259"/>
+      <c r="F2" s="259"/>
+      <c r="G2" s="259"/>
+      <c r="H2" s="259"/>
+      <c r="I2" s="259"/>
+      <c r="J2" s="259"/>
+      <c r="K2" s="259"/>
+      <c r="M2" s="262"/>
+      <c r="N2" s="262"/>
+      <c r="O2" s="262"/>
+      <c r="P2" s="262"/>
+      <c r="Q2" s="262"/>
+      <c r="R2" s="262"/>
+      <c r="S2" s="262"/>
+      <c r="T2" s="262"/>
+      <c r="U2" s="262"/>
+      <c r="V2" s="262"/>
+      <c r="W2" s="262"/>
+      <c r="X2" s="262"/>
+      <c r="Y2" s="262"/>
+      <c r="Z2" s="262"/>
     </row>
     <row r="3" spans="1:48" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="253" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="254" t="s">
+      <c r="A3" s="255" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="256" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="28" t="s">
@@ -26171,70 +26171,70 @@
       <c r="K3" s="28" t="s">
         <v>249</v>
       </c>
-      <c r="M3" s="258" t="s">
+      <c r="M3" s="260" t="s">
         <v>34</v>
       </c>
-      <c r="N3" s="204" t="s">
+      <c r="N3" s="202" t="s">
         <v>250</v>
       </c>
-      <c r="O3" s="205"/>
-      <c r="P3" s="205"/>
-      <c r="Q3" s="205"/>
-      <c r="R3" s="261" t="s">
+      <c r="O3" s="203"/>
+      <c r="P3" s="203"/>
+      <c r="Q3" s="203"/>
+      <c r="R3" s="253" t="s">
         <v>251</v>
       </c>
-      <c r="S3" s="204" t="s">
+      <c r="S3" s="202" t="s">
         <v>252</v>
       </c>
-      <c r="T3" s="205"/>
-      <c r="U3" s="205"/>
-      <c r="V3" s="205"/>
-      <c r="W3" s="261" t="s">
+      <c r="T3" s="203"/>
+      <c r="U3" s="203"/>
+      <c r="V3" s="203"/>
+      <c r="W3" s="253" t="s">
         <v>251</v>
       </c>
-      <c r="X3" s="207" t="s">
+      <c r="X3" s="215" t="s">
         <v>41</v>
       </c>
-      <c r="Y3" s="208"/>
-      <c r="Z3" s="208"/>
-      <c r="AA3" s="261" t="s">
+      <c r="Y3" s="216"/>
+      <c r="Z3" s="216"/>
+      <c r="AA3" s="253" t="s">
         <v>251</v>
       </c>
       <c r="AB3" s="71"/>
-      <c r="AC3" s="204" t="s">
+      <c r="AC3" s="202" t="s">
         <v>42</v>
       </c>
-      <c r="AD3" s="205"/>
-      <c r="AE3" s="205"/>
-      <c r="AF3" s="205"/>
-      <c r="AG3" s="204" t="s">
+      <c r="AD3" s="203"/>
+      <c r="AE3" s="203"/>
+      <c r="AF3" s="203"/>
+      <c r="AG3" s="202" t="s">
         <v>43</v>
       </c>
-      <c r="AH3" s="205"/>
-      <c r="AI3" s="205"/>
-      <c r="AJ3" s="205"/>
-      <c r="AK3" s="204" t="s">
+      <c r="AH3" s="203"/>
+      <c r="AI3" s="203"/>
+      <c r="AJ3" s="203"/>
+      <c r="AK3" s="202" t="s">
         <v>44</v>
       </c>
-      <c r="AL3" s="205"/>
-      <c r="AM3" s="205"/>
-      <c r="AN3" s="205"/>
-      <c r="AO3" s="204" t="s">
+      <c r="AL3" s="203"/>
+      <c r="AM3" s="203"/>
+      <c r="AN3" s="203"/>
+      <c r="AO3" s="202" t="s">
         <v>46</v>
       </c>
-      <c r="AP3" s="205"/>
-      <c r="AQ3" s="205"/>
-      <c r="AR3" s="205"/>
-      <c r="AS3" s="204" t="s">
+      <c r="AP3" s="203"/>
+      <c r="AQ3" s="203"/>
+      <c r="AR3" s="203"/>
+      <c r="AS3" s="202" t="s">
         <v>47</v>
       </c>
-      <c r="AT3" s="205"/>
-      <c r="AU3" s="205"/>
-      <c r="AV3" s="205"/>
+      <c r="AT3" s="203"/>
+      <c r="AU3" s="203"/>
+      <c r="AV3" s="203"/>
     </row>
     <row r="4" spans="1:48" ht="22.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="253"/>
-      <c r="B4" s="255"/>
+      <c r="A4" s="255"/>
+      <c r="B4" s="257"/>
       <c r="C4" s="24">
         <f t="shared" ref="C4:K4" si="0">SUM(C5:C19)</f>
         <v>15</v>
@@ -26271,7 +26271,7 @@
         <f t="shared" si="0"/>
         <v>134</v>
       </c>
-      <c r="M4" s="258"/>
+      <c r="M4" s="260"/>
       <c r="N4" s="8" t="s">
         <v>2</v>
       </c>
@@ -26284,7 +26284,7 @@
       <c r="Q4" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="R4" s="262"/>
+      <c r="R4" s="254"/>
       <c r="S4" s="8" t="s">
         <v>2</v>
       </c>
@@ -26297,7 +26297,7 @@
       <c r="V4" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="W4" s="262"/>
+      <c r="W4" s="254"/>
       <c r="X4" s="8" t="s">
         <v>2</v>
       </c>
@@ -26307,7 +26307,7 @@
       <c r="Z4" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="AA4" s="262"/>
+      <c r="AA4" s="254"/>
       <c r="AB4" s="51" t="s">
         <v>59</v>
       </c>
@@ -28696,6 +28696,12 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="A1:K2"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="N3:Q3"/>
+    <mergeCell ref="M1:Z2"/>
     <mergeCell ref="AS3:AV3"/>
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="W3:W4"/>
@@ -28706,12 +28712,6 @@
     <mergeCell ref="AK3:AN3"/>
     <mergeCell ref="AO3:AR3"/>
     <mergeCell ref="S3:V3"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="A1:K2"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="N3:Q3"/>
-    <mergeCell ref="M1:Z2"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="P5:P20">
@@ -28851,44 +28851,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="263"/>
-      <c r="B1" s="263"/>
-      <c r="C1" s="263"/>
-      <c r="D1" s="263"/>
-      <c r="E1" s="263"/>
-      <c r="F1" s="263"/>
-      <c r="G1" s="263"/>
-      <c r="H1" s="263"/>
-      <c r="I1" s="263"/>
-      <c r="J1" s="263"/>
-      <c r="K1" s="263"/>
-      <c r="L1" s="263"/>
-      <c r="M1" s="263"/>
-      <c r="N1" s="263"/>
-      <c r="O1" s="263"/>
-      <c r="P1" s="263"/>
+      <c r="A1" s="265"/>
+      <c r="B1" s="265"/>
+      <c r="C1" s="265"/>
+      <c r="D1" s="265"/>
+      <c r="E1" s="265"/>
+      <c r="F1" s="265"/>
+      <c r="G1" s="265"/>
+      <c r="H1" s="265"/>
+      <c r="I1" s="265"/>
+      <c r="J1" s="265"/>
+      <c r="K1" s="265"/>
+      <c r="L1" s="265"/>
+      <c r="M1" s="265"/>
+      <c r="N1" s="265"/>
+      <c r="O1" s="265"/>
+      <c r="P1" s="265"/>
     </row>
     <row r="2" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="264"/>
-      <c r="B2" s="264"/>
-      <c r="C2" s="264"/>
-      <c r="D2" s="264"/>
-      <c r="E2" s="264"/>
-      <c r="F2" s="264"/>
-      <c r="G2" s="264"/>
-      <c r="H2" s="264"/>
-      <c r="I2" s="264"/>
-      <c r="J2" s="264"/>
-      <c r="K2" s="264"/>
-      <c r="L2" s="264"/>
-      <c r="M2" s="264"/>
-      <c r="N2" s="264"/>
-      <c r="O2" s="264"/>
-      <c r="P2" s="264"/>
+      <c r="A2" s="266"/>
+      <c r="B2" s="266"/>
+      <c r="C2" s="266"/>
+      <c r="D2" s="266"/>
+      <c r="E2" s="266"/>
+      <c r="F2" s="266"/>
+      <c r="G2" s="266"/>
+      <c r="H2" s="266"/>
+      <c r="I2" s="266"/>
+      <c r="J2" s="266"/>
+      <c r="K2" s="266"/>
+      <c r="L2" s="266"/>
+      <c r="M2" s="266"/>
+      <c r="N2" s="266"/>
+      <c r="O2" s="266"/>
+      <c r="P2" s="266"/>
     </row>
     <row r="3" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="265"/>
-      <c r="B3" s="265"/>
+      <c r="A3" s="267"/>
+      <c r="B3" s="267"/>
       <c r="C3" s="133"/>
       <c r="D3" s="133"/>
       <c r="E3" s="133"/>
@@ -28905,10 +28905,10 @@
       <c r="P3" s="133"/>
     </row>
     <row r="4" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="267" t="s">
+      <c r="A4" s="269" t="s">
         <v>255</v>
       </c>
-      <c r="B4" s="267" t="s">
+      <c r="B4" s="269" t="s">
         <v>39</v>
       </c>
       <c r="C4" s="141"/>
@@ -28916,70 +28916,70 @@
       <c r="E4" s="141"/>
       <c r="F4" s="141"/>
       <c r="G4" s="141"/>
-      <c r="H4" s="266"/>
-      <c r="I4" s="266"/>
-      <c r="J4" s="266"/>
-      <c r="K4" s="266"/>
-      <c r="L4" s="266"/>
-      <c r="M4" s="266"/>
-      <c r="N4" s="266"/>
-      <c r="O4" s="266"/>
-      <c r="P4" s="266"/>
+      <c r="H4" s="268"/>
+      <c r="I4" s="268"/>
+      <c r="J4" s="268"/>
+      <c r="K4" s="268"/>
+      <c r="L4" s="268"/>
+      <c r="M4" s="268"/>
+      <c r="N4" s="268"/>
+      <c r="O4" s="268"/>
+      <c r="P4" s="268"/>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A5" s="270"/>
-      <c r="B5" s="270"/>
-      <c r="C5" s="267" t="s">
+      <c r="A5" s="272"/>
+      <c r="B5" s="272"/>
+      <c r="C5" s="269" t="s">
         <v>256</v>
       </c>
-      <c r="D5" s="267" t="s">
+      <c r="D5" s="269" t="s">
         <v>257</v>
       </c>
-      <c r="E5" s="268"/>
-      <c r="F5" s="267" t="s">
+      <c r="E5" s="270"/>
+      <c r="F5" s="269" t="s">
         <v>258</v>
       </c>
-      <c r="G5" s="268"/>
-      <c r="H5" s="267" t="s">
+      <c r="G5" s="270"/>
+      <c r="H5" s="269" t="s">
         <v>259</v>
       </c>
-      <c r="I5" s="268"/>
-      <c r="J5" s="267" t="s">
+      <c r="I5" s="270"/>
+      <c r="J5" s="269" t="s">
         <v>260</v>
       </c>
-      <c r="K5" s="268"/>
-      <c r="L5" s="271" t="s">
+      <c r="K5" s="270"/>
+      <c r="L5" s="273" t="s">
         <v>261</v>
       </c>
-      <c r="M5" s="268"/>
-      <c r="N5" s="266" t="s">
+      <c r="M5" s="270"/>
+      <c r="N5" s="268" t="s">
         <v>262</v>
       </c>
-      <c r="O5" s="272"/>
-      <c r="P5" s="267" t="s">
+      <c r="O5" s="274"/>
+      <c r="P5" s="269" t="s">
         <v>266</v>
       </c>
-      <c r="R5" s="273" t="s">
+      <c r="R5" s="263" t="s">
         <v>34</v>
       </c>
-      <c r="S5" s="273" t="s">
+      <c r="S5" s="263" t="s">
         <v>289</v>
       </c>
-      <c r="T5" s="273" t="s">
+      <c r="T5" s="263" t="s">
         <v>290</v>
       </c>
-      <c r="U5" s="273" t="s">
+      <c r="U5" s="263" t="s">
         <v>292</v>
       </c>
-      <c r="V5" s="274" t="s">
+      <c r="V5" s="264" t="s">
         <v>291</v>
       </c>
       <c r="W5" s="172"/>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A6" s="269"/>
-      <c r="B6" s="269"/>
-      <c r="C6" s="270"/>
+      <c r="A6" s="271"/>
+      <c r="B6" s="271"/>
+      <c r="C6" s="272"/>
       <c r="D6" s="134" t="s">
         <v>2</v>
       </c>
@@ -29016,12 +29016,12 @@
       <c r="O6" s="134" t="s">
         <v>263</v>
       </c>
-      <c r="P6" s="269"/>
-      <c r="R6" s="273"/>
-      <c r="S6" s="273"/>
-      <c r="T6" s="273"/>
-      <c r="U6" s="273"/>
-      <c r="V6" s="273"/>
+      <c r="P6" s="271"/>
+      <c r="R6" s="263"/>
+      <c r="S6" s="263"/>
+      <c r="T6" s="263"/>
+      <c r="U6" s="263"/>
+      <c r="V6" s="263"/>
       <c r="W6" s="172"/>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.45">
@@ -29029,16 +29029,16 @@
         <v>179</v>
       </c>
       <c r="B7" s="190" t="s">
-        <v>101</v>
+        <v>288</v>
       </c>
       <c r="C7" s="190" t="s">
-        <v>102</v>
+        <v>284</v>
       </c>
       <c r="D7" s="191">
-        <v>454</v>
+        <v>318</v>
       </c>
       <c r="E7" s="191">
-        <v>70243418</v>
+        <v>50351985</v>
       </c>
       <c r="F7" s="191">
         <v>0</v>
@@ -29047,32 +29047,32 @@
         <v>0</v>
       </c>
       <c r="H7" s="191">
-        <v>454</v>
+        <v>318</v>
       </c>
       <c r="I7" s="191">
-        <v>70243418</v>
+        <v>50351985</v>
       </c>
       <c r="J7" s="191">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="K7" s="191">
-        <v>4265641</v>
+        <v>205000</v>
       </c>
       <c r="L7" s="191">
-        <v>402</v>
+        <v>272</v>
       </c>
       <c r="M7" s="191">
-        <v>61794506</v>
+        <v>44738967</v>
       </c>
       <c r="N7" s="192">
-        <v>88.55</v>
+        <v>85.53</v>
       </c>
       <c r="O7" s="192">
-        <v>87.97</v>
+        <v>88.85</v>
       </c>
       <c r="P7" s="135">
         <f>I7*0.97-M7</f>
-        <v>6341609.4599999934</v>
+        <v>4102458.4499999955</v>
       </c>
       <c r="R7" s="173" t="s">
         <v>117</v>
@@ -29086,11 +29086,11 @@
       </c>
       <c r="U7" s="189">
         <f>VLOOKUP(R7,$C$7:$P$27,14,0)</f>
-        <v>17116720.799999997</v>
+        <v>16052355.799999997</v>
       </c>
       <c r="V7" s="175">
         <f>VLOOKUP(R7,$C$7:$P$27,14,0)-T7</f>
-        <v>-6122769</v>
+        <v>-7187134</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.45">
@@ -29098,16 +29098,16 @@
         <v>179</v>
       </c>
       <c r="B8" s="193" t="s">
-        <v>68</v>
+        <v>101</v>
       </c>
       <c r="C8" s="193" t="s">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="D8" s="194">
-        <v>434</v>
+        <v>454</v>
       </c>
       <c r="E8" s="194">
-        <v>72573808</v>
+        <v>70243418</v>
       </c>
       <c r="F8" s="194">
         <v>0</v>
@@ -29116,32 +29116,32 @@
         <v>0</v>
       </c>
       <c r="H8" s="194">
-        <v>434</v>
+        <v>454</v>
       </c>
       <c r="I8" s="194">
-        <v>72573808</v>
+        <v>70243418</v>
       </c>
       <c r="J8" s="194">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K8" s="194">
-        <v>2760329</v>
+        <v>0</v>
       </c>
       <c r="L8" s="194">
-        <v>388</v>
+        <v>405</v>
       </c>
       <c r="M8" s="194">
-        <v>63028138</v>
+        <v>62386506</v>
       </c>
       <c r="N8" s="195">
-        <v>89.4</v>
+        <v>89.21</v>
       </c>
       <c r="O8" s="195">
-        <v>86.85</v>
+        <v>88.81</v>
       </c>
       <c r="P8" s="135">
         <f t="shared" ref="P8:P27" si="0">I8*0.97-M8</f>
-        <v>7368455.7600000054</v>
+        <v>5749609.4599999934</v>
       </c>
       <c r="R8" s="173" t="s">
         <v>67</v>
@@ -29155,11 +29155,11 @@
       </c>
       <c r="U8" s="189">
         <f t="shared" ref="U8:U17" si="2">VLOOKUP(R8,$C$7:$P$27,14,0)</f>
-        <v>18332228.310000002</v>
+        <v>17997728.310000002</v>
       </c>
       <c r="V8" s="175">
         <f t="shared" ref="V8:V17" si="3">VLOOKUP(R8,$C$7:$P$27,14,0)-T8</f>
-        <v>-6225853</v>
+        <v>-6560353</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.45">
@@ -29167,16 +29167,16 @@
         <v>179</v>
       </c>
       <c r="B9" s="190" t="s">
-        <v>288</v>
+        <v>68</v>
       </c>
       <c r="C9" s="190" t="s">
-        <v>284</v>
+        <v>69</v>
       </c>
       <c r="D9" s="191">
-        <v>318</v>
+        <v>434</v>
       </c>
       <c r="E9" s="191">
-        <v>50351985</v>
+        <v>72573808</v>
       </c>
       <c r="F9" s="191">
         <v>0</v>
@@ -29185,32 +29185,32 @@
         <v>0</v>
       </c>
       <c r="H9" s="191">
-        <v>318</v>
+        <v>434</v>
       </c>
       <c r="I9" s="191">
-        <v>50351985</v>
+        <v>72573808</v>
       </c>
       <c r="J9" s="191">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K9" s="191">
-        <v>5920895</v>
+        <v>0</v>
       </c>
       <c r="L9" s="191">
-        <v>261</v>
+        <v>389</v>
       </c>
       <c r="M9" s="191">
-        <v>42943093</v>
+        <v>63048138</v>
       </c>
       <c r="N9" s="192">
-        <v>82.08</v>
+        <v>89.63</v>
       </c>
       <c r="O9" s="192">
-        <v>85.29</v>
+        <v>86.87</v>
       </c>
       <c r="P9" s="135">
         <f t="shared" si="0"/>
-        <v>5898332.4499999955</v>
+        <v>7348455.7600000054</v>
       </c>
       <c r="R9" s="174" t="s">
         <v>87</v>
@@ -29224,28 +29224,28 @@
       </c>
       <c r="U9" s="189">
         <f t="shared" si="2"/>
-        <v>30707826.270000011</v>
+        <v>26717600.270000011</v>
       </c>
       <c r="V9" s="175">
         <f t="shared" si="3"/>
-        <v>-5251752</v>
+        <v>-9241978</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A10" s="193" t="s">
-        <v>128</v>
+        <v>179</v>
       </c>
       <c r="B10" s="193" t="s">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="C10" s="193" t="s">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="D10" s="194">
-        <v>876</v>
+        <v>716</v>
       </c>
       <c r="E10" s="194">
-        <v>145101823</v>
+        <v>116427734</v>
       </c>
       <c r="F10" s="194">
         <v>0</v>
@@ -29254,32 +29254,32 @@
         <v>0</v>
       </c>
       <c r="H10" s="194">
-        <v>876</v>
+        <v>716</v>
       </c>
       <c r="I10" s="194">
-        <v>145101823</v>
+        <v>116427734</v>
       </c>
       <c r="J10" s="194">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="K10" s="194">
-        <v>7535812</v>
+        <v>140000</v>
       </c>
       <c r="L10" s="194">
-        <v>728</v>
+        <v>591</v>
       </c>
       <c r="M10" s="194">
-        <v>122416540</v>
+        <v>98695646</v>
       </c>
       <c r="N10" s="195">
-        <v>83.11</v>
+        <v>82.54</v>
       </c>
       <c r="O10" s="195">
-        <v>84.37</v>
+        <v>84.77</v>
       </c>
       <c r="P10" s="135">
         <f t="shared" si="0"/>
-        <v>18332228.310000002</v>
+        <v>14239255.980000004</v>
       </c>
       <c r="R10" s="174" t="s">
         <v>110</v>
@@ -29293,28 +29293,28 @@
       </c>
       <c r="U10" s="189">
         <f t="shared" si="2"/>
-        <v>42404016.859999985</v>
+        <v>41487548.859999985</v>
       </c>
       <c r="V10" s="175">
         <f t="shared" si="3"/>
-        <v>-3782226</v>
+        <v>-4698694</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A11" s="190" t="s">
-        <v>179</v>
+        <v>128</v>
       </c>
       <c r="B11" s="190" t="s">
-        <v>104</v>
+        <v>66</v>
       </c>
       <c r="C11" s="190" t="s">
-        <v>105</v>
+        <v>67</v>
       </c>
       <c r="D11" s="191">
-        <v>716</v>
+        <v>876</v>
       </c>
       <c r="E11" s="191">
-        <v>116427734</v>
+        <v>145101823</v>
       </c>
       <c r="F11" s="191">
         <v>0</v>
@@ -29323,32 +29323,32 @@
         <v>0</v>
       </c>
       <c r="H11" s="191">
-        <v>716</v>
+        <v>876</v>
       </c>
       <c r="I11" s="191">
-        <v>116427734</v>
+        <v>145101823</v>
       </c>
       <c r="J11" s="191">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="K11" s="191">
-        <v>8397670</v>
+        <v>334500</v>
       </c>
       <c r="L11" s="191">
-        <v>587</v>
+        <v>729</v>
       </c>
       <c r="M11" s="191">
-        <v>97820646</v>
+        <v>122751040</v>
       </c>
       <c r="N11" s="192">
-        <v>81.98</v>
+        <v>83.22</v>
       </c>
       <c r="O11" s="192">
-        <v>84.02</v>
+        <v>84.6</v>
       </c>
       <c r="P11" s="135">
         <f t="shared" si="0"/>
-        <v>15114255.980000004</v>
+        <v>17997728.310000002</v>
       </c>
       <c r="R11" s="173" t="s">
         <v>99</v>
@@ -29362,11 +29362,11 @@
       </c>
       <c r="U11" s="189">
         <f t="shared" si="2"/>
-        <v>26230855.75</v>
+        <v>18693450.75</v>
       </c>
       <c r="V11" s="175">
         <f t="shared" si="3"/>
-        <v>-3269885</v>
+        <v>-10807290</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.45">
@@ -29398,26 +29398,26 @@
         <v>180440547</v>
       </c>
       <c r="J12" s="194">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="K12" s="194">
-        <v>10913215</v>
+        <v>556433</v>
       </c>
       <c r="L12" s="194">
-        <v>859</v>
+        <v>866</v>
       </c>
       <c r="M12" s="194">
-        <v>151013262</v>
+        <v>152127195</v>
       </c>
       <c r="N12" s="195">
-        <v>81.97</v>
+        <v>82.63</v>
       </c>
       <c r="O12" s="195">
-        <v>83.69</v>
+        <v>84.31</v>
       </c>
       <c r="P12" s="135">
         <f t="shared" si="0"/>
-        <v>24014068.590000004</v>
+        <v>22900135.590000004</v>
       </c>
       <c r="R12" s="173" t="s">
         <v>75</v>
@@ -29431,11 +29431,11 @@
       </c>
       <c r="U12" s="189">
         <f t="shared" si="2"/>
-        <v>23492697.520000011</v>
+        <v>22033021.520000011</v>
       </c>
       <c r="V12" s="175">
         <f t="shared" si="3"/>
-        <v>-7704406</v>
+        <v>-9164082</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.45">
@@ -29443,16 +29443,16 @@
         <v>179</v>
       </c>
       <c r="B13" s="190" t="s">
-        <v>122</v>
+        <v>89</v>
       </c>
       <c r="C13" s="190" t="s">
-        <v>123</v>
+        <v>90</v>
       </c>
       <c r="D13" s="191">
-        <v>308</v>
+        <v>356</v>
       </c>
       <c r="E13" s="191">
-        <v>51982396</v>
+        <v>53605661</v>
       </c>
       <c r="F13" s="191">
         <v>0</v>
@@ -29461,32 +29461,32 @@
         <v>0</v>
       </c>
       <c r="H13" s="191">
-        <v>308</v>
+        <v>356</v>
       </c>
       <c r="I13" s="191">
-        <v>51982396</v>
+        <v>53605661</v>
       </c>
       <c r="J13" s="191">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="K13" s="191">
-        <v>3001015</v>
+        <v>353627</v>
       </c>
       <c r="L13" s="191">
-        <v>254</v>
+        <v>290</v>
       </c>
       <c r="M13" s="191">
-        <v>43395854</v>
+        <v>45077922</v>
       </c>
       <c r="N13" s="192">
-        <v>82.47</v>
+        <v>81.459999999999994</v>
       </c>
       <c r="O13" s="192">
-        <v>83.48</v>
+        <v>84.09</v>
       </c>
       <c r="P13" s="135">
         <f t="shared" si="0"/>
-        <v>7027070.1199999973</v>
+        <v>6919569.1700000018</v>
       </c>
       <c r="R13" s="173" t="s">
         <v>107</v>
@@ -29500,11 +29500,11 @@
       </c>
       <c r="U13" s="189">
         <f t="shared" si="2"/>
-        <v>24014068.590000004</v>
+        <v>22900135.590000004</v>
       </c>
       <c r="V13" s="175">
         <f t="shared" si="3"/>
-        <v>-7821939</v>
+        <v>-8935872</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.45">
@@ -29536,26 +29536,26 @@
         <v>93597302</v>
       </c>
       <c r="J14" s="194">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K14" s="194">
-        <v>5828410</v>
+        <v>0</v>
       </c>
       <c r="L14" s="194">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="M14" s="194">
-        <v>77879062</v>
+        <v>78494292</v>
       </c>
       <c r="N14" s="195">
-        <v>81.569999999999993</v>
+        <v>82.29</v>
       </c>
       <c r="O14" s="195">
-        <v>83.21</v>
+        <v>83.86</v>
       </c>
       <c r="P14" s="135">
         <f t="shared" si="0"/>
-        <v>12910320.939999998</v>
+        <v>12295090.939999998</v>
       </c>
       <c r="R14" s="174" t="s">
         <v>72</v>
@@ -29569,11 +29569,11 @@
       </c>
       <c r="U14" s="189">
         <f t="shared" si="2"/>
-        <v>31740385.199999988</v>
+        <v>30539293.199999988</v>
       </c>
       <c r="V14" s="175">
         <f t="shared" si="3"/>
-        <v>-9972524</v>
+        <v>-11173616</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.45">
@@ -29581,16 +29581,16 @@
         <v>179</v>
       </c>
       <c r="B15" s="190" t="s">
-        <v>89</v>
+        <v>122</v>
       </c>
       <c r="C15" s="190" t="s">
-        <v>90</v>
+        <v>123</v>
       </c>
       <c r="D15" s="191">
-        <v>356</v>
+        <v>308</v>
       </c>
       <c r="E15" s="191">
-        <v>53605661</v>
+        <v>51982396</v>
       </c>
       <c r="F15" s="191">
         <v>0</v>
@@ -29599,32 +29599,32 @@
         <v>0</v>
       </c>
       <c r="H15" s="191">
-        <v>356</v>
+        <v>308</v>
       </c>
       <c r="I15" s="191">
-        <v>53605661</v>
+        <v>51982396</v>
       </c>
       <c r="J15" s="191">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K15" s="191">
-        <v>4972415</v>
+        <v>0</v>
       </c>
       <c r="L15" s="191">
-        <v>286</v>
+        <v>254</v>
       </c>
       <c r="M15" s="191">
-        <v>44552295</v>
+        <v>43395854</v>
       </c>
       <c r="N15" s="192">
-        <v>80.34</v>
+        <v>82.47</v>
       </c>
       <c r="O15" s="192">
-        <v>83.11</v>
+        <v>83.48</v>
       </c>
       <c r="P15" s="135">
         <f t="shared" si="0"/>
-        <v>7445196.1700000018</v>
+        <v>7027070.1199999973</v>
       </c>
       <c r="R15" s="174" t="s">
         <v>113</v>
@@ -29638,11 +29638,11 @@
       </c>
       <c r="U15" s="189">
         <f t="shared" si="2"/>
-        <v>47005029.400000006</v>
+        <v>46118158.400000006</v>
       </c>
       <c r="V15" s="175">
         <f t="shared" si="3"/>
-        <v>-12628777</v>
+        <v>-13515648</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.45">
@@ -29650,16 +29650,16 @@
         <v>129</v>
       </c>
       <c r="B16" s="193" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C16" s="193" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D16" s="194">
-        <v>683</v>
+        <v>941</v>
       </c>
       <c r="E16" s="194">
-        <v>105983346</v>
+        <v>152862316</v>
       </c>
       <c r="F16" s="194">
         <v>0</v>
@@ -29668,32 +29668,32 @@
         <v>0</v>
       </c>
       <c r="H16" s="194">
-        <v>683</v>
+        <v>941</v>
       </c>
       <c r="I16" s="194">
-        <v>105983346</v>
+        <v>152862316</v>
       </c>
       <c r="J16" s="194">
-        <v>273</v>
+        <v>1</v>
       </c>
       <c r="K16" s="194">
-        <v>42777833</v>
+        <v>119835</v>
       </c>
       <c r="L16" s="194">
-        <v>551</v>
+        <v>749</v>
       </c>
       <c r="M16" s="194">
-        <v>86621147</v>
+        <v>126243425</v>
       </c>
       <c r="N16" s="195">
-        <v>80.67</v>
+        <v>79.599999999999994</v>
       </c>
       <c r="O16" s="195">
-        <v>81.73</v>
+        <v>82.59</v>
       </c>
       <c r="P16" s="135">
         <f t="shared" si="0"/>
-        <v>16182698.61999999</v>
+        <v>22033021.520000011</v>
       </c>
       <c r="R16" s="174" t="s">
         <v>119</v>
@@ -29707,28 +29707,28 @@
       </c>
       <c r="U16" s="189">
         <f t="shared" si="2"/>
-        <v>30837114.409999996</v>
+        <v>29992114.409999996</v>
       </c>
       <c r="V16" s="175">
         <f t="shared" si="3"/>
-        <v>-6729817</v>
+        <v>-7574817</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A17" s="190" t="s">
-        <v>129</v>
+        <v>179</v>
       </c>
       <c r="B17" s="190" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C17" s="190" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D17" s="191">
-        <v>941</v>
+        <v>546</v>
       </c>
       <c r="E17" s="191">
-        <v>152862316</v>
+        <v>89879995</v>
       </c>
       <c r="F17" s="191">
         <v>0</v>
@@ -29737,32 +29737,32 @@
         <v>0</v>
       </c>
       <c r="H17" s="191">
-        <v>941</v>
+        <v>546</v>
       </c>
       <c r="I17" s="191">
-        <v>152862316</v>
+        <v>89879995</v>
       </c>
       <c r="J17" s="191">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="K17" s="191">
-        <v>9044977</v>
+        <v>9221509</v>
       </c>
       <c r="L17" s="191">
-        <v>740</v>
+        <v>436</v>
       </c>
       <c r="M17" s="191">
-        <v>124783749</v>
+        <v>74117019</v>
       </c>
       <c r="N17" s="192">
-        <v>78.64</v>
+        <v>79.849999999999994</v>
       </c>
       <c r="O17" s="192">
-        <v>81.63</v>
+        <v>82.46</v>
       </c>
       <c r="P17" s="135">
         <f t="shared" si="0"/>
-        <v>23492697.520000011</v>
+        <v>13066576.149999991</v>
       </c>
       <c r="R17" s="173" t="s">
         <v>84</v>
@@ -29776,11 +29776,11 @@
       </c>
       <c r="U17" s="189">
         <f t="shared" si="2"/>
-        <v>17611017.670000002</v>
+        <v>17311017.670000002</v>
       </c>
       <c r="V17" s="175">
         <f t="shared" si="3"/>
-        <v>-4899753</v>
+        <v>-5199753</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.45">
@@ -29788,16 +29788,16 @@
         <v>129</v>
       </c>
       <c r="B18" s="193" t="s">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="C18" s="193" t="s">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="D18" s="194">
-        <v>1181</v>
+        <v>683</v>
       </c>
       <c r="E18" s="194">
-        <v>189656153</v>
+        <v>105983346</v>
       </c>
       <c r="F18" s="194">
         <v>0</v>
@@ -29806,32 +29806,32 @@
         <v>0</v>
       </c>
       <c r="H18" s="194">
-        <v>1181</v>
+        <v>683</v>
       </c>
       <c r="I18" s="194">
-        <v>189656153</v>
+        <v>105983346</v>
       </c>
       <c r="J18" s="194">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="K18" s="194">
-        <v>8704685</v>
+        <v>0</v>
       </c>
       <c r="L18" s="194">
-        <v>941</v>
+        <v>552</v>
       </c>
       <c r="M18" s="194">
-        <v>153129354</v>
+        <v>86701147</v>
       </c>
       <c r="N18" s="195">
-        <v>79.680000000000007</v>
+        <v>80.819999999999993</v>
       </c>
       <c r="O18" s="195">
-        <v>80.739999999999995</v>
+        <v>81.81</v>
       </c>
       <c r="P18" s="135">
         <f t="shared" si="0"/>
-        <v>30837114.409999996</v>
+        <v>16102698.61999999</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.45">
@@ -29863,26 +29863,26 @@
         <v>101866340</v>
       </c>
       <c r="J19" s="191">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K19" s="191">
-        <v>7677756</v>
+        <v>0</v>
       </c>
       <c r="L19" s="191">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="M19" s="191">
-        <v>81693629</v>
+        <v>82757994</v>
       </c>
       <c r="N19" s="192">
-        <v>77.41</v>
+        <v>78.5</v>
       </c>
       <c r="O19" s="192">
-        <v>80.2</v>
+        <v>81.239999999999995</v>
       </c>
       <c r="P19" s="135">
         <f t="shared" si="0"/>
-        <v>17116720.799999997</v>
+        <v>16052355.799999997</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.45">
@@ -29890,16 +29890,16 @@
         <v>129</v>
       </c>
       <c r="B20" s="193" t="s">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="C20" s="193" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="D20" s="194">
-        <v>588</v>
+        <v>1181</v>
       </c>
       <c r="E20" s="194">
-        <v>95369711</v>
+        <v>189656153</v>
       </c>
       <c r="F20" s="194">
         <v>0</v>
@@ -29908,49 +29908,49 @@
         <v>0</v>
       </c>
       <c r="H20" s="194">
-        <v>588</v>
+        <v>1181</v>
       </c>
       <c r="I20" s="194">
-        <v>95369711</v>
+        <v>189656153</v>
       </c>
       <c r="J20" s="194">
-        <v>124</v>
+        <v>1</v>
       </c>
       <c r="K20" s="194">
-        <v>19056657</v>
+        <v>285000</v>
       </c>
       <c r="L20" s="194">
-        <v>458</v>
+        <v>945</v>
       </c>
       <c r="M20" s="194">
-        <v>74897602</v>
+        <v>153974354</v>
       </c>
       <c r="N20" s="195">
-        <v>77.89</v>
+        <v>80.02</v>
       </c>
       <c r="O20" s="195">
-        <v>78.53</v>
+        <v>81.19</v>
       </c>
       <c r="P20" s="135">
         <f t="shared" si="0"/>
-        <v>17611017.670000002</v>
+        <v>29992114.409999996</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A21" s="190" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B21" s="190" t="s">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="C21" s="190" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="D21" s="191">
-        <v>968</v>
+        <v>687</v>
       </c>
       <c r="E21" s="191">
-        <v>162344260</v>
+        <v>105953075</v>
       </c>
       <c r="F21" s="191">
         <v>0</v>
@@ -29959,49 +29959,49 @@
         <v>0</v>
       </c>
       <c r="H21" s="191">
-        <v>968</v>
+        <v>687</v>
       </c>
       <c r="I21" s="191">
-        <v>162344260</v>
+        <v>105953075</v>
       </c>
       <c r="J21" s="191">
-        <v>76</v>
+        <v>1</v>
       </c>
       <c r="K21" s="191">
-        <v>12177318</v>
+        <v>165000</v>
       </c>
       <c r="L21" s="191">
-        <v>743</v>
+        <v>532</v>
       </c>
       <c r="M21" s="191">
-        <v>125733547</v>
+        <v>84081032</v>
       </c>
       <c r="N21" s="192">
-        <v>76.760000000000005</v>
+        <v>77.44</v>
       </c>
       <c r="O21" s="192">
-        <v>77.45</v>
+        <v>79.36</v>
       </c>
       <c r="P21" s="135">
         <f t="shared" si="0"/>
-        <v>31740385.199999988</v>
+        <v>18693450.75</v>
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A22" s="193" t="s">
-        <v>179</v>
+        <v>129</v>
       </c>
       <c r="B22" s="193" t="s">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="C22" s="193" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="D22" s="194">
-        <v>415</v>
+        <v>588</v>
       </c>
       <c r="E22" s="194">
-        <v>66800107</v>
+        <v>95369711</v>
       </c>
       <c r="F22" s="194">
         <v>0</v>
@@ -30010,49 +30010,49 @@
         <v>0</v>
       </c>
       <c r="H22" s="194">
-        <v>415</v>
+        <v>588</v>
       </c>
       <c r="I22" s="194">
-        <v>66800107</v>
+        <v>95369711</v>
       </c>
       <c r="J22" s="194">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="K22" s="194">
-        <v>2117813</v>
+        <v>210000</v>
       </c>
       <c r="L22" s="194">
-        <v>308</v>
+        <v>460</v>
       </c>
       <c r="M22" s="194">
-        <v>51430398</v>
+        <v>75197602</v>
       </c>
       <c r="N22" s="195">
-        <v>74.22</v>
+        <v>78.23</v>
       </c>
       <c r="O22" s="195">
-        <v>76.989999999999995</v>
+        <v>78.849999999999994</v>
       </c>
       <c r="P22" s="135">
         <f t="shared" si="0"/>
-        <v>13365705.789999999</v>
+        <v>17311017.670000002</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A23" s="190" t="s">
-        <v>128</v>
+        <v>179</v>
       </c>
       <c r="B23" s="190" t="s">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="C23" s="190" t="s">
-        <v>87</v>
+        <v>121</v>
       </c>
       <c r="D23" s="191">
-        <v>853</v>
+        <v>415</v>
       </c>
       <c r="E23" s="191">
-        <v>141474291</v>
+        <v>66800107</v>
       </c>
       <c r="F23" s="191">
         <v>0</v>
@@ -30061,32 +30061,32 @@
         <v>0</v>
       </c>
       <c r="H23" s="191">
-        <v>853</v>
+        <v>415</v>
       </c>
       <c r="I23" s="191">
-        <v>141474291</v>
+        <v>66800107</v>
       </c>
       <c r="J23" s="191">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="K23" s="191">
-        <v>7328212</v>
+        <v>237402</v>
       </c>
       <c r="L23" s="191">
-        <v>642</v>
+        <v>314</v>
       </c>
       <c r="M23" s="191">
-        <v>106522236</v>
+        <v>52293422</v>
       </c>
       <c r="N23" s="192">
-        <v>75.260000000000005</v>
+        <v>75.66</v>
       </c>
       <c r="O23" s="192">
-        <v>75.290000000000006</v>
+        <v>78.28</v>
       </c>
       <c r="P23" s="135">
         <f t="shared" si="0"/>
-        <v>30707826.270000011</v>
+        <v>12502681.789999999</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.45">
@@ -30094,16 +30094,16 @@
         <v>129</v>
       </c>
       <c r="B24" s="193" t="s">
-        <v>112</v>
+        <v>71</v>
       </c>
       <c r="C24" s="193" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
       <c r="D24" s="194">
-        <v>1198</v>
+        <v>968</v>
       </c>
       <c r="E24" s="194">
-        <v>194517020</v>
+        <v>162344260</v>
       </c>
       <c r="F24" s="194">
         <v>0</v>
@@ -30112,32 +30112,32 @@
         <v>0</v>
       </c>
       <c r="H24" s="194">
-        <v>1198</v>
+        <v>968</v>
       </c>
       <c r="I24" s="194">
-        <v>194517020</v>
+        <v>162344260</v>
       </c>
       <c r="J24" s="194">
-        <v>94</v>
+        <v>1</v>
       </c>
       <c r="K24" s="194">
-        <v>15632452</v>
+        <v>109968</v>
       </c>
       <c r="L24" s="194">
-        <v>852</v>
+        <v>756</v>
       </c>
       <c r="M24" s="194">
-        <v>141676480</v>
+        <v>126934639</v>
       </c>
       <c r="N24" s="195">
-        <v>71.12</v>
+        <v>78.099999999999994</v>
       </c>
       <c r="O24" s="195">
-        <v>72.84</v>
+        <v>78.19</v>
       </c>
       <c r="P24" s="135">
         <f t="shared" si="0"/>
-        <v>47005029.400000006</v>
+        <v>30539293.199999988</v>
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.45">
@@ -30145,16 +30145,16 @@
         <v>128</v>
       </c>
       <c r="B25" s="190" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="C25" s="190" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="D25" s="191">
-        <v>687</v>
+        <v>853</v>
       </c>
       <c r="E25" s="191">
-        <v>105953075</v>
+        <v>141474291</v>
       </c>
       <c r="F25" s="191">
         <v>0</v>
@@ -30163,49 +30163,49 @@
         <v>0</v>
       </c>
       <c r="H25" s="191">
-        <v>687</v>
+        <v>853</v>
       </c>
       <c r="I25" s="191">
-        <v>105953075</v>
+        <v>141474291</v>
       </c>
       <c r="J25" s="191">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="K25" s="191">
-        <v>5197166</v>
+        <v>245000</v>
       </c>
       <c r="L25" s="191">
-        <v>486</v>
+        <v>664</v>
       </c>
       <c r="M25" s="191">
-        <v>76543627</v>
+        <v>110512462</v>
       </c>
       <c r="N25" s="192">
-        <v>70.739999999999995</v>
+        <v>77.84</v>
       </c>
       <c r="O25" s="192">
-        <v>72.239999999999995</v>
+        <v>78.11</v>
       </c>
       <c r="P25" s="135">
         <f t="shared" si="0"/>
-        <v>26230855.75</v>
+        <v>26717600.270000011</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A26" s="193" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B26" s="193" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C26" s="193" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D26" s="194">
-        <v>892</v>
+        <v>1198</v>
       </c>
       <c r="E26" s="194">
-        <v>149379338</v>
+        <v>194517020</v>
       </c>
       <c r="F26" s="194">
         <v>0</v>
@@ -30214,49 +30214,49 @@
         <v>0</v>
       </c>
       <c r="H26" s="194">
-        <v>892</v>
+        <v>1198</v>
       </c>
       <c r="I26" s="194">
-        <v>149379338</v>
+        <v>194517020</v>
       </c>
       <c r="J26" s="194">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="K26" s="194">
-        <v>12187071</v>
+        <v>380000</v>
       </c>
       <c r="L26" s="194">
-        <v>625</v>
+        <v>856</v>
       </c>
       <c r="M26" s="194">
-        <v>102493941</v>
+        <v>142563351</v>
       </c>
       <c r="N26" s="195">
-        <v>70.069999999999993</v>
+        <v>71.45</v>
       </c>
       <c r="O26" s="195">
-        <v>68.61</v>
+        <v>73.290000000000006</v>
       </c>
       <c r="P26" s="135">
         <f t="shared" si="0"/>
-        <v>42404016.859999985</v>
+        <v>46118158.400000006</v>
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A27" s="190" t="s">
-        <v>179</v>
+        <v>128</v>
       </c>
       <c r="B27" s="190" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="C27" s="190" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="D27" s="191">
-        <v>546</v>
+        <v>892</v>
       </c>
       <c r="E27" s="191">
-        <v>89879995</v>
+        <v>149379338</v>
       </c>
       <c r="F27" s="191">
         <v>0</v>
@@ -30265,41 +30265,36 @@
         <v>0</v>
       </c>
       <c r="H27" s="191">
-        <v>546</v>
+        <v>892</v>
       </c>
       <c r="I27" s="191">
-        <v>89879995</v>
+        <v>149379338</v>
       </c>
       <c r="J27" s="191">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="K27" s="191">
-        <v>4450889</v>
+        <v>282349</v>
       </c>
       <c r="L27" s="191">
-        <v>360</v>
+        <v>632</v>
       </c>
       <c r="M27" s="191">
-        <v>60568049</v>
+        <v>103410409</v>
       </c>
       <c r="N27" s="192">
-        <v>65.930000000000007</v>
+        <v>70.849999999999994</v>
       </c>
       <c r="O27" s="192">
-        <v>67.39</v>
+        <v>69.23</v>
       </c>
       <c r="P27" s="135">
         <f t="shared" si="0"/>
-        <v>26615546.149999991</v>
+        <v>41487548.859999985</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="U5:U6"/>
-    <mergeCell ref="V5:V6"/>
-    <mergeCell ref="R5:R6"/>
-    <mergeCell ref="S5:S6"/>
-    <mergeCell ref="T5:T6"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
     <mergeCell ref="A3:B3"/>
@@ -30314,6 +30309,11 @@
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="L5:M5"/>
     <mergeCell ref="N5:O5"/>
+    <mergeCell ref="U5:U6"/>
+    <mergeCell ref="V5:V6"/>
+    <mergeCell ref="R5:R6"/>
+    <mergeCell ref="S5:S6"/>
+    <mergeCell ref="T5:T6"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="P7:P27">

--- a/filetiendo.xlsx
+++ b/filetiendo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\viettel 2026\thang 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DE384A6-4232-461E-959E-21F4D7E6C84F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E11F8EA0-BDE0-4D1F-82DB-7444F7E0F384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="808" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4189,17 +4189,41 @@
     <xf numFmtId="0" fontId="65" fillId="0" borderId="94" xfId="11" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="94" xfId="11" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="162" xfId="11" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="49" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="5" borderId="112" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="120" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="119" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="118" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="5" borderId="115" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="113" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="125" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="124" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="123" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="5" borderId="112" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="24" borderId="117" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4213,34 +4237,10 @@
     <xf numFmtId="0" fontId="17" fillId="5" borderId="114" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="120" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="119" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="118" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="35" fillId="16" borderId="121" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="2" borderId="122" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="125" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="124" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="123" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="66" fillId="18" borderId="150" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4312,16 +4312,16 @@
     <xf numFmtId="0" fontId="62" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="133" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="132" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="46" fillId="5" borderId="137" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="5" borderId="136" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="133" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="132" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="50" fillId="5" borderId="135" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4341,12 +4341,6 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="140" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="143" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="142" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="144" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4372,10 +4366,10 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="149" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="68" fillId="29" borderId="150" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="143" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="68" fillId="29" borderId="150" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="142" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4400,6 +4394,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="153" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="68" fillId="29" borderId="150" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="29" borderId="150" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="12">
     <cellStyle name="Comma" xfId="8" builtinId="3"/>
@@ -5289,166 +5289,166 @@
       </c>
     </row>
     <row r="2" spans="1:675" ht="23.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="183" t="s">
+      <c r="A2" s="193" t="s">
         <v>34</v>
       </c>
       <c r="B2" s="69"/>
       <c r="C2" s="15"/>
-      <c r="D2" s="194" t="s">
+      <c r="D2" s="199" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="194"/>
-      <c r="F2" s="194"/>
-      <c r="G2" s="194"/>
-      <c r="H2" s="194"/>
-      <c r="I2" s="194"/>
-      <c r="J2" s="194"/>
-      <c r="K2" s="194"/>
-      <c r="L2" s="194"/>
-      <c r="M2" s="194"/>
-      <c r="N2" s="194"/>
-      <c r="O2" s="194"/>
-      <c r="P2" s="194"/>
-      <c r="Q2" s="194"/>
-      <c r="R2" s="194"/>
-      <c r="S2" s="194"/>
-      <c r="T2" s="189" t="s">
+      <c r="E2" s="199"/>
+      <c r="F2" s="199"/>
+      <c r="G2" s="199"/>
+      <c r="H2" s="199"/>
+      <c r="I2" s="199"/>
+      <c r="J2" s="199"/>
+      <c r="K2" s="199"/>
+      <c r="L2" s="199"/>
+      <c r="M2" s="199"/>
+      <c r="N2" s="199"/>
+      <c r="O2" s="199"/>
+      <c r="P2" s="199"/>
+      <c r="Q2" s="199"/>
+      <c r="R2" s="199"/>
+      <c r="S2" s="199"/>
+      <c r="T2" s="197" t="s">
         <v>36</v>
       </c>
-      <c r="U2" s="189"/>
-      <c r="V2" s="189"/>
-      <c r="W2" s="189"/>
-      <c r="X2" s="189"/>
-      <c r="Y2" s="189"/>
-      <c r="Z2" s="189"/>
-      <c r="AA2" s="189"/>
-      <c r="AB2" s="189"/>
-      <c r="AC2" s="189"/>
-      <c r="AD2" s="189"/>
-      <c r="AE2" s="189"/>
-      <c r="AF2" s="189"/>
-      <c r="AG2" s="189"/>
-      <c r="AH2" s="189"/>
-      <c r="AI2" s="189"/>
-      <c r="AJ2" s="188" t="s">
+      <c r="U2" s="197"/>
+      <c r="V2" s="197"/>
+      <c r="W2" s="197"/>
+      <c r="X2" s="197"/>
+      <c r="Y2" s="197"/>
+      <c r="Z2" s="197"/>
+      <c r="AA2" s="197"/>
+      <c r="AB2" s="197"/>
+      <c r="AC2" s="197"/>
+      <c r="AD2" s="197"/>
+      <c r="AE2" s="197"/>
+      <c r="AF2" s="197"/>
+      <c r="AG2" s="197"/>
+      <c r="AH2" s="197"/>
+      <c r="AI2" s="197"/>
+      <c r="AJ2" s="196" t="s">
         <v>37</v>
       </c>
-      <c r="AK2" s="188"/>
-      <c r="AL2" s="188"/>
-      <c r="AM2" s="188"/>
-      <c r="AN2" s="188"/>
-      <c r="AO2" s="188"/>
-      <c r="AP2" s="188"/>
-      <c r="AQ2" s="188"/>
-      <c r="AR2" s="188"/>
-      <c r="AS2" s="188"/>
-      <c r="AT2" s="188"/>
-      <c r="AU2" s="188"/>
-      <c r="AV2" s="187" t="s">
+      <c r="AK2" s="196"/>
+      <c r="AL2" s="196"/>
+      <c r="AM2" s="196"/>
+      <c r="AN2" s="196"/>
+      <c r="AO2" s="196"/>
+      <c r="AP2" s="196"/>
+      <c r="AQ2" s="196"/>
+      <c r="AR2" s="196"/>
+      <c r="AS2" s="196"/>
+      <c r="AT2" s="196"/>
+      <c r="AU2" s="196"/>
+      <c r="AV2" s="195" t="s">
         <v>38</v>
       </c>
-      <c r="AW2" s="187"/>
-      <c r="AX2" s="187"/>
-      <c r="AY2" s="187"/>
-      <c r="AZ2" s="187"/>
-      <c r="BA2" s="187"/>
-      <c r="BB2" s="187"/>
-      <c r="BC2" s="187"/>
-      <c r="BD2" s="187"/>
-      <c r="BE2" s="187"/>
-      <c r="BF2" s="187"/>
-      <c r="BG2" s="187"/>
+      <c r="AW2" s="195"/>
+      <c r="AX2" s="195"/>
+      <c r="AY2" s="195"/>
+      <c r="AZ2" s="195"/>
+      <c r="BA2" s="195"/>
+      <c r="BB2" s="195"/>
+      <c r="BC2" s="195"/>
+      <c r="BD2" s="195"/>
+      <c r="BE2" s="195"/>
+      <c r="BF2" s="195"/>
+      <c r="BG2" s="195"/>
     </row>
     <row r="3" spans="1:675" s="3" customFormat="1" ht="28.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="183"/>
-      <c r="B3" s="195" t="s">
+      <c r="A3" s="193"/>
+      <c r="B3" s="200" t="s">
         <v>39</v>
       </c>
       <c r="C3" s="70"/>
-      <c r="D3" s="185" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="186"/>
-      <c r="F3" s="186"/>
-      <c r="G3" s="186"/>
-      <c r="H3" s="185" t="s">
+      <c r="D3" s="187" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="188"/>
+      <c r="F3" s="188"/>
+      <c r="G3" s="188"/>
+      <c r="H3" s="187" t="s">
         <v>40</v>
       </c>
-      <c r="I3" s="186"/>
-      <c r="J3" s="186"/>
-      <c r="K3" s="186"/>
-      <c r="L3" s="185" t="s">
+      <c r="I3" s="188"/>
+      <c r="J3" s="188"/>
+      <c r="K3" s="188"/>
+      <c r="L3" s="187" t="s">
         <v>41</v>
       </c>
-      <c r="M3" s="186"/>
-      <c r="N3" s="186"/>
-      <c r="O3" s="186"/>
-      <c r="P3" s="198" t="s">
+      <c r="M3" s="188"/>
+      <c r="N3" s="188"/>
+      <c r="O3" s="188"/>
+      <c r="P3" s="190" t="s">
         <v>42</v>
       </c>
-      <c r="Q3" s="199"/>
-      <c r="R3" s="199"/>
-      <c r="S3" s="200"/>
-      <c r="T3" s="185" t="s">
+      <c r="Q3" s="191"/>
+      <c r="R3" s="191"/>
+      <c r="S3" s="192"/>
+      <c r="T3" s="187" t="s">
         <v>43</v>
       </c>
-      <c r="U3" s="186"/>
-      <c r="V3" s="186"/>
-      <c r="W3" s="186"/>
-      <c r="X3" s="185" t="s">
+      <c r="U3" s="188"/>
+      <c r="V3" s="188"/>
+      <c r="W3" s="188"/>
+      <c r="X3" s="187" t="s">
         <v>45</v>
       </c>
-      <c r="Y3" s="186"/>
-      <c r="Z3" s="186"/>
-      <c r="AA3" s="186"/>
-      <c r="AB3" s="185" t="s">
+      <c r="Y3" s="188"/>
+      <c r="Z3" s="188"/>
+      <c r="AA3" s="188"/>
+      <c r="AB3" s="187" t="s">
         <v>47</v>
       </c>
-      <c r="AC3" s="186"/>
-      <c r="AD3" s="186"/>
-      <c r="AE3" s="186"/>
-      <c r="AF3" s="185" t="s">
+      <c r="AC3" s="188"/>
+      <c r="AD3" s="188"/>
+      <c r="AE3" s="188"/>
+      <c r="AF3" s="187" t="s">
         <v>48</v>
       </c>
-      <c r="AG3" s="186"/>
-      <c r="AH3" s="186"/>
-      <c r="AI3" s="186"/>
-      <c r="AJ3" s="191" t="s">
+      <c r="AG3" s="188"/>
+      <c r="AH3" s="188"/>
+      <c r="AI3" s="188"/>
+      <c r="AJ3" s="184" t="s">
         <v>51</v>
       </c>
-      <c r="AK3" s="192"/>
-      <c r="AL3" s="192"/>
-      <c r="AM3" s="193"/>
-      <c r="AN3" s="191" t="s">
+      <c r="AK3" s="185"/>
+      <c r="AL3" s="185"/>
+      <c r="AM3" s="186"/>
+      <c r="AN3" s="184" t="s">
         <v>14</v>
       </c>
-      <c r="AO3" s="192"/>
-      <c r="AP3" s="192"/>
-      <c r="AQ3" s="193"/>
-      <c r="AR3" s="191" t="s">
+      <c r="AO3" s="185"/>
+      <c r="AP3" s="185"/>
+      <c r="AQ3" s="186"/>
+      <c r="AR3" s="184" t="s">
         <v>52</v>
       </c>
-      <c r="AS3" s="192"/>
-      <c r="AT3" s="192"/>
-      <c r="AU3" s="193"/>
-      <c r="AV3" s="186" t="s">
+      <c r="AS3" s="185"/>
+      <c r="AT3" s="185"/>
+      <c r="AU3" s="186"/>
+      <c r="AV3" s="188" t="s">
         <v>16</v>
       </c>
-      <c r="AW3" s="186"/>
-      <c r="AX3" s="186"/>
-      <c r="AY3" s="186"/>
-      <c r="AZ3" s="186" t="s">
+      <c r="AW3" s="188"/>
+      <c r="AX3" s="188"/>
+      <c r="AY3" s="188"/>
+      <c r="AZ3" s="188" t="s">
         <v>54</v>
       </c>
-      <c r="BA3" s="186"/>
-      <c r="BB3" s="186"/>
-      <c r="BC3" s="186"/>
-      <c r="BD3" s="185" t="s">
+      <c r="BA3" s="188"/>
+      <c r="BB3" s="188"/>
+      <c r="BC3" s="188"/>
+      <c r="BD3" s="187" t="s">
         <v>55</v>
       </c>
-      <c r="BE3" s="186"/>
-      <c r="BF3" s="190"/>
-      <c r="BG3" s="186"/>
+      <c r="BE3" s="188"/>
+      <c r="BF3" s="198"/>
+      <c r="BG3" s="188"/>
       <c r="BH3" s="2"/>
       <c r="BI3" s="2"/>
       <c r="BJ3" s="2"/>
@@ -6067,8 +6067,8 @@
       <c r="YY3" s="2"/>
     </row>
     <row r="4" spans="1:675" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="184"/>
-      <c r="B4" s="195"/>
+      <c r="A4" s="194"/>
+      <c r="B4" s="200"/>
       <c r="C4" s="71"/>
       <c r="D4" s="8" t="s">
         <v>2</v>
@@ -6413,7 +6413,7 @@
       </c>
       <c r="AS5" s="112">
         <f>(VLOOKUP(B5,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.87430000000000008</v>
+        <v>0.89329999999999998</v>
       </c>
       <c r="AT5" s="14">
         <f t="shared" ref="AT5:AT18" si="20">IF(AS5&lt;94.5%,0,IF(AS5&lt;95.54%,50%,IF(AS5&lt;AR5,80%,100%+(30%*(AS5-AR5)/3.39%))))</f>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="AU5" s="48">
         <f t="shared" ref="AU5:AU18" si="21">AR5-AS5</f>
-        <v>9.5699999999999896E-2</v>
+        <v>7.669999999999999E-2</v>
       </c>
       <c r="AV5" s="51">
         <f>VLOOKUP(C5,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -6646,7 +6646,7 @@
       </c>
       <c r="AS6" s="112">
         <f>(VLOOKUP(B6,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.80620000000000003</v>
+        <v>0.81969999999999998</v>
       </c>
       <c r="AT6" s="14">
         <f t="shared" si="20"/>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="AU6" s="48">
         <f t="shared" si="21"/>
-        <v>0.16379999999999995</v>
+        <v>0.15029999999999999</v>
       </c>
       <c r="AV6" s="51">
         <f>VLOOKUP(C6,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="AS7" s="112">
         <f>(VLOOKUP(B7,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.84689999999999999</v>
+        <v>0.86109999999999998</v>
       </c>
       <c r="AT7" s="14">
         <f t="shared" si="20"/>
@@ -6887,7 +6887,7 @@
       </c>
       <c r="AU7" s="48">
         <f t="shared" si="21"/>
-        <v>0.12309999999999999</v>
+        <v>0.1089</v>
       </c>
       <c r="AV7" s="51">
         <f>VLOOKUP(C7,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7112,7 +7112,7 @@
       </c>
       <c r="AS8" s="112">
         <f>(VLOOKUP(B8,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.84279999999999999</v>
+        <v>0.85849999999999993</v>
       </c>
       <c r="AT8" s="14">
         <f t="shared" si="20"/>
@@ -7120,7 +7120,7 @@
       </c>
       <c r="AU8" s="48">
         <f t="shared" si="21"/>
-        <v>0.12719999999999998</v>
+        <v>0.11150000000000004</v>
       </c>
       <c r="AV8" s="51">
         <f>VLOOKUP(C8,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7345,7 +7345,7 @@
       </c>
       <c r="AS9" s="112">
         <f>(VLOOKUP(B9,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.84599999999999997</v>
+        <v>0.85400000000000009</v>
       </c>
       <c r="AT9" s="14">
         <f t="shared" si="20"/>
@@ -7353,7 +7353,7 @@
       </c>
       <c r="AU9" s="48">
         <f t="shared" si="21"/>
-        <v>0.124</v>
+        <v>0.11599999999999988</v>
       </c>
       <c r="AV9" s="51">
         <f>VLOOKUP(C9,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7578,7 +7578,7 @@
       </c>
       <c r="AS10" s="112">
         <f>(VLOOKUP(B10,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.82200000000000006</v>
+        <v>0.84360000000000002</v>
       </c>
       <c r="AT10" s="14">
         <f t="shared" si="20"/>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="AU10" s="48">
         <f t="shared" si="21"/>
-        <v>0.14799999999999991</v>
+        <v>0.12639999999999996</v>
       </c>
       <c r="AV10" s="51">
         <f>VLOOKUP(C10,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7811,7 +7811,7 @@
       </c>
       <c r="AS11" s="112">
         <f>(VLOOKUP(B11,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.8237000000000001</v>
+        <v>0.84090000000000009</v>
       </c>
       <c r="AT11" s="14">
         <f t="shared" si="20"/>
@@ -7819,7 +7819,7 @@
       </c>
       <c r="AU11" s="48">
         <f t="shared" si="21"/>
-        <v>0.14629999999999987</v>
+        <v>0.12909999999999988</v>
       </c>
       <c r="AV11" s="51">
         <f>VLOOKUP(C11,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8044,7 +8044,7 @@
       </c>
       <c r="AS12" s="112">
         <f>(VLOOKUP(B12,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.82950000000000002</v>
+        <v>0.84370000000000012</v>
       </c>
       <c r="AT12" s="14">
         <f t="shared" si="20"/>
@@ -8052,7 +8052,7 @@
       </c>
       <c r="AU12" s="48">
         <f t="shared" si="21"/>
-        <v>0.14049999999999996</v>
+        <v>0.12629999999999986</v>
       </c>
       <c r="AV12" s="51">
         <f>VLOOKUP(C12,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8277,7 +8277,7 @@
       </c>
       <c r="AS13" s="112">
         <f>(VLOOKUP(B13,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.87209999999999999</v>
+        <v>0.88650000000000007</v>
       </c>
       <c r="AT13" s="14">
         <f t="shared" si="20"/>
@@ -8285,7 +8285,7 @@
       </c>
       <c r="AU13" s="48">
         <f t="shared" si="21"/>
-        <v>9.7899999999999987E-2</v>
+        <v>8.3499999999999908E-2</v>
       </c>
       <c r="AV13" s="51">
         <f>VLOOKUP(C13,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="AS14" s="112">
         <f>(VLOOKUP(B14,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.74349999999999994</v>
+        <v>0.76450000000000007</v>
       </c>
       <c r="AT14" s="14">
         <f t="shared" si="20"/>
@@ -8518,7 +8518,7 @@
       </c>
       <c r="AU14" s="48">
         <f t="shared" si="21"/>
-        <v>0.22650000000000003</v>
+        <v>0.2054999999999999</v>
       </c>
       <c r="AV14" s="51">
         <f>VLOOKUP(C14,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8743,7 +8743,7 @@
       </c>
       <c r="AS15" s="112">
         <f>(VLOOKUP(B15,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.78670000000000007</v>
+        <v>0.81780000000000008</v>
       </c>
       <c r="AT15" s="14">
         <f t="shared" si="20"/>
@@ -8751,7 +8751,7 @@
       </c>
       <c r="AU15" s="48">
         <f t="shared" si="21"/>
-        <v>0.18329999999999991</v>
+        <v>0.15219999999999989</v>
       </c>
       <c r="AV15" s="51">
         <f>VLOOKUP(C15,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8976,7 +8976,7 @@
       </c>
       <c r="AS16" s="112">
         <f>(VLOOKUP(B16,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.85739999999999994</v>
+        <v>0.88970000000000005</v>
       </c>
       <c r="AT16" s="14">
         <f t="shared" si="20"/>
@@ -8984,7 +8984,7 @@
       </c>
       <c r="AU16" s="48">
         <f t="shared" si="21"/>
-        <v>0.11260000000000003</v>
+        <v>8.0299999999999927E-2</v>
       </c>
       <c r="AV16" s="51">
         <f>VLOOKUP(C16,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -9209,7 +9209,7 @@
       </c>
       <c r="AS17" s="112">
         <f>(VLOOKUP(B17,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.85599999999999998</v>
+        <v>0.87209999999999999</v>
       </c>
       <c r="AT17" s="14">
         <f t="shared" si="20"/>
@@ -9217,7 +9217,7 @@
       </c>
       <c r="AU17" s="48">
         <f t="shared" si="21"/>
-        <v>0.11399999999999999</v>
+        <v>9.7899999999999987E-2</v>
       </c>
       <c r="AV17" s="51">
         <f>VLOOKUP(C17,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -9442,7 +9442,7 @@
       </c>
       <c r="AS18" s="112">
         <f>(VLOOKUP(B18,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.81530000000000002</v>
+        <v>0.83870000000000011</v>
       </c>
       <c r="AT18" s="14">
         <f t="shared" si="20"/>
@@ -9450,7 +9450,7 @@
       </c>
       <c r="AU18" s="48">
         <f t="shared" si="21"/>
-        <v>0.15469999999999995</v>
+        <v>0.13129999999999986</v>
       </c>
       <c r="AV18" s="51">
         <f>VLOOKUP(C18,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -9507,11 +9507,11 @@
       <c r="C19" s="15"/>
       <c r="D19" s="15"/>
       <c r="E19" s="16"/>
-      <c r="F19" s="196">
+      <c r="F19" s="183">
         <f ca="1">TODAY()</f>
         <v>46078</v>
       </c>
-      <c r="G19" s="196"/>
+      <c r="G19" s="183"/>
       <c r="H19" s="73"/>
       <c r="I19" s="74">
         <f ca="1">DAY(F19)</f>
@@ -9524,33 +9524,33 @@
         <f ca="1">I19/J19</f>
         <v>0.80645161290322576</v>
       </c>
-      <c r="L19" s="197" t="s">
+      <c r="L19" s="189" t="s">
         <v>124</v>
       </c>
-      <c r="M19" s="197"/>
-      <c r="N19" s="197"/>
-      <c r="O19" s="197"/>
-      <c r="P19" s="197"/>
-      <c r="Q19" s="197"/>
-      <c r="R19" s="197"/>
-      <c r="S19" s="197"/>
-      <c r="T19" s="197"/>
-      <c r="U19" s="197"/>
-      <c r="V19" s="197"/>
-      <c r="W19" s="197"/>
-      <c r="X19" s="197"/>
-      <c r="Y19" s="197"/>
-      <c r="Z19" s="197"/>
-      <c r="AA19" s="197"/>
-      <c r="AB19" s="197"/>
-      <c r="AC19" s="197"/>
-      <c r="AD19" s="197"/>
-      <c r="AE19" s="197"/>
-      <c r="AF19" s="197"/>
-      <c r="AG19" s="197"/>
-      <c r="AH19" s="197"/>
-      <c r="AI19" s="197"/>
-      <c r="AJ19" s="197"/>
+      <c r="M19" s="189"/>
+      <c r="N19" s="189"/>
+      <c r="O19" s="189"/>
+      <c r="P19" s="189"/>
+      <c r="Q19" s="189"/>
+      <c r="R19" s="189"/>
+      <c r="S19" s="189"/>
+      <c r="T19" s="189"/>
+      <c r="U19" s="189"/>
+      <c r="V19" s="189"/>
+      <c r="W19" s="189"/>
+      <c r="X19" s="189"/>
+      <c r="Y19" s="189"/>
+      <c r="Z19" s="189"/>
+      <c r="AA19" s="189"/>
+      <c r="AB19" s="189"/>
+      <c r="AC19" s="189"/>
+      <c r="AD19" s="189"/>
+      <c r="AE19" s="189"/>
+      <c r="AF19" s="189"/>
+      <c r="AG19" s="189"/>
+      <c r="AH19" s="189"/>
+      <c r="AI19" s="189"/>
+      <c r="AJ19" s="189"/>
       <c r="AK19" s="16"/>
       <c r="AL19" s="32"/>
       <c r="AM19" s="16"/>
@@ -9743,12 +9743,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="AN3:AQ3"/>
-    <mergeCell ref="AF3:AI3"/>
-    <mergeCell ref="L19:AJ19"/>
-    <mergeCell ref="P3:S3"/>
-    <mergeCell ref="T3:W3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="X3:AA3"/>
     <mergeCell ref="AV2:BG2"/>
@@ -9765,6 +9759,12 @@
     <mergeCell ref="D3:G3"/>
     <mergeCell ref="H3:K3"/>
     <mergeCell ref="L3:O3"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="AN3:AQ3"/>
+    <mergeCell ref="AF3:AI3"/>
+    <mergeCell ref="L19:AJ19"/>
+    <mergeCell ref="P3:S3"/>
+    <mergeCell ref="T3:W3"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="C3:C4">
@@ -10445,7 +10445,7 @@
       </c>
       <c r="D14" s="68">
         <f>VLOOKUP($B$2,'TH NV'!$A$5:$BG$18,N14,0)</f>
-        <v>0.74349999999999994</v>
+        <v>0.76450000000000007</v>
       </c>
       <c r="E14" s="43" t="e">
         <f>VLOOKUP($B$2,'TH NV'!$A$1:$BG$18,70,0)</f>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="J14" s="59">
         <f t="shared" si="2"/>
-        <v>0.22650000000000003</v>
+        <v>0.2054999999999999</v>
       </c>
       <c r="K14" s="205"/>
       <c r="L14" s="97" t="s">
@@ -10649,42 +10649,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:59" s="1" customFormat="1" ht="24.75" x14ac:dyDescent="0.45">
-      <c r="D1" s="194" t="s">
+      <c r="D1" s="199" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="194"/>
-      <c r="F1" s="194"/>
-      <c r="G1" s="194"/>
-      <c r="H1" s="194"/>
-      <c r="I1" s="194"/>
-      <c r="J1" s="194"/>
-      <c r="K1" s="194"/>
-      <c r="L1" s="194"/>
-      <c r="M1" s="194"/>
-      <c r="N1" s="194"/>
-      <c r="O1" s="194"/>
-      <c r="P1" s="194"/>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="189" t="s">
+      <c r="E1" s="199"/>
+      <c r="F1" s="199"/>
+      <c r="G1" s="199"/>
+      <c r="H1" s="199"/>
+      <c r="I1" s="199"/>
+      <c r="J1" s="199"/>
+      <c r="K1" s="199"/>
+      <c r="L1" s="199"/>
+      <c r="M1" s="199"/>
+      <c r="N1" s="199"/>
+      <c r="O1" s="199"/>
+      <c r="P1" s="199"/>
+      <c r="Q1" s="199"/>
+      <c r="R1" s="199"/>
+      <c r="S1" s="199"/>
+      <c r="T1" s="197" t="s">
         <v>36</v>
       </c>
-      <c r="U1" s="189"/>
-      <c r="V1" s="189"/>
-      <c r="W1" s="189"/>
-      <c r="X1" s="189"/>
-      <c r="Y1" s="189"/>
-      <c r="Z1" s="189"/>
-      <c r="AA1" s="189"/>
-      <c r="AB1" s="189"/>
-      <c r="AC1" s="189"/>
-      <c r="AD1" s="189"/>
-      <c r="AE1" s="189"/>
-      <c r="AF1" s="189"/>
-      <c r="AG1" s="189"/>
-      <c r="AH1" s="189"/>
-      <c r="AI1" s="189"/>
+      <c r="U1" s="197"/>
+      <c r="V1" s="197"/>
+      <c r="W1" s="197"/>
+      <c r="X1" s="197"/>
+      <c r="Y1" s="197"/>
+      <c r="Z1" s="197"/>
+      <c r="AA1" s="197"/>
+      <c r="AB1" s="197"/>
+      <c r="AC1" s="197"/>
+      <c r="AD1" s="197"/>
+      <c r="AE1" s="197"/>
+      <c r="AF1" s="197"/>
+      <c r="AG1" s="197"/>
+      <c r="AH1" s="197"/>
+      <c r="AI1" s="197"/>
       <c r="AJ1" s="217" t="s">
         <v>37</v>
       </c>
@@ -10717,90 +10717,90 @@
     <row r="2" spans="1:59" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="185" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="186"/>
-      <c r="F2" s="186"/>
-      <c r="G2" s="186"/>
-      <c r="H2" s="185" t="s">
+      <c r="D2" s="187" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="188"/>
+      <c r="F2" s="188"/>
+      <c r="G2" s="188"/>
+      <c r="H2" s="187" t="s">
         <v>40</v>
       </c>
-      <c r="I2" s="186"/>
-      <c r="J2" s="186"/>
-      <c r="K2" s="186"/>
-      <c r="L2" s="185" t="s">
+      <c r="I2" s="188"/>
+      <c r="J2" s="188"/>
+      <c r="K2" s="188"/>
+      <c r="L2" s="187" t="s">
         <v>41</v>
       </c>
-      <c r="M2" s="186"/>
-      <c r="N2" s="186"/>
-      <c r="O2" s="186"/>
-      <c r="P2" s="198" t="s">
+      <c r="M2" s="188"/>
+      <c r="N2" s="188"/>
+      <c r="O2" s="188"/>
+      <c r="P2" s="190" t="s">
         <v>42</v>
       </c>
-      <c r="Q2" s="199"/>
-      <c r="R2" s="199"/>
-      <c r="S2" s="200"/>
-      <c r="T2" s="185" t="s">
+      <c r="Q2" s="191"/>
+      <c r="R2" s="191"/>
+      <c r="S2" s="192"/>
+      <c r="T2" s="187" t="s">
         <v>43</v>
       </c>
-      <c r="U2" s="186"/>
-      <c r="V2" s="186"/>
-      <c r="W2" s="186"/>
-      <c r="X2" s="185" t="s">
+      <c r="U2" s="188"/>
+      <c r="V2" s="188"/>
+      <c r="W2" s="188"/>
+      <c r="X2" s="187" t="s">
         <v>45</v>
       </c>
-      <c r="Y2" s="186"/>
-      <c r="Z2" s="186"/>
-      <c r="AA2" s="186"/>
-      <c r="AB2" s="185" t="s">
+      <c r="Y2" s="188"/>
+      <c r="Z2" s="188"/>
+      <c r="AA2" s="188"/>
+      <c r="AB2" s="187" t="s">
         <v>47</v>
       </c>
-      <c r="AC2" s="186"/>
-      <c r="AD2" s="186"/>
-      <c r="AE2" s="186"/>
-      <c r="AF2" s="185" t="s">
+      <c r="AC2" s="188"/>
+      <c r="AD2" s="188"/>
+      <c r="AE2" s="188"/>
+      <c r="AF2" s="187" t="s">
         <v>48</v>
       </c>
-      <c r="AG2" s="186"/>
-      <c r="AH2" s="186"/>
-      <c r="AI2" s="186"/>
-      <c r="AJ2" s="191" t="s">
+      <c r="AG2" s="188"/>
+      <c r="AH2" s="188"/>
+      <c r="AI2" s="188"/>
+      <c r="AJ2" s="184" t="s">
         <v>51</v>
       </c>
-      <c r="AK2" s="192"/>
-      <c r="AL2" s="192"/>
-      <c r="AM2" s="193"/>
-      <c r="AN2" s="191" t="s">
+      <c r="AK2" s="185"/>
+      <c r="AL2" s="185"/>
+      <c r="AM2" s="186"/>
+      <c r="AN2" s="184" t="s">
         <v>14</v>
       </c>
-      <c r="AO2" s="192"/>
-      <c r="AP2" s="192"/>
-      <c r="AQ2" s="193"/>
-      <c r="AR2" s="191" t="s">
+      <c r="AO2" s="185"/>
+      <c r="AP2" s="185"/>
+      <c r="AQ2" s="186"/>
+      <c r="AR2" s="184" t="s">
         <v>52</v>
       </c>
-      <c r="AS2" s="192"/>
-      <c r="AT2" s="192"/>
-      <c r="AU2" s="193"/>
-      <c r="AV2" s="186" t="s">
+      <c r="AS2" s="185"/>
+      <c r="AT2" s="185"/>
+      <c r="AU2" s="186"/>
+      <c r="AV2" s="188" t="s">
         <v>16</v>
       </c>
-      <c r="AW2" s="186"/>
-      <c r="AX2" s="186"/>
-      <c r="AY2" s="186"/>
-      <c r="AZ2" s="186" t="s">
+      <c r="AW2" s="188"/>
+      <c r="AX2" s="188"/>
+      <c r="AY2" s="188"/>
+      <c r="AZ2" s="188" t="s">
         <v>54</v>
       </c>
-      <c r="BA2" s="186"/>
-      <c r="BB2" s="186"/>
-      <c r="BC2" s="186"/>
-      <c r="BD2" s="185" t="s">
+      <c r="BA2" s="188"/>
+      <c r="BB2" s="188"/>
+      <c r="BC2" s="188"/>
+      <c r="BD2" s="187" t="s">
         <v>55</v>
       </c>
-      <c r="BE2" s="186"/>
-      <c r="BF2" s="190"/>
-      <c r="BG2" s="186"/>
+      <c r="BE2" s="188"/>
+      <c r="BF2" s="198"/>
+      <c r="BG2" s="188"/>
     </row>
     <row r="3" spans="1:59" ht="15" x14ac:dyDescent="0.45">
       <c r="B3" s="8" t="s">
@@ -11153,7 +11153,7 @@
       </c>
       <c r="AS4" s="112">
         <f>(VLOOKUP(B4,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.87430000000000008</v>
+        <v>0.89329999999999998</v>
       </c>
       <c r="AT4" s="14">
         <f t="shared" ref="AT4" si="20">IF(AS4&lt;94.5%,0,IF(AS4&lt;95.54%,50%,IF(AS4&lt;AR4,80%,100%+(30%*(AS4-AR4)/3.39%))))</f>
@@ -11161,7 +11161,7 @@
       </c>
       <c r="AU4" s="48">
         <f t="shared" ref="AU4" si="21">AR4-AS4</f>
-        <v>9.5699999999999896E-2</v>
+        <v>7.669999999999999E-2</v>
       </c>
       <c r="AV4" s="51">
         <f>VLOOKUP(A4,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -11387,7 +11387,7 @@
       </c>
       <c r="AS5" s="112">
         <f>(VLOOKUP(B5,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.8237000000000001</v>
+        <v>0.84090000000000009</v>
       </c>
       <c r="AT5" s="14">
         <f t="shared" ref="AT5:AT16" si="48">IF(AS5&lt;94.5%,0,IF(AS5&lt;95.54%,50%,IF(AS5&lt;AR5,80%,100%+(30%*(AS5-AR5)/3.39%))))</f>
@@ -11395,7 +11395,7 @@
       </c>
       <c r="AU5" s="48">
         <f t="shared" ref="AU5:AU16" si="49">AR5-AS5</f>
-        <v>0.14629999999999987</v>
+        <v>0.12909999999999988</v>
       </c>
       <c r="AV5" s="51">
         <f>VLOOKUP(A5,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -11621,7 +11621,7 @@
       </c>
       <c r="AS6" s="112">
         <f>(VLOOKUP(B6,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.82950000000000002</v>
+        <v>0.84370000000000012</v>
       </c>
       <c r="AT6" s="14">
         <f t="shared" si="48"/>
@@ -11629,7 +11629,7 @@
       </c>
       <c r="AU6" s="48">
         <f t="shared" si="49"/>
-        <v>0.14049999999999996</v>
+        <v>0.12629999999999986</v>
       </c>
       <c r="AV6" s="51">
         <f>VLOOKUP(A6,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -11855,7 +11855,7 @@
       </c>
       <c r="AS7" s="112">
         <f>(VLOOKUP(B7,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.74349999999999994</v>
+        <v>0.76450000000000007</v>
       </c>
       <c r="AT7" s="14">
         <f t="shared" si="48"/>
@@ -11863,7 +11863,7 @@
       </c>
       <c r="AU7" s="48">
         <f t="shared" si="49"/>
-        <v>0.22650000000000003</v>
+        <v>0.2054999999999999</v>
       </c>
       <c r="AV7" s="51">
         <f>VLOOKUP(A7,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -12089,7 +12089,7 @@
       </c>
       <c r="AS8" s="112">
         <f>(VLOOKUP(B8,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.85739999999999994</v>
+        <v>0.88970000000000005</v>
       </c>
       <c r="AT8" s="14">
         <f t="shared" si="48"/>
@@ -12097,7 +12097,7 @@
       </c>
       <c r="AU8" s="48">
         <f t="shared" si="49"/>
-        <v>0.11260000000000003</v>
+        <v>8.0299999999999927E-2</v>
       </c>
       <c r="AV8" s="51">
         <f>VLOOKUP(A8,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -12384,7 +12384,7 @@
       </c>
       <c r="AS10" s="112">
         <f>(VLOOKUP(B10,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.80620000000000003</v>
+        <v>0.81969999999999998</v>
       </c>
       <c r="AT10" s="14">
         <f t="shared" si="48"/>
@@ -12392,7 +12392,7 @@
       </c>
       <c r="AU10" s="48">
         <f t="shared" si="49"/>
-        <v>0.16379999999999995</v>
+        <v>0.15029999999999999</v>
       </c>
       <c r="AV10" s="51">
         <f>VLOOKUP(A10,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -12618,7 +12618,7 @@
       </c>
       <c r="AS11" s="112">
         <f>(VLOOKUP(B11,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.84689999999999999</v>
+        <v>0.86109999999999998</v>
       </c>
       <c r="AT11" s="14">
         <f t="shared" si="48"/>
@@ -12626,7 +12626,7 @@
       </c>
       <c r="AU11" s="48">
         <f t="shared" si="49"/>
-        <v>0.12309999999999999</v>
+        <v>0.1089</v>
       </c>
       <c r="AV11" s="51">
         <f>VLOOKUP(A11,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -12852,7 +12852,7 @@
       </c>
       <c r="AS12" s="112">
         <f>(VLOOKUP(B12,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.84279999999999999</v>
+        <v>0.85849999999999993</v>
       </c>
       <c r="AT12" s="14">
         <f t="shared" si="48"/>
@@ -12860,7 +12860,7 @@
       </c>
       <c r="AU12" s="48">
         <f t="shared" si="49"/>
-        <v>0.12719999999999998</v>
+        <v>0.11150000000000004</v>
       </c>
       <c r="AV12" s="51">
         <f>VLOOKUP(A12,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -13086,7 +13086,7 @@
       </c>
       <c r="AS13" s="112">
         <f>(VLOOKUP(B13,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.82200000000000006</v>
+        <v>0.84360000000000002</v>
       </c>
       <c r="AT13" s="14">
         <f t="shared" si="48"/>
@@ -13094,7 +13094,7 @@
       </c>
       <c r="AU13" s="48">
         <f t="shared" si="49"/>
-        <v>0.14799999999999991</v>
+        <v>0.12639999999999996</v>
       </c>
       <c r="AV13" s="51">
         <f>VLOOKUP(A13,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -13320,7 +13320,7 @@
       </c>
       <c r="AS14" s="112">
         <f>(VLOOKUP(B14,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.87209999999999999</v>
+        <v>0.88650000000000007</v>
       </c>
       <c r="AT14" s="14">
         <f t="shared" si="48"/>
@@ -13328,7 +13328,7 @@
       </c>
       <c r="AU14" s="48">
         <f t="shared" si="49"/>
-        <v>9.7899999999999987E-2</v>
+        <v>8.3499999999999908E-2</v>
       </c>
       <c r="AV14" s="51">
         <f>VLOOKUP(A14,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -13554,7 +13554,7 @@
       </c>
       <c r="AS15" s="112">
         <f>(VLOOKUP(B15,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.78670000000000007</v>
+        <v>0.81780000000000008</v>
       </c>
       <c r="AT15" s="14">
         <f t="shared" si="48"/>
@@ -13562,7 +13562,7 @@
       </c>
       <c r="AU15" s="48">
         <f t="shared" si="49"/>
-        <v>0.18329999999999991</v>
+        <v>0.15219999999999989</v>
       </c>
       <c r="AV15" s="51">
         <f>VLOOKUP(A15,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -13788,7 +13788,7 @@
       </c>
       <c r="AS16" s="112">
         <f>(VLOOKUP(B16,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.85599999999999998</v>
+        <v>0.87209999999999999</v>
       </c>
       <c r="AT16" s="14">
         <f t="shared" si="48"/>
@@ -13796,7 +13796,7 @@
       </c>
       <c r="AU16" s="48">
         <f t="shared" si="49"/>
-        <v>0.11399999999999999</v>
+        <v>9.7899999999999987E-2</v>
       </c>
       <c r="AV16" s="51">
         <f>VLOOKUP(A16,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -13880,11 +13880,11 @@
       </c>
       <c r="C19" s="125">
         <f ca="1">SUMIF(cuoc!A7:P27,'tiến độ'!A19,cuoc!M7:M27)</f>
-        <v>529700544</v>
+        <v>542791891</v>
       </c>
       <c r="D19" s="125">
         <f ca="1">B19*0.968-C19</f>
-        <v>93473527.255999923</v>
+        <v>80382180.255999923</v>
       </c>
       <c r="E19" s="120"/>
       <c r="H19" s="120"/>
@@ -13901,11 +13901,11 @@
       </c>
       <c r="C20" s="126">
         <f ca="1">SUMIF(cuoc!A8:P27,'tiến độ'!A20,cuoc!M8:M27)</f>
-        <v>900798487</v>
+        <v>920566066</v>
       </c>
       <c r="D20" s="125">
         <f ca="1">B20*0.968-C20</f>
-        <v>145777318.704</v>
+        <v>126009739.704</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.45">
@@ -14091,11 +14091,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="D1:S1"/>
-    <mergeCell ref="D2:G2"/>
-    <mergeCell ref="H2:K2"/>
-    <mergeCell ref="L2:O2"/>
-    <mergeCell ref="P2:S2"/>
     <mergeCell ref="X2:AA2"/>
     <mergeCell ref="AB2:AE2"/>
     <mergeCell ref="AF2:AI2"/>
@@ -14109,6 +14104,11 @@
     <mergeCell ref="AJ2:AM2"/>
     <mergeCell ref="AN2:AQ2"/>
     <mergeCell ref="T2:W2"/>
+    <mergeCell ref="D1:S1"/>
+    <mergeCell ref="D2:G2"/>
+    <mergeCell ref="H2:K2"/>
+    <mergeCell ref="L2:O2"/>
+    <mergeCell ref="P2:S2"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="F4:F16">
@@ -22585,12 +22585,6 @@
   </sheetData>
   <autoFilter ref="A6:DG6" xr:uid="{035AF4C2-379E-4E05-A870-198385941EC5}"/>
   <mergeCells count="16">
-    <mergeCell ref="X5:AE5"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="H5:O5"/>
-    <mergeCell ref="P5:W5"/>
     <mergeCell ref="CB5:CI5"/>
     <mergeCell ref="CJ5:CQ5"/>
     <mergeCell ref="CR5:CY5"/>
@@ -22601,6 +22595,12 @@
     <mergeCell ref="BD5:BK5"/>
     <mergeCell ref="BL5:BS5"/>
     <mergeCell ref="BT5:CA5"/>
+    <mergeCell ref="X5:AE5"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="H5:O5"/>
+    <mergeCell ref="P5:W5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -22698,7 +22698,7 @@
       <c r="A3" s="83" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="226" t="s">
+      <c r="B3" s="228" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="84" t="s">
@@ -22710,70 +22710,70 @@
       <c r="E3" s="230" t="s">
         <v>202</v>
       </c>
-      <c r="F3" s="228" t="s">
+      <c r="F3" s="226" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="228" t="s">
+      <c r="G3" s="226" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="228" t="s">
+      <c r="H3" s="226" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="228" t="s">
+      <c r="I3" s="226" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="228" t="s">
+      <c r="J3" s="226" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="228" t="s">
+      <c r="K3" s="226" t="s">
         <v>11</v>
       </c>
-      <c r="L3" s="228" t="s">
+      <c r="L3" s="226" t="s">
         <v>12</v>
       </c>
-      <c r="M3" s="228" t="s">
+      <c r="M3" s="226" t="s">
         <v>203</v>
       </c>
-      <c r="N3" s="228" t="s">
+      <c r="N3" s="226" t="s">
         <v>255</v>
       </c>
-      <c r="O3" s="228" t="s">
+      <c r="O3" s="226" t="s">
         <v>14</v>
       </c>
-      <c r="P3" s="228" t="s">
+      <c r="P3" s="226" t="s">
         <v>15</v>
       </c>
-      <c r="Q3" s="228" t="s">
+      <c r="Q3" s="226" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="228" t="s">
+      <c r="R3" s="226" t="s">
         <v>17</v>
       </c>
-      <c r="S3" s="228" t="s">
+      <c r="S3" s="226" t="s">
         <v>18</v>
       </c>
       <c r="T3" s="82"/>
     </row>
     <row r="4" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="83"/>
-      <c r="B4" s="227"/>
+      <c r="B4" s="229"/>
       <c r="C4" s="84"/>
       <c r="D4" s="84"/>
       <c r="E4" s="231"/>
-      <c r="F4" s="229"/>
-      <c r="G4" s="229"/>
-      <c r="H4" s="229"/>
-      <c r="I4" s="229"/>
-      <c r="J4" s="229"/>
-      <c r="K4" s="229"/>
-      <c r="L4" s="229"/>
-      <c r="M4" s="229"/>
-      <c r="N4" s="229"/>
-      <c r="O4" s="229"/>
-      <c r="P4" s="229"/>
-      <c r="Q4" s="229"/>
-      <c r="R4" s="229"/>
-      <c r="S4" s="229"/>
+      <c r="F4" s="227"/>
+      <c r="G4" s="227"/>
+      <c r="H4" s="227"/>
+      <c r="I4" s="227"/>
+      <c r="J4" s="227"/>
+      <c r="K4" s="227"/>
+      <c r="L4" s="227"/>
+      <c r="M4" s="227"/>
+      <c r="N4" s="227"/>
+      <c r="O4" s="227"/>
+      <c r="P4" s="227"/>
+      <c r="Q4" s="227"/>
+      <c r="R4" s="227"/>
+      <c r="S4" s="227"/>
       <c r="T4" s="82"/>
     </row>
     <row r="5" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.45">
@@ -24091,12 +24091,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="S3:S4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="R3:R4"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="H3:H4"/>
@@ -24107,6 +24101,12 @@
     <mergeCell ref="K3:K4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="E3:E4"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="S3:S4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="R3:R4"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.69991251615088756" right="0.69991251615088756" top="0.74990626395218019" bottom="0.74990626395218019" header="0.29996251027415122" footer="0.29996251027415122"/>
@@ -24690,68 +24690,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:48" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="241" t="s">
+      <c r="A1" s="239" t="s">
         <v>209</v>
       </c>
-      <c r="B1" s="241"/>
-      <c r="C1" s="241"/>
-      <c r="D1" s="241"/>
-      <c r="E1" s="241"/>
-      <c r="F1" s="241"/>
-      <c r="G1" s="241"/>
-      <c r="H1" s="241"/>
-      <c r="I1" s="241"/>
-      <c r="J1" s="241"/>
-      <c r="K1" s="241"/>
-      <c r="M1" s="244" t="s">
+      <c r="B1" s="239"/>
+      <c r="C1" s="239"/>
+      <c r="D1" s="239"/>
+      <c r="E1" s="239"/>
+      <c r="F1" s="239"/>
+      <c r="G1" s="239"/>
+      <c r="H1" s="239"/>
+      <c r="I1" s="239"/>
+      <c r="J1" s="239"/>
+      <c r="K1" s="239"/>
+      <c r="M1" s="242" t="s">
         <v>210</v>
       </c>
-      <c r="N1" s="244"/>
-      <c r="O1" s="244"/>
-      <c r="P1" s="244"/>
-      <c r="Q1" s="244"/>
-      <c r="R1" s="244"/>
-      <c r="S1" s="244"/>
-      <c r="T1" s="244"/>
-      <c r="U1" s="244"/>
-      <c r="V1" s="244"/>
-      <c r="W1" s="244"/>
-      <c r="X1" s="244"/>
-      <c r="Y1" s="244"/>
-      <c r="Z1" s="244"/>
+      <c r="N1" s="242"/>
+      <c r="O1" s="242"/>
+      <c r="P1" s="242"/>
+      <c r="Q1" s="242"/>
+      <c r="R1" s="242"/>
+      <c r="S1" s="242"/>
+      <c r="T1" s="242"/>
+      <c r="U1" s="242"/>
+      <c r="V1" s="242"/>
+      <c r="W1" s="242"/>
+      <c r="X1" s="242"/>
+      <c r="Y1" s="242"/>
+      <c r="Z1" s="242"/>
     </row>
     <row r="2" spans="1:48" ht="24.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="242"/>
-      <c r="B2" s="242"/>
-      <c r="C2" s="242"/>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
-      <c r="G2" s="242"/>
-      <c r="H2" s="242"/>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="M2" s="245"/>
-      <c r="N2" s="245"/>
-      <c r="O2" s="245"/>
-      <c r="P2" s="245"/>
-      <c r="Q2" s="245"/>
-      <c r="R2" s="245"/>
-      <c r="S2" s="245"/>
-      <c r="T2" s="245"/>
-      <c r="U2" s="245"/>
-      <c r="V2" s="245"/>
-      <c r="W2" s="245"/>
-      <c r="X2" s="245"/>
-      <c r="Y2" s="245"/>
-      <c r="Z2" s="245"/>
+      <c r="A2" s="240"/>
+      <c r="B2" s="240"/>
+      <c r="C2" s="240"/>
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
+      <c r="G2" s="240"/>
+      <c r="H2" s="240"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="M2" s="243"/>
+      <c r="N2" s="243"/>
+      <c r="O2" s="243"/>
+      <c r="P2" s="243"/>
+      <c r="Q2" s="243"/>
+      <c r="R2" s="243"/>
+      <c r="S2" s="243"/>
+      <c r="T2" s="243"/>
+      <c r="U2" s="243"/>
+      <c r="V2" s="243"/>
+      <c r="W2" s="243"/>
+      <c r="X2" s="243"/>
+      <c r="Y2" s="243"/>
+      <c r="Z2" s="243"/>
     </row>
     <row r="3" spans="1:48" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="238" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="239" t="s">
+      <c r="A3" s="236" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="237" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="28" t="s">
@@ -24781,70 +24781,70 @@
       <c r="K3" s="28" t="s">
         <v>218</v>
       </c>
-      <c r="M3" s="243" t="s">
+      <c r="M3" s="241" t="s">
         <v>34</v>
       </c>
-      <c r="N3" s="185" t="s">
+      <c r="N3" s="187" t="s">
         <v>219</v>
       </c>
-      <c r="O3" s="186"/>
-      <c r="P3" s="186"/>
-      <c r="Q3" s="186"/>
-      <c r="R3" s="236" t="s">
+      <c r="O3" s="188"/>
+      <c r="P3" s="188"/>
+      <c r="Q3" s="188"/>
+      <c r="R3" s="244" t="s">
         <v>220</v>
       </c>
-      <c r="S3" s="185" t="s">
+      <c r="S3" s="187" t="s">
         <v>221</v>
       </c>
-      <c r="T3" s="186"/>
-      <c r="U3" s="186"/>
-      <c r="V3" s="186"/>
-      <c r="W3" s="236" t="s">
+      <c r="T3" s="188"/>
+      <c r="U3" s="188"/>
+      <c r="V3" s="188"/>
+      <c r="W3" s="244" t="s">
         <v>220</v>
       </c>
-      <c r="X3" s="198" t="s">
+      <c r="X3" s="190" t="s">
         <v>41</v>
       </c>
-      <c r="Y3" s="199"/>
-      <c r="Z3" s="199"/>
-      <c r="AA3" s="236" t="s">
+      <c r="Y3" s="191"/>
+      <c r="Z3" s="191"/>
+      <c r="AA3" s="244" t="s">
         <v>220</v>
       </c>
       <c r="AB3" s="65"/>
-      <c r="AC3" s="185" t="s">
+      <c r="AC3" s="187" t="s">
         <v>42</v>
       </c>
-      <c r="AD3" s="186"/>
-      <c r="AE3" s="186"/>
-      <c r="AF3" s="186"/>
-      <c r="AG3" s="185" t="s">
+      <c r="AD3" s="188"/>
+      <c r="AE3" s="188"/>
+      <c r="AF3" s="188"/>
+      <c r="AG3" s="187" t="s">
         <v>43</v>
       </c>
-      <c r="AH3" s="186"/>
-      <c r="AI3" s="186"/>
-      <c r="AJ3" s="186"/>
-      <c r="AK3" s="185" t="s">
+      <c r="AH3" s="188"/>
+      <c r="AI3" s="188"/>
+      <c r="AJ3" s="188"/>
+      <c r="AK3" s="187" t="s">
         <v>44</v>
       </c>
-      <c r="AL3" s="186"/>
-      <c r="AM3" s="186"/>
-      <c r="AN3" s="186"/>
-      <c r="AO3" s="185" t="s">
+      <c r="AL3" s="188"/>
+      <c r="AM3" s="188"/>
+      <c r="AN3" s="188"/>
+      <c r="AO3" s="187" t="s">
         <v>46</v>
       </c>
-      <c r="AP3" s="186"/>
-      <c r="AQ3" s="186"/>
-      <c r="AR3" s="186"/>
-      <c r="AS3" s="185" t="s">
+      <c r="AP3" s="188"/>
+      <c r="AQ3" s="188"/>
+      <c r="AR3" s="188"/>
+      <c r="AS3" s="187" t="s">
         <v>47</v>
       </c>
-      <c r="AT3" s="186"/>
-      <c r="AU3" s="186"/>
-      <c r="AV3" s="186"/>
+      <c r="AT3" s="188"/>
+      <c r="AU3" s="188"/>
+      <c r="AV3" s="188"/>
     </row>
     <row r="4" spans="1:48" ht="22.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="238"/>
-      <c r="B4" s="240"/>
+      <c r="A4" s="236"/>
+      <c r="B4" s="238"/>
       <c r="C4" s="24">
         <f t="shared" ref="C4:K4" si="0">SUM(C5:C19)</f>
         <v>15</v>
@@ -24881,7 +24881,7 @@
         <f t="shared" si="0"/>
         <v>134</v>
       </c>
-      <c r="M4" s="243"/>
+      <c r="M4" s="241"/>
       <c r="N4" s="8" t="s">
         <v>2</v>
       </c>
@@ -24894,7 +24894,7 @@
       <c r="Q4" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="R4" s="237"/>
+      <c r="R4" s="245"/>
       <c r="S4" s="8" t="s">
         <v>2</v>
       </c>
@@ -24907,7 +24907,7 @@
       <c r="V4" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="W4" s="237"/>
+      <c r="W4" s="245"/>
       <c r="X4" s="8" t="s">
         <v>2</v>
       </c>
@@ -24917,7 +24917,7 @@
       <c r="Z4" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="AA4" s="237"/>
+      <c r="AA4" s="245"/>
       <c r="AB4" s="45" t="s">
         <v>59</v>
       </c>
@@ -27306,12 +27306,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="A1:K2"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="N3:Q3"/>
-    <mergeCell ref="M1:Z2"/>
     <mergeCell ref="AS3:AV3"/>
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="W3:W4"/>
@@ -27322,6 +27316,12 @@
     <mergeCell ref="AK3:AN3"/>
     <mergeCell ref="AO3:AR3"/>
     <mergeCell ref="S3:V3"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="A1:K2"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="N3:Q3"/>
+    <mergeCell ref="M1:Z2"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="P5:P20">
@@ -27461,44 +27461,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="248"/>
-      <c r="B1" s="248"/>
-      <c r="C1" s="248"/>
-      <c r="D1" s="248"/>
-      <c r="E1" s="248"/>
-      <c r="F1" s="248"/>
-      <c r="G1" s="248"/>
-      <c r="H1" s="248"/>
-      <c r="I1" s="248"/>
-      <c r="J1" s="248"/>
-      <c r="K1" s="248"/>
-      <c r="L1" s="248"/>
-      <c r="M1" s="248"/>
-      <c r="N1" s="248"/>
-      <c r="O1" s="248"/>
-      <c r="P1" s="248"/>
+      <c r="A1" s="246"/>
+      <c r="B1" s="246"/>
+      <c r="C1" s="246"/>
+      <c r="D1" s="246"/>
+      <c r="E1" s="246"/>
+      <c r="F1" s="246"/>
+      <c r="G1" s="246"/>
+      <c r="H1" s="246"/>
+      <c r="I1" s="246"/>
+      <c r="J1" s="246"/>
+      <c r="K1" s="246"/>
+      <c r="L1" s="246"/>
+      <c r="M1" s="246"/>
+      <c r="N1" s="246"/>
+      <c r="O1" s="246"/>
+      <c r="P1" s="246"/>
     </row>
     <row r="2" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="249"/>
-      <c r="B2" s="249"/>
-      <c r="C2" s="249"/>
-      <c r="D2" s="249"/>
-      <c r="E2" s="249"/>
-      <c r="F2" s="249"/>
-      <c r="G2" s="249"/>
-      <c r="H2" s="249"/>
-      <c r="I2" s="249"/>
-      <c r="J2" s="249"/>
-      <c r="K2" s="249"/>
-      <c r="L2" s="249"/>
-      <c r="M2" s="249"/>
-      <c r="N2" s="249"/>
-      <c r="O2" s="249"/>
-      <c r="P2" s="249"/>
+      <c r="A2" s="247"/>
+      <c r="B2" s="247"/>
+      <c r="C2" s="247"/>
+      <c r="D2" s="247"/>
+      <c r="E2" s="247"/>
+      <c r="F2" s="247"/>
+      <c r="G2" s="247"/>
+      <c r="H2" s="247"/>
+      <c r="I2" s="247"/>
+      <c r="J2" s="247"/>
+      <c r="K2" s="247"/>
+      <c r="L2" s="247"/>
+      <c r="M2" s="247"/>
+      <c r="N2" s="247"/>
+      <c r="O2" s="247"/>
+      <c r="P2" s="247"/>
     </row>
     <row r="3" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="250"/>
-      <c r="B3" s="250"/>
+      <c r="A3" s="248"/>
+      <c r="B3" s="248"/>
       <c r="C3" s="116"/>
       <c r="D3" s="116"/>
       <c r="E3" s="116"/>
@@ -27515,10 +27515,10 @@
       <c r="P3" s="116"/>
     </row>
     <row r="4" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="252" t="s">
+      <c r="A4" s="250" t="s">
         <v>224</v>
       </c>
-      <c r="B4" s="252" t="s">
+      <c r="B4" s="250" t="s">
         <v>39</v>
       </c>
       <c r="C4" s="124"/>
@@ -27526,70 +27526,70 @@
       <c r="E4" s="124"/>
       <c r="F4" s="124"/>
       <c r="G4" s="124"/>
-      <c r="H4" s="251"/>
-      <c r="I4" s="251"/>
-      <c r="J4" s="251"/>
-      <c r="K4" s="251"/>
-      <c r="L4" s="251"/>
-      <c r="M4" s="251"/>
-      <c r="N4" s="251"/>
-      <c r="O4" s="251"/>
-      <c r="P4" s="251"/>
+      <c r="H4" s="249"/>
+      <c r="I4" s="249"/>
+      <c r="J4" s="249"/>
+      <c r="K4" s="249"/>
+      <c r="L4" s="249"/>
+      <c r="M4" s="249"/>
+      <c r="N4" s="249"/>
+      <c r="O4" s="249"/>
+      <c r="P4" s="249"/>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A5" s="255"/>
-      <c r="B5" s="255"/>
-      <c r="C5" s="252" t="s">
+      <c r="A5" s="253"/>
+      <c r="B5" s="253"/>
+      <c r="C5" s="250" t="s">
         <v>225</v>
       </c>
-      <c r="D5" s="252" t="s">
+      <c r="D5" s="250" t="s">
         <v>226</v>
       </c>
-      <c r="E5" s="253"/>
-      <c r="F5" s="252" t="s">
+      <c r="E5" s="251"/>
+      <c r="F5" s="250" t="s">
         <v>227</v>
       </c>
-      <c r="G5" s="253"/>
-      <c r="H5" s="252" t="s">
+      <c r="G5" s="251"/>
+      <c r="H5" s="250" t="s">
         <v>228</v>
       </c>
-      <c r="I5" s="253"/>
-      <c r="J5" s="252" t="s">
+      <c r="I5" s="251"/>
+      <c r="J5" s="250" t="s">
         <v>229</v>
       </c>
-      <c r="K5" s="253"/>
-      <c r="L5" s="256" t="s">
+      <c r="K5" s="251"/>
+      <c r="L5" s="254" t="s">
         <v>230</v>
       </c>
-      <c r="M5" s="253"/>
-      <c r="N5" s="251" t="s">
+      <c r="M5" s="251"/>
+      <c r="N5" s="249" t="s">
         <v>231</v>
       </c>
-      <c r="O5" s="257"/>
-      <c r="P5" s="252" t="s">
+      <c r="O5" s="255"/>
+      <c r="P5" s="250" t="s">
         <v>235</v>
       </c>
-      <c r="R5" s="246" t="s">
+      <c r="R5" s="256" t="s">
         <v>34</v>
       </c>
-      <c r="S5" s="246" t="s">
+      <c r="S5" s="256" t="s">
         <v>258</v>
       </c>
-      <c r="T5" s="246" t="s">
+      <c r="T5" s="256" t="s">
         <v>259</v>
       </c>
-      <c r="U5" s="246" t="s">
+      <c r="U5" s="256" t="s">
         <v>261</v>
       </c>
-      <c r="V5" s="247" t="s">
+      <c r="V5" s="257" t="s">
         <v>260</v>
       </c>
       <c r="W5" s="155"/>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A6" s="254"/>
-      <c r="B6" s="254"/>
-      <c r="C6" s="255"/>
+      <c r="A6" s="252"/>
+      <c r="B6" s="252"/>
+      <c r="C6" s="253"/>
       <c r="D6" s="117" t="s">
         <v>2</v>
       </c>
@@ -27626,12 +27626,12 @@
       <c r="O6" s="117" t="s">
         <v>232</v>
       </c>
-      <c r="P6" s="254"/>
-      <c r="R6" s="246"/>
-      <c r="S6" s="246"/>
-      <c r="T6" s="246"/>
-      <c r="U6" s="246"/>
-      <c r="V6" s="246"/>
+      <c r="P6" s="252"/>
+      <c r="R6" s="256"/>
+      <c r="S6" s="256"/>
+      <c r="T6" s="256"/>
+      <c r="U6" s="256"/>
+      <c r="V6" s="256"/>
       <c r="W6" s="155"/>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.45">
@@ -27639,16 +27639,16 @@
         <v>179</v>
       </c>
       <c r="B7" s="173" t="s">
-        <v>101</v>
+        <v>68</v>
       </c>
       <c r="C7" s="173" t="s">
-        <v>102</v>
+        <v>69</v>
       </c>
       <c r="D7" s="174">
-        <v>454</v>
+        <v>434</v>
       </c>
       <c r="E7" s="174">
-        <v>70243418</v>
+        <v>72573808</v>
       </c>
       <c r="F7" s="174">
         <v>0</v>
@@ -27657,32 +27657,32 @@
         <v>0</v>
       </c>
       <c r="H7" s="174">
-        <v>454</v>
+        <v>434</v>
       </c>
       <c r="I7" s="174">
-        <v>70243418</v>
+        <v>72573808</v>
       </c>
       <c r="J7" s="174">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="K7" s="174">
-        <v>1990150</v>
+        <v>5052687</v>
       </c>
       <c r="L7" s="174">
-        <v>416</v>
+        <v>396</v>
       </c>
       <c r="M7" s="174">
-        <v>64376656</v>
+        <v>68100825</v>
       </c>
       <c r="N7" s="175">
-        <v>91.63</v>
+        <v>91.24</v>
       </c>
       <c r="O7" s="175">
-        <v>91.65</v>
+        <v>93.84</v>
       </c>
       <c r="P7" s="118">
         <f>I7*0.97-M7</f>
-        <v>3759459.4599999934</v>
+        <v>2295768.7600000054</v>
       </c>
       <c r="R7" s="156" t="s">
         <v>117</v>
@@ -27696,11 +27696,11 @@
       </c>
       <c r="U7" s="172">
         <f>VLOOKUP(R7,$C$7:$P$27,14,0)</f>
-        <v>11468259.799999997</v>
+        <v>8180283.799999997</v>
       </c>
       <c r="V7" s="158">
         <f>VLOOKUP(R7,$C$7:$P$27,14,0)-T7</f>
-        <v>-4584096</v>
+        <v>-7872072</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.45">
@@ -27708,16 +27708,16 @@
         <v>179</v>
       </c>
       <c r="B8" s="176" t="s">
-        <v>257</v>
+        <v>101</v>
       </c>
       <c r="C8" s="176" t="s">
-        <v>253</v>
+        <v>102</v>
       </c>
       <c r="D8" s="177">
-        <v>318</v>
+        <v>454</v>
       </c>
       <c r="E8" s="177">
-        <v>50351985</v>
+        <v>70243418</v>
       </c>
       <c r="F8" s="177">
         <v>0</v>
@@ -27726,32 +27726,32 @@
         <v>0</v>
       </c>
       <c r="H8" s="177">
-        <v>318</v>
+        <v>454</v>
       </c>
       <c r="I8" s="177">
-        <v>50351985</v>
+        <v>70243418</v>
       </c>
       <c r="J8" s="177">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="K8" s="177">
-        <v>666595</v>
+        <v>2650314</v>
       </c>
       <c r="L8" s="177">
-        <v>276</v>
+        <v>419</v>
       </c>
       <c r="M8" s="177">
-        <v>45200562</v>
+        <v>65036820</v>
       </c>
       <c r="N8" s="178">
-        <v>86.79</v>
+        <v>92.29</v>
       </c>
       <c r="O8" s="178">
-        <v>89.77</v>
+        <v>92.59</v>
       </c>
       <c r="P8" s="118">
         <f t="shared" ref="P8:P27" si="0">I8*0.97-M8</f>
-        <v>3640863.4499999955</v>
+        <v>3099295.4599999934</v>
       </c>
       <c r="R8" s="156" t="s">
         <v>67</v>
@@ -27765,11 +27765,11 @@
       </c>
       <c r="U8" s="172">
         <f t="shared" ref="U8:U17" si="2">VLOOKUP(R8,$C$7:$P$27,14,0)</f>
-        <v>13885488.310000002</v>
+        <v>11129522.310000002</v>
       </c>
       <c r="V8" s="158">
         <f t="shared" ref="V8:V17" si="3">VLOOKUP(R8,$C$7:$P$27,14,0)-T8</f>
-        <v>-4112240</v>
+        <v>-6868206</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.45">
@@ -27777,16 +27777,16 @@
         <v>179</v>
       </c>
       <c r="B9" s="173" t="s">
-        <v>114</v>
+        <v>257</v>
       </c>
       <c r="C9" s="173" t="s">
-        <v>115</v>
+        <v>253</v>
       </c>
       <c r="D9" s="174">
-        <v>559</v>
+        <v>318</v>
       </c>
       <c r="E9" s="174">
-        <v>93597302</v>
+        <v>50351985</v>
       </c>
       <c r="F9" s="174">
         <v>0</v>
@@ -27795,32 +27795,32 @@
         <v>0</v>
       </c>
       <c r="H9" s="174">
-        <v>559</v>
+        <v>318</v>
       </c>
       <c r="I9" s="174">
-        <v>93597302</v>
+        <v>50351985</v>
       </c>
       <c r="J9" s="174">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="K9" s="174">
-        <v>4022818</v>
+        <v>906595</v>
       </c>
       <c r="L9" s="174">
-        <v>481</v>
+        <v>277</v>
       </c>
       <c r="M9" s="174">
-        <v>82517110</v>
+        <v>45440562</v>
       </c>
       <c r="N9" s="175">
-        <v>86.05</v>
+        <v>87.11</v>
       </c>
       <c r="O9" s="175">
-        <v>88.16</v>
+        <v>90.25</v>
       </c>
       <c r="P9" s="118">
         <f t="shared" si="0"/>
-        <v>8272272.9399999976</v>
+        <v>3400863.4499999955</v>
       </c>
       <c r="R9" s="157" t="s">
         <v>87</v>
@@ -27834,11 +27834,11 @@
       </c>
       <c r="U9" s="172">
         <f t="shared" si="2"/>
-        <v>20691227.270000011</v>
+        <v>18270398.270000011</v>
       </c>
       <c r="V9" s="158">
         <f t="shared" si="3"/>
-        <v>-6026373</v>
+        <v>-8447202</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.45">
@@ -27846,16 +27846,16 @@
         <v>179</v>
       </c>
       <c r="B10" s="176" t="s">
-        <v>68</v>
+        <v>114</v>
       </c>
       <c r="C10" s="176" t="s">
-        <v>69</v>
+        <v>115</v>
       </c>
       <c r="D10" s="177">
-        <v>434</v>
+        <v>559</v>
       </c>
       <c r="E10" s="177">
-        <v>72573808</v>
+        <v>93597302</v>
       </c>
       <c r="F10" s="177">
         <v>0</v>
@@ -27864,32 +27864,32 @@
         <v>0</v>
       </c>
       <c r="H10" s="177">
-        <v>434</v>
+        <v>559</v>
       </c>
       <c r="I10" s="177">
-        <v>72573808</v>
+        <v>93597302</v>
       </c>
       <c r="J10" s="177">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="K10" s="177">
-        <v>924797</v>
+        <v>5842103</v>
       </c>
       <c r="L10" s="177">
-        <v>394</v>
+        <v>493</v>
       </c>
       <c r="M10" s="177">
-        <v>63972935</v>
+        <v>84336395</v>
       </c>
       <c r="N10" s="178">
-        <v>90.78</v>
+        <v>88.19</v>
       </c>
       <c r="O10" s="178">
-        <v>88.15</v>
+        <v>90.11</v>
       </c>
       <c r="P10" s="118">
         <f t="shared" si="0"/>
-        <v>6423658.7600000054</v>
+        <v>6452987.9399999976</v>
       </c>
       <c r="R10" s="157" t="s">
         <v>110</v>
@@ -27903,11 +27903,11 @@
       </c>
       <c r="U10" s="172">
         <f t="shared" si="2"/>
-        <v>33829922.859999985</v>
+        <v>30702491.859999985</v>
       </c>
       <c r="V10" s="158">
         <f t="shared" si="3"/>
-        <v>-7657626</v>
+        <v>-10785057</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.45">
@@ -27915,16 +27915,16 @@
         <v>179</v>
       </c>
       <c r="B11" s="173" t="s">
-        <v>122</v>
+        <v>89</v>
       </c>
       <c r="C11" s="173" t="s">
-        <v>123</v>
+        <v>90</v>
       </c>
       <c r="D11" s="174">
-        <v>308</v>
+        <v>356</v>
       </c>
       <c r="E11" s="174">
-        <v>51982396</v>
+        <v>53605661</v>
       </c>
       <c r="F11" s="174">
         <v>0</v>
@@ -27933,32 +27933,32 @@
         <v>0</v>
       </c>
       <c r="H11" s="174">
-        <v>308</v>
+        <v>356</v>
       </c>
       <c r="I11" s="174">
-        <v>51982396</v>
+        <v>53605661</v>
       </c>
       <c r="J11" s="174">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K11" s="174">
-        <v>2416666</v>
+        <v>3374641</v>
       </c>
       <c r="L11" s="174">
-        <v>267</v>
+        <v>304</v>
       </c>
       <c r="M11" s="174">
-        <v>45812520</v>
+        <v>48098936</v>
       </c>
       <c r="N11" s="175">
-        <v>86.69</v>
+        <v>85.39</v>
       </c>
       <c r="O11" s="175">
-        <v>88.13</v>
+        <v>89.73</v>
       </c>
       <c r="P11" s="118">
         <f t="shared" si="0"/>
-        <v>4610404.1199999973</v>
+        <v>3898555.1700000018</v>
       </c>
       <c r="R11" s="156" t="s">
         <v>99</v>
@@ -27972,28 +27972,28 @@
       </c>
       <c r="U11" s="172">
         <f t="shared" si="2"/>
-        <v>14886178.75</v>
+        <v>13387033.75</v>
       </c>
       <c r="V11" s="158">
         <f t="shared" si="3"/>
-        <v>-3807272</v>
+        <v>-5306417</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A12" s="176" t="s">
-        <v>128</v>
+        <v>179</v>
       </c>
       <c r="B12" s="176" t="s">
-        <v>66</v>
+        <v>122</v>
       </c>
       <c r="C12" s="176" t="s">
-        <v>67</v>
+        <v>123</v>
       </c>
       <c r="D12" s="177">
-        <v>876</v>
+        <v>308</v>
       </c>
       <c r="E12" s="177">
-        <v>145101823</v>
+        <v>51982396</v>
       </c>
       <c r="F12" s="177">
         <v>0</v>
@@ -28002,32 +28002,32 @@
         <v>0</v>
       </c>
       <c r="H12" s="177">
-        <v>876</v>
+        <v>308</v>
       </c>
       <c r="I12" s="177">
-        <v>145101823</v>
+        <v>51982396</v>
       </c>
       <c r="J12" s="177">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="K12" s="177">
-        <v>4446740</v>
+        <v>3150090</v>
       </c>
       <c r="L12" s="177">
-        <v>755</v>
+        <v>272</v>
       </c>
       <c r="M12" s="177">
-        <v>126863280</v>
+        <v>46545944</v>
       </c>
       <c r="N12" s="178">
-        <v>86.19</v>
+        <v>88.31</v>
       </c>
       <c r="O12" s="178">
-        <v>87.43</v>
+        <v>89.54</v>
       </c>
       <c r="P12" s="118">
         <f t="shared" si="0"/>
-        <v>13885488.310000002</v>
+        <v>3876980.1199999973</v>
       </c>
       <c r="R12" s="156" t="s">
         <v>75</v>
@@ -28041,28 +28041,28 @@
       </c>
       <c r="U12" s="172">
         <f t="shared" si="2"/>
-        <v>18816247.520000011</v>
+        <v>16644792.520000011</v>
       </c>
       <c r="V12" s="158">
         <f t="shared" si="3"/>
-        <v>-3216774</v>
+        <v>-5388229</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A13" s="173" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B13" s="173" t="s">
-        <v>106</v>
+        <v>66</v>
       </c>
       <c r="C13" s="173" t="s">
-        <v>107</v>
+        <v>67</v>
       </c>
       <c r="D13" s="174">
-        <v>1048</v>
+        <v>876</v>
       </c>
       <c r="E13" s="174">
-        <v>180440547</v>
+        <v>145101823</v>
       </c>
       <c r="F13" s="174">
         <v>0</v>
@@ -28071,32 +28071,32 @@
         <v>0</v>
       </c>
       <c r="H13" s="174">
-        <v>1048</v>
+        <v>876</v>
       </c>
       <c r="I13" s="174">
-        <v>180440547</v>
+        <v>145101823</v>
       </c>
       <c r="J13" s="174">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="K13" s="174">
-        <v>5794678</v>
+        <v>7202706</v>
       </c>
       <c r="L13" s="174">
-        <v>895</v>
+        <v>772</v>
       </c>
       <c r="M13" s="174">
-        <v>157365440</v>
+        <v>129619246</v>
       </c>
       <c r="N13" s="175">
-        <v>85.4</v>
+        <v>88.13</v>
       </c>
       <c r="O13" s="175">
-        <v>87.21</v>
+        <v>89.33</v>
       </c>
       <c r="P13" s="118">
         <f t="shared" si="0"/>
-        <v>17661890.590000004</v>
+        <v>11129522.310000002</v>
       </c>
       <c r="R13" s="156" t="s">
         <v>107</v>
@@ -28110,28 +28110,28 @@
       </c>
       <c r="U13" s="172">
         <f t="shared" si="2"/>
-        <v>17661890.590000004</v>
+        <v>15069660.590000004</v>
       </c>
       <c r="V13" s="158">
         <f t="shared" si="3"/>
-        <v>-5238245</v>
+        <v>-7830475</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A14" s="176" t="s">
-        <v>179</v>
+        <v>128</v>
       </c>
       <c r="B14" s="176" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="C14" s="176" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="D14" s="177">
-        <v>716</v>
+        <v>642</v>
       </c>
       <c r="E14" s="177">
-        <v>116427734</v>
+        <v>101866340</v>
       </c>
       <c r="F14" s="177">
         <v>0</v>
@@ -28140,32 +28140,32 @@
         <v>0</v>
       </c>
       <c r="H14" s="177">
-        <v>716</v>
+        <v>642</v>
       </c>
       <c r="I14" s="177">
-        <v>116427734</v>
+        <v>101866340</v>
       </c>
       <c r="J14" s="177">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="K14" s="177">
-        <v>2375727</v>
+        <v>7872072</v>
       </c>
       <c r="L14" s="177">
-        <v>605</v>
+        <v>547</v>
       </c>
       <c r="M14" s="177">
-        <v>100931373</v>
+        <v>90630066</v>
       </c>
       <c r="N14" s="178">
-        <v>84.5</v>
+        <v>85.2</v>
       </c>
       <c r="O14" s="178">
-        <v>86.69</v>
+        <v>88.97</v>
       </c>
       <c r="P14" s="118">
         <f t="shared" si="0"/>
-        <v>12003528.980000004</v>
+        <v>8180283.799999997</v>
       </c>
       <c r="R14" s="157" t="s">
         <v>72</v>
@@ -28179,11 +28179,11 @@
       </c>
       <c r="U14" s="172">
         <f t="shared" si="2"/>
-        <v>26591675.199999988</v>
+        <v>24402791.199999988</v>
       </c>
       <c r="V14" s="158">
         <f t="shared" si="3"/>
-        <v>-3947618</v>
+        <v>-6136502</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.45">
@@ -28191,16 +28191,16 @@
         <v>179</v>
       </c>
       <c r="B15" s="173" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="C15" s="173" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="D15" s="174">
-        <v>356</v>
+        <v>716</v>
       </c>
       <c r="E15" s="174">
-        <v>53605661</v>
+        <v>116427734</v>
       </c>
       <c r="F15" s="174">
         <v>0</v>
@@ -28209,32 +28209,32 @@
         <v>0</v>
       </c>
       <c r="H15" s="174">
-        <v>356</v>
+        <v>716</v>
       </c>
       <c r="I15" s="174">
-        <v>53605661</v>
+        <v>116427734</v>
       </c>
       <c r="J15" s="174">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="K15" s="174">
-        <v>1562383</v>
+        <v>4767679</v>
       </c>
       <c r="L15" s="174">
-        <v>295</v>
+        <v>621</v>
       </c>
       <c r="M15" s="174">
-        <v>46286678</v>
+        <v>103323325</v>
       </c>
       <c r="N15" s="175">
-        <v>82.87</v>
+        <v>86.73</v>
       </c>
       <c r="O15" s="175">
-        <v>86.35</v>
+        <v>88.74</v>
       </c>
       <c r="P15" s="118">
         <f t="shared" si="0"/>
-        <v>5710813.1700000018</v>
+        <v>9611576.9800000042</v>
       </c>
       <c r="R15" s="157" t="s">
         <v>113</v>
@@ -28248,28 +28248,28 @@
       </c>
       <c r="U15" s="172">
         <f t="shared" si="2"/>
-        <v>35659904.400000006</v>
+        <v>29608427.400000006</v>
       </c>
       <c r="V15" s="158">
         <f t="shared" si="3"/>
-        <v>-10458254</v>
+        <v>-16509731</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A16" s="176" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B16" s="176" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="C16" s="176" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="D16" s="177">
-        <v>642</v>
+        <v>1048</v>
       </c>
       <c r="E16" s="177">
-        <v>101866340</v>
+        <v>180440547</v>
       </c>
       <c r="F16" s="177">
         <v>0</v>
@@ -28278,32 +28278,32 @@
         <v>0</v>
       </c>
       <c r="H16" s="177">
-        <v>642</v>
+        <v>1048</v>
       </c>
       <c r="I16" s="177">
-        <v>101866340</v>
+        <v>180440547</v>
       </c>
       <c r="J16" s="177">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="K16" s="177">
-        <v>4584096</v>
+        <v>8386908</v>
       </c>
       <c r="L16" s="177">
-        <v>532</v>
+        <v>911</v>
       </c>
       <c r="M16" s="177">
-        <v>87342090</v>
+        <v>159957670</v>
       </c>
       <c r="N16" s="178">
-        <v>82.87</v>
+        <v>86.93</v>
       </c>
       <c r="O16" s="178">
-        <v>85.74</v>
+        <v>88.65</v>
       </c>
       <c r="P16" s="118">
         <f t="shared" si="0"/>
-        <v>11468259.799999997</v>
+        <v>15069660.590000004</v>
       </c>
       <c r="R16" s="157" t="s">
         <v>119</v>
@@ -28317,11 +28317,11 @@
       </c>
       <c r="U16" s="172">
         <f t="shared" si="2"/>
-        <v>21616065.409999996</v>
+        <v>18572643.409999996</v>
       </c>
       <c r="V16" s="158">
         <f t="shared" si="3"/>
-        <v>-8376049</v>
+        <v>-11419471</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.45">
@@ -28353,26 +28353,26 @@
         <v>189656153</v>
       </c>
       <c r="J17" s="174">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="K17" s="174">
-        <v>8661049</v>
+        <v>11704471</v>
       </c>
       <c r="L17" s="174">
-        <v>989</v>
+        <v>1007</v>
       </c>
       <c r="M17" s="174">
-        <v>162350403</v>
+        <v>165393825</v>
       </c>
       <c r="N17" s="175">
-        <v>83.74</v>
+        <v>85.27</v>
       </c>
       <c r="O17" s="175">
-        <v>85.6</v>
+        <v>87.21</v>
       </c>
       <c r="P17" s="118">
         <f t="shared" si="0"/>
-        <v>21616065.409999996</v>
+        <v>18572643.409999996</v>
       </c>
       <c r="R17" s="156" t="s">
         <v>84</v>
@@ -28386,11 +28386,11 @@
       </c>
       <c r="U17" s="172">
         <f t="shared" si="2"/>
-        <v>14113519.670000002</v>
+        <v>12058141.670000002</v>
       </c>
       <c r="V17" s="158">
         <f t="shared" si="3"/>
-        <v>-3197498</v>
+        <v>-5252876</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.45">
@@ -28422,43 +28422,43 @@
         <v>152862316</v>
       </c>
       <c r="J18" s="177">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="K18" s="177">
-        <v>3336609</v>
+        <v>5508064</v>
       </c>
       <c r="L18" s="177">
-        <v>769</v>
+        <v>783</v>
       </c>
       <c r="M18" s="177">
-        <v>129460199</v>
+        <v>131631654</v>
       </c>
       <c r="N18" s="178">
-        <v>81.72</v>
+        <v>83.21</v>
       </c>
       <c r="O18" s="178">
-        <v>84.69</v>
+        <v>86.11</v>
       </c>
       <c r="P18" s="118">
         <f t="shared" si="0"/>
-        <v>18816247.520000011</v>
+        <v>16644792.520000011</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A19" s="173" t="s">
-        <v>179</v>
+        <v>129</v>
       </c>
       <c r="B19" s="173" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C19" s="173" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D19" s="174">
-        <v>546</v>
+        <v>683</v>
       </c>
       <c r="E19" s="174">
-        <v>89879995</v>
+        <v>105983346</v>
       </c>
       <c r="F19" s="174">
         <v>0</v>
@@ -28467,49 +28467,49 @@
         <v>0</v>
       </c>
       <c r="H19" s="174">
-        <v>546</v>
+        <v>683</v>
       </c>
       <c r="I19" s="174">
-        <v>89879995</v>
+        <v>105983346</v>
       </c>
       <c r="J19" s="174">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="K19" s="174">
-        <v>11142818</v>
+        <v>4287069</v>
       </c>
       <c r="L19" s="174">
-        <v>448</v>
+        <v>582</v>
       </c>
       <c r="M19" s="174">
-        <v>76038328</v>
+        <v>90988216</v>
       </c>
       <c r="N19" s="175">
-        <v>82.05</v>
+        <v>85.21</v>
       </c>
       <c r="O19" s="175">
-        <v>84.6</v>
+        <v>85.85</v>
       </c>
       <c r="P19" s="118">
         <f t="shared" si="0"/>
-        <v>11145267.149999991</v>
+        <v>11815629.61999999</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A20" s="176" t="s">
-        <v>129</v>
+        <v>179</v>
       </c>
       <c r="B20" s="176" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C20" s="176" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D20" s="177">
-        <v>683</v>
+        <v>546</v>
       </c>
       <c r="E20" s="177">
-        <v>105983346</v>
+        <v>89879995</v>
       </c>
       <c r="F20" s="177">
         <v>0</v>
@@ -28518,32 +28518,32 @@
         <v>0</v>
       </c>
       <c r="H20" s="177">
-        <v>683</v>
+        <v>546</v>
       </c>
       <c r="I20" s="177">
-        <v>105983346</v>
+        <v>89879995</v>
       </c>
       <c r="J20" s="177">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="K20" s="177">
-        <v>2622336</v>
+        <v>11865907</v>
       </c>
       <c r="L20" s="177">
-        <v>569</v>
+        <v>452</v>
       </c>
       <c r="M20" s="177">
-        <v>89323483</v>
+        <v>76761417</v>
       </c>
       <c r="N20" s="178">
-        <v>83.31</v>
+        <v>82.78</v>
       </c>
       <c r="O20" s="178">
-        <v>84.28</v>
+        <v>85.4</v>
       </c>
       <c r="P20" s="118">
         <f t="shared" si="0"/>
-        <v>13480362.61999999</v>
+        <v>10422178.149999991</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.45">
@@ -28575,43 +28575,43 @@
         <v>105953075</v>
       </c>
       <c r="J21" s="174">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="K21" s="174">
-        <v>3972272</v>
+        <v>5471417</v>
       </c>
       <c r="L21" s="174">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="M21" s="174">
-        <v>87888304</v>
+        <v>89387449</v>
       </c>
       <c r="N21" s="175">
-        <v>79.91</v>
+        <v>80.930000000000007</v>
       </c>
       <c r="O21" s="175">
-        <v>82.95</v>
+        <v>84.37</v>
       </c>
       <c r="P21" s="118">
         <f t="shared" si="0"/>
-        <v>14886178.75</v>
+        <v>13387033.75</v>
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A22" s="176" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B22" s="176" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C22" s="176" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D22" s="177">
-        <v>853</v>
+        <v>588</v>
       </c>
       <c r="E22" s="177">
-        <v>141474291</v>
+        <v>95369711</v>
       </c>
       <c r="F22" s="177">
         <v>0</v>
@@ -28620,83 +28620,83 @@
         <v>0</v>
       </c>
       <c r="H22" s="177">
-        <v>853</v>
+        <v>588</v>
       </c>
       <c r="I22" s="177">
-        <v>141474291</v>
+        <v>95369711</v>
       </c>
       <c r="J22" s="177">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="K22" s="177">
-        <v>6271373</v>
+        <v>5462876</v>
       </c>
       <c r="L22" s="177">
-        <v>694</v>
+        <v>496</v>
       </c>
       <c r="M22" s="177">
-        <v>116538835</v>
+        <v>80450478</v>
       </c>
       <c r="N22" s="178">
-        <v>81.36</v>
+        <v>84.35</v>
       </c>
       <c r="O22" s="178">
-        <v>82.37</v>
+        <v>84.36</v>
       </c>
       <c r="P22" s="118">
         <f t="shared" si="0"/>
-        <v>20691227.270000011</v>
+        <v>12058141.670000002</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A23" s="173" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B23" s="173" t="s">
+        <v>86</v>
+      </c>
+      <c r="C23" s="173" t="s">
+        <v>87</v>
+      </c>
+      <c r="D23" s="174">
+        <v>853</v>
+      </c>
+      <c r="E23" s="174">
+        <v>141474291</v>
+      </c>
+      <c r="F23" s="174">
+        <v>0</v>
+      </c>
+      <c r="G23" s="174">
+        <v>0</v>
+      </c>
+      <c r="H23" s="174">
+        <v>853</v>
+      </c>
+      <c r="I23" s="174">
+        <v>141474291</v>
+      </c>
+      <c r="J23" s="174">
+        <v>45</v>
+      </c>
+      <c r="K23" s="174">
+        <v>8692202</v>
+      </c>
+      <c r="L23" s="174">
+        <v>708</v>
+      </c>
+      <c r="M23" s="174">
+        <v>118959664</v>
+      </c>
+      <c r="N23" s="175">
         <v>83</v>
       </c>
-      <c r="C23" s="173" t="s">
-        <v>84</v>
-      </c>
-      <c r="D23" s="174">
-        <v>588</v>
-      </c>
-      <c r="E23" s="174">
-        <v>95369711</v>
-      </c>
-      <c r="F23" s="174">
-        <v>0</v>
-      </c>
-      <c r="G23" s="174">
-        <v>0</v>
-      </c>
-      <c r="H23" s="174">
-        <v>588</v>
-      </c>
-      <c r="I23" s="174">
-        <v>95369711</v>
-      </c>
-      <c r="J23" s="174">
-        <v>22</v>
-      </c>
-      <c r="K23" s="174">
-        <v>3407498</v>
-      </c>
-      <c r="L23" s="174">
-        <v>481</v>
-      </c>
-      <c r="M23" s="174">
-        <v>78395100</v>
-      </c>
-      <c r="N23" s="175">
-        <v>81.8</v>
-      </c>
       <c r="O23" s="175">
-        <v>82.2</v>
+        <v>84.09</v>
       </c>
       <c r="P23" s="118">
         <f t="shared" si="0"/>
-        <v>14113519.670000002</v>
+        <v>18270398.270000011</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.45">
@@ -28728,26 +28728,26 @@
         <v>66800107</v>
       </c>
       <c r="J24" s="177">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="K24" s="177">
-        <v>2407464</v>
+        <v>3966599</v>
       </c>
       <c r="L24" s="177">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="M24" s="177">
-        <v>54463484</v>
+        <v>56022619</v>
       </c>
       <c r="N24" s="178">
-        <v>79.52</v>
+        <v>81.93</v>
       </c>
       <c r="O24" s="178">
-        <v>81.53</v>
+        <v>83.87</v>
       </c>
       <c r="P24" s="118">
         <f t="shared" si="0"/>
-        <v>10332619.789999999</v>
+        <v>8773484.7899999991</v>
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.45">
@@ -28779,26 +28779,26 @@
         <v>162344260</v>
       </c>
       <c r="J25" s="174">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="K25" s="174">
-        <v>4057586</v>
+        <v>6246470</v>
       </c>
       <c r="L25" s="174">
-        <v>779</v>
+        <v>790</v>
       </c>
       <c r="M25" s="174">
-        <v>130882257</v>
+        <v>133071141</v>
       </c>
       <c r="N25" s="175">
-        <v>80.48</v>
+        <v>81.61</v>
       </c>
       <c r="O25" s="175">
-        <v>80.62</v>
+        <v>81.97</v>
       </c>
       <c r="P25" s="118">
         <f t="shared" si="0"/>
-        <v>26591675.199999988</v>
+        <v>24402791.199999988</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.45">
@@ -28830,26 +28830,26 @@
         <v>194517020</v>
       </c>
       <c r="J26" s="177">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="K26" s="177">
-        <v>10838254</v>
+        <v>16889731</v>
       </c>
       <c r="L26" s="177">
-        <v>914</v>
+        <v>951</v>
       </c>
       <c r="M26" s="177">
-        <v>153021605</v>
+        <v>159073082</v>
       </c>
       <c r="N26" s="178">
-        <v>76.290000000000006</v>
+        <v>79.38</v>
       </c>
       <c r="O26" s="178">
-        <v>78.67</v>
+        <v>81.78</v>
       </c>
       <c r="P26" s="118">
         <f t="shared" si="0"/>
-        <v>35659904.400000006</v>
+        <v>29608427.400000006</v>
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.45">
@@ -28881,30 +28881,35 @@
         <v>149379338</v>
       </c>
       <c r="J27" s="174">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="K27" s="174">
-        <v>7939975</v>
+        <v>11067406</v>
       </c>
       <c r="L27" s="174">
-        <v>656</v>
+        <v>676</v>
       </c>
       <c r="M27" s="174">
-        <v>111068035</v>
+        <v>114195466</v>
       </c>
       <c r="N27" s="175">
-        <v>73.540000000000006</v>
+        <v>75.78</v>
       </c>
       <c r="O27" s="175">
-        <v>74.349999999999994</v>
+        <v>76.45</v>
       </c>
       <c r="P27" s="118">
         <f t="shared" si="0"/>
-        <v>33829922.859999985</v>
+        <v>30702491.859999985</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="U5:U6"/>
+    <mergeCell ref="V5:V6"/>
+    <mergeCell ref="R5:R6"/>
+    <mergeCell ref="S5:S6"/>
+    <mergeCell ref="T5:T6"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
     <mergeCell ref="A3:B3"/>
@@ -28919,11 +28924,6 @@
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="L5:M5"/>
     <mergeCell ref="N5:O5"/>
-    <mergeCell ref="U5:U6"/>
-    <mergeCell ref="V5:V6"/>
-    <mergeCell ref="R5:R6"/>
-    <mergeCell ref="S5:S6"/>
-    <mergeCell ref="T5:T6"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="P7:P27">

--- a/filetiendo.xlsx
+++ b/filetiendo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\viettel 2026\thang 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E11F8EA0-BDE0-4D1F-82DB-7444F7E0F384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AA4F45D-1F0B-4704-BC51-3A2C010D90CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="808" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6413,7 +6413,7 @@
       </c>
       <c r="AS5" s="112">
         <f>(VLOOKUP(B5,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.89329999999999998</v>
+        <v>0.90390000000000004</v>
       </c>
       <c r="AT5" s="14">
         <f t="shared" ref="AT5:AT18" si="20">IF(AS5&lt;94.5%,0,IF(AS5&lt;95.54%,50%,IF(AS5&lt;AR5,80%,100%+(30%*(AS5-AR5)/3.39%))))</f>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="AU5" s="48">
         <f t="shared" ref="AU5:AU18" si="21">AR5-AS5</f>
-        <v>7.669999999999999E-2</v>
+        <v>6.6099999999999937E-2</v>
       </c>
       <c r="AV5" s="51">
         <f>VLOOKUP(C5,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -6646,7 +6646,7 @@
       </c>
       <c r="AS6" s="112">
         <f>(VLOOKUP(B6,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.81969999999999998</v>
+        <v>0.86480000000000001</v>
       </c>
       <c r="AT6" s="14">
         <f t="shared" si="20"/>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="AU6" s="48">
         <f t="shared" si="21"/>
-        <v>0.15029999999999999</v>
+        <v>0.10519999999999996</v>
       </c>
       <c r="AV6" s="51">
         <f>VLOOKUP(C6,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="AS7" s="112">
         <f>(VLOOKUP(B7,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.86109999999999998</v>
+        <v>0.90249999999999997</v>
       </c>
       <c r="AT7" s="14">
         <f t="shared" si="20"/>
@@ -6887,7 +6887,7 @@
       </c>
       <c r="AU7" s="48">
         <f t="shared" si="21"/>
-        <v>0.1089</v>
+        <v>6.7500000000000004E-2</v>
       </c>
       <c r="AV7" s="51">
         <f>VLOOKUP(C7,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7112,7 +7112,7 @@
       </c>
       <c r="AS8" s="112">
         <f>(VLOOKUP(B8,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.85849999999999993</v>
+        <v>0.87849999999999995</v>
       </c>
       <c r="AT8" s="14">
         <f t="shared" si="20"/>
@@ -7120,7 +7120,7 @@
       </c>
       <c r="AU8" s="48">
         <f t="shared" si="21"/>
-        <v>0.11150000000000004</v>
+        <v>9.1500000000000026E-2</v>
       </c>
       <c r="AV8" s="51">
         <f>VLOOKUP(C8,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7345,7 +7345,7 @@
       </c>
       <c r="AS9" s="112">
         <f>(VLOOKUP(B9,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.85400000000000009</v>
+        <v>0.91450000000000009</v>
       </c>
       <c r="AT9" s="14">
         <f t="shared" si="20"/>
@@ -7353,7 +7353,7 @@
       </c>
       <c r="AU9" s="48">
         <f t="shared" si="21"/>
-        <v>0.11599999999999988</v>
+        <v>5.5499999999999883E-2</v>
       </c>
       <c r="AV9" s="51">
         <f>VLOOKUP(C9,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7578,7 +7578,7 @@
       </c>
       <c r="AS10" s="112">
         <f>(VLOOKUP(B10,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.84360000000000002</v>
+        <v>0.90629999999999999</v>
       </c>
       <c r="AT10" s="14">
         <f t="shared" si="20"/>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="AU10" s="48">
         <f t="shared" si="21"/>
-        <v>0.12639999999999996</v>
+        <v>6.3699999999999979E-2</v>
       </c>
       <c r="AV10" s="51">
         <f>VLOOKUP(C10,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7811,7 +7811,7 @@
       </c>
       <c r="AS11" s="112">
         <f>(VLOOKUP(B11,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.84090000000000009</v>
+        <v>0.91500000000000004</v>
       </c>
       <c r="AT11" s="14">
         <f t="shared" si="20"/>
@@ -7819,7 +7819,7 @@
       </c>
       <c r="AU11" s="48">
         <f t="shared" si="21"/>
-        <v>0.12909999999999988</v>
+        <v>5.4999999999999938E-2</v>
       </c>
       <c r="AV11" s="51">
         <f>VLOOKUP(C11,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8044,7 +8044,7 @@
       </c>
       <c r="AS12" s="112">
         <f>(VLOOKUP(B12,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.84370000000000012</v>
+        <v>0.93220000000000003</v>
       </c>
       <c r="AT12" s="14">
         <f t="shared" si="20"/>
@@ -8052,7 +8052,7 @@
       </c>
       <c r="AU12" s="48">
         <f t="shared" si="21"/>
-        <v>0.12629999999999986</v>
+        <v>3.7799999999999945E-2</v>
       </c>
       <c r="AV12" s="51">
         <f>VLOOKUP(C12,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8277,7 +8277,7 @@
       </c>
       <c r="AS13" s="112">
         <f>(VLOOKUP(B13,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.88650000000000007</v>
+        <v>0.9023000000000001</v>
       </c>
       <c r="AT13" s="14">
         <f t="shared" si="20"/>
@@ -8285,7 +8285,7 @@
       </c>
       <c r="AU13" s="48">
         <f t="shared" si="21"/>
-        <v>8.3499999999999908E-2</v>
+        <v>6.7699999999999871E-2</v>
       </c>
       <c r="AV13" s="51">
         <f>VLOOKUP(C13,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="AS14" s="112">
         <f>(VLOOKUP(B14,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.76450000000000007</v>
+        <v>0.86739999999999995</v>
       </c>
       <c r="AT14" s="14">
         <f t="shared" si="20"/>
@@ -8518,7 +8518,7 @@
       </c>
       <c r="AU14" s="48">
         <f t="shared" si="21"/>
-        <v>0.2054999999999999</v>
+        <v>0.10260000000000002</v>
       </c>
       <c r="AV14" s="51">
         <f>VLOOKUP(C14,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8743,7 +8743,7 @@
       </c>
       <c r="AS15" s="112">
         <f>(VLOOKUP(B15,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.81780000000000008</v>
+        <v>0.85819999999999996</v>
       </c>
       <c r="AT15" s="14">
         <f t="shared" si="20"/>
@@ -8751,7 +8751,7 @@
       </c>
       <c r="AU15" s="48">
         <f t="shared" si="21"/>
-        <v>0.15219999999999989</v>
+        <v>0.11180000000000001</v>
       </c>
       <c r="AV15" s="51">
         <f>VLOOKUP(C15,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8976,7 +8976,7 @@
       </c>
       <c r="AS16" s="112">
         <f>(VLOOKUP(B16,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.88970000000000005</v>
+        <v>0.8931</v>
       </c>
       <c r="AT16" s="14">
         <f t="shared" si="20"/>
@@ -8984,7 +8984,7 @@
       </c>
       <c r="AU16" s="48">
         <f t="shared" si="21"/>
-        <v>8.0299999999999927E-2</v>
+        <v>7.6899999999999968E-2</v>
       </c>
       <c r="AV16" s="51">
         <f>VLOOKUP(C16,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -9209,7 +9209,7 @@
       </c>
       <c r="AS17" s="112">
         <f>(VLOOKUP(B17,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.87209999999999999</v>
+        <v>0.90620000000000012</v>
       </c>
       <c r="AT17" s="14">
         <f t="shared" si="20"/>
@@ -9217,7 +9217,7 @@
       </c>
       <c r="AU17" s="48">
         <f t="shared" si="21"/>
-        <v>9.7899999999999987E-2</v>
+        <v>6.3799999999999857E-2</v>
       </c>
       <c r="AV17" s="51">
         <f>VLOOKUP(C17,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -9442,7 +9442,7 @@
       </c>
       <c r="AS18" s="112">
         <f>(VLOOKUP(B18,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.83870000000000011</v>
+        <v>0.85209999999999997</v>
       </c>
       <c r="AT18" s="14">
         <f t="shared" si="20"/>
@@ -9450,7 +9450,7 @@
       </c>
       <c r="AU18" s="48">
         <f t="shared" si="21"/>
-        <v>0.13129999999999986</v>
+        <v>0.1179</v>
       </c>
       <c r="AV18" s="51">
         <f>VLOOKUP(C18,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -9509,20 +9509,20 @@
       <c r="E19" s="16"/>
       <c r="F19" s="183">
         <f ca="1">TODAY()</f>
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="G19" s="183"/>
       <c r="H19" s="73"/>
       <c r="I19" s="74">
         <f ca="1">DAY(F19)</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J19" s="75">
         <v>31</v>
       </c>
       <c r="K19" s="78">
         <f ca="1">I19/J19</f>
-        <v>0.80645161290322576</v>
+        <v>0.83870967741935487</v>
       </c>
       <c r="L19" s="189" t="s">
         <v>124</v>
@@ -10445,7 +10445,7 @@
       </c>
       <c r="D14" s="68">
         <f>VLOOKUP($B$2,'TH NV'!$A$5:$BG$18,N14,0)</f>
-        <v>0.76450000000000007</v>
+        <v>0.86739999999999995</v>
       </c>
       <c r="E14" s="43" t="e">
         <f>VLOOKUP($B$2,'TH NV'!$A$1:$BG$18,70,0)</f>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="J14" s="59">
         <f t="shared" si="2"/>
-        <v>0.2054999999999999</v>
+        <v>0.10260000000000002</v>
       </c>
       <c r="K14" s="205"/>
       <c r="L14" s="97" t="s">
@@ -11153,7 +11153,7 @@
       </c>
       <c r="AS4" s="112">
         <f>(VLOOKUP(B4,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.89329999999999998</v>
+        <v>0.90390000000000004</v>
       </c>
       <c r="AT4" s="14">
         <f t="shared" ref="AT4" si="20">IF(AS4&lt;94.5%,0,IF(AS4&lt;95.54%,50%,IF(AS4&lt;AR4,80%,100%+(30%*(AS4-AR4)/3.39%))))</f>
@@ -11161,7 +11161,7 @@
       </c>
       <c r="AU4" s="48">
         <f t="shared" ref="AU4" si="21">AR4-AS4</f>
-        <v>7.669999999999999E-2</v>
+        <v>6.6099999999999937E-2</v>
       </c>
       <c r="AV4" s="51">
         <f>VLOOKUP(A4,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -11387,7 +11387,7 @@
       </c>
       <c r="AS5" s="112">
         <f>(VLOOKUP(B5,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.84090000000000009</v>
+        <v>0.91500000000000004</v>
       </c>
       <c r="AT5" s="14">
         <f t="shared" ref="AT5:AT16" si="48">IF(AS5&lt;94.5%,0,IF(AS5&lt;95.54%,50%,IF(AS5&lt;AR5,80%,100%+(30%*(AS5-AR5)/3.39%))))</f>
@@ -11395,7 +11395,7 @@
       </c>
       <c r="AU5" s="48">
         <f t="shared" ref="AU5:AU16" si="49">AR5-AS5</f>
-        <v>0.12909999999999988</v>
+        <v>5.4999999999999938E-2</v>
       </c>
       <c r="AV5" s="51">
         <f>VLOOKUP(A5,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -11621,7 +11621,7 @@
       </c>
       <c r="AS6" s="112">
         <f>(VLOOKUP(B6,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.84370000000000012</v>
+        <v>0.93220000000000003</v>
       </c>
       <c r="AT6" s="14">
         <f t="shared" si="48"/>
@@ -11629,7 +11629,7 @@
       </c>
       <c r="AU6" s="48">
         <f t="shared" si="49"/>
-        <v>0.12629999999999986</v>
+        <v>3.7799999999999945E-2</v>
       </c>
       <c r="AV6" s="51">
         <f>VLOOKUP(A6,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -11855,7 +11855,7 @@
       </c>
       <c r="AS7" s="112">
         <f>(VLOOKUP(B7,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.76450000000000007</v>
+        <v>0.86739999999999995</v>
       </c>
       <c r="AT7" s="14">
         <f t="shared" si="48"/>
@@ -11863,7 +11863,7 @@
       </c>
       <c r="AU7" s="48">
         <f t="shared" si="49"/>
-        <v>0.2054999999999999</v>
+        <v>0.10260000000000002</v>
       </c>
       <c r="AV7" s="51">
         <f>VLOOKUP(A7,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -12089,7 +12089,7 @@
       </c>
       <c r="AS8" s="112">
         <f>(VLOOKUP(B8,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.88970000000000005</v>
+        <v>0.8931</v>
       </c>
       <c r="AT8" s="14">
         <f t="shared" si="48"/>
@@ -12097,7 +12097,7 @@
       </c>
       <c r="AU8" s="48">
         <f t="shared" si="49"/>
-        <v>8.0299999999999927E-2</v>
+        <v>7.6899999999999968E-2</v>
       </c>
       <c r="AV8" s="51">
         <f>VLOOKUP(A8,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -12384,7 +12384,7 @@
       </c>
       <c r="AS10" s="112">
         <f>(VLOOKUP(B10,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.81969999999999998</v>
+        <v>0.86480000000000001</v>
       </c>
       <c r="AT10" s="14">
         <f t="shared" si="48"/>
@@ -12392,7 +12392,7 @@
       </c>
       <c r="AU10" s="48">
         <f t="shared" si="49"/>
-        <v>0.15029999999999999</v>
+        <v>0.10519999999999996</v>
       </c>
       <c r="AV10" s="51">
         <f>VLOOKUP(A10,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -12618,7 +12618,7 @@
       </c>
       <c r="AS11" s="112">
         <f>(VLOOKUP(B11,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.86109999999999998</v>
+        <v>0.90249999999999997</v>
       </c>
       <c r="AT11" s="14">
         <f t="shared" si="48"/>
@@ -12626,7 +12626,7 @@
       </c>
       <c r="AU11" s="48">
         <f t="shared" si="49"/>
-        <v>0.1089</v>
+        <v>6.7500000000000004E-2</v>
       </c>
       <c r="AV11" s="51">
         <f>VLOOKUP(A11,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -12852,7 +12852,7 @@
       </c>
       <c r="AS12" s="112">
         <f>(VLOOKUP(B12,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.85849999999999993</v>
+        <v>0.87849999999999995</v>
       </c>
       <c r="AT12" s="14">
         <f t="shared" si="48"/>
@@ -12860,7 +12860,7 @@
       </c>
       <c r="AU12" s="48">
         <f t="shared" si="49"/>
-        <v>0.11150000000000004</v>
+        <v>9.1500000000000026E-2</v>
       </c>
       <c r="AV12" s="51">
         <f>VLOOKUP(A12,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -13086,7 +13086,7 @@
       </c>
       <c r="AS13" s="112">
         <f>(VLOOKUP(B13,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.84360000000000002</v>
+        <v>0.90629999999999999</v>
       </c>
       <c r="AT13" s="14">
         <f t="shared" si="48"/>
@@ -13094,7 +13094,7 @@
       </c>
       <c r="AU13" s="48">
         <f t="shared" si="49"/>
-        <v>0.12639999999999996</v>
+        <v>6.3699999999999979E-2</v>
       </c>
       <c r="AV13" s="51">
         <f>VLOOKUP(A13,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -13320,7 +13320,7 @@
       </c>
       <c r="AS14" s="112">
         <f>(VLOOKUP(B14,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.88650000000000007</v>
+        <v>0.9023000000000001</v>
       </c>
       <c r="AT14" s="14">
         <f t="shared" si="48"/>
@@ -13328,7 +13328,7 @@
       </c>
       <c r="AU14" s="48">
         <f t="shared" si="49"/>
-        <v>8.3499999999999908E-2</v>
+        <v>6.7699999999999871E-2</v>
       </c>
       <c r="AV14" s="51">
         <f>VLOOKUP(A14,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -13554,7 +13554,7 @@
       </c>
       <c r="AS15" s="112">
         <f>(VLOOKUP(B15,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.81780000000000008</v>
+        <v>0.85819999999999996</v>
       </c>
       <c r="AT15" s="14">
         <f t="shared" si="48"/>
@@ -13562,7 +13562,7 @@
       </c>
       <c r="AU15" s="48">
         <f t="shared" si="49"/>
-        <v>0.15219999999999989</v>
+        <v>0.11180000000000001</v>
       </c>
       <c r="AV15" s="51">
         <f>VLOOKUP(A15,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -13788,7 +13788,7 @@
       </c>
       <c r="AS16" s="112">
         <f>(VLOOKUP(B16,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.87209999999999999</v>
+        <v>0.90620000000000012</v>
       </c>
       <c r="AT16" s="14">
         <f t="shared" si="48"/>
@@ -13796,7 +13796,7 @@
       </c>
       <c r="AU16" s="48">
         <f t="shared" si="49"/>
-        <v>9.7899999999999987E-2</v>
+        <v>6.3799999999999857E-2</v>
       </c>
       <c r="AV16" s="51">
         <f>VLOOKUP(A16,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -13880,11 +13880,11 @@
       </c>
       <c r="C19" s="125">
         <f ca="1">SUMIF(cuoc!A7:P27,'tiến độ'!A19,cuoc!M7:M27)</f>
-        <v>542791891</v>
+        <v>579918128</v>
       </c>
       <c r="D19" s="125">
         <f ca="1">B19*0.968-C19</f>
-        <v>80382180.255999923</v>
+        <v>43255943.255999923</v>
       </c>
       <c r="E19" s="120"/>
       <c r="H19" s="120"/>
@@ -13901,11 +13901,11 @@
       </c>
       <c r="C20" s="126">
         <f ca="1">SUMIF(cuoc!A8:P27,'tiến độ'!A20,cuoc!M8:M27)</f>
-        <v>920566066</v>
+        <v>959503618</v>
       </c>
       <c r="D20" s="125">
         <f ca="1">B20*0.968-C20</f>
-        <v>126009739.704</v>
+        <v>87072187.703999996</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.45">
@@ -27663,26 +27663,26 @@
         <v>72573808</v>
       </c>
       <c r="J7" s="174">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K7" s="174">
-        <v>5052687</v>
+        <v>0</v>
       </c>
       <c r="L7" s="174">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="M7" s="174">
-        <v>68100825</v>
+        <v>69152648</v>
       </c>
       <c r="N7" s="175">
-        <v>91.24</v>
+        <v>94.47</v>
       </c>
       <c r="O7" s="175">
-        <v>93.84</v>
+        <v>95.29</v>
       </c>
       <c r="P7" s="118">
         <f>I7*0.97-M7</f>
-        <v>2295768.7600000054</v>
+        <v>1243945.7600000054</v>
       </c>
       <c r="R7" s="156" t="s">
         <v>117</v>
@@ -27696,28 +27696,28 @@
       </c>
       <c r="U7" s="172">
         <f>VLOOKUP(R7,$C$7:$P$27,14,0)</f>
-        <v>8180283.799999997</v>
+        <v>7830615.799999997</v>
       </c>
       <c r="V7" s="158">
         <f>VLOOKUP(R7,$C$7:$P$27,14,0)-T7</f>
-        <v>-7872072</v>
+        <v>-8221740</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A8" s="176" t="s">
-        <v>179</v>
+        <v>128</v>
       </c>
       <c r="B8" s="176" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C8" s="176" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D8" s="177">
-        <v>454</v>
+        <v>687</v>
       </c>
       <c r="E8" s="177">
-        <v>70243418</v>
+        <v>105953075</v>
       </c>
       <c r="F8" s="177">
         <v>0</v>
@@ -27726,32 +27726,32 @@
         <v>0</v>
       </c>
       <c r="H8" s="177">
-        <v>454</v>
+        <v>687</v>
       </c>
       <c r="I8" s="177">
-        <v>70243418</v>
+        <v>105953075</v>
       </c>
       <c r="J8" s="177">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K8" s="177">
-        <v>2650314</v>
+        <v>0</v>
       </c>
       <c r="L8" s="177">
-        <v>419</v>
+        <v>620</v>
       </c>
       <c r="M8" s="177">
-        <v>65036820</v>
+        <v>98772069</v>
       </c>
       <c r="N8" s="178">
-        <v>92.29</v>
+        <v>90.25</v>
       </c>
       <c r="O8" s="178">
-        <v>92.59</v>
+        <v>93.22</v>
       </c>
       <c r="P8" s="118">
         <f t="shared" ref="P8:P27" si="0">I8*0.97-M8</f>
-        <v>3099295.4599999934</v>
+        <v>4002413.75</v>
       </c>
       <c r="R8" s="156" t="s">
         <v>67</v>
@@ -27765,11 +27765,11 @@
       </c>
       <c r="U8" s="172">
         <f t="shared" ref="U8:U17" si="2">VLOOKUP(R8,$C$7:$P$27,14,0)</f>
-        <v>11129522.310000002</v>
+        <v>9597357.3100000024</v>
       </c>
       <c r="V8" s="158">
         <f t="shared" ref="V8:V17" si="3">VLOOKUP(R8,$C$7:$P$27,14,0)-T8</f>
-        <v>-6868206</v>
+        <v>-8400371</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.45">
@@ -27777,16 +27777,16 @@
         <v>179</v>
       </c>
       <c r="B9" s="173" t="s">
-        <v>257</v>
+        <v>101</v>
       </c>
       <c r="C9" s="173" t="s">
-        <v>253</v>
+        <v>102</v>
       </c>
       <c r="D9" s="174">
-        <v>318</v>
+        <v>454</v>
       </c>
       <c r="E9" s="174">
-        <v>50351985</v>
+        <v>70243418</v>
       </c>
       <c r="F9" s="174">
         <v>0</v>
@@ -27795,32 +27795,32 @@
         <v>0</v>
       </c>
       <c r="H9" s="174">
-        <v>318</v>
+        <v>454</v>
       </c>
       <c r="I9" s="174">
-        <v>50351985</v>
+        <v>70243418</v>
       </c>
       <c r="J9" s="174">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K9" s="174">
-        <v>906595</v>
+        <v>0</v>
       </c>
       <c r="L9" s="174">
-        <v>277</v>
+        <v>422</v>
       </c>
       <c r="M9" s="174">
-        <v>45440562</v>
+        <v>65368540</v>
       </c>
       <c r="N9" s="175">
-        <v>87.11</v>
+        <v>92.95</v>
       </c>
       <c r="O9" s="175">
-        <v>90.25</v>
+        <v>93.06</v>
       </c>
       <c r="P9" s="118">
         <f t="shared" si="0"/>
-        <v>3400863.4499999955</v>
+        <v>2767575.4599999934</v>
       </c>
       <c r="R9" s="157" t="s">
         <v>87</v>
@@ -27834,11 +27834,11 @@
       </c>
       <c r="U9" s="172">
         <f t="shared" si="2"/>
-        <v>18270398.270000011</v>
+        <v>7784285.2700000107</v>
       </c>
       <c r="V9" s="158">
         <f t="shared" si="3"/>
-        <v>-8447202</v>
+        <v>-18933315</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.45">
@@ -27846,16 +27846,16 @@
         <v>179</v>
       </c>
       <c r="B10" s="176" t="s">
-        <v>114</v>
+        <v>257</v>
       </c>
       <c r="C10" s="176" t="s">
-        <v>115</v>
+        <v>253</v>
       </c>
       <c r="D10" s="177">
-        <v>559</v>
+        <v>318</v>
       </c>
       <c r="E10" s="177">
-        <v>93597302</v>
+        <v>50351985</v>
       </c>
       <c r="F10" s="177">
         <v>0</v>
@@ -27864,32 +27864,32 @@
         <v>0</v>
       </c>
       <c r="H10" s="177">
-        <v>559</v>
+        <v>318</v>
       </c>
       <c r="I10" s="177">
-        <v>93597302</v>
+        <v>50351985</v>
       </c>
       <c r="J10" s="177">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="K10" s="177">
-        <v>5842103</v>
+        <v>180000</v>
       </c>
       <c r="L10" s="177">
-        <v>493</v>
+        <v>284</v>
       </c>
       <c r="M10" s="177">
-        <v>84336395</v>
+        <v>46289562</v>
       </c>
       <c r="N10" s="178">
-        <v>88.19</v>
+        <v>89.31</v>
       </c>
       <c r="O10" s="178">
-        <v>90.11</v>
+        <v>91.93</v>
       </c>
       <c r="P10" s="118">
         <f t="shared" si="0"/>
-        <v>6452987.9399999976</v>
+        <v>2551863.4499999955</v>
       </c>
       <c r="R10" s="157" t="s">
         <v>110</v>
@@ -27903,28 +27903,28 @@
       </c>
       <c r="U10" s="172">
         <f t="shared" si="2"/>
-        <v>30702491.859999985</v>
+        <v>15328820.859999985</v>
       </c>
       <c r="V10" s="158">
         <f t="shared" si="3"/>
-        <v>-10785057</v>
+        <v>-26158728</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A11" s="173" t="s">
-        <v>179</v>
+        <v>128</v>
       </c>
       <c r="B11" s="173" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C11" s="173" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D11" s="174">
-        <v>356</v>
+        <v>853</v>
       </c>
       <c r="E11" s="174">
-        <v>53605661</v>
+        <v>141474291</v>
       </c>
       <c r="F11" s="174">
         <v>0</v>
@@ -27933,32 +27933,32 @@
         <v>0</v>
       </c>
       <c r="H11" s="174">
-        <v>356</v>
+        <v>853</v>
       </c>
       <c r="I11" s="174">
-        <v>53605661</v>
+        <v>141474291</v>
       </c>
       <c r="J11" s="174">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="K11" s="174">
-        <v>3374641</v>
+        <v>195000</v>
       </c>
       <c r="L11" s="174">
-        <v>304</v>
+        <v>769</v>
       </c>
       <c r="M11" s="174">
-        <v>48098936</v>
+        <v>129445777</v>
       </c>
       <c r="N11" s="175">
-        <v>85.39</v>
+        <v>90.15</v>
       </c>
       <c r="O11" s="175">
-        <v>89.73</v>
+        <v>91.5</v>
       </c>
       <c r="P11" s="118">
         <f t="shared" si="0"/>
-        <v>3898555.1700000018</v>
+        <v>7784285.2700000107</v>
       </c>
       <c r="R11" s="156" t="s">
         <v>99</v>
@@ -27972,11 +27972,11 @@
       </c>
       <c r="U11" s="172">
         <f t="shared" si="2"/>
-        <v>13387033.75</v>
+        <v>4002413.75</v>
       </c>
       <c r="V11" s="158">
         <f t="shared" si="3"/>
-        <v>-5306417</v>
+        <v>-14691037</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.45">
@@ -27984,16 +27984,16 @@
         <v>179</v>
       </c>
       <c r="B12" s="176" t="s">
-        <v>122</v>
+        <v>80</v>
       </c>
       <c r="C12" s="176" t="s">
-        <v>123</v>
+        <v>81</v>
       </c>
       <c r="D12" s="177">
-        <v>308</v>
+        <v>546</v>
       </c>
       <c r="E12" s="177">
-        <v>51982396</v>
+        <v>89879995</v>
       </c>
       <c r="F12" s="177">
         <v>0</v>
@@ -28002,32 +28002,32 @@
         <v>0</v>
       </c>
       <c r="H12" s="177">
-        <v>308</v>
+        <v>546</v>
       </c>
       <c r="I12" s="177">
-        <v>51982396</v>
+        <v>89879995</v>
       </c>
       <c r="J12" s="177">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="K12" s="177">
-        <v>3150090</v>
+        <v>1298870</v>
       </c>
       <c r="L12" s="177">
-        <v>272</v>
+        <v>480</v>
       </c>
       <c r="M12" s="177">
-        <v>46545944</v>
+        <v>82198707</v>
       </c>
       <c r="N12" s="178">
-        <v>88.31</v>
+        <v>87.91</v>
       </c>
       <c r="O12" s="178">
-        <v>89.54</v>
+        <v>91.45</v>
       </c>
       <c r="P12" s="118">
         <f t="shared" si="0"/>
-        <v>3876980.1199999973</v>
+        <v>4984888.1499999911</v>
       </c>
       <c r="R12" s="156" t="s">
         <v>75</v>
@@ -28041,28 +28041,28 @@
       </c>
       <c r="U12" s="172">
         <f t="shared" si="2"/>
-        <v>16644792.520000011</v>
+        <v>10320404.520000011</v>
       </c>
       <c r="V12" s="158">
         <f t="shared" si="3"/>
-        <v>-5388229</v>
+        <v>-11712617</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A13" s="173" t="s">
-        <v>128</v>
+        <v>179</v>
       </c>
       <c r="B13" s="173" t="s">
-        <v>66</v>
+        <v>114</v>
       </c>
       <c r="C13" s="173" t="s">
-        <v>67</v>
+        <v>115</v>
       </c>
       <c r="D13" s="174">
-        <v>876</v>
+        <v>559</v>
       </c>
       <c r="E13" s="174">
-        <v>145101823</v>
+        <v>93597302</v>
       </c>
       <c r="F13" s="174">
         <v>0</v>
@@ -28071,32 +28071,32 @@
         <v>0</v>
       </c>
       <c r="H13" s="174">
-        <v>876</v>
+        <v>559</v>
       </c>
       <c r="I13" s="174">
-        <v>145101823</v>
+        <v>93597302</v>
       </c>
       <c r="J13" s="174">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="K13" s="174">
-        <v>7202706</v>
+        <v>271500</v>
       </c>
       <c r="L13" s="174">
-        <v>772</v>
+        <v>501</v>
       </c>
       <c r="M13" s="174">
-        <v>129619246</v>
+        <v>85350859</v>
       </c>
       <c r="N13" s="175">
-        <v>88.13</v>
+        <v>89.62</v>
       </c>
       <c r="O13" s="175">
-        <v>89.33</v>
+        <v>91.19</v>
       </c>
       <c r="P13" s="118">
         <f t="shared" si="0"/>
-        <v>11129522.310000002</v>
+        <v>5438523.9399999976</v>
       </c>
       <c r="R13" s="156" t="s">
         <v>107</v>
@@ -28110,28 +28110,28 @@
       </c>
       <c r="U13" s="172">
         <f t="shared" si="2"/>
-        <v>15069660.590000004</v>
+        <v>12207250.590000004</v>
       </c>
       <c r="V13" s="158">
         <f t="shared" si="3"/>
-        <v>-7830475</v>
+        <v>-10692885</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A14" s="176" t="s">
-        <v>128</v>
+        <v>179</v>
       </c>
       <c r="B14" s="176" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="C14" s="176" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="D14" s="177">
-        <v>642</v>
+        <v>356</v>
       </c>
       <c r="E14" s="177">
-        <v>101866340</v>
+        <v>53605661</v>
       </c>
       <c r="F14" s="177">
         <v>0</v>
@@ -28140,32 +28140,32 @@
         <v>0</v>
       </c>
       <c r="H14" s="177">
-        <v>642</v>
+        <v>356</v>
       </c>
       <c r="I14" s="177">
-        <v>101866340</v>
+        <v>53605661</v>
       </c>
       <c r="J14" s="177">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K14" s="177">
-        <v>7872072</v>
+        <v>0</v>
       </c>
       <c r="L14" s="177">
-        <v>547</v>
+        <v>307</v>
       </c>
       <c r="M14" s="177">
-        <v>90630066</v>
+        <v>48663936</v>
       </c>
       <c r="N14" s="178">
-        <v>85.2</v>
+        <v>86.24</v>
       </c>
       <c r="O14" s="178">
-        <v>88.97</v>
+        <v>90.78</v>
       </c>
       <c r="P14" s="118">
         <f t="shared" si="0"/>
-        <v>8180283.799999997</v>
+        <v>3333555.1700000018</v>
       </c>
       <c r="R14" s="157" t="s">
         <v>72</v>
@@ -28179,28 +28179,28 @@
       </c>
       <c r="U14" s="172">
         <f t="shared" si="2"/>
-        <v>24402791.199999988</v>
+        <v>17074222.199999988</v>
       </c>
       <c r="V14" s="158">
         <f t="shared" si="3"/>
-        <v>-6136502</v>
+        <v>-13465071</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A15" s="173" t="s">
-        <v>179</v>
+        <v>129</v>
       </c>
       <c r="B15" s="173" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="C15" s="173" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="D15" s="174">
-        <v>716</v>
+        <v>588</v>
       </c>
       <c r="E15" s="174">
-        <v>116427734</v>
+        <v>95369711</v>
       </c>
       <c r="F15" s="174">
         <v>0</v>
@@ -28209,32 +28209,32 @@
         <v>0</v>
       </c>
       <c r="H15" s="174">
-        <v>716</v>
+        <v>588</v>
       </c>
       <c r="I15" s="174">
-        <v>116427734</v>
+        <v>95369711</v>
       </c>
       <c r="J15" s="174">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="K15" s="174">
-        <v>4767679</v>
+        <v>228334</v>
       </c>
       <c r="L15" s="174">
-        <v>621</v>
+        <v>526</v>
       </c>
       <c r="M15" s="174">
-        <v>103323325</v>
+        <v>86428817</v>
       </c>
       <c r="N15" s="175">
-        <v>86.73</v>
+        <v>89.46</v>
       </c>
       <c r="O15" s="175">
-        <v>88.74</v>
+        <v>90.63</v>
       </c>
       <c r="P15" s="118">
         <f t="shared" si="0"/>
-        <v>9611576.9800000042</v>
+        <v>6079802.6700000018</v>
       </c>
       <c r="R15" s="157" t="s">
         <v>113</v>
@@ -28248,11 +28248,11 @@
       </c>
       <c r="U15" s="172">
         <f t="shared" si="2"/>
-        <v>29608427.400000006</v>
+        <v>21748143.400000006</v>
       </c>
       <c r="V15" s="158">
         <f t="shared" si="3"/>
-        <v>-16509731</v>
+        <v>-24370015</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.45">
@@ -28260,16 +28260,16 @@
         <v>129</v>
       </c>
       <c r="B16" s="176" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="C16" s="176" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="D16" s="177">
-        <v>1048</v>
+        <v>1181</v>
       </c>
       <c r="E16" s="177">
-        <v>180440547</v>
+        <v>189656153</v>
       </c>
       <c r="F16" s="177">
         <v>0</v>
@@ -28278,32 +28278,32 @@
         <v>0</v>
       </c>
       <c r="H16" s="177">
-        <v>1048</v>
+        <v>1181</v>
       </c>
       <c r="I16" s="177">
-        <v>180440547</v>
+        <v>189656153</v>
       </c>
       <c r="J16" s="177">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="K16" s="177">
-        <v>8386908</v>
+        <v>1535646</v>
       </c>
       <c r="L16" s="177">
-        <v>911</v>
+        <v>1047</v>
       </c>
       <c r="M16" s="177">
-        <v>159957670</v>
+        <v>171864455</v>
       </c>
       <c r="N16" s="178">
-        <v>86.93</v>
+        <v>88.65</v>
       </c>
       <c r="O16" s="178">
-        <v>88.65</v>
+        <v>90.62</v>
       </c>
       <c r="P16" s="118">
         <f t="shared" si="0"/>
-        <v>15069660.590000004</v>
+        <v>12102013.409999996</v>
       </c>
       <c r="R16" s="157" t="s">
         <v>119</v>
@@ -28317,28 +28317,28 @@
       </c>
       <c r="U16" s="172">
         <f t="shared" si="2"/>
-        <v>18572643.409999996</v>
+        <v>12102013.409999996</v>
       </c>
       <c r="V16" s="158">
         <f t="shared" si="3"/>
-        <v>-11419471</v>
+        <v>-17890101</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A17" s="173" t="s">
-        <v>129</v>
+        <v>179</v>
       </c>
       <c r="B17" s="173" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="C17" s="173" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="D17" s="174">
-        <v>1181</v>
+        <v>716</v>
       </c>
       <c r="E17" s="174">
-        <v>189656153</v>
+        <v>116427734</v>
       </c>
       <c r="F17" s="174">
         <v>0</v>
@@ -28347,32 +28347,32 @@
         <v>0</v>
       </c>
       <c r="H17" s="174">
-        <v>1181</v>
+        <v>716</v>
       </c>
       <c r="I17" s="174">
-        <v>189656153</v>
+        <v>116427734</v>
       </c>
       <c r="J17" s="174">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="K17" s="174">
-        <v>11704471</v>
+        <v>239000</v>
       </c>
       <c r="L17" s="174">
-        <v>1007</v>
+        <v>637</v>
       </c>
       <c r="M17" s="174">
-        <v>165393825</v>
+        <v>105365939</v>
       </c>
       <c r="N17" s="175">
-        <v>85.27</v>
+        <v>88.97</v>
       </c>
       <c r="O17" s="175">
-        <v>87.21</v>
+        <v>90.5</v>
       </c>
       <c r="P17" s="118">
         <f t="shared" si="0"/>
-        <v>18572643.409999996</v>
+        <v>7568962.9800000042</v>
       </c>
       <c r="R17" s="156" t="s">
         <v>84</v>
@@ -28386,28 +28386,28 @@
       </c>
       <c r="U17" s="172">
         <f t="shared" si="2"/>
-        <v>12058141.670000002</v>
+        <v>6079802.6700000018</v>
       </c>
       <c r="V17" s="158">
         <f t="shared" si="3"/>
-        <v>-5252876</v>
+        <v>-11231215</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A18" s="176" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B18" s="176" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C18" s="176" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="D18" s="177">
-        <v>941</v>
+        <v>876</v>
       </c>
       <c r="E18" s="177">
-        <v>152862316</v>
+        <v>145101823</v>
       </c>
       <c r="F18" s="177">
         <v>0</v>
@@ -28416,32 +28416,32 @@
         <v>0</v>
       </c>
       <c r="H18" s="177">
-        <v>941</v>
+        <v>876</v>
       </c>
       <c r="I18" s="177">
-        <v>152862316</v>
+        <v>145101823</v>
       </c>
       <c r="J18" s="177">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K18" s="177">
-        <v>5508064</v>
+        <v>0</v>
       </c>
       <c r="L18" s="177">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="M18" s="177">
-        <v>131631654</v>
+        <v>131151411</v>
       </c>
       <c r="N18" s="178">
-        <v>83.21</v>
+        <v>89.61</v>
       </c>
       <c r="O18" s="178">
-        <v>86.11</v>
+        <v>90.39</v>
       </c>
       <c r="P18" s="118">
         <f t="shared" si="0"/>
-        <v>16644792.520000011</v>
+        <v>9597357.3100000024</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.45">
@@ -28449,16 +28449,16 @@
         <v>129</v>
       </c>
       <c r="B19" s="173" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C19" s="173" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D19" s="174">
-        <v>683</v>
+        <v>941</v>
       </c>
       <c r="E19" s="174">
-        <v>105983346</v>
+        <v>152862316</v>
       </c>
       <c r="F19" s="174">
         <v>0</v>
@@ -28467,49 +28467,49 @@
         <v>0</v>
       </c>
       <c r="H19" s="174">
-        <v>683</v>
+        <v>941</v>
       </c>
       <c r="I19" s="174">
-        <v>105983346</v>
+        <v>152862316</v>
       </c>
       <c r="J19" s="174">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K19" s="174">
-        <v>4287069</v>
+        <v>0</v>
       </c>
       <c r="L19" s="174">
-        <v>582</v>
+        <v>816</v>
       </c>
       <c r="M19" s="174">
-        <v>90988216</v>
+        <v>137956042</v>
       </c>
       <c r="N19" s="175">
-        <v>85.21</v>
+        <v>86.72</v>
       </c>
       <c r="O19" s="175">
-        <v>85.85</v>
+        <v>90.25</v>
       </c>
       <c r="P19" s="118">
         <f t="shared" si="0"/>
-        <v>11815629.61999999</v>
+        <v>10320404.520000011</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A20" s="176" t="s">
-        <v>179</v>
+        <v>129</v>
       </c>
       <c r="B20" s="176" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="C20" s="176" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="D20" s="177">
-        <v>546</v>
+        <v>1048</v>
       </c>
       <c r="E20" s="177">
-        <v>89879995</v>
+        <v>180440547</v>
       </c>
       <c r="F20" s="177">
         <v>0</v>
@@ -28518,49 +28518,49 @@
         <v>0</v>
       </c>
       <c r="H20" s="177">
-        <v>546</v>
+        <v>1048</v>
       </c>
       <c r="I20" s="177">
-        <v>89879995</v>
+        <v>180440547</v>
       </c>
       <c r="J20" s="177">
-        <v>66</v>
+        <v>2</v>
       </c>
       <c r="K20" s="177">
-        <v>11865907</v>
+        <v>455000</v>
       </c>
       <c r="L20" s="177">
-        <v>452</v>
+        <v>929</v>
       </c>
       <c r="M20" s="177">
-        <v>76761417</v>
+        <v>162820080</v>
       </c>
       <c r="N20" s="178">
-        <v>82.78</v>
+        <v>88.65</v>
       </c>
       <c r="O20" s="178">
-        <v>85.4</v>
+        <v>90.23</v>
       </c>
       <c r="P20" s="118">
         <f t="shared" si="0"/>
-        <v>10422178.149999991</v>
+        <v>12207250.590000004</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A21" s="173" t="s">
-        <v>128</v>
+        <v>179</v>
       </c>
       <c r="B21" s="173" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="C21" s="173" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="D21" s="174">
-        <v>687</v>
+        <v>308</v>
       </c>
       <c r="E21" s="174">
-        <v>105953075</v>
+        <v>51982396</v>
       </c>
       <c r="F21" s="174">
         <v>0</v>
@@ -28569,49 +28569,49 @@
         <v>0</v>
       </c>
       <c r="H21" s="174">
-        <v>687</v>
+        <v>308</v>
       </c>
       <c r="I21" s="174">
-        <v>105953075</v>
+        <v>51982396</v>
       </c>
       <c r="J21" s="174">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K21" s="174">
-        <v>5471417</v>
+        <v>0</v>
       </c>
       <c r="L21" s="174">
-        <v>556</v>
+        <v>274</v>
       </c>
       <c r="M21" s="174">
-        <v>89387449</v>
+        <v>46875944</v>
       </c>
       <c r="N21" s="175">
-        <v>80.930000000000007</v>
+        <v>88.96</v>
       </c>
       <c r="O21" s="175">
-        <v>84.37</v>
+        <v>90.18</v>
       </c>
       <c r="P21" s="118">
         <f t="shared" si="0"/>
-        <v>13387033.75</v>
+        <v>3546980.1199999973</v>
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A22" s="176" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B22" s="176" t="s">
-        <v>83</v>
+        <v>116</v>
       </c>
       <c r="C22" s="176" t="s">
-        <v>84</v>
+        <v>117</v>
       </c>
       <c r="D22" s="177">
-        <v>588</v>
+        <v>642</v>
       </c>
       <c r="E22" s="177">
-        <v>95369711</v>
+        <v>101866340</v>
       </c>
       <c r="F22" s="177">
         <v>0</v>
@@ -28620,49 +28620,49 @@
         <v>0</v>
       </c>
       <c r="H22" s="177">
-        <v>588</v>
+        <v>642</v>
       </c>
       <c r="I22" s="177">
-        <v>95369711</v>
+        <v>101866340</v>
       </c>
       <c r="J22" s="177">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K22" s="177">
-        <v>5462876</v>
+        <v>0</v>
       </c>
       <c r="L22" s="177">
-        <v>496</v>
+        <v>550</v>
       </c>
       <c r="M22" s="177">
-        <v>80450478</v>
+        <v>90979734</v>
       </c>
       <c r="N22" s="178">
-        <v>84.35</v>
+        <v>85.67</v>
       </c>
       <c r="O22" s="178">
-        <v>84.36</v>
+        <v>89.31</v>
       </c>
       <c r="P22" s="118">
         <f t="shared" si="0"/>
-        <v>12058141.670000002</v>
+        <v>7830615.799999997</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A23" s="173" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B23" s="173" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="C23" s="173" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="D23" s="174">
-        <v>853</v>
+        <v>683</v>
       </c>
       <c r="E23" s="174">
-        <v>141474291</v>
+        <v>105983346</v>
       </c>
       <c r="F23" s="174">
         <v>0</v>
@@ -28671,49 +28671,49 @@
         <v>0</v>
       </c>
       <c r="H23" s="174">
-        <v>853</v>
+        <v>683</v>
       </c>
       <c r="I23" s="174">
-        <v>141474291</v>
+        <v>105983346</v>
       </c>
       <c r="J23" s="174">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="K23" s="174">
-        <v>8692202</v>
+        <v>230000</v>
       </c>
       <c r="L23" s="174">
-        <v>708</v>
+        <v>594</v>
       </c>
       <c r="M23" s="174">
-        <v>118959664</v>
+        <v>93101148</v>
       </c>
       <c r="N23" s="175">
-        <v>83</v>
+        <v>86.97</v>
       </c>
       <c r="O23" s="175">
-        <v>84.09</v>
+        <v>87.85</v>
       </c>
       <c r="P23" s="118">
         <f t="shared" si="0"/>
-        <v>18270398.270000011</v>
+        <v>9702697.6199999899</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A24" s="176" t="s">
-        <v>179</v>
+        <v>128</v>
       </c>
       <c r="B24" s="176" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="C24" s="176" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="D24" s="177">
-        <v>415</v>
+        <v>892</v>
       </c>
       <c r="E24" s="177">
-        <v>66800107</v>
+        <v>149379338</v>
       </c>
       <c r="F24" s="177">
         <v>0</v>
@@ -28722,32 +28722,32 @@
         <v>0</v>
       </c>
       <c r="H24" s="177">
-        <v>415</v>
+        <v>892</v>
       </c>
       <c r="I24" s="177">
-        <v>66800107</v>
+        <v>149379338</v>
       </c>
       <c r="J24" s="177">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="K24" s="177">
-        <v>3966599</v>
+        <v>669689</v>
       </c>
       <c r="L24" s="177">
-        <v>340</v>
+        <v>780</v>
       </c>
       <c r="M24" s="177">
-        <v>56022619</v>
+        <v>129569137</v>
       </c>
       <c r="N24" s="178">
-        <v>81.93</v>
+        <v>87.44</v>
       </c>
       <c r="O24" s="178">
-        <v>83.87</v>
+        <v>86.74</v>
       </c>
       <c r="P24" s="118">
         <f t="shared" si="0"/>
-        <v>8773484.7899999991</v>
+        <v>15328820.859999985</v>
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.45">
@@ -28779,26 +28779,26 @@
         <v>162344260</v>
       </c>
       <c r="J25" s="174">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="K25" s="174">
-        <v>6246470</v>
+        <v>185000</v>
       </c>
       <c r="L25" s="174">
-        <v>790</v>
+        <v>835</v>
       </c>
       <c r="M25" s="174">
-        <v>133071141</v>
+        <v>140399710</v>
       </c>
       <c r="N25" s="175">
-        <v>81.61</v>
+        <v>86.26</v>
       </c>
       <c r="O25" s="175">
-        <v>81.97</v>
+        <v>86.48</v>
       </c>
       <c r="P25" s="118">
         <f t="shared" si="0"/>
-        <v>24402791.199999988</v>
+        <v>17074222.199999988</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.45">
@@ -28830,43 +28830,43 @@
         <v>194517020</v>
       </c>
       <c r="J26" s="177">
-        <v>96</v>
+        <v>4</v>
       </c>
       <c r="K26" s="177">
-        <v>16889731</v>
+        <v>789000</v>
       </c>
       <c r="L26" s="177">
-        <v>951</v>
+        <v>996</v>
       </c>
       <c r="M26" s="177">
-        <v>159073082</v>
+        <v>166933366</v>
       </c>
       <c r="N26" s="178">
-        <v>79.38</v>
+        <v>83.14</v>
       </c>
       <c r="O26" s="178">
-        <v>81.78</v>
+        <v>85.82</v>
       </c>
       <c r="P26" s="118">
         <f t="shared" si="0"/>
-        <v>29608427.400000006</v>
+        <v>21748143.400000006</v>
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A27" s="173" t="s">
-        <v>128</v>
+        <v>179</v>
       </c>
       <c r="B27" s="173" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="C27" s="173" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="D27" s="174">
-        <v>892</v>
+        <v>415</v>
       </c>
       <c r="E27" s="174">
-        <v>149379338</v>
+        <v>66800107</v>
       </c>
       <c r="F27" s="174">
         <v>0</v>
@@ -28875,32 +28875,32 @@
         <v>0</v>
       </c>
       <c r="H27" s="174">
-        <v>892</v>
+        <v>415</v>
       </c>
       <c r="I27" s="174">
-        <v>149379338</v>
+        <v>66800107</v>
       </c>
       <c r="J27" s="174">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="K27" s="174">
-        <v>11067406</v>
+        <v>0</v>
       </c>
       <c r="L27" s="174">
-        <v>676</v>
+        <v>346</v>
       </c>
       <c r="M27" s="174">
-        <v>114195466</v>
+        <v>56917297</v>
       </c>
       <c r="N27" s="175">
-        <v>75.78</v>
+        <v>83.37</v>
       </c>
       <c r="O27" s="175">
-        <v>76.45</v>
+        <v>85.21</v>
       </c>
       <c r="P27" s="118">
         <f t="shared" si="0"/>
-        <v>30702491.859999985</v>
+        <v>7878806.7899999991</v>
       </c>
     </row>
   </sheetData>

--- a/filetiendo.xlsx
+++ b/filetiendo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\viettel 2026\thang 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AA4F45D-1F0B-4704-BC51-3A2C010D90CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76652FA4-DBD6-4CB1-9D46-097B1F5DFF0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="808" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6413,7 +6413,7 @@
       </c>
       <c r="AS5" s="112">
         <f>(VLOOKUP(B5,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.90390000000000004</v>
+        <v>0.91230000000000011</v>
       </c>
       <c r="AT5" s="14">
         <f t="shared" ref="AT5:AT18" si="20">IF(AS5&lt;94.5%,0,IF(AS5&lt;95.54%,50%,IF(AS5&lt;AR5,80%,100%+(30%*(AS5-AR5)/3.39%))))</f>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="AU5" s="48">
         <f t="shared" ref="AU5:AU18" si="21">AR5-AS5</f>
-        <v>6.6099999999999937E-2</v>
+        <v>5.7699999999999863E-2</v>
       </c>
       <c r="AV5" s="51">
         <f>VLOOKUP(C5,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -6646,7 +6646,7 @@
       </c>
       <c r="AS6" s="112">
         <f>(VLOOKUP(B6,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.86480000000000001</v>
+        <v>0.86750000000000005</v>
       </c>
       <c r="AT6" s="14">
         <f t="shared" si="20"/>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="AU6" s="48">
         <f t="shared" si="21"/>
-        <v>0.10519999999999996</v>
+        <v>0.10249999999999992</v>
       </c>
       <c r="AV6" s="51">
         <f>VLOOKUP(C6,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="AS7" s="112">
         <f>(VLOOKUP(B7,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.90249999999999997</v>
+        <v>0.90540000000000009</v>
       </c>
       <c r="AT7" s="14">
         <f t="shared" si="20"/>
@@ -6887,7 +6887,7 @@
       </c>
       <c r="AU7" s="48">
         <f t="shared" si="21"/>
-        <v>6.7500000000000004E-2</v>
+        <v>6.459999999999988E-2</v>
       </c>
       <c r="AV7" s="51">
         <f>VLOOKUP(C7,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7112,7 +7112,7 @@
       </c>
       <c r="AS8" s="112">
         <f>(VLOOKUP(B8,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.87849999999999995</v>
+        <v>0.88230000000000008</v>
       </c>
       <c r="AT8" s="14">
         <f t="shared" si="20"/>
@@ -7120,7 +7120,7 @@
       </c>
       <c r="AU8" s="48">
         <f t="shared" si="21"/>
-        <v>9.1500000000000026E-2</v>
+        <v>8.7699999999999889E-2</v>
       </c>
       <c r="AV8" s="51">
         <f>VLOOKUP(C8,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7345,7 +7345,7 @@
       </c>
       <c r="AS9" s="112">
         <f>(VLOOKUP(B9,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.91450000000000009</v>
+        <v>0.91870000000000007</v>
       </c>
       <c r="AT9" s="14">
         <f t="shared" si="20"/>
@@ -7353,7 +7353,7 @@
       </c>
       <c r="AU9" s="48">
         <f t="shared" si="21"/>
-        <v>5.5499999999999883E-2</v>
+        <v>5.1299999999999901E-2</v>
       </c>
       <c r="AV9" s="51">
         <f>VLOOKUP(C9,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7578,7 +7578,7 @@
       </c>
       <c r="AS10" s="112">
         <f>(VLOOKUP(B10,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.90629999999999999</v>
+        <v>0.9103</v>
       </c>
       <c r="AT10" s="14">
         <f t="shared" si="20"/>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="AU10" s="48">
         <f t="shared" si="21"/>
-        <v>6.3699999999999979E-2</v>
+        <v>5.9699999999999975E-2</v>
       </c>
       <c r="AV10" s="51">
         <f>VLOOKUP(C10,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7811,7 +7811,7 @@
       </c>
       <c r="AS11" s="112">
         <f>(VLOOKUP(B11,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.91500000000000004</v>
+        <v>0.91620000000000001</v>
       </c>
       <c r="AT11" s="14">
         <f t="shared" si="20"/>
@@ -7819,7 +7819,7 @@
       </c>
       <c r="AU11" s="48">
         <f t="shared" si="21"/>
-        <v>5.4999999999999938E-2</v>
+        <v>5.3799999999999959E-2</v>
       </c>
       <c r="AV11" s="51">
         <f>VLOOKUP(C11,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8044,7 +8044,7 @@
       </c>
       <c r="AS12" s="112">
         <f>(VLOOKUP(B12,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.93220000000000003</v>
+        <v>0.93370000000000009</v>
       </c>
       <c r="AT12" s="14">
         <f t="shared" si="20"/>
@@ -8052,7 +8052,7 @@
       </c>
       <c r="AU12" s="48">
         <f t="shared" si="21"/>
-        <v>3.7799999999999945E-2</v>
+        <v>3.6299999999999888E-2</v>
       </c>
       <c r="AV12" s="51">
         <f>VLOOKUP(C12,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8277,7 +8277,7 @@
       </c>
       <c r="AS13" s="112">
         <f>(VLOOKUP(B13,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.9023000000000001</v>
+        <v>0.9043000000000001</v>
       </c>
       <c r="AT13" s="14">
         <f t="shared" si="20"/>
@@ -8285,7 +8285,7 @@
       </c>
       <c r="AU13" s="48">
         <f t="shared" si="21"/>
-        <v>6.7699999999999871E-2</v>
+        <v>6.569999999999987E-2</v>
       </c>
       <c r="AV13" s="51">
         <f>VLOOKUP(C13,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="AS14" s="112">
         <f>(VLOOKUP(B14,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.86739999999999995</v>
+        <v>0.89</v>
       </c>
       <c r="AT14" s="14">
         <f t="shared" si="20"/>
@@ -8518,7 +8518,7 @@
       </c>
       <c r="AU14" s="48">
         <f t="shared" si="21"/>
-        <v>0.10260000000000002</v>
+        <v>7.999999999999996E-2</v>
       </c>
       <c r="AV14" s="51">
         <f>VLOOKUP(C14,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8743,7 +8743,7 @@
       </c>
       <c r="AS15" s="112">
         <f>(VLOOKUP(B15,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.85819999999999996</v>
+        <v>0.86609999999999998</v>
       </c>
       <c r="AT15" s="14">
         <f t="shared" si="20"/>
@@ -8751,7 +8751,7 @@
       </c>
       <c r="AU15" s="48">
         <f t="shared" si="21"/>
-        <v>0.11180000000000001</v>
+        <v>0.10389999999999999</v>
       </c>
       <c r="AV15" s="51">
         <f>VLOOKUP(C15,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8976,7 +8976,7 @@
       </c>
       <c r="AS16" s="112">
         <f>(VLOOKUP(B16,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.8931</v>
+        <v>0.89710000000000001</v>
       </c>
       <c r="AT16" s="14">
         <f t="shared" si="20"/>
@@ -8984,7 +8984,7 @@
       </c>
       <c r="AU16" s="48">
         <f t="shared" si="21"/>
-        <v>7.6899999999999968E-2</v>
+        <v>7.2899999999999965E-2</v>
       </c>
       <c r="AV16" s="51">
         <f>VLOOKUP(C16,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -9209,7 +9209,7 @@
       </c>
       <c r="AS17" s="112">
         <f>(VLOOKUP(B17,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.90620000000000012</v>
+        <v>0.9133</v>
       </c>
       <c r="AT17" s="14">
         <f t="shared" si="20"/>
@@ -9217,7 +9217,7 @@
       </c>
       <c r="AU17" s="48">
         <f t="shared" si="21"/>
-        <v>6.3799999999999857E-2</v>
+        <v>5.6699999999999973E-2</v>
       </c>
       <c r="AV17" s="51">
         <f>VLOOKUP(C17,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -9442,7 +9442,7 @@
       </c>
       <c r="AS18" s="112">
         <f>(VLOOKUP(B18,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.85209999999999997</v>
+        <v>0.86780000000000002</v>
       </c>
       <c r="AT18" s="14">
         <f t="shared" si="20"/>
@@ -9450,7 +9450,7 @@
       </c>
       <c r="AU18" s="48">
         <f t="shared" si="21"/>
-        <v>0.1179</v>
+        <v>0.10219999999999996</v>
       </c>
       <c r="AV18" s="51">
         <f>VLOOKUP(C18,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -10445,7 +10445,7 @@
       </c>
       <c r="D14" s="68">
         <f>VLOOKUP($B$2,'TH NV'!$A$5:$BG$18,N14,0)</f>
-        <v>0.86739999999999995</v>
+        <v>0.89</v>
       </c>
       <c r="E14" s="43" t="e">
         <f>VLOOKUP($B$2,'TH NV'!$A$1:$BG$18,70,0)</f>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="J14" s="59">
         <f t="shared" si="2"/>
-        <v>0.10260000000000002</v>
+        <v>7.999999999999996E-2</v>
       </c>
       <c r="K14" s="205"/>
       <c r="L14" s="97" t="s">
@@ -11153,7 +11153,7 @@
       </c>
       <c r="AS4" s="112">
         <f>(VLOOKUP(B4,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.90390000000000004</v>
+        <v>0.91230000000000011</v>
       </c>
       <c r="AT4" s="14">
         <f t="shared" ref="AT4" si="20">IF(AS4&lt;94.5%,0,IF(AS4&lt;95.54%,50%,IF(AS4&lt;AR4,80%,100%+(30%*(AS4-AR4)/3.39%))))</f>
@@ -11161,7 +11161,7 @@
       </c>
       <c r="AU4" s="48">
         <f t="shared" ref="AU4" si="21">AR4-AS4</f>
-        <v>6.6099999999999937E-2</v>
+        <v>5.7699999999999863E-2</v>
       </c>
       <c r="AV4" s="51">
         <f>VLOOKUP(A4,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -11387,7 +11387,7 @@
       </c>
       <c r="AS5" s="112">
         <f>(VLOOKUP(B5,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.91500000000000004</v>
+        <v>0.91620000000000001</v>
       </c>
       <c r="AT5" s="14">
         <f t="shared" ref="AT5:AT16" si="48">IF(AS5&lt;94.5%,0,IF(AS5&lt;95.54%,50%,IF(AS5&lt;AR5,80%,100%+(30%*(AS5-AR5)/3.39%))))</f>
@@ -11395,7 +11395,7 @@
       </c>
       <c r="AU5" s="48">
         <f t="shared" ref="AU5:AU16" si="49">AR5-AS5</f>
-        <v>5.4999999999999938E-2</v>
+        <v>5.3799999999999959E-2</v>
       </c>
       <c r="AV5" s="51">
         <f>VLOOKUP(A5,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -11621,7 +11621,7 @@
       </c>
       <c r="AS6" s="112">
         <f>(VLOOKUP(B6,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.93220000000000003</v>
+        <v>0.93370000000000009</v>
       </c>
       <c r="AT6" s="14">
         <f t="shared" si="48"/>
@@ -11629,7 +11629,7 @@
       </c>
       <c r="AU6" s="48">
         <f t="shared" si="49"/>
-        <v>3.7799999999999945E-2</v>
+        <v>3.6299999999999888E-2</v>
       </c>
       <c r="AV6" s="51">
         <f>VLOOKUP(A6,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -11855,7 +11855,7 @@
       </c>
       <c r="AS7" s="112">
         <f>(VLOOKUP(B7,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.86739999999999995</v>
+        <v>0.89</v>
       </c>
       <c r="AT7" s="14">
         <f t="shared" si="48"/>
@@ -11863,7 +11863,7 @@
       </c>
       <c r="AU7" s="48">
         <f t="shared" si="49"/>
-        <v>0.10260000000000002</v>
+        <v>7.999999999999996E-2</v>
       </c>
       <c r="AV7" s="51">
         <f>VLOOKUP(A7,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -12089,7 +12089,7 @@
       </c>
       <c r="AS8" s="112">
         <f>(VLOOKUP(B8,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.8931</v>
+        <v>0.89710000000000001</v>
       </c>
       <c r="AT8" s="14">
         <f t="shared" si="48"/>
@@ -12097,7 +12097,7 @@
       </c>
       <c r="AU8" s="48">
         <f t="shared" si="49"/>
-        <v>7.6899999999999968E-2</v>
+        <v>7.2899999999999965E-2</v>
       </c>
       <c r="AV8" s="51">
         <f>VLOOKUP(A8,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -12384,7 +12384,7 @@
       </c>
       <c r="AS10" s="112">
         <f>(VLOOKUP(B10,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.86480000000000001</v>
+        <v>0.86750000000000005</v>
       </c>
       <c r="AT10" s="14">
         <f t="shared" si="48"/>
@@ -12392,7 +12392,7 @@
       </c>
       <c r="AU10" s="48">
         <f t="shared" si="49"/>
-        <v>0.10519999999999996</v>
+        <v>0.10249999999999992</v>
       </c>
       <c r="AV10" s="51">
         <f>VLOOKUP(A10,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -12618,7 +12618,7 @@
       </c>
       <c r="AS11" s="112">
         <f>(VLOOKUP(B11,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.90249999999999997</v>
+        <v>0.90540000000000009</v>
       </c>
       <c r="AT11" s="14">
         <f t="shared" si="48"/>
@@ -12626,7 +12626,7 @@
       </c>
       <c r="AU11" s="48">
         <f t="shared" si="49"/>
-        <v>6.7500000000000004E-2</v>
+        <v>6.459999999999988E-2</v>
       </c>
       <c r="AV11" s="51">
         <f>VLOOKUP(A11,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -12852,7 +12852,7 @@
       </c>
       <c r="AS12" s="112">
         <f>(VLOOKUP(B12,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.87849999999999995</v>
+        <v>0.88230000000000008</v>
       </c>
       <c r="AT12" s="14">
         <f t="shared" si="48"/>
@@ -12860,7 +12860,7 @@
       </c>
       <c r="AU12" s="48">
         <f t="shared" si="49"/>
-        <v>9.1500000000000026E-2</v>
+        <v>8.7699999999999889E-2</v>
       </c>
       <c r="AV12" s="51">
         <f>VLOOKUP(A12,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -13086,7 +13086,7 @@
       </c>
       <c r="AS13" s="112">
         <f>(VLOOKUP(B13,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.90629999999999999</v>
+        <v>0.9103</v>
       </c>
       <c r="AT13" s="14">
         <f t="shared" si="48"/>
@@ -13094,7 +13094,7 @@
       </c>
       <c r="AU13" s="48">
         <f t="shared" si="49"/>
-        <v>6.3699999999999979E-2</v>
+        <v>5.9699999999999975E-2</v>
       </c>
       <c r="AV13" s="51">
         <f>VLOOKUP(A13,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -13320,7 +13320,7 @@
       </c>
       <c r="AS14" s="112">
         <f>(VLOOKUP(B14,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.9023000000000001</v>
+        <v>0.9043000000000001</v>
       </c>
       <c r="AT14" s="14">
         <f t="shared" si="48"/>
@@ -13328,7 +13328,7 @@
       </c>
       <c r="AU14" s="48">
         <f t="shared" si="49"/>
-        <v>6.7699999999999871E-2</v>
+        <v>6.569999999999987E-2</v>
       </c>
       <c r="AV14" s="51">
         <f>VLOOKUP(A14,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -13554,7 +13554,7 @@
       </c>
       <c r="AS15" s="112">
         <f>(VLOOKUP(B15,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.85819999999999996</v>
+        <v>0.86609999999999998</v>
       </c>
       <c r="AT15" s="14">
         <f t="shared" si="48"/>
@@ -13562,7 +13562,7 @@
       </c>
       <c r="AU15" s="48">
         <f t="shared" si="49"/>
-        <v>0.11180000000000001</v>
+        <v>0.10389999999999999</v>
       </c>
       <c r="AV15" s="51">
         <f>VLOOKUP(A15,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -13788,7 +13788,7 @@
       </c>
       <c r="AS16" s="112">
         <f>(VLOOKUP(B16,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.90620000000000012</v>
+        <v>0.9133</v>
       </c>
       <c r="AT16" s="14">
         <f t="shared" si="48"/>
@@ -13796,7 +13796,7 @@
       </c>
       <c r="AU16" s="48">
         <f t="shared" si="49"/>
-        <v>6.3799999999999857E-2</v>
+        <v>5.6699999999999973E-2</v>
       </c>
       <c r="AV16" s="51">
         <f>VLOOKUP(A16,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -13880,11 +13880,11 @@
       </c>
       <c r="C19" s="125">
         <f ca="1">SUMIF(cuoc!A7:P27,'tiến độ'!A19,cuoc!M7:M27)</f>
-        <v>579918128</v>
+        <v>585269431</v>
       </c>
       <c r="D19" s="125">
         <f ca="1">B19*0.968-C19</f>
-        <v>43255943.255999923</v>
+        <v>37904640.255999923</v>
       </c>
       <c r="E19" s="120"/>
       <c r="H19" s="120"/>
@@ -13901,11 +13901,11 @@
       </c>
       <c r="C20" s="126">
         <f ca="1">SUMIF(cuoc!A8:P27,'tiến độ'!A20,cuoc!M8:M27)</f>
-        <v>959503618</v>
+        <v>964414681</v>
       </c>
       <c r="D20" s="125">
         <f ca="1">B20*0.968-C20</f>
-        <v>87072187.703999996</v>
+        <v>82161124.703999996</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.45">
@@ -27692,32 +27692,32 @@
         <v>101866340</v>
       </c>
       <c r="T7" s="158">
-        <v>16052355.799999997</v>
+        <v>7830615.799999997</v>
       </c>
       <c r="U7" s="172">
         <f>VLOOKUP(R7,$C$7:$P$27,14,0)</f>
-        <v>7830615.799999997</v>
+        <v>7421615.799999997</v>
       </c>
       <c r="V7" s="158">
         <f>VLOOKUP(R7,$C$7:$P$27,14,0)-T7</f>
-        <v>-8221740</v>
+        <v>-409000</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A8" s="176" t="s">
-        <v>128</v>
+        <v>179</v>
       </c>
       <c r="B8" s="176" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C8" s="176" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D8" s="177">
-        <v>687</v>
+        <v>454</v>
       </c>
       <c r="E8" s="177">
-        <v>105953075</v>
+        <v>70243418</v>
       </c>
       <c r="F8" s="177">
         <v>0</v>
@@ -27726,32 +27726,32 @@
         <v>0</v>
       </c>
       <c r="H8" s="177">
-        <v>687</v>
+        <v>454</v>
       </c>
       <c r="I8" s="177">
-        <v>105953075</v>
+        <v>70243418</v>
       </c>
       <c r="J8" s="177">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" s="177">
-        <v>0</v>
+        <v>250985</v>
       </c>
       <c r="L8" s="177">
-        <v>620</v>
+        <v>423</v>
       </c>
       <c r="M8" s="177">
-        <v>98772069</v>
+        <v>65619525</v>
       </c>
       <c r="N8" s="178">
-        <v>90.25</v>
+        <v>93.17</v>
       </c>
       <c r="O8" s="178">
-        <v>93.22</v>
+        <v>93.42</v>
       </c>
       <c r="P8" s="118">
         <f t="shared" ref="P8:P27" si="0">I8*0.97-M8</f>
-        <v>4002413.75</v>
+        <v>2516590.4599999934</v>
       </c>
       <c r="R8" s="156" t="s">
         <v>67</v>
@@ -27761,32 +27761,32 @@
         <v>145101823</v>
       </c>
       <c r="T8" s="158">
-        <v>17997728.310000002</v>
+        <v>9597357.3100000024</v>
       </c>
       <c r="U8" s="172">
         <f t="shared" ref="U8:U17" si="2">VLOOKUP(R8,$C$7:$P$27,14,0)</f>
-        <v>9597357.3100000024</v>
+        <v>8366106.3100000024</v>
       </c>
       <c r="V8" s="158">
         <f t="shared" ref="V8:V17" si="3">VLOOKUP(R8,$C$7:$P$27,14,0)-T8</f>
-        <v>-8400371</v>
+        <v>-1231251</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A9" s="173" t="s">
-        <v>179</v>
+        <v>128</v>
       </c>
       <c r="B9" s="173" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C9" s="173" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D9" s="174">
-        <v>454</v>
+        <v>687</v>
       </c>
       <c r="E9" s="174">
-        <v>70243418</v>
+        <v>105953075</v>
       </c>
       <c r="F9" s="174">
         <v>0</v>
@@ -27795,32 +27795,32 @@
         <v>0</v>
       </c>
       <c r="H9" s="174">
-        <v>454</v>
+        <v>687</v>
       </c>
       <c r="I9" s="174">
-        <v>70243418</v>
+        <v>105953075</v>
       </c>
       <c r="J9" s="174">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9" s="174">
-        <v>0</v>
+        <v>155806</v>
       </c>
       <c r="L9" s="174">
-        <v>422</v>
+        <v>622</v>
       </c>
       <c r="M9" s="174">
-        <v>65368540</v>
+        <v>98927875</v>
       </c>
       <c r="N9" s="175">
-        <v>92.95</v>
+        <v>90.54</v>
       </c>
       <c r="O9" s="175">
-        <v>93.06</v>
+        <v>93.37</v>
       </c>
       <c r="P9" s="118">
         <f t="shared" si="0"/>
-        <v>2767575.4599999934</v>
+        <v>3846607.75</v>
       </c>
       <c r="R9" s="157" t="s">
         <v>87</v>
@@ -27830,15 +27830,15 @@
         <v>141474291</v>
       </c>
       <c r="T9" s="158">
-        <v>26717600.270000011</v>
+        <v>7784285.2700000107</v>
       </c>
       <c r="U9" s="172">
         <f t="shared" si="2"/>
-        <v>7784285.2700000107</v>
+        <v>7604285.2700000107</v>
       </c>
       <c r="V9" s="158">
         <f t="shared" si="3"/>
-        <v>-18933315</v>
+        <v>-180000</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.45">
@@ -27899,32 +27899,32 @@
         <v>149379338</v>
       </c>
       <c r="T10" s="158">
-        <v>41487548.859999985</v>
+        <v>15328820.859999985</v>
       </c>
       <c r="U10" s="172">
         <f t="shared" si="2"/>
-        <v>15328820.859999985</v>
+        <v>11953574.859999985</v>
       </c>
       <c r="V10" s="158">
         <f t="shared" si="3"/>
-        <v>-26158728</v>
+        <v>-3375246</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A11" s="173" t="s">
-        <v>128</v>
+        <v>179</v>
       </c>
       <c r="B11" s="173" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C11" s="173" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D11" s="174">
-        <v>853</v>
+        <v>546</v>
       </c>
       <c r="E11" s="174">
-        <v>141474291</v>
+        <v>89879995</v>
       </c>
       <c r="F11" s="174">
         <v>0</v>
@@ -27933,32 +27933,32 @@
         <v>0</v>
       </c>
       <c r="H11" s="174">
-        <v>853</v>
+        <v>546</v>
       </c>
       <c r="I11" s="174">
-        <v>141474291</v>
+        <v>89879995</v>
       </c>
       <c r="J11" s="174">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K11" s="174">
-        <v>195000</v>
+        <v>1671526</v>
       </c>
       <c r="L11" s="174">
-        <v>769</v>
+        <v>482</v>
       </c>
       <c r="M11" s="174">
-        <v>129445777</v>
+        <v>82571363</v>
       </c>
       <c r="N11" s="175">
-        <v>90.15</v>
+        <v>88.28</v>
       </c>
       <c r="O11" s="175">
-        <v>91.5</v>
+        <v>91.87</v>
       </c>
       <c r="P11" s="118">
         <f t="shared" si="0"/>
-        <v>7784285.2700000107</v>
+        <v>4612232.1499999911</v>
       </c>
       <c r="R11" s="156" t="s">
         <v>99</v>
@@ -27968,32 +27968,32 @@
         <v>105953075</v>
       </c>
       <c r="T11" s="158">
-        <v>18693450.75</v>
+        <v>4002413.75</v>
       </c>
       <c r="U11" s="172">
         <f t="shared" si="2"/>
-        <v>4002413.75</v>
+        <v>3846607.75</v>
       </c>
       <c r="V11" s="158">
         <f t="shared" si="3"/>
-        <v>-14691037</v>
+        <v>-155806</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A12" s="176" t="s">
-        <v>179</v>
+        <v>128</v>
       </c>
       <c r="B12" s="176" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C12" s="176" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D12" s="177">
-        <v>546</v>
+        <v>853</v>
       </c>
       <c r="E12" s="177">
-        <v>89879995</v>
+        <v>141474291</v>
       </c>
       <c r="F12" s="177">
         <v>0</v>
@@ -28002,32 +28002,32 @@
         <v>0</v>
       </c>
       <c r="H12" s="177">
-        <v>546</v>
+        <v>853</v>
       </c>
       <c r="I12" s="177">
-        <v>89879995</v>
+        <v>141474291</v>
       </c>
       <c r="J12" s="177">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K12" s="177">
-        <v>1298870</v>
+        <v>375000</v>
       </c>
       <c r="L12" s="177">
-        <v>480</v>
+        <v>770</v>
       </c>
       <c r="M12" s="177">
-        <v>82198707</v>
+        <v>129625777</v>
       </c>
       <c r="N12" s="178">
-        <v>87.91</v>
+        <v>90.27</v>
       </c>
       <c r="O12" s="178">
-        <v>91.45</v>
+        <v>91.62</v>
       </c>
       <c r="P12" s="118">
         <f t="shared" si="0"/>
-        <v>4984888.1499999911</v>
+        <v>7604285.2700000107</v>
       </c>
       <c r="R12" s="156" t="s">
         <v>75</v>
@@ -28037,15 +28037,15 @@
         <v>152862316</v>
       </c>
       <c r="T12" s="158">
-        <v>22033021.520000011</v>
+        <v>10320404.520000011</v>
       </c>
       <c r="U12" s="172">
         <f t="shared" si="2"/>
-        <v>10320404.520000011</v>
+        <v>9882393.5200000107</v>
       </c>
       <c r="V12" s="158">
         <f t="shared" si="3"/>
-        <v>-11712617</v>
+        <v>-438011</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.45">
@@ -28077,26 +28077,26 @@
         <v>93597302</v>
       </c>
       <c r="J13" s="174">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K13" s="174">
-        <v>271500</v>
+        <v>460500</v>
       </c>
       <c r="L13" s="174">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M13" s="174">
-        <v>85350859</v>
+        <v>85539859</v>
       </c>
       <c r="N13" s="175">
-        <v>89.62</v>
+        <v>89.8</v>
       </c>
       <c r="O13" s="175">
-        <v>91.19</v>
+        <v>91.39</v>
       </c>
       <c r="P13" s="118">
         <f t="shared" si="0"/>
-        <v>5438523.9399999976</v>
+        <v>5249523.9399999976</v>
       </c>
       <c r="R13" s="156" t="s">
         <v>107</v>
@@ -28106,32 +28106,32 @@
         <v>180440547</v>
       </c>
       <c r="T13" s="158">
-        <v>22900135.590000004</v>
+        <v>12207250.590000004</v>
       </c>
       <c r="U13" s="172">
         <f t="shared" si="2"/>
-        <v>12207250.590000004</v>
+        <v>11847250.590000004</v>
       </c>
       <c r="V13" s="158">
         <f t="shared" si="3"/>
-        <v>-10692885</v>
+        <v>-360000</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A14" s="176" t="s">
-        <v>179</v>
+        <v>129</v>
       </c>
       <c r="B14" s="176" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="C14" s="176" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="D14" s="177">
-        <v>356</v>
+        <v>1181</v>
       </c>
       <c r="E14" s="177">
-        <v>53605661</v>
+        <v>189656153</v>
       </c>
       <c r="F14" s="177">
         <v>0</v>
@@ -28140,32 +28140,32 @@
         <v>0</v>
       </c>
       <c r="H14" s="177">
-        <v>356</v>
+        <v>1181</v>
       </c>
       <c r="I14" s="177">
-        <v>53605661</v>
+        <v>189656153</v>
       </c>
       <c r="J14" s="177">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K14" s="177">
-        <v>0</v>
+        <v>2889271</v>
       </c>
       <c r="L14" s="177">
-        <v>307</v>
+        <v>1056</v>
       </c>
       <c r="M14" s="177">
-        <v>48663936</v>
+        <v>173218080</v>
       </c>
       <c r="N14" s="178">
-        <v>86.24</v>
+        <v>89.42</v>
       </c>
       <c r="O14" s="178">
-        <v>90.78</v>
+        <v>91.33</v>
       </c>
       <c r="P14" s="118">
         <f t="shared" si="0"/>
-        <v>3333555.1700000018</v>
+        <v>10748388.409999996</v>
       </c>
       <c r="R14" s="157" t="s">
         <v>72</v>
@@ -28175,32 +28175,32 @@
         <v>162344260</v>
       </c>
       <c r="T14" s="158">
-        <v>30539293.199999988</v>
+        <v>17074222.199999988</v>
       </c>
       <c r="U14" s="172">
         <f t="shared" si="2"/>
-        <v>17074222.199999988</v>
+        <v>16644698.199999988</v>
       </c>
       <c r="V14" s="158">
         <f t="shared" si="3"/>
-        <v>-13465071</v>
+        <v>-429524</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A15" s="173" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B15" s="173" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="C15" s="173" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="D15" s="174">
-        <v>588</v>
+        <v>876</v>
       </c>
       <c r="E15" s="174">
-        <v>95369711</v>
+        <v>145101823</v>
       </c>
       <c r="F15" s="174">
         <v>0</v>
@@ -28209,32 +28209,32 @@
         <v>0</v>
       </c>
       <c r="H15" s="174">
-        <v>588</v>
+        <v>876</v>
       </c>
       <c r="I15" s="174">
-        <v>95369711</v>
+        <v>145101823</v>
       </c>
       <c r="J15" s="174">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K15" s="174">
-        <v>228334</v>
+        <v>1231251</v>
       </c>
       <c r="L15" s="174">
-        <v>526</v>
+        <v>791</v>
       </c>
       <c r="M15" s="174">
-        <v>86428817</v>
+        <v>132382662</v>
       </c>
       <c r="N15" s="175">
-        <v>89.46</v>
+        <v>90.3</v>
       </c>
       <c r="O15" s="175">
-        <v>90.63</v>
+        <v>91.23</v>
       </c>
       <c r="P15" s="118">
         <f t="shared" si="0"/>
-        <v>6079802.6700000018</v>
+        <v>8366106.3100000024</v>
       </c>
       <c r="R15" s="157" t="s">
         <v>113</v>
@@ -28244,15 +28244,15 @@
         <v>194517020</v>
       </c>
       <c r="T15" s="158">
-        <v>46118158.400000006</v>
+        <v>21748143.400000006</v>
       </c>
       <c r="U15" s="172">
         <f t="shared" si="2"/>
-        <v>21748143.400000006</v>
+        <v>20212240.400000006</v>
       </c>
       <c r="V15" s="158">
         <f t="shared" si="3"/>
-        <v>-24370015</v>
+        <v>-1535903</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.45">
@@ -28260,16 +28260,16 @@
         <v>129</v>
       </c>
       <c r="B16" s="176" t="s">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="C16" s="176" t="s">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="D16" s="177">
-        <v>1181</v>
+        <v>588</v>
       </c>
       <c r="E16" s="177">
-        <v>189656153</v>
+        <v>95369711</v>
       </c>
       <c r="F16" s="177">
         <v>0</v>
@@ -28278,32 +28278,32 @@
         <v>0</v>
       </c>
       <c r="H16" s="177">
-        <v>1181</v>
+        <v>588</v>
       </c>
       <c r="I16" s="177">
-        <v>189656153</v>
+        <v>95369711</v>
       </c>
       <c r="J16" s="177">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K16" s="177">
-        <v>1535646</v>
+        <v>613334</v>
       </c>
       <c r="L16" s="177">
-        <v>1047</v>
+        <v>528</v>
       </c>
       <c r="M16" s="177">
-        <v>171864455</v>
+        <v>86813817</v>
       </c>
       <c r="N16" s="178">
-        <v>88.65</v>
+        <v>89.8</v>
       </c>
       <c r="O16" s="178">
-        <v>90.62</v>
+        <v>91.03</v>
       </c>
       <c r="P16" s="118">
         <f t="shared" si="0"/>
-        <v>12102013.409999996</v>
+        <v>5694802.6700000018</v>
       </c>
       <c r="R16" s="157" t="s">
         <v>119</v>
@@ -28313,15 +28313,15 @@
         <v>189656153</v>
       </c>
       <c r="T16" s="158">
-        <v>29992114.409999996</v>
+        <v>12102013.409999996</v>
       </c>
       <c r="U16" s="172">
         <f t="shared" si="2"/>
-        <v>12102013.409999996</v>
+        <v>10748388.409999996</v>
       </c>
       <c r="V16" s="158">
         <f t="shared" si="3"/>
-        <v>-17890101</v>
+        <v>-1353625</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.45">
@@ -28329,16 +28329,16 @@
         <v>179</v>
       </c>
       <c r="B17" s="173" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="C17" s="173" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="D17" s="174">
-        <v>716</v>
+        <v>356</v>
       </c>
       <c r="E17" s="174">
-        <v>116427734</v>
+        <v>53605661</v>
       </c>
       <c r="F17" s="174">
         <v>0</v>
@@ -28347,32 +28347,32 @@
         <v>0</v>
       </c>
       <c r="H17" s="174">
-        <v>716</v>
+        <v>356</v>
       </c>
       <c r="I17" s="174">
-        <v>116427734</v>
+        <v>53605661</v>
       </c>
       <c r="J17" s="174">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" s="174">
-        <v>239000</v>
+        <v>0</v>
       </c>
       <c r="L17" s="174">
-        <v>637</v>
+        <v>307</v>
       </c>
       <c r="M17" s="174">
-        <v>105365939</v>
+        <v>48663936</v>
       </c>
       <c r="N17" s="175">
-        <v>88.97</v>
+        <v>86.24</v>
       </c>
       <c r="O17" s="175">
-        <v>90.5</v>
+        <v>90.78</v>
       </c>
       <c r="P17" s="118">
         <f t="shared" si="0"/>
-        <v>7568962.9800000042</v>
+        <v>3333555.1700000018</v>
       </c>
       <c r="R17" s="156" t="s">
         <v>84</v>
@@ -28382,32 +28382,32 @@
         <v>95369711</v>
       </c>
       <c r="T17" s="158">
-        <v>17311017.670000002</v>
+        <v>6079802.6700000018</v>
       </c>
       <c r="U17" s="172">
         <f t="shared" si="2"/>
-        <v>6079802.6700000018</v>
+        <v>5694802.6700000018</v>
       </c>
       <c r="V17" s="158">
         <f t="shared" si="3"/>
-        <v>-11231215</v>
+        <v>-385000</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A18" s="176" t="s">
-        <v>128</v>
+        <v>179</v>
       </c>
       <c r="B18" s="176" t="s">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="C18" s="176" t="s">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="D18" s="177">
-        <v>876</v>
+        <v>716</v>
       </c>
       <c r="E18" s="177">
-        <v>145101823</v>
+        <v>116427734</v>
       </c>
       <c r="F18" s="177">
         <v>0</v>
@@ -28416,32 +28416,32 @@
         <v>0</v>
       </c>
       <c r="H18" s="177">
-        <v>876</v>
+        <v>716</v>
       </c>
       <c r="I18" s="177">
-        <v>145101823</v>
+        <v>116427734</v>
       </c>
       <c r="J18" s="177">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K18" s="177">
-        <v>0</v>
+        <v>521903</v>
       </c>
       <c r="L18" s="177">
-        <v>785</v>
+        <v>639</v>
       </c>
       <c r="M18" s="177">
-        <v>131151411</v>
+        <v>105648842</v>
       </c>
       <c r="N18" s="178">
-        <v>89.61</v>
+        <v>89.25</v>
       </c>
       <c r="O18" s="178">
-        <v>90.39</v>
+        <v>90.74</v>
       </c>
       <c r="P18" s="118">
         <f t="shared" si="0"/>
-        <v>9597357.3100000024</v>
+        <v>7286059.9800000042</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.45">
@@ -28473,26 +28473,26 @@
         <v>152862316</v>
       </c>
       <c r="J19" s="174">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K19" s="174">
-        <v>0</v>
+        <v>438011</v>
       </c>
       <c r="L19" s="174">
-        <v>816</v>
+        <v>822</v>
       </c>
       <c r="M19" s="174">
-        <v>137956042</v>
+        <v>138394053</v>
       </c>
       <c r="N19" s="175">
-        <v>86.72</v>
+        <v>87.35</v>
       </c>
       <c r="O19" s="175">
-        <v>90.25</v>
+        <v>90.54</v>
       </c>
       <c r="P19" s="118">
         <f t="shared" si="0"/>
-        <v>10320404.520000011</v>
+        <v>9882393.5200000107</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.45">
@@ -28524,26 +28524,26 @@
         <v>180440547</v>
       </c>
       <c r="J20" s="177">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K20" s="177">
-        <v>455000</v>
+        <v>815000</v>
       </c>
       <c r="L20" s="177">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="M20" s="177">
-        <v>162820080</v>
+        <v>163180080</v>
       </c>
       <c r="N20" s="178">
-        <v>88.65</v>
+        <v>88.84</v>
       </c>
       <c r="O20" s="178">
-        <v>90.23</v>
+        <v>90.43</v>
       </c>
       <c r="P20" s="118">
         <f t="shared" si="0"/>
-        <v>12207250.590000004</v>
+        <v>11847250.590000004</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.45">
@@ -28626,43 +28626,43 @@
         <v>101866340</v>
       </c>
       <c r="J22" s="177">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K22" s="177">
-        <v>0</v>
+        <v>409000</v>
       </c>
       <c r="L22" s="177">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="M22" s="177">
-        <v>90979734</v>
+        <v>91388734</v>
       </c>
       <c r="N22" s="178">
-        <v>85.67</v>
+        <v>85.98</v>
       </c>
       <c r="O22" s="178">
-        <v>89.31</v>
+        <v>89.71</v>
       </c>
       <c r="P22" s="118">
         <f t="shared" si="0"/>
-        <v>7830615.799999997</v>
+        <v>7421615.799999997</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A23" s="173" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B23" s="173" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="C23" s="173" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="D23" s="174">
-        <v>683</v>
+        <v>892</v>
       </c>
       <c r="E23" s="174">
-        <v>105983346</v>
+        <v>149379338</v>
       </c>
       <c r="F23" s="174">
         <v>0</v>
@@ -28671,49 +28671,49 @@
         <v>0</v>
       </c>
       <c r="H23" s="174">
-        <v>683</v>
+        <v>892</v>
       </c>
       <c r="I23" s="174">
-        <v>105983346</v>
+        <v>149379338</v>
       </c>
       <c r="J23" s="174">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="K23" s="174">
-        <v>230000</v>
+        <v>4044935</v>
       </c>
       <c r="L23" s="174">
-        <v>594</v>
+        <v>799</v>
       </c>
       <c r="M23" s="174">
-        <v>93101148</v>
+        <v>132944383</v>
       </c>
       <c r="N23" s="175">
-        <v>86.97</v>
+        <v>89.57</v>
       </c>
       <c r="O23" s="175">
-        <v>87.85</v>
+        <v>89</v>
       </c>
       <c r="P23" s="118">
         <f t="shared" si="0"/>
-        <v>9702697.6199999899</v>
+        <v>11953574.859999985</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A24" s="176" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B24" s="176" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="C24" s="176" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="D24" s="177">
-        <v>892</v>
+        <v>683</v>
       </c>
       <c r="E24" s="177">
-        <v>149379338</v>
+        <v>105983346</v>
       </c>
       <c r="F24" s="177">
         <v>0</v>
@@ -28722,49 +28722,49 @@
         <v>0</v>
       </c>
       <c r="H24" s="177">
-        <v>892</v>
+        <v>683</v>
       </c>
       <c r="I24" s="177">
-        <v>149379338</v>
+        <v>105983346</v>
       </c>
       <c r="J24" s="177">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K24" s="177">
-        <v>669689</v>
+        <v>639000</v>
       </c>
       <c r="L24" s="177">
-        <v>780</v>
+        <v>596</v>
       </c>
       <c r="M24" s="177">
-        <v>129569137</v>
+        <v>93510148</v>
       </c>
       <c r="N24" s="178">
-        <v>87.44</v>
+        <v>87.26</v>
       </c>
       <c r="O24" s="178">
-        <v>86.74</v>
+        <v>88.23</v>
       </c>
       <c r="P24" s="118">
         <f t="shared" si="0"/>
-        <v>15328820.859999985</v>
+        <v>9293697.6199999899</v>
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A25" s="173" t="s">
-        <v>129</v>
+        <v>179</v>
       </c>
       <c r="B25" s="173" t="s">
-        <v>71</v>
+        <v>120</v>
       </c>
       <c r="C25" s="173" t="s">
-        <v>72</v>
+        <v>121</v>
       </c>
       <c r="D25" s="174">
-        <v>968</v>
+        <v>415</v>
       </c>
       <c r="E25" s="174">
-        <v>162344260</v>
+        <v>66800107</v>
       </c>
       <c r="F25" s="174">
         <v>0</v>
@@ -28773,32 +28773,32 @@
         <v>0</v>
       </c>
       <c r="H25" s="174">
-        <v>968</v>
+        <v>415</v>
       </c>
       <c r="I25" s="174">
-        <v>162344260</v>
+        <v>66800107</v>
       </c>
       <c r="J25" s="174">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K25" s="174">
-        <v>185000</v>
+        <v>1049194</v>
       </c>
       <c r="L25" s="174">
-        <v>835</v>
+        <v>351</v>
       </c>
       <c r="M25" s="174">
-        <v>140399710</v>
+        <v>57966491</v>
       </c>
       <c r="N25" s="175">
-        <v>86.26</v>
+        <v>84.58</v>
       </c>
       <c r="O25" s="175">
-        <v>86.48</v>
+        <v>86.78</v>
       </c>
       <c r="P25" s="118">
         <f t="shared" si="0"/>
-        <v>17074222.199999988</v>
+        <v>6829612.7899999991</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.45">
@@ -28806,16 +28806,16 @@
         <v>129</v>
       </c>
       <c r="B26" s="176" t="s">
-        <v>112</v>
+        <v>71</v>
       </c>
       <c r="C26" s="176" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
       <c r="D26" s="177">
-        <v>1198</v>
+        <v>968</v>
       </c>
       <c r="E26" s="177">
-        <v>194517020</v>
+        <v>162344260</v>
       </c>
       <c r="F26" s="177">
         <v>0</v>
@@ -28824,49 +28824,49 @@
         <v>0</v>
       </c>
       <c r="H26" s="177">
-        <v>1198</v>
+        <v>968</v>
       </c>
       <c r="I26" s="177">
-        <v>194517020</v>
+        <v>162344260</v>
       </c>
       <c r="J26" s="177">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K26" s="177">
-        <v>789000</v>
+        <v>614524</v>
       </c>
       <c r="L26" s="177">
-        <v>996</v>
+        <v>839</v>
       </c>
       <c r="M26" s="177">
-        <v>166933366</v>
+        <v>140829234</v>
       </c>
       <c r="N26" s="178">
-        <v>83.14</v>
+        <v>86.67</v>
       </c>
       <c r="O26" s="178">
-        <v>85.82</v>
+        <v>86.75</v>
       </c>
       <c r="P26" s="118">
         <f t="shared" si="0"/>
-        <v>21748143.400000006</v>
+        <v>16644698.199999988</v>
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A27" s="173" t="s">
-        <v>179</v>
+        <v>129</v>
       </c>
       <c r="B27" s="173" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C27" s="173" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="D27" s="174">
-        <v>415</v>
+        <v>1198</v>
       </c>
       <c r="E27" s="174">
-        <v>66800107</v>
+        <v>194517020</v>
       </c>
       <c r="F27" s="174">
         <v>0</v>
@@ -28875,32 +28875,32 @@
         <v>0</v>
       </c>
       <c r="H27" s="174">
-        <v>415</v>
+        <v>1198</v>
       </c>
       <c r="I27" s="174">
-        <v>66800107</v>
+        <v>194517020</v>
       </c>
       <c r="J27" s="174">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K27" s="174">
-        <v>0</v>
+        <v>2324903</v>
       </c>
       <c r="L27" s="174">
-        <v>346</v>
+        <v>1004</v>
       </c>
       <c r="M27" s="174">
-        <v>56917297</v>
+        <v>168469269</v>
       </c>
       <c r="N27" s="175">
-        <v>83.37</v>
+        <v>83.81</v>
       </c>
       <c r="O27" s="175">
-        <v>85.21</v>
+        <v>86.61</v>
       </c>
       <c r="P27" s="118">
         <f t="shared" si="0"/>
-        <v>7878806.7899999991</v>
+        <v>20212240.400000006</v>
       </c>
     </row>
   </sheetData>

--- a/filetiendo.xlsx
+++ b/filetiendo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\viettel 2026\thang 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76652FA4-DBD6-4CB1-9D46-097B1F5DFF0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ADF4A03-B967-441D-869A-8B611639EDA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="808" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="808" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TH NV" sheetId="2" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="265">
   <si>
     <t>STT</t>
   </si>
@@ -840,6 +840,15 @@
   <si>
     <t>Cước cần thu</t>
   </si>
+  <si>
+    <t>CNKD_LDG_VIDNT</t>
+  </si>
+  <si>
+    <t>CNKD_Đoàn Nguyễn Tường Vi</t>
+  </si>
+  <si>
+    <t/>
+  </si>
 </sst>
 </file>
 
@@ -4189,41 +4198,17 @@
     <xf numFmtId="0" fontId="65" fillId="0" borderId="94" xfId="11" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="94" xfId="11" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="162" xfId="11" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="49" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="120" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="119" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="118" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="49" fillId="5" borderId="112" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="5" borderId="115" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="113" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="125" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="124" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="123" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="5" borderId="112" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="24" borderId="117" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4237,10 +4222,34 @@
     <xf numFmtId="0" fontId="17" fillId="5" borderId="114" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="120" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="119" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="118" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="35" fillId="16" borderId="121" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="2" borderId="122" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="125" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="124" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="123" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="66" fillId="18" borderId="150" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4312,16 +4321,16 @@
     <xf numFmtId="0" fontId="62" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="46" fillId="5" borderId="137" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="5" borderId="136" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="133" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="132" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="5" borderId="137" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="5" borderId="136" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="50" fillId="5" borderId="135" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4341,6 +4350,12 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="140" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="143" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="142" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="144" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4366,10 +4381,10 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="149" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="143" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="68" fillId="29" borderId="150" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="142" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="68" fillId="29" borderId="150" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4394,12 +4409,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="153" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="68" fillId="29" borderId="150" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="29" borderId="150" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="12">
     <cellStyle name="Comma" xfId="8" builtinId="3"/>
@@ -5289,166 +5298,166 @@
       </c>
     </row>
     <row r="2" spans="1:675" ht="23.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="193" t="s">
+      <c r="A2" s="183" t="s">
         <v>34</v>
       </c>
       <c r="B2" s="69"/>
       <c r="C2" s="15"/>
-      <c r="D2" s="199" t="s">
+      <c r="D2" s="194" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="199"/>
-      <c r="F2" s="199"/>
-      <c r="G2" s="199"/>
-      <c r="H2" s="199"/>
-      <c r="I2" s="199"/>
-      <c r="J2" s="199"/>
-      <c r="K2" s="199"/>
-      <c r="L2" s="199"/>
-      <c r="M2" s="199"/>
-      <c r="N2" s="199"/>
-      <c r="O2" s="199"/>
-      <c r="P2" s="199"/>
-      <c r="Q2" s="199"/>
-      <c r="R2" s="199"/>
-      <c r="S2" s="199"/>
-      <c r="T2" s="197" t="s">
+      <c r="E2" s="194"/>
+      <c r="F2" s="194"/>
+      <c r="G2" s="194"/>
+      <c r="H2" s="194"/>
+      <c r="I2" s="194"/>
+      <c r="J2" s="194"/>
+      <c r="K2" s="194"/>
+      <c r="L2" s="194"/>
+      <c r="M2" s="194"/>
+      <c r="N2" s="194"/>
+      <c r="O2" s="194"/>
+      <c r="P2" s="194"/>
+      <c r="Q2" s="194"/>
+      <c r="R2" s="194"/>
+      <c r="S2" s="194"/>
+      <c r="T2" s="189" t="s">
         <v>36</v>
       </c>
-      <c r="U2" s="197"/>
-      <c r="V2" s="197"/>
-      <c r="W2" s="197"/>
-      <c r="X2" s="197"/>
-      <c r="Y2" s="197"/>
-      <c r="Z2" s="197"/>
-      <c r="AA2" s="197"/>
-      <c r="AB2" s="197"/>
-      <c r="AC2" s="197"/>
-      <c r="AD2" s="197"/>
-      <c r="AE2" s="197"/>
-      <c r="AF2" s="197"/>
-      <c r="AG2" s="197"/>
-      <c r="AH2" s="197"/>
-      <c r="AI2" s="197"/>
-      <c r="AJ2" s="196" t="s">
+      <c r="U2" s="189"/>
+      <c r="V2" s="189"/>
+      <c r="W2" s="189"/>
+      <c r="X2" s="189"/>
+      <c r="Y2" s="189"/>
+      <c r="Z2" s="189"/>
+      <c r="AA2" s="189"/>
+      <c r="AB2" s="189"/>
+      <c r="AC2" s="189"/>
+      <c r="AD2" s="189"/>
+      <c r="AE2" s="189"/>
+      <c r="AF2" s="189"/>
+      <c r="AG2" s="189"/>
+      <c r="AH2" s="189"/>
+      <c r="AI2" s="189"/>
+      <c r="AJ2" s="188" t="s">
         <v>37</v>
       </c>
-      <c r="AK2" s="196"/>
-      <c r="AL2" s="196"/>
-      <c r="AM2" s="196"/>
-      <c r="AN2" s="196"/>
-      <c r="AO2" s="196"/>
-      <c r="AP2" s="196"/>
-      <c r="AQ2" s="196"/>
-      <c r="AR2" s="196"/>
-      <c r="AS2" s="196"/>
-      <c r="AT2" s="196"/>
-      <c r="AU2" s="196"/>
-      <c r="AV2" s="195" t="s">
+      <c r="AK2" s="188"/>
+      <c r="AL2" s="188"/>
+      <c r="AM2" s="188"/>
+      <c r="AN2" s="188"/>
+      <c r="AO2" s="188"/>
+      <c r="AP2" s="188"/>
+      <c r="AQ2" s="188"/>
+      <c r="AR2" s="188"/>
+      <c r="AS2" s="188"/>
+      <c r="AT2" s="188"/>
+      <c r="AU2" s="188"/>
+      <c r="AV2" s="187" t="s">
         <v>38</v>
       </c>
-      <c r="AW2" s="195"/>
-      <c r="AX2" s="195"/>
-      <c r="AY2" s="195"/>
-      <c r="AZ2" s="195"/>
-      <c r="BA2" s="195"/>
-      <c r="BB2" s="195"/>
-      <c r="BC2" s="195"/>
-      <c r="BD2" s="195"/>
-      <c r="BE2" s="195"/>
-      <c r="BF2" s="195"/>
-      <c r="BG2" s="195"/>
+      <c r="AW2" s="187"/>
+      <c r="AX2" s="187"/>
+      <c r="AY2" s="187"/>
+      <c r="AZ2" s="187"/>
+      <c r="BA2" s="187"/>
+      <c r="BB2" s="187"/>
+      <c r="BC2" s="187"/>
+      <c r="BD2" s="187"/>
+      <c r="BE2" s="187"/>
+      <c r="BF2" s="187"/>
+      <c r="BG2" s="187"/>
     </row>
     <row r="3" spans="1:675" s="3" customFormat="1" ht="28.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="193"/>
-      <c r="B3" s="200" t="s">
+      <c r="A3" s="183"/>
+      <c r="B3" s="195" t="s">
         <v>39</v>
       </c>
       <c r="C3" s="70"/>
-      <c r="D3" s="187" t="s">
+      <c r="D3" s="185" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="188"/>
-      <c r="F3" s="188"/>
-      <c r="G3" s="188"/>
-      <c r="H3" s="187" t="s">
+      <c r="E3" s="186"/>
+      <c r="F3" s="186"/>
+      <c r="G3" s="186"/>
+      <c r="H3" s="185" t="s">
         <v>40</v>
       </c>
-      <c r="I3" s="188"/>
-      <c r="J3" s="188"/>
-      <c r="K3" s="188"/>
-      <c r="L3" s="187" t="s">
+      <c r="I3" s="186"/>
+      <c r="J3" s="186"/>
+      <c r="K3" s="186"/>
+      <c r="L3" s="185" t="s">
         <v>41</v>
       </c>
-      <c r="M3" s="188"/>
-      <c r="N3" s="188"/>
-      <c r="O3" s="188"/>
-      <c r="P3" s="190" t="s">
+      <c r="M3" s="186"/>
+      <c r="N3" s="186"/>
+      <c r="O3" s="186"/>
+      <c r="P3" s="198" t="s">
         <v>42</v>
       </c>
-      <c r="Q3" s="191"/>
-      <c r="R3" s="191"/>
-      <c r="S3" s="192"/>
-      <c r="T3" s="187" t="s">
+      <c r="Q3" s="199"/>
+      <c r="R3" s="199"/>
+      <c r="S3" s="200"/>
+      <c r="T3" s="185" t="s">
         <v>43</v>
       </c>
-      <c r="U3" s="188"/>
-      <c r="V3" s="188"/>
-      <c r="W3" s="188"/>
-      <c r="X3" s="187" t="s">
+      <c r="U3" s="186"/>
+      <c r="V3" s="186"/>
+      <c r="W3" s="186"/>
+      <c r="X3" s="185" t="s">
         <v>45</v>
       </c>
-      <c r="Y3" s="188"/>
-      <c r="Z3" s="188"/>
-      <c r="AA3" s="188"/>
-      <c r="AB3" s="187" t="s">
+      <c r="Y3" s="186"/>
+      <c r="Z3" s="186"/>
+      <c r="AA3" s="186"/>
+      <c r="AB3" s="185" t="s">
         <v>47</v>
       </c>
-      <c r="AC3" s="188"/>
-      <c r="AD3" s="188"/>
-      <c r="AE3" s="188"/>
-      <c r="AF3" s="187" t="s">
+      <c r="AC3" s="186"/>
+      <c r="AD3" s="186"/>
+      <c r="AE3" s="186"/>
+      <c r="AF3" s="185" t="s">
         <v>48</v>
       </c>
-      <c r="AG3" s="188"/>
-      <c r="AH3" s="188"/>
-      <c r="AI3" s="188"/>
-      <c r="AJ3" s="184" t="s">
+      <c r="AG3" s="186"/>
+      <c r="AH3" s="186"/>
+      <c r="AI3" s="186"/>
+      <c r="AJ3" s="191" t="s">
         <v>51</v>
       </c>
-      <c r="AK3" s="185"/>
-      <c r="AL3" s="185"/>
-      <c r="AM3" s="186"/>
-      <c r="AN3" s="184" t="s">
+      <c r="AK3" s="192"/>
+      <c r="AL3" s="192"/>
+      <c r="AM3" s="193"/>
+      <c r="AN3" s="191" t="s">
         <v>14</v>
       </c>
-      <c r="AO3" s="185"/>
-      <c r="AP3" s="185"/>
-      <c r="AQ3" s="186"/>
-      <c r="AR3" s="184" t="s">
+      <c r="AO3" s="192"/>
+      <c r="AP3" s="192"/>
+      <c r="AQ3" s="193"/>
+      <c r="AR3" s="191" t="s">
         <v>52</v>
       </c>
-      <c r="AS3" s="185"/>
-      <c r="AT3" s="185"/>
-      <c r="AU3" s="186"/>
-      <c r="AV3" s="188" t="s">
+      <c r="AS3" s="192"/>
+      <c r="AT3" s="192"/>
+      <c r="AU3" s="193"/>
+      <c r="AV3" s="186" t="s">
         <v>16</v>
       </c>
-      <c r="AW3" s="188"/>
-      <c r="AX3" s="188"/>
-      <c r="AY3" s="188"/>
-      <c r="AZ3" s="188" t="s">
+      <c r="AW3" s="186"/>
+      <c r="AX3" s="186"/>
+      <c r="AY3" s="186"/>
+      <c r="AZ3" s="186" t="s">
         <v>54</v>
       </c>
-      <c r="BA3" s="188"/>
-      <c r="BB3" s="188"/>
-      <c r="BC3" s="188"/>
-      <c r="BD3" s="187" t="s">
+      <c r="BA3" s="186"/>
+      <c r="BB3" s="186"/>
+      <c r="BC3" s="186"/>
+      <c r="BD3" s="185" t="s">
         <v>55</v>
       </c>
-      <c r="BE3" s="188"/>
-      <c r="BF3" s="198"/>
-      <c r="BG3" s="188"/>
+      <c r="BE3" s="186"/>
+      <c r="BF3" s="190"/>
+      <c r="BG3" s="186"/>
       <c r="BH3" s="2"/>
       <c r="BI3" s="2"/>
       <c r="BJ3" s="2"/>
@@ -6067,8 +6076,8 @@
       <c r="YY3" s="2"/>
     </row>
     <row r="4" spans="1:675" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="194"/>
-      <c r="B4" s="200"/>
+      <c r="A4" s="184"/>
+      <c r="B4" s="195"/>
       <c r="C4" s="71"/>
       <c r="D4" s="8" t="s">
         <v>2</v>
@@ -6631,15 +6640,15 @@
       </c>
       <c r="AO6" s="13">
         <f>VLOOKUP(C6,GBOC!$E$7:$DG$29,$B$29,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP6" s="14">
         <f t="shared" si="18"/>
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AQ6" s="61">
         <f t="shared" si="19"/>
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AR6" s="33">
         <v>0.97</v>
@@ -6769,15 +6778,15 @@
       </c>
       <c r="Q7" s="58">
         <f>VLOOKUP(C7,GBOC!$E$7:$DG$29,$B$23,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R7" s="14">
         <f t="shared" si="6"/>
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="S7" s="46">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" s="52">
         <f>VLOOKUP(C7,'Giao CT'!$D$6:$S$20,7,0)</f>
@@ -6801,15 +6810,15 @@
       </c>
       <c r="Y7" s="13">
         <f>VLOOKUP(C7,GBOC!$E$7:$DG$29,$B$25,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z7" s="14">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA7" s="46">
         <f t="shared" si="11"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AB7" s="51">
         <f>VLOOKUP(C7,'Giao CT'!$D$6:$S$20,9,0)</f>
@@ -6817,15 +6826,15 @@
       </c>
       <c r="AC7" s="13">
         <f>VLOOKUP(C7,GBOC!$E$7:$DG$29,$B$26,0)</f>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AD7" s="14">
         <f t="shared" si="12"/>
-        <v>0.9</v>
+        <v>0.96666666666666667</v>
       </c>
       <c r="AE7" s="46">
         <f t="shared" si="13"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF7" s="51">
         <f>VLOOKUP(C7,'Giao CT'!$D$6:$S$20,10,0)</f>
@@ -6864,15 +6873,15 @@
       </c>
       <c r="AO7" s="13">
         <f>VLOOKUP(C7,GBOC!$E$7:$DG$29,$B$29,0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP7" s="14">
         <f t="shared" si="18"/>
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AQ7" s="61">
         <f t="shared" si="19"/>
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AR7" s="33">
         <v>0.97</v>
@@ -7219,15 +7228,15 @@
       </c>
       <c r="M9" s="58">
         <f>VLOOKUP(C9,GBOC!$E$7:$DG$29,$B$22,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N9" s="14">
         <f t="shared" si="4"/>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="O9" s="46">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P9" s="52">
         <f>VLOOKUP(C9,'Giao CT'!$D$6:$S$20,6,0)</f>
@@ -7267,15 +7276,15 @@
       </c>
       <c r="Y9" s="13">
         <f>VLOOKUP(C9,GBOC!$E$7:$DG$29,$B$25,0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z9" s="14">
         <f t="shared" si="10"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA9" s="46">
         <f t="shared" si="11"/>
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="AB9" s="51">
         <f>VLOOKUP(C9,'Giao CT'!$D$6:$S$20,9,0)</f>
@@ -7330,15 +7339,15 @@
       </c>
       <c r="AO9" s="13">
         <f>VLOOKUP(C9,GBOC!$E$7:$DG$29,$B$29,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP9" s="14">
         <f t="shared" si="18"/>
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AQ9" s="61">
         <f t="shared" si="19"/>
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AR9" s="33">
         <v>0.97</v>
@@ -7452,15 +7461,15 @@
       </c>
       <c r="M10" s="58">
         <f>VLOOKUP(C10,GBOC!$E$7:$DG$29,$B$22,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N10" s="14">
         <f t="shared" si="4"/>
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="O10" s="46">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P10" s="52">
         <f>VLOOKUP(C10,'Giao CT'!$D$6:$S$20,6,0)</f>
@@ -7484,15 +7493,15 @@
       </c>
       <c r="U10" s="13">
         <f>VLOOKUP(C10,GBOC!$E$7:$DG$29,$B$24,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V10" s="14">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="W10" s="44">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="X10" s="12">
         <f>VLOOKUP(C10,'Giao CT'!$D$6:$S$20,8,0)</f>
@@ -7563,15 +7572,15 @@
       </c>
       <c r="AO10" s="13">
         <f>VLOOKUP(C10,GBOC!$E$7:$DG$29,$B$29,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP10" s="14">
         <f t="shared" si="18"/>
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ10" s="61">
         <f t="shared" si="19"/>
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AR10" s="33">
         <v>0.97</v>
@@ -7717,15 +7726,15 @@
       </c>
       <c r="U11" s="13">
         <f>VLOOKUP(C11,GBOC!$E$7:$DG$29,$B$24,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V11" s="14">
         <f t="shared" si="8"/>
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="W11" s="44">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X11" s="12">
         <f>VLOOKUP(C11,'Giao CT'!$D$6:$S$20,8,0)</f>
@@ -7749,15 +7758,15 @@
       </c>
       <c r="AC11" s="13">
         <f>VLOOKUP(C11,GBOC!$E$7:$DG$29,$B$26,0)</f>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AD11" s="14">
         <f t="shared" si="12"/>
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE11" s="46">
         <f t="shared" si="13"/>
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="AF11" s="51">
         <f>VLOOKUP(C11,'Giao CT'!$D$6:$S$20,10,0)</f>
@@ -7843,15 +7852,15 @@
       </c>
       <c r="BA11" s="13">
         <f>VLOOKUP(C11,GBOC!$E$7:$DG$29,$B$32,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB11" s="104">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC11" s="48">
         <f t="shared" si="25"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD11" s="51">
         <f>VLOOKUP(C11,'Giao CT'!$D$6:$S$20,16,0)</f>
@@ -8029,15 +8038,15 @@
       </c>
       <c r="AO12" s="13">
         <f>VLOOKUP(C12,GBOC!$E$7:$DG$29,$B$29,0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AP12" s="14">
         <f t="shared" si="18"/>
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AQ12" s="61">
         <f t="shared" si="19"/>
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AR12" s="33">
         <v>0.97</v>
@@ -8199,15 +8208,15 @@
       </c>
       <c r="Y13" s="13">
         <f>VLOOKUP(C13,GBOC!$E$7:$DG$29,$B$25,0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z13" s="14">
         <f t="shared" si="10"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA13" s="46">
         <f t="shared" si="11"/>
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="AB13" s="51">
         <f>VLOOKUP(C13,'Giao CT'!$D$6:$S$20,9,0)</f>
@@ -8262,15 +8271,15 @@
       </c>
       <c r="AO13" s="13">
         <f>VLOOKUP(C13,GBOC!$E$7:$DG$29,$B$29,0)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AP13" s="14">
         <f t="shared" si="18"/>
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AQ13" s="61">
         <f t="shared" si="19"/>
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AR13" s="33">
         <v>0.97</v>
@@ -8464,15 +8473,15 @@
       </c>
       <c r="AG14" s="13">
         <f>VLOOKUP(C14,GBOC!$E$7:$DG$29,$B$27,0)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AH14" s="14">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1.1111111111111112</v>
       </c>
       <c r="AI14" s="46">
         <f t="shared" si="15"/>
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="AJ14" s="51">
         <f>VLOOKUP(C14,'Giao CT'!$D$6:$S$20,11,0)</f>
@@ -8495,15 +8504,15 @@
       </c>
       <c r="AO14" s="13">
         <f>VLOOKUP(C14,GBOC!$E$7:$DG$29,$B$29,0)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AP14" s="14">
         <f t="shared" si="18"/>
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="AQ14" s="61">
         <f t="shared" si="19"/>
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="AR14" s="33">
         <v>0.97</v>
@@ -8633,15 +8642,15 @@
       </c>
       <c r="Q15" s="58">
         <f>VLOOKUP(C15,GBOC!$E$7:$DG$29,$B$23,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R15" s="14">
         <f t="shared" si="6"/>
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="S15" s="46">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T15" s="52">
         <f>VLOOKUP(C15,'Giao CT'!$D$6:$S$20,7,0)</f>
@@ -8728,15 +8737,15 @@
       </c>
       <c r="AO15" s="13">
         <f>VLOOKUP(C15,GBOC!$E$7:$DG$29,$B$29,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP15" s="14">
         <f t="shared" si="18"/>
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ15" s="61">
         <f t="shared" si="19"/>
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AR15" s="33">
         <v>0.97</v>
@@ -8775,15 +8784,15 @@
       </c>
       <c r="BA15" s="13">
         <f>VLOOKUP(C15,GBOC!$E$7:$DG$29,$B$32,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB15" s="104">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC15" s="48">
         <f t="shared" si="25"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD15" s="51">
         <f>VLOOKUP(C15,'Giao CT'!$D$6:$S$20,16,0)</f>
@@ -8961,15 +8970,15 @@
       </c>
       <c r="AO16" s="13">
         <f>VLOOKUP(C16,GBOC!$E$7:$DG$29,$B$29,0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AP16" s="14">
         <f t="shared" si="18"/>
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AQ16" s="61">
         <f t="shared" si="19"/>
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AR16" s="33">
         <v>0.97</v>
@@ -9147,15 +9156,15 @@
       </c>
       <c r="AC17" s="13">
         <f>VLOOKUP(C17,GBOC!$E$7:$DG$29,$B$26,0)</f>
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="AD17" s="14">
         <f t="shared" si="12"/>
-        <v>2.8666666666666667</v>
+        <v>3.0666666666666669</v>
       </c>
       <c r="AE17" s="46">
         <f t="shared" si="13"/>
-        <v>-112</v>
+        <v>-124</v>
       </c>
       <c r="AF17" s="51">
         <f>VLOOKUP(C17,'Giao CT'!$D$6:$S$20,10,0)</f>
@@ -9163,15 +9172,15 @@
       </c>
       <c r="AG17" s="13">
         <f>VLOOKUP(C17,GBOC!$E$7:$DG$29,$B$27,0)</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH17" s="14">
         <f t="shared" si="14"/>
-        <v>2.625</v>
+        <v>2.75</v>
       </c>
       <c r="AI17" s="46">
         <f t="shared" si="15"/>
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="AJ17" s="51">
         <f>VLOOKUP(C17,'Giao CT'!$D$6:$S$20,11,0)</f>
@@ -9194,15 +9203,15 @@
       </c>
       <c r="AO17" s="13">
         <f>VLOOKUP(C17,GBOC!$E$7:$DG$29,$B$29,0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP17" s="14">
         <f t="shared" si="18"/>
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AQ17" s="61">
         <f t="shared" si="19"/>
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AR17" s="33">
         <v>0.97</v>
@@ -9474,15 +9483,15 @@
       </c>
       <c r="BA18" s="13">
         <f>VLOOKUP(C18,GBOC!$E$7:$DG$29,$B$32,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB18" s="104">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC18" s="48">
         <f t="shared" si="25"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD18" s="51">
         <f>VLOOKUP(C18,'Giao CT'!$D$6:$S$20,16,0)</f>
@@ -9507,11 +9516,11 @@
       <c r="C19" s="15"/>
       <c r="D19" s="15"/>
       <c r="E19" s="16"/>
-      <c r="F19" s="183">
+      <c r="F19" s="196">
         <f ca="1">TODAY()</f>
         <v>46079</v>
       </c>
-      <c r="G19" s="183"/>
+      <c r="G19" s="196"/>
       <c r="H19" s="73"/>
       <c r="I19" s="74">
         <f ca="1">DAY(F19)</f>
@@ -9524,33 +9533,33 @@
         <f ca="1">I19/J19</f>
         <v>0.83870967741935487</v>
       </c>
-      <c r="L19" s="189" t="s">
+      <c r="L19" s="197" t="s">
         <v>124</v>
       </c>
-      <c r="M19" s="189"/>
-      <c r="N19" s="189"/>
-      <c r="O19" s="189"/>
-      <c r="P19" s="189"/>
-      <c r="Q19" s="189"/>
-      <c r="R19" s="189"/>
-      <c r="S19" s="189"/>
-      <c r="T19" s="189"/>
-      <c r="U19" s="189"/>
-      <c r="V19" s="189"/>
-      <c r="W19" s="189"/>
-      <c r="X19" s="189"/>
-      <c r="Y19" s="189"/>
-      <c r="Z19" s="189"/>
-      <c r="AA19" s="189"/>
-      <c r="AB19" s="189"/>
-      <c r="AC19" s="189"/>
-      <c r="AD19" s="189"/>
-      <c r="AE19" s="189"/>
-      <c r="AF19" s="189"/>
-      <c r="AG19" s="189"/>
-      <c r="AH19" s="189"/>
-      <c r="AI19" s="189"/>
-      <c r="AJ19" s="189"/>
+      <c r="M19" s="197"/>
+      <c r="N19" s="197"/>
+      <c r="O19" s="197"/>
+      <c r="P19" s="197"/>
+      <c r="Q19" s="197"/>
+      <c r="R19" s="197"/>
+      <c r="S19" s="197"/>
+      <c r="T19" s="197"/>
+      <c r="U19" s="197"/>
+      <c r="V19" s="197"/>
+      <c r="W19" s="197"/>
+      <c r="X19" s="197"/>
+      <c r="Y19" s="197"/>
+      <c r="Z19" s="197"/>
+      <c r="AA19" s="197"/>
+      <c r="AB19" s="197"/>
+      <c r="AC19" s="197"/>
+      <c r="AD19" s="197"/>
+      <c r="AE19" s="197"/>
+      <c r="AF19" s="197"/>
+      <c r="AG19" s="197"/>
+      <c r="AH19" s="197"/>
+      <c r="AI19" s="197"/>
+      <c r="AJ19" s="197"/>
       <c r="AK19" s="16"/>
       <c r="AL19" s="32"/>
       <c r="AM19" s="16"/>
@@ -9743,6 +9752,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="AN3:AQ3"/>
+    <mergeCell ref="AF3:AI3"/>
+    <mergeCell ref="L19:AJ19"/>
+    <mergeCell ref="P3:S3"/>
+    <mergeCell ref="T3:W3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="X3:AA3"/>
     <mergeCell ref="AV2:BG2"/>
@@ -9759,12 +9774,6 @@
     <mergeCell ref="D3:G3"/>
     <mergeCell ref="H3:K3"/>
     <mergeCell ref="L3:O3"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="AN3:AQ3"/>
-    <mergeCell ref="AF3:AI3"/>
-    <mergeCell ref="L19:AJ19"/>
-    <mergeCell ref="P3:S3"/>
-    <mergeCell ref="T3:W3"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="C3:C4">
@@ -10249,15 +10258,15 @@
       </c>
       <c r="D10" s="68">
         <f>VLOOKUP($B$2,'TH NV'!$A$5:$BG$18,N13,0)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E10" s="42">
         <f>200%-IFERROR(D10/C10,2)</f>
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="F10" s="42">
         <f t="shared" si="1"/>
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="G10" s="110">
         <v>10</v>
@@ -10268,11 +10277,11 @@
       </c>
       <c r="I10" s="109">
         <f t="shared" si="5"/>
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J10" s="59">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="K10" s="205"/>
       <c r="L10" s="102" t="s">
@@ -10299,15 +10308,15 @@
       </c>
       <c r="D11" s="68">
         <f>VLOOKUP($B$2,'TH NV'!$A$5:$BG$18,N11,0)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E11" s="42">
         <f>D11/C11</f>
-        <v>0</v>
+        <v>1.1111111111111112</v>
       </c>
       <c r="F11" s="42">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.1111111111111112</v>
       </c>
       <c r="G11" s="110">
         <v>5</v>
@@ -10318,11 +10327,11 @@
       </c>
       <c r="I11" s="109">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5.5555555555555554</v>
       </c>
       <c r="J11" s="59">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="K11" s="205"/>
       <c r="L11" s="102" t="s">
@@ -10493,7 +10502,7 @@
       <c r="H15" s="204"/>
       <c r="I15" s="66">
         <f>SUM(I4:I14)</f>
-        <v>61</v>
+        <v>62.555555555555557</v>
       </c>
       <c r="J15" s="39"/>
       <c r="K15" s="205"/>
@@ -10649,42 +10658,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:59" s="1" customFormat="1" ht="24.75" x14ac:dyDescent="0.45">
-      <c r="D1" s="199" t="s">
+      <c r="D1" s="194" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="199"/>
-      <c r="F1" s="199"/>
-      <c r="G1" s="199"/>
-      <c r="H1" s="199"/>
-      <c r="I1" s="199"/>
-      <c r="J1" s="199"/>
-      <c r="K1" s="199"/>
-      <c r="L1" s="199"/>
-      <c r="M1" s="199"/>
-      <c r="N1" s="199"/>
-      <c r="O1" s="199"/>
-      <c r="P1" s="199"/>
-      <c r="Q1" s="199"/>
-      <c r="R1" s="199"/>
-      <c r="S1" s="199"/>
-      <c r="T1" s="197" t="s">
+      <c r="E1" s="194"/>
+      <c r="F1" s="194"/>
+      <c r="G1" s="194"/>
+      <c r="H1" s="194"/>
+      <c r="I1" s="194"/>
+      <c r="J1" s="194"/>
+      <c r="K1" s="194"/>
+      <c r="L1" s="194"/>
+      <c r="M1" s="194"/>
+      <c r="N1" s="194"/>
+      <c r="O1" s="194"/>
+      <c r="P1" s="194"/>
+      <c r="Q1" s="194"/>
+      <c r="R1" s="194"/>
+      <c r="S1" s="194"/>
+      <c r="T1" s="189" t="s">
         <v>36</v>
       </c>
-      <c r="U1" s="197"/>
-      <c r="V1" s="197"/>
-      <c r="W1" s="197"/>
-      <c r="X1" s="197"/>
-      <c r="Y1" s="197"/>
-      <c r="Z1" s="197"/>
-      <c r="AA1" s="197"/>
-      <c r="AB1" s="197"/>
-      <c r="AC1" s="197"/>
-      <c r="AD1" s="197"/>
-      <c r="AE1" s="197"/>
-      <c r="AF1" s="197"/>
-      <c r="AG1" s="197"/>
-      <c r="AH1" s="197"/>
-      <c r="AI1" s="197"/>
+      <c r="U1" s="189"/>
+      <c r="V1" s="189"/>
+      <c r="W1" s="189"/>
+      <c r="X1" s="189"/>
+      <c r="Y1" s="189"/>
+      <c r="Z1" s="189"/>
+      <c r="AA1" s="189"/>
+      <c r="AB1" s="189"/>
+      <c r="AC1" s="189"/>
+      <c r="AD1" s="189"/>
+      <c r="AE1" s="189"/>
+      <c r="AF1" s="189"/>
+      <c r="AG1" s="189"/>
+      <c r="AH1" s="189"/>
+      <c r="AI1" s="189"/>
       <c r="AJ1" s="217" t="s">
         <v>37</v>
       </c>
@@ -10717,90 +10726,90 @@
     <row r="2" spans="1:59" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="187" t="s">
+      <c r="D2" s="185" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="188"/>
-      <c r="F2" s="188"/>
-      <c r="G2" s="188"/>
-      <c r="H2" s="187" t="s">
+      <c r="E2" s="186"/>
+      <c r="F2" s="186"/>
+      <c r="G2" s="186"/>
+      <c r="H2" s="185" t="s">
         <v>40</v>
       </c>
-      <c r="I2" s="188"/>
-      <c r="J2" s="188"/>
-      <c r="K2" s="188"/>
-      <c r="L2" s="187" t="s">
+      <c r="I2" s="186"/>
+      <c r="J2" s="186"/>
+      <c r="K2" s="186"/>
+      <c r="L2" s="185" t="s">
         <v>41</v>
       </c>
-      <c r="M2" s="188"/>
-      <c r="N2" s="188"/>
-      <c r="O2" s="188"/>
-      <c r="P2" s="190" t="s">
+      <c r="M2" s="186"/>
+      <c r="N2" s="186"/>
+      <c r="O2" s="186"/>
+      <c r="P2" s="198" t="s">
         <v>42</v>
       </c>
-      <c r="Q2" s="191"/>
-      <c r="R2" s="191"/>
-      <c r="S2" s="192"/>
-      <c r="T2" s="187" t="s">
+      <c r="Q2" s="199"/>
+      <c r="R2" s="199"/>
+      <c r="S2" s="200"/>
+      <c r="T2" s="185" t="s">
         <v>43</v>
       </c>
-      <c r="U2" s="188"/>
-      <c r="V2" s="188"/>
-      <c r="W2" s="188"/>
-      <c r="X2" s="187" t="s">
+      <c r="U2" s="186"/>
+      <c r="V2" s="186"/>
+      <c r="W2" s="186"/>
+      <c r="X2" s="185" t="s">
         <v>45</v>
       </c>
-      <c r="Y2" s="188"/>
-      <c r="Z2" s="188"/>
-      <c r="AA2" s="188"/>
-      <c r="AB2" s="187" t="s">
+      <c r="Y2" s="186"/>
+      <c r="Z2" s="186"/>
+      <c r="AA2" s="186"/>
+      <c r="AB2" s="185" t="s">
         <v>47</v>
       </c>
-      <c r="AC2" s="188"/>
-      <c r="AD2" s="188"/>
-      <c r="AE2" s="188"/>
-      <c r="AF2" s="187" t="s">
+      <c r="AC2" s="186"/>
+      <c r="AD2" s="186"/>
+      <c r="AE2" s="186"/>
+      <c r="AF2" s="185" t="s">
         <v>48</v>
       </c>
-      <c r="AG2" s="188"/>
-      <c r="AH2" s="188"/>
-      <c r="AI2" s="188"/>
-      <c r="AJ2" s="184" t="s">
+      <c r="AG2" s="186"/>
+      <c r="AH2" s="186"/>
+      <c r="AI2" s="186"/>
+      <c r="AJ2" s="191" t="s">
         <v>51</v>
       </c>
-      <c r="AK2" s="185"/>
-      <c r="AL2" s="185"/>
-      <c r="AM2" s="186"/>
-      <c r="AN2" s="184" t="s">
+      <c r="AK2" s="192"/>
+      <c r="AL2" s="192"/>
+      <c r="AM2" s="193"/>
+      <c r="AN2" s="191" t="s">
         <v>14</v>
       </c>
-      <c r="AO2" s="185"/>
-      <c r="AP2" s="185"/>
-      <c r="AQ2" s="186"/>
-      <c r="AR2" s="184" t="s">
+      <c r="AO2" s="192"/>
+      <c r="AP2" s="192"/>
+      <c r="AQ2" s="193"/>
+      <c r="AR2" s="191" t="s">
         <v>52</v>
       </c>
-      <c r="AS2" s="185"/>
-      <c r="AT2" s="185"/>
-      <c r="AU2" s="186"/>
-      <c r="AV2" s="188" t="s">
+      <c r="AS2" s="192"/>
+      <c r="AT2" s="192"/>
+      <c r="AU2" s="193"/>
+      <c r="AV2" s="186" t="s">
         <v>16</v>
       </c>
-      <c r="AW2" s="188"/>
-      <c r="AX2" s="188"/>
-      <c r="AY2" s="188"/>
-      <c r="AZ2" s="188" t="s">
+      <c r="AW2" s="186"/>
+      <c r="AX2" s="186"/>
+      <c r="AY2" s="186"/>
+      <c r="AZ2" s="186" t="s">
         <v>54</v>
       </c>
-      <c r="BA2" s="188"/>
-      <c r="BB2" s="188"/>
-      <c r="BC2" s="188"/>
-      <c r="BD2" s="187" t="s">
+      <c r="BA2" s="186"/>
+      <c r="BB2" s="186"/>
+      <c r="BC2" s="186"/>
+      <c r="BD2" s="185" t="s">
         <v>55</v>
       </c>
-      <c r="BE2" s="188"/>
-      <c r="BF2" s="198"/>
-      <c r="BG2" s="188"/>
+      <c r="BE2" s="186"/>
+      <c r="BF2" s="190"/>
+      <c r="BG2" s="186"/>
     </row>
     <row r="3" spans="1:59" ht="15" x14ac:dyDescent="0.45">
       <c r="B3" s="8" t="s">
@@ -11292,15 +11301,15 @@
       </c>
       <c r="U5" s="13">
         <f>VLOOKUP(A5,GBOC!$E$7:$DG$29,$B$25,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V5" s="14">
         <f t="shared" ref="V5:V16" si="36">IFERROR(U5/T5,0)</f>
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="W5" s="44">
         <f t="shared" ref="W5:W16" si="37">T5-U5</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X5" s="52">
         <f>VLOOKUP(A5,'Giao CT'!$D$6:$S$20,8,0)</f>
@@ -11324,15 +11333,15 @@
       </c>
       <c r="AC5" s="13">
         <f>VLOOKUP(A5,GBOC!$E$7:$DG$29,$B$27,0)</f>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AD5" s="14">
         <f t="shared" ref="AD5:AD16" si="40">IFERROR(AC5/AB5,0)</f>
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE5" s="46">
         <f t="shared" ref="AE5:AE16" si="41">AB5-AC5</f>
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="AF5" s="51">
         <f>VLOOKUP(A5,'Giao CT'!$D$6:$S$20,10,0)</f>
@@ -11419,15 +11428,15 @@
       </c>
       <c r="BA5" s="13">
         <f>VLOOKUP(A5,GBOC!$E$7:$DG$29,$B$33,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB5" s="14">
         <f t="shared" ref="BB5:BB16" si="52">IFERROR(BA5/AZ5,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC5" s="48">
         <f t="shared" ref="BC5:BC16" si="53">AZ5-BA5</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD5" s="51">
         <f>VLOOKUP(A5,'Giao CT'!$D$6:$S$20,16,0)</f>
@@ -11606,15 +11615,15 @@
       </c>
       <c r="AO6" s="13">
         <f>VLOOKUP(A6,GBOC!$E$7:$DG$29,$B$30,0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AP6" s="14">
         <f t="shared" si="46"/>
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AQ6" s="61">
         <f t="shared" si="47"/>
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AR6" s="33">
         <v>0.97</v>
@@ -11808,15 +11817,15 @@
       </c>
       <c r="AG7" s="13">
         <f>VLOOKUP(A7,GBOC!$E$7:$DG$29,$B$28,0)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AH7" s="14">
         <f t="shared" si="42"/>
-        <v>0</v>
+        <v>1.1111111111111112</v>
       </c>
       <c r="AI7" s="46">
         <f t="shared" si="43"/>
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="AJ7" s="51">
         <f>VLOOKUP(A7,'Giao CT'!$D$6:$S$20,11,0)</f>
@@ -11840,15 +11849,15 @@
       </c>
       <c r="AO7" s="13">
         <f>VLOOKUP(A7,GBOC!$E$7:$DG$29,$B$30,0)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AP7" s="14">
         <f t="shared" si="46"/>
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="AQ7" s="61">
         <f t="shared" si="47"/>
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="AR7" s="33">
         <v>0.97</v>
@@ -12074,15 +12083,15 @@
       </c>
       <c r="AO8" s="13">
         <f>VLOOKUP(A8,GBOC!$E$7:$DG$29,$B$30,0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AP8" s="14">
         <f t="shared" si="46"/>
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AQ8" s="61">
         <f t="shared" si="47"/>
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AR8" s="33">
         <v>0.97</v>
@@ -12369,15 +12378,15 @@
       </c>
       <c r="AO10" s="13">
         <f>VLOOKUP(A10,GBOC!$E$7:$DG$29,$B$30,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP10" s="14">
         <f t="shared" si="46"/>
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AQ10" s="61">
         <f t="shared" si="47"/>
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AR10" s="33">
         <v>0.97</v>
@@ -12507,15 +12516,15 @@
       </c>
       <c r="Q11" s="58">
         <f>VLOOKUP(A11,GBOC!$E$7:$DG$29,$B$24,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R11" s="14">
         <f t="shared" si="34"/>
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="S11" s="46">
         <f t="shared" si="35"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T11" s="52">
         <f>VLOOKUP(A11,'Giao CT'!$D$6:$S$20,7,0)</f>
@@ -12539,15 +12548,15 @@
       </c>
       <c r="Y11" s="13">
         <f>VLOOKUP(A11,GBOC!$E$7:$DG$29,$B$26,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z11" s="14">
         <f t="shared" si="38"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA11" s="46">
         <f t="shared" si="39"/>
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AB11" s="51">
         <f>VLOOKUP(A11,'Giao CT'!$D$6:$S$20,9,0)</f>
@@ -12555,15 +12564,15 @@
       </c>
       <c r="AC11" s="13">
         <f>VLOOKUP(A11,GBOC!$E$7:$DG$29,$B$27,0)</f>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AD11" s="14">
         <f t="shared" si="40"/>
-        <v>0.9</v>
+        <v>0.96666666666666667</v>
       </c>
       <c r="AE11" s="46">
         <f t="shared" si="41"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF11" s="51">
         <f>VLOOKUP(A11,'Giao CT'!$D$6:$S$20,10,0)</f>
@@ -12603,15 +12612,15 @@
       </c>
       <c r="AO11" s="13">
         <f>VLOOKUP(A11,GBOC!$E$7:$DG$29,$B$30,0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP11" s="14">
         <f t="shared" si="46"/>
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AQ11" s="61">
         <f t="shared" si="47"/>
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AR11" s="33">
         <v>0.97</v>
@@ -12959,15 +12968,15 @@
       </c>
       <c r="M13" s="58">
         <f>VLOOKUP(A13,GBOC!$E$7:$DG$29,$B$23,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N13" s="14">
         <f t="shared" si="32"/>
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="O13" s="46">
         <f t="shared" si="33"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P13" s="52">
         <f>VLOOKUP(A13,'Giao CT'!$D$6:$S$20,6,0)</f>
@@ -12991,15 +13000,15 @@
       </c>
       <c r="U13" s="13">
         <f>VLOOKUP(A13,GBOC!$E$7:$DG$29,$B$25,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V13" s="14">
         <f t="shared" si="36"/>
-        <v>1</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="W13" s="44">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="X13" s="52">
         <f>VLOOKUP(A13,'Giao CT'!$D$6:$S$20,8,0)</f>
@@ -13071,15 +13080,15 @@
       </c>
       <c r="AO13" s="13">
         <f>VLOOKUP(A13,GBOC!$E$7:$DG$29,$B$30,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP13" s="14">
         <f t="shared" si="46"/>
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ13" s="61">
         <f t="shared" si="47"/>
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AR13" s="33">
         <v>0.97</v>
@@ -13241,15 +13250,15 @@
       </c>
       <c r="Y14" s="13">
         <f>VLOOKUP(A14,GBOC!$E$7:$DG$29,$B$26,0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z14" s="14">
         <f t="shared" si="38"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA14" s="46">
         <f t="shared" si="39"/>
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="AB14" s="51">
         <f>VLOOKUP(A14,'Giao CT'!$D$6:$S$20,9,0)</f>
@@ -13305,15 +13314,15 @@
       </c>
       <c r="AO14" s="13">
         <f>VLOOKUP(A14,GBOC!$E$7:$DG$29,$B$30,0)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AP14" s="14">
         <f t="shared" si="46"/>
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AQ14" s="61">
         <f t="shared" si="47"/>
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AR14" s="33">
         <v>0.97</v>
@@ -13443,15 +13452,15 @@
       </c>
       <c r="Q15" s="58">
         <f>VLOOKUP(A15,GBOC!$E$7:$DG$29,$B$24,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R15" s="14">
         <f t="shared" si="34"/>
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="S15" s="46">
         <f t="shared" si="35"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T15" s="52">
         <f>VLOOKUP(A15,'Giao CT'!$D$6:$S$20,7,0)</f>
@@ -13539,15 +13548,15 @@
       </c>
       <c r="AO15" s="13">
         <f>VLOOKUP(A15,GBOC!$E$7:$DG$29,$B$30,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP15" s="14">
         <f t="shared" si="46"/>
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ15" s="61">
         <f t="shared" si="47"/>
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AR15" s="33">
         <v>0.97</v>
@@ -13586,15 +13595,15 @@
       </c>
       <c r="BA15" s="13">
         <f>VLOOKUP(A15,GBOC!$E$7:$DG$29,$B$33,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB15" s="14">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC15" s="48">
         <f t="shared" si="53"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD15" s="51">
         <f>VLOOKUP(A15,'Giao CT'!$D$6:$S$20,16,0)</f>
@@ -13725,15 +13734,15 @@
       </c>
       <c r="AC16" s="13">
         <f>VLOOKUP(A16,GBOC!$E$7:$DG$29,$B$27,0)</f>
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="AD16" s="14">
         <f t="shared" si="40"/>
-        <v>2.8666666666666667</v>
+        <v>3.0666666666666669</v>
       </c>
       <c r="AE16" s="46">
         <f t="shared" si="41"/>
-        <v>-112</v>
+        <v>-124</v>
       </c>
       <c r="AF16" s="51">
         <f>VLOOKUP(A16,'Giao CT'!$D$6:$S$20,10,0)</f>
@@ -13741,15 +13750,15 @@
       </c>
       <c r="AG16" s="13">
         <f>VLOOKUP(A16,GBOC!$E$7:$DG$29,$B$28,0)</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH16" s="14">
         <f t="shared" si="42"/>
-        <v>2.625</v>
+        <v>2.75</v>
       </c>
       <c r="AI16" s="46">
         <f t="shared" si="43"/>
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="AJ16" s="51">
         <f>VLOOKUP(A16,'Giao CT'!$D$6:$S$20,11,0)</f>
@@ -13773,15 +13782,15 @@
       </c>
       <c r="AO16" s="13">
         <f>VLOOKUP(A16,GBOC!$E$7:$DG$29,$B$30,0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP16" s="14">
         <f t="shared" si="46"/>
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AQ16" s="61">
         <f t="shared" si="47"/>
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AR16" s="33">
         <v>0.97</v>
@@ -14091,6 +14100,11 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="D1:S1"/>
+    <mergeCell ref="D2:G2"/>
+    <mergeCell ref="H2:K2"/>
+    <mergeCell ref="L2:O2"/>
+    <mergeCell ref="P2:S2"/>
     <mergeCell ref="X2:AA2"/>
     <mergeCell ref="AB2:AE2"/>
     <mergeCell ref="AF2:AI2"/>
@@ -14104,11 +14118,6 @@
     <mergeCell ref="AJ2:AM2"/>
     <mergeCell ref="AN2:AQ2"/>
     <mergeCell ref="T2:W2"/>
-    <mergeCell ref="D1:S1"/>
-    <mergeCell ref="D2:G2"/>
-    <mergeCell ref="H2:K2"/>
-    <mergeCell ref="L2:O2"/>
-    <mergeCell ref="P2:S2"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="F4:F16">
@@ -14362,7 +14371,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{035AF4C2-379E-4E05-A870-198385941EC5}">
-  <dimension ref="A1:DG29"/>
+  <dimension ref="A1:DG30"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="13.265625" bestFit="1" customWidth="1"/>
@@ -15248,7 +15257,7 @@
         <v>12</v>
       </c>
       <c r="L7" s="180">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="M7" s="180">
         <v>171.43</v>
@@ -15260,7 +15269,7 @@
         <v>100</v>
       </c>
       <c r="P7" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q7" s="180">
         <v>4</v>
@@ -15272,7 +15281,7 @@
         <v>6</v>
       </c>
       <c r="T7" s="180">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="U7" s="180">
         <v>150</v>
@@ -15308,22 +15317,22 @@
         <v>100</v>
       </c>
       <c r="AF7" s="180">
+        <v>4</v>
+      </c>
+      <c r="AG7" s="180">
+        <v>4</v>
+      </c>
+      <c r="AH7" s="180">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="180">
         <v>3</v>
       </c>
-      <c r="AG7" s="180">
-        <v>4</v>
-      </c>
-      <c r="AH7" s="180">
-        <v>0</v>
-      </c>
-      <c r="AI7" s="180">
-        <v>1</v>
-      </c>
       <c r="AJ7" s="180">
-        <v>170.83</v>
+        <v>116</v>
       </c>
       <c r="AK7" s="180">
-        <v>175</v>
+        <v>125</v>
       </c>
       <c r="AL7" s="180">
         <v>0</v>
@@ -15332,7 +15341,7 @@
         <v>100</v>
       </c>
       <c r="AN7" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO7" s="180">
         <v>4</v>
@@ -15356,7 +15365,7 @@
         <v>-100</v>
       </c>
       <c r="AV7" s="180">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AW7" s="180">
         <v>35</v>
@@ -15368,7 +15377,7 @@
         <v>52</v>
       </c>
       <c r="AZ7" s="180">
-        <v>173.33</v>
+        <v>166.4</v>
       </c>
       <c r="BA7" s="180">
         <v>148.57</v>
@@ -15392,7 +15401,7 @@
         <v>4</v>
       </c>
       <c r="BH7" s="180">
-        <v>93.33</v>
+        <v>89.6</v>
       </c>
       <c r="BI7" s="180">
         <v>80</v>
@@ -15440,7 +15449,7 @@
         <v>1</v>
       </c>
       <c r="BX7" s="180">
-        <v>116.67</v>
+        <v>112</v>
       </c>
       <c r="BY7" s="180">
         <v>100</v>
@@ -15461,13 +15470,13 @@
         <v>0</v>
       </c>
       <c r="CE7" s="180">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CF7" s="180">
-        <v>72.92</v>
+        <v>84</v>
       </c>
       <c r="CG7" s="180">
-        <v>62.5</v>
+        <v>75</v>
       </c>
       <c r="CH7" s="180">
         <v>0</v>
@@ -15476,7 +15485,7 @@
         <v>100</v>
       </c>
       <c r="CJ7" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CK7" s="180">
         <v>4</v>
@@ -15488,7 +15497,7 @@
         <v>9</v>
       </c>
       <c r="CN7" s="180">
-        <v>262.5</v>
+        <v>252</v>
       </c>
       <c r="CO7" s="180">
         <v>225</v>
@@ -15500,7 +15509,7 @@
         <v>100</v>
       </c>
       <c r="CR7" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CS7" s="180">
         <v>4</v>
@@ -15512,7 +15521,7 @@
         <v>5</v>
       </c>
       <c r="CV7" s="180">
-        <v>145.83000000000001</v>
+        <v>140</v>
       </c>
       <c r="CW7" s="180">
         <v>125</v>
@@ -15536,7 +15545,7 @@
         <v>6</v>
       </c>
       <c r="DD7" s="180">
-        <v>700</v>
+        <v>672</v>
       </c>
       <c r="DE7" s="180">
         <v>600</v>
@@ -15583,7 +15592,7 @@
         <v>13</v>
       </c>
       <c r="L8" s="180">
-        <v>216.67</v>
+        <v>208</v>
       </c>
       <c r="M8" s="180">
         <v>185.71</v>
@@ -15595,19 +15604,19 @@
         <v>100</v>
       </c>
       <c r="P8" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q8" s="180">
         <v>4</v>
       </c>
       <c r="R8" s="180">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" s="180">
         <v>5</v>
       </c>
       <c r="T8" s="180">
-        <v>145.83000000000001</v>
+        <v>140</v>
       </c>
       <c r="U8" s="180">
         <v>125</v>
@@ -15652,22 +15661,22 @@
         <v>0</v>
       </c>
       <c r="AI8" s="180">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ8" s="180">
-        <v>153.33000000000001</v>
+        <v>132.80000000000001</v>
       </c>
       <c r="AK8" s="180">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AL8" s="180">
         <v>5</v>
       </c>
       <c r="AM8" s="180">
-        <v>-60</v>
+        <v>-40</v>
       </c>
       <c r="AN8" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO8" s="180">
         <v>4</v>
@@ -15691,7 +15700,7 @@
         <v>100</v>
       </c>
       <c r="AV8" s="180">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW8" s="180">
         <v>30</v>
@@ -15703,7 +15712,7 @@
         <v>71</v>
       </c>
       <c r="AZ8" s="180">
-        <v>276.11</v>
+        <v>265.07</v>
       </c>
       <c r="BA8" s="180">
         <v>236.67</v>
@@ -15727,7 +15736,7 @@
         <v>5</v>
       </c>
       <c r="BH8" s="180">
-        <v>116.67</v>
+        <v>112</v>
       </c>
       <c r="BI8" s="180">
         <v>100</v>
@@ -15799,7 +15808,7 @@
         <v>10</v>
       </c>
       <c r="CF8" s="180">
-        <v>145.83000000000001</v>
+        <v>140</v>
       </c>
       <c r="CG8" s="180">
         <v>125</v>
@@ -15811,7 +15820,7 @@
         <v>100</v>
       </c>
       <c r="CJ8" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CK8" s="180">
         <v>4</v>
@@ -15823,7 +15832,7 @@
         <v>7</v>
       </c>
       <c r="CN8" s="180">
-        <v>204.17</v>
+        <v>196</v>
       </c>
       <c r="CO8" s="180">
         <v>175</v>
@@ -15835,7 +15844,7 @@
         <v>100</v>
       </c>
       <c r="CR8" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CS8" s="180">
         <v>4</v>
@@ -15847,7 +15856,7 @@
         <v>4</v>
       </c>
       <c r="CV8" s="180">
-        <v>116.67</v>
+        <v>112</v>
       </c>
       <c r="CW8" s="180">
         <v>100</v>
@@ -15871,7 +15880,7 @@
         <v>6</v>
       </c>
       <c r="DD8" s="180">
-        <v>700</v>
+        <v>672</v>
       </c>
       <c r="DE8" s="180">
         <v>600</v>
@@ -15918,7 +15927,7 @@
         <v>12</v>
       </c>
       <c r="L9" s="180">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="M9" s="180">
         <v>171.43</v>
@@ -15930,7 +15939,7 @@
         <v>100</v>
       </c>
       <c r="P9" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q9" s="180">
         <v>4</v>
@@ -15942,7 +15951,7 @@
         <v>4</v>
       </c>
       <c r="T9" s="180">
-        <v>116.67</v>
+        <v>112</v>
       </c>
       <c r="U9" s="180">
         <v>100</v>
@@ -15966,7 +15975,7 @@
         <v>1</v>
       </c>
       <c r="AB9" s="180">
-        <v>38.89</v>
+        <v>37.33</v>
       </c>
       <c r="AC9" s="180">
         <v>33.33</v>
@@ -15987,22 +15996,22 @@
         <v>0</v>
       </c>
       <c r="AI9" s="180">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AJ9" s="180">
+        <v>132.80000000000001</v>
+      </c>
+      <c r="AK9" s="180">
+        <v>140</v>
+      </c>
+      <c r="AL9" s="180">
+        <v>1</v>
+      </c>
+      <c r="AM9" s="180">
         <v>200</v>
       </c>
-      <c r="AK9" s="180">
-        <v>200</v>
-      </c>
-      <c r="AL9" s="180">
-        <v>1</v>
-      </c>
-      <c r="AM9" s="180">
-        <v>-100</v>
-      </c>
       <c r="AN9" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO9" s="180">
         <v>4</v>
@@ -16026,7 +16035,7 @@
         <v>100</v>
       </c>
       <c r="AV9" s="180">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW9" s="180">
         <v>30</v>
@@ -16035,13 +16044,13 @@
         <v>0</v>
       </c>
       <c r="AY9" s="180">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AZ9" s="180">
-        <v>105</v>
+        <v>108.27</v>
       </c>
       <c r="BA9" s="180">
-        <v>90</v>
+        <v>96.67</v>
       </c>
       <c r="BB9" s="180">
         <v>0</v>
@@ -16062,7 +16071,7 @@
         <v>5</v>
       </c>
       <c r="BH9" s="180">
-        <v>116.67</v>
+        <v>112</v>
       </c>
       <c r="BI9" s="180">
         <v>100</v>
@@ -16134,7 +16143,7 @@
         <v>12</v>
       </c>
       <c r="CF9" s="180">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="CG9" s="180">
         <v>150</v>
@@ -16146,22 +16155,22 @@
         <v>100</v>
       </c>
       <c r="CJ9" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CK9" s="180">
         <v>4</v>
       </c>
       <c r="CL9" s="180">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM9" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CN9" s="180">
-        <v>87.5</v>
+        <v>112</v>
       </c>
       <c r="CO9" s="180">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="CP9" s="180">
         <v>0</v>
@@ -16182,7 +16191,7 @@
         <v>5</v>
       </c>
       <c r="CV9" s="180">
-        <v>194.44</v>
+        <v>186.67</v>
       </c>
       <c r="CW9" s="180">
         <v>166.67</v>
@@ -16203,13 +16212,13 @@
         <v>0</v>
       </c>
       <c r="DC9" s="180">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DD9" s="180">
-        <v>233.33</v>
+        <v>336</v>
       </c>
       <c r="DE9" s="180">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="DF9" s="180">
         <v>0</v>
@@ -16253,7 +16262,7 @@
         <v>5</v>
       </c>
       <c r="L10" s="180">
-        <v>83.33</v>
+        <v>80</v>
       </c>
       <c r="M10" s="180">
         <v>71.430000000000007</v>
@@ -16277,7 +16286,7 @@
         <v>4</v>
       </c>
       <c r="T10" s="180">
-        <v>155.56</v>
+        <v>149.33000000000001</v>
       </c>
       <c r="U10" s="180">
         <v>133.33000000000001</v>
@@ -16325,7 +16334,7 @@
         <v>1</v>
       </c>
       <c r="AJ10" s="180">
-        <v>161.11000000000001</v>
+        <v>162.66999999999999</v>
       </c>
       <c r="AK10" s="180">
         <v>166.67</v>
@@ -16337,7 +16346,7 @@
         <v>100</v>
       </c>
       <c r="AN10" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO10" s="180">
         <v>4</v>
@@ -16361,7 +16370,7 @@
         <v>100</v>
       </c>
       <c r="AV10" s="180">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW10" s="180">
         <v>30</v>
@@ -16373,7 +16382,7 @@
         <v>9</v>
       </c>
       <c r="AZ10" s="180">
-        <v>35</v>
+        <v>33.6</v>
       </c>
       <c r="BA10" s="180">
         <v>30</v>
@@ -16385,7 +16394,7 @@
         <v>200</v>
       </c>
       <c r="BD10" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BE10" s="180">
         <v>4</v>
@@ -16397,7 +16406,7 @@
         <v>2</v>
       </c>
       <c r="BH10" s="180">
-        <v>58.33</v>
+        <v>56</v>
       </c>
       <c r="BI10" s="180">
         <v>50</v>
@@ -16481,7 +16490,7 @@
         <v>100</v>
       </c>
       <c r="CJ10" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CK10" s="180">
         <v>4</v>
@@ -16493,7 +16502,7 @@
         <v>3</v>
       </c>
       <c r="CN10" s="180">
-        <v>87.5</v>
+        <v>84</v>
       </c>
       <c r="CO10" s="180">
         <v>75</v>
@@ -16588,7 +16597,7 @@
         <v>8</v>
       </c>
       <c r="L11" s="180">
-        <v>133.33000000000001</v>
+        <v>128</v>
       </c>
       <c r="M11" s="180">
         <v>114.29</v>
@@ -16600,76 +16609,76 @@
         <v>100</v>
       </c>
       <c r="P11" s="180">
+        <v>4</v>
+      </c>
+      <c r="Q11" s="180">
+        <v>4</v>
+      </c>
+      <c r="R11" s="180">
+        <v>0</v>
+      </c>
+      <c r="S11" s="180">
+        <v>4</v>
+      </c>
+      <c r="T11" s="180">
+        <v>112</v>
+      </c>
+      <c r="U11" s="180">
+        <v>100</v>
+      </c>
+      <c r="V11" s="180">
+        <v>0</v>
+      </c>
+      <c r="W11" s="180">
+        <v>100</v>
+      </c>
+      <c r="X11" s="180">
+        <v>2</v>
+      </c>
+      <c r="Y11" s="180">
+        <v>2</v>
+      </c>
+      <c r="Z11" s="180">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="180">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="180">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="180">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="180">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="180">
+        <v>100</v>
+      </c>
+      <c r="AF11" s="180">
+        <v>4</v>
+      </c>
+      <c r="AG11" s="180">
+        <v>4</v>
+      </c>
+      <c r="AH11" s="180">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="180">
         <v>3</v>
       </c>
-      <c r="Q11" s="180">
-        <v>4</v>
-      </c>
-      <c r="R11" s="180">
-        <v>0</v>
-      </c>
-      <c r="S11" s="180">
-        <v>4</v>
-      </c>
-      <c r="T11" s="180">
-        <v>116.67</v>
-      </c>
-      <c r="U11" s="180">
-        <v>100</v>
-      </c>
-      <c r="V11" s="180">
-        <v>0</v>
-      </c>
-      <c r="W11" s="180">
-        <v>100</v>
-      </c>
-      <c r="X11" s="180">
-        <v>2</v>
-      </c>
-      <c r="Y11" s="180">
-        <v>2</v>
-      </c>
-      <c r="Z11" s="180">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="180">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="180">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="180">
-        <v>0</v>
-      </c>
-      <c r="AD11" s="180">
-        <v>0</v>
-      </c>
-      <c r="AE11" s="180">
-        <v>100</v>
-      </c>
-      <c r="AF11" s="180">
-        <v>3</v>
-      </c>
-      <c r="AG11" s="180">
-        <v>4</v>
-      </c>
-      <c r="AH11" s="180">
-        <v>0</v>
-      </c>
-      <c r="AI11" s="180">
-        <v>2</v>
-      </c>
       <c r="AJ11" s="180">
-        <v>141.66999999999999</v>
+        <v>116</v>
       </c>
       <c r="AK11" s="180">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="AL11" s="180">
         <v>2</v>
       </c>
       <c r="AM11" s="180">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AN11" s="180">
         <v>3</v>
@@ -16696,7 +16705,7 @@
         <v>100</v>
       </c>
       <c r="AV11" s="180">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AW11" s="180">
         <v>40</v>
@@ -16708,7 +16717,7 @@
         <v>85</v>
       </c>
       <c r="AZ11" s="180">
-        <v>247.92</v>
+        <v>238</v>
       </c>
       <c r="BA11" s="180">
         <v>212.5</v>
@@ -16729,13 +16738,13 @@
         <v>1</v>
       </c>
       <c r="BG11" s="180">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BH11" s="180">
-        <v>93.33</v>
+        <v>112</v>
       </c>
       <c r="BI11" s="180">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="BJ11" s="180">
         <v>0</v>
@@ -16780,7 +16789,7 @@
         <v>1</v>
       </c>
       <c r="BX11" s="180">
-        <v>116.67</v>
+        <v>112</v>
       </c>
       <c r="BY11" s="180">
         <v>100</v>
@@ -16804,7 +16813,7 @@
         <v>7</v>
       </c>
       <c r="CF11" s="180">
-        <v>102.08</v>
+        <v>98</v>
       </c>
       <c r="CG11" s="180">
         <v>87.5</v>
@@ -16816,7 +16825,7 @@
         <v>100</v>
       </c>
       <c r="CJ11" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CK11" s="180">
         <v>4</v>
@@ -16828,7 +16837,7 @@
         <v>3</v>
       </c>
       <c r="CN11" s="180">
-        <v>87.5</v>
+        <v>84</v>
       </c>
       <c r="CO11" s="180">
         <v>75</v>
@@ -16840,7 +16849,7 @@
         <v>100</v>
       </c>
       <c r="CR11" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CS11" s="180">
         <v>4</v>
@@ -16852,7 +16861,7 @@
         <v>3</v>
       </c>
       <c r="CV11" s="180">
-        <v>87.5</v>
+        <v>84</v>
       </c>
       <c r="CW11" s="180">
         <v>75</v>
@@ -16873,19 +16882,19 @@
         <v>0</v>
       </c>
       <c r="DC11" s="180">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DD11" s="180">
-        <v>1050</v>
+        <v>1120</v>
       </c>
       <c r="DE11" s="180">
+        <v>1000</v>
+      </c>
+      <c r="DF11" s="180">
+        <v>1</v>
+      </c>
+      <c r="DG11" s="180">
         <v>900</v>
-      </c>
-      <c r="DF11" s="180">
-        <v>1</v>
-      </c>
-      <c r="DG11" s="180">
-        <v>800</v>
       </c>
     </row>
     <row r="12" spans="1:111" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -16917,13 +16926,13 @@
         <v>7</v>
       </c>
       <c r="J12" s="180">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K12" s="180">
         <v>7</v>
       </c>
       <c r="L12" s="180">
-        <v>116.67</v>
+        <v>112</v>
       </c>
       <c r="M12" s="180">
         <v>100</v>
@@ -16947,7 +16956,7 @@
         <v>2</v>
       </c>
       <c r="T12" s="180">
-        <v>77.78</v>
+        <v>74.67</v>
       </c>
       <c r="U12" s="180">
         <v>66.67</v>
@@ -16983,7 +16992,7 @@
         <v>100</v>
       </c>
       <c r="AF12" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG12" s="180">
         <v>4</v>
@@ -16992,22 +17001,22 @@
         <v>0</v>
       </c>
       <c r="AI12" s="180">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ12" s="180">
-        <v>200</v>
+        <v>172</v>
       </c>
       <c r="AK12" s="180">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="AL12" s="180">
         <v>3</v>
       </c>
       <c r="AM12" s="180">
-        <v>-100</v>
+        <v>-66.67</v>
       </c>
       <c r="AN12" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO12" s="180">
         <v>4</v>
@@ -17031,7 +17040,7 @@
         <v>100</v>
       </c>
       <c r="AV12" s="180">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW12" s="180">
         <v>30</v>
@@ -17043,7 +17052,7 @@
         <v>26</v>
       </c>
       <c r="AZ12" s="180">
-        <v>101.11</v>
+        <v>97.07</v>
       </c>
       <c r="BA12" s="180">
         <v>86.67</v>
@@ -17055,22 +17064,22 @@
         <v>100</v>
       </c>
       <c r="BD12" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BE12" s="180">
         <v>4</v>
       </c>
       <c r="BF12" s="180">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BG12" s="180">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BH12" s="180">
-        <v>29.17</v>
+        <v>56</v>
       </c>
       <c r="BI12" s="180">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="BJ12" s="180">
         <v>0</v>
@@ -17139,7 +17148,7 @@
         <v>3</v>
       </c>
       <c r="CF12" s="180">
-        <v>43.75</v>
+        <v>42</v>
       </c>
       <c r="CG12" s="180">
         <v>37.5</v>
@@ -17151,7 +17160,7 @@
         <v>100</v>
       </c>
       <c r="CJ12" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CK12" s="180">
         <v>4</v>
@@ -17163,7 +17172,7 @@
         <v>2</v>
       </c>
       <c r="CN12" s="180">
-        <v>58.33</v>
+        <v>56</v>
       </c>
       <c r="CO12" s="180">
         <v>50</v>
@@ -17184,13 +17193,13 @@
         <v>0</v>
       </c>
       <c r="CU12" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV12" s="180">
-        <v>116.67</v>
+        <v>149.33000000000001</v>
       </c>
       <c r="CW12" s="180">
-        <v>100</v>
+        <v>133.33000000000001</v>
       </c>
       <c r="CX12" s="180">
         <v>0</v>
@@ -17211,16 +17220,16 @@
         <v>3</v>
       </c>
       <c r="DD12" s="180">
-        <v>350</v>
+        <v>336</v>
       </c>
       <c r="DE12" s="180">
         <v>300</v>
       </c>
       <c r="DF12" s="180">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DG12" s="180">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13" spans="1:111" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -17258,7 +17267,7 @@
         <v>8</v>
       </c>
       <c r="L13" s="180">
-        <v>116.67</v>
+        <v>112</v>
       </c>
       <c r="M13" s="180">
         <v>100</v>
@@ -17270,7 +17279,7 @@
         <v>100</v>
       </c>
       <c r="P13" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q13" s="180">
         <v>4</v>
@@ -17282,7 +17291,7 @@
         <v>3</v>
       </c>
       <c r="T13" s="180">
-        <v>87.5</v>
+        <v>84</v>
       </c>
       <c r="U13" s="180">
         <v>75</v>
@@ -17330,7 +17339,7 @@
         <v>2</v>
       </c>
       <c r="AJ13" s="180">
-        <v>153.33000000000001</v>
+        <v>155.19999999999999</v>
       </c>
       <c r="AK13" s="180">
         <v>160</v>
@@ -17342,7 +17351,7 @@
         <v>100</v>
       </c>
       <c r="AN13" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO13" s="180">
         <v>4</v>
@@ -17366,7 +17375,7 @@
         <v>100</v>
       </c>
       <c r="AV13" s="180">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="AW13" s="180">
         <v>50</v>
@@ -17375,13 +17384,13 @@
         <v>0</v>
       </c>
       <c r="AY13" s="180">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AZ13" s="180">
-        <v>161</v>
+        <v>156.80000000000001</v>
       </c>
       <c r="BA13" s="180">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="BB13" s="180">
         <v>0</v>
@@ -17402,7 +17411,7 @@
         <v>4</v>
       </c>
       <c r="BH13" s="180">
-        <v>93.33</v>
+        <v>89.6</v>
       </c>
       <c r="BI13" s="180">
         <v>80</v>
@@ -17444,16 +17453,16 @@
         <v>1</v>
       </c>
       <c r="BV13" s="180">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW13" s="180">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX13" s="180">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="BY13" s="180">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BZ13" s="180">
         <v>0</v>
@@ -17474,7 +17483,7 @@
         <v>11</v>
       </c>
       <c r="CF13" s="180">
-        <v>142.59</v>
+        <v>136.88999999999999</v>
       </c>
       <c r="CG13" s="180">
         <v>122.22</v>
@@ -17498,7 +17507,7 @@
         <v>1</v>
       </c>
       <c r="CN13" s="180">
-        <v>23.33</v>
+        <v>22.4</v>
       </c>
       <c r="CO13" s="180">
         <v>20</v>
@@ -17510,22 +17519,22 @@
         <v>100</v>
       </c>
       <c r="CR13" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CS13" s="180">
         <v>4</v>
       </c>
       <c r="CT13" s="180">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CU13" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV13" s="180">
-        <v>87.5</v>
+        <v>112</v>
       </c>
       <c r="CW13" s="180">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="CX13" s="180">
         <v>0</v>
@@ -17587,13 +17596,13 @@
         <v>7</v>
       </c>
       <c r="J14" s="180">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" s="180">
         <v>9</v>
       </c>
       <c r="L14" s="180">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="M14" s="180">
         <v>128.57</v>
@@ -17605,7 +17614,7 @@
         <v>100</v>
       </c>
       <c r="P14" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q14" s="180">
         <v>4</v>
@@ -17617,7 +17626,7 @@
         <v>5</v>
       </c>
       <c r="T14" s="180">
-        <v>145.83000000000001</v>
+        <v>140</v>
       </c>
       <c r="U14" s="180">
         <v>125</v>
@@ -17641,7 +17650,7 @@
         <v>1</v>
       </c>
       <c r="AB14" s="180">
-        <v>58.33</v>
+        <v>56</v>
       </c>
       <c r="AC14" s="180">
         <v>50</v>
@@ -17653,22 +17662,22 @@
         <v>100</v>
       </c>
       <c r="AF14" s="180">
+        <v>4</v>
+      </c>
+      <c r="AG14" s="180">
+        <v>4</v>
+      </c>
+      <c r="AH14" s="180">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="180">
         <v>3</v>
       </c>
-      <c r="AG14" s="180">
-        <v>4</v>
-      </c>
-      <c r="AH14" s="180">
-        <v>0</v>
-      </c>
-      <c r="AI14" s="180">
-        <v>2</v>
-      </c>
       <c r="AJ14" s="180">
-        <v>141.66999999999999</v>
+        <v>116</v>
       </c>
       <c r="AK14" s="180">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="AL14" s="180">
         <v>0</v>
@@ -17677,7 +17686,7 @@
         <v>100</v>
       </c>
       <c r="AN14" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO14" s="180">
         <v>4</v>
@@ -17701,7 +17710,7 @@
         <v>100</v>
       </c>
       <c r="AV14" s="180">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="AW14" s="180">
         <v>60</v>
@@ -17710,13 +17719,13 @@
         <v>0</v>
       </c>
       <c r="AY14" s="180">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AZ14" s="180">
-        <v>416.11</v>
+        <v>405.07</v>
       </c>
       <c r="BA14" s="180">
-        <v>356.67</v>
+        <v>361.67</v>
       </c>
       <c r="BB14" s="180">
         <v>0</v>
@@ -17734,13 +17743,13 @@
         <v>1</v>
       </c>
       <c r="BG14" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BH14" s="180">
-        <v>70</v>
+        <v>89.6</v>
       </c>
       <c r="BI14" s="180">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="BJ14" s="180">
         <v>0</v>
@@ -17761,7 +17770,7 @@
         <v>6</v>
       </c>
       <c r="BP14" s="180">
-        <v>700</v>
+        <v>672</v>
       </c>
       <c r="BQ14" s="180">
         <v>600</v>
@@ -17785,7 +17794,7 @@
         <v>1</v>
       </c>
       <c r="BX14" s="180">
-        <v>116.67</v>
+        <v>112</v>
       </c>
       <c r="BY14" s="180">
         <v>100</v>
@@ -17809,7 +17818,7 @@
         <v>17</v>
       </c>
       <c r="CF14" s="180">
-        <v>247.92</v>
+        <v>238</v>
       </c>
       <c r="CG14" s="180">
         <v>212.5</v>
@@ -17821,7 +17830,7 @@
         <v>100</v>
       </c>
       <c r="CJ14" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CK14" s="180">
         <v>4</v>
@@ -17833,7 +17842,7 @@
         <v>7</v>
       </c>
       <c r="CN14" s="180">
-        <v>204.17</v>
+        <v>196</v>
       </c>
       <c r="CO14" s="180">
         <v>175</v>
@@ -17845,7 +17854,7 @@
         <v>100</v>
       </c>
       <c r="CR14" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CS14" s="180">
         <v>4</v>
@@ -17857,7 +17866,7 @@
         <v>9</v>
       </c>
       <c r="CV14" s="180">
-        <v>262.5</v>
+        <v>252</v>
       </c>
       <c r="CW14" s="180">
         <v>225</v>
@@ -17878,19 +17887,19 @@
         <v>0</v>
       </c>
       <c r="DC14" s="180">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DD14" s="180">
-        <v>1750</v>
+        <v>1792</v>
       </c>
       <c r="DE14" s="180">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="DF14" s="180">
         <v>2</v>
       </c>
       <c r="DG14" s="180">
-        <v>650</v>
+        <v>700</v>
       </c>
     </row>
     <row r="15" spans="1:111" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -17928,7 +17937,7 @@
         <v>10</v>
       </c>
       <c r="L15" s="180">
-        <v>145.83000000000001</v>
+        <v>140</v>
       </c>
       <c r="M15" s="180">
         <v>125</v>
@@ -17940,7 +17949,7 @@
         <v>100</v>
       </c>
       <c r="P15" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q15" s="180">
         <v>4</v>
@@ -17952,7 +17961,7 @@
         <v>3</v>
       </c>
       <c r="T15" s="180">
-        <v>87.5</v>
+        <v>84</v>
       </c>
       <c r="U15" s="180">
         <v>75</v>
@@ -17982,7 +17991,7 @@
         <v>0</v>
       </c>
       <c r="AD15" s="180">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE15" s="180">
         <v>-100</v>
@@ -17997,22 +18006,22 @@
         <v>0</v>
       </c>
       <c r="AI15" s="180">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ15" s="180">
-        <v>200</v>
+        <v>155.19999999999999</v>
       </c>
       <c r="AK15" s="180">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="AL15" s="180">
         <v>1</v>
       </c>
       <c r="AM15" s="180">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="AN15" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO15" s="180">
         <v>4</v>
@@ -18036,7 +18045,7 @@
         <v>100</v>
       </c>
       <c r="AV15" s="180">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW15" s="180">
         <v>30</v>
@@ -18048,7 +18057,7 @@
         <v>60</v>
       </c>
       <c r="AZ15" s="180">
-        <v>233.33</v>
+        <v>224</v>
       </c>
       <c r="BA15" s="180">
         <v>200</v>
@@ -18072,7 +18081,7 @@
         <v>3</v>
       </c>
       <c r="BH15" s="180">
-        <v>70</v>
+        <v>67.2</v>
       </c>
       <c r="BI15" s="180">
         <v>60</v>
@@ -18120,7 +18129,7 @@
         <v>1</v>
       </c>
       <c r="BX15" s="180">
-        <v>116.67</v>
+        <v>112</v>
       </c>
       <c r="BY15" s="180">
         <v>100</v>
@@ -18144,7 +18153,7 @@
         <v>11</v>
       </c>
       <c r="CF15" s="180">
-        <v>142.59</v>
+        <v>136.88999999999999</v>
       </c>
       <c r="CG15" s="180">
         <v>122.22</v>
@@ -18168,7 +18177,7 @@
         <v>6</v>
       </c>
       <c r="CN15" s="180">
-        <v>140</v>
+        <v>134.4</v>
       </c>
       <c r="CO15" s="180">
         <v>120</v>
@@ -18192,7 +18201,7 @@
         <v>2</v>
       </c>
       <c r="CV15" s="180">
-        <v>77.78</v>
+        <v>74.67</v>
       </c>
       <c r="CW15" s="180">
         <v>66.67</v>
@@ -18216,7 +18225,7 @@
         <v>1</v>
       </c>
       <c r="DD15" s="180">
-        <v>116.67</v>
+        <v>112</v>
       </c>
       <c r="DE15" s="180">
         <v>100</v>
@@ -18263,7 +18272,7 @@
         <v>6</v>
       </c>
       <c r="L16" s="180">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="M16" s="180">
         <v>85.71</v>
@@ -18275,7 +18284,7 @@
         <v>100</v>
       </c>
       <c r="P16" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q16" s="180">
         <v>4</v>
@@ -18287,7 +18296,7 @@
         <v>2</v>
       </c>
       <c r="T16" s="180">
-        <v>58.33</v>
+        <v>56</v>
       </c>
       <c r="U16" s="180">
         <v>50</v>
@@ -18323,7 +18332,7 @@
         <v>100</v>
       </c>
       <c r="AF16" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG16" s="180">
         <v>4</v>
@@ -18332,22 +18341,22 @@
         <v>0</v>
       </c>
       <c r="AI16" s="180">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ16" s="180">
-        <v>54.17</v>
+        <v>32</v>
       </c>
       <c r="AK16" s="180">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="AL16" s="180">
         <v>3</v>
       </c>
       <c r="AM16" s="180">
-        <v>66.67</v>
+        <v>100</v>
       </c>
       <c r="AN16" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO16" s="180">
         <v>4</v>
@@ -18371,7 +18380,7 @@
         <v>100</v>
       </c>
       <c r="AV16" s="180">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AW16" s="180">
         <v>35</v>
@@ -18380,13 +18389,13 @@
         <v>0</v>
       </c>
       <c r="AY16" s="180">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="AZ16" s="180">
-        <v>310</v>
+        <v>307.2</v>
       </c>
       <c r="BA16" s="180">
-        <v>265.70999999999998</v>
+        <v>274.29000000000002</v>
       </c>
       <c r="BB16" s="180">
         <v>0</v>
@@ -18407,7 +18416,7 @@
         <v>2</v>
       </c>
       <c r="BH16" s="180">
-        <v>46.67</v>
+        <v>44.8</v>
       </c>
       <c r="BI16" s="180">
         <v>40</v>
@@ -18431,7 +18440,7 @@
         <v>2</v>
       </c>
       <c r="BP16" s="180">
-        <v>233.33</v>
+        <v>224</v>
       </c>
       <c r="BQ16" s="180">
         <v>200</v>
@@ -18455,7 +18464,7 @@
         <v>1</v>
       </c>
       <c r="BX16" s="180">
-        <v>116.67</v>
+        <v>112</v>
       </c>
       <c r="BY16" s="180">
         <v>100</v>
@@ -18479,7 +18488,7 @@
         <v>6</v>
       </c>
       <c r="CF16" s="180">
-        <v>87.5</v>
+        <v>84</v>
       </c>
       <c r="CG16" s="180">
         <v>75</v>
@@ -18491,7 +18500,7 @@
         <v>100</v>
       </c>
       <c r="CJ16" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CK16" s="180">
         <v>4</v>
@@ -18503,7 +18512,7 @@
         <v>4</v>
       </c>
       <c r="CN16" s="180">
-        <v>116.67</v>
+        <v>112</v>
       </c>
       <c r="CO16" s="180">
         <v>100</v>
@@ -18515,19 +18524,19 @@
         <v>100</v>
       </c>
       <c r="CR16" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CS16" s="180">
         <v>4</v>
       </c>
       <c r="CT16" s="180">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CU16" s="180">
         <v>9</v>
       </c>
       <c r="CV16" s="180">
-        <v>262.5</v>
+        <v>252</v>
       </c>
       <c r="CW16" s="180">
         <v>225</v>
@@ -18551,7 +18560,7 @@
         <v>10</v>
       </c>
       <c r="DD16" s="180">
-        <v>1166.67</v>
+        <v>1120</v>
       </c>
       <c r="DE16" s="180">
         <v>1000</v>
@@ -18598,7 +18607,7 @@
         <v>5</v>
       </c>
       <c r="L17" s="180">
-        <v>83.33</v>
+        <v>80</v>
       </c>
       <c r="M17" s="180">
         <v>71.430000000000007</v>
@@ -18610,7 +18619,7 @@
         <v>100</v>
       </c>
       <c r="P17" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q17" s="180">
         <v>4</v>
@@ -18622,7 +18631,7 @@
         <v>6</v>
       </c>
       <c r="T17" s="180">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="U17" s="180">
         <v>150</v>
@@ -18646,7 +18655,7 @@
         <v>1</v>
       </c>
       <c r="AB17" s="180">
-        <v>38.89</v>
+        <v>37.33</v>
       </c>
       <c r="AC17" s="180">
         <v>33.33</v>
@@ -18658,7 +18667,7 @@
         <v>100</v>
       </c>
       <c r="AF17" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG17" s="180">
         <v>4</v>
@@ -18667,22 +18676,22 @@
         <v>0</v>
       </c>
       <c r="AI17" s="180">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AJ17" s="180">
-        <v>141.66999999999999</v>
+        <v>88</v>
       </c>
       <c r="AK17" s="180">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="AL17" s="180">
         <v>1</v>
       </c>
       <c r="AM17" s="180">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AN17" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO17" s="180">
         <v>4</v>
@@ -18706,7 +18715,7 @@
         <v>100</v>
       </c>
       <c r="AV17" s="180">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AW17" s="180">
         <v>35</v>
@@ -18718,7 +18727,7 @@
         <v>57</v>
       </c>
       <c r="AZ17" s="180">
-        <v>190</v>
+        <v>182.4</v>
       </c>
       <c r="BA17" s="180">
         <v>162.86000000000001</v>
@@ -18742,7 +18751,7 @@
         <v>6</v>
       </c>
       <c r="BH17" s="180">
-        <v>140</v>
+        <v>134.4</v>
       </c>
       <c r="BI17" s="180">
         <v>120</v>
@@ -18784,16 +18793,16 @@
         <v>1</v>
       </c>
       <c r="BV17" s="180">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW17" s="180">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX17" s="180">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="BY17" s="180">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BZ17" s="180">
         <v>0</v>
@@ -18814,7 +18823,7 @@
         <v>12</v>
       </c>
       <c r="CF17" s="180">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="CG17" s="180">
         <v>150</v>
@@ -18826,7 +18835,7 @@
         <v>100</v>
       </c>
       <c r="CJ17" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CK17" s="180">
         <v>4</v>
@@ -18838,7 +18847,7 @@
         <v>6</v>
       </c>
       <c r="CN17" s="180">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="CO17" s="180">
         <v>150</v>
@@ -18850,7 +18859,7 @@
         <v>100</v>
       </c>
       <c r="CR17" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CS17" s="180">
         <v>4</v>
@@ -18862,7 +18871,7 @@
         <v>5</v>
       </c>
       <c r="CV17" s="180">
-        <v>145.83000000000001</v>
+        <v>140</v>
       </c>
       <c r="CW17" s="180">
         <v>125</v>
@@ -18886,7 +18895,7 @@
         <v>10</v>
       </c>
       <c r="DD17" s="180">
-        <v>1166.67</v>
+        <v>1120</v>
       </c>
       <c r="DE17" s="180">
         <v>1000</v>
@@ -18933,7 +18942,7 @@
         <v>6</v>
       </c>
       <c r="L18" s="180">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="M18" s="180">
         <v>85.71</v>
@@ -18945,19 +18954,19 @@
         <v>100</v>
       </c>
       <c r="P18" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q18" s="180">
         <v>4</v>
       </c>
       <c r="R18" s="180">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" s="180">
         <v>10</v>
       </c>
       <c r="T18" s="180">
-        <v>291.67</v>
+        <v>280</v>
       </c>
       <c r="U18" s="180">
         <v>250</v>
@@ -18981,7 +18990,7 @@
         <v>1</v>
       </c>
       <c r="AB18" s="180">
-        <v>38.89</v>
+        <v>37.33</v>
       </c>
       <c r="AC18" s="180">
         <v>33.33</v>
@@ -19002,13 +19011,13 @@
         <v>0</v>
       </c>
       <c r="AI18" s="180">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AJ18" s="180">
-        <v>130</v>
+        <v>88</v>
       </c>
       <c r="AK18" s="180">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="AL18" s="180">
         <v>0</v>
@@ -19017,7 +19026,7 @@
         <v>100</v>
       </c>
       <c r="AN18" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO18" s="180">
         <v>4</v>
@@ -19041,7 +19050,7 @@
         <v>100</v>
       </c>
       <c r="AV18" s="180">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW18" s="180">
         <v>30</v>
@@ -19053,7 +19062,7 @@
         <v>67</v>
       </c>
       <c r="AZ18" s="180">
-        <v>260.56</v>
+        <v>250.13</v>
       </c>
       <c r="BA18" s="180">
         <v>223.33</v>
@@ -19077,7 +19086,7 @@
         <v>3</v>
       </c>
       <c r="BH18" s="180">
-        <v>70</v>
+        <v>67.2</v>
       </c>
       <c r="BI18" s="180">
         <v>60</v>
@@ -19149,7 +19158,7 @@
         <v>8</v>
       </c>
       <c r="CF18" s="180">
-        <v>116.67</v>
+        <v>112</v>
       </c>
       <c r="CG18" s="180">
         <v>100</v>
@@ -19161,7 +19170,7 @@
         <v>100</v>
       </c>
       <c r="CJ18" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CK18" s="180">
         <v>4</v>
@@ -19173,7 +19182,7 @@
         <v>6</v>
       </c>
       <c r="CN18" s="180">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="CO18" s="180">
         <v>150</v>
@@ -19185,7 +19194,7 @@
         <v>100</v>
       </c>
       <c r="CR18" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CS18" s="180">
         <v>4</v>
@@ -19197,7 +19206,7 @@
         <v>5</v>
       </c>
       <c r="CV18" s="180">
-        <v>145.83000000000001</v>
+        <v>140</v>
       </c>
       <c r="CW18" s="180">
         <v>125</v>
@@ -19218,19 +19227,19 @@
         <v>0</v>
       </c>
       <c r="DC18" s="180">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DD18" s="180">
-        <v>1050</v>
+        <v>1120</v>
       </c>
       <c r="DE18" s="180">
+        <v>1000</v>
+      </c>
+      <c r="DF18" s="180">
+        <v>1</v>
+      </c>
+      <c r="DG18" s="180">
         <v>900</v>
-      </c>
-      <c r="DF18" s="180">
-        <v>1</v>
-      </c>
-      <c r="DG18" s="180">
-        <v>800</v>
       </c>
     </row>
     <row r="19" spans="1:111" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -19268,7 +19277,7 @@
         <v>8</v>
       </c>
       <c r="L19" s="180">
-        <v>116.67</v>
+        <v>112</v>
       </c>
       <c r="M19" s="180">
         <v>100</v>
@@ -19280,7 +19289,7 @@
         <v>100</v>
       </c>
       <c r="P19" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q19" s="180">
         <v>4</v>
@@ -19292,7 +19301,7 @@
         <v>2</v>
       </c>
       <c r="T19" s="180">
-        <v>58.33</v>
+        <v>56</v>
       </c>
       <c r="U19" s="180">
         <v>50</v>
@@ -19337,13 +19346,13 @@
         <v>0</v>
       </c>
       <c r="AI19" s="180">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AJ19" s="180">
-        <v>153.33000000000001</v>
+        <v>65.599999999999994</v>
       </c>
       <c r="AK19" s="180">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="AL19" s="180">
         <v>0</v>
@@ -19352,7 +19361,7 @@
         <v>100</v>
       </c>
       <c r="AN19" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO19" s="180">
         <v>4</v>
@@ -19376,7 +19385,7 @@
         <v>100</v>
       </c>
       <c r="AV19" s="180">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW19" s="180">
         <v>30</v>
@@ -19388,7 +19397,7 @@
         <v>13</v>
       </c>
       <c r="AZ19" s="180">
-        <v>50.56</v>
+        <v>48.53</v>
       </c>
       <c r="BA19" s="180">
         <v>43.33</v>
@@ -19412,7 +19421,7 @@
         <v>1</v>
       </c>
       <c r="BH19" s="180">
-        <v>23.33</v>
+        <v>22.4</v>
       </c>
       <c r="BI19" s="180">
         <v>20</v>
@@ -19454,13 +19463,13 @@
         <v>1</v>
       </c>
       <c r="BV19" s="180">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BW19" s="180">
         <v>1</v>
       </c>
       <c r="BX19" s="180">
-        <v>116.67</v>
+        <v>112</v>
       </c>
       <c r="BY19" s="180">
         <v>100</v>
@@ -19481,13 +19490,13 @@
         <v>0</v>
       </c>
       <c r="CE19" s="180">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="CF19" s="180">
-        <v>0</v>
+        <v>124.44</v>
       </c>
       <c r="CG19" s="180">
-        <v>0</v>
+        <v>111.11</v>
       </c>
       <c r="CH19" s="180">
         <v>0</v>
@@ -19508,7 +19517,7 @@
         <v>3</v>
       </c>
       <c r="CN19" s="180">
-        <v>70</v>
+        <v>67.2</v>
       </c>
       <c r="CO19" s="180">
         <v>60</v>
@@ -19526,13 +19535,13 @@
         <v>3</v>
       </c>
       <c r="CT19" s="180">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CU19" s="180">
         <v>2</v>
       </c>
       <c r="CV19" s="180">
-        <v>77.78</v>
+        <v>74.67</v>
       </c>
       <c r="CW19" s="180">
         <v>66.67</v>
@@ -19556,7 +19565,7 @@
         <v>1</v>
       </c>
       <c r="DD19" s="180">
-        <v>116.67</v>
+        <v>112</v>
       </c>
       <c r="DE19" s="180">
         <v>100</v>
@@ -19603,7 +19612,7 @@
         <v>7</v>
       </c>
       <c r="L20" s="180">
-        <v>116.67</v>
+        <v>112</v>
       </c>
       <c r="M20" s="180">
         <v>100</v>
@@ -19615,7 +19624,7 @@
         <v>100</v>
       </c>
       <c r="P20" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q20" s="180">
         <v>4</v>
@@ -19627,7 +19636,7 @@
         <v>5</v>
       </c>
       <c r="T20" s="180">
-        <v>145.83000000000001</v>
+        <v>140</v>
       </c>
       <c r="U20" s="180">
         <v>125</v>
@@ -19663,7 +19672,7 @@
         <v>100</v>
       </c>
       <c r="AF20" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG20" s="180">
         <v>4</v>
@@ -19672,13 +19681,13 @@
         <v>0</v>
       </c>
       <c r="AI20" s="180">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ20" s="180">
-        <v>200</v>
+        <v>172</v>
       </c>
       <c r="AK20" s="180">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="AL20" s="180">
         <v>0</v>
@@ -19687,7 +19696,7 @@
         <v>100</v>
       </c>
       <c r="AN20" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO20" s="180">
         <v>4</v>
@@ -19711,7 +19720,7 @@
         <v>100</v>
       </c>
       <c r="AV20" s="180">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW20" s="180">
         <v>30</v>
@@ -19723,7 +19732,7 @@
         <v>51</v>
       </c>
       <c r="AZ20" s="180">
-        <v>198.33</v>
+        <v>190.4</v>
       </c>
       <c r="BA20" s="180">
         <v>170</v>
@@ -19747,7 +19756,7 @@
         <v>2</v>
       </c>
       <c r="BH20" s="180">
-        <v>46.67</v>
+        <v>44.8</v>
       </c>
       <c r="BI20" s="180">
         <v>40</v>
@@ -19789,16 +19798,16 @@
         <v>1</v>
       </c>
       <c r="BV20" s="180">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW20" s="180">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX20" s="180">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="BY20" s="180">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BZ20" s="180">
         <v>0</v>
@@ -19819,7 +19828,7 @@
         <v>5</v>
       </c>
       <c r="CF20" s="180">
-        <v>72.92</v>
+        <v>70</v>
       </c>
       <c r="CG20" s="180">
         <v>62.5</v>
@@ -19831,31 +19840,31 @@
         <v>100</v>
       </c>
       <c r="CJ20" s="180">
+        <v>4</v>
+      </c>
+      <c r="CK20" s="180">
+        <v>4</v>
+      </c>
+      <c r="CL20" s="180">
+        <v>1</v>
+      </c>
+      <c r="CM20" s="180">
         <v>3</v>
       </c>
-      <c r="CK20" s="180">
-        <v>4</v>
-      </c>
-      <c r="CL20" s="180">
-        <v>0</v>
-      </c>
-      <c r="CM20" s="180">
-        <v>2</v>
-      </c>
       <c r="CN20" s="180">
-        <v>58.33</v>
+        <v>84</v>
       </c>
       <c r="CO20" s="180">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="CP20" s="180">
         <v>1</v>
       </c>
       <c r="CQ20" s="180">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="CR20" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CS20" s="180">
         <v>4</v>
@@ -19867,7 +19876,7 @@
         <v>4</v>
       </c>
       <c r="CV20" s="180">
-        <v>116.67</v>
+        <v>112</v>
       </c>
       <c r="CW20" s="180">
         <v>100</v>
@@ -19891,7 +19900,7 @@
         <v>1</v>
       </c>
       <c r="DD20" s="180">
-        <v>116.67</v>
+        <v>112</v>
       </c>
       <c r="DE20" s="180">
         <v>100</v>
@@ -19938,7 +19947,7 @@
         <v>3</v>
       </c>
       <c r="L21" s="180">
-        <v>70</v>
+        <v>67.2</v>
       </c>
       <c r="M21" s="180">
         <v>60</v>
@@ -19962,7 +19971,7 @@
         <v>3</v>
       </c>
       <c r="T21" s="180">
-        <v>116.67</v>
+        <v>112</v>
       </c>
       <c r="U21" s="180">
         <v>100</v>
@@ -20007,22 +20016,22 @@
         <v>0</v>
       </c>
       <c r="AI21" s="180">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ21" s="180">
-        <v>161.11000000000001</v>
+        <v>125.33</v>
       </c>
       <c r="AK21" s="180">
-        <v>166.67</v>
+        <v>133.33000000000001</v>
       </c>
       <c r="AL21" s="180">
         <v>1</v>
       </c>
       <c r="AM21" s="180">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN21" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO21" s="180">
         <v>4</v>
@@ -20046,7 +20055,7 @@
         <v>100</v>
       </c>
       <c r="AV21" s="180">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW21" s="180">
         <v>20</v>
@@ -20055,13 +20064,13 @@
         <v>0</v>
       </c>
       <c r="AY21" s="180">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="AZ21" s="180">
-        <v>87.5</v>
+        <v>151.19999999999999</v>
       </c>
       <c r="BA21" s="180">
-        <v>75</v>
+        <v>135</v>
       </c>
       <c r="BB21" s="180">
         <v>0</v>
@@ -20082,7 +20091,7 @@
         <v>1</v>
       </c>
       <c r="BH21" s="180">
-        <v>23.33</v>
+        <v>22.4</v>
       </c>
       <c r="BI21" s="180">
         <v>20</v>
@@ -20154,7 +20163,7 @@
         <v>1</v>
       </c>
       <c r="CF21" s="180">
-        <v>14.58</v>
+        <v>14</v>
       </c>
       <c r="CG21" s="180">
         <v>12.5</v>
@@ -20166,7 +20175,7 @@
         <v>100</v>
       </c>
       <c r="CJ21" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CK21" s="180">
         <v>4</v>
@@ -20178,7 +20187,7 @@
         <v>3</v>
       </c>
       <c r="CN21" s="180">
-        <v>87.5</v>
+        <v>84</v>
       </c>
       <c r="CO21" s="180">
         <v>75</v>
@@ -20196,13 +20205,13 @@
         <v>3</v>
       </c>
       <c r="CT21" s="180">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CU21" s="180">
         <v>4</v>
       </c>
       <c r="CV21" s="180">
-        <v>155.56</v>
+        <v>149.33000000000001</v>
       </c>
       <c r="CW21" s="180">
         <v>133.33000000000001</v>
@@ -20223,19 +20232,19 @@
         <v>0</v>
       </c>
       <c r="DC21" s="180">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DD21" s="180">
-        <v>233.33</v>
+        <v>336</v>
       </c>
       <c r="DE21" s="180">
+        <v>300</v>
+      </c>
+      <c r="DF21" s="180">
+        <v>1</v>
+      </c>
+      <c r="DG21" s="180">
         <v>200</v>
-      </c>
-      <c r="DF21" s="180">
-        <v>1</v>
-      </c>
-      <c r="DG21" s="180">
-        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:111" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -20273,7 +20282,7 @@
         <v>8</v>
       </c>
       <c r="L22" s="180">
-        <v>116.67</v>
+        <v>112</v>
       </c>
       <c r="M22" s="180">
         <v>100</v>
@@ -20285,7 +20294,7 @@
         <v>100</v>
       </c>
       <c r="P22" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q22" s="180">
         <v>4</v>
@@ -20297,7 +20306,7 @@
         <v>6</v>
       </c>
       <c r="T22" s="180">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="U22" s="180">
         <v>150</v>
@@ -20342,13 +20351,13 @@
         <v>0</v>
       </c>
       <c r="AI22" s="180">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ22" s="180">
-        <v>200</v>
+        <v>155.19999999999999</v>
       </c>
       <c r="AK22" s="180">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="AL22" s="180">
         <v>0</v>
@@ -20357,7 +20366,7 @@
         <v>100</v>
       </c>
       <c r="AN22" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO22" s="180">
         <v>4</v>
@@ -20381,7 +20390,7 @@
         <v>100</v>
       </c>
       <c r="AV22" s="180">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW22" s="180">
         <v>30</v>
@@ -20393,7 +20402,7 @@
         <v>61</v>
       </c>
       <c r="AZ22" s="180">
-        <v>237.22</v>
+        <v>227.73</v>
       </c>
       <c r="BA22" s="180">
         <v>203.33</v>
@@ -20417,7 +20426,7 @@
         <v>3</v>
       </c>
       <c r="BH22" s="180">
-        <v>70</v>
+        <v>67.2</v>
       </c>
       <c r="BI22" s="180">
         <v>60</v>
@@ -20465,7 +20474,7 @@
         <v>2</v>
       </c>
       <c r="BX22" s="180">
-        <v>233.33</v>
+        <v>224</v>
       </c>
       <c r="BY22" s="180">
         <v>200</v>
@@ -20489,7 +20498,7 @@
         <v>11</v>
       </c>
       <c r="CF22" s="180">
-        <v>142.59</v>
+        <v>136.88999999999999</v>
       </c>
       <c r="CG22" s="180">
         <v>122.22</v>
@@ -20507,13 +20516,13 @@
         <v>5</v>
       </c>
       <c r="CL22" s="180">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM22" s="180">
         <v>4</v>
       </c>
       <c r="CN22" s="180">
-        <v>93.33</v>
+        <v>89.6</v>
       </c>
       <c r="CO22" s="180">
         <v>80</v>
@@ -20525,7 +20534,7 @@
         <v>100</v>
       </c>
       <c r="CR22" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CS22" s="180">
         <v>4</v>
@@ -20537,7 +20546,7 @@
         <v>4</v>
       </c>
       <c r="CV22" s="180">
-        <v>116.67</v>
+        <v>112</v>
       </c>
       <c r="CW22" s="180">
         <v>100</v>
@@ -20561,7 +20570,7 @@
         <v>2</v>
       </c>
       <c r="DD22" s="180">
-        <v>233.33</v>
+        <v>224</v>
       </c>
       <c r="DE22" s="180">
         <v>200</v>
@@ -20608,7 +20617,7 @@
         <v>11</v>
       </c>
       <c r="L23" s="180">
-        <v>183.33</v>
+        <v>176</v>
       </c>
       <c r="M23" s="180">
         <v>157.13999999999999</v>
@@ -20620,7 +20629,7 @@
         <v>100</v>
       </c>
       <c r="P23" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q23" s="180">
         <v>4</v>
@@ -20632,7 +20641,7 @@
         <v>5</v>
       </c>
       <c r="T23" s="180">
-        <v>145.83000000000001</v>
+        <v>140</v>
       </c>
       <c r="U23" s="180">
         <v>125</v>
@@ -20677,22 +20686,22 @@
         <v>0</v>
       </c>
       <c r="AI23" s="180">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AJ23" s="180">
-        <v>200</v>
+        <v>132.80000000000001</v>
       </c>
       <c r="AK23" s="180">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="AL23" s="180">
         <v>2</v>
       </c>
       <c r="AM23" s="180">
-        <v>-100</v>
+        <v>50</v>
       </c>
       <c r="AN23" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO23" s="180">
         <v>4</v>
@@ -20716,7 +20725,7 @@
         <v>100</v>
       </c>
       <c r="AV23" s="180">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="AW23" s="180">
         <v>60</v>
@@ -20725,13 +20734,13 @@
         <v>0</v>
       </c>
       <c r="AY23" s="180">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="AZ23" s="180">
-        <v>334.44</v>
+        <v>343.47</v>
       </c>
       <c r="BA23" s="180">
-        <v>286.67</v>
+        <v>306.67</v>
       </c>
       <c r="BB23" s="180">
         <v>0</v>
@@ -20752,7 +20761,7 @@
         <v>4</v>
       </c>
       <c r="BH23" s="180">
-        <v>93.33</v>
+        <v>89.6</v>
       </c>
       <c r="BI23" s="180">
         <v>80</v>
@@ -20800,7 +20809,7 @@
         <v>1</v>
       </c>
       <c r="BX23" s="180">
-        <v>116.67</v>
+        <v>112</v>
       </c>
       <c r="BY23" s="180">
         <v>100</v>
@@ -20821,13 +20830,13 @@
         <v>0</v>
       </c>
       <c r="CE23" s="180">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CF23" s="180">
-        <v>306.25</v>
+        <v>308</v>
       </c>
       <c r="CG23" s="180">
-        <v>262.5</v>
+        <v>275</v>
       </c>
       <c r="CH23" s="180">
         <v>0</v>
@@ -20836,7 +20845,7 @@
         <v>100</v>
       </c>
       <c r="CJ23" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CK23" s="180">
         <v>4</v>
@@ -20848,7 +20857,7 @@
         <v>5</v>
       </c>
       <c r="CN23" s="180">
-        <v>145.83000000000001</v>
+        <v>140</v>
       </c>
       <c r="CO23" s="180">
         <v>125</v>
@@ -20860,19 +20869,19 @@
         <v>100</v>
       </c>
       <c r="CR23" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CS23" s="180">
         <v>4</v>
       </c>
       <c r="CT23" s="180">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CU23" s="180">
         <v>9</v>
       </c>
       <c r="CV23" s="180">
-        <v>262.5</v>
+        <v>252</v>
       </c>
       <c r="CW23" s="180">
         <v>225</v>
@@ -20896,7 +20905,7 @@
         <v>21</v>
       </c>
       <c r="DD23" s="180">
-        <v>2450</v>
+        <v>2352</v>
       </c>
       <c r="DE23" s="180">
         <v>2100</v>
@@ -20943,7 +20952,7 @@
         <v>4</v>
       </c>
       <c r="L24" s="180">
-        <v>155.56</v>
+        <v>149.33000000000001</v>
       </c>
       <c r="M24" s="180">
         <v>133.33000000000001</v>
@@ -21051,7 +21060,7 @@
         <v>100</v>
       </c>
       <c r="AV24" s="180">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW24" s="180">
         <v>14</v>
@@ -21063,7 +21072,7 @@
         <v>15</v>
       </c>
       <c r="AZ24" s="180">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="BA24" s="180">
         <v>107.14</v>
@@ -21087,7 +21096,7 @@
         <v>2</v>
       </c>
       <c r="BH24" s="180">
-        <v>116.67</v>
+        <v>112</v>
       </c>
       <c r="BI24" s="180">
         <v>100</v>
@@ -21129,16 +21138,16 @@
         <v>1</v>
       </c>
       <c r="BV24" s="180">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW24" s="180">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX24" s="180">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="BY24" s="180">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BZ24" s="180">
         <v>0</v>
@@ -21177,13 +21186,13 @@
         <v>3</v>
       </c>
       <c r="CL24" s="180">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM24" s="180">
         <v>1</v>
       </c>
       <c r="CN24" s="180">
-        <v>38.89</v>
+        <v>37.33</v>
       </c>
       <c r="CO24" s="180">
         <v>33.33</v>
@@ -21207,7 +21216,7 @@
         <v>2</v>
       </c>
       <c r="CV24" s="180">
-        <v>77.78</v>
+        <v>74.67</v>
       </c>
       <c r="CW24" s="180">
         <v>66.67</v>
@@ -21306,7 +21315,7 @@
       <c r="AT25" s="181"/>
       <c r="AU25" s="181"/>
       <c r="AV25" s="180">
-        <v>1166</v>
+        <v>1214</v>
       </c>
       <c r="AW25" s="180">
         <v>1360</v>
@@ -21370,7 +21379,7 @@
         <v>100</v>
       </c>
       <c r="CB25" s="180">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="CC25" s="180">
         <v>120</v>
@@ -21410,7 +21419,7 @@
       <c r="CX25" s="181"/>
       <c r="CY25" s="181"/>
       <c r="CZ25" s="180">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="DA25" s="180">
         <v>257</v>
@@ -21491,10 +21500,10 @@
         <v>100</v>
       </c>
       <c r="AD26" s="180">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE26" s="180">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="AF26" s="181"/>
       <c r="AG26" s="181"/>
@@ -21600,7 +21609,7 @@
         <v>179</v>
       </c>
       <c r="H27" s="180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I27" s="180">
         <v>4</v>
@@ -21612,7 +21621,7 @@
         <v>3</v>
       </c>
       <c r="L27" s="180">
-        <v>87.5</v>
+        <v>84</v>
       </c>
       <c r="M27" s="180">
         <v>75</v>
@@ -21636,7 +21645,7 @@
         <v>4</v>
       </c>
       <c r="T27" s="180">
-        <v>233.33</v>
+        <v>224</v>
       </c>
       <c r="U27" s="180">
         <v>200</v>
@@ -21681,13 +21690,13 @@
         <v>0</v>
       </c>
       <c r="AI27" s="180">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AJ27" s="180">
-        <v>141.66999999999999</v>
+        <v>32</v>
       </c>
       <c r="AK27" s="180">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="AL27" s="180">
         <v>0</v>
@@ -21720,7 +21729,7 @@
         <v>100</v>
       </c>
       <c r="AV27" s="180">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW27" s="180">
         <v>21</v>
@@ -21732,7 +21741,7 @@
         <v>30</v>
       </c>
       <c r="AZ27" s="180">
-        <v>166.67</v>
+        <v>160</v>
       </c>
       <c r="BA27" s="180">
         <v>142.86000000000001</v>
@@ -21756,7 +21765,7 @@
         <v>1</v>
       </c>
       <c r="BH27" s="180">
-        <v>38.89</v>
+        <v>37.33</v>
       </c>
       <c r="BI27" s="180">
         <v>33.33</v>
@@ -21804,7 +21813,7 @@
         <v>1</v>
       </c>
       <c r="BX27" s="180">
-        <v>116.67</v>
+        <v>112</v>
       </c>
       <c r="BY27" s="180">
         <v>100</v>
@@ -21828,7 +21837,7 @@
         <v>6</v>
       </c>
       <c r="CF27" s="180">
-        <v>116.67</v>
+        <v>112</v>
       </c>
       <c r="CG27" s="180">
         <v>100</v>
@@ -21852,7 +21861,7 @@
         <v>2</v>
       </c>
       <c r="CN27" s="180">
-        <v>77.78</v>
+        <v>74.67</v>
       </c>
       <c r="CO27" s="180">
         <v>66.67</v>
@@ -21873,13 +21882,13 @@
         <v>1</v>
       </c>
       <c r="CU27" s="180">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CV27" s="180">
-        <v>77.78</v>
+        <v>112</v>
       </c>
       <c r="CW27" s="180">
-        <v>66.67</v>
+        <v>100</v>
       </c>
       <c r="CX27" s="180">
         <v>0</v>
@@ -21900,7 +21909,7 @@
         <v>3</v>
       </c>
       <c r="DD27" s="180">
-        <v>350</v>
+        <v>336</v>
       </c>
       <c r="DE27" s="180">
         <v>300</v>
@@ -21926,151 +21935,71 @@
         <v>251</v>
       </c>
       <c r="E28" s="179" t="s">
-        <v>67</v>
+        <v>262</v>
       </c>
       <c r="F28" s="179" t="s">
-        <v>199</v>
+        <v>263</v>
       </c>
       <c r="G28" s="179" t="s">
-        <v>128</v>
-      </c>
-      <c r="H28" s="180">
-        <v>7</v>
-      </c>
-      <c r="I28" s="180">
-        <v>8</v>
-      </c>
-      <c r="J28" s="180">
-        <v>1</v>
-      </c>
-      <c r="K28" s="180">
-        <v>8</v>
-      </c>
-      <c r="L28" s="180">
-        <v>116.67</v>
-      </c>
-      <c r="M28" s="180">
-        <v>100</v>
-      </c>
-      <c r="N28" s="180">
-        <v>0</v>
-      </c>
-      <c r="O28" s="180">
-        <v>100</v>
-      </c>
-      <c r="P28" s="180">
-        <v>3</v>
-      </c>
-      <c r="Q28" s="180">
-        <v>4</v>
-      </c>
-      <c r="R28" s="180">
-        <v>0</v>
-      </c>
-      <c r="S28" s="180">
-        <v>6</v>
-      </c>
-      <c r="T28" s="180">
-        <v>175</v>
-      </c>
-      <c r="U28" s="180">
-        <v>150</v>
-      </c>
-      <c r="V28" s="180">
-        <v>0</v>
-      </c>
-      <c r="W28" s="180">
-        <v>100</v>
-      </c>
-      <c r="X28" s="180">
-        <v>2</v>
-      </c>
-      <c r="Y28" s="180">
-        <v>2</v>
-      </c>
-      <c r="Z28" s="180">
-        <v>0</v>
-      </c>
-      <c r="AA28" s="180">
-        <v>0</v>
-      </c>
-      <c r="AB28" s="180">
-        <v>0</v>
-      </c>
-      <c r="AC28" s="180">
-        <v>0</v>
-      </c>
-      <c r="AD28" s="180">
-        <v>1</v>
-      </c>
-      <c r="AE28" s="180">
-        <v>-100</v>
-      </c>
-      <c r="AF28" s="180">
-        <v>4</v>
-      </c>
-      <c r="AG28" s="180">
-        <v>5</v>
-      </c>
-      <c r="AH28" s="180">
-        <v>0</v>
-      </c>
-      <c r="AI28" s="180">
-        <v>3</v>
-      </c>
-      <c r="AJ28" s="180">
-        <v>130</v>
-      </c>
-      <c r="AK28" s="180">
-        <v>140</v>
-      </c>
-      <c r="AL28" s="180">
-        <v>1</v>
-      </c>
-      <c r="AM28" s="180">
-        <v>200</v>
-      </c>
-      <c r="AN28" s="180">
-        <v>3</v>
-      </c>
-      <c r="AO28" s="180">
-        <v>4</v>
-      </c>
-      <c r="AP28" s="180">
-        <v>0</v>
-      </c>
-      <c r="AQ28" s="180">
-        <v>1</v>
-      </c>
-      <c r="AR28" s="180">
-        <v>29.17</v>
-      </c>
-      <c r="AS28" s="180">
-        <v>25</v>
-      </c>
-      <c r="AT28" s="180">
-        <v>0</v>
-      </c>
-      <c r="AU28" s="180">
-        <v>100</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="H28" s="181"/>
+      <c r="I28" s="181"/>
+      <c r="J28" s="181"/>
+      <c r="K28" s="181"/>
+      <c r="L28" s="181"/>
+      <c r="M28" s="181"/>
+      <c r="N28" s="181"/>
+      <c r="O28" s="181"/>
+      <c r="P28" s="181"/>
+      <c r="Q28" s="181"/>
+      <c r="R28" s="181"/>
+      <c r="S28" s="181"/>
+      <c r="T28" s="181"/>
+      <c r="U28" s="181"/>
+      <c r="V28" s="181"/>
+      <c r="W28" s="181"/>
+      <c r="X28" s="181"/>
+      <c r="Y28" s="181"/>
+      <c r="Z28" s="181"/>
+      <c r="AA28" s="181"/>
+      <c r="AB28" s="181"/>
+      <c r="AC28" s="181"/>
+      <c r="AD28" s="181"/>
+      <c r="AE28" s="181"/>
+      <c r="AF28" s="181"/>
+      <c r="AG28" s="181"/>
+      <c r="AH28" s="181"/>
+      <c r="AI28" s="181"/>
+      <c r="AJ28" s="181"/>
+      <c r="AK28" s="181"/>
+      <c r="AL28" s="181"/>
+      <c r="AM28" s="181"/>
+      <c r="AN28" s="181"/>
+      <c r="AO28" s="181"/>
+      <c r="AP28" s="181"/>
+      <c r="AQ28" s="181"/>
+      <c r="AR28" s="181"/>
+      <c r="AS28" s="181"/>
+      <c r="AT28" s="181"/>
+      <c r="AU28" s="181"/>
       <c r="AV28" s="180">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AW28" s="180">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AX28" s="180">
         <v>0</v>
       </c>
       <c r="AY28" s="180">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="AZ28" s="180">
-        <v>128.33000000000001</v>
+        <v>100</v>
       </c>
       <c r="BA28" s="180">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="BB28" s="180">
         <v>0</v>
@@ -22078,174 +22007,62 @@
       <c r="BC28" s="180">
         <v>100</v>
       </c>
-      <c r="BD28" s="180">
-        <v>4</v>
-      </c>
-      <c r="BE28" s="180">
-        <v>5</v>
-      </c>
-      <c r="BF28" s="180">
-        <v>1</v>
-      </c>
-      <c r="BG28" s="180">
-        <v>5</v>
-      </c>
-      <c r="BH28" s="180">
-        <v>116.67</v>
-      </c>
-      <c r="BI28" s="180">
-        <v>100</v>
-      </c>
-      <c r="BJ28" s="180">
-        <v>0</v>
-      </c>
-      <c r="BK28" s="180">
-        <v>100</v>
-      </c>
-      <c r="BL28" s="180">
-        <v>0</v>
-      </c>
-      <c r="BM28" s="180">
-        <v>0</v>
-      </c>
-      <c r="BN28" s="180">
-        <v>0</v>
-      </c>
-      <c r="BO28" s="180">
-        <v>0</v>
-      </c>
-      <c r="BP28" s="180">
-        <v>100</v>
-      </c>
-      <c r="BQ28" s="180">
-        <v>100</v>
-      </c>
-      <c r="BR28" s="180">
-        <v>0</v>
-      </c>
-      <c r="BS28" s="180">
-        <v>100</v>
-      </c>
-      <c r="BT28" s="180">
-        <v>1</v>
-      </c>
-      <c r="BU28" s="180">
-        <v>1</v>
-      </c>
-      <c r="BV28" s="180">
-        <v>0</v>
-      </c>
-      <c r="BW28" s="180">
-        <v>1</v>
-      </c>
-      <c r="BX28" s="180">
-        <v>116.67</v>
-      </c>
-      <c r="BY28" s="180">
-        <v>100</v>
-      </c>
-      <c r="BZ28" s="180">
-        <v>0</v>
-      </c>
-      <c r="CA28" s="180">
-        <v>100</v>
-      </c>
-      <c r="CB28" s="180">
-        <v>8</v>
-      </c>
-      <c r="CC28" s="180">
-        <v>9</v>
-      </c>
-      <c r="CD28" s="180">
-        <v>0</v>
-      </c>
-      <c r="CE28" s="180">
-        <v>12</v>
-      </c>
-      <c r="CF28" s="180">
-        <v>155.56</v>
-      </c>
-      <c r="CG28" s="180">
-        <v>133.33000000000001</v>
-      </c>
-      <c r="CH28" s="180">
-        <v>0</v>
-      </c>
-      <c r="CI28" s="180">
-        <v>100</v>
-      </c>
-      <c r="CJ28" s="180">
-        <v>4</v>
-      </c>
-      <c r="CK28" s="180">
-        <v>5</v>
-      </c>
-      <c r="CL28" s="180">
-        <v>0</v>
-      </c>
-      <c r="CM28" s="180">
-        <v>6</v>
-      </c>
-      <c r="CN28" s="180">
-        <v>140</v>
-      </c>
-      <c r="CO28" s="180">
-        <v>120</v>
-      </c>
-      <c r="CP28" s="180">
-        <v>0</v>
-      </c>
-      <c r="CQ28" s="180">
-        <v>100</v>
-      </c>
-      <c r="CR28" s="180">
-        <v>3</v>
-      </c>
-      <c r="CS28" s="180">
-        <v>4</v>
-      </c>
-      <c r="CT28" s="180">
-        <v>0</v>
-      </c>
-      <c r="CU28" s="180">
-        <v>4</v>
-      </c>
-      <c r="CV28" s="180">
-        <v>116.67</v>
-      </c>
-      <c r="CW28" s="180">
-        <v>100</v>
-      </c>
-      <c r="CX28" s="180">
-        <v>0</v>
-      </c>
-      <c r="CY28" s="180">
-        <v>100</v>
-      </c>
-      <c r="CZ28" s="180">
-        <v>1</v>
-      </c>
-      <c r="DA28" s="180">
-        <v>1</v>
-      </c>
-      <c r="DB28" s="180">
-        <v>0</v>
-      </c>
-      <c r="DC28" s="180">
-        <v>1</v>
-      </c>
-      <c r="DD28" s="180">
-        <v>116.67</v>
-      </c>
-      <c r="DE28" s="180">
-        <v>100</v>
-      </c>
-      <c r="DF28" s="180">
-        <v>0</v>
-      </c>
-      <c r="DG28" s="180">
-        <v>100</v>
-      </c>
+      <c r="BD28" s="181"/>
+      <c r="BE28" s="181"/>
+      <c r="BF28" s="181"/>
+      <c r="BG28" s="181"/>
+      <c r="BH28" s="181"/>
+      <c r="BI28" s="181"/>
+      <c r="BJ28" s="181"/>
+      <c r="BK28" s="181"/>
+      <c r="BL28" s="181"/>
+      <c r="BM28" s="181"/>
+      <c r="BN28" s="181"/>
+      <c r="BO28" s="181"/>
+      <c r="BP28" s="181"/>
+      <c r="BQ28" s="181"/>
+      <c r="BR28" s="181"/>
+      <c r="BS28" s="181"/>
+      <c r="BT28" s="181"/>
+      <c r="BU28" s="181"/>
+      <c r="BV28" s="181"/>
+      <c r="BW28" s="181"/>
+      <c r="BX28" s="181"/>
+      <c r="BY28" s="181"/>
+      <c r="BZ28" s="181"/>
+      <c r="CA28" s="181"/>
+      <c r="CB28" s="181"/>
+      <c r="CC28" s="181"/>
+      <c r="CD28" s="181"/>
+      <c r="CE28" s="181"/>
+      <c r="CF28" s="181"/>
+      <c r="CG28" s="181"/>
+      <c r="CH28" s="181"/>
+      <c r="CI28" s="181"/>
+      <c r="CJ28" s="181"/>
+      <c r="CK28" s="181"/>
+      <c r="CL28" s="181"/>
+      <c r="CM28" s="181"/>
+      <c r="CN28" s="181"/>
+      <c r="CO28" s="181"/>
+      <c r="CP28" s="181"/>
+      <c r="CQ28" s="181"/>
+      <c r="CR28" s="181"/>
+      <c r="CS28" s="181"/>
+      <c r="CT28" s="181"/>
+      <c r="CU28" s="181"/>
+      <c r="CV28" s="181"/>
+      <c r="CW28" s="181"/>
+      <c r="CX28" s="181"/>
+      <c r="CY28" s="181"/>
+      <c r="CZ28" s="181"/>
+      <c r="DA28" s="181"/>
+      <c r="DB28" s="181"/>
+      <c r="DC28" s="181"/>
+      <c r="DD28" s="181"/>
+      <c r="DE28" s="181"/>
+      <c r="DF28" s="181"/>
+      <c r="DG28" s="181"/>
     </row>
     <row r="29" spans="1:111" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A29" s="148" t="s">
@@ -22260,331 +22077,660 @@
       <c r="D29" s="149" t="s">
         <v>252</v>
       </c>
-      <c r="E29" s="182" t="s">
+      <c r="E29" s="179" t="s">
+        <v>67</v>
+      </c>
+      <c r="F29" s="179" t="s">
+        <v>199</v>
+      </c>
+      <c r="G29" s="179" t="s">
+        <v>128</v>
+      </c>
+      <c r="H29" s="180">
+        <v>7</v>
+      </c>
+      <c r="I29" s="180">
+        <v>8</v>
+      </c>
+      <c r="J29" s="180">
+        <v>0</v>
+      </c>
+      <c r="K29" s="180">
+        <v>8</v>
+      </c>
+      <c r="L29" s="180">
+        <v>112</v>
+      </c>
+      <c r="M29" s="180">
+        <v>100</v>
+      </c>
+      <c r="N29" s="180">
+        <v>0</v>
+      </c>
+      <c r="O29" s="180">
+        <v>100</v>
+      </c>
+      <c r="P29" s="180">
+        <v>4</v>
+      </c>
+      <c r="Q29" s="180">
+        <v>4</v>
+      </c>
+      <c r="R29" s="180">
+        <v>0</v>
+      </c>
+      <c r="S29" s="180">
+        <v>6</v>
+      </c>
+      <c r="T29" s="180">
+        <v>168</v>
+      </c>
+      <c r="U29" s="180">
+        <v>150</v>
+      </c>
+      <c r="V29" s="180">
+        <v>0</v>
+      </c>
+      <c r="W29" s="180">
+        <v>100</v>
+      </c>
+      <c r="X29" s="180">
+        <v>2</v>
+      </c>
+      <c r="Y29" s="180">
+        <v>2</v>
+      </c>
+      <c r="Z29" s="180">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="180">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="180">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="180">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="180">
+        <v>1</v>
+      </c>
+      <c r="AE29" s="180">
+        <v>-100</v>
+      </c>
+      <c r="AF29" s="180">
+        <v>4</v>
+      </c>
+      <c r="AG29" s="180">
+        <v>5</v>
+      </c>
+      <c r="AH29" s="180">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="180">
+        <v>3</v>
+      </c>
+      <c r="AJ29" s="180">
+        <v>132.80000000000001</v>
+      </c>
+      <c r="AK29" s="180">
+        <v>140</v>
+      </c>
+      <c r="AL29" s="180">
+        <v>1</v>
+      </c>
+      <c r="AM29" s="180">
+        <v>200</v>
+      </c>
+      <c r="AN29" s="180">
+        <v>4</v>
+      </c>
+      <c r="AO29" s="180">
+        <v>4</v>
+      </c>
+      <c r="AP29" s="180">
+        <v>0</v>
+      </c>
+      <c r="AQ29" s="180">
+        <v>1</v>
+      </c>
+      <c r="AR29" s="180">
+        <v>28</v>
+      </c>
+      <c r="AS29" s="180">
+        <v>25</v>
+      </c>
+      <c r="AT29" s="180">
+        <v>0</v>
+      </c>
+      <c r="AU29" s="180">
+        <v>100</v>
+      </c>
+      <c r="AV29" s="180">
+        <v>27</v>
+      </c>
+      <c r="AW29" s="180">
+        <v>30</v>
+      </c>
+      <c r="AX29" s="180">
+        <v>0</v>
+      </c>
+      <c r="AY29" s="180">
+        <v>33</v>
+      </c>
+      <c r="AZ29" s="180">
+        <v>123.2</v>
+      </c>
+      <c r="BA29" s="180">
+        <v>110</v>
+      </c>
+      <c r="BB29" s="180">
+        <v>0</v>
+      </c>
+      <c r="BC29" s="180">
+        <v>100</v>
+      </c>
+      <c r="BD29" s="180">
+        <v>4</v>
+      </c>
+      <c r="BE29" s="180">
+        <v>5</v>
+      </c>
+      <c r="BF29" s="180">
+        <v>1</v>
+      </c>
+      <c r="BG29" s="180">
+        <v>5</v>
+      </c>
+      <c r="BH29" s="180">
+        <v>112</v>
+      </c>
+      <c r="BI29" s="180">
+        <v>100</v>
+      </c>
+      <c r="BJ29" s="180">
+        <v>0</v>
+      </c>
+      <c r="BK29" s="180">
+        <v>100</v>
+      </c>
+      <c r="BL29" s="180">
+        <v>0</v>
+      </c>
+      <c r="BM29" s="180">
+        <v>0</v>
+      </c>
+      <c r="BN29" s="180">
+        <v>0</v>
+      </c>
+      <c r="BO29" s="180">
+        <v>0</v>
+      </c>
+      <c r="BP29" s="180">
+        <v>100</v>
+      </c>
+      <c r="BQ29" s="180">
+        <v>100</v>
+      </c>
+      <c r="BR29" s="180">
+        <v>0</v>
+      </c>
+      <c r="BS29" s="180">
+        <v>100</v>
+      </c>
+      <c r="BT29" s="180">
+        <v>1</v>
+      </c>
+      <c r="BU29" s="180">
+        <v>1</v>
+      </c>
+      <c r="BV29" s="180">
+        <v>0</v>
+      </c>
+      <c r="BW29" s="180">
+        <v>1</v>
+      </c>
+      <c r="BX29" s="180">
+        <v>112</v>
+      </c>
+      <c r="BY29" s="180">
+        <v>100</v>
+      </c>
+      <c r="BZ29" s="180">
+        <v>0</v>
+      </c>
+      <c r="CA29" s="180">
+        <v>100</v>
+      </c>
+      <c r="CB29" s="180">
+        <v>8</v>
+      </c>
+      <c r="CC29" s="180">
+        <v>9</v>
+      </c>
+      <c r="CD29" s="180">
+        <v>0</v>
+      </c>
+      <c r="CE29" s="180">
+        <v>12</v>
+      </c>
+      <c r="CF29" s="180">
+        <v>149.33000000000001</v>
+      </c>
+      <c r="CG29" s="180">
+        <v>133.33000000000001</v>
+      </c>
+      <c r="CH29" s="180">
+        <v>0</v>
+      </c>
+      <c r="CI29" s="180">
+        <v>100</v>
+      </c>
+      <c r="CJ29" s="180">
+        <v>4</v>
+      </c>
+      <c r="CK29" s="180">
+        <v>5</v>
+      </c>
+      <c r="CL29" s="180">
+        <v>0</v>
+      </c>
+      <c r="CM29" s="180">
+        <v>6</v>
+      </c>
+      <c r="CN29" s="180">
+        <v>134.4</v>
+      </c>
+      <c r="CO29" s="180">
+        <v>120</v>
+      </c>
+      <c r="CP29" s="180">
+        <v>0</v>
+      </c>
+      <c r="CQ29" s="180">
+        <v>100</v>
+      </c>
+      <c r="CR29" s="180">
+        <v>4</v>
+      </c>
+      <c r="CS29" s="180">
+        <v>4</v>
+      </c>
+      <c r="CT29" s="180">
+        <v>0</v>
+      </c>
+      <c r="CU29" s="180">
+        <v>4</v>
+      </c>
+      <c r="CV29" s="180">
+        <v>112</v>
+      </c>
+      <c r="CW29" s="180">
+        <v>100</v>
+      </c>
+      <c r="CX29" s="180">
+        <v>0</v>
+      </c>
+      <c r="CY29" s="180">
+        <v>100</v>
+      </c>
+      <c r="CZ29" s="180">
+        <v>1</v>
+      </c>
+      <c r="DA29" s="180">
+        <v>1</v>
+      </c>
+      <c r="DB29" s="180">
+        <v>0</v>
+      </c>
+      <c r="DC29" s="180">
+        <v>1</v>
+      </c>
+      <c r="DD29" s="180">
+        <v>112</v>
+      </c>
+      <c r="DE29" s="180">
+        <v>100</v>
+      </c>
+      <c r="DF29" s="180">
+        <v>0</v>
+      </c>
+      <c r="DG29" s="180">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:111" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="E30" s="182" t="s">
         <v>253</v>
       </c>
-      <c r="F29" s="182" t="s">
+      <c r="F30" s="182" t="s">
         <v>254</v>
       </c>
-      <c r="G29" s="182" t="s">
+      <c r="G30" s="182" t="s">
         <v>179</v>
       </c>
-      <c r="H29" s="180">
+      <c r="H30" s="180">
         <v>3</v>
       </c>
-      <c r="I29" s="180">
+      <c r="I30" s="180">
         <v>3</v>
       </c>
-      <c r="J29" s="180">
-        <v>1</v>
-      </c>
-      <c r="K29" s="180">
+      <c r="J30" s="180">
+        <v>0</v>
+      </c>
+      <c r="K30" s="180">
         <v>3</v>
       </c>
-      <c r="L29" s="180">
-        <v>116.67</v>
-      </c>
-      <c r="M29" s="180">
-        <v>100</v>
-      </c>
-      <c r="N29" s="180">
-        <v>0</v>
-      </c>
-      <c r="O29" s="180">
-        <v>100</v>
-      </c>
-      <c r="P29" s="180">
-        <v>2</v>
-      </c>
-      <c r="Q29" s="180">
-        <v>2</v>
-      </c>
-      <c r="R29" s="180">
-        <v>0</v>
-      </c>
-      <c r="S29" s="180">
-        <v>2</v>
-      </c>
-      <c r="T29" s="180">
-        <v>116.67</v>
-      </c>
-      <c r="U29" s="180">
-        <v>100</v>
-      </c>
-      <c r="V29" s="180">
-        <v>0</v>
-      </c>
-      <c r="W29" s="180">
-        <v>100</v>
-      </c>
-      <c r="X29" s="180">
-        <v>1</v>
-      </c>
-      <c r="Y29" s="180">
-        <v>1</v>
-      </c>
-      <c r="Z29" s="180">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="180">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="180">
-        <v>0</v>
-      </c>
-      <c r="AC29" s="180">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="180">
-        <v>0</v>
-      </c>
-      <c r="AE29" s="180">
-        <v>100</v>
-      </c>
-      <c r="AF29" s="180">
-        <v>2</v>
-      </c>
-      <c r="AG29" s="180">
-        <v>2</v>
-      </c>
-      <c r="AH29" s="180">
-        <v>0</v>
-      </c>
-      <c r="AI29" s="180">
-        <v>0</v>
-      </c>
-      <c r="AJ29" s="180">
+      <c r="L30" s="180">
+        <v>112</v>
+      </c>
+      <c r="M30" s="180">
+        <v>100</v>
+      </c>
+      <c r="N30" s="180">
+        <v>0</v>
+      </c>
+      <c r="O30" s="180">
+        <v>100</v>
+      </c>
+      <c r="P30" s="180">
+        <v>2</v>
+      </c>
+      <c r="Q30" s="180">
+        <v>2</v>
+      </c>
+      <c r="R30" s="180">
+        <v>0</v>
+      </c>
+      <c r="S30" s="180">
+        <v>2</v>
+      </c>
+      <c r="T30" s="180">
+        <v>112</v>
+      </c>
+      <c r="U30" s="180">
+        <v>100</v>
+      </c>
+      <c r="V30" s="180">
+        <v>0</v>
+      </c>
+      <c r="W30" s="180">
+        <v>100</v>
+      </c>
+      <c r="X30" s="180">
+        <v>1</v>
+      </c>
+      <c r="Y30" s="180">
+        <v>1</v>
+      </c>
+      <c r="Z30" s="180">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="180">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="180">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="180">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="180">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="180">
+        <v>100</v>
+      </c>
+      <c r="AF30" s="180">
+        <v>2</v>
+      </c>
+      <c r="AG30" s="180">
+        <v>2</v>
+      </c>
+      <c r="AH30" s="180">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="180">
+        <v>1</v>
+      </c>
+      <c r="AJ30" s="180">
+        <v>144</v>
+      </c>
+      <c r="AK30" s="180">
+        <v>150</v>
+      </c>
+      <c r="AL30" s="180">
+        <v>0</v>
+      </c>
+      <c r="AM30" s="180">
+        <v>100</v>
+      </c>
+      <c r="AN30" s="180">
+        <v>3</v>
+      </c>
+      <c r="AO30" s="180">
+        <v>3</v>
+      </c>
+      <c r="AP30" s="180">
+        <v>0</v>
+      </c>
+      <c r="AQ30" s="180">
+        <v>0</v>
+      </c>
+      <c r="AR30" s="180">
+        <v>0</v>
+      </c>
+      <c r="AS30" s="180">
+        <v>0</v>
+      </c>
+      <c r="AT30" s="180">
+        <v>0</v>
+      </c>
+      <c r="AU30" s="180">
+        <v>100</v>
+      </c>
+      <c r="AV30" s="180">
+        <v>13</v>
+      </c>
+      <c r="AW30" s="180">
+        <v>14</v>
+      </c>
+      <c r="AX30" s="180">
+        <v>0</v>
+      </c>
+      <c r="AY30" s="180">
+        <v>14</v>
+      </c>
+      <c r="AZ30" s="180">
+        <v>112</v>
+      </c>
+      <c r="BA30" s="180">
+        <v>100</v>
+      </c>
+      <c r="BB30" s="180">
+        <v>0</v>
+      </c>
+      <c r="BC30" s="180">
+        <v>100</v>
+      </c>
+      <c r="BD30" s="180">
+        <v>2</v>
+      </c>
+      <c r="BE30" s="180">
+        <v>2</v>
+      </c>
+      <c r="BF30" s="180">
+        <v>0</v>
+      </c>
+      <c r="BG30" s="180">
+        <v>0</v>
+      </c>
+      <c r="BH30" s="180">
+        <v>0</v>
+      </c>
+      <c r="BI30" s="180">
+        <v>0</v>
+      </c>
+      <c r="BJ30" s="180">
+        <v>0</v>
+      </c>
+      <c r="BK30" s="180">
+        <v>100</v>
+      </c>
+      <c r="BL30" s="180">
+        <v>0</v>
+      </c>
+      <c r="BM30" s="180">
+        <v>0</v>
+      </c>
+      <c r="BN30" s="180">
+        <v>0</v>
+      </c>
+      <c r="BO30" s="180">
+        <v>0</v>
+      </c>
+      <c r="BP30" s="180">
+        <v>100</v>
+      </c>
+      <c r="BQ30" s="180">
+        <v>100</v>
+      </c>
+      <c r="BR30" s="180">
+        <v>0</v>
+      </c>
+      <c r="BS30" s="180">
+        <v>100</v>
+      </c>
+      <c r="BT30" s="180">
+        <v>1</v>
+      </c>
+      <c r="BU30" s="180">
+        <v>1</v>
+      </c>
+      <c r="BV30" s="180">
+        <v>0</v>
+      </c>
+      <c r="BW30" s="180">
+        <v>1</v>
+      </c>
+      <c r="BX30" s="180">
+        <v>112</v>
+      </c>
+      <c r="BY30" s="180">
+        <v>100</v>
+      </c>
+      <c r="BZ30" s="180">
+        <v>1</v>
+      </c>
+      <c r="CA30" s="180">
+        <v>0</v>
+      </c>
+      <c r="CB30" s="180">
+        <v>4</v>
+      </c>
+      <c r="CC30" s="180">
+        <v>5</v>
+      </c>
+      <c r="CD30" s="180">
+        <v>0</v>
+      </c>
+      <c r="CE30" s="180">
+        <v>3</v>
+      </c>
+      <c r="CF30" s="180">
+        <v>67.2</v>
+      </c>
+      <c r="CG30" s="180">
+        <v>60</v>
+      </c>
+      <c r="CH30" s="180">
+        <v>0</v>
+      </c>
+      <c r="CI30" s="180">
+        <v>100</v>
+      </c>
+      <c r="CJ30" s="180">
+        <v>3</v>
+      </c>
+      <c r="CK30" s="180">
+        <v>3</v>
+      </c>
+      <c r="CL30" s="180">
+        <v>0</v>
+      </c>
+      <c r="CM30" s="180">
+        <v>1</v>
+      </c>
+      <c r="CN30" s="180">
+        <v>37.33</v>
+      </c>
+      <c r="CO30" s="180">
+        <v>33.33</v>
+      </c>
+      <c r="CP30" s="180">
+        <v>0</v>
+      </c>
+      <c r="CQ30" s="180">
+        <v>100</v>
+      </c>
+      <c r="CR30" s="180">
+        <v>3</v>
+      </c>
+      <c r="CS30" s="180">
+        <v>3</v>
+      </c>
+      <c r="CT30" s="180">
+        <v>0</v>
+      </c>
+      <c r="CU30" s="180">
+        <v>4</v>
+      </c>
+      <c r="CV30" s="180">
+        <v>149.33000000000001</v>
+      </c>
+      <c r="CW30" s="180">
+        <v>133.33000000000001</v>
+      </c>
+      <c r="CX30" s="180">
+        <v>0</v>
+      </c>
+      <c r="CY30" s="180">
+        <v>100</v>
+      </c>
+      <c r="CZ30" s="180">
+        <v>1</v>
+      </c>
+      <c r="DA30" s="180">
+        <v>1</v>
+      </c>
+      <c r="DB30" s="180">
+        <v>0</v>
+      </c>
+      <c r="DC30" s="180">
+        <v>2</v>
+      </c>
+      <c r="DD30" s="180">
+        <v>224</v>
+      </c>
+      <c r="DE30" s="180">
         <v>200</v>
       </c>
-      <c r="AK29" s="180">
-        <v>200</v>
-      </c>
-      <c r="AL29" s="180">
-        <v>0</v>
-      </c>
-      <c r="AM29" s="180">
-        <v>100</v>
-      </c>
-      <c r="AN29" s="180">
-        <v>3</v>
-      </c>
-      <c r="AO29" s="180">
-        <v>3</v>
-      </c>
-      <c r="AP29" s="180">
-        <v>0</v>
-      </c>
-      <c r="AQ29" s="180">
-        <v>0</v>
-      </c>
-      <c r="AR29" s="180">
-        <v>0</v>
-      </c>
-      <c r="AS29" s="180">
-        <v>0</v>
-      </c>
-      <c r="AT29" s="180">
-        <v>0</v>
-      </c>
-      <c r="AU29" s="180">
-        <v>100</v>
-      </c>
-      <c r="AV29" s="180">
-        <v>12</v>
-      </c>
-      <c r="AW29" s="180">
-        <v>14</v>
-      </c>
-      <c r="AX29" s="180">
-        <v>0</v>
-      </c>
-      <c r="AY29" s="180">
-        <v>13</v>
-      </c>
-      <c r="AZ29" s="180">
-        <v>108.33</v>
-      </c>
-      <c r="BA29" s="180">
-        <v>92.86</v>
-      </c>
-      <c r="BB29" s="180">
-        <v>0</v>
-      </c>
-      <c r="BC29" s="180">
-        <v>100</v>
-      </c>
-      <c r="BD29" s="180">
-        <v>2</v>
-      </c>
-      <c r="BE29" s="180">
-        <v>2</v>
-      </c>
-      <c r="BF29" s="180">
-        <v>0</v>
-      </c>
-      <c r="BG29" s="180">
-        <v>0</v>
-      </c>
-      <c r="BH29" s="180">
-        <v>0</v>
-      </c>
-      <c r="BI29" s="180">
-        <v>0</v>
-      </c>
-      <c r="BJ29" s="180">
-        <v>0</v>
-      </c>
-      <c r="BK29" s="180">
-        <v>100</v>
-      </c>
-      <c r="BL29" s="180">
-        <v>0</v>
-      </c>
-      <c r="BM29" s="180">
-        <v>0</v>
-      </c>
-      <c r="BN29" s="180">
-        <v>0</v>
-      </c>
-      <c r="BO29" s="180">
-        <v>0</v>
-      </c>
-      <c r="BP29" s="180">
-        <v>100</v>
-      </c>
-      <c r="BQ29" s="180">
-        <v>100</v>
-      </c>
-      <c r="BR29" s="180">
-        <v>0</v>
-      </c>
-      <c r="BS29" s="180">
-        <v>100</v>
-      </c>
-      <c r="BT29" s="180">
-        <v>1</v>
-      </c>
-      <c r="BU29" s="180">
-        <v>1</v>
-      </c>
-      <c r="BV29" s="180">
-        <v>1</v>
-      </c>
-      <c r="BW29" s="180">
-        <v>1</v>
-      </c>
-      <c r="BX29" s="180">
-        <v>116.67</v>
-      </c>
-      <c r="BY29" s="180">
-        <v>100</v>
-      </c>
-      <c r="BZ29" s="180">
-        <v>1</v>
-      </c>
-      <c r="CA29" s="180">
-        <v>0</v>
-      </c>
-      <c r="CB29" s="180">
-        <v>4</v>
-      </c>
-      <c r="CC29" s="180">
-        <v>5</v>
-      </c>
-      <c r="CD29" s="180">
-        <v>0</v>
-      </c>
-      <c r="CE29" s="180">
-        <v>3</v>
-      </c>
-      <c r="CF29" s="180">
-        <v>70</v>
-      </c>
-      <c r="CG29" s="180">
-        <v>60</v>
-      </c>
-      <c r="CH29" s="180">
-        <v>0</v>
-      </c>
-      <c r="CI29" s="180">
-        <v>100</v>
-      </c>
-      <c r="CJ29" s="180">
-        <v>3</v>
-      </c>
-      <c r="CK29" s="180">
-        <v>3</v>
-      </c>
-      <c r="CL29" s="180">
-        <v>0</v>
-      </c>
-      <c r="CM29" s="180">
-        <v>1</v>
-      </c>
-      <c r="CN29" s="180">
-        <v>38.89</v>
-      </c>
-      <c r="CO29" s="180">
-        <v>33.33</v>
-      </c>
-      <c r="CP29" s="180">
-        <v>0</v>
-      </c>
-      <c r="CQ29" s="180">
-        <v>100</v>
-      </c>
-      <c r="CR29" s="180">
-        <v>3</v>
-      </c>
-      <c r="CS29" s="180">
-        <v>3</v>
-      </c>
-      <c r="CT29" s="180">
-        <v>0</v>
-      </c>
-      <c r="CU29" s="180">
-        <v>4</v>
-      </c>
-      <c r="CV29" s="180">
-        <v>155.56</v>
-      </c>
-      <c r="CW29" s="180">
-        <v>133.33000000000001</v>
-      </c>
-      <c r="CX29" s="180">
-        <v>0</v>
-      </c>
-      <c r="CY29" s="180">
-        <v>100</v>
-      </c>
-      <c r="CZ29" s="180">
-        <v>1</v>
-      </c>
-      <c r="DA29" s="180">
-        <v>1</v>
-      </c>
-      <c r="DB29" s="180">
-        <v>0</v>
-      </c>
-      <c r="DC29" s="180">
-        <v>1</v>
-      </c>
-      <c r="DD29" s="180">
-        <v>116.67</v>
-      </c>
-      <c r="DE29" s="180">
-        <v>100</v>
-      </c>
-      <c r="DF29" s="180">
-        <v>0</v>
-      </c>
-      <c r="DG29" s="180">
+      <c r="DF30" s="180">
+        <v>0</v>
+      </c>
+      <c r="DG30" s="180">
         <v>100</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A6:DG6" xr:uid="{035AF4C2-379E-4E05-A870-198385941EC5}"/>
   <mergeCells count="16">
+    <mergeCell ref="X5:AE5"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="H5:O5"/>
+    <mergeCell ref="P5:W5"/>
     <mergeCell ref="CB5:CI5"/>
     <mergeCell ref="CJ5:CQ5"/>
     <mergeCell ref="CR5:CY5"/>
@@ -22595,12 +22741,6 @@
     <mergeCell ref="BD5:BK5"/>
     <mergeCell ref="BL5:BS5"/>
     <mergeCell ref="BT5:CA5"/>
-    <mergeCell ref="X5:AE5"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="H5:O5"/>
-    <mergeCell ref="P5:W5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -22698,7 +22838,7 @@
       <c r="A3" s="83" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="228" t="s">
+      <c r="B3" s="226" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="84" t="s">
@@ -22710,70 +22850,70 @@
       <c r="E3" s="230" t="s">
         <v>202</v>
       </c>
-      <c r="F3" s="226" t="s">
+      <c r="F3" s="228" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="226" t="s">
+      <c r="G3" s="228" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="226" t="s">
+      <c r="H3" s="228" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="226" t="s">
+      <c r="I3" s="228" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="226" t="s">
+      <c r="J3" s="228" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="226" t="s">
+      <c r="K3" s="228" t="s">
         <v>11</v>
       </c>
-      <c r="L3" s="226" t="s">
+      <c r="L3" s="228" t="s">
         <v>12</v>
       </c>
-      <c r="M3" s="226" t="s">
+      <c r="M3" s="228" t="s">
         <v>203</v>
       </c>
-      <c r="N3" s="226" t="s">
+      <c r="N3" s="228" t="s">
         <v>255</v>
       </c>
-      <c r="O3" s="226" t="s">
+      <c r="O3" s="228" t="s">
         <v>14</v>
       </c>
-      <c r="P3" s="226" t="s">
+      <c r="P3" s="228" t="s">
         <v>15</v>
       </c>
-      <c r="Q3" s="226" t="s">
+      <c r="Q3" s="228" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="226" t="s">
+      <c r="R3" s="228" t="s">
         <v>17</v>
       </c>
-      <c r="S3" s="226" t="s">
+      <c r="S3" s="228" t="s">
         <v>18</v>
       </c>
       <c r="T3" s="82"/>
     </row>
     <row r="4" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="83"/>
-      <c r="B4" s="229"/>
+      <c r="B4" s="227"/>
       <c r="C4" s="84"/>
       <c r="D4" s="84"/>
       <c r="E4" s="231"/>
-      <c r="F4" s="227"/>
-      <c r="G4" s="227"/>
-      <c r="H4" s="227"/>
-      <c r="I4" s="227"/>
-      <c r="J4" s="227"/>
-      <c r="K4" s="227"/>
-      <c r="L4" s="227"/>
-      <c r="M4" s="227"/>
-      <c r="N4" s="227"/>
-      <c r="O4" s="227"/>
-      <c r="P4" s="227"/>
-      <c r="Q4" s="227"/>
-      <c r="R4" s="227"/>
-      <c r="S4" s="227"/>
+      <c r="F4" s="229"/>
+      <c r="G4" s="229"/>
+      <c r="H4" s="229"/>
+      <c r="I4" s="229"/>
+      <c r="J4" s="229"/>
+      <c r="K4" s="229"/>
+      <c r="L4" s="229"/>
+      <c r="M4" s="229"/>
+      <c r="N4" s="229"/>
+      <c r="O4" s="229"/>
+      <c r="P4" s="229"/>
+      <c r="Q4" s="229"/>
+      <c r="R4" s="229"/>
+      <c r="S4" s="229"/>
       <c r="T4" s="82"/>
     </row>
     <row r="5" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.45">
@@ -24091,6 +24231,12 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="S3:S4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="R3:R4"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="H3:H4"/>
@@ -24101,12 +24247,6 @@
     <mergeCell ref="K3:K4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="E3:E4"/>
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="S3:S4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="R3:R4"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.69991251615088756" right="0.69991251615088756" top="0.74990626395218019" bottom="0.74990626395218019" header="0.29996251027415122" footer="0.29996251027415122"/>
@@ -24690,68 +24830,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:48" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="239" t="s">
+      <c r="A1" s="241" t="s">
         <v>209</v>
       </c>
-      <c r="B1" s="239"/>
-      <c r="C1" s="239"/>
-      <c r="D1" s="239"/>
-      <c r="E1" s="239"/>
-      <c r="F1" s="239"/>
-      <c r="G1" s="239"/>
-      <c r="H1" s="239"/>
-      <c r="I1" s="239"/>
-      <c r="J1" s="239"/>
-      <c r="K1" s="239"/>
-      <c r="M1" s="242" t="s">
+      <c r="B1" s="241"/>
+      <c r="C1" s="241"/>
+      <c r="D1" s="241"/>
+      <c r="E1" s="241"/>
+      <c r="F1" s="241"/>
+      <c r="G1" s="241"/>
+      <c r="H1" s="241"/>
+      <c r="I1" s="241"/>
+      <c r="J1" s="241"/>
+      <c r="K1" s="241"/>
+      <c r="M1" s="244" t="s">
         <v>210</v>
       </c>
-      <c r="N1" s="242"/>
-      <c r="O1" s="242"/>
-      <c r="P1" s="242"/>
-      <c r="Q1" s="242"/>
-      <c r="R1" s="242"/>
-      <c r="S1" s="242"/>
-      <c r="T1" s="242"/>
-      <c r="U1" s="242"/>
-      <c r="V1" s="242"/>
-      <c r="W1" s="242"/>
-      <c r="X1" s="242"/>
-      <c r="Y1" s="242"/>
-      <c r="Z1" s="242"/>
+      <c r="N1" s="244"/>
+      <c r="O1" s="244"/>
+      <c r="P1" s="244"/>
+      <c r="Q1" s="244"/>
+      <c r="R1" s="244"/>
+      <c r="S1" s="244"/>
+      <c r="T1" s="244"/>
+      <c r="U1" s="244"/>
+      <c r="V1" s="244"/>
+      <c r="W1" s="244"/>
+      <c r="X1" s="244"/>
+      <c r="Y1" s="244"/>
+      <c r="Z1" s="244"/>
     </row>
     <row r="2" spans="1:48" ht="24.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="240"/>
-      <c r="B2" s="240"/>
-      <c r="C2" s="240"/>
-      <c r="D2" s="240"/>
-      <c r="E2" s="240"/>
-      <c r="F2" s="240"/>
-      <c r="G2" s="240"/>
-      <c r="H2" s="240"/>
-      <c r="I2" s="240"/>
-      <c r="J2" s="240"/>
-      <c r="K2" s="240"/>
-      <c r="M2" s="243"/>
-      <c r="N2" s="243"/>
-      <c r="O2" s="243"/>
-      <c r="P2" s="243"/>
-      <c r="Q2" s="243"/>
-      <c r="R2" s="243"/>
-      <c r="S2" s="243"/>
-      <c r="T2" s="243"/>
-      <c r="U2" s="243"/>
-      <c r="V2" s="243"/>
-      <c r="W2" s="243"/>
-      <c r="X2" s="243"/>
-      <c r="Y2" s="243"/>
-      <c r="Z2" s="243"/>
+      <c r="A2" s="242"/>
+      <c r="B2" s="242"/>
+      <c r="C2" s="242"/>
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
+      <c r="G2" s="242"/>
+      <c r="H2" s="242"/>
+      <c r="I2" s="242"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="242"/>
+      <c r="M2" s="245"/>
+      <c r="N2" s="245"/>
+      <c r="O2" s="245"/>
+      <c r="P2" s="245"/>
+      <c r="Q2" s="245"/>
+      <c r="R2" s="245"/>
+      <c r="S2" s="245"/>
+      <c r="T2" s="245"/>
+      <c r="U2" s="245"/>
+      <c r="V2" s="245"/>
+      <c r="W2" s="245"/>
+      <c r="X2" s="245"/>
+      <c r="Y2" s="245"/>
+      <c r="Z2" s="245"/>
     </row>
     <row r="3" spans="1:48" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="236" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="237" t="s">
+      <c r="A3" s="238" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="239" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="28" t="s">
@@ -24781,70 +24921,70 @@
       <c r="K3" s="28" t="s">
         <v>218</v>
       </c>
-      <c r="M3" s="241" t="s">
+      <c r="M3" s="243" t="s">
         <v>34</v>
       </c>
-      <c r="N3" s="187" t="s">
+      <c r="N3" s="185" t="s">
         <v>219</v>
       </c>
-      <c r="O3" s="188"/>
-      <c r="P3" s="188"/>
-      <c r="Q3" s="188"/>
-      <c r="R3" s="244" t="s">
+      <c r="O3" s="186"/>
+      <c r="P3" s="186"/>
+      <c r="Q3" s="186"/>
+      <c r="R3" s="236" t="s">
         <v>220</v>
       </c>
-      <c r="S3" s="187" t="s">
+      <c r="S3" s="185" t="s">
         <v>221</v>
       </c>
-      <c r="T3" s="188"/>
-      <c r="U3" s="188"/>
-      <c r="V3" s="188"/>
-      <c r="W3" s="244" t="s">
+      <c r="T3" s="186"/>
+      <c r="U3" s="186"/>
+      <c r="V3" s="186"/>
+      <c r="W3" s="236" t="s">
         <v>220</v>
       </c>
-      <c r="X3" s="190" t="s">
+      <c r="X3" s="198" t="s">
         <v>41</v>
       </c>
-      <c r="Y3" s="191"/>
-      <c r="Z3" s="191"/>
-      <c r="AA3" s="244" t="s">
+      <c r="Y3" s="199"/>
+      <c r="Z3" s="199"/>
+      <c r="AA3" s="236" t="s">
         <v>220</v>
       </c>
       <c r="AB3" s="65"/>
-      <c r="AC3" s="187" t="s">
+      <c r="AC3" s="185" t="s">
         <v>42</v>
       </c>
-      <c r="AD3" s="188"/>
-      <c r="AE3" s="188"/>
-      <c r="AF3" s="188"/>
-      <c r="AG3" s="187" t="s">
+      <c r="AD3" s="186"/>
+      <c r="AE3" s="186"/>
+      <c r="AF3" s="186"/>
+      <c r="AG3" s="185" t="s">
         <v>43</v>
       </c>
-      <c r="AH3" s="188"/>
-      <c r="AI3" s="188"/>
-      <c r="AJ3" s="188"/>
-      <c r="AK3" s="187" t="s">
+      <c r="AH3" s="186"/>
+      <c r="AI3" s="186"/>
+      <c r="AJ3" s="186"/>
+      <c r="AK3" s="185" t="s">
         <v>44</v>
       </c>
-      <c r="AL3" s="188"/>
-      <c r="AM3" s="188"/>
-      <c r="AN3" s="188"/>
-      <c r="AO3" s="187" t="s">
+      <c r="AL3" s="186"/>
+      <c r="AM3" s="186"/>
+      <c r="AN3" s="186"/>
+      <c r="AO3" s="185" t="s">
         <v>46</v>
       </c>
-      <c r="AP3" s="188"/>
-      <c r="AQ3" s="188"/>
-      <c r="AR3" s="188"/>
-      <c r="AS3" s="187" t="s">
+      <c r="AP3" s="186"/>
+      <c r="AQ3" s="186"/>
+      <c r="AR3" s="186"/>
+      <c r="AS3" s="185" t="s">
         <v>47</v>
       </c>
-      <c r="AT3" s="188"/>
-      <c r="AU3" s="188"/>
-      <c r="AV3" s="188"/>
+      <c r="AT3" s="186"/>
+      <c r="AU3" s="186"/>
+      <c r="AV3" s="186"/>
     </row>
     <row r="4" spans="1:48" ht="22.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="236"/>
-      <c r="B4" s="238"/>
+      <c r="A4" s="238"/>
+      <c r="B4" s="240"/>
       <c r="C4" s="24">
         <f t="shared" ref="C4:K4" si="0">SUM(C5:C19)</f>
         <v>15</v>
@@ -24881,7 +25021,7 @@
         <f t="shared" si="0"/>
         <v>134</v>
       </c>
-      <c r="M4" s="241"/>
+      <c r="M4" s="243"/>
       <c r="N4" s="8" t="s">
         <v>2</v>
       </c>
@@ -24894,7 +25034,7 @@
       <c r="Q4" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="R4" s="245"/>
+      <c r="R4" s="237"/>
       <c r="S4" s="8" t="s">
         <v>2</v>
       </c>
@@ -24907,7 +25047,7 @@
       <c r="V4" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="W4" s="245"/>
+      <c r="W4" s="237"/>
       <c r="X4" s="8" t="s">
         <v>2</v>
       </c>
@@ -24917,7 +25057,7 @@
       <c r="Z4" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="AA4" s="245"/>
+      <c r="AA4" s="237"/>
       <c r="AB4" s="45" t="s">
         <v>59</v>
       </c>
@@ -27306,6 +27446,12 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="A1:K2"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="N3:Q3"/>
+    <mergeCell ref="M1:Z2"/>
     <mergeCell ref="AS3:AV3"/>
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="W3:W4"/>
@@ -27316,12 +27462,6 @@
     <mergeCell ref="AK3:AN3"/>
     <mergeCell ref="AO3:AR3"/>
     <mergeCell ref="S3:V3"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="A1:K2"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="N3:Q3"/>
-    <mergeCell ref="M1:Z2"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="P5:P20">
@@ -27461,44 +27601,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="246"/>
-      <c r="B1" s="246"/>
-      <c r="C1" s="246"/>
-      <c r="D1" s="246"/>
-      <c r="E1" s="246"/>
-      <c r="F1" s="246"/>
-      <c r="G1" s="246"/>
-      <c r="H1" s="246"/>
-      <c r="I1" s="246"/>
-      <c r="J1" s="246"/>
-      <c r="K1" s="246"/>
-      <c r="L1" s="246"/>
-      <c r="M1" s="246"/>
-      <c r="N1" s="246"/>
-      <c r="O1" s="246"/>
-      <c r="P1" s="246"/>
+      <c r="A1" s="248"/>
+      <c r="B1" s="248"/>
+      <c r="C1" s="248"/>
+      <c r="D1" s="248"/>
+      <c r="E1" s="248"/>
+      <c r="F1" s="248"/>
+      <c r="G1" s="248"/>
+      <c r="H1" s="248"/>
+      <c r="I1" s="248"/>
+      <c r="J1" s="248"/>
+      <c r="K1" s="248"/>
+      <c r="L1" s="248"/>
+      <c r="M1" s="248"/>
+      <c r="N1" s="248"/>
+      <c r="O1" s="248"/>
+      <c r="P1" s="248"/>
     </row>
     <row r="2" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="247"/>
-      <c r="B2" s="247"/>
-      <c r="C2" s="247"/>
-      <c r="D2" s="247"/>
-      <c r="E2" s="247"/>
-      <c r="F2" s="247"/>
-      <c r="G2" s="247"/>
-      <c r="H2" s="247"/>
-      <c r="I2" s="247"/>
-      <c r="J2" s="247"/>
-      <c r="K2" s="247"/>
-      <c r="L2" s="247"/>
-      <c r="M2" s="247"/>
-      <c r="N2" s="247"/>
-      <c r="O2" s="247"/>
-      <c r="P2" s="247"/>
+      <c r="A2" s="249"/>
+      <c r="B2" s="249"/>
+      <c r="C2" s="249"/>
+      <c r="D2" s="249"/>
+      <c r="E2" s="249"/>
+      <c r="F2" s="249"/>
+      <c r="G2" s="249"/>
+      <c r="H2" s="249"/>
+      <c r="I2" s="249"/>
+      <c r="J2" s="249"/>
+      <c r="K2" s="249"/>
+      <c r="L2" s="249"/>
+      <c r="M2" s="249"/>
+      <c r="N2" s="249"/>
+      <c r="O2" s="249"/>
+      <c r="P2" s="249"/>
     </row>
     <row r="3" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="248"/>
-      <c r="B3" s="248"/>
+      <c r="A3" s="250"/>
+      <c r="B3" s="250"/>
       <c r="C3" s="116"/>
       <c r="D3" s="116"/>
       <c r="E3" s="116"/>
@@ -27515,10 +27655,10 @@
       <c r="P3" s="116"/>
     </row>
     <row r="4" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="250" t="s">
+      <c r="A4" s="252" t="s">
         <v>224</v>
       </c>
-      <c r="B4" s="250" t="s">
+      <c r="B4" s="252" t="s">
         <v>39</v>
       </c>
       <c r="C4" s="124"/>
@@ -27526,70 +27666,70 @@
       <c r="E4" s="124"/>
       <c r="F4" s="124"/>
       <c r="G4" s="124"/>
-      <c r="H4" s="249"/>
-      <c r="I4" s="249"/>
-      <c r="J4" s="249"/>
-      <c r="K4" s="249"/>
-      <c r="L4" s="249"/>
-      <c r="M4" s="249"/>
-      <c r="N4" s="249"/>
-      <c r="O4" s="249"/>
-      <c r="P4" s="249"/>
+      <c r="H4" s="251"/>
+      <c r="I4" s="251"/>
+      <c r="J4" s="251"/>
+      <c r="K4" s="251"/>
+      <c r="L4" s="251"/>
+      <c r="M4" s="251"/>
+      <c r="N4" s="251"/>
+      <c r="O4" s="251"/>
+      <c r="P4" s="251"/>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A5" s="253"/>
-      <c r="B5" s="253"/>
-      <c r="C5" s="250" t="s">
+      <c r="A5" s="255"/>
+      <c r="B5" s="255"/>
+      <c r="C5" s="252" t="s">
         <v>225</v>
       </c>
-      <c r="D5" s="250" t="s">
+      <c r="D5" s="252" t="s">
         <v>226</v>
       </c>
-      <c r="E5" s="251"/>
-      <c r="F5" s="250" t="s">
+      <c r="E5" s="253"/>
+      <c r="F5" s="252" t="s">
         <v>227</v>
       </c>
-      <c r="G5" s="251"/>
-      <c r="H5" s="250" t="s">
+      <c r="G5" s="253"/>
+      <c r="H5" s="252" t="s">
         <v>228</v>
       </c>
-      <c r="I5" s="251"/>
-      <c r="J5" s="250" t="s">
+      <c r="I5" s="253"/>
+      <c r="J5" s="252" t="s">
         <v>229</v>
       </c>
-      <c r="K5" s="251"/>
-      <c r="L5" s="254" t="s">
+      <c r="K5" s="253"/>
+      <c r="L5" s="256" t="s">
         <v>230</v>
       </c>
-      <c r="M5" s="251"/>
-      <c r="N5" s="249" t="s">
+      <c r="M5" s="253"/>
+      <c r="N5" s="251" t="s">
         <v>231</v>
       </c>
-      <c r="O5" s="255"/>
-      <c r="P5" s="250" t="s">
+      <c r="O5" s="257"/>
+      <c r="P5" s="252" t="s">
         <v>235</v>
       </c>
-      <c r="R5" s="256" t="s">
+      <c r="R5" s="246" t="s">
         <v>34</v>
       </c>
-      <c r="S5" s="256" t="s">
+      <c r="S5" s="246" t="s">
         <v>258</v>
       </c>
-      <c r="T5" s="256" t="s">
+      <c r="T5" s="246" t="s">
         <v>259</v>
       </c>
-      <c r="U5" s="256" t="s">
+      <c r="U5" s="246" t="s">
         <v>261</v>
       </c>
-      <c r="V5" s="257" t="s">
+      <c r="V5" s="247" t="s">
         <v>260</v>
       </c>
       <c r="W5" s="155"/>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A6" s="252"/>
-      <c r="B6" s="252"/>
-      <c r="C6" s="253"/>
+      <c r="A6" s="254"/>
+      <c r="B6" s="254"/>
+      <c r="C6" s="255"/>
       <c r="D6" s="117" t="s">
         <v>2</v>
       </c>
@@ -27626,12 +27766,12 @@
       <c r="O6" s="117" t="s">
         <v>232</v>
       </c>
-      <c r="P6" s="252"/>
-      <c r="R6" s="256"/>
-      <c r="S6" s="256"/>
-      <c r="T6" s="256"/>
-      <c r="U6" s="256"/>
-      <c r="V6" s="256"/>
+      <c r="P6" s="254"/>
+      <c r="R6" s="246"/>
+      <c r="S6" s="246"/>
+      <c r="T6" s="246"/>
+      <c r="U6" s="246"/>
+      <c r="V6" s="246"/>
       <c r="W6" s="155"/>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.45">
@@ -28905,11 +29045,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="U5:U6"/>
-    <mergeCell ref="V5:V6"/>
-    <mergeCell ref="R5:R6"/>
-    <mergeCell ref="S5:S6"/>
-    <mergeCell ref="T5:T6"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
     <mergeCell ref="A3:B3"/>
@@ -28924,6 +29059,11 @@
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="L5:M5"/>
     <mergeCell ref="N5:O5"/>
+    <mergeCell ref="U5:U6"/>
+    <mergeCell ref="V5:V6"/>
+    <mergeCell ref="R5:R6"/>
+    <mergeCell ref="S5:S6"/>
+    <mergeCell ref="T5:T6"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="P7:P27">

--- a/filetiendo.xlsx
+++ b/filetiendo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\viettel 2026\thang 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ADF4A03-B967-441D-869A-8B611639EDA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D31953-C0CE-4C6B-851F-85A14272FAF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="808" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="808" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TH NV" sheetId="2" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="266">
   <si>
     <t>STT</t>
   </si>
@@ -849,6 +849,9 @@
   <si>
     <t/>
   </si>
+  <si>
+    <t>Ư</t>
+  </si>
 </sst>
 </file>
 
@@ -4198,17 +4201,41 @@
     <xf numFmtId="0" fontId="65" fillId="0" borderId="94" xfId="11" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="94" xfId="11" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="162" xfId="11" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="49" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="5" borderId="112" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="120" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="119" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="118" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="5" borderId="115" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="113" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="125" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="124" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="123" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="5" borderId="112" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="24" borderId="117" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4222,34 +4249,10 @@
     <xf numFmtId="0" fontId="17" fillId="5" borderId="114" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="120" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="119" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="118" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="35" fillId="16" borderId="121" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="2" borderId="122" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="125" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="124" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="123" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="66" fillId="18" borderId="150" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4321,16 +4324,16 @@
     <xf numFmtId="0" fontId="62" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="133" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="132" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="46" fillId="5" borderId="137" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="5" borderId="136" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="133" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="132" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="50" fillId="5" borderId="135" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4350,12 +4353,6 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="140" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="143" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="142" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="144" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4381,10 +4378,10 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="149" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="68" fillId="29" borderId="150" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="143" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="68" fillId="29" borderId="150" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="142" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4409,6 +4406,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="153" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="68" fillId="29" borderId="150" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="29" borderId="150" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="12">
     <cellStyle name="Comma" xfId="8" builtinId="3"/>
@@ -5298,166 +5301,166 @@
       </c>
     </row>
     <row r="2" spans="1:675" ht="23.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="183" t="s">
+      <c r="A2" s="193" t="s">
         <v>34</v>
       </c>
       <c r="B2" s="69"/>
       <c r="C2" s="15"/>
-      <c r="D2" s="194" t="s">
+      <c r="D2" s="199" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="194"/>
-      <c r="F2" s="194"/>
-      <c r="G2" s="194"/>
-      <c r="H2" s="194"/>
-      <c r="I2" s="194"/>
-      <c r="J2" s="194"/>
-      <c r="K2" s="194"/>
-      <c r="L2" s="194"/>
-      <c r="M2" s="194"/>
-      <c r="N2" s="194"/>
-      <c r="O2" s="194"/>
-      <c r="P2" s="194"/>
-      <c r="Q2" s="194"/>
-      <c r="R2" s="194"/>
-      <c r="S2" s="194"/>
-      <c r="T2" s="189" t="s">
+      <c r="E2" s="199"/>
+      <c r="F2" s="199"/>
+      <c r="G2" s="199"/>
+      <c r="H2" s="199"/>
+      <c r="I2" s="199"/>
+      <c r="J2" s="199"/>
+      <c r="K2" s="199"/>
+      <c r="L2" s="199"/>
+      <c r="M2" s="199"/>
+      <c r="N2" s="199"/>
+      <c r="O2" s="199"/>
+      <c r="P2" s="199"/>
+      <c r="Q2" s="199"/>
+      <c r="R2" s="199"/>
+      <c r="S2" s="199"/>
+      <c r="T2" s="197" t="s">
         <v>36</v>
       </c>
-      <c r="U2" s="189"/>
-      <c r="V2" s="189"/>
-      <c r="W2" s="189"/>
-      <c r="X2" s="189"/>
-      <c r="Y2" s="189"/>
-      <c r="Z2" s="189"/>
-      <c r="AA2" s="189"/>
-      <c r="AB2" s="189"/>
-      <c r="AC2" s="189"/>
-      <c r="AD2" s="189"/>
-      <c r="AE2" s="189"/>
-      <c r="AF2" s="189"/>
-      <c r="AG2" s="189"/>
-      <c r="AH2" s="189"/>
-      <c r="AI2" s="189"/>
-      <c r="AJ2" s="188" t="s">
+      <c r="U2" s="197"/>
+      <c r="V2" s="197"/>
+      <c r="W2" s="197"/>
+      <c r="X2" s="197"/>
+      <c r="Y2" s="197"/>
+      <c r="Z2" s="197"/>
+      <c r="AA2" s="197"/>
+      <c r="AB2" s="197"/>
+      <c r="AC2" s="197"/>
+      <c r="AD2" s="197"/>
+      <c r="AE2" s="197"/>
+      <c r="AF2" s="197"/>
+      <c r="AG2" s="197"/>
+      <c r="AH2" s="197"/>
+      <c r="AI2" s="197"/>
+      <c r="AJ2" s="196" t="s">
         <v>37</v>
       </c>
-      <c r="AK2" s="188"/>
-      <c r="AL2" s="188"/>
-      <c r="AM2" s="188"/>
-      <c r="AN2" s="188"/>
-      <c r="AO2" s="188"/>
-      <c r="AP2" s="188"/>
-      <c r="AQ2" s="188"/>
-      <c r="AR2" s="188"/>
-      <c r="AS2" s="188"/>
-      <c r="AT2" s="188"/>
-      <c r="AU2" s="188"/>
-      <c r="AV2" s="187" t="s">
+      <c r="AK2" s="196"/>
+      <c r="AL2" s="196"/>
+      <c r="AM2" s="196"/>
+      <c r="AN2" s="196"/>
+      <c r="AO2" s="196"/>
+      <c r="AP2" s="196"/>
+      <c r="AQ2" s="196"/>
+      <c r="AR2" s="196"/>
+      <c r="AS2" s="196"/>
+      <c r="AT2" s="196"/>
+      <c r="AU2" s="196"/>
+      <c r="AV2" s="195" t="s">
         <v>38</v>
       </c>
-      <c r="AW2" s="187"/>
-      <c r="AX2" s="187"/>
-      <c r="AY2" s="187"/>
-      <c r="AZ2" s="187"/>
-      <c r="BA2" s="187"/>
-      <c r="BB2" s="187"/>
-      <c r="BC2" s="187"/>
-      <c r="BD2" s="187"/>
-      <c r="BE2" s="187"/>
-      <c r="BF2" s="187"/>
-      <c r="BG2" s="187"/>
+      <c r="AW2" s="195"/>
+      <c r="AX2" s="195"/>
+      <c r="AY2" s="195"/>
+      <c r="AZ2" s="195"/>
+      <c r="BA2" s="195"/>
+      <c r="BB2" s="195"/>
+      <c r="BC2" s="195"/>
+      <c r="BD2" s="195"/>
+      <c r="BE2" s="195"/>
+      <c r="BF2" s="195"/>
+      <c r="BG2" s="195"/>
     </row>
     <row r="3" spans="1:675" s="3" customFormat="1" ht="28.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="183"/>
-      <c r="B3" s="195" t="s">
+      <c r="A3" s="193"/>
+      <c r="B3" s="200" t="s">
         <v>39</v>
       </c>
       <c r="C3" s="70"/>
-      <c r="D3" s="185" t="s">
+      <c r="D3" s="187" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="186"/>
-      <c r="F3" s="186"/>
-      <c r="G3" s="186"/>
-      <c r="H3" s="185" t="s">
+      <c r="E3" s="188"/>
+      <c r="F3" s="188"/>
+      <c r="G3" s="188"/>
+      <c r="H3" s="187" t="s">
         <v>40</v>
       </c>
-      <c r="I3" s="186"/>
-      <c r="J3" s="186"/>
-      <c r="K3" s="186"/>
-      <c r="L3" s="185" t="s">
+      <c r="I3" s="188"/>
+      <c r="J3" s="188"/>
+      <c r="K3" s="188"/>
+      <c r="L3" s="187" t="s">
         <v>41</v>
       </c>
-      <c r="M3" s="186"/>
-      <c r="N3" s="186"/>
-      <c r="O3" s="186"/>
-      <c r="P3" s="198" t="s">
+      <c r="M3" s="188"/>
+      <c r="N3" s="188"/>
+      <c r="O3" s="188"/>
+      <c r="P3" s="190" t="s">
         <v>42</v>
       </c>
-      <c r="Q3" s="199"/>
-      <c r="R3" s="199"/>
-      <c r="S3" s="200"/>
-      <c r="T3" s="185" t="s">
+      <c r="Q3" s="191"/>
+      <c r="R3" s="191"/>
+      <c r="S3" s="192"/>
+      <c r="T3" s="187" t="s">
         <v>43</v>
       </c>
-      <c r="U3" s="186"/>
-      <c r="V3" s="186"/>
-      <c r="W3" s="186"/>
-      <c r="X3" s="185" t="s">
+      <c r="U3" s="188"/>
+      <c r="V3" s="188"/>
+      <c r="W3" s="188"/>
+      <c r="X3" s="187" t="s">
         <v>45</v>
       </c>
-      <c r="Y3" s="186"/>
-      <c r="Z3" s="186"/>
-      <c r="AA3" s="186"/>
-      <c r="AB3" s="185" t="s">
+      <c r="Y3" s="188"/>
+      <c r="Z3" s="188"/>
+      <c r="AA3" s="188"/>
+      <c r="AB3" s="187" t="s">
         <v>47</v>
       </c>
-      <c r="AC3" s="186"/>
-      <c r="AD3" s="186"/>
-      <c r="AE3" s="186"/>
-      <c r="AF3" s="185" t="s">
+      <c r="AC3" s="188"/>
+      <c r="AD3" s="188"/>
+      <c r="AE3" s="188"/>
+      <c r="AF3" s="187" t="s">
         <v>48</v>
       </c>
-      <c r="AG3" s="186"/>
-      <c r="AH3" s="186"/>
-      <c r="AI3" s="186"/>
-      <c r="AJ3" s="191" t="s">
+      <c r="AG3" s="188"/>
+      <c r="AH3" s="188"/>
+      <c r="AI3" s="188"/>
+      <c r="AJ3" s="184" t="s">
         <v>51</v>
       </c>
-      <c r="AK3" s="192"/>
-      <c r="AL3" s="192"/>
-      <c r="AM3" s="193"/>
-      <c r="AN3" s="191" t="s">
+      <c r="AK3" s="185"/>
+      <c r="AL3" s="185"/>
+      <c r="AM3" s="186"/>
+      <c r="AN3" s="184" t="s">
         <v>14</v>
       </c>
-      <c r="AO3" s="192"/>
-      <c r="AP3" s="192"/>
-      <c r="AQ3" s="193"/>
-      <c r="AR3" s="191" t="s">
+      <c r="AO3" s="185"/>
+      <c r="AP3" s="185"/>
+      <c r="AQ3" s="186"/>
+      <c r="AR3" s="184" t="s">
         <v>52</v>
       </c>
-      <c r="AS3" s="192"/>
-      <c r="AT3" s="192"/>
-      <c r="AU3" s="193"/>
-      <c r="AV3" s="186" t="s">
+      <c r="AS3" s="185"/>
+      <c r="AT3" s="185"/>
+      <c r="AU3" s="186"/>
+      <c r="AV3" s="188" t="s">
         <v>16</v>
       </c>
-      <c r="AW3" s="186"/>
-      <c r="AX3" s="186"/>
-      <c r="AY3" s="186"/>
-      <c r="AZ3" s="186" t="s">
+      <c r="AW3" s="188"/>
+      <c r="AX3" s="188"/>
+      <c r="AY3" s="188"/>
+      <c r="AZ3" s="188" t="s">
         <v>54</v>
       </c>
-      <c r="BA3" s="186"/>
-      <c r="BB3" s="186"/>
-      <c r="BC3" s="186"/>
-      <c r="BD3" s="185" t="s">
+      <c r="BA3" s="188"/>
+      <c r="BB3" s="188"/>
+      <c r="BC3" s="188"/>
+      <c r="BD3" s="187" t="s">
         <v>55</v>
       </c>
-      <c r="BE3" s="186"/>
-      <c r="BF3" s="190"/>
-      <c r="BG3" s="186"/>
+      <c r="BE3" s="188"/>
+      <c r="BF3" s="198"/>
+      <c r="BG3" s="188"/>
       <c r="BH3" s="2"/>
       <c r="BI3" s="2"/>
       <c r="BJ3" s="2"/>
@@ -6076,8 +6079,8 @@
       <c r="YY3" s="2"/>
     </row>
     <row r="4" spans="1:675" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="184"/>
-      <c r="B4" s="195"/>
+      <c r="A4" s="194"/>
+      <c r="B4" s="200"/>
       <c r="C4" s="71"/>
       <c r="D4" s="8" t="s">
         <v>2</v>
@@ -6422,7 +6425,7 @@
       </c>
       <c r="AS5" s="112">
         <f>(VLOOKUP(B5,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.91230000000000011</v>
+        <v>0.94040000000000012</v>
       </c>
       <c r="AT5" s="14">
         <f t="shared" ref="AT5:AT18" si="20">IF(AS5&lt;94.5%,0,IF(AS5&lt;95.54%,50%,IF(AS5&lt;AR5,80%,100%+(30%*(AS5-AR5)/3.39%))))</f>
@@ -6430,7 +6433,7 @@
       </c>
       <c r="AU5" s="48">
         <f t="shared" ref="AU5:AU18" si="21">AR5-AS5</f>
-        <v>5.7699999999999863E-2</v>
+        <v>2.9599999999999849E-2</v>
       </c>
       <c r="AV5" s="51">
         <f>VLOOKUP(C5,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -6655,7 +6658,7 @@
       </c>
       <c r="AS6" s="112">
         <f>(VLOOKUP(B6,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.86750000000000005</v>
+        <v>0.90849999999999997</v>
       </c>
       <c r="AT6" s="14">
         <f t="shared" si="20"/>
@@ -6663,7 +6666,7 @@
       </c>
       <c r="AU6" s="48">
         <f t="shared" si="21"/>
-        <v>0.10249999999999992</v>
+        <v>6.1499999999999999E-2</v>
       </c>
       <c r="AV6" s="51">
         <f>VLOOKUP(C6,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -6888,7 +6891,7 @@
       </c>
       <c r="AS7" s="112">
         <f>(VLOOKUP(B7,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.90540000000000009</v>
+        <v>0.9375</v>
       </c>
       <c r="AT7" s="14">
         <f t="shared" si="20"/>
@@ -6896,7 +6899,7 @@
       </c>
       <c r="AU7" s="48">
         <f t="shared" si="21"/>
-        <v>6.459999999999988E-2</v>
+        <v>3.2499999999999973E-2</v>
       </c>
       <c r="AV7" s="51">
         <f>VLOOKUP(C7,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7121,7 +7124,7 @@
       </c>
       <c r="AS8" s="112">
         <f>(VLOOKUP(B8,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.88230000000000008</v>
+        <v>0.90459999999999996</v>
       </c>
       <c r="AT8" s="14">
         <f t="shared" si="20"/>
@@ -7129,7 +7132,7 @@
       </c>
       <c r="AU8" s="48">
         <f t="shared" si="21"/>
-        <v>8.7699999999999889E-2</v>
+        <v>6.5400000000000014E-2</v>
       </c>
       <c r="AV8" s="51">
         <f>VLOOKUP(C8,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7354,7 +7357,7 @@
       </c>
       <c r="AS9" s="112">
         <f>(VLOOKUP(B9,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.91870000000000007</v>
+        <v>0.92249999999999999</v>
       </c>
       <c r="AT9" s="14">
         <f t="shared" si="20"/>
@@ -7362,7 +7365,7 @@
       </c>
       <c r="AU9" s="48">
         <f t="shared" si="21"/>
-        <v>5.1299999999999901E-2</v>
+        <v>4.7499999999999987E-2</v>
       </c>
       <c r="AV9" s="51">
         <f>VLOOKUP(C9,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7587,15 +7590,15 @@
       </c>
       <c r="AS10" s="112">
         <f>(VLOOKUP(B10,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.9103</v>
+        <v>0.95180000000000009</v>
       </c>
       <c r="AT10" s="14">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AU10" s="48">
         <f t="shared" si="21"/>
-        <v>5.9699999999999975E-2</v>
+        <v>1.8199999999999883E-2</v>
       </c>
       <c r="AV10" s="51">
         <f>VLOOKUP(C10,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -7820,7 +7823,7 @@
       </c>
       <c r="AS11" s="112">
         <f>(VLOOKUP(B11,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.91620000000000001</v>
+        <v>0.93909999999999993</v>
       </c>
       <c r="AT11" s="14">
         <f t="shared" si="20"/>
@@ -7828,7 +7831,7 @@
       </c>
       <c r="AU11" s="48">
         <f t="shared" si="21"/>
-        <v>5.3799999999999959E-2</v>
+        <v>3.0900000000000039E-2</v>
       </c>
       <c r="AV11" s="51">
         <f>VLOOKUP(C11,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8053,15 +8056,15 @@
       </c>
       <c r="AS12" s="112">
         <f>(VLOOKUP(B12,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.93370000000000009</v>
+        <v>0.94840000000000002</v>
       </c>
       <c r="AT12" s="14">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AU12" s="48">
         <f t="shared" si="21"/>
-        <v>3.6299999999999888E-2</v>
+        <v>2.1599999999999953E-2</v>
       </c>
       <c r="AV12" s="51">
         <f>VLOOKUP(C12,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8286,7 +8289,7 @@
       </c>
       <c r="AS13" s="112">
         <f>(VLOOKUP(B13,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.9043000000000001</v>
+        <v>0.9224</v>
       </c>
       <c r="AT13" s="14">
         <f t="shared" si="20"/>
@@ -8294,7 +8297,7 @@
       </c>
       <c r="AU13" s="48">
         <f t="shared" si="21"/>
-        <v>6.569999999999987E-2</v>
+        <v>4.7599999999999976E-2</v>
       </c>
       <c r="AV13" s="51">
         <f>VLOOKUP(C13,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8519,7 +8522,7 @@
       </c>
       <c r="AS14" s="112">
         <f>(VLOOKUP(B14,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.89</v>
+        <v>0.92469999999999997</v>
       </c>
       <c r="AT14" s="14">
         <f t="shared" si="20"/>
@@ -8527,7 +8530,7 @@
       </c>
       <c r="AU14" s="48">
         <f t="shared" si="21"/>
-        <v>7.999999999999996E-2</v>
+        <v>4.5300000000000007E-2</v>
       </c>
       <c r="AV14" s="51">
         <f>VLOOKUP(C14,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8752,7 +8755,7 @@
       </c>
       <c r="AS15" s="112">
         <f>(VLOOKUP(B15,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.86609999999999998</v>
+        <v>0.90529999999999999</v>
       </c>
       <c r="AT15" s="14">
         <f t="shared" si="20"/>
@@ -8760,7 +8763,7 @@
       </c>
       <c r="AU15" s="48">
         <f t="shared" si="21"/>
-        <v>0.10389999999999999</v>
+        <v>6.469999999999998E-2</v>
       </c>
       <c r="AV15" s="51">
         <f>VLOOKUP(C15,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -8985,7 +8988,7 @@
       </c>
       <c r="AS16" s="112">
         <f>(VLOOKUP(B16,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.89710000000000001</v>
+        <v>0.93359999999999999</v>
       </c>
       <c r="AT16" s="14">
         <f t="shared" si="20"/>
@@ -8993,7 +8996,7 @@
       </c>
       <c r="AU16" s="48">
         <f t="shared" si="21"/>
-        <v>7.2899999999999965E-2</v>
+        <v>3.6399999999999988E-2</v>
       </c>
       <c r="AV16" s="51">
         <f>VLOOKUP(C16,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -9218,7 +9221,7 @@
       </c>
       <c r="AS17" s="112">
         <f>(VLOOKUP(B17,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.9133</v>
+        <v>0.93769999999999998</v>
       </c>
       <c r="AT17" s="14">
         <f t="shared" si="20"/>
@@ -9226,7 +9229,7 @@
       </c>
       <c r="AU17" s="48">
         <f t="shared" si="21"/>
-        <v>5.6699999999999973E-2</v>
+        <v>3.2299999999999995E-2</v>
       </c>
       <c r="AV17" s="51">
         <f>VLOOKUP(C17,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -9451,7 +9454,7 @@
       </c>
       <c r="AS18" s="112">
         <f>(VLOOKUP(B18,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.86780000000000002</v>
+        <v>0.89430000000000009</v>
       </c>
       <c r="AT18" s="14">
         <f t="shared" si="20"/>
@@ -9459,7 +9462,7 @@
       </c>
       <c r="AU18" s="48">
         <f t="shared" si="21"/>
-        <v>0.10219999999999996</v>
+        <v>7.5699999999999878E-2</v>
       </c>
       <c r="AV18" s="51">
         <f>VLOOKUP(C18,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -9516,11 +9519,11 @@
       <c r="C19" s="15"/>
       <c r="D19" s="15"/>
       <c r="E19" s="16"/>
-      <c r="F19" s="196">
+      <c r="F19" s="183">
         <f ca="1">TODAY()</f>
         <v>46079</v>
       </c>
-      <c r="G19" s="196"/>
+      <c r="G19" s="183"/>
       <c r="H19" s="73"/>
       <c r="I19" s="74">
         <f ca="1">DAY(F19)</f>
@@ -9533,33 +9536,33 @@
         <f ca="1">I19/J19</f>
         <v>0.83870967741935487</v>
       </c>
-      <c r="L19" s="197" t="s">
+      <c r="L19" s="189" t="s">
         <v>124</v>
       </c>
-      <c r="M19" s="197"/>
-      <c r="N19" s="197"/>
-      <c r="O19" s="197"/>
-      <c r="P19" s="197"/>
-      <c r="Q19" s="197"/>
-      <c r="R19" s="197"/>
-      <c r="S19" s="197"/>
-      <c r="T19" s="197"/>
-      <c r="U19" s="197"/>
-      <c r="V19" s="197"/>
-      <c r="W19" s="197"/>
-      <c r="X19" s="197"/>
-      <c r="Y19" s="197"/>
-      <c r="Z19" s="197"/>
-      <c r="AA19" s="197"/>
-      <c r="AB19" s="197"/>
-      <c r="AC19" s="197"/>
-      <c r="AD19" s="197"/>
-      <c r="AE19" s="197"/>
-      <c r="AF19" s="197"/>
-      <c r="AG19" s="197"/>
-      <c r="AH19" s="197"/>
-      <c r="AI19" s="197"/>
-      <c r="AJ19" s="197"/>
+      <c r="M19" s="189"/>
+      <c r="N19" s="189"/>
+      <c r="O19" s="189"/>
+      <c r="P19" s="189"/>
+      <c r="Q19" s="189"/>
+      <c r="R19" s="189"/>
+      <c r="S19" s="189"/>
+      <c r="T19" s="189"/>
+      <c r="U19" s="189"/>
+      <c r="V19" s="189"/>
+      <c r="W19" s="189"/>
+      <c r="X19" s="189"/>
+      <c r="Y19" s="189"/>
+      <c r="Z19" s="189"/>
+      <c r="AA19" s="189"/>
+      <c r="AB19" s="189"/>
+      <c r="AC19" s="189"/>
+      <c r="AD19" s="189"/>
+      <c r="AE19" s="189"/>
+      <c r="AF19" s="189"/>
+      <c r="AG19" s="189"/>
+      <c r="AH19" s="189"/>
+      <c r="AI19" s="189"/>
+      <c r="AJ19" s="189"/>
       <c r="AK19" s="16"/>
       <c r="AL19" s="32"/>
       <c r="AM19" s="16"/>
@@ -9752,12 +9755,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="AN3:AQ3"/>
-    <mergeCell ref="AF3:AI3"/>
-    <mergeCell ref="L19:AJ19"/>
-    <mergeCell ref="P3:S3"/>
-    <mergeCell ref="T3:W3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="X3:AA3"/>
     <mergeCell ref="AV2:BG2"/>
@@ -9774,6 +9771,12 @@
     <mergeCell ref="D3:G3"/>
     <mergeCell ref="H3:K3"/>
     <mergeCell ref="L3:O3"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="AN3:AQ3"/>
+    <mergeCell ref="AF3:AI3"/>
+    <mergeCell ref="L19:AJ19"/>
+    <mergeCell ref="P3:S3"/>
+    <mergeCell ref="T3:W3"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="C3:C4">
@@ -10454,7 +10457,7 @@
       </c>
       <c r="D14" s="68">
         <f>VLOOKUP($B$2,'TH NV'!$A$5:$BG$18,N14,0)</f>
-        <v>0.89</v>
+        <v>0.92469999999999997</v>
       </c>
       <c r="E14" s="43" t="e">
         <f>VLOOKUP($B$2,'TH NV'!$A$1:$BG$18,70,0)</f>
@@ -10477,7 +10480,7 @@
       </c>
       <c r="J14" s="59">
         <f t="shared" si="2"/>
-        <v>7.999999999999996E-2</v>
+        <v>4.5300000000000007E-2</v>
       </c>
       <c r="K14" s="205"/>
       <c r="L14" s="97" t="s">
@@ -10658,42 +10661,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:59" s="1" customFormat="1" ht="24.75" x14ac:dyDescent="0.45">
-      <c r="D1" s="194" t="s">
+      <c r="D1" s="199" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="194"/>
-      <c r="F1" s="194"/>
-      <c r="G1" s="194"/>
-      <c r="H1" s="194"/>
-      <c r="I1" s="194"/>
-      <c r="J1" s="194"/>
-      <c r="K1" s="194"/>
-      <c r="L1" s="194"/>
-      <c r="M1" s="194"/>
-      <c r="N1" s="194"/>
-      <c r="O1" s="194"/>
-      <c r="P1" s="194"/>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="189" t="s">
+      <c r="E1" s="199"/>
+      <c r="F1" s="199"/>
+      <c r="G1" s="199"/>
+      <c r="H1" s="199"/>
+      <c r="I1" s="199"/>
+      <c r="J1" s="199"/>
+      <c r="K1" s="199"/>
+      <c r="L1" s="199"/>
+      <c r="M1" s="199"/>
+      <c r="N1" s="199"/>
+      <c r="O1" s="199"/>
+      <c r="P1" s="199"/>
+      <c r="Q1" s="199"/>
+      <c r="R1" s="199"/>
+      <c r="S1" s="199"/>
+      <c r="T1" s="197" t="s">
         <v>36</v>
       </c>
-      <c r="U1" s="189"/>
-      <c r="V1" s="189"/>
-      <c r="W1" s="189"/>
-      <c r="X1" s="189"/>
-      <c r="Y1" s="189"/>
-      <c r="Z1" s="189"/>
-      <c r="AA1" s="189"/>
-      <c r="AB1" s="189"/>
-      <c r="AC1" s="189"/>
-      <c r="AD1" s="189"/>
-      <c r="AE1" s="189"/>
-      <c r="AF1" s="189"/>
-      <c r="AG1" s="189"/>
-      <c r="AH1" s="189"/>
-      <c r="AI1" s="189"/>
+      <c r="U1" s="197"/>
+      <c r="V1" s="197"/>
+      <c r="W1" s="197"/>
+      <c r="X1" s="197"/>
+      <c r="Y1" s="197"/>
+      <c r="Z1" s="197"/>
+      <c r="AA1" s="197"/>
+      <c r="AB1" s="197"/>
+      <c r="AC1" s="197"/>
+      <c r="AD1" s="197"/>
+      <c r="AE1" s="197"/>
+      <c r="AF1" s="197"/>
+      <c r="AG1" s="197"/>
+      <c r="AH1" s="197"/>
+      <c r="AI1" s="197"/>
       <c r="AJ1" s="217" t="s">
         <v>37</v>
       </c>
@@ -10726,90 +10729,90 @@
     <row r="2" spans="1:59" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="185" t="s">
+      <c r="D2" s="187" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="186"/>
-      <c r="F2" s="186"/>
-      <c r="G2" s="186"/>
-      <c r="H2" s="185" t="s">
+      <c r="E2" s="188"/>
+      <c r="F2" s="188"/>
+      <c r="G2" s="188"/>
+      <c r="H2" s="187" t="s">
         <v>40</v>
       </c>
-      <c r="I2" s="186"/>
-      <c r="J2" s="186"/>
-      <c r="K2" s="186"/>
-      <c r="L2" s="185" t="s">
+      <c r="I2" s="188"/>
+      <c r="J2" s="188"/>
+      <c r="K2" s="188"/>
+      <c r="L2" s="187" t="s">
         <v>41</v>
       </c>
-      <c r="M2" s="186"/>
-      <c r="N2" s="186"/>
-      <c r="O2" s="186"/>
-      <c r="P2" s="198" t="s">
+      <c r="M2" s="188"/>
+      <c r="N2" s="188"/>
+      <c r="O2" s="188"/>
+      <c r="P2" s="190" t="s">
         <v>42</v>
       </c>
-      <c r="Q2" s="199"/>
-      <c r="R2" s="199"/>
-      <c r="S2" s="200"/>
-      <c r="T2" s="185" t="s">
+      <c r="Q2" s="191"/>
+      <c r="R2" s="191"/>
+      <c r="S2" s="192"/>
+      <c r="T2" s="187" t="s">
         <v>43</v>
       </c>
-      <c r="U2" s="186"/>
-      <c r="V2" s="186"/>
-      <c r="W2" s="186"/>
-      <c r="X2" s="185" t="s">
+      <c r="U2" s="188"/>
+      <c r="V2" s="188"/>
+      <c r="W2" s="188"/>
+      <c r="X2" s="187" t="s">
         <v>45</v>
       </c>
-      <c r="Y2" s="186"/>
-      <c r="Z2" s="186"/>
-      <c r="AA2" s="186"/>
-      <c r="AB2" s="185" t="s">
+      <c r="Y2" s="188"/>
+      <c r="Z2" s="188"/>
+      <c r="AA2" s="188"/>
+      <c r="AB2" s="187" t="s">
         <v>47</v>
       </c>
-      <c r="AC2" s="186"/>
-      <c r="AD2" s="186"/>
-      <c r="AE2" s="186"/>
-      <c r="AF2" s="185" t="s">
+      <c r="AC2" s="188"/>
+      <c r="AD2" s="188"/>
+      <c r="AE2" s="188"/>
+      <c r="AF2" s="187" t="s">
         <v>48</v>
       </c>
-      <c r="AG2" s="186"/>
-      <c r="AH2" s="186"/>
-      <c r="AI2" s="186"/>
-      <c r="AJ2" s="191" t="s">
+      <c r="AG2" s="188"/>
+      <c r="AH2" s="188"/>
+      <c r="AI2" s="188"/>
+      <c r="AJ2" s="184" t="s">
         <v>51</v>
       </c>
-      <c r="AK2" s="192"/>
-      <c r="AL2" s="192"/>
-      <c r="AM2" s="193"/>
-      <c r="AN2" s="191" t="s">
+      <c r="AK2" s="185"/>
+      <c r="AL2" s="185"/>
+      <c r="AM2" s="186"/>
+      <c r="AN2" s="184" t="s">
         <v>14</v>
       </c>
-      <c r="AO2" s="192"/>
-      <c r="AP2" s="192"/>
-      <c r="AQ2" s="193"/>
-      <c r="AR2" s="191" t="s">
+      <c r="AO2" s="185"/>
+      <c r="AP2" s="185"/>
+      <c r="AQ2" s="186"/>
+      <c r="AR2" s="184" t="s">
         <v>52</v>
       </c>
-      <c r="AS2" s="192"/>
-      <c r="AT2" s="192"/>
-      <c r="AU2" s="193"/>
-      <c r="AV2" s="186" t="s">
+      <c r="AS2" s="185"/>
+      <c r="AT2" s="185"/>
+      <c r="AU2" s="186"/>
+      <c r="AV2" s="188" t="s">
         <v>16</v>
       </c>
-      <c r="AW2" s="186"/>
-      <c r="AX2" s="186"/>
-      <c r="AY2" s="186"/>
-      <c r="AZ2" s="186" t="s">
+      <c r="AW2" s="188"/>
+      <c r="AX2" s="188"/>
+      <c r="AY2" s="188"/>
+      <c r="AZ2" s="188" t="s">
         <v>54</v>
       </c>
-      <c r="BA2" s="186"/>
-      <c r="BB2" s="186"/>
-      <c r="BC2" s="186"/>
-      <c r="BD2" s="185" t="s">
+      <c r="BA2" s="188"/>
+      <c r="BB2" s="188"/>
+      <c r="BC2" s="188"/>
+      <c r="BD2" s="187" t="s">
         <v>55</v>
       </c>
-      <c r="BE2" s="186"/>
-      <c r="BF2" s="190"/>
-      <c r="BG2" s="186"/>
+      <c r="BE2" s="188"/>
+      <c r="BF2" s="198"/>
+      <c r="BG2" s="188"/>
     </row>
     <row r="3" spans="1:59" ht="15" x14ac:dyDescent="0.45">
       <c r="B3" s="8" t="s">
@@ -11162,7 +11165,7 @@
       </c>
       <c r="AS4" s="112">
         <f>(VLOOKUP(B4,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.91230000000000011</v>
+        <v>0.94040000000000012</v>
       </c>
       <c r="AT4" s="14">
         <f t="shared" ref="AT4" si="20">IF(AS4&lt;94.5%,0,IF(AS4&lt;95.54%,50%,IF(AS4&lt;AR4,80%,100%+(30%*(AS4-AR4)/3.39%))))</f>
@@ -11170,7 +11173,7 @@
       </c>
       <c r="AU4" s="48">
         <f t="shared" ref="AU4" si="21">AR4-AS4</f>
-        <v>5.7699999999999863E-2</v>
+        <v>2.9599999999999849E-2</v>
       </c>
       <c r="AV4" s="51">
         <f>VLOOKUP(A4,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -11396,7 +11399,7 @@
       </c>
       <c r="AS5" s="112">
         <f>(VLOOKUP(B5,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.91620000000000001</v>
+        <v>0.93909999999999993</v>
       </c>
       <c r="AT5" s="14">
         <f t="shared" ref="AT5:AT16" si="48">IF(AS5&lt;94.5%,0,IF(AS5&lt;95.54%,50%,IF(AS5&lt;AR5,80%,100%+(30%*(AS5-AR5)/3.39%))))</f>
@@ -11404,7 +11407,7 @@
       </c>
       <c r="AU5" s="48">
         <f t="shared" ref="AU5:AU16" si="49">AR5-AS5</f>
-        <v>5.3799999999999959E-2</v>
+        <v>3.0900000000000039E-2</v>
       </c>
       <c r="AV5" s="51">
         <f>VLOOKUP(A5,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -11630,15 +11633,15 @@
       </c>
       <c r="AS6" s="112">
         <f>(VLOOKUP(B6,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.93370000000000009</v>
+        <v>0.94840000000000002</v>
       </c>
       <c r="AT6" s="14">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AU6" s="48">
         <f t="shared" si="49"/>
-        <v>3.6299999999999888E-2</v>
+        <v>2.1599999999999953E-2</v>
       </c>
       <c r="AV6" s="51">
         <f>VLOOKUP(A6,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -11864,7 +11867,7 @@
       </c>
       <c r="AS7" s="112">
         <f>(VLOOKUP(B7,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.89</v>
+        <v>0.92469999999999997</v>
       </c>
       <c r="AT7" s="14">
         <f t="shared" si="48"/>
@@ -11872,7 +11875,7 @@
       </c>
       <c r="AU7" s="48">
         <f t="shared" si="49"/>
-        <v>7.999999999999996E-2</v>
+        <v>4.5300000000000007E-2</v>
       </c>
       <c r="AV7" s="51">
         <f>VLOOKUP(A7,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -12098,7 +12101,7 @@
       </c>
       <c r="AS8" s="112">
         <f>(VLOOKUP(B8,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.89710000000000001</v>
+        <v>0.93359999999999999</v>
       </c>
       <c r="AT8" s="14">
         <f t="shared" si="48"/>
@@ -12106,7 +12109,7 @@
       </c>
       <c r="AU8" s="48">
         <f t="shared" si="49"/>
-        <v>7.2899999999999965E-2</v>
+        <v>3.6399999999999988E-2</v>
       </c>
       <c r="AV8" s="51">
         <f>VLOOKUP(A8,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -12393,7 +12396,7 @@
       </c>
       <c r="AS10" s="112">
         <f>(VLOOKUP(B10,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.86750000000000005</v>
+        <v>0.90849999999999997</v>
       </c>
       <c r="AT10" s="14">
         <f t="shared" si="48"/>
@@ -12401,7 +12404,7 @@
       </c>
       <c r="AU10" s="48">
         <f t="shared" si="49"/>
-        <v>0.10249999999999992</v>
+        <v>6.1499999999999999E-2</v>
       </c>
       <c r="AV10" s="51">
         <f>VLOOKUP(A10,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -12627,7 +12630,7 @@
       </c>
       <c r="AS11" s="112">
         <f>(VLOOKUP(B11,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.90540000000000009</v>
+        <v>0.9375</v>
       </c>
       <c r="AT11" s="14">
         <f t="shared" si="48"/>
@@ -12635,7 +12638,7 @@
       </c>
       <c r="AU11" s="48">
         <f t="shared" si="49"/>
-        <v>6.459999999999988E-2</v>
+        <v>3.2499999999999973E-2</v>
       </c>
       <c r="AV11" s="51">
         <f>VLOOKUP(A11,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -12861,7 +12864,7 @@
       </c>
       <c r="AS12" s="112">
         <f>(VLOOKUP(B12,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.88230000000000008</v>
+        <v>0.90459999999999996</v>
       </c>
       <c r="AT12" s="14">
         <f t="shared" si="48"/>
@@ -12869,7 +12872,7 @@
       </c>
       <c r="AU12" s="48">
         <f t="shared" si="49"/>
-        <v>8.7699999999999889E-2</v>
+        <v>6.5400000000000014E-2</v>
       </c>
       <c r="AV12" s="51">
         <f>VLOOKUP(A12,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -13095,15 +13098,15 @@
       </c>
       <c r="AS13" s="112">
         <f>(VLOOKUP(B13,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.9103</v>
+        <v>0.95180000000000009</v>
       </c>
       <c r="AT13" s="14">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AU13" s="48">
         <f t="shared" si="49"/>
-        <v>5.9699999999999975E-2</v>
+        <v>1.8199999999999883E-2</v>
       </c>
       <c r="AV13" s="51">
         <f>VLOOKUP(A13,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -13329,7 +13332,7 @@
       </c>
       <c r="AS14" s="112">
         <f>(VLOOKUP(B14,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.9043000000000001</v>
+        <v>0.9224</v>
       </c>
       <c r="AT14" s="14">
         <f t="shared" si="48"/>
@@ -13337,7 +13340,7 @@
       </c>
       <c r="AU14" s="48">
         <f t="shared" si="49"/>
-        <v>6.569999999999987E-2</v>
+        <v>4.7599999999999976E-2</v>
       </c>
       <c r="AV14" s="51">
         <f>VLOOKUP(A14,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -13563,7 +13566,7 @@
       </c>
       <c r="AS15" s="112">
         <f>(VLOOKUP(B15,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.86609999999999998</v>
+        <v>0.90529999999999999</v>
       </c>
       <c r="AT15" s="14">
         <f t="shared" si="48"/>
@@ -13571,7 +13574,7 @@
       </c>
       <c r="AU15" s="48">
         <f t="shared" si="49"/>
-        <v>0.10389999999999999</v>
+        <v>6.469999999999998E-2</v>
       </c>
       <c r="AV15" s="51">
         <f>VLOOKUP(A15,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -13797,7 +13800,7 @@
       </c>
       <c r="AS16" s="112">
         <f>(VLOOKUP(B16,cuoc!$B$7:$P$27,14,0))*1%</f>
-        <v>0.9133</v>
+        <v>0.93769999999999998</v>
       </c>
       <c r="AT16" s="14">
         <f t="shared" si="48"/>
@@ -13805,7 +13808,7 @@
       </c>
       <c r="AU16" s="48">
         <f t="shared" si="49"/>
-        <v>5.6699999999999973E-2</v>
+        <v>3.2299999999999995E-2</v>
       </c>
       <c r="AV16" s="51">
         <f>VLOOKUP(A16,'Giao CT'!$D$6:$S$20,14,0)</f>
@@ -13889,11 +13892,11 @@
       </c>
       <c r="C19" s="125">
         <f ca="1">SUMIF(cuoc!A7:P27,'tiến độ'!A19,cuoc!M7:M27)</f>
-        <v>585269431</v>
+        <v>603032234</v>
       </c>
       <c r="D19" s="125">
         <f ca="1">B19*0.968-C19</f>
-        <v>37904640.255999923</v>
+        <v>20141837.255999923</v>
       </c>
       <c r="E19" s="120"/>
       <c r="H19" s="120"/>
@@ -13910,11 +13913,11 @@
       </c>
       <c r="C20" s="126">
         <f ca="1">SUMIF(cuoc!A8:P27,'tiến độ'!A20,cuoc!M8:M27)</f>
-        <v>964414681</v>
+        <v>997845568</v>
       </c>
       <c r="D20" s="125">
         <f ca="1">B20*0.968-C20</f>
-        <v>82161124.703999996</v>
+        <v>48730237.703999996</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.45">
@@ -14100,11 +14103,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="D1:S1"/>
-    <mergeCell ref="D2:G2"/>
-    <mergeCell ref="H2:K2"/>
-    <mergeCell ref="L2:O2"/>
-    <mergeCell ref="P2:S2"/>
     <mergeCell ref="X2:AA2"/>
     <mergeCell ref="AB2:AE2"/>
     <mergeCell ref="AF2:AI2"/>
@@ -14118,6 +14116,11 @@
     <mergeCell ref="AJ2:AM2"/>
     <mergeCell ref="AN2:AQ2"/>
     <mergeCell ref="T2:W2"/>
+    <mergeCell ref="D1:S1"/>
+    <mergeCell ref="D2:G2"/>
+    <mergeCell ref="H2:K2"/>
+    <mergeCell ref="L2:O2"/>
+    <mergeCell ref="P2:S2"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="F4:F16">
@@ -22725,12 +22728,6 @@
   </sheetData>
   <autoFilter ref="A6:DG6" xr:uid="{035AF4C2-379E-4E05-A870-198385941EC5}"/>
   <mergeCells count="16">
-    <mergeCell ref="X5:AE5"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="H5:O5"/>
-    <mergeCell ref="P5:W5"/>
     <mergeCell ref="CB5:CI5"/>
     <mergeCell ref="CJ5:CQ5"/>
     <mergeCell ref="CR5:CY5"/>
@@ -22741,6 +22738,12 @@
     <mergeCell ref="BD5:BK5"/>
     <mergeCell ref="BL5:BS5"/>
     <mergeCell ref="BT5:CA5"/>
+    <mergeCell ref="X5:AE5"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="H5:O5"/>
+    <mergeCell ref="P5:W5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -22838,7 +22841,7 @@
       <c r="A3" s="83" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="226" t="s">
+      <c r="B3" s="228" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="84" t="s">
@@ -22850,70 +22853,70 @@
       <c r="E3" s="230" t="s">
         <v>202</v>
       </c>
-      <c r="F3" s="228" t="s">
+      <c r="F3" s="226" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="228" t="s">
+      <c r="G3" s="226" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="228" t="s">
+      <c r="H3" s="226" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="228" t="s">
+      <c r="I3" s="226" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="228" t="s">
+      <c r="J3" s="226" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="228" t="s">
+      <c r="K3" s="226" t="s">
         <v>11</v>
       </c>
-      <c r="L3" s="228" t="s">
+      <c r="L3" s="226" t="s">
         <v>12</v>
       </c>
-      <c r="M3" s="228" t="s">
+      <c r="M3" s="226" t="s">
         <v>203</v>
       </c>
-      <c r="N3" s="228" t="s">
+      <c r="N3" s="226" t="s">
         <v>255</v>
       </c>
-      <c r="O3" s="228" t="s">
+      <c r="O3" s="226" t="s">
         <v>14</v>
       </c>
-      <c r="P3" s="228" t="s">
+      <c r="P3" s="226" t="s">
         <v>15</v>
       </c>
-      <c r="Q3" s="228" t="s">
+      <c r="Q3" s="226" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="228" t="s">
+      <c r="R3" s="226" t="s">
         <v>17</v>
       </c>
-      <c r="S3" s="228" t="s">
+      <c r="S3" s="226" t="s">
         <v>18</v>
       </c>
       <c r="T3" s="82"/>
     </row>
     <row r="4" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="83"/>
-      <c r="B4" s="227"/>
+      <c r="B4" s="229"/>
       <c r="C4" s="84"/>
       <c r="D4" s="84"/>
       <c r="E4" s="231"/>
-      <c r="F4" s="229"/>
-      <c r="G4" s="229"/>
-      <c r="H4" s="229"/>
-      <c r="I4" s="229"/>
-      <c r="J4" s="229"/>
-      <c r="K4" s="229"/>
-      <c r="L4" s="229"/>
-      <c r="M4" s="229"/>
-      <c r="N4" s="229"/>
-      <c r="O4" s="229"/>
-      <c r="P4" s="229"/>
-      <c r="Q4" s="229"/>
-      <c r="R4" s="229"/>
-      <c r="S4" s="229"/>
+      <c r="F4" s="227"/>
+      <c r="G4" s="227"/>
+      <c r="H4" s="227"/>
+      <c r="I4" s="227"/>
+      <c r="J4" s="227"/>
+      <c r="K4" s="227"/>
+      <c r="L4" s="227"/>
+      <c r="M4" s="227"/>
+      <c r="N4" s="227"/>
+      <c r="O4" s="227"/>
+      <c r="P4" s="227"/>
+      <c r="Q4" s="227"/>
+      <c r="R4" s="227"/>
+      <c r="S4" s="227"/>
       <c r="T4" s="82"/>
     </row>
     <row r="5" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.45">
@@ -24231,12 +24234,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="S3:S4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="R3:R4"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="H3:H4"/>
@@ -24247,6 +24244,12 @@
     <mergeCell ref="K3:K4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="E3:E4"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="S3:S4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="R3:R4"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.69991251615088756" right="0.69991251615088756" top="0.74990626395218019" bottom="0.74990626395218019" header="0.29996251027415122" footer="0.29996251027415122"/>
@@ -24830,68 +24833,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:48" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="241" t="s">
+      <c r="A1" s="239" t="s">
         <v>209</v>
       </c>
-      <c r="B1" s="241"/>
-      <c r="C1" s="241"/>
-      <c r="D1" s="241"/>
-      <c r="E1" s="241"/>
-      <c r="F1" s="241"/>
-      <c r="G1" s="241"/>
-      <c r="H1" s="241"/>
-      <c r="I1" s="241"/>
-      <c r="J1" s="241"/>
-      <c r="K1" s="241"/>
-      <c r="M1" s="244" t="s">
+      <c r="B1" s="239"/>
+      <c r="C1" s="239"/>
+      <c r="D1" s="239"/>
+      <c r="E1" s="239"/>
+      <c r="F1" s="239"/>
+      <c r="G1" s="239"/>
+      <c r="H1" s="239"/>
+      <c r="I1" s="239"/>
+      <c r="J1" s="239"/>
+      <c r="K1" s="239"/>
+      <c r="M1" s="242" t="s">
         <v>210</v>
       </c>
-      <c r="N1" s="244"/>
-      <c r="O1" s="244"/>
-      <c r="P1" s="244"/>
-      <c r="Q1" s="244"/>
-      <c r="R1" s="244"/>
-      <c r="S1" s="244"/>
-      <c r="T1" s="244"/>
-      <c r="U1" s="244"/>
-      <c r="V1" s="244"/>
-      <c r="W1" s="244"/>
-      <c r="X1" s="244"/>
-      <c r="Y1" s="244"/>
-      <c r="Z1" s="244"/>
+      <c r="N1" s="242"/>
+      <c r="O1" s="242"/>
+      <c r="P1" s="242"/>
+      <c r="Q1" s="242"/>
+      <c r="R1" s="242"/>
+      <c r="S1" s="242"/>
+      <c r="T1" s="242"/>
+      <c r="U1" s="242"/>
+      <c r="V1" s="242"/>
+      <c r="W1" s="242"/>
+      <c r="X1" s="242"/>
+      <c r="Y1" s="242"/>
+      <c r="Z1" s="242"/>
     </row>
     <row r="2" spans="1:48" ht="24.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="242"/>
-      <c r="B2" s="242"/>
-      <c r="C2" s="242"/>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
-      <c r="G2" s="242"/>
-      <c r="H2" s="242"/>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="M2" s="245"/>
-      <c r="N2" s="245"/>
-      <c r="O2" s="245"/>
-      <c r="P2" s="245"/>
-      <c r="Q2" s="245"/>
-      <c r="R2" s="245"/>
-      <c r="S2" s="245"/>
-      <c r="T2" s="245"/>
-      <c r="U2" s="245"/>
-      <c r="V2" s="245"/>
-      <c r="W2" s="245"/>
-      <c r="X2" s="245"/>
-      <c r="Y2" s="245"/>
-      <c r="Z2" s="245"/>
+      <c r="A2" s="240"/>
+      <c r="B2" s="240"/>
+      <c r="C2" s="240"/>
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
+      <c r="G2" s="240"/>
+      <c r="H2" s="240"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="M2" s="243"/>
+      <c r="N2" s="243"/>
+      <c r="O2" s="243"/>
+      <c r="P2" s="243"/>
+      <c r="Q2" s="243"/>
+      <c r="R2" s="243"/>
+      <c r="S2" s="243"/>
+      <c r="T2" s="243"/>
+      <c r="U2" s="243"/>
+      <c r="V2" s="243"/>
+      <c r="W2" s="243"/>
+      <c r="X2" s="243"/>
+      <c r="Y2" s="243"/>
+      <c r="Z2" s="243"/>
     </row>
     <row r="3" spans="1:48" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="238" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="239" t="s">
+      <c r="A3" s="236" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="237" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="28" t="s">
@@ -24921,70 +24924,70 @@
       <c r="K3" s="28" t="s">
         <v>218</v>
       </c>
-      <c r="M3" s="243" t="s">
+      <c r="M3" s="241" t="s">
         <v>34</v>
       </c>
-      <c r="N3" s="185" t="s">
+      <c r="N3" s="187" t="s">
         <v>219</v>
       </c>
-      <c r="O3" s="186"/>
-      <c r="P3" s="186"/>
-      <c r="Q3" s="186"/>
-      <c r="R3" s="236" t="s">
+      <c r="O3" s="188"/>
+      <c r="P3" s="188"/>
+      <c r="Q3" s="188"/>
+      <c r="R3" s="244" t="s">
         <v>220</v>
       </c>
-      <c r="S3" s="185" t="s">
+      <c r="S3" s="187" t="s">
         <v>221</v>
       </c>
-      <c r="T3" s="186"/>
-      <c r="U3" s="186"/>
-      <c r="V3" s="186"/>
-      <c r="W3" s="236" t="s">
+      <c r="T3" s="188"/>
+      <c r="U3" s="188"/>
+      <c r="V3" s="188"/>
+      <c r="W3" s="244" t="s">
         <v>220</v>
       </c>
-      <c r="X3" s="198" t="s">
+      <c r="X3" s="190" t="s">
         <v>41</v>
       </c>
-      <c r="Y3" s="199"/>
-      <c r="Z3" s="199"/>
-      <c r="AA3" s="236" t="s">
+      <c r="Y3" s="191"/>
+      <c r="Z3" s="191"/>
+      <c r="AA3" s="244" t="s">
         <v>220</v>
       </c>
       <c r="AB3" s="65"/>
-      <c r="AC3" s="185" t="s">
+      <c r="AC3" s="187" t="s">
         <v>42</v>
       </c>
-      <c r="AD3" s="186"/>
-      <c r="AE3" s="186"/>
-      <c r="AF3" s="186"/>
-      <c r="AG3" s="185" t="s">
+      <c r="AD3" s="188"/>
+      <c r="AE3" s="188"/>
+      <c r="AF3" s="188"/>
+      <c r="AG3" s="187" t="s">
         <v>43</v>
       </c>
-      <c r="AH3" s="186"/>
-      <c r="AI3" s="186"/>
-      <c r="AJ3" s="186"/>
-      <c r="AK3" s="185" t="s">
+      <c r="AH3" s="188"/>
+      <c r="AI3" s="188"/>
+      <c r="AJ3" s="188"/>
+      <c r="AK3" s="187" t="s">
         <v>44</v>
       </c>
-      <c r="AL3" s="186"/>
-      <c r="AM3" s="186"/>
-      <c r="AN3" s="186"/>
-      <c r="AO3" s="185" t="s">
+      <c r="AL3" s="188"/>
+      <c r="AM3" s="188"/>
+      <c r="AN3" s="188"/>
+      <c r="AO3" s="187" t="s">
         <v>46</v>
       </c>
-      <c r="AP3" s="186"/>
-      <c r="AQ3" s="186"/>
-      <c r="AR3" s="186"/>
-      <c r="AS3" s="185" t="s">
+      <c r="AP3" s="188"/>
+      <c r="AQ3" s="188"/>
+      <c r="AR3" s="188"/>
+      <c r="AS3" s="187" t="s">
         <v>47</v>
       </c>
-      <c r="AT3" s="186"/>
-      <c r="AU3" s="186"/>
-      <c r="AV3" s="186"/>
+      <c r="AT3" s="188"/>
+      <c r="AU3" s="188"/>
+      <c r="AV3" s="188"/>
     </row>
     <row r="4" spans="1:48" ht="22.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="238"/>
-      <c r="B4" s="240"/>
+      <c r="A4" s="236"/>
+      <c r="B4" s="238"/>
       <c r="C4" s="24">
         <f t="shared" ref="C4:K4" si="0">SUM(C5:C19)</f>
         <v>15</v>
@@ -25021,7 +25024,7 @@
         <f t="shared" si="0"/>
         <v>134</v>
       </c>
-      <c r="M4" s="243"/>
+      <c r="M4" s="241"/>
       <c r="N4" s="8" t="s">
         <v>2</v>
       </c>
@@ -25034,7 +25037,7 @@
       <c r="Q4" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="R4" s="237"/>
+      <c r="R4" s="245"/>
       <c r="S4" s="8" t="s">
         <v>2</v>
       </c>
@@ -25047,7 +25050,7 @@
       <c r="V4" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="W4" s="237"/>
+      <c r="W4" s="245"/>
       <c r="X4" s="8" t="s">
         <v>2</v>
       </c>
@@ -25057,7 +25060,7 @@
       <c r="Z4" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="AA4" s="237"/>
+      <c r="AA4" s="245"/>
       <c r="AB4" s="45" t="s">
         <v>59</v>
       </c>
@@ -27446,12 +27449,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="A1:K2"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="N3:Q3"/>
-    <mergeCell ref="M1:Z2"/>
     <mergeCell ref="AS3:AV3"/>
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="W3:W4"/>
@@ -27462,6 +27459,12 @@
     <mergeCell ref="AK3:AN3"/>
     <mergeCell ref="AO3:AR3"/>
     <mergeCell ref="S3:V3"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="A1:K2"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="N3:Q3"/>
+    <mergeCell ref="M1:Z2"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="P5:P20">
@@ -27601,44 +27604,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="248"/>
-      <c r="B1" s="248"/>
-      <c r="C1" s="248"/>
-      <c r="D1" s="248"/>
-      <c r="E1" s="248"/>
-      <c r="F1" s="248"/>
-      <c r="G1" s="248"/>
-      <c r="H1" s="248"/>
-      <c r="I1" s="248"/>
-      <c r="J1" s="248"/>
-      <c r="K1" s="248"/>
-      <c r="L1" s="248"/>
-      <c r="M1" s="248"/>
-      <c r="N1" s="248"/>
-      <c r="O1" s="248"/>
-      <c r="P1" s="248"/>
+      <c r="A1" s="246"/>
+      <c r="B1" s="246"/>
+      <c r="C1" s="246"/>
+      <c r="D1" s="246"/>
+      <c r="E1" s="246"/>
+      <c r="F1" s="246"/>
+      <c r="G1" s="246"/>
+      <c r="H1" s="246"/>
+      <c r="I1" s="246"/>
+      <c r="J1" s="246"/>
+      <c r="K1" s="246"/>
+      <c r="L1" s="246"/>
+      <c r="M1" s="246"/>
+      <c r="N1" s="246"/>
+      <c r="O1" s="246"/>
+      <c r="P1" s="246"/>
     </row>
     <row r="2" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="249"/>
-      <c r="B2" s="249"/>
-      <c r="C2" s="249"/>
-      <c r="D2" s="249"/>
-      <c r="E2" s="249"/>
-      <c r="F2" s="249"/>
-      <c r="G2" s="249"/>
-      <c r="H2" s="249"/>
-      <c r="I2" s="249"/>
-      <c r="J2" s="249"/>
-      <c r="K2" s="249"/>
-      <c r="L2" s="249"/>
-      <c r="M2" s="249"/>
-      <c r="N2" s="249"/>
-      <c r="O2" s="249"/>
-      <c r="P2" s="249"/>
+      <c r="A2" s="247"/>
+      <c r="B2" s="247"/>
+      <c r="C2" s="247"/>
+      <c r="D2" s="247"/>
+      <c r="E2" s="247"/>
+      <c r="F2" s="247"/>
+      <c r="G2" s="247"/>
+      <c r="H2" s="247"/>
+      <c r="I2" s="247"/>
+      <c r="J2" s="247"/>
+      <c r="K2" s="247"/>
+      <c r="L2" s="247"/>
+      <c r="M2" s="247"/>
+      <c r="N2" s="247"/>
+      <c r="O2" s="247"/>
+      <c r="P2" s="247"/>
     </row>
     <row r="3" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="250"/>
-      <c r="B3" s="250"/>
+      <c r="A3" s="248"/>
+      <c r="B3" s="248"/>
       <c r="C3" s="116"/>
       <c r="D3" s="116"/>
       <c r="E3" s="116"/>
@@ -27655,10 +27658,10 @@
       <c r="P3" s="116"/>
     </row>
     <row r="4" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="252" t="s">
+      <c r="A4" s="250" t="s">
         <v>224</v>
       </c>
-      <c r="B4" s="252" t="s">
+      <c r="B4" s="250" t="s">
         <v>39</v>
       </c>
       <c r="C4" s="124"/>
@@ -27666,70 +27669,70 @@
       <c r="E4" s="124"/>
       <c r="F4" s="124"/>
       <c r="G4" s="124"/>
-      <c r="H4" s="251"/>
-      <c r="I4" s="251"/>
-      <c r="J4" s="251"/>
-      <c r="K4" s="251"/>
-      <c r="L4" s="251"/>
-      <c r="M4" s="251"/>
-      <c r="N4" s="251"/>
-      <c r="O4" s="251"/>
-      <c r="P4" s="251"/>
+      <c r="H4" s="249"/>
+      <c r="I4" s="249"/>
+      <c r="J4" s="249"/>
+      <c r="K4" s="249"/>
+      <c r="L4" s="249"/>
+      <c r="M4" s="249"/>
+      <c r="N4" s="249"/>
+      <c r="O4" s="249"/>
+      <c r="P4" s="249"/>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A5" s="255"/>
-      <c r="B5" s="255"/>
-      <c r="C5" s="252" t="s">
+      <c r="A5" s="253"/>
+      <c r="B5" s="253"/>
+      <c r="C5" s="250" t="s">
         <v>225</v>
       </c>
-      <c r="D5" s="252" t="s">
+      <c r="D5" s="250" t="s">
         <v>226</v>
       </c>
-      <c r="E5" s="253"/>
-      <c r="F5" s="252" t="s">
+      <c r="E5" s="251"/>
+      <c r="F5" s="250" t="s">
         <v>227</v>
       </c>
-      <c r="G5" s="253"/>
-      <c r="H5" s="252" t="s">
+      <c r="G5" s="251"/>
+      <c r="H5" s="250" t="s">
         <v>228</v>
       </c>
-      <c r="I5" s="253"/>
-      <c r="J5" s="252" t="s">
+      <c r="I5" s="251"/>
+      <c r="J5" s="250" t="s">
         <v>229</v>
       </c>
-      <c r="K5" s="253"/>
-      <c r="L5" s="256" t="s">
+      <c r="K5" s="251"/>
+      <c r="L5" s="254" t="s">
         <v>230</v>
       </c>
-      <c r="M5" s="253"/>
-      <c r="N5" s="251" t="s">
+      <c r="M5" s="251"/>
+      <c r="N5" s="249" t="s">
         <v>231</v>
       </c>
-      <c r="O5" s="257"/>
-      <c r="P5" s="252" t="s">
+      <c r="O5" s="255"/>
+      <c r="P5" s="250" t="s">
         <v>235</v>
       </c>
-      <c r="R5" s="246" t="s">
+      <c r="R5" s="256" t="s">
         <v>34</v>
       </c>
-      <c r="S5" s="246" t="s">
+      <c r="S5" s="256" t="s">
         <v>258</v>
       </c>
-      <c r="T5" s="246" t="s">
+      <c r="T5" s="256" t="s">
         <v>259</v>
       </c>
-      <c r="U5" s="246" t="s">
+      <c r="U5" s="256" t="s">
         <v>261</v>
       </c>
-      <c r="V5" s="247" t="s">
+      <c r="V5" s="257" t="s">
         <v>260</v>
       </c>
       <c r="W5" s="155"/>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A6" s="254"/>
-      <c r="B6" s="254"/>
-      <c r="C6" s="255"/>
+      <c r="A6" s="252"/>
+      <c r="B6" s="252"/>
+      <c r="C6" s="253"/>
       <c r="D6" s="117" t="s">
         <v>2</v>
       </c>
@@ -27766,12 +27769,12 @@
       <c r="O6" s="117" t="s">
         <v>232</v>
       </c>
-      <c r="P6" s="254"/>
-      <c r="R6" s="246"/>
-      <c r="S6" s="246"/>
-      <c r="T6" s="246"/>
-      <c r="U6" s="246"/>
-      <c r="V6" s="246"/>
+      <c r="P6" s="252"/>
+      <c r="R6" s="256"/>
+      <c r="S6" s="256"/>
+      <c r="T6" s="256"/>
+      <c r="U6" s="256"/>
+      <c r="V6" s="256"/>
       <c r="W6" s="155"/>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.45">
@@ -27779,16 +27782,16 @@
         <v>179</v>
       </c>
       <c r="B7" s="173" t="s">
-        <v>68</v>
+        <v>101</v>
       </c>
       <c r="C7" s="173" t="s">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="D7" s="174">
-        <v>434</v>
+        <v>454</v>
       </c>
       <c r="E7" s="174">
-        <v>72573808</v>
+        <v>70243418</v>
       </c>
       <c r="F7" s="174">
         <v>0</v>
@@ -27797,32 +27800,32 @@
         <v>0</v>
       </c>
       <c r="H7" s="174">
-        <v>434</v>
+        <v>454</v>
       </c>
       <c r="I7" s="174">
-        <v>72573808</v>
+        <v>70243418</v>
       </c>
       <c r="J7" s="174">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K7" s="174">
-        <v>0</v>
+        <v>1728961</v>
       </c>
       <c r="L7" s="174">
-        <v>410</v>
+        <v>435</v>
       </c>
       <c r="M7" s="174">
-        <v>69152648</v>
+        <v>67097501</v>
       </c>
       <c r="N7" s="175">
-        <v>94.47</v>
+        <v>95.81</v>
       </c>
       <c r="O7" s="175">
-        <v>95.29</v>
+        <v>95.52</v>
       </c>
       <c r="P7" s="118">
         <f>I7*0.97-M7</f>
-        <v>1243945.7600000054</v>
+        <v>1038614.4599999934</v>
       </c>
       <c r="R7" s="156" t="s">
         <v>117</v>
@@ -27836,11 +27839,11 @@
       </c>
       <c r="U7" s="172">
         <f>VLOOKUP(R7,$C$7:$P$27,14,0)</f>
-        <v>7421615.799999997</v>
+        <v>3706834.799999997</v>
       </c>
       <c r="V7" s="158">
         <f>VLOOKUP(R7,$C$7:$P$27,14,0)-T7</f>
-        <v>-409000</v>
+        <v>-4123781</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.45">
@@ -27848,16 +27851,16 @@
         <v>179</v>
       </c>
       <c r="B8" s="176" t="s">
-        <v>101</v>
+        <v>68</v>
       </c>
       <c r="C8" s="176" t="s">
-        <v>102</v>
+        <v>69</v>
       </c>
       <c r="D8" s="177">
-        <v>454</v>
+        <v>434</v>
       </c>
       <c r="E8" s="177">
-        <v>70243418</v>
+        <v>72573808</v>
       </c>
       <c r="F8" s="177">
         <v>0</v>
@@ -27866,32 +27869,32 @@
         <v>0</v>
       </c>
       <c r="H8" s="177">
-        <v>454</v>
+        <v>434</v>
       </c>
       <c r="I8" s="177">
-        <v>70243418</v>
+        <v>72573808</v>
       </c>
       <c r="J8" s="177">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" s="177">
-        <v>250985</v>
+        <v>120000</v>
       </c>
       <c r="L8" s="177">
-        <v>423</v>
+        <v>410</v>
       </c>
       <c r="M8" s="177">
-        <v>65619525</v>
+        <v>69272648</v>
       </c>
       <c r="N8" s="178">
-        <v>93.17</v>
+        <v>94.47</v>
       </c>
       <c r="O8" s="178">
-        <v>93.42</v>
+        <v>95.45</v>
       </c>
       <c r="P8" s="118">
         <f t="shared" ref="P8:P27" si="0">I8*0.97-M8</f>
-        <v>2516590.4599999934</v>
+        <v>1123945.7600000054</v>
       </c>
       <c r="R8" s="156" t="s">
         <v>67</v>
@@ -27905,28 +27908,28 @@
       </c>
       <c r="U8" s="172">
         <f t="shared" ref="U8:U17" si="2">VLOOKUP(R8,$C$7:$P$27,14,0)</f>
-        <v>8366106.3100000024</v>
+        <v>4287894.3100000024</v>
       </c>
       <c r="V8" s="158">
         <f t="shared" ref="V8:V17" si="3">VLOOKUP(R8,$C$7:$P$27,14,0)-T8</f>
-        <v>-1231251</v>
+        <v>-5309463</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A9" s="173" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B9" s="173" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="C9" s="173" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="D9" s="174">
-        <v>687</v>
+        <v>588</v>
       </c>
       <c r="E9" s="174">
-        <v>105953075</v>
+        <v>95369711</v>
       </c>
       <c r="F9" s="174">
         <v>0</v>
@@ -27935,32 +27938,32 @@
         <v>0</v>
       </c>
       <c r="H9" s="174">
-        <v>687</v>
+        <v>588</v>
       </c>
       <c r="I9" s="174">
-        <v>105953075</v>
+        <v>95369711</v>
       </c>
       <c r="J9" s="174">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="K9" s="174">
-        <v>155806</v>
+        <v>4570318</v>
       </c>
       <c r="L9" s="174">
-        <v>622</v>
+        <v>554</v>
       </c>
       <c r="M9" s="174">
-        <v>98927875</v>
+        <v>90770801</v>
       </c>
       <c r="N9" s="175">
-        <v>90.54</v>
+        <v>94.22</v>
       </c>
       <c r="O9" s="175">
-        <v>93.37</v>
+        <v>95.18</v>
       </c>
       <c r="P9" s="118">
         <f t="shared" si="0"/>
-        <v>3846607.75</v>
+        <v>1737818.6700000018</v>
       </c>
       <c r="R9" s="157" t="s">
         <v>87</v>
@@ -27974,28 +27977,28 @@
       </c>
       <c r="U9" s="172">
         <f t="shared" si="2"/>
-        <v>7604285.2700000107</v>
+        <v>4376027.2700000107</v>
       </c>
       <c r="V9" s="158">
         <f t="shared" si="3"/>
-        <v>-180000</v>
+        <v>-3408258</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A10" s="176" t="s">
-        <v>179</v>
+        <v>128</v>
       </c>
       <c r="B10" s="176" t="s">
-        <v>257</v>
+        <v>98</v>
       </c>
       <c r="C10" s="176" t="s">
-        <v>253</v>
+        <v>99</v>
       </c>
       <c r="D10" s="177">
-        <v>318</v>
+        <v>687</v>
       </c>
       <c r="E10" s="177">
-        <v>50351985</v>
+        <v>105953075</v>
       </c>
       <c r="F10" s="177">
         <v>0</v>
@@ -28004,32 +28007,32 @@
         <v>0</v>
       </c>
       <c r="H10" s="177">
-        <v>318</v>
+        <v>687</v>
       </c>
       <c r="I10" s="177">
-        <v>50351985</v>
+        <v>105953075</v>
       </c>
       <c r="J10" s="177">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="K10" s="177">
-        <v>180000</v>
+        <v>1716274</v>
       </c>
       <c r="L10" s="177">
-        <v>284</v>
+        <v>636</v>
       </c>
       <c r="M10" s="177">
-        <v>46289562</v>
+        <v>100488343</v>
       </c>
       <c r="N10" s="178">
-        <v>89.31</v>
+        <v>92.58</v>
       </c>
       <c r="O10" s="178">
-        <v>91.93</v>
+        <v>94.84</v>
       </c>
       <c r="P10" s="118">
         <f t="shared" si="0"/>
-        <v>2551863.4499999955</v>
+        <v>2286139.75</v>
       </c>
       <c r="R10" s="157" t="s">
         <v>110</v>
@@ -28043,28 +28046,28 @@
       </c>
       <c r="U10" s="172">
         <f t="shared" si="2"/>
-        <v>11953574.859999985</v>
+        <v>6772490.8599999845</v>
       </c>
       <c r="V10" s="158">
         <f t="shared" si="3"/>
-        <v>-3375246</v>
+        <v>-8556330</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A11" s="173" t="s">
-        <v>179</v>
+        <v>128</v>
       </c>
       <c r="B11" s="173" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="C11" s="173" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="D11" s="174">
-        <v>546</v>
+        <v>876</v>
       </c>
       <c r="E11" s="174">
-        <v>89879995</v>
+        <v>145101823</v>
       </c>
       <c r="F11" s="174">
         <v>0</v>
@@ -28073,32 +28076,32 @@
         <v>0</v>
       </c>
       <c r="H11" s="174">
-        <v>546</v>
+        <v>876</v>
       </c>
       <c r="I11" s="174">
-        <v>89879995</v>
+        <v>145101823</v>
       </c>
       <c r="J11" s="174">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="K11" s="174">
-        <v>1671526</v>
+        <v>5309463</v>
       </c>
       <c r="L11" s="174">
-        <v>482</v>
+        <v>811</v>
       </c>
       <c r="M11" s="174">
-        <v>82571363</v>
+        <v>136460874</v>
       </c>
       <c r="N11" s="175">
-        <v>88.28</v>
+        <v>92.58</v>
       </c>
       <c r="O11" s="175">
-        <v>91.87</v>
+        <v>94.04</v>
       </c>
       <c r="P11" s="118">
         <f t="shared" si="0"/>
-        <v>4612232.1499999911</v>
+        <v>4287894.3100000024</v>
       </c>
       <c r="R11" s="156" t="s">
         <v>99</v>
@@ -28112,11 +28115,11 @@
       </c>
       <c r="U11" s="172">
         <f t="shared" si="2"/>
-        <v>3846607.75</v>
+        <v>2286139.75</v>
       </c>
       <c r="V11" s="158">
         <f t="shared" si="3"/>
-        <v>-155806</v>
+        <v>-1716274</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.45">
@@ -28148,26 +28151,26 @@
         <v>141474291</v>
       </c>
       <c r="J12" s="177">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="K12" s="177">
-        <v>375000</v>
+        <v>3603258</v>
       </c>
       <c r="L12" s="177">
-        <v>770</v>
+        <v>789</v>
       </c>
       <c r="M12" s="177">
-        <v>129625777</v>
+        <v>132854035</v>
       </c>
       <c r="N12" s="178">
-        <v>90.27</v>
+        <v>92.5</v>
       </c>
       <c r="O12" s="178">
-        <v>91.62</v>
+        <v>93.91</v>
       </c>
       <c r="P12" s="118">
         <f t="shared" si="0"/>
-        <v>7604285.2700000107</v>
+        <v>4376027.2700000107</v>
       </c>
       <c r="R12" s="156" t="s">
         <v>75</v>
@@ -28181,28 +28184,28 @@
       </c>
       <c r="U12" s="172">
         <f t="shared" si="2"/>
-        <v>9882393.5200000107</v>
+        <v>4961782.5200000107</v>
       </c>
       <c r="V12" s="158">
         <f t="shared" si="3"/>
-        <v>-438011</v>
+        <v>-5358622</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A13" s="173" t="s">
-        <v>179</v>
+        <v>129</v>
       </c>
       <c r="B13" s="173" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C13" s="173" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D13" s="174">
-        <v>559</v>
+        <v>1181</v>
       </c>
       <c r="E13" s="174">
-        <v>93597302</v>
+        <v>189656153</v>
       </c>
       <c r="F13" s="174">
         <v>0</v>
@@ -28211,32 +28214,32 @@
         <v>0</v>
       </c>
       <c r="H13" s="174">
-        <v>559</v>
+        <v>1181</v>
       </c>
       <c r="I13" s="174">
-        <v>93597302</v>
+        <v>189656153</v>
       </c>
       <c r="J13" s="174">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="K13" s="174">
-        <v>460500</v>
+        <v>7519518</v>
       </c>
       <c r="L13" s="174">
-        <v>502</v>
+        <v>1085</v>
       </c>
       <c r="M13" s="174">
-        <v>85539859</v>
+        <v>177848327</v>
       </c>
       <c r="N13" s="175">
-        <v>89.8</v>
+        <v>91.87</v>
       </c>
       <c r="O13" s="175">
-        <v>91.39</v>
+        <v>93.77</v>
       </c>
       <c r="P13" s="118">
         <f t="shared" si="0"/>
-        <v>5249523.9399999976</v>
+        <v>6118141.4099999964</v>
       </c>
       <c r="R13" s="156" t="s">
         <v>107</v>
@@ -28250,11 +28253,11 @@
       </c>
       <c r="U13" s="172">
         <f t="shared" si="2"/>
-        <v>11847250.590000004</v>
+        <v>8587701.5900000036</v>
       </c>
       <c r="V13" s="158">
         <f t="shared" si="3"/>
-        <v>-360000</v>
+        <v>-3619549</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.45">
@@ -28262,16 +28265,16 @@
         <v>129</v>
       </c>
       <c r="B14" s="176" t="s">
-        <v>118</v>
+        <v>74</v>
       </c>
       <c r="C14" s="176" t="s">
-        <v>119</v>
+        <v>75</v>
       </c>
       <c r="D14" s="177">
-        <v>1181</v>
+        <v>941</v>
       </c>
       <c r="E14" s="177">
-        <v>189656153</v>
+        <v>152862316</v>
       </c>
       <c r="F14" s="177">
         <v>0</v>
@@ -28280,32 +28283,32 @@
         <v>0</v>
       </c>
       <c r="H14" s="177">
-        <v>1181</v>
+        <v>941</v>
       </c>
       <c r="I14" s="177">
-        <v>189656153</v>
+        <v>152862316</v>
       </c>
       <c r="J14" s="177">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="K14" s="177">
-        <v>2889271</v>
+        <v>5358622</v>
       </c>
       <c r="L14" s="177">
-        <v>1056</v>
+        <v>851</v>
       </c>
       <c r="M14" s="177">
-        <v>173218080</v>
+        <v>143314664</v>
       </c>
       <c r="N14" s="178">
-        <v>89.42</v>
+        <v>90.44</v>
       </c>
       <c r="O14" s="178">
-        <v>91.33</v>
+        <v>93.75</v>
       </c>
       <c r="P14" s="118">
         <f t="shared" si="0"/>
-        <v>10748388.409999996</v>
+        <v>4961782.5200000107</v>
       </c>
       <c r="R14" s="157" t="s">
         <v>72</v>
@@ -28319,28 +28322,28 @@
       </c>
       <c r="U14" s="172">
         <f t="shared" si="2"/>
-        <v>16644698.199999988</v>
+        <v>9976148.1999999881</v>
       </c>
       <c r="V14" s="158">
         <f t="shared" si="3"/>
-        <v>-429524</v>
+        <v>-7098074</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A15" s="173" t="s">
-        <v>128</v>
+        <v>179</v>
       </c>
       <c r="B15" s="173" t="s">
-        <v>66</v>
+        <v>257</v>
       </c>
       <c r="C15" s="173" t="s">
-        <v>67</v>
+        <v>253</v>
       </c>
       <c r="D15" s="174">
-        <v>876</v>
+        <v>318</v>
       </c>
       <c r="E15" s="174">
-        <v>145101823</v>
+        <v>50351985</v>
       </c>
       <c r="F15" s="174">
         <v>0</v>
@@ -28349,32 +28352,32 @@
         <v>0</v>
       </c>
       <c r="H15" s="174">
-        <v>876</v>
+        <v>318</v>
       </c>
       <c r="I15" s="174">
-        <v>145101823</v>
+        <v>50351985</v>
       </c>
       <c r="J15" s="174">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K15" s="174">
-        <v>1231251</v>
+        <v>1059908</v>
       </c>
       <c r="L15" s="174">
-        <v>791</v>
+        <v>291</v>
       </c>
       <c r="M15" s="174">
-        <v>132382662</v>
+        <v>47169470</v>
       </c>
       <c r="N15" s="175">
-        <v>90.3</v>
+        <v>91.51</v>
       </c>
       <c r="O15" s="175">
-        <v>91.23</v>
+        <v>93.68</v>
       </c>
       <c r="P15" s="118">
         <f t="shared" si="0"/>
-        <v>8366106.3100000024</v>
+        <v>1671955.4499999955</v>
       </c>
       <c r="R15" s="157" t="s">
         <v>113</v>
@@ -28388,28 +28391,28 @@
       </c>
       <c r="U15" s="172">
         <f t="shared" si="2"/>
-        <v>20212240.400000006</v>
+        <v>12578665.400000006</v>
       </c>
       <c r="V15" s="158">
         <f t="shared" si="3"/>
-        <v>-1535903</v>
+        <v>-9169478</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A16" s="176" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B16" s="176" t="s">
-        <v>83</v>
+        <v>116</v>
       </c>
       <c r="C16" s="176" t="s">
-        <v>84</v>
+        <v>117</v>
       </c>
       <c r="D16" s="177">
-        <v>588</v>
+        <v>642</v>
       </c>
       <c r="E16" s="177">
-        <v>95369711</v>
+        <v>101866340</v>
       </c>
       <c r="F16" s="177">
         <v>0</v>
@@ -28418,32 +28421,32 @@
         <v>0</v>
       </c>
       <c r="H16" s="177">
-        <v>588</v>
+        <v>642</v>
       </c>
       <c r="I16" s="177">
-        <v>95369711</v>
+        <v>101866340</v>
       </c>
       <c r="J16" s="177">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="K16" s="177">
-        <v>613334</v>
+        <v>4123781</v>
       </c>
       <c r="L16" s="177">
-        <v>528</v>
+        <v>587</v>
       </c>
       <c r="M16" s="177">
-        <v>86813817</v>
+        <v>95103515</v>
       </c>
       <c r="N16" s="178">
-        <v>89.8</v>
+        <v>91.43</v>
       </c>
       <c r="O16" s="178">
-        <v>91.03</v>
+        <v>93.36</v>
       </c>
       <c r="P16" s="118">
         <f t="shared" si="0"/>
-        <v>5694802.6700000018</v>
+        <v>3706834.799999997</v>
       </c>
       <c r="R16" s="157" t="s">
         <v>119</v>
@@ -28457,11 +28460,11 @@
       </c>
       <c r="U16" s="172">
         <f t="shared" si="2"/>
-        <v>10748388.409999996</v>
+        <v>6118141.4099999964</v>
       </c>
       <c r="V16" s="158">
         <f t="shared" si="3"/>
-        <v>-1353625</v>
+        <v>-5983872</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.45">
@@ -28469,16 +28472,16 @@
         <v>179</v>
       </c>
       <c r="B17" s="173" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="C17" s="173" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="D17" s="174">
-        <v>356</v>
+        <v>559</v>
       </c>
       <c r="E17" s="174">
-        <v>53605661</v>
+        <v>93597302</v>
       </c>
       <c r="F17" s="174">
         <v>0</v>
@@ -28487,32 +28490,32 @@
         <v>0</v>
       </c>
       <c r="H17" s="174">
-        <v>356</v>
+        <v>559</v>
       </c>
       <c r="I17" s="174">
-        <v>53605661</v>
+        <v>93597302</v>
       </c>
       <c r="J17" s="174">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K17" s="174">
-        <v>0</v>
+        <v>2255451</v>
       </c>
       <c r="L17" s="174">
-        <v>307</v>
+        <v>511</v>
       </c>
       <c r="M17" s="174">
-        <v>48663936</v>
+        <v>87334810</v>
       </c>
       <c r="N17" s="175">
-        <v>86.24</v>
+        <v>91.41</v>
       </c>
       <c r="O17" s="175">
-        <v>90.78</v>
+        <v>93.31</v>
       </c>
       <c r="P17" s="118">
         <f t="shared" si="0"/>
-        <v>3333555.1700000018</v>
+        <v>3454572.9399999976</v>
       </c>
       <c r="R17" s="156" t="s">
         <v>84</v>
@@ -28526,11 +28529,11 @@
       </c>
       <c r="U17" s="172">
         <f t="shared" si="2"/>
-        <v>5694802.6700000018</v>
+        <v>1737818.6700000018</v>
       </c>
       <c r="V17" s="158">
         <f t="shared" si="3"/>
-        <v>-385000</v>
+        <v>-4341984</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.45">
@@ -28562,43 +28565,43 @@
         <v>116427734</v>
       </c>
       <c r="J18" s="177">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="K18" s="177">
-        <v>521903</v>
+        <v>3185827</v>
       </c>
       <c r="L18" s="177">
-        <v>639</v>
+        <v>654</v>
       </c>
       <c r="M18" s="177">
-        <v>105648842</v>
+        <v>108312766</v>
       </c>
       <c r="N18" s="178">
-        <v>89.25</v>
+        <v>91.34</v>
       </c>
       <c r="O18" s="178">
-        <v>90.74</v>
+        <v>93.03</v>
       </c>
       <c r="P18" s="118">
         <f t="shared" si="0"/>
-        <v>7286059.9800000042</v>
+        <v>4622135.9800000042</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A19" s="173" t="s">
-        <v>129</v>
+        <v>179</v>
       </c>
       <c r="B19" s="173" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="C19" s="173" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="D19" s="174">
-        <v>941</v>
+        <v>356</v>
       </c>
       <c r="E19" s="174">
-        <v>152862316</v>
+        <v>53605661</v>
       </c>
       <c r="F19" s="174">
         <v>0</v>
@@ -28607,49 +28610,49 @@
         <v>0</v>
       </c>
       <c r="H19" s="174">
-        <v>941</v>
+        <v>356</v>
       </c>
       <c r="I19" s="174">
-        <v>152862316</v>
+        <v>53605661</v>
       </c>
       <c r="J19" s="174">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K19" s="174">
-        <v>438011</v>
+        <v>1116088</v>
       </c>
       <c r="L19" s="174">
-        <v>822</v>
+        <v>314</v>
       </c>
       <c r="M19" s="174">
-        <v>138394053</v>
+        <v>49780024</v>
       </c>
       <c r="N19" s="175">
-        <v>87.35</v>
+        <v>88.2</v>
       </c>
       <c r="O19" s="175">
-        <v>90.54</v>
+        <v>92.86</v>
       </c>
       <c r="P19" s="118">
         <f t="shared" si="0"/>
-        <v>9882393.5200000107</v>
+        <v>2217467.1700000018</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A20" s="176" t="s">
-        <v>129</v>
+        <v>179</v>
       </c>
       <c r="B20" s="176" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="C20" s="176" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="D20" s="177">
-        <v>1048</v>
+        <v>308</v>
       </c>
       <c r="E20" s="177">
-        <v>180440547</v>
+        <v>51982396</v>
       </c>
       <c r="F20" s="177">
         <v>0</v>
@@ -28658,49 +28661,49 @@
         <v>0</v>
       </c>
       <c r="H20" s="177">
-        <v>1048</v>
+        <v>308</v>
       </c>
       <c r="I20" s="177">
-        <v>180440547</v>
+        <v>51982396</v>
       </c>
       <c r="J20" s="177">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K20" s="177">
-        <v>815000</v>
+        <v>1322830</v>
       </c>
       <c r="L20" s="177">
-        <v>931</v>
+        <v>282</v>
       </c>
       <c r="M20" s="177">
-        <v>163180080</v>
+        <v>48198774</v>
       </c>
       <c r="N20" s="178">
-        <v>88.84</v>
+        <v>91.56</v>
       </c>
       <c r="O20" s="178">
-        <v>90.43</v>
+        <v>92.72</v>
       </c>
       <c r="P20" s="118">
         <f t="shared" si="0"/>
-        <v>11847250.590000004</v>
+        <v>2224150.1199999973</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A21" s="173" t="s">
-        <v>179</v>
+        <v>128</v>
       </c>
       <c r="B21" s="173" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="C21" s="173" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="D21" s="174">
-        <v>308</v>
+        <v>892</v>
       </c>
       <c r="E21" s="174">
-        <v>51982396</v>
+        <v>149379338</v>
       </c>
       <c r="F21" s="174">
         <v>0</v>
@@ -28709,49 +28712,49 @@
         <v>0</v>
       </c>
       <c r="H21" s="174">
-        <v>308</v>
+        <v>892</v>
       </c>
       <c r="I21" s="174">
-        <v>51982396</v>
+        <v>149379338</v>
       </c>
       <c r="J21" s="174">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="K21" s="174">
-        <v>0</v>
+        <v>9226019</v>
       </c>
       <c r="L21" s="174">
-        <v>274</v>
+        <v>822</v>
       </c>
       <c r="M21" s="174">
-        <v>46875944</v>
+        <v>138125467</v>
       </c>
       <c r="N21" s="175">
-        <v>88.96</v>
+        <v>92.15</v>
       </c>
       <c r="O21" s="175">
-        <v>90.18</v>
+        <v>92.47</v>
       </c>
       <c r="P21" s="118">
         <f t="shared" si="0"/>
-        <v>3546980.1199999973</v>
+        <v>6772490.8599999845</v>
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A22" s="176" t="s">
-        <v>128</v>
+        <v>179</v>
       </c>
       <c r="B22" s="176" t="s">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="C22" s="176" t="s">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="D22" s="177">
-        <v>642</v>
+        <v>546</v>
       </c>
       <c r="E22" s="177">
-        <v>101866340</v>
+        <v>89879995</v>
       </c>
       <c r="F22" s="177">
         <v>0</v>
@@ -28760,49 +28763,49 @@
         <v>0</v>
       </c>
       <c r="H22" s="177">
-        <v>642</v>
+        <v>546</v>
       </c>
       <c r="I22" s="177">
-        <v>101866340</v>
+        <v>89879995</v>
       </c>
       <c r="J22" s="177">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K22" s="177">
-        <v>409000</v>
+        <v>2014163</v>
       </c>
       <c r="L22" s="177">
-        <v>552</v>
+        <v>483</v>
       </c>
       <c r="M22" s="177">
-        <v>91388734</v>
+        <v>82914000</v>
       </c>
       <c r="N22" s="178">
-        <v>85.98</v>
+        <v>88.46</v>
       </c>
       <c r="O22" s="178">
-        <v>89.71</v>
+        <v>92.25</v>
       </c>
       <c r="P22" s="118">
         <f t="shared" si="0"/>
-        <v>7421615.799999997</v>
+        <v>4269595.1499999911</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A23" s="173" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B23" s="173" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C23" s="173" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D23" s="174">
-        <v>892</v>
+        <v>1048</v>
       </c>
       <c r="E23" s="174">
-        <v>149379338</v>
+        <v>180440547</v>
       </c>
       <c r="F23" s="174">
         <v>0</v>
@@ -28811,32 +28814,32 @@
         <v>0</v>
       </c>
       <c r="H23" s="174">
-        <v>892</v>
+        <v>1048</v>
       </c>
       <c r="I23" s="174">
-        <v>149379338</v>
+        <v>180440547</v>
       </c>
       <c r="J23" s="174">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K23" s="174">
-        <v>4044935</v>
+        <v>4074549</v>
       </c>
       <c r="L23" s="174">
-        <v>799</v>
+        <v>954</v>
       </c>
       <c r="M23" s="174">
-        <v>132944383</v>
+        <v>166439629</v>
       </c>
       <c r="N23" s="175">
-        <v>89.57</v>
+        <v>91.03</v>
       </c>
       <c r="O23" s="175">
-        <v>89</v>
+        <v>92.24</v>
       </c>
       <c r="P23" s="118">
         <f t="shared" si="0"/>
-        <v>11953574.859999985</v>
+        <v>8587701.5900000036</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.45">
@@ -28844,16 +28847,16 @@
         <v>129</v>
       </c>
       <c r="B24" s="176" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C24" s="176" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D24" s="177">
-        <v>683</v>
+        <v>968</v>
       </c>
       <c r="E24" s="177">
-        <v>105983346</v>
+        <v>162344260</v>
       </c>
       <c r="F24" s="177">
         <v>0</v>
@@ -28862,49 +28865,49 @@
         <v>0</v>
       </c>
       <c r="H24" s="177">
-        <v>683</v>
+        <v>968</v>
       </c>
       <c r="I24" s="177">
-        <v>105983346</v>
+        <v>162344260</v>
       </c>
       <c r="J24" s="177">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="K24" s="177">
-        <v>639000</v>
+        <v>7283074</v>
       </c>
       <c r="L24" s="177">
-        <v>596</v>
+        <v>872</v>
       </c>
       <c r="M24" s="177">
-        <v>93510148</v>
+        <v>147497784</v>
       </c>
       <c r="N24" s="178">
-        <v>87.26</v>
+        <v>90.08</v>
       </c>
       <c r="O24" s="178">
-        <v>88.23</v>
+        <v>90.85</v>
       </c>
       <c r="P24" s="118">
         <f t="shared" si="0"/>
-        <v>9293697.6199999899</v>
+        <v>9976148.1999999881</v>
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A25" s="173" t="s">
-        <v>179</v>
+        <v>129</v>
       </c>
       <c r="B25" s="173" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C25" s="173" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="D25" s="174">
-        <v>415</v>
+        <v>1198</v>
       </c>
       <c r="E25" s="174">
-        <v>66800107</v>
+        <v>194517020</v>
       </c>
       <c r="F25" s="174">
         <v>0</v>
@@ -28913,32 +28916,32 @@
         <v>0</v>
       </c>
       <c r="H25" s="174">
-        <v>415</v>
+        <v>1198</v>
       </c>
       <c r="I25" s="174">
-        <v>66800107</v>
+        <v>194517020</v>
       </c>
       <c r="J25" s="174">
-        <v>5</v>
+        <v>57</v>
       </c>
       <c r="K25" s="174">
-        <v>1049194</v>
+        <v>9958478</v>
       </c>
       <c r="L25" s="174">
-        <v>351</v>
+        <v>1049</v>
       </c>
       <c r="M25" s="174">
-        <v>57966491</v>
+        <v>176102844</v>
       </c>
       <c r="N25" s="175">
-        <v>84.58</v>
+        <v>87.56</v>
       </c>
       <c r="O25" s="175">
-        <v>86.78</v>
+        <v>90.53</v>
       </c>
       <c r="P25" s="118">
         <f t="shared" si="0"/>
-        <v>6829612.7899999991</v>
+        <v>12578665.400000006</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.45">
@@ -28946,16 +28949,16 @@
         <v>129</v>
       </c>
       <c r="B26" s="176" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C26" s="176" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D26" s="177">
-        <v>968</v>
+        <v>683</v>
       </c>
       <c r="E26" s="177">
-        <v>162344260</v>
+        <v>105983346</v>
       </c>
       <c r="F26" s="177">
         <v>0</v>
@@ -28964,49 +28967,49 @@
         <v>0</v>
       </c>
       <c r="H26" s="177">
-        <v>968</v>
+        <v>683</v>
       </c>
       <c r="I26" s="177">
-        <v>162344260</v>
+        <v>105983346</v>
       </c>
       <c r="J26" s="177">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="K26" s="177">
-        <v>614524</v>
+        <v>3000371</v>
       </c>
       <c r="L26" s="177">
-        <v>839</v>
+        <v>610</v>
       </c>
       <c r="M26" s="177">
-        <v>140829234</v>
+        <v>95871519</v>
       </c>
       <c r="N26" s="178">
-        <v>86.67</v>
+        <v>89.31</v>
       </c>
       <c r="O26" s="178">
-        <v>86.75</v>
+        <v>90.46</v>
       </c>
       <c r="P26" s="118">
         <f t="shared" si="0"/>
-        <v>16644698.199999988</v>
+        <v>6932326.6199999899</v>
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A27" s="173" t="s">
-        <v>129</v>
+        <v>179</v>
       </c>
       <c r="B27" s="173" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="C27" s="173" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="D27" s="174">
-        <v>1198</v>
+        <v>415</v>
       </c>
       <c r="E27" s="174">
-        <v>194517020</v>
+        <v>66800107</v>
       </c>
       <c r="F27" s="174">
         <v>0</v>
@@ -29015,36 +29018,44 @@
         <v>0</v>
       </c>
       <c r="H27" s="174">
-        <v>1198</v>
+        <v>415</v>
       </c>
       <c r="I27" s="174">
-        <v>194517020</v>
+        <v>66800107</v>
       </c>
       <c r="J27" s="174">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K27" s="174">
-        <v>2324903</v>
+        <v>2823201</v>
       </c>
       <c r="L27" s="174">
-        <v>1004</v>
+        <v>361</v>
       </c>
       <c r="M27" s="174">
-        <v>168469269</v>
+        <v>59740498</v>
       </c>
       <c r="N27" s="175">
-        <v>83.81</v>
+        <v>86.99</v>
       </c>
       <c r="O27" s="175">
-        <v>86.61</v>
+        <v>89.43</v>
       </c>
       <c r="P27" s="118">
         <f t="shared" si="0"/>
-        <v>20212240.400000006</v>
+        <v>5055605.7899999991</v>
+      </c>
+      <c r="R27" s="1" t="s">
+        <v>265</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="U5:U6"/>
+    <mergeCell ref="V5:V6"/>
+    <mergeCell ref="R5:R6"/>
+    <mergeCell ref="S5:S6"/>
+    <mergeCell ref="T5:T6"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
     <mergeCell ref="A3:B3"/>
@@ -29059,11 +29070,6 @@
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="L5:M5"/>
     <mergeCell ref="N5:O5"/>
-    <mergeCell ref="U5:U6"/>
-    <mergeCell ref="V5:V6"/>
-    <mergeCell ref="R5:R6"/>
-    <mergeCell ref="S5:S6"/>
-    <mergeCell ref="T5:T6"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="P7:P27">
